--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2113.57</v>
+        <v>2140.2</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -19855,11 +19855,11 @@
         </is>
       </c>
       <c r="E647" s="3" t="n">
-        <v>1363.14</v>
+        <v>1399</v>
       </c>
       <c r="F647" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>887.4299999999999</v>
+        <v>896.01</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -19931,12 +19931,12 @@
       </c>
       <c r="B650" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084602TKW</t>
+          <t>KIT4P0008460369B</t>
         </is>
       </c>
       <c r="C650" s="2" t="inlineStr">
         <is>
-          <t>816225</t>
+          <t>816224</t>
         </is>
       </c>
       <c r="D650" s="2" t="inlineStr">
@@ -19945,11 +19945,11 @@
         </is>
       </c>
       <c r="E650" s="3" t="n">
-        <v>771.66</v>
+        <v>779.38</v>
       </c>
       <c r="F650" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -19961,12 +19961,12 @@
       </c>
       <c r="B651" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008460369B</t>
+          <t>KIT4P00084602TKW</t>
         </is>
       </c>
       <c r="C651" s="2" t="inlineStr">
         <is>
-          <t>816224</t>
+          <t>816225</t>
         </is>
       </c>
       <c r="D651" s="2" t="inlineStr">
@@ -19975,7 +19975,7 @@
         </is>
       </c>
       <c r="E651" s="3" t="n">
-        <v>763.9</v>
+        <v>771.66</v>
       </c>
       <c r="F651" s="2" t="inlineStr">
         <is>
@@ -20005,11 +20005,11 @@
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>648.33</v>
+        <v>652.58</v>
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20065,11 +20065,11 @@
         </is>
       </c>
       <c r="E654" s="3" t="n">
-        <v>586.5599999999999</v>
+        <v>588.77</v>
       </c>
       <c r="F654" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20095,11 +20095,11 @@
         </is>
       </c>
       <c r="E655" s="3" t="n">
-        <v>583.7</v>
+        <v>585.03</v>
       </c>
       <c r="F655" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20125,11 +20125,11 @@
         </is>
       </c>
       <c r="E656" s="3" t="n">
-        <v>571.9299999999999</v>
+        <v>578.52</v>
       </c>
       <c r="F656" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20155,11 +20155,11 @@
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>518.22</v>
+        <v>519.2</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20215,11 +20215,11 @@
         </is>
       </c>
       <c r="E659" s="3" t="n">
-        <v>504.24</v>
+        <v>512.46</v>
       </c>
       <c r="F659" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20261,25 +20261,25 @@
       </c>
       <c r="B661" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C661" s="2" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="D661" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>480.85</v>
+        <v>482.26</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20291,21 +20291,21 @@
       </c>
       <c r="B662" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C662" s="2" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="D662" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E662" s="3" t="n">
-        <v>477.6</v>
+        <v>480.85</v>
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
@@ -20335,11 +20335,11 @@
         </is>
       </c>
       <c r="E663" s="3" t="n">
-        <v>475.84</v>
+        <v>478.98</v>
       </c>
       <c r="F663" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20395,11 +20395,11 @@
         </is>
       </c>
       <c r="E665" s="3" t="n">
-        <v>450.49</v>
+        <v>453.29</v>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20411,25 +20411,25 @@
       </c>
       <c r="B666" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4P000739257CR</t>
         </is>
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>814609</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>430.3</v>
+        <v>439.55</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20441,25 +20441,25 @@
       </c>
       <c r="B667" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065631CPZ</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C667" s="2" t="inlineStr">
         <is>
-          <t>812930</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="D667" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E667" s="3" t="n">
-        <v>415.73</v>
+        <v>431.51</v>
       </c>
       <c r="F667" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20485,11 +20485,11 @@
         </is>
       </c>
       <c r="E668" s="3" t="n">
-        <v>411.34</v>
+        <v>420.1</v>
       </c>
       <c r="F668" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20501,12 +20501,12 @@
       </c>
       <c r="B669" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739257CR</t>
+          <t>KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="C669" s="2" t="inlineStr">
         <is>
-          <t>814609</t>
+          <t>812930</t>
         </is>
       </c>
       <c r="D669" s="2" t="inlineStr">
@@ -20515,7 +20515,7 @@
         </is>
       </c>
       <c r="E669" s="3" t="n">
-        <v>410.41</v>
+        <v>415.73</v>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
@@ -20545,11 +20545,11 @@
         </is>
       </c>
       <c r="E670" s="3" t="n">
-        <v>409.72</v>
+        <v>411.97</v>
       </c>
       <c r="F670" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20605,11 +20605,11 @@
         </is>
       </c>
       <c r="E672" s="3" t="n">
-        <v>349.13</v>
+        <v>354.56</v>
       </c>
       <c r="F672" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20665,11 +20665,11 @@
         </is>
       </c>
       <c r="E674" s="3" t="n">
-        <v>313.77</v>
+        <v>315.63</v>
       </c>
       <c r="F674" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20695,11 +20695,11 @@
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>301.23</v>
+        <v>309.31</v>
       </c>
       <c r="F675" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20725,11 +20725,11 @@
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>299.95</v>
+        <v>300.33</v>
       </c>
       <c r="F676" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20755,11 +20755,11 @@
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>298.74</v>
+        <v>299.36</v>
       </c>
       <c r="F677" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20801,25 +20801,25 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563510TWC</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
         <is>
-          <t>814433</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="D679" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>267.37</v>
+        <v>269.41</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>267.29</v>
+        <v>267.43</v>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20861,12 +20861,12 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="D681" s="2" t="inlineStr">
@@ -20875,7 +20875,7 @@
         </is>
       </c>
       <c r="E681" s="3" t="n">
-        <v>258.41</v>
+        <v>267.37</v>
       </c>
       <c r="F681" s="2" t="inlineStr">
         <is>
@@ -20891,12 +20891,12 @@
       </c>
       <c r="B682" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C682" s="2" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="D682" s="2" t="inlineStr">
@@ -20905,11 +20905,11 @@
         </is>
       </c>
       <c r="E682" s="3" t="n">
-        <v>256.73</v>
+        <v>259.45</v>
       </c>
       <c r="F682" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -20921,25 +20921,25 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="D683" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E683" s="3" t="n">
-        <v>251.47</v>
+        <v>257.48</v>
       </c>
       <c r="F683" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21055,11 +21055,11 @@
         </is>
       </c>
       <c r="E687" s="3" t="n">
-        <v>199.31</v>
+        <v>201.84</v>
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21071,12 +21071,12 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="D688" s="2" t="inlineStr">
@@ -21085,11 +21085,11 @@
         </is>
       </c>
       <c r="E688" s="3" t="n">
-        <v>198.88</v>
+        <v>201.2</v>
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21101,12 +21101,12 @@
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="D689" s="2" t="inlineStr">
@@ -21115,11 +21115,11 @@
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>197.74</v>
+        <v>199.59</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21145,11 +21145,11 @@
         </is>
       </c>
       <c r="E690" s="3" t="n">
-        <v>188.74</v>
+        <v>193.33</v>
       </c>
       <c r="F690" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21175,11 +21175,11 @@
         </is>
       </c>
       <c r="E691" s="3" t="n">
-        <v>182.69</v>
+        <v>183.72</v>
       </c>
       <c r="F691" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21221,12 +21221,12 @@
       </c>
       <c r="B693" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="C693" s="2" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="D693" s="2" t="inlineStr">
@@ -21235,11 +21235,11 @@
         </is>
       </c>
       <c r="E693" s="3" t="n">
-        <v>174.58</v>
+        <v>178.13</v>
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="B694" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C694" s="2" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="D694" s="2" t="inlineStr">
@@ -21265,11 +21265,11 @@
         </is>
       </c>
       <c r="E694" s="3" t="n">
-        <v>174.02</v>
+        <v>176.64</v>
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>170.1</v>
+        <v>171.09</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21341,12 +21341,12 @@
       </c>
       <c r="B697" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C697" s="2" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="D697" s="2" t="inlineStr">
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>146.99</v>
+        <v>151.02</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21371,12 +21371,12 @@
       </c>
       <c r="B698" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C698" s="2" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="D698" s="2" t="inlineStr">
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="E698" s="3" t="n">
-        <v>145.5</v>
+        <v>147.1</v>
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>143.61</v>
+        <v>145.79</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21445,11 +21445,11 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>139.82</v>
+        <v>140.79</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21461,12 +21461,12 @@
       </c>
       <c r="B701" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C701" s="2" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="D701" s="2" t="inlineStr">
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>132.39</v>
+        <v>137.09</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21491,12 +21491,12 @@
       </c>
       <c r="B702" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C702" s="2" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="D702" s="2" t="inlineStr">
@@ -21505,7 +21505,7 @@
         </is>
       </c>
       <c r="E702" s="3" t="n">
-        <v>131.59</v>
+        <v>132.39</v>
       </c>
       <c r="F702" s="2" t="inlineStr">
         <is>
@@ -21521,12 +21521,12 @@
       </c>
       <c r="B703" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C703" s="2" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="D703" s="2" t="inlineStr">
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>131.31</v>
+        <v>132.08</v>
       </c>
       <c r="F703" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21551,12 +21551,12 @@
       </c>
       <c r="B704" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C704" s="2" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="D704" s="2" t="inlineStr">
@@ -21565,11 +21565,11 @@
         </is>
       </c>
       <c r="E704" s="3" t="n">
-        <v>131.04</v>
+        <v>131.78</v>
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21581,12 +21581,12 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="D705" s="2" t="inlineStr">
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>130.72</v>
+        <v>131.46</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21611,12 +21611,12 @@
       </c>
       <c r="B706" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C706" s="2" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="D706" s="2" t="inlineStr">
@@ -21625,7 +21625,7 @@
         </is>
       </c>
       <c r="E706" s="3" t="n">
-        <v>130.55</v>
+        <v>131.31</v>
       </c>
       <c r="F706" s="2" t="inlineStr">
         <is>
@@ -21641,12 +21641,12 @@
       </c>
       <c r="B707" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C707" s="2" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="D707" s="2" t="inlineStr">
@@ -21655,7 +21655,7 @@
         </is>
       </c>
       <c r="E707" s="3" t="n">
-        <v>127.38</v>
+        <v>131.04</v>
       </c>
       <c r="F707" s="2" t="inlineStr">
         <is>
@@ -21671,12 +21671,12 @@
       </c>
       <c r="B708" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C708" s="2" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="D708" s="2" t="inlineStr">
@@ -21685,11 +21685,11 @@
         </is>
       </c>
       <c r="E708" s="3" t="n">
-        <v>126.03</v>
+        <v>128.03</v>
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21701,12 +21701,12 @@
       </c>
       <c r="B709" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C709" s="2" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="D709" s="2" t="inlineStr">
@@ -21715,7 +21715,7 @@
         </is>
       </c>
       <c r="E709" s="3" t="n">
-        <v>123.21</v>
+        <v>126.03</v>
       </c>
       <c r="F709" s="2" t="inlineStr">
         <is>
@@ -21731,12 +21731,12 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="D710" s="2" t="inlineStr">
@@ -21745,11 +21745,11 @@
         </is>
       </c>
       <c r="E710" s="3" t="n">
-        <v>120.81</v>
+        <v>125.27</v>
       </c>
       <c r="F710" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21775,11 +21775,11 @@
         </is>
       </c>
       <c r="E711" s="3" t="n">
-        <v>120.11</v>
+        <v>124.24</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21791,12 +21791,12 @@
       </c>
       <c r="B712" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C712" s="2" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="D712" s="2" t="inlineStr">
@@ -21805,11 +21805,11 @@
         </is>
       </c>
       <c r="E712" s="3" t="n">
-        <v>119.92</v>
+        <v>122.45</v>
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21821,12 +21821,12 @@
       </c>
       <c r="B713" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C713" s="2" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="D713" s="2" t="inlineStr">
@@ -21835,11 +21835,11 @@
         </is>
       </c>
       <c r="E713" s="3" t="n">
-        <v>119.79</v>
+        <v>120.86</v>
       </c>
       <c r="F713" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21851,12 +21851,12 @@
       </c>
       <c r="B714" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C714" s="2" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="D714" s="2" t="inlineStr">
@@ -21865,7 +21865,7 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>117.29</v>
+        <v>119.92</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
@@ -21895,11 +21895,11 @@
         </is>
       </c>
       <c r="E715" s="3" t="n">
-        <v>117.13</v>
+        <v>118.72</v>
       </c>
       <c r="F715" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21925,11 +21925,11 @@
         </is>
       </c>
       <c r="E716" s="3" t="n">
-        <v>114.81</v>
+        <v>117.35</v>
       </c>
       <c r="F716" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B717" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C717" s="2" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="D717" s="2" t="inlineStr">
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>113.25</v>
+        <v>116.39</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -21971,12 +21971,12 @@
       </c>
       <c r="B718" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr">
@@ -21985,7 +21985,7 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>110.35</v>
+        <v>113.25</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
@@ -22001,12 +22001,12 @@
       </c>
       <c r="B719" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C719" s="2" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="D719" s="2" t="inlineStr">
@@ -22015,11 +22015,11 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>109.38</v>
+        <v>112.96</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -22031,25 +22031,25 @@
       </c>
       <c r="B720" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C720" s="2" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="D720" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E720" s="3" t="n">
-        <v>106.48</v>
+        <v>112.9</v>
       </c>
       <c r="F720" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -22061,12 +22061,12 @@
       </c>
       <c r="B721" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C721" s="2" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="D721" s="2" t="inlineStr">
@@ -22075,11 +22075,11 @@
         </is>
       </c>
       <c r="E721" s="3" t="n">
-        <v>105.3</v>
+        <v>109.31</v>
       </c>
       <c r="F721" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -22091,12 +22091,12 @@
       </c>
       <c r="B722" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C722" s="2" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="D722" s="2" t="inlineStr">
@@ -22105,7 +22105,7 @@
         </is>
       </c>
       <c r="E722" s="3" t="n">
-        <v>104.62</v>
+        <v>106.48</v>
       </c>
       <c r="F722" s="2" t="inlineStr">
         <is>
@@ -22121,12 +22121,12 @@
       </c>
       <c r="B723" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C723" s="2" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="D723" s="2" t="inlineStr">
@@ -22135,11 +22135,11 @@
         </is>
       </c>
       <c r="E723" s="3" t="n">
-        <v>101.97</v>
+        <v>106.33</v>
       </c>
       <c r="F723" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -22151,12 +22151,12 @@
       </c>
       <c r="B724" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C724" s="2" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="D724" s="2" t="inlineStr">
@@ -22165,11 +22165,11 @@
         </is>
       </c>
       <c r="E724" s="3" t="n">
-        <v>100.93</v>
+        <v>104.76</v>
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -22181,12 +22181,12 @@
       </c>
       <c r="B725" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C725" s="2" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="D725" s="2" t="inlineStr">
@@ -22195,11 +22195,11 @@
         </is>
       </c>
       <c r="E725" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>104.74</v>
       </c>
       <c r="F725" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -22211,21 +22211,21 @@
       </c>
       <c r="B726" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C726" s="2" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="D726" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E726" s="3" t="n">
-        <v>98.69</v>
+        <v>100.93</v>
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
@@ -22241,12 +22241,12 @@
       </c>
       <c r="B727" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C727" s="2" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="D727" s="2" t="inlineStr">
@@ -22255,7 +22255,7 @@
         </is>
       </c>
       <c r="E727" s="3" t="n">
-        <v>98.25</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F727" s="2" t="inlineStr">
         <is>
@@ -22271,12 +22271,12 @@
       </c>
       <c r="B728" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C728" s="2" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="D728" s="2" t="inlineStr">
@@ -22285,11 +22285,11 @@
         </is>
       </c>
       <c r="E728" s="3" t="n">
-        <v>97.44</v>
+        <v>99.55</v>
       </c>
       <c r="F728" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -22301,12 +22301,12 @@
       </c>
       <c r="B729" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C729" s="2" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="D729" s="2" t="inlineStr">
@@ -22315,11 +22315,11 @@
         </is>
       </c>
       <c r="E729" s="3" t="n">
-        <v>96</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="F729" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -22331,12 +22331,12 @@
       </c>
       <c r="B730" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C730" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="D730" s="2" t="inlineStr">
@@ -22345,7 +22345,7 @@
         </is>
       </c>
       <c r="E730" s="3" t="n">
-        <v>93.22</v>
+        <v>97.44</v>
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
@@ -22361,12 +22361,12 @@
       </c>
       <c r="B731" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="D731" s="2" t="inlineStr">
@@ -22375,11 +22375,11 @@
         </is>
       </c>
       <c r="E731" s="3" t="n">
-        <v>91.65000000000001</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -22391,12 +22391,12 @@
       </c>
       <c r="B732" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D732" s="2" t="inlineStr">
@@ -22405,7 +22405,7 @@
         </is>
       </c>
       <c r="E732" s="3" t="n">
-        <v>91.20999999999999</v>
+        <v>93.22</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
@@ -22421,12 +22421,12 @@
       </c>
       <c r="B733" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="D733" s="2" t="inlineStr">
@@ -22435,11 +22435,11 @@
         </is>
       </c>
       <c r="E733" s="3" t="n">
-        <v>89.79000000000001</v>
+        <v>92.13</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -22451,21 +22451,21 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E734" s="3" t="n">
-        <v>89.48999999999999</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
@@ -22481,21 +22481,21 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>87.73</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
@@ -22511,12 +22511,12 @@
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
@@ -22525,7 +22525,7 @@
         </is>
       </c>
       <c r="E736" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>87.73</v>
       </c>
       <c r="F736" s="2" t="inlineStr">
         <is>
@@ -22555,11 +22555,11 @@
         </is>
       </c>
       <c r="E737" s="3" t="n">
-        <v>85.70999999999999</v>
+        <v>86.92</v>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -22571,12 +22571,12 @@
       </c>
       <c r="B738" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="D738" s="2" t="inlineStr">
@@ -22585,7 +22585,7 @@
         </is>
       </c>
       <c r="E738" s="3" t="n">
-        <v>85.20999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
@@ -22615,11 +22615,11 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>84.04000000000001</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -22631,12 +22631,12 @@
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
@@ -22645,11 +22645,11 @@
         </is>
       </c>
       <c r="E740" s="3" t="n">
-        <v>82.18000000000001</v>
+        <v>85.11</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -22661,12 +22661,12 @@
       </c>
       <c r="B741" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="D741" s="2" t="inlineStr">
@@ -22675,7 +22675,7 @@
         </is>
       </c>
       <c r="E741" s="3" t="n">
-        <v>81.84</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F741" s="2" t="inlineStr">
         <is>
@@ -22691,12 +22691,12 @@
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>79.44</v>
+        <v>79.67</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -22735,11 +22735,11 @@
         </is>
       </c>
       <c r="E743" s="3" t="n">
-        <v>79.13</v>
+        <v>79.63</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -22751,12 +22751,12 @@
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="D744" s="2" t="inlineStr">
@@ -22765,7 +22765,7 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>78</v>
+        <v>79.44</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
@@ -22781,12 +22781,12 @@
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr">
@@ -22795,11 +22795,11 @@
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>77.84</v>
+        <v>78.52</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -22811,12 +22811,12 @@
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
@@ -22825,7 +22825,7 @@
         </is>
       </c>
       <c r="E746" s="3" t="n">
-        <v>76.44</v>
+        <v>77.84</v>
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
@@ -22841,12 +22841,12 @@
       </c>
       <c r="B747" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C747" s="2" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="D747" s="2" t="inlineStr">
@@ -22855,11 +22855,11 @@
         </is>
       </c>
       <c r="E747" s="3" t="n">
-        <v>75.94</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="F747" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -22871,12 +22871,12 @@
       </c>
       <c r="B748" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C748" s="2" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="D748" s="2" t="inlineStr">
@@ -22885,7 +22885,7 @@
         </is>
       </c>
       <c r="E748" s="3" t="n">
-        <v>75.81</v>
+        <v>75.94</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
@@ -22901,12 +22901,12 @@
       </c>
       <c r="B749" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C749" s="2" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="D749" s="2" t="inlineStr">
@@ -22915,7 +22915,7 @@
         </is>
       </c>
       <c r="E749" s="3" t="n">
-        <v>74.76000000000001</v>
+        <v>75.81</v>
       </c>
       <c r="F749" s="2" t="inlineStr">
         <is>
@@ -22931,12 +22931,12 @@
       </c>
       <c r="B750" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C750" s="2" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="D750" s="2" t="inlineStr">
@@ -22945,7 +22945,7 @@
         </is>
       </c>
       <c r="E750" s="3" t="n">
-        <v>74.65000000000001</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="F750" s="2" t="inlineStr">
         <is>
@@ -23005,11 +23005,11 @@
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>72.54000000000001</v>
+        <v>73.63</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23065,11 +23065,11 @@
         </is>
       </c>
       <c r="E754" s="3" t="n">
-        <v>70.47</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="F754" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23095,11 +23095,11 @@
         </is>
       </c>
       <c r="E755" s="3" t="n">
-        <v>69.34999999999999</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="F755" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23125,11 +23125,11 @@
         </is>
       </c>
       <c r="E756" s="3" t="n">
-        <v>67.18000000000001</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23155,11 +23155,11 @@
         </is>
       </c>
       <c r="E757" s="3" t="n">
-        <v>65.45999999999999</v>
+        <v>67.09</v>
       </c>
       <c r="F757" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23171,12 +23171,12 @@
       </c>
       <c r="B758" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C758" s="2" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D758" s="2" t="inlineStr">
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>64.33</v>
+        <v>66.59</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23201,12 +23201,12 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="D759" s="2" t="inlineStr">
@@ -23215,7 +23215,7 @@
         </is>
       </c>
       <c r="E759" s="3" t="n">
-        <v>63.53</v>
+        <v>64.33</v>
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
@@ -23231,12 +23231,12 @@
       </c>
       <c r="B760" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C760" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="D760" s="2" t="inlineStr">
@@ -23245,11 +23245,11 @@
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>63.49</v>
+        <v>63.6</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23291,12 +23291,12 @@
       </c>
       <c r="B762" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C762" s="2" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="D762" s="2" t="inlineStr">
@@ -23305,11 +23305,11 @@
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>60.48</v>
+        <v>61.91</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23321,12 +23321,12 @@
       </c>
       <c r="B763" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C763" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="D763" s="2" t="inlineStr">
@@ -23335,11 +23335,11 @@
         </is>
       </c>
       <c r="E763" s="3" t="n">
-        <v>60.31</v>
+        <v>60.66</v>
       </c>
       <c r="F763" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23351,12 +23351,12 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D764" s="2" t="inlineStr">
@@ -23365,7 +23365,7 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>59.38</v>
+        <v>60.31</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
@@ -23395,11 +23395,11 @@
         </is>
       </c>
       <c r="E765" s="3" t="n">
-        <v>58.61</v>
+        <v>58.84</v>
       </c>
       <c r="F765" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23411,12 +23411,12 @@
       </c>
       <c r="B766" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C766" s="2" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D766" s="2" t="inlineStr">
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>58.27</v>
+        <v>58.62</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23441,12 +23441,12 @@
       </c>
       <c r="B767" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C767" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="D767" s="2" t="inlineStr">
@@ -23455,11 +23455,11 @@
         </is>
       </c>
       <c r="E767" s="3" t="n">
-        <v>57.67</v>
+        <v>58.62</v>
       </c>
       <c r="F767" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23471,25 +23471,25 @@
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="D768" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>57.22</v>
+        <v>58.57</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23501,12 @@
       </c>
       <c r="B769" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C769" s="2" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="D769" s="2" t="inlineStr">
@@ -23515,11 +23515,11 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>56.5</v>
+        <v>58.05</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23531,21 +23531,21 @@
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E770" s="3" t="n">
-        <v>56.35</v>
+        <v>57.22</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
@@ -23561,12 +23561,12 @@
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
@@ -23575,7 +23575,7 @@
         </is>
       </c>
       <c r="E771" s="3" t="n">
-        <v>55.94</v>
+        <v>56.5</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
@@ -23591,12 +23591,12 @@
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -23605,7 +23605,7 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>55.64</v>
+        <v>56.35</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
@@ -23621,12 +23621,12 @@
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="D773" s="2" t="inlineStr">
@@ -23635,11 +23635,11 @@
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>55.05</v>
+        <v>56.07</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23651,12 +23651,12 @@
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr">
@@ -23665,11 +23665,11 @@
         </is>
       </c>
       <c r="E774" s="3" t="n">
-        <v>54.83</v>
+        <v>55.54</v>
       </c>
       <c r="F774" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23681,12 +23681,12 @@
       </c>
       <c r="B775" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C775" s="2" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="D775" s="2" t="inlineStr">
@@ -23695,7 +23695,7 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>54.77</v>
+        <v>55.05</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
@@ -23711,12 +23711,12 @@
       </c>
       <c r="B776" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C776" s="2" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="D776" s="2" t="inlineStr">
@@ -23725,11 +23725,11 @@
         </is>
       </c>
       <c r="E776" s="3" t="n">
-        <v>54.26</v>
+        <v>55</v>
       </c>
       <c r="F776" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23741,12 +23741,12 @@
       </c>
       <c r="B777" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C777" s="2" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="D777" s="2" t="inlineStr">
@@ -23755,11 +23755,11 @@
         </is>
       </c>
       <c r="E777" s="3" t="n">
-        <v>53.95</v>
+        <v>54.3</v>
       </c>
       <c r="F777" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23771,12 +23771,12 @@
       </c>
       <c r="B778" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C778" s="2" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="D778" s="2" t="inlineStr">
@@ -23785,7 +23785,7 @@
         </is>
       </c>
       <c r="E778" s="3" t="n">
-        <v>53.34</v>
+        <v>53.95</v>
       </c>
       <c r="F778" s="2" t="inlineStr">
         <is>
@@ -23801,12 +23801,12 @@
       </c>
       <c r="B779" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C779" s="2" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="D779" s="2" t="inlineStr">
@@ -23815,11 +23815,11 @@
         </is>
       </c>
       <c r="E779" s="3" t="n">
-        <v>53.2</v>
+        <v>53.36</v>
       </c>
       <c r="F779" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23831,12 +23831,12 @@
       </c>
       <c r="B780" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C780" s="2" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="D780" s="2" t="inlineStr">
@@ -23845,11 +23845,11 @@
         </is>
       </c>
       <c r="E780" s="3" t="n">
-        <v>52.59</v>
+        <v>53.21</v>
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23861,12 +23861,12 @@
       </c>
       <c r="B781" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C781" s="2" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="D781" s="2" t="inlineStr">
@@ -23875,11 +23875,11 @@
         </is>
       </c>
       <c r="E781" s="3" t="n">
-        <v>52.57</v>
+        <v>52.66</v>
       </c>
       <c r="F781" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23891,12 +23891,12 @@
       </c>
       <c r="B782" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C782" s="2" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="D782" s="2" t="inlineStr">
@@ -23905,7 +23905,7 @@
         </is>
       </c>
       <c r="E782" s="3" t="n">
-        <v>52.54</v>
+        <v>52.57</v>
       </c>
       <c r="F782" s="2" t="inlineStr">
         <is>
@@ -23965,11 +23965,11 @@
         </is>
       </c>
       <c r="E784" s="3" t="n">
-        <v>49.07</v>
+        <v>50.49</v>
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23995,11 +23995,11 @@
         </is>
       </c>
       <c r="E785" s="3" t="n">
-        <v>48.69</v>
+        <v>50.3</v>
       </c>
       <c r="F785" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>48.6</v>
+        <v>49.55</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>48.09</v>
+        <v>49.42</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24071,12 +24071,12 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D788" s="2" t="inlineStr">
@@ -24085,11 +24085,11 @@
         </is>
       </c>
       <c r="E788" s="3" t="n">
-        <v>48.04</v>
+        <v>49.33</v>
       </c>
       <c r="F788" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24101,12 +24101,12 @@
       </c>
       <c r="B789" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C789" s="2" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="D789" s="2" t="inlineStr">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>47.38</v>
+        <v>48.04</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
@@ -24131,12 +24131,12 @@
       </c>
       <c r="B790" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C790" s="2" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="D790" s="2" t="inlineStr">
@@ -24145,11 +24145,11 @@
         </is>
       </c>
       <c r="E790" s="3" t="n">
-        <v>47.23</v>
+        <v>47.99</v>
       </c>
       <c r="F790" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24161,12 +24161,12 @@
       </c>
       <c r="B791" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C791" s="2" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="D791" s="2" t="inlineStr">
@@ -24175,11 +24175,11 @@
         </is>
       </c>
       <c r="E791" s="3" t="n">
-        <v>47.19</v>
+        <v>47.5</v>
       </c>
       <c r="F791" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24191,12 +24191,12 @@
       </c>
       <c r="B792" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C792" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="D792" s="2" t="inlineStr">
@@ -24205,7 +24205,7 @@
         </is>
       </c>
       <c r="E792" s="3" t="n">
-        <v>46.87</v>
+        <v>47.23</v>
       </c>
       <c r="F792" s="2" t="inlineStr">
         <is>
@@ -24281,12 +24281,12 @@
       </c>
       <c r="B795" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C795" s="2" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D795" s="2" t="inlineStr">
@@ -24295,11 +24295,11 @@
         </is>
       </c>
       <c r="E795" s="3" t="n">
-        <v>44.19</v>
+        <v>44.52</v>
       </c>
       <c r="F795" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24311,12 +24311,12 @@
       </c>
       <c r="B796" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C796" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="D796" s="2" t="inlineStr">
@@ -24325,11 +24325,11 @@
         </is>
       </c>
       <c r="E796" s="3" t="n">
-        <v>43.95</v>
+        <v>44.33</v>
       </c>
       <c r="F796" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24341,12 +24341,12 @@
       </c>
       <c r="B797" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C797" s="2" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="D797" s="2" t="inlineStr">
@@ -24355,7 +24355,7 @@
         </is>
       </c>
       <c r="E797" s="3" t="n">
-        <v>43.73</v>
+        <v>44.19</v>
       </c>
       <c r="F797" s="2" t="inlineStr">
         <is>
@@ -24371,12 +24371,12 @@
       </c>
       <c r="B798" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C798" s="2" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="D798" s="2" t="inlineStr">
@@ -24385,11 +24385,11 @@
         </is>
       </c>
       <c r="E798" s="3" t="n">
-        <v>41.54</v>
+        <v>44.09</v>
       </c>
       <c r="F798" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="B799" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C799" s="2" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="D799" s="2" t="inlineStr">
@@ -24415,11 +24415,11 @@
         </is>
       </c>
       <c r="E799" s="3" t="n">
-        <v>40.59</v>
+        <v>43.42</v>
       </c>
       <c r="F799" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24431,12 +24431,12 @@
       </c>
       <c r="B800" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C800" s="2" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="D800" s="2" t="inlineStr">
@@ -24445,11 +24445,11 @@
         </is>
       </c>
       <c r="E800" s="3" t="n">
-        <v>39.41</v>
+        <v>39.46</v>
       </c>
       <c r="F800" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24461,12 +24461,12 @@
       </c>
       <c r="B801" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C801" s="2" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="D801" s="2" t="inlineStr">
@@ -24475,7 +24475,7 @@
         </is>
       </c>
       <c r="E801" s="3" t="n">
-        <v>38.88</v>
+        <v>39.41</v>
       </c>
       <c r="F801" s="2" t="inlineStr">
         <is>
@@ -24491,12 +24491,12 @@
       </c>
       <c r="B802" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C802" s="2" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="D802" s="2" t="inlineStr">
@@ -24505,11 +24505,11 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>38.74</v>
+        <v>38.91</v>
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24521,12 +24521,12 @@
       </c>
       <c r="B803" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C803" s="2" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="D803" s="2" t="inlineStr">
@@ -24535,7 +24535,7 @@
         </is>
       </c>
       <c r="E803" s="3" t="n">
-        <v>38.62</v>
+        <v>38.88</v>
       </c>
       <c r="F803" s="2" t="inlineStr">
         <is>
@@ -24581,12 +24581,12 @@
       </c>
       <c r="B805" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C805" s="2" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="D805" s="2" t="inlineStr">
@@ -24595,11 +24595,11 @@
         </is>
       </c>
       <c r="E805" s="3" t="n">
-        <v>36.48</v>
+        <v>36.59</v>
       </c>
       <c r="F805" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24611,12 +24611,12 @@
       </c>
       <c r="B806" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C806" s="2" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="D806" s="2" t="inlineStr">
@@ -24625,7 +24625,7 @@
         </is>
       </c>
       <c r="E806" s="3" t="n">
-        <v>36.31</v>
+        <v>36.48</v>
       </c>
       <c r="F806" s="2" t="inlineStr">
         <is>
@@ -24641,12 +24641,12 @@
       </c>
       <c r="B807" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C807" s="2" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="D807" s="2" t="inlineStr">
@@ -24655,7 +24655,7 @@
         </is>
       </c>
       <c r="E807" s="3" t="n">
-        <v>36.26</v>
+        <v>36.31</v>
       </c>
       <c r="F807" s="2" t="inlineStr">
         <is>
@@ -24685,11 +24685,11 @@
         </is>
       </c>
       <c r="E808" s="3" t="n">
-        <v>35.43</v>
+        <v>35.44</v>
       </c>
       <c r="F808" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24701,12 +24701,12 @@
       </c>
       <c r="B809" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C809" s="2" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="D809" s="2" t="inlineStr">
@@ -24715,11 +24715,11 @@
         </is>
       </c>
       <c r="E809" s="3" t="n">
-        <v>34.1</v>
+        <v>35.16</v>
       </c>
       <c r="F809" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24731,12 +24731,12 @@
       </c>
       <c r="B810" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C810" s="2" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="D810" s="2" t="inlineStr">
@@ -24745,7 +24745,7 @@
         </is>
       </c>
       <c r="E810" s="3" t="n">
-        <v>34.05</v>
+        <v>34.1</v>
       </c>
       <c r="F810" s="2" t="inlineStr">
         <is>
@@ -24761,12 +24761,12 @@
       </c>
       <c r="B811" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="C811" s="2" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="D811" s="2" t="inlineStr">
@@ -24775,7 +24775,7 @@
         </is>
       </c>
       <c r="E811" s="3" t="n">
-        <v>32.88</v>
+        <v>34.05</v>
       </c>
       <c r="F811" s="2" t="inlineStr">
         <is>
@@ -24805,11 +24805,11 @@
         </is>
       </c>
       <c r="E812" s="3" t="n">
-        <v>32.12</v>
+        <v>32.72</v>
       </c>
       <c r="F812" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24851,12 +24851,12 @@
       </c>
       <c r="B814" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C814" s="2" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D814" s="2" t="inlineStr">
@@ -24865,11 +24865,11 @@
         </is>
       </c>
       <c r="E814" s="3" t="n">
-        <v>29.87</v>
+        <v>30.64</v>
       </c>
       <c r="F814" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24881,12 +24881,12 @@
       </c>
       <c r="B815" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C815" s="2" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="D815" s="2" t="inlineStr">
@@ -24895,11 +24895,11 @@
         </is>
       </c>
       <c r="E815" s="3" t="n">
-        <v>29.83</v>
+        <v>30.08</v>
       </c>
       <c r="F815" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24911,12 +24911,12 @@
       </c>
       <c r="B816" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C816" s="2" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="D816" s="2" t="inlineStr">
@@ -24925,11 +24925,11 @@
         </is>
       </c>
       <c r="E816" s="3" t="n">
-        <v>29.38</v>
+        <v>30.03</v>
       </c>
       <c r="F816" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24941,12 +24941,12 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="D817" s="2" t="inlineStr">
@@ -24955,7 +24955,7 @@
         </is>
       </c>
       <c r="E817" s="3" t="n">
-        <v>29.27</v>
+        <v>29.83</v>
       </c>
       <c r="F817" s="2" t="inlineStr">
         <is>
@@ -24971,12 +24971,12 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="D818" s="2" t="inlineStr">
@@ -24985,7 +24985,7 @@
         </is>
       </c>
       <c r="E818" s="3" t="n">
-        <v>29.05</v>
+        <v>29.27</v>
       </c>
       <c r="F818" s="2" t="inlineStr">
         <is>
@@ -25045,11 +25045,11 @@
         </is>
       </c>
       <c r="E820" s="3" t="n">
-        <v>27.21</v>
+        <v>28.46</v>
       </c>
       <c r="F820" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -25075,11 +25075,11 @@
         </is>
       </c>
       <c r="E821" s="3" t="n">
-        <v>26.53</v>
+        <v>26.96</v>
       </c>
       <c r="F821" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -25121,12 +25121,12 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="D823" s="2" t="inlineStr">
@@ -25135,11 +25135,11 @@
         </is>
       </c>
       <c r="E823" s="3" t="n">
-        <v>25.79</v>
+        <v>26.01</v>
       </c>
       <c r="F823" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -25151,12 +25151,12 @@
       </c>
       <c r="B824" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C824" s="2" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D824" s="2" t="inlineStr">
@@ -25165,7 +25165,7 @@
         </is>
       </c>
       <c r="E824" s="3" t="n">
-        <v>25.7</v>
+        <v>25.79</v>
       </c>
       <c r="F824" s="2" t="inlineStr">
         <is>
@@ -25195,11 +25195,11 @@
         </is>
       </c>
       <c r="E825" s="3" t="n">
-        <v>24.97</v>
+        <v>25.34</v>
       </c>
       <c r="F825" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -25225,11 +25225,11 @@
         </is>
       </c>
       <c r="E826" s="3" t="n">
-        <v>24.29</v>
+        <v>25.24</v>
       </c>
       <c r="F826" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -25511,12 +25511,12 @@
       </c>
       <c r="B836" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C836" s="2" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="D836" s="2" t="inlineStr">
@@ -25525,11 +25525,11 @@
         </is>
       </c>
       <c r="E836" s="3" t="n">
-        <v>20.12</v>
+        <v>20.13</v>
       </c>
       <c r="F836" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -25541,12 +25541,12 @@
       </c>
       <c r="B837" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C837" s="2" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="D837" s="2" t="inlineStr">
@@ -25555,7 +25555,7 @@
         </is>
       </c>
       <c r="E837" s="3" t="n">
-        <v>20.07</v>
+        <v>20.12</v>
       </c>
       <c r="F837" s="2" t="inlineStr">
         <is>
@@ -25615,11 +25615,11 @@
         </is>
       </c>
       <c r="E839" s="3" t="n">
-        <v>17.99</v>
+        <v>18.47</v>
       </c>
       <c r="F839" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -25735,11 +25735,11 @@
         </is>
       </c>
       <c r="E843" s="3" t="n">
-        <v>16.24</v>
+        <v>16.45</v>
       </c>
       <c r="F843" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -25751,25 +25751,25 @@
       </c>
       <c r="B844" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C844" s="2" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="D844" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E844" s="3" t="n">
-        <v>15.77</v>
+        <v>15.81</v>
       </c>
       <c r="F844" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -25781,21 +25781,21 @@
       </c>
       <c r="B845" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C845" s="2" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="D845" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E845" s="3" t="n">
-        <v>15.64</v>
+        <v>15.77</v>
       </c>
       <c r="F845" s="2" t="inlineStr">
         <is>
@@ -25961,12 +25961,12 @@
       </c>
       <c r="B851" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C851" s="2" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="D851" s="2" t="inlineStr">
@@ -25975,11 +25975,11 @@
         </is>
       </c>
       <c r="E851" s="3" t="n">
-        <v>10.07</v>
+        <v>10.4</v>
       </c>
       <c r="F851" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -26005,11 +26005,11 @@
         </is>
       </c>
       <c r="E852" s="3" t="n">
-        <v>10.04</v>
+        <v>10.08</v>
       </c>
       <c r="F852" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -26021,12 +26021,12 @@
       </c>
       <c r="B853" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C853" s="2" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="D853" s="2" t="inlineStr">
@@ -26035,7 +26035,7 @@
         </is>
       </c>
       <c r="E853" s="3" t="n">
-        <v>9.859999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="F853" s="2" t="inlineStr">
         <is>
@@ -26051,12 +26051,12 @@
       </c>
       <c r="B854" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C854" s="2" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="D854" s="2" t="inlineStr">
@@ -26065,11 +26065,11 @@
         </is>
       </c>
       <c r="E854" s="3" t="n">
-        <v>9.380000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="F854" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -26081,12 +26081,12 @@
       </c>
       <c r="B855" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C855" s="2" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D855" s="2" t="inlineStr">
@@ -26095,11 +26095,11 @@
         </is>
       </c>
       <c r="E855" s="3" t="n">
-        <v>9.27</v>
+        <v>9.67</v>
       </c>
       <c r="F855" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -26111,12 +26111,12 @@
       </c>
       <c r="B856" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C856" s="2" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="D856" s="2" t="inlineStr">
@@ -26125,7 +26125,7 @@
         </is>
       </c>
       <c r="E856" s="3" t="n">
-        <v>8.529999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="F856" s="2" t="inlineStr">
         <is>
@@ -26141,12 +26141,12 @@
       </c>
       <c r="B857" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C857" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="D857" s="2" t="inlineStr">
@@ -26155,7 +26155,7 @@
         </is>
       </c>
       <c r="E857" s="3" t="n">
-        <v>7.92</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="F857" s="2" t="inlineStr">
         <is>
@@ -26455,11 +26455,11 @@
         </is>
       </c>
       <c r="E867" s="3" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="F867" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2140.2</v>
+        <v>2184.28</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -19855,11 +19855,11 @@
         </is>
       </c>
       <c r="E647" s="3" t="n">
-        <v>1399</v>
+        <v>1469.32</v>
       </c>
       <c r="F647" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>896.01</v>
+        <v>921.52</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -19945,11 +19945,11 @@
         </is>
       </c>
       <c r="E650" s="3" t="n">
-        <v>779.38</v>
+        <v>839.87</v>
       </c>
       <c r="F650" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20005,11 +20005,11 @@
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>652.58</v>
+        <v>676.47</v>
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20065,11 +20065,11 @@
         </is>
       </c>
       <c r="E654" s="3" t="n">
-        <v>588.77</v>
+        <v>592.1</v>
       </c>
       <c r="F654" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20095,11 +20095,11 @@
         </is>
       </c>
       <c r="E655" s="3" t="n">
-        <v>585.03</v>
+        <v>586.64</v>
       </c>
       <c r="F655" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20125,11 +20125,11 @@
         </is>
       </c>
       <c r="E656" s="3" t="n">
-        <v>578.52</v>
+        <v>581.29</v>
       </c>
       <c r="F656" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20141,25 +20141,25 @@
       </c>
       <c r="B657" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C657" s="2" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="D657" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>519.2</v>
+        <v>532.12</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20171,12 +20171,12 @@
       </c>
       <c r="B658" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C658" s="2" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="D658" s="2" t="inlineStr">
@@ -20185,11 +20185,11 @@
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>513.88</v>
+        <v>526.3</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20201,25 +20201,25 @@
       </c>
       <c r="B659" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C659" s="2" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="D659" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E659" s="3" t="n">
-        <v>512.46</v>
+        <v>513.88</v>
       </c>
       <c r="F659" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20231,12 +20231,12 @@
       </c>
       <c r="B660" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066901JZZ</t>
+          <t>KIT4P000739257CR</t>
         </is>
       </c>
       <c r="C660" s="2" t="inlineStr">
         <is>
-          <t>812926</t>
+          <t>814609</t>
         </is>
       </c>
       <c r="D660" s="2" t="inlineStr">
@@ -20245,11 +20245,11 @@
         </is>
       </c>
       <c r="E660" s="3" t="n">
-        <v>500.45</v>
+        <v>512.21</v>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20261,25 +20261,25 @@
       </c>
       <c r="B661" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="C661" s="2" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>812926</t>
         </is>
       </c>
       <c r="D661" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>482.26</v>
+        <v>500.45</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20291,25 +20291,25 @@
       </c>
       <c r="B662" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C662" s="2" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="D662" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E662" s="3" t="n">
-        <v>480.85</v>
+        <v>493.34</v>
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         </is>
       </c>
       <c r="E663" s="3" t="n">
-        <v>478.98</v>
+        <v>481.33</v>
       </c>
       <c r="F663" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20351,12 +20351,12 @@
       </c>
       <c r="B664" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
@@ -20365,7 +20365,7 @@
         </is>
       </c>
       <c r="E664" s="3" t="n">
-        <v>466.53</v>
+        <v>480.85</v>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
@@ -20381,12 +20381,12 @@
       </c>
       <c r="B665" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
@@ -20395,11 +20395,11 @@
         </is>
       </c>
       <c r="E665" s="3" t="n">
-        <v>453.29</v>
+        <v>466.53</v>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20411,12 +20411,12 @@
       </c>
       <c r="B666" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739257CR</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>814609</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
@@ -20425,11 +20425,11 @@
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>439.55</v>
+        <v>459.82</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20455,11 +20455,11 @@
         </is>
       </c>
       <c r="E667" s="3" t="n">
-        <v>431.51</v>
+        <v>442.6</v>
       </c>
       <c r="F667" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20485,11 +20485,11 @@
         </is>
       </c>
       <c r="E668" s="3" t="n">
-        <v>420.1</v>
+        <v>436.67</v>
       </c>
       <c r="F668" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20501,25 +20501,25 @@
       </c>
       <c r="B669" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065631CPZ</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C669" s="2" t="inlineStr">
         <is>
-          <t>812930</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="D669" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E669" s="3" t="n">
-        <v>415.73</v>
+        <v>419.61</v>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20531,25 +20531,25 @@
       </c>
       <c r="B670" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="C670" s="2" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>812930</t>
         </is>
       </c>
       <c r="D670" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E670" s="3" t="n">
-        <v>411.97</v>
+        <v>415.73</v>
       </c>
       <c r="F670" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20605,11 +20605,11 @@
         </is>
       </c>
       <c r="E672" s="3" t="n">
-        <v>354.56</v>
+        <v>372.44</v>
       </c>
       <c r="F672" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20621,12 +20621,12 @@
       </c>
       <c r="B673" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C673" s="2" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="D673" s="2" t="inlineStr">
@@ -20635,11 +20635,11 @@
         </is>
       </c>
       <c r="E673" s="3" t="n">
-        <v>322.69</v>
+        <v>328.15</v>
       </c>
       <c r="F673" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20651,12 +20651,12 @@
       </c>
       <c r="B674" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C674" s="2" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="D674" s="2" t="inlineStr">
@@ -20665,11 +20665,11 @@
         </is>
       </c>
       <c r="E674" s="3" t="n">
-        <v>315.63</v>
+        <v>324.92</v>
       </c>
       <c r="F674" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20681,12 +20681,12 @@
       </c>
       <c r="B675" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C675" s="2" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="D675" s="2" t="inlineStr">
@@ -20695,11 +20695,11 @@
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>309.31</v>
+        <v>316.07</v>
       </c>
       <c r="F675" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20725,11 +20725,11 @@
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>300.33</v>
+        <v>304.71</v>
       </c>
       <c r="F676" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20755,11 +20755,11 @@
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>299.36</v>
+        <v>301.88</v>
       </c>
       <c r="F677" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20771,25 +20771,25 @@
       </c>
       <c r="B678" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C678" s="2" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="D678" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E678" s="3" t="n">
-        <v>273.78</v>
+        <v>290.91</v>
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20801,25 +20801,25 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="D679" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>269.41</v>
+        <v>275.18</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>267.43</v>
+        <v>267.96</v>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20905,11 +20905,11 @@
         </is>
       </c>
       <c r="E682" s="3" t="n">
-        <v>259.45</v>
+        <v>263.81</v>
       </c>
       <c r="F682" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -20935,11 +20935,11 @@
         </is>
       </c>
       <c r="E683" s="3" t="n">
-        <v>257.48</v>
+        <v>257.93</v>
       </c>
       <c r="F683" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21041,12 +21041,12 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="D687" s="2" t="inlineStr">
@@ -21055,11 +21055,11 @@
         </is>
       </c>
       <c r="E687" s="3" t="n">
-        <v>201.84</v>
+        <v>208.19</v>
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21071,12 +21071,12 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="D688" s="2" t="inlineStr">
@@ -21085,11 +21085,11 @@
         </is>
       </c>
       <c r="E688" s="3" t="n">
-        <v>201.2</v>
+        <v>204.08</v>
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21101,12 +21101,12 @@
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="D689" s="2" t="inlineStr">
@@ -21115,11 +21115,11 @@
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>199.59</v>
+        <v>204</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21131,12 +21131,12 @@
       </c>
       <c r="B690" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C690" s="2" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="D690" s="2" t="inlineStr">
@@ -21145,11 +21145,11 @@
         </is>
       </c>
       <c r="E690" s="3" t="n">
-        <v>193.33</v>
+        <v>202.75</v>
       </c>
       <c r="F690" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21175,11 +21175,11 @@
         </is>
       </c>
       <c r="E691" s="3" t="n">
-        <v>183.72</v>
+        <v>185.54</v>
       </c>
       <c r="F691" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21191,12 +21191,12 @@
       </c>
       <c r="B692" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="C692" s="2" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="D692" s="2" t="inlineStr">
@@ -21205,11 +21205,11 @@
         </is>
       </c>
       <c r="E692" s="3" t="n">
-        <v>180.28</v>
+        <v>184.22</v>
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21221,12 +21221,12 @@
       </c>
       <c r="B693" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C693" s="2" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="D693" s="2" t="inlineStr">
@@ -21235,11 +21235,11 @@
         </is>
       </c>
       <c r="E693" s="3" t="n">
-        <v>178.13</v>
+        <v>183.45</v>
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="B694" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C694" s="2" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="D694" s="2" t="inlineStr">
@@ -21265,11 +21265,11 @@
         </is>
       </c>
       <c r="E694" s="3" t="n">
-        <v>176.64</v>
+        <v>180.28</v>
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>171.09</v>
+        <v>178.8</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>151.02</v>
+        <v>155.8</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21371,25 +21371,25 @@
       </c>
       <c r="B698" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C698" s="2" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="D698" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E698" s="3" t="n">
-        <v>147.1</v>
+        <v>148.73</v>
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21401,12 +21401,12 @@
       </c>
       <c r="B699" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C699" s="2" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="D699" s="2" t="inlineStr">
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>145.79</v>
+        <v>147.73</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21431,12 +21431,12 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="D700" s="2" t="inlineStr">
@@ -21445,11 +21445,11 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>140.79</v>
+        <v>147.61</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21461,12 +21461,12 @@
       </c>
       <c r="B701" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C701" s="2" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="D701" s="2" t="inlineStr">
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>137.09</v>
+        <v>143.8</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21491,12 +21491,12 @@
       </c>
       <c r="B702" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C702" s="2" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="D702" s="2" t="inlineStr">
@@ -21505,11 +21505,11 @@
         </is>
       </c>
       <c r="E702" s="3" t="n">
-        <v>132.39</v>
+        <v>140.59</v>
       </c>
       <c r="F702" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>132.08</v>
+        <v>139.16</v>
       </c>
       <c r="F703" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21551,12 +21551,12 @@
       </c>
       <c r="B704" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C704" s="2" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="D704" s="2" t="inlineStr">
@@ -21565,11 +21565,11 @@
         </is>
       </c>
       <c r="E704" s="3" t="n">
-        <v>131.78</v>
+        <v>134.45</v>
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>131.46</v>
+        <v>133.95</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21611,12 +21611,12 @@
       </c>
       <c r="B706" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C706" s="2" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="D706" s="2" t="inlineStr">
@@ -21625,11 +21625,11 @@
         </is>
       </c>
       <c r="E706" s="3" t="n">
-        <v>131.31</v>
+        <v>133.43</v>
       </c>
       <c r="F706" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21641,12 +21641,12 @@
       </c>
       <c r="B707" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C707" s="2" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="D707" s="2" t="inlineStr">
@@ -21655,7 +21655,7 @@
         </is>
       </c>
       <c r="E707" s="3" t="n">
-        <v>131.04</v>
+        <v>132.39</v>
       </c>
       <c r="F707" s="2" t="inlineStr">
         <is>
@@ -21671,12 +21671,12 @@
       </c>
       <c r="B708" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C708" s="2" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="D708" s="2" t="inlineStr">
@@ -21685,11 +21685,11 @@
         </is>
       </c>
       <c r="E708" s="3" t="n">
-        <v>128.03</v>
+        <v>131.31</v>
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21701,12 +21701,12 @@
       </c>
       <c r="B709" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C709" s="2" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="D709" s="2" t="inlineStr">
@@ -21715,7 +21715,7 @@
         </is>
       </c>
       <c r="E709" s="3" t="n">
-        <v>126.03</v>
+        <v>131.04</v>
       </c>
       <c r="F709" s="2" t="inlineStr">
         <is>
@@ -21745,11 +21745,11 @@
         </is>
       </c>
       <c r="E710" s="3" t="n">
-        <v>125.27</v>
+        <v>129.58</v>
       </c>
       <c r="F710" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21761,12 +21761,12 @@
       </c>
       <c r="B711" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C711" s="2" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="D711" s="2" t="inlineStr">
@@ -21775,11 +21775,11 @@
         </is>
       </c>
       <c r="E711" s="3" t="n">
-        <v>124.24</v>
+        <v>129.24</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21805,11 +21805,11 @@
         </is>
       </c>
       <c r="E712" s="3" t="n">
-        <v>122.45</v>
+        <v>126.69</v>
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21821,12 +21821,12 @@
       </c>
       <c r="B713" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C713" s="2" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="D713" s="2" t="inlineStr">
@@ -21835,11 +21835,11 @@
         </is>
       </c>
       <c r="E713" s="3" t="n">
-        <v>120.86</v>
+        <v>126.03</v>
       </c>
       <c r="F713" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21851,12 +21851,12 @@
       </c>
       <c r="B714" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C714" s="2" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="D714" s="2" t="inlineStr">
@@ -21865,11 +21865,11 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>119.92</v>
+        <v>123.68</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21881,12 +21881,12 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="D715" s="2" t="inlineStr">
@@ -21895,11 +21895,11 @@
         </is>
       </c>
       <c r="E715" s="3" t="n">
-        <v>118.72</v>
+        <v>123.06</v>
       </c>
       <c r="F715" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21911,12 +21911,12 @@
       </c>
       <c r="B716" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C716" s="2" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="D716" s="2" t="inlineStr">
@@ -21925,11 +21925,11 @@
         </is>
       </c>
       <c r="E716" s="3" t="n">
-        <v>117.35</v>
+        <v>119.92</v>
       </c>
       <c r="F716" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B717" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C717" s="2" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="D717" s="2" t="inlineStr">
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>116.39</v>
+        <v>119.87</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -21971,12 +21971,12 @@
       </c>
       <c r="B718" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr">
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>113.25</v>
+        <v>119.12</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22015,11 +22015,11 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>112.96</v>
+        <v>114.7</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22031,25 +22031,25 @@
       </c>
       <c r="B720" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C720" s="2" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="D720" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E720" s="3" t="n">
-        <v>112.9</v>
+        <v>114.07</v>
       </c>
       <c r="F720" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22061,12 +22061,12 @@
       </c>
       <c r="B721" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C721" s="2" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="D721" s="2" t="inlineStr">
@@ -22075,11 +22075,11 @@
         </is>
       </c>
       <c r="E721" s="3" t="n">
-        <v>109.31</v>
+        <v>113.25</v>
       </c>
       <c r="F721" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22091,12 +22091,12 @@
       </c>
       <c r="B722" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C722" s="2" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="D722" s="2" t="inlineStr">
@@ -22105,11 +22105,11 @@
         </is>
       </c>
       <c r="E722" s="3" t="n">
-        <v>106.48</v>
+        <v>109.82</v>
       </c>
       <c r="F722" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22121,12 +22121,12 @@
       </c>
       <c r="B723" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C723" s="2" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="D723" s="2" t="inlineStr">
@@ -22135,11 +22135,11 @@
         </is>
       </c>
       <c r="E723" s="3" t="n">
-        <v>106.33</v>
+        <v>106.72</v>
       </c>
       <c r="F723" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22151,12 +22151,12 @@
       </c>
       <c r="B724" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C724" s="2" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="D724" s="2" t="inlineStr">
@@ -22165,11 +22165,11 @@
         </is>
       </c>
       <c r="E724" s="3" t="n">
-        <v>104.76</v>
+        <v>106.48</v>
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22195,11 +22195,11 @@
         </is>
       </c>
       <c r="E725" s="3" t="n">
-        <v>104.74</v>
+        <v>104.78</v>
       </c>
       <c r="F725" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22211,12 +22211,12 @@
       </c>
       <c r="B726" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C726" s="2" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="D726" s="2" t="inlineStr">
@@ -22225,11 +22225,11 @@
         </is>
       </c>
       <c r="E726" s="3" t="n">
-        <v>100.93</v>
+        <v>103.85</v>
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22241,12 +22241,12 @@
       </c>
       <c r="B727" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C727" s="2" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="D727" s="2" t="inlineStr">
@@ -22255,11 +22255,11 @@
         </is>
       </c>
       <c r="E727" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>101.39</v>
       </c>
       <c r="F727" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22271,12 +22271,12 @@
       </c>
       <c r="B728" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C728" s="2" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="D728" s="2" t="inlineStr">
@@ -22285,11 +22285,11 @@
         </is>
       </c>
       <c r="E728" s="3" t="n">
-        <v>99.55</v>
+        <v>100.93</v>
       </c>
       <c r="F728" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22301,12 +22301,12 @@
       </c>
       <c r="B729" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C729" s="2" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="D729" s="2" t="inlineStr">
@@ -22315,11 +22315,11 @@
         </is>
       </c>
       <c r="E729" s="3" t="n">
-        <v>98.95999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F729" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22331,12 +22331,12 @@
       </c>
       <c r="B730" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C730" s="2" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="D730" s="2" t="inlineStr">
@@ -22345,11 +22345,11 @@
         </is>
       </c>
       <c r="E730" s="3" t="n">
-        <v>97.44</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22361,12 +22361,12 @@
       </c>
       <c r="B731" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="D731" s="2" t="inlineStr">
@@ -22375,11 +22375,11 @@
         </is>
       </c>
       <c r="E731" s="3" t="n">
-        <v>93.51000000000001</v>
+        <v>97.44</v>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22405,11 +22405,11 @@
         </is>
       </c>
       <c r="E732" s="3" t="n">
-        <v>93.22</v>
+        <v>93.83</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22435,11 +22435,11 @@
         </is>
       </c>
       <c r="E733" s="3" t="n">
-        <v>92.13</v>
+        <v>92.27</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22451,12 +22451,12 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
@@ -22465,11 +22465,11 @@
         </is>
       </c>
       <c r="E734" s="3" t="n">
-        <v>89.79000000000001</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22481,25 +22481,25 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>89.48999999999999</v>
+        <v>90.08</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22511,12 +22511,12 @@
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
@@ -22525,7 +22525,7 @@
         </is>
       </c>
       <c r="E736" s="3" t="n">
-        <v>87.73</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F736" s="2" t="inlineStr">
         <is>
@@ -22541,25 +22541,25 @@
       </c>
       <c r="B737" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="D737" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E737" s="3" t="n">
-        <v>86.92</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22571,12 +22571,12 @@
       </c>
       <c r="B738" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="D738" s="2" t="inlineStr">
@@ -22585,7 +22585,7 @@
         </is>
       </c>
       <c r="E738" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>87.73</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
@@ -22601,12 +22601,12 @@
       </c>
       <c r="B739" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C739" s="2" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D739" s="2" t="inlineStr">
@@ -22615,11 +22615,11 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>86.15000000000001</v>
+        <v>87.64</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22631,12 +22631,12 @@
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
@@ -22645,11 +22645,11 @@
         </is>
       </c>
       <c r="E740" s="3" t="n">
-        <v>85.11</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22691,12 +22691,12 @@
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>79.67</v>
+        <v>81.73</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22721,12 +22721,12 @@
       </c>
       <c r="B743" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C743" s="2" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="D743" s="2" t="inlineStr">
@@ -22735,11 +22735,11 @@
         </is>
       </c>
       <c r="E743" s="3" t="n">
-        <v>79.63</v>
+        <v>80.87</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22751,12 +22751,12 @@
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D744" s="2" t="inlineStr">
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>79.44</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22781,12 +22781,12 @@
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr">
@@ -22795,11 +22795,11 @@
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>78.52</v>
+        <v>79.81</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22811,12 +22811,12 @@
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
@@ -22825,7 +22825,7 @@
         </is>
       </c>
       <c r="E746" s="3" t="n">
-        <v>77.84</v>
+        <v>79.44</v>
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
@@ -22855,11 +22855,11 @@
         </is>
       </c>
       <c r="E747" s="3" t="n">
-        <v>77.18000000000001</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="F747" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22871,12 +22871,12 @@
       </c>
       <c r="B748" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C748" s="2" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="D748" s="2" t="inlineStr">
@@ -22885,11 +22885,11 @@
         </is>
       </c>
       <c r="E748" s="3" t="n">
-        <v>75.94</v>
+        <v>76.11</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22901,12 +22901,12 @@
       </c>
       <c r="B749" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C749" s="2" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="D749" s="2" t="inlineStr">
@@ -22915,7 +22915,7 @@
         </is>
       </c>
       <c r="E749" s="3" t="n">
-        <v>75.81</v>
+        <v>75.94</v>
       </c>
       <c r="F749" s="2" t="inlineStr">
         <is>
@@ -22931,12 +22931,12 @@
       </c>
       <c r="B750" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C750" s="2" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="D750" s="2" t="inlineStr">
@@ -22945,7 +22945,7 @@
         </is>
       </c>
       <c r="E750" s="3" t="n">
-        <v>74.76000000000001</v>
+        <v>75.81</v>
       </c>
       <c r="F750" s="2" t="inlineStr">
         <is>
@@ -22961,25 +22961,25 @@
       </c>
       <c r="B751" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C751" s="2" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="D751" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E751" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="F751" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22991,12 +22991,12 @@
       </c>
       <c r="B752" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C752" s="2" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="D752" s="2" t="inlineStr">
@@ -23005,11 +23005,11 @@
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>73.63</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23021,21 +23021,21 @@
       </c>
       <c r="B753" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C753" s="2" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="D753" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E753" s="3" t="n">
-        <v>71.38</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F753" s="2" t="inlineStr">
         <is>
@@ -23051,12 +23051,12 @@
       </c>
       <c r="B754" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C754" s="2" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D754" s="2" t="inlineStr">
@@ -23065,11 +23065,11 @@
         </is>
       </c>
       <c r="E754" s="3" t="n">
-        <v>71.26000000000001</v>
+        <v>74.28</v>
       </c>
       <c r="F754" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23081,12 +23081,12 @@
       </c>
       <c r="B755" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C755" s="2" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="D755" s="2" t="inlineStr">
@@ -23095,11 +23095,11 @@
         </is>
       </c>
       <c r="E755" s="3" t="n">
-        <v>69.48999999999999</v>
+        <v>74.17</v>
       </c>
       <c r="F755" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23111,12 +23111,12 @@
       </c>
       <c r="B756" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C756" s="2" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="D756" s="2" t="inlineStr">
@@ -23125,11 +23125,11 @@
         </is>
       </c>
       <c r="E756" s="3" t="n">
-        <v>67.29000000000001</v>
+        <v>71.38</v>
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23141,12 +23141,12 @@
       </c>
       <c r="B757" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="C757" s="2" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="D757" s="2" t="inlineStr">
@@ -23155,11 +23155,11 @@
         </is>
       </c>
       <c r="E757" s="3" t="n">
-        <v>67.09</v>
+        <v>69.72</v>
       </c>
       <c r="F757" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23171,12 +23171,12 @@
       </c>
       <c r="B758" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C758" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="D758" s="2" t="inlineStr">
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>66.59</v>
+        <v>67.34</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23231,12 +23231,12 @@
       </c>
       <c r="B760" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C760" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="D760" s="2" t="inlineStr">
@@ -23245,11 +23245,11 @@
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>63.6</v>
+        <v>64.27</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23261,12 +23261,12 @@
       </c>
       <c r="B761" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C761" s="2" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="D761" s="2" t="inlineStr">
@@ -23275,11 +23275,11 @@
         </is>
       </c>
       <c r="E761" s="3" t="n">
-        <v>62.58</v>
+        <v>63.6</v>
       </c>
       <c r="F761" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23291,12 +23291,12 @@
       </c>
       <c r="B762" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C762" s="2" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="D762" s="2" t="inlineStr">
@@ -23305,11 +23305,11 @@
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>61.91</v>
+        <v>63.51</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23321,12 +23321,12 @@
       </c>
       <c r="B763" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C763" s="2" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="D763" s="2" t="inlineStr">
@@ -23335,11 +23335,11 @@
         </is>
       </c>
       <c r="E763" s="3" t="n">
-        <v>60.66</v>
+        <v>62.58</v>
       </c>
       <c r="F763" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23351,12 +23351,12 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="D764" s="2" t="inlineStr">
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>60.31</v>
+        <v>61.79</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23381,12 +23381,12 @@
       </c>
       <c r="B765" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C765" s="2" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="D765" s="2" t="inlineStr">
@@ -23395,11 +23395,11 @@
         </is>
       </c>
       <c r="E765" s="3" t="n">
-        <v>58.84</v>
+        <v>60.47</v>
       </c>
       <c r="F765" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23411,12 +23411,12 @@
       </c>
       <c r="B766" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C766" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D766" s="2" t="inlineStr">
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>58.62</v>
+        <v>60.31</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23455,11 +23455,11 @@
         </is>
       </c>
       <c r="E767" s="3" t="n">
-        <v>58.62</v>
+        <v>59.91</v>
       </c>
       <c r="F767" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23471,12 +23471,12 @@
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D768" s="2" t="inlineStr">
@@ -23485,11 +23485,11 @@
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>58.57</v>
+        <v>59.75</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23501,12 @@
       </c>
       <c r="B769" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C769" s="2" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="D769" s="2" t="inlineStr">
@@ -23515,11 +23515,11 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>58.05</v>
+        <v>59.69</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23531,25 +23531,25 @@
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E770" s="3" t="n">
-        <v>57.22</v>
+        <v>59.35</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23561,12 +23561,12 @@
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
@@ -23575,11 +23575,11 @@
         </is>
       </c>
       <c r="E771" s="3" t="n">
-        <v>56.5</v>
+        <v>58.93</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23591,12 +23591,12 @@
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -23605,11 +23605,11 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>56.35</v>
+        <v>58.42</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23621,12 +23621,12 @@
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="D773" s="2" t="inlineStr">
@@ -23635,11 +23635,11 @@
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>56.07</v>
+        <v>58.16</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23651,25 +23651,25 @@
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E774" s="3" t="n">
-        <v>55.54</v>
+        <v>57.22</v>
       </c>
       <c r="F774" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23681,12 +23681,12 @@
       </c>
       <c r="B775" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C775" s="2" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="D775" s="2" t="inlineStr">
@@ -23695,11 +23695,11 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>55.05</v>
+        <v>56.83</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23711,12 +23711,12 @@
       </c>
       <c r="B776" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C776" s="2" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="D776" s="2" t="inlineStr">
@@ -23725,11 +23725,11 @@
         </is>
       </c>
       <c r="E776" s="3" t="n">
-        <v>55</v>
+        <v>56.5</v>
       </c>
       <c r="F776" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23741,12 +23741,12 @@
       </c>
       <c r="B777" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C777" s="2" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="D777" s="2" t="inlineStr">
@@ -23755,11 +23755,11 @@
         </is>
       </c>
       <c r="E777" s="3" t="n">
-        <v>54.3</v>
+        <v>56.35</v>
       </c>
       <c r="F777" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23771,12 +23771,12 @@
       </c>
       <c r="B778" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C778" s="2" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="D778" s="2" t="inlineStr">
@@ -23785,7 +23785,7 @@
         </is>
       </c>
       <c r="E778" s="3" t="n">
-        <v>53.95</v>
+        <v>55.05</v>
       </c>
       <c r="F778" s="2" t="inlineStr">
         <is>
@@ -23801,12 +23801,12 @@
       </c>
       <c r="B779" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C779" s="2" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="D779" s="2" t="inlineStr">
@@ -23815,11 +23815,11 @@
         </is>
       </c>
       <c r="E779" s="3" t="n">
-        <v>53.36</v>
+        <v>53.95</v>
       </c>
       <c r="F779" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23845,11 +23845,11 @@
         </is>
       </c>
       <c r="E780" s="3" t="n">
-        <v>53.21</v>
+        <v>53.24</v>
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23861,12 +23861,12 @@
       </c>
       <c r="B781" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C781" s="2" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="D781" s="2" t="inlineStr">
@@ -23875,11 +23875,11 @@
         </is>
       </c>
       <c r="E781" s="3" t="n">
-        <v>52.66</v>
+        <v>53.05</v>
       </c>
       <c r="F781" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23891,12 +23891,12 @@
       </c>
       <c r="B782" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C782" s="2" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="D782" s="2" t="inlineStr">
@@ -23905,11 +23905,11 @@
         </is>
       </c>
       <c r="E782" s="3" t="n">
-        <v>52.57</v>
+        <v>52.75</v>
       </c>
       <c r="F782" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23921,12 +23921,12 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="D783" s="2" t="inlineStr">
@@ -23935,7 +23935,7 @@
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>52.12</v>
+        <v>52.57</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
@@ -23951,12 +23951,12 @@
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
@@ -23965,11 +23965,11 @@
         </is>
       </c>
       <c r="E784" s="3" t="n">
-        <v>50.49</v>
+        <v>52.12</v>
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23981,12 +23981,12 @@
       </c>
       <c r="B785" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C785" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D785" s="2" t="inlineStr">
@@ -23995,11 +23995,11 @@
         </is>
       </c>
       <c r="E785" s="3" t="n">
-        <v>50.3</v>
+        <v>51.86</v>
       </c>
       <c r="F785" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24011,12 +24011,12 @@
       </c>
       <c r="B786" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C786" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="D786" s="2" t="inlineStr">
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>49.55</v>
+        <v>51.7</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24041,12 +24041,12 @@
       </c>
       <c r="B787" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C787" s="2" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D787" s="2" t="inlineStr">
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>49.42</v>
+        <v>51.5</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24085,11 +24085,11 @@
         </is>
       </c>
       <c r="E788" s="3" t="n">
-        <v>49.33</v>
+        <v>51.31</v>
       </c>
       <c r="F788" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24101,12 +24101,12 @@
       </c>
       <c r="B789" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C789" s="2" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="D789" s="2" t="inlineStr">
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>48.04</v>
+        <v>49.09</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24131,12 +24131,12 @@
       </c>
       <c r="B790" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C790" s="2" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="D790" s="2" t="inlineStr">
@@ -24145,11 +24145,11 @@
         </is>
       </c>
       <c r="E790" s="3" t="n">
-        <v>47.99</v>
+        <v>48.04</v>
       </c>
       <c r="F790" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24161,12 +24161,12 @@
       </c>
       <c r="B791" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C791" s="2" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="D791" s="2" t="inlineStr">
@@ -24175,7 +24175,7 @@
         </is>
       </c>
       <c r="E791" s="3" t="n">
-        <v>47.5</v>
+        <v>47.99</v>
       </c>
       <c r="F791" s="2" t="inlineStr">
         <is>
@@ -24221,12 +24221,12 @@
       </c>
       <c r="B793" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C793" s="2" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="D793" s="2" t="inlineStr">
@@ -24235,11 +24235,11 @@
         </is>
       </c>
       <c r="E793" s="3" t="n">
-        <v>46.1</v>
+        <v>46.89</v>
       </c>
       <c r="F793" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24251,12 +24251,12 @@
       </c>
       <c r="B794" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C794" s="2" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D794" s="2" t="inlineStr">
@@ -24265,11 +24265,11 @@
         </is>
       </c>
       <c r="E794" s="3" t="n">
-        <v>45.68</v>
+        <v>46.47</v>
       </c>
       <c r="F794" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24281,12 +24281,12 @@
       </c>
       <c r="B795" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C795" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="D795" s="2" t="inlineStr">
@@ -24295,11 +24295,11 @@
         </is>
       </c>
       <c r="E795" s="3" t="n">
-        <v>44.52</v>
+        <v>46.1</v>
       </c>
       <c r="F795" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24311,12 +24311,12 @@
       </c>
       <c r="B796" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C796" s="2" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="D796" s="2" t="inlineStr">
@@ -24325,11 +24325,11 @@
         </is>
       </c>
       <c r="E796" s="3" t="n">
-        <v>44.33</v>
+        <v>45.68</v>
       </c>
       <c r="F796" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24341,12 +24341,12 @@
       </c>
       <c r="B797" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C797" s="2" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="D797" s="2" t="inlineStr">
@@ -24355,11 +24355,11 @@
         </is>
       </c>
       <c r="E797" s="3" t="n">
-        <v>44.19</v>
+        <v>44.68</v>
       </c>
       <c r="F797" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24385,11 +24385,11 @@
         </is>
       </c>
       <c r="E798" s="3" t="n">
-        <v>44.09</v>
+        <v>44.36</v>
       </c>
       <c r="F798" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="B799" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C799" s="2" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="D799" s="2" t="inlineStr">
@@ -24415,11 +24415,11 @@
         </is>
       </c>
       <c r="E799" s="3" t="n">
-        <v>43.42</v>
+        <v>44.19</v>
       </c>
       <c r="F799" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24431,12 +24431,12 @@
       </c>
       <c r="B800" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C800" s="2" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="D800" s="2" t="inlineStr">
@@ -24445,11 +24445,11 @@
         </is>
       </c>
       <c r="E800" s="3" t="n">
-        <v>39.46</v>
+        <v>41.1</v>
       </c>
       <c r="F800" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24461,12 +24461,12 @@
       </c>
       <c r="B801" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C801" s="2" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="D801" s="2" t="inlineStr">
@@ -24475,11 +24475,11 @@
         </is>
       </c>
       <c r="E801" s="3" t="n">
-        <v>39.41</v>
+        <v>40.27</v>
       </c>
       <c r="F801" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24491,12 +24491,12 @@
       </c>
       <c r="B802" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C802" s="2" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="D802" s="2" t="inlineStr">
@@ -24505,11 +24505,11 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>38.91</v>
+        <v>39.51</v>
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24521,12 +24521,12 @@
       </c>
       <c r="B803" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C803" s="2" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="D803" s="2" t="inlineStr">
@@ -24535,7 +24535,7 @@
         </is>
       </c>
       <c r="E803" s="3" t="n">
-        <v>38.88</v>
+        <v>39.41</v>
       </c>
       <c r="F803" s="2" t="inlineStr">
         <is>
@@ -24551,12 +24551,12 @@
       </c>
       <c r="B804" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C804" s="2" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="D804" s="2" t="inlineStr">
@@ -24565,11 +24565,11 @@
         </is>
       </c>
       <c r="E804" s="3" t="n">
-        <v>37.65</v>
+        <v>38.92</v>
       </c>
       <c r="F804" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24581,12 +24581,12 @@
       </c>
       <c r="B805" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C805" s="2" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="D805" s="2" t="inlineStr">
@@ -24595,11 +24595,11 @@
         </is>
       </c>
       <c r="E805" s="3" t="n">
-        <v>36.59</v>
+        <v>38.88</v>
       </c>
       <c r="F805" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24611,12 +24611,12 @@
       </c>
       <c r="B806" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C806" s="2" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="D806" s="2" t="inlineStr">
@@ -24625,7 +24625,7 @@
         </is>
       </c>
       <c r="E806" s="3" t="n">
-        <v>36.48</v>
+        <v>37.65</v>
       </c>
       <c r="F806" s="2" t="inlineStr">
         <is>
@@ -24641,12 +24641,12 @@
       </c>
       <c r="B807" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C807" s="2" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="D807" s="2" t="inlineStr">
@@ -24655,11 +24655,11 @@
         </is>
       </c>
       <c r="E807" s="3" t="n">
-        <v>36.31</v>
+        <v>36.59</v>
       </c>
       <c r="F807" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24671,12 +24671,12 @@
       </c>
       <c r="B808" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C808" s="2" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="D808" s="2" t="inlineStr">
@@ -24685,11 +24685,11 @@
         </is>
       </c>
       <c r="E808" s="3" t="n">
-        <v>35.44</v>
+        <v>36.48</v>
       </c>
       <c r="F808" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24701,12 +24701,12 @@
       </c>
       <c r="B809" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C809" s="2" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="D809" s="2" t="inlineStr">
@@ -24715,11 +24715,11 @@
         </is>
       </c>
       <c r="E809" s="3" t="n">
-        <v>35.16</v>
+        <v>36.43</v>
       </c>
       <c r="F809" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24731,12 +24731,12 @@
       </c>
       <c r="B810" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C810" s="2" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="D810" s="2" t="inlineStr">
@@ -24745,7 +24745,7 @@
         </is>
       </c>
       <c r="E810" s="3" t="n">
-        <v>34.1</v>
+        <v>36.31</v>
       </c>
       <c r="F810" s="2" t="inlineStr">
         <is>
@@ -24761,12 +24761,12 @@
       </c>
       <c r="B811" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C811" s="2" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D811" s="2" t="inlineStr">
@@ -24775,11 +24775,11 @@
         </is>
       </c>
       <c r="E811" s="3" t="n">
-        <v>34.05</v>
+        <v>35.34</v>
       </c>
       <c r="F811" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24791,12 +24791,12 @@
       </c>
       <c r="B812" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C812" s="2" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="D812" s="2" t="inlineStr">
@@ -24805,11 +24805,11 @@
         </is>
       </c>
       <c r="E812" s="3" t="n">
-        <v>32.72</v>
+        <v>34.1</v>
       </c>
       <c r="F812" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24821,12 +24821,12 @@
       </c>
       <c r="B813" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="C813" s="2" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="D813" s="2" t="inlineStr">
@@ -24835,7 +24835,7 @@
         </is>
       </c>
       <c r="E813" s="3" t="n">
-        <v>31.24</v>
+        <v>34.05</v>
       </c>
       <c r="F813" s="2" t="inlineStr">
         <is>
@@ -24851,12 +24851,12 @@
       </c>
       <c r="B814" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C814" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="D814" s="2" t="inlineStr">
@@ -24865,11 +24865,11 @@
         </is>
       </c>
       <c r="E814" s="3" t="n">
-        <v>30.64</v>
+        <v>31.32</v>
       </c>
       <c r="F814" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24881,12 +24881,12 @@
       </c>
       <c r="B815" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C815" s="2" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="D815" s="2" t="inlineStr">
@@ -24895,11 +24895,11 @@
         </is>
       </c>
       <c r="E815" s="3" t="n">
-        <v>30.08</v>
+        <v>31.26</v>
       </c>
       <c r="F815" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24911,12 +24911,12 @@
       </c>
       <c r="B816" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="C816" s="2" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="D816" s="2" t="inlineStr">
@@ -24925,11 +24925,11 @@
         </is>
       </c>
       <c r="E816" s="3" t="n">
-        <v>30.03</v>
+        <v>31.24</v>
       </c>
       <c r="F816" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24941,12 +24941,12 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="D817" s="2" t="inlineStr">
@@ -24955,11 +24955,11 @@
         </is>
       </c>
       <c r="E817" s="3" t="n">
-        <v>29.83</v>
+        <v>30.17</v>
       </c>
       <c r="F817" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24971,12 +24971,12 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="D818" s="2" t="inlineStr">
@@ -24985,11 +24985,11 @@
         </is>
       </c>
       <c r="E818" s="3" t="n">
-        <v>29.27</v>
+        <v>30.11</v>
       </c>
       <c r="F818" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -25001,12 +25001,12 @@
       </c>
       <c r="B819" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C819" s="2" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="D819" s="2" t="inlineStr">
@@ -25015,7 +25015,7 @@
         </is>
       </c>
       <c r="E819" s="3" t="n">
-        <v>28.85</v>
+        <v>29.27</v>
       </c>
       <c r="F819" s="2" t="inlineStr">
         <is>
@@ -25031,12 +25031,12 @@
       </c>
       <c r="B820" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="C820" s="2" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="D820" s="2" t="inlineStr">
@@ -25045,11 +25045,11 @@
         </is>
       </c>
       <c r="E820" s="3" t="n">
-        <v>28.46</v>
+        <v>28.91</v>
       </c>
       <c r="F820" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -25061,12 +25061,12 @@
       </c>
       <c r="B821" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C821" s="2" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="D821" s="2" t="inlineStr">
@@ -25075,11 +25075,11 @@
         </is>
       </c>
       <c r="E821" s="3" t="n">
-        <v>26.96</v>
+        <v>28.85</v>
       </c>
       <c r="F821" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25091,25 +25091,25 @@
       </c>
       <c r="B822" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C822" s="2" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="D822" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E822" s="3" t="n">
-        <v>26.15</v>
+        <v>28.43</v>
       </c>
       <c r="F822" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -25121,12 +25121,12 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="D823" s="2" t="inlineStr">
@@ -25135,11 +25135,11 @@
         </is>
       </c>
       <c r="E823" s="3" t="n">
-        <v>26.01</v>
+        <v>27.03</v>
       </c>
       <c r="F823" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -25151,12 +25151,12 @@
       </c>
       <c r="B824" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C824" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="D824" s="2" t="inlineStr">
@@ -25165,11 +25165,11 @@
         </is>
       </c>
       <c r="E824" s="3" t="n">
-        <v>25.79</v>
+        <v>26.22</v>
       </c>
       <c r="F824" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -25181,25 +25181,25 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="D825" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E825" s="3" t="n">
-        <v>25.34</v>
+        <v>26.15</v>
       </c>
       <c r="F825" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25211,12 +25211,12 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D826" s="2" t="inlineStr">
@@ -25225,11 +25225,11 @@
         </is>
       </c>
       <c r="E826" s="3" t="n">
-        <v>25.24</v>
+        <v>25.79</v>
       </c>
       <c r="F826" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25525,11 +25525,11 @@
         </is>
       </c>
       <c r="E836" s="3" t="n">
-        <v>20.13</v>
+        <v>20.57</v>
       </c>
       <c r="F836" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -25615,11 +25615,11 @@
         </is>
       </c>
       <c r="E839" s="3" t="n">
-        <v>18.47</v>
+        <v>19.52</v>
       </c>
       <c r="F839" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -25631,12 +25631,12 @@
       </c>
       <c r="B840" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C840" s="2" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="D840" s="2" t="inlineStr">
@@ -25645,11 +25645,11 @@
         </is>
       </c>
       <c r="E840" s="3" t="n">
-        <v>17.57</v>
+        <v>17.76</v>
       </c>
       <c r="F840" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -25661,12 +25661,12 @@
       </c>
       <c r="B841" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C841" s="2" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="D841" s="2" t="inlineStr">
@@ -25675,7 +25675,7 @@
         </is>
       </c>
       <c r="E841" s="3" t="n">
-        <v>17.49</v>
+        <v>17.57</v>
       </c>
       <c r="F841" s="2" t="inlineStr">
         <is>
@@ -25691,12 +25691,12 @@
       </c>
       <c r="B842" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C842" s="2" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="D842" s="2" t="inlineStr">
@@ -25705,7 +25705,7 @@
         </is>
       </c>
       <c r="E842" s="3" t="n">
-        <v>17.45</v>
+        <v>17.49</v>
       </c>
       <c r="F842" s="2" t="inlineStr">
         <is>
@@ -25721,12 +25721,12 @@
       </c>
       <c r="B843" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C843" s="2" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="D843" s="2" t="inlineStr">
@@ -25735,11 +25735,11 @@
         </is>
       </c>
       <c r="E843" s="3" t="n">
-        <v>16.45</v>
+        <v>17.45</v>
       </c>
       <c r="F843" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25765,11 +25765,11 @@
         </is>
       </c>
       <c r="E844" s="3" t="n">
-        <v>15.81</v>
+        <v>15.97</v>
       </c>
       <c r="F844" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -25931,12 +25931,12 @@
       </c>
       <c r="B850" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C850" s="2" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="D850" s="2" t="inlineStr">
@@ -25945,11 +25945,11 @@
         </is>
       </c>
       <c r="E850" s="3" t="n">
-        <v>10.75</v>
+        <v>11.69</v>
       </c>
       <c r="F850" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -25961,12 +25961,12 @@
       </c>
       <c r="B851" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C851" s="2" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="D851" s="2" t="inlineStr">
@@ -25975,11 +25975,11 @@
         </is>
       </c>
       <c r="E851" s="3" t="n">
-        <v>10.4</v>
+        <v>11.34</v>
       </c>
       <c r="F851" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -25991,12 +25991,12 @@
       </c>
       <c r="B852" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413801QJB</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C852" s="2" t="inlineStr">
         <is>
-          <t>812824</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="D852" s="2" t="inlineStr">
@@ -26005,11 +26005,11 @@
         </is>
       </c>
       <c r="E852" s="3" t="n">
-        <v>10.08</v>
+        <v>10.75</v>
       </c>
       <c r="F852" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26021,12 +26021,12 @@
       </c>
       <c r="B853" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C853" s="2" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D853" s="2" t="inlineStr">
@@ -26035,11 +26035,11 @@
         </is>
       </c>
       <c r="E853" s="3" t="n">
-        <v>10.07</v>
+        <v>10.7</v>
       </c>
       <c r="F853" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -26051,12 +26051,12 @@
       </c>
       <c r="B854" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="C854" s="2" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>812824</t>
         </is>
       </c>
       <c r="D854" s="2" t="inlineStr">
@@ -26065,11 +26065,11 @@
         </is>
       </c>
       <c r="E854" s="3" t="n">
-        <v>9.869999999999999</v>
+        <v>10.48</v>
       </c>
       <c r="F854" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -26081,12 +26081,12 @@
       </c>
       <c r="B855" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C855" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="D855" s="2" t="inlineStr">
@@ -26095,11 +26095,11 @@
         </is>
       </c>
       <c r="E855" s="3" t="n">
-        <v>9.67</v>
+        <v>10.07</v>
       </c>
       <c r="F855" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26411,12 +26411,12 @@
       </c>
       <c r="B866" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413772977</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C866" s="2" t="inlineStr">
         <is>
-          <t>812841</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="D866" s="2" t="inlineStr">
@@ -26425,11 +26425,11 @@
         </is>
       </c>
       <c r="E866" s="3" t="n">
-        <v>1.76</v>
+        <v>2.5</v>
       </c>
       <c r="F866" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -26441,12 +26441,12 @@
       </c>
       <c r="B867" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413780XFH</t>
+          <t>KIT4M05413772977</t>
         </is>
       </c>
       <c r="C867" s="2" t="inlineStr">
         <is>
-          <t>812833</t>
+          <t>812841</t>
         </is>
       </c>
       <c r="D867" s="2" t="inlineStr">
@@ -26455,11 +26455,11 @@
         </is>
       </c>
       <c r="E867" s="3" t="n">
-        <v>1.36</v>
+        <v>1.76</v>
       </c>
       <c r="F867" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26471,12 +26471,12 @@
       </c>
       <c r="B868" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="C868" s="2" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>812833</t>
         </is>
       </c>
       <c r="D868" s="2" t="inlineStr">
@@ -26485,11 +26485,11 @@
         </is>
       </c>
       <c r="E868" s="3" t="n">
-        <v>0.98</v>
+        <v>1.55</v>
       </c>
       <c r="F868" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2184.28</v>
+        <v>2197.76</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -19811,12 +19811,12 @@
       </c>
       <c r="B646" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073915XX6</t>
+          <t>KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="C646" s="2" t="inlineStr">
         <is>
-          <t>814643</t>
+          <t>816227</t>
         </is>
       </c>
       <c r="D646" s="2" t="inlineStr">
@@ -19825,11 +19825,11 @@
         </is>
       </c>
       <c r="E646" s="3" t="n">
-        <v>1493</v>
+        <v>1503.58</v>
       </c>
       <c r="F646" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -19841,12 +19841,12 @@
       </c>
       <c r="B647" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084593R9F</t>
+          <t>KIT4P00073915XX6</t>
         </is>
       </c>
       <c r="C647" s="2" t="inlineStr">
         <is>
-          <t>816227</t>
+          <t>814643</t>
         </is>
       </c>
       <c r="D647" s="2" t="inlineStr">
@@ -19855,11 +19855,11 @@
         </is>
       </c>
       <c r="E647" s="3" t="n">
-        <v>1469.32</v>
+        <v>1493</v>
       </c>
       <c r="F647" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>921.52</v>
+        <v>926.78</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -19945,11 +19945,11 @@
         </is>
       </c>
       <c r="E650" s="3" t="n">
-        <v>839.87</v>
+        <v>852.04</v>
       </c>
       <c r="F650" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20005,11 +20005,11 @@
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>676.47</v>
+        <v>682.47</v>
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20065,11 +20065,11 @@
         </is>
       </c>
       <c r="E654" s="3" t="n">
-        <v>592.1</v>
+        <v>593.62</v>
       </c>
       <c r="F654" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20095,11 +20095,11 @@
         </is>
       </c>
       <c r="E655" s="3" t="n">
-        <v>586.64</v>
+        <v>586.76</v>
       </c>
       <c r="F655" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20125,11 +20125,11 @@
         </is>
       </c>
       <c r="E656" s="3" t="n">
-        <v>581.29</v>
+        <v>583.1799999999999</v>
       </c>
       <c r="F656" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20155,11 +20155,11 @@
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>532.12</v>
+        <v>541.5599999999999</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20171,25 +20171,25 @@
       </c>
       <c r="B658" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4P000739257CR</t>
         </is>
       </c>
       <c r="C658" s="2" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>814609</t>
         </is>
       </c>
       <c r="D658" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>526.3</v>
+        <v>538.85</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20201,12 +20201,12 @@
       </c>
       <c r="B659" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C659" s="2" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="D659" s="2" t="inlineStr">
@@ -20215,11 +20215,11 @@
         </is>
       </c>
       <c r="E659" s="3" t="n">
-        <v>513.88</v>
+        <v>526.49</v>
       </c>
       <c r="F659" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20231,25 +20231,25 @@
       </c>
       <c r="B660" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739257CR</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C660" s="2" t="inlineStr">
         <is>
-          <t>814609</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="D660" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E660" s="3" t="n">
-        <v>512.21</v>
+        <v>513.88</v>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20305,11 +20305,11 @@
         </is>
       </c>
       <c r="E662" s="3" t="n">
-        <v>493.34</v>
+        <v>496.57</v>
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20425,11 +20425,11 @@
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>459.82</v>
+        <v>461.07</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20455,11 +20455,11 @@
         </is>
       </c>
       <c r="E667" s="3" t="n">
-        <v>442.6</v>
+        <v>444.01</v>
       </c>
       <c r="F667" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20485,11 +20485,11 @@
         </is>
       </c>
       <c r="E668" s="3" t="n">
-        <v>436.67</v>
+        <v>437.84</v>
       </c>
       <c r="F668" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20515,11 +20515,11 @@
         </is>
       </c>
       <c r="E669" s="3" t="n">
-        <v>419.61</v>
+        <v>423.21</v>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20605,11 +20605,11 @@
         </is>
       </c>
       <c r="E672" s="3" t="n">
-        <v>372.44</v>
+        <v>376.43</v>
       </c>
       <c r="F672" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20635,11 +20635,11 @@
         </is>
       </c>
       <c r="E673" s="3" t="n">
-        <v>328.15</v>
+        <v>330.28</v>
       </c>
       <c r="F673" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20665,11 +20665,11 @@
         </is>
       </c>
       <c r="E674" s="3" t="n">
-        <v>324.92</v>
+        <v>326.28</v>
       </c>
       <c r="F674" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20695,11 +20695,11 @@
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>316.07</v>
+        <v>317.29</v>
       </c>
       <c r="F675" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20711,25 +20711,25 @@
       </c>
       <c r="B676" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C676" s="2" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="D676" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>304.71</v>
+        <v>309.15</v>
       </c>
       <c r="F676" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20741,25 +20741,25 @@
       </c>
       <c r="B677" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C677" s="2" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="D677" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>301.88</v>
+        <v>305.3</v>
       </c>
       <c r="F677" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20785,11 +20785,11 @@
         </is>
       </c>
       <c r="E678" s="3" t="n">
-        <v>290.91</v>
+        <v>294.08</v>
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>267.96</v>
+        <v>268.31</v>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -20905,11 +20905,11 @@
         </is>
       </c>
       <c r="E682" s="3" t="n">
-        <v>263.81</v>
+        <v>267.23</v>
       </c>
       <c r="F682" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21055,11 +21055,11 @@
         </is>
       </c>
       <c r="E687" s="3" t="n">
-        <v>208.19</v>
+        <v>210.11</v>
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21085,11 +21085,11 @@
         </is>
       </c>
       <c r="E688" s="3" t="n">
-        <v>204.08</v>
+        <v>205.87</v>
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21101,12 +21101,12 @@
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="D689" s="2" t="inlineStr">
@@ -21115,11 +21115,11 @@
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>204</v>
+        <v>204.92</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21131,12 +21131,12 @@
       </c>
       <c r="B690" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C690" s="2" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="D690" s="2" t="inlineStr">
@@ -21145,11 +21145,11 @@
         </is>
       </c>
       <c r="E690" s="3" t="n">
-        <v>202.75</v>
+        <v>204.85</v>
       </c>
       <c r="F690" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21175,11 +21175,11 @@
         </is>
       </c>
       <c r="E691" s="3" t="n">
-        <v>185.54</v>
+        <v>187.03</v>
       </c>
       <c r="F691" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21205,11 +21205,11 @@
         </is>
       </c>
       <c r="E692" s="3" t="n">
-        <v>184.22</v>
+        <v>185.64</v>
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21235,11 +21235,11 @@
         </is>
       </c>
       <c r="E693" s="3" t="n">
-        <v>183.45</v>
+        <v>184.42</v>
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21251,25 +21251,25 @@
       </c>
       <c r="B694" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C694" s="2" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="D694" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E694" s="3" t="n">
-        <v>180.28</v>
+        <v>181.15</v>
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21281,25 +21281,25 @@
       </c>
       <c r="B695" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C695" s="2" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="D695" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>178.8</v>
+        <v>180.28</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21311,12 +21311,12 @@
       </c>
       <c r="B696" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C696" s="2" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="D696" s="2" t="inlineStr">
@@ -21325,11 +21325,11 @@
         </is>
       </c>
       <c r="E696" s="3" t="n">
-        <v>158.82</v>
+        <v>161.61</v>
       </c>
       <c r="F696" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21341,12 +21341,12 @@
       </c>
       <c r="B697" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C697" s="2" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="D697" s="2" t="inlineStr">
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>155.8</v>
+        <v>158.82</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="E698" s="3" t="n">
-        <v>148.73</v>
+        <v>157.78</v>
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21401,12 +21401,12 @@
       </c>
       <c r="B699" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C699" s="2" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="D699" s="2" t="inlineStr">
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>147.73</v>
+        <v>147.97</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21431,12 +21431,12 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="D700" s="2" t="inlineStr">
@@ -21445,7 +21445,7 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>147.61</v>
+        <v>147.73</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>143.8</v>
+        <v>145.59</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21505,11 +21505,11 @@
         </is>
       </c>
       <c r="E702" s="3" t="n">
-        <v>140.59</v>
+        <v>140.73</v>
       </c>
       <c r="F702" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>139.16</v>
+        <v>140.69</v>
       </c>
       <c r="F703" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21565,11 +21565,11 @@
         </is>
       </c>
       <c r="E704" s="3" t="n">
-        <v>134.45</v>
+        <v>138.35</v>
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>133.95</v>
+        <v>134.58</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21625,11 +21625,11 @@
         </is>
       </c>
       <c r="E706" s="3" t="n">
-        <v>133.43</v>
+        <v>134.19</v>
       </c>
       <c r="F706" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21745,11 +21745,11 @@
         </is>
       </c>
       <c r="E710" s="3" t="n">
-        <v>129.58</v>
+        <v>130.26</v>
       </c>
       <c r="F710" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21805,11 +21805,11 @@
         </is>
       </c>
       <c r="E712" s="3" t="n">
-        <v>126.69</v>
+        <v>128.77</v>
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21865,11 +21865,11 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>123.68</v>
+        <v>125.25</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21895,11 +21895,11 @@
         </is>
       </c>
       <c r="E715" s="3" t="n">
-        <v>123.06</v>
+        <v>123.24</v>
       </c>
       <c r="F715" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21911,12 +21911,12 @@
       </c>
       <c r="B716" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C716" s="2" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="D716" s="2" t="inlineStr">
@@ -21925,11 +21925,11 @@
         </is>
       </c>
       <c r="E716" s="3" t="n">
-        <v>119.92</v>
+        <v>120.41</v>
       </c>
       <c r="F716" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B717" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C717" s="2" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="D717" s="2" t="inlineStr">
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>119.87</v>
+        <v>119.92</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22015,11 +22015,11 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>114.7</v>
+        <v>114.8</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -22105,11 +22105,11 @@
         </is>
       </c>
       <c r="E722" s="3" t="n">
-        <v>109.82</v>
+        <v>111.07</v>
       </c>
       <c r="F722" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -22135,11 +22135,11 @@
         </is>
       </c>
       <c r="E723" s="3" t="n">
-        <v>106.72</v>
+        <v>106.73</v>
       </c>
       <c r="F723" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -22195,11 +22195,11 @@
         </is>
       </c>
       <c r="E725" s="3" t="n">
-        <v>104.78</v>
+        <v>104.93</v>
       </c>
       <c r="F725" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -22225,11 +22225,11 @@
         </is>
       </c>
       <c r="E726" s="3" t="n">
-        <v>103.85</v>
+        <v>104.6</v>
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -22255,11 +22255,11 @@
         </is>
       </c>
       <c r="E727" s="3" t="n">
-        <v>101.39</v>
+        <v>102.77</v>
       </c>
       <c r="F727" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -22301,12 +22301,12 @@
       </c>
       <c r="B729" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C729" s="2" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="D729" s="2" t="inlineStr">
@@ -22315,11 +22315,11 @@
         </is>
       </c>
       <c r="E729" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="F729" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -22331,12 +22331,12 @@
       </c>
       <c r="B730" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C730" s="2" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="D730" s="2" t="inlineStr">
@@ -22345,11 +22345,11 @@
         </is>
       </c>
       <c r="E730" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22391,12 +22391,12 @@
       </c>
       <c r="B732" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="D732" s="2" t="inlineStr">
@@ -22405,11 +22405,11 @@
         </is>
       </c>
       <c r="E732" s="3" t="n">
-        <v>93.83</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -22421,12 +22421,12 @@
       </c>
       <c r="B733" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D733" s="2" t="inlineStr">
@@ -22435,7 +22435,7 @@
         </is>
       </c>
       <c r="E733" s="3" t="n">
-        <v>92.27</v>
+        <v>93.83</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
@@ -22451,12 +22451,12 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
@@ -22465,7 +22465,7 @@
         </is>
       </c>
       <c r="E734" s="3" t="n">
-        <v>90.29000000000001</v>
+        <v>92.27</v>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
@@ -22481,12 +22481,12 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
@@ -22495,11 +22495,11 @@
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>90.08</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -22571,12 +22571,12 @@
       </c>
       <c r="B738" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D738" s="2" t="inlineStr">
@@ -22585,11 +22585,11 @@
         </is>
       </c>
       <c r="E738" s="3" t="n">
-        <v>87.73</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -22601,12 +22601,12 @@
       </c>
       <c r="B739" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C739" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="D739" s="2" t="inlineStr">
@@ -22615,11 +22615,11 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>87.64</v>
+        <v>87.73</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22691,12 +22691,12 @@
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>81.73</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -22721,12 +22721,12 @@
       </c>
       <c r="B743" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C743" s="2" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="D743" s="2" t="inlineStr">
@@ -22735,7 +22735,7 @@
         </is>
       </c>
       <c r="E743" s="3" t="n">
-        <v>80.87</v>
+        <v>81.73</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
@@ -22751,12 +22751,12 @@
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="D744" s="2" t="inlineStr">
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>80.70999999999999</v>
+        <v>80.88</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -22841,12 +22841,12 @@
       </c>
       <c r="B747" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C747" s="2" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="D747" s="2" t="inlineStr">
@@ -22855,11 +22855,11 @@
         </is>
       </c>
       <c r="E747" s="3" t="n">
-        <v>78.01000000000001</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="F747" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -22871,12 +22871,12 @@
       </c>
       <c r="B748" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C748" s="2" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="D748" s="2" t="inlineStr">
@@ -22885,11 +22885,11 @@
         </is>
       </c>
       <c r="E748" s="3" t="n">
-        <v>76.11</v>
+        <v>78.02</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -22901,12 +22901,12 @@
       </c>
       <c r="B749" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C749" s="2" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="D749" s="2" t="inlineStr">
@@ -22915,11 +22915,11 @@
         </is>
       </c>
       <c r="E749" s="3" t="n">
-        <v>75.94</v>
+        <v>76.16</v>
       </c>
       <c r="F749" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -22961,12 +22961,12 @@
       </c>
       <c r="B751" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C751" s="2" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D751" s="2" t="inlineStr">
@@ -22975,11 +22975,11 @@
         </is>
       </c>
       <c r="E751" s="3" t="n">
-        <v>75.18000000000001</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="F751" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -22991,12 +22991,12 @@
       </c>
       <c r="B752" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C752" s="2" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="D752" s="2" t="inlineStr">
@@ -23005,11 +23005,11 @@
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>74.76000000000001</v>
+        <v>75.75</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -23021,21 +23021,21 @@
       </c>
       <c r="B753" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C753" s="2" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="D753" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E753" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="F753" s="2" t="inlineStr">
         <is>
@@ -23051,25 +23051,25 @@
       </c>
       <c r="B754" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C754" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="D754" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E754" s="3" t="n">
-        <v>74.28</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F754" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23155,11 +23155,11 @@
         </is>
       </c>
       <c r="E757" s="3" t="n">
-        <v>69.72</v>
+        <v>69.83</v>
       </c>
       <c r="F757" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>67.34</v>
+        <v>67.39</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -23201,12 +23201,12 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="D759" s="2" t="inlineStr">
@@ -23215,11 +23215,11 @@
         </is>
       </c>
       <c r="E759" s="3" t="n">
-        <v>64.33</v>
+        <v>65.89</v>
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -23231,12 +23231,12 @@
       </c>
       <c r="B760" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C760" s="2" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="D760" s="2" t="inlineStr">
@@ -23245,11 +23245,11 @@
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>64.27</v>
+        <v>65.09</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -23261,12 +23261,12 @@
       </c>
       <c r="B761" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C761" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="D761" s="2" t="inlineStr">
@@ -23275,11 +23275,11 @@
         </is>
       </c>
       <c r="E761" s="3" t="n">
-        <v>63.6</v>
+        <v>64.33</v>
       </c>
       <c r="F761" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23291,12 +23291,12 @@
       </c>
       <c r="B762" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C762" s="2" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="D762" s="2" t="inlineStr">
@@ -23305,11 +23305,11 @@
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>63.51</v>
+        <v>63.6</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23351,12 +23351,12 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="D764" s="2" t="inlineStr">
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>61.79</v>
+        <v>62.22</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -23381,12 +23381,12 @@
       </c>
       <c r="B765" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C765" s="2" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="D765" s="2" t="inlineStr">
@@ -23395,7 +23395,7 @@
         </is>
       </c>
       <c r="E765" s="3" t="n">
-        <v>60.47</v>
+        <v>61.79</v>
       </c>
       <c r="F765" s="2" t="inlineStr">
         <is>
@@ -23411,12 +23411,12 @@
       </c>
       <c r="B766" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C766" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="D766" s="2" t="inlineStr">
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>60.31</v>
+        <v>60.87</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -23441,12 +23441,12 @@
       </c>
       <c r="B767" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C767" s="2" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="D767" s="2" t="inlineStr">
@@ -23455,11 +23455,11 @@
         </is>
       </c>
       <c r="E767" s="3" t="n">
-        <v>59.91</v>
+        <v>60.68</v>
       </c>
       <c r="F767" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -23471,12 +23471,12 @@
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D768" s="2" t="inlineStr">
@@ -23485,11 +23485,11 @@
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>59.75</v>
+        <v>60.31</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23501,12 @@
       </c>
       <c r="B769" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C769" s="2" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="D769" s="2" t="inlineStr">
@@ -23515,11 +23515,11 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>59.69</v>
+        <v>60.3</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -23531,12 +23531,12 @@
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
@@ -23545,7 +23545,7 @@
         </is>
       </c>
       <c r="E770" s="3" t="n">
-        <v>59.35</v>
+        <v>59.75</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
@@ -23591,12 +23591,12 @@
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -23605,11 +23605,11 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>58.42</v>
+        <v>58.85</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -23621,12 +23621,12 @@
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="D773" s="2" t="inlineStr">
@@ -23635,11 +23635,11 @@
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>58.16</v>
+        <v>58.47</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -23831,12 +23831,12 @@
       </c>
       <c r="B780" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C780" s="2" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="D780" s="2" t="inlineStr">
@@ -23845,11 +23845,11 @@
         </is>
       </c>
       <c r="E780" s="3" t="n">
-        <v>53.24</v>
+        <v>53.65</v>
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -23861,12 +23861,12 @@
       </c>
       <c r="B781" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C781" s="2" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="D781" s="2" t="inlineStr">
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="E781" s="3" t="n">
-        <v>53.05</v>
+        <v>53.24</v>
       </c>
       <c r="F781" s="2" t="inlineStr">
         <is>
@@ -23891,12 +23891,12 @@
       </c>
       <c r="B782" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C782" s="2" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D782" s="2" t="inlineStr">
@@ -23905,11 +23905,11 @@
         </is>
       </c>
       <c r="E782" s="3" t="n">
-        <v>52.75</v>
+        <v>53.15</v>
       </c>
       <c r="F782" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -23921,12 +23921,12 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="D783" s="2" t="inlineStr">
@@ -23935,11 +23935,11 @@
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>52.57</v>
+        <v>52.93</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -23951,12 +23951,12 @@
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
@@ -23965,11 +23965,11 @@
         </is>
       </c>
       <c r="E784" s="3" t="n">
-        <v>52.12</v>
+        <v>52.76</v>
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -23981,12 +23981,12 @@
       </c>
       <c r="B785" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C785" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="D785" s="2" t="inlineStr">
@@ -23995,11 +23995,11 @@
         </is>
       </c>
       <c r="E785" s="3" t="n">
-        <v>51.86</v>
+        <v>52.57</v>
       </c>
       <c r="F785" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24011,12 +24011,12 @@
       </c>
       <c r="B786" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C786" s="2" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="D786" s="2" t="inlineStr">
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>51.7</v>
+        <v>52.12</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24041,12 +24041,12 @@
       </c>
       <c r="B787" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C787" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="D787" s="2" t="inlineStr">
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>51.5</v>
+        <v>51.71</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -24071,12 +24071,12 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D788" s="2" t="inlineStr">
@@ -24085,7 +24085,7 @@
         </is>
       </c>
       <c r="E788" s="3" t="n">
-        <v>51.31</v>
+        <v>51.5</v>
       </c>
       <c r="F788" s="2" t="inlineStr">
         <is>
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>49.09</v>
+        <v>49.22</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -24191,12 +24191,12 @@
       </c>
       <c r="B792" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C792" s="2" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D792" s="2" t="inlineStr">
@@ -24205,11 +24205,11 @@
         </is>
       </c>
       <c r="E792" s="3" t="n">
-        <v>47.23</v>
+        <v>47.84</v>
       </c>
       <c r="F792" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -24235,11 +24235,11 @@
         </is>
       </c>
       <c r="E793" s="3" t="n">
-        <v>46.89</v>
+        <v>47.32</v>
       </c>
       <c r="F793" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -24251,12 +24251,12 @@
       </c>
       <c r="B794" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C794" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="D794" s="2" t="inlineStr">
@@ -24265,11 +24265,11 @@
         </is>
       </c>
       <c r="E794" s="3" t="n">
-        <v>46.47</v>
+        <v>47.23</v>
       </c>
       <c r="F794" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24341,12 +24341,12 @@
       </c>
       <c r="B797" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C797" s="2" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="D797" s="2" t="inlineStr">
@@ -24355,11 +24355,11 @@
         </is>
       </c>
       <c r="E797" s="3" t="n">
-        <v>44.68</v>
+        <v>45.53</v>
       </c>
       <c r="F797" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -24371,12 +24371,12 @@
       </c>
       <c r="B798" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C798" s="2" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="D798" s="2" t="inlineStr">
@@ -24385,7 +24385,7 @@
         </is>
       </c>
       <c r="E798" s="3" t="n">
-        <v>44.36</v>
+        <v>44.68</v>
       </c>
       <c r="F798" s="2" t="inlineStr">
         <is>
@@ -24445,11 +24445,11 @@
         </is>
       </c>
       <c r="E800" s="3" t="n">
-        <v>41.1</v>
+        <v>41.34</v>
       </c>
       <c r="F800" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -24475,11 +24475,11 @@
         </is>
       </c>
       <c r="E801" s="3" t="n">
-        <v>40.27</v>
+        <v>40.43</v>
       </c>
       <c r="F801" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -24565,11 +24565,11 @@
         </is>
       </c>
       <c r="E804" s="3" t="n">
-        <v>38.92</v>
+        <v>38.97</v>
       </c>
       <c r="F804" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -24671,12 +24671,12 @@
       </c>
       <c r="B808" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C808" s="2" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="D808" s="2" t="inlineStr">
@@ -24685,11 +24685,11 @@
         </is>
       </c>
       <c r="E808" s="3" t="n">
-        <v>36.48</v>
+        <v>36.5</v>
       </c>
       <c r="F808" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -24701,12 +24701,12 @@
       </c>
       <c r="B809" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C809" s="2" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="D809" s="2" t="inlineStr">
@@ -24715,11 +24715,11 @@
         </is>
       </c>
       <c r="E809" s="3" t="n">
-        <v>36.43</v>
+        <v>36.48</v>
       </c>
       <c r="F809" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24775,11 +24775,11 @@
         </is>
       </c>
       <c r="E811" s="3" t="n">
-        <v>35.34</v>
+        <v>36.05</v>
       </c>
       <c r="F811" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -24955,11 +24955,11 @@
         </is>
       </c>
       <c r="E817" s="3" t="n">
-        <v>30.17</v>
+        <v>30.47</v>
       </c>
       <c r="F817" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -25045,11 +25045,11 @@
         </is>
       </c>
       <c r="E820" s="3" t="n">
-        <v>28.91</v>
+        <v>29.1</v>
       </c>
       <c r="F820" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -25105,11 +25105,11 @@
         </is>
       </c>
       <c r="E822" s="3" t="n">
-        <v>28.43</v>
+        <v>28.46</v>
       </c>
       <c r="F822" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -25165,11 +25165,11 @@
         </is>
       </c>
       <c r="E824" s="3" t="n">
-        <v>26.22</v>
+        <v>26.3</v>
       </c>
       <c r="F824" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -25211,12 +25211,12 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="D826" s="2" t="inlineStr">
@@ -25225,11 +25225,11 @@
         </is>
       </c>
       <c r="E826" s="3" t="n">
-        <v>25.79</v>
+        <v>26.14</v>
       </c>
       <c r="F826" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -25241,12 +25241,12 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D827" s="2" t="inlineStr">
@@ -25255,7 +25255,7 @@
         </is>
       </c>
       <c r="E827" s="3" t="n">
-        <v>24.1</v>
+        <v>25.79</v>
       </c>
       <c r="F827" s="2" t="inlineStr">
         <is>
@@ -25271,12 +25271,12 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="D828" s="2" t="inlineStr">
@@ -25285,7 +25285,7 @@
         </is>
       </c>
       <c r="E828" s="3" t="n">
-        <v>23.74</v>
+        <v>24.1</v>
       </c>
       <c r="F828" s="2" t="inlineStr">
         <is>
@@ -25301,12 +25301,12 @@
       </c>
       <c r="B829" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C829" s="2" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="D829" s="2" t="inlineStr">
@@ -25315,7 +25315,7 @@
         </is>
       </c>
       <c r="E829" s="3" t="n">
-        <v>22.39</v>
+        <v>23.74</v>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
@@ -25331,12 +25331,12 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="D830" s="2" t="inlineStr">
@@ -25345,7 +25345,7 @@
         </is>
       </c>
       <c r="E830" s="3" t="n">
-        <v>22.3</v>
+        <v>22.39</v>
       </c>
       <c r="F830" s="2" t="inlineStr">
         <is>
@@ -25361,12 +25361,12 @@
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C831" s="2" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D831" s="2" t="inlineStr">
@@ -25375,7 +25375,7 @@
         </is>
       </c>
       <c r="E831" s="3" t="n">
-        <v>21.69</v>
+        <v>22.3</v>
       </c>
       <c r="F831" s="2" t="inlineStr">
         <is>
@@ -25391,12 +25391,12 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="D832" s="2" t="inlineStr">
@@ -25405,7 +25405,7 @@
         </is>
       </c>
       <c r="E832" s="3" t="n">
-        <v>21.21</v>
+        <v>21.69</v>
       </c>
       <c r="F832" s="2" t="inlineStr">
         <is>
@@ -25421,12 +25421,12 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="D833" s="2" t="inlineStr">
@@ -25435,7 +25435,7 @@
         </is>
       </c>
       <c r="E833" s="3" t="n">
-        <v>21.17</v>
+        <v>21.21</v>
       </c>
       <c r="F833" s="2" t="inlineStr">
         <is>
@@ -25451,12 +25451,12 @@
       </c>
       <c r="B834" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C834" s="2" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="D834" s="2" t="inlineStr">
@@ -25465,7 +25465,7 @@
         </is>
       </c>
       <c r="E834" s="3" t="n">
-        <v>20.98</v>
+        <v>21.17</v>
       </c>
       <c r="F834" s="2" t="inlineStr">
         <is>
@@ -25481,12 +25481,12 @@
       </c>
       <c r="B835" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C835" s="2" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="D835" s="2" t="inlineStr">
@@ -25495,7 +25495,7 @@
         </is>
       </c>
       <c r="E835" s="3" t="n">
-        <v>20.61</v>
+        <v>20.98</v>
       </c>
       <c r="F835" s="2" t="inlineStr">
         <is>
@@ -25511,12 +25511,12 @@
       </c>
       <c r="B836" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C836" s="2" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="D836" s="2" t="inlineStr">
@@ -25525,11 +25525,11 @@
         </is>
       </c>
       <c r="E836" s="3" t="n">
-        <v>20.57</v>
+        <v>20.61</v>
       </c>
       <c r="F836" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25645,11 +25645,11 @@
         </is>
       </c>
       <c r="E840" s="3" t="n">
-        <v>17.76</v>
+        <v>17.81</v>
       </c>
       <c r="F840" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -25765,11 +25765,11 @@
         </is>
       </c>
       <c r="E844" s="3" t="n">
-        <v>15.97</v>
+        <v>16.14</v>
       </c>
       <c r="F844" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -25901,12 +25901,12 @@
       </c>
       <c r="B849" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C849" s="2" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="D849" s="2" t="inlineStr">
@@ -25915,11 +25915,11 @@
         </is>
       </c>
       <c r="E849" s="3" t="n">
-        <v>12.19</v>
+        <v>12.21</v>
       </c>
       <c r="F849" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -25931,12 +25931,12 @@
       </c>
       <c r="B850" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C850" s="2" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="D850" s="2" t="inlineStr">
@@ -25945,11 +25945,11 @@
         </is>
       </c>
       <c r="E850" s="3" t="n">
-        <v>11.69</v>
+        <v>12.19</v>
       </c>
       <c r="F850" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25961,12 +25961,12 @@
       </c>
       <c r="B851" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C851" s="2" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="D851" s="2" t="inlineStr">
@@ -25975,11 +25975,11 @@
         </is>
       </c>
       <c r="E851" s="3" t="n">
-        <v>11.34</v>
+        <v>11.86</v>
       </c>
       <c r="F851" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -26021,12 +26021,12 @@
       </c>
       <c r="B853" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="C853" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>812824</t>
         </is>
       </c>
       <c r="D853" s="2" t="inlineStr">
@@ -26035,11 +26035,11 @@
         </is>
       </c>
       <c r="E853" s="3" t="n">
-        <v>10.7</v>
+        <v>10.72</v>
       </c>
       <c r="F853" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -26051,12 +26051,12 @@
       </c>
       <c r="B854" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413801QJB</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C854" s="2" t="inlineStr">
         <is>
-          <t>812824</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D854" s="2" t="inlineStr">
@@ -26065,7 +26065,7 @@
         </is>
       </c>
       <c r="E854" s="3" t="n">
-        <v>10.48</v>
+        <v>10.7</v>
       </c>
       <c r="F854" s="2" t="inlineStr">
         <is>
@@ -26425,11 +26425,11 @@
         </is>
       </c>
       <c r="E866" s="3" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="F866" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>
@@ -26485,11 +26485,11 @@
         </is>
       </c>
       <c r="E868" s="3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="F868" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-22 13:59</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2197.76</v>
+        <v>2245.64</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -19781,12 +19781,12 @@
       </c>
       <c r="B645" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000832806P4</t>
+          <t>KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="C645" s="2" t="inlineStr">
         <is>
-          <t>816228</t>
+          <t>816227</t>
         </is>
       </c>
       <c r="D645" s="2" t="inlineStr">
@@ -19795,11 +19795,11 @@
         </is>
       </c>
       <c r="E645" s="3" t="n">
-        <v>1740.7</v>
+        <v>1784.76</v>
       </c>
       <c r="F645" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -19811,12 +19811,12 @@
       </c>
       <c r="B646" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084593R9F</t>
+          <t>KIT4P000832806P4</t>
         </is>
       </c>
       <c r="C646" s="2" t="inlineStr">
         <is>
-          <t>816227</t>
+          <t>816228</t>
         </is>
       </c>
       <c r="D646" s="2" t="inlineStr">
@@ -19825,11 +19825,11 @@
         </is>
       </c>
       <c r="E646" s="3" t="n">
-        <v>1503.58</v>
+        <v>1740.7</v>
       </c>
       <c r="F646" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -19871,12 +19871,12 @@
       </c>
       <c r="B648" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083897XCW</t>
+          <t>KIT4P00065641GDF</t>
         </is>
       </c>
       <c r="C648" s="2" t="inlineStr">
         <is>
-          <t>816223</t>
+          <t>812924</t>
         </is>
       </c>
       <c r="D648" s="2" t="inlineStr">
@@ -19885,11 +19885,11 @@
         </is>
       </c>
       <c r="E648" s="3" t="n">
-        <v>937.86</v>
+        <v>992.95</v>
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -19901,12 +19901,12 @@
       </c>
       <c r="B649" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065641GDF</t>
+          <t>KIT4P0008460369B</t>
         </is>
       </c>
       <c r="C649" s="2" t="inlineStr">
         <is>
-          <t>812924</t>
+          <t>816224</t>
         </is>
       </c>
       <c r="D649" s="2" t="inlineStr">
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>926.78</v>
+        <v>960.47</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -19931,12 +19931,12 @@
       </c>
       <c r="B650" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008460369B</t>
+          <t>KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="C650" s="2" t="inlineStr">
         <is>
-          <t>816224</t>
+          <t>816223</t>
         </is>
       </c>
       <c r="D650" s="2" t="inlineStr">
@@ -19945,11 +19945,11 @@
         </is>
       </c>
       <c r="E650" s="3" t="n">
-        <v>852.04</v>
+        <v>938.21</v>
       </c>
       <c r="F650" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20021,12 +20021,12 @@
       </c>
       <c r="B653" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00072391SZM</t>
+          <t>KIT4P000739257CR</t>
         </is>
       </c>
       <c r="C653" s="2" t="inlineStr">
         <is>
-          <t>814493</t>
+          <t>814609</t>
         </is>
       </c>
       <c r="D653" s="2" t="inlineStr">
@@ -20035,11 +20035,11 @@
         </is>
       </c>
       <c r="E653" s="3" t="n">
-        <v>638.87</v>
+        <v>669.9400000000001</v>
       </c>
       <c r="F653" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20051,25 +20051,25 @@
       </c>
       <c r="B654" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="C654" s="2" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>814493</t>
         </is>
       </c>
       <c r="D654" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E654" s="3" t="n">
-        <v>593.62</v>
+        <v>638.87</v>
       </c>
       <c r="F654" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20081,12 +20081,12 @@
       </c>
       <c r="B655" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C655" s="2" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="D655" s="2" t="inlineStr">
@@ -20095,11 +20095,11 @@
         </is>
       </c>
       <c r="E655" s="3" t="n">
-        <v>586.76</v>
+        <v>604.02</v>
       </c>
       <c r="F655" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20125,11 +20125,11 @@
         </is>
       </c>
       <c r="E656" s="3" t="n">
-        <v>583.1799999999999</v>
+        <v>592.92</v>
       </c>
       <c r="F656" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20141,25 +20141,25 @@
       </c>
       <c r="B657" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C657" s="2" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="D657" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>541.5599999999999</v>
+        <v>591.8099999999999</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20171,12 +20171,12 @@
       </c>
       <c r="B658" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739257CR</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C658" s="2" t="inlineStr">
         <is>
-          <t>814609</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="D658" s="2" t="inlineStr">
@@ -20185,11 +20185,11 @@
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>538.85</v>
+        <v>582.08</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20201,12 +20201,12 @@
       </c>
       <c r="B659" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C659" s="2" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="D659" s="2" t="inlineStr">
@@ -20215,11 +20215,11 @@
         </is>
       </c>
       <c r="E659" s="3" t="n">
-        <v>526.49</v>
+        <v>550.36</v>
       </c>
       <c r="F659" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20231,12 +20231,12 @@
       </c>
       <c r="B660" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C660" s="2" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="D660" s="2" t="inlineStr">
@@ -20245,11 +20245,11 @@
         </is>
       </c>
       <c r="E660" s="3" t="n">
-        <v>513.88</v>
+        <v>542.9</v>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20261,21 +20261,21 @@
       </c>
       <c r="B661" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066901JZZ</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C661" s="2" t="inlineStr">
         <is>
-          <t>812926</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="D661" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>500.45</v>
+        <v>513.88</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
@@ -20305,11 +20305,11 @@
         </is>
       </c>
       <c r="E662" s="3" t="n">
-        <v>496.57</v>
+        <v>512.99</v>
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20321,25 +20321,25 @@
       </c>
       <c r="B663" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="C663" s="2" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>812926</t>
         </is>
       </c>
       <c r="D663" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E663" s="3" t="n">
-        <v>481.33</v>
+        <v>500.46</v>
       </c>
       <c r="F663" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20351,12 +20351,12 @@
       </c>
       <c r="B664" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
@@ -20365,11 +20365,11 @@
         </is>
       </c>
       <c r="E664" s="3" t="n">
-        <v>480.85</v>
+        <v>482.48</v>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20381,12 +20381,12 @@
       </c>
       <c r="B665" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
@@ -20395,7 +20395,7 @@
         </is>
       </c>
       <c r="E665" s="3" t="n">
-        <v>466.53</v>
+        <v>480.85</v>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
@@ -20411,12 +20411,12 @@
       </c>
       <c r="B666" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
@@ -20425,11 +20425,11 @@
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>461.07</v>
+        <v>472.04</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20441,25 +20441,25 @@
       </c>
       <c r="B667" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C667" s="2" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="D667" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E667" s="3" t="n">
-        <v>444.01</v>
+        <v>466.53</v>
       </c>
       <c r="F667" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20471,25 +20471,25 @@
       </c>
       <c r="B668" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C668" s="2" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="D668" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E668" s="3" t="n">
-        <v>437.84</v>
+        <v>460.8</v>
       </c>
       <c r="F668" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20515,11 +20515,11 @@
         </is>
       </c>
       <c r="E669" s="3" t="n">
-        <v>423.21</v>
+        <v>446.17</v>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20605,11 +20605,11 @@
         </is>
       </c>
       <c r="E672" s="3" t="n">
-        <v>376.43</v>
+        <v>394.8</v>
       </c>
       <c r="F672" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20621,25 +20621,25 @@
       </c>
       <c r="B673" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C673" s="2" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="D673" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E673" s="3" t="n">
-        <v>330.28</v>
+        <v>372</v>
       </c>
       <c r="F673" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20651,12 +20651,12 @@
       </c>
       <c r="B674" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C674" s="2" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="D674" s="2" t="inlineStr">
@@ -20665,11 +20665,11 @@
         </is>
       </c>
       <c r="E674" s="3" t="n">
-        <v>326.28</v>
+        <v>366.52</v>
       </c>
       <c r="F674" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20681,25 +20681,25 @@
       </c>
       <c r="B675" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C675" s="2" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="D675" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>317.29</v>
+        <v>365</v>
       </c>
       <c r="F675" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20711,21 +20711,21 @@
       </c>
       <c r="B676" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C676" s="2" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="D676" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>309.15</v>
+        <v>326.28</v>
       </c>
       <c r="F676" s="2" t="inlineStr">
         <is>
@@ -20741,12 +20741,12 @@
       </c>
       <c r="B677" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C677" s="2" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="D677" s="2" t="inlineStr">
@@ -20755,11 +20755,11 @@
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>305.3</v>
+        <v>318.87</v>
       </c>
       <c r="F677" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20771,25 +20771,25 @@
       </c>
       <c r="B678" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C678" s="2" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="D678" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E678" s="3" t="n">
-        <v>294.08</v>
+        <v>309.36</v>
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20801,12 +20801,12 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="D679" s="2" t="inlineStr">
@@ -20815,11 +20815,11 @@
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>275.18</v>
+        <v>297.42</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>268.31</v>
+        <v>278.51</v>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20861,12 +20861,12 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563510TWC</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
         <is>
-          <t>814433</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="D681" s="2" t="inlineStr">
@@ -20875,11 +20875,11 @@
         </is>
       </c>
       <c r="E681" s="3" t="n">
-        <v>267.37</v>
+        <v>275.32</v>
       </c>
       <c r="F681" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20891,12 +20891,12 @@
       </c>
       <c r="B682" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="C682" s="2" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="D682" s="2" t="inlineStr">
@@ -20905,11 +20905,11 @@
         </is>
       </c>
       <c r="E682" s="3" t="n">
-        <v>267.23</v>
+        <v>267.37</v>
       </c>
       <c r="F682" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20935,11 +20935,11 @@
         </is>
       </c>
       <c r="E683" s="3" t="n">
-        <v>257.93</v>
+        <v>264</v>
       </c>
       <c r="F683" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20995,11 +20995,11 @@
         </is>
       </c>
       <c r="E685" s="3" t="n">
-        <v>241.16</v>
+        <v>242.62</v>
       </c>
       <c r="F685" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21011,12 +21011,12 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="D686" s="2" t="inlineStr">
@@ -21025,11 +21025,11 @@
         </is>
       </c>
       <c r="E686" s="3" t="n">
-        <v>237.44</v>
+        <v>237.92</v>
       </c>
       <c r="F686" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21041,12 +21041,12 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="D687" s="2" t="inlineStr">
@@ -21055,11 +21055,11 @@
         </is>
       </c>
       <c r="E687" s="3" t="n">
-        <v>210.11</v>
+        <v>237.44</v>
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21071,12 +21071,12 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="D688" s="2" t="inlineStr">
@@ -21085,11 +21085,11 @@
         </is>
       </c>
       <c r="E688" s="3" t="n">
-        <v>205.87</v>
+        <v>222.04</v>
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21115,11 +21115,11 @@
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>204.92</v>
+        <v>210.22</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21145,11 +21145,11 @@
         </is>
       </c>
       <c r="E690" s="3" t="n">
-        <v>204.85</v>
+        <v>208.78</v>
       </c>
       <c r="F690" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21161,25 +21161,25 @@
       </c>
       <c r="B691" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872531DSZ</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C691" s="2" t="inlineStr">
         <is>
-          <t>816171</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="D691" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E691" s="3" t="n">
-        <v>187.03</v>
+        <v>206.24</v>
       </c>
       <c r="F691" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21205,11 +21205,11 @@
         </is>
       </c>
       <c r="E692" s="3" t="n">
-        <v>185.64</v>
+        <v>204.31</v>
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21221,25 +21221,25 @@
       </c>
       <c r="B693" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C693" s="2" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="D693" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E693" s="3" t="n">
-        <v>184.42</v>
+        <v>193.94</v>
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21251,25 +21251,25 @@
       </c>
       <c r="B694" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="C694" s="2" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>816171</t>
         </is>
       </c>
       <c r="D694" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E694" s="3" t="n">
-        <v>181.15</v>
+        <v>193.42</v>
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21281,12 +21281,12 @@
       </c>
       <c r="B695" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C695" s="2" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="D695" s="2" t="inlineStr">
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>180.28</v>
+        <v>192.37</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21311,12 +21311,12 @@
       </c>
       <c r="B696" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C696" s="2" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="D696" s="2" t="inlineStr">
@@ -21325,11 +21325,11 @@
         </is>
       </c>
       <c r="E696" s="3" t="n">
-        <v>161.61</v>
+        <v>180.28</v>
       </c>
       <c r="F696" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21341,12 +21341,12 @@
       </c>
       <c r="B697" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C697" s="2" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="D697" s="2" t="inlineStr">
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>158.82</v>
+        <v>173.09</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21371,25 +21371,25 @@
       </c>
       <c r="B698" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C698" s="2" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="D698" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E698" s="3" t="n">
-        <v>157.78</v>
+        <v>170.77</v>
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21401,12 +21401,12 @@
       </c>
       <c r="B699" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C699" s="2" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="D699" s="2" t="inlineStr">
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>147.97</v>
+        <v>168.2</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21431,12 +21431,12 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="D700" s="2" t="inlineStr">
@@ -21445,11 +21445,11 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>147.73</v>
+        <v>158.82</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>145.59</v>
+        <v>158.38</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21491,12 +21491,12 @@
       </c>
       <c r="B702" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C702" s="2" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="D702" s="2" t="inlineStr">
@@ -21505,11 +21505,11 @@
         </is>
       </c>
       <c r="E702" s="3" t="n">
-        <v>140.73</v>
+        <v>154.17</v>
       </c>
       <c r="F702" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21521,12 +21521,12 @@
       </c>
       <c r="B703" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C703" s="2" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="D703" s="2" t="inlineStr">
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>140.69</v>
+        <v>149.78</v>
       </c>
       <c r="F703" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21551,12 +21551,12 @@
       </c>
       <c r="B704" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C704" s="2" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="D704" s="2" t="inlineStr">
@@ -21565,11 +21565,11 @@
         </is>
       </c>
       <c r="E704" s="3" t="n">
-        <v>138.35</v>
+        <v>147.36</v>
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21581,12 +21581,12 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="D705" s="2" t="inlineStr">
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>134.58</v>
+        <v>146.72</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21611,12 +21611,12 @@
       </c>
       <c r="B706" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C706" s="2" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="D706" s="2" t="inlineStr">
@@ -21625,11 +21625,11 @@
         </is>
       </c>
       <c r="E706" s="3" t="n">
-        <v>134.19</v>
+        <v>140.59</v>
       </c>
       <c r="F706" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21641,12 +21641,12 @@
       </c>
       <c r="B707" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C707" s="2" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="D707" s="2" t="inlineStr">
@@ -21655,11 +21655,11 @@
         </is>
       </c>
       <c r="E707" s="3" t="n">
-        <v>132.39</v>
+        <v>138.36</v>
       </c>
       <c r="F707" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21671,12 +21671,12 @@
       </c>
       <c r="B708" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C708" s="2" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="D708" s="2" t="inlineStr">
@@ -21685,11 +21685,11 @@
         </is>
       </c>
       <c r="E708" s="3" t="n">
-        <v>131.31</v>
+        <v>134.03</v>
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21701,12 +21701,12 @@
       </c>
       <c r="B709" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C709" s="2" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="D709" s="2" t="inlineStr">
@@ -21715,7 +21715,7 @@
         </is>
       </c>
       <c r="E709" s="3" t="n">
-        <v>131.04</v>
+        <v>132.39</v>
       </c>
       <c r="F709" s="2" t="inlineStr">
         <is>
@@ -21745,11 +21745,11 @@
         </is>
       </c>
       <c r="E710" s="3" t="n">
-        <v>130.26</v>
+        <v>131.75</v>
       </c>
       <c r="F710" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21761,12 +21761,12 @@
       </c>
       <c r="B711" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C711" s="2" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="D711" s="2" t="inlineStr">
@@ -21775,11 +21775,11 @@
         </is>
       </c>
       <c r="E711" s="3" t="n">
-        <v>129.24</v>
+        <v>131.31</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21791,12 +21791,12 @@
       </c>
       <c r="B712" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C712" s="2" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="D712" s="2" t="inlineStr">
@@ -21805,11 +21805,11 @@
         </is>
       </c>
       <c r="E712" s="3" t="n">
-        <v>128.77</v>
+        <v>131.27</v>
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21821,12 +21821,12 @@
       </c>
       <c r="B713" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C713" s="2" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="D713" s="2" t="inlineStr">
@@ -21835,7 +21835,7 @@
         </is>
       </c>
       <c r="E713" s="3" t="n">
-        <v>126.03</v>
+        <v>131.04</v>
       </c>
       <c r="F713" s="2" t="inlineStr">
         <is>
@@ -21851,12 +21851,12 @@
       </c>
       <c r="B714" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C714" s="2" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="D714" s="2" t="inlineStr">
@@ -21865,11 +21865,11 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>125.25</v>
+        <v>127.39</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21881,12 +21881,12 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="D715" s="2" t="inlineStr">
@@ -21895,11 +21895,11 @@
         </is>
       </c>
       <c r="E715" s="3" t="n">
-        <v>123.24</v>
+        <v>126.03</v>
       </c>
       <c r="F715" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21911,12 +21911,12 @@
       </c>
       <c r="B716" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C716" s="2" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="D716" s="2" t="inlineStr">
@@ -21925,7 +21925,7 @@
         </is>
       </c>
       <c r="E716" s="3" t="n">
-        <v>120.41</v>
+        <v>125.25</v>
       </c>
       <c r="F716" s="2" t="inlineStr">
         <is>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B717" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C717" s="2" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="D717" s="2" t="inlineStr">
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>119.92</v>
+        <v>123.44</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21971,12 +21971,12 @@
       </c>
       <c r="B718" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr">
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>119.12</v>
+        <v>121.08</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22015,11 +22015,11 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>114.8</v>
+        <v>120.6</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22031,12 +22031,12 @@
       </c>
       <c r="B720" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C720" s="2" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="D720" s="2" t="inlineStr">
@@ -22045,11 +22045,11 @@
         </is>
       </c>
       <c r="E720" s="3" t="n">
-        <v>114.07</v>
+        <v>119.92</v>
       </c>
       <c r="F720" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22061,12 +22061,12 @@
       </c>
       <c r="B721" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C721" s="2" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="D721" s="2" t="inlineStr">
@@ -22075,11 +22075,11 @@
         </is>
       </c>
       <c r="E721" s="3" t="n">
-        <v>113.25</v>
+        <v>116.72</v>
       </c>
       <c r="F721" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22091,12 +22091,12 @@
       </c>
       <c r="B722" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C722" s="2" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="D722" s="2" t="inlineStr">
@@ -22105,11 +22105,11 @@
         </is>
       </c>
       <c r="E722" s="3" t="n">
-        <v>111.07</v>
+        <v>114.07</v>
       </c>
       <c r="F722" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22121,12 +22121,12 @@
       </c>
       <c r="B723" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C723" s="2" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="D723" s="2" t="inlineStr">
@@ -22135,11 +22135,11 @@
         </is>
       </c>
       <c r="E723" s="3" t="n">
-        <v>106.73</v>
+        <v>113.25</v>
       </c>
       <c r="F723" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22151,12 +22151,12 @@
       </c>
       <c r="B724" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C724" s="2" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="D724" s="2" t="inlineStr">
@@ -22165,11 +22165,11 @@
         </is>
       </c>
       <c r="E724" s="3" t="n">
-        <v>106.48</v>
+        <v>111.11</v>
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22181,12 +22181,12 @@
       </c>
       <c r="B725" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C725" s="2" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="D725" s="2" t="inlineStr">
@@ -22195,11 +22195,11 @@
         </is>
       </c>
       <c r="E725" s="3" t="n">
-        <v>104.93</v>
+        <v>110.55</v>
       </c>
       <c r="F725" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22211,12 +22211,12 @@
       </c>
       <c r="B726" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C726" s="2" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="D726" s="2" t="inlineStr">
@@ -22225,11 +22225,11 @@
         </is>
       </c>
       <c r="E726" s="3" t="n">
-        <v>104.6</v>
+        <v>108.09</v>
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22241,12 +22241,12 @@
       </c>
       <c r="B727" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C727" s="2" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="D727" s="2" t="inlineStr">
@@ -22255,11 +22255,11 @@
         </is>
       </c>
       <c r="E727" s="3" t="n">
-        <v>102.77</v>
+        <v>107.86</v>
       </c>
       <c r="F727" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22271,12 +22271,12 @@
       </c>
       <c r="B728" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C728" s="2" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="D728" s="2" t="inlineStr">
@@ -22285,11 +22285,11 @@
         </is>
       </c>
       <c r="E728" s="3" t="n">
-        <v>100.93</v>
+        <v>106.76</v>
       </c>
       <c r="F728" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22315,11 +22315,11 @@
         </is>
       </c>
       <c r="E729" s="3" t="n">
-        <v>99.93000000000001</v>
+        <v>103.72</v>
       </c>
       <c r="F729" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22331,12 +22331,12 @@
       </c>
       <c r="B730" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C730" s="2" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="D730" s="2" t="inlineStr">
@@ -22345,7 +22345,7 @@
         </is>
       </c>
       <c r="E730" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>100.93</v>
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
@@ -22361,12 +22361,12 @@
       </c>
       <c r="B731" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="D731" s="2" t="inlineStr">
@@ -22375,7 +22375,7 @@
         </is>
       </c>
       <c r="E731" s="3" t="n">
-        <v>97.44</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
@@ -22391,12 +22391,12 @@
       </c>
       <c r="B732" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="D732" s="2" t="inlineStr">
@@ -22405,11 +22405,11 @@
         </is>
       </c>
       <c r="E732" s="3" t="n">
-        <v>94.81999999999999</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22421,12 +22421,12 @@
       </c>
       <c r="B733" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="D733" s="2" t="inlineStr">
@@ -22435,11 +22435,11 @@
         </is>
       </c>
       <c r="E733" s="3" t="n">
-        <v>93.83</v>
+        <v>97.44</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22451,12 +22451,12 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
@@ -22465,11 +22465,11 @@
         </is>
       </c>
       <c r="E734" s="3" t="n">
-        <v>92.27</v>
+        <v>96.97</v>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22481,12 +22481,12 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
@@ -22495,11 +22495,11 @@
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>90.81999999999999</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22511,12 +22511,12 @@
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
@@ -22525,11 +22525,11 @@
         </is>
       </c>
       <c r="E736" s="3" t="n">
-        <v>89.79000000000001</v>
+        <v>93.83</v>
       </c>
       <c r="F736" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22541,25 +22541,25 @@
       </c>
       <c r="B737" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="D737" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E737" s="3" t="n">
-        <v>89.48999999999999</v>
+        <v>93.78</v>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22571,12 +22571,12 @@
       </c>
       <c r="B738" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D738" s="2" t="inlineStr">
@@ -22585,11 +22585,11 @@
         </is>
       </c>
       <c r="E738" s="3" t="n">
-        <v>88.54000000000001</v>
+        <v>91.25</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22601,12 +22601,12 @@
       </c>
       <c r="B739" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C739" s="2" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="D739" s="2" t="inlineStr">
@@ -22615,7 +22615,7 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>87.73</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
@@ -22631,21 +22631,21 @@
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E740" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
@@ -22661,12 +22661,12 @@
       </c>
       <c r="B741" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D741" s="2" t="inlineStr">
@@ -22675,11 +22675,11 @@
         </is>
       </c>
       <c r="E741" s="3" t="n">
-        <v>82.18000000000001</v>
+        <v>88.95</v>
       </c>
       <c r="F741" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22691,12 +22691,12 @@
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>82.06999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22721,12 +22721,12 @@
       </c>
       <c r="B743" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C743" s="2" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="D743" s="2" t="inlineStr">
@@ -22735,11 +22735,11 @@
         </is>
       </c>
       <c r="E743" s="3" t="n">
-        <v>81.73</v>
+        <v>87.73</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22751,12 +22751,12 @@
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="D744" s="2" t="inlineStr">
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>80.88</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22781,12 +22781,12 @@
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr">
@@ -22795,11 +22795,11 @@
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>79.81</v>
+        <v>84.86</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22811,12 +22811,12 @@
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
@@ -22825,11 +22825,11 @@
         </is>
       </c>
       <c r="E746" s="3" t="n">
-        <v>79.44</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22841,12 +22841,12 @@
       </c>
       <c r="B747" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C747" s="2" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="D747" s="2" t="inlineStr">
@@ -22855,11 +22855,11 @@
         </is>
       </c>
       <c r="E747" s="3" t="n">
-        <v>78.26000000000001</v>
+        <v>84.08</v>
       </c>
       <c r="F747" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22871,12 +22871,12 @@
       </c>
       <c r="B748" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C748" s="2" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="D748" s="2" t="inlineStr">
@@ -22885,11 +22885,11 @@
         </is>
       </c>
       <c r="E748" s="3" t="n">
-        <v>78.02</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22915,11 +22915,11 @@
         </is>
       </c>
       <c r="E749" s="3" t="n">
-        <v>76.16</v>
+        <v>82.73</v>
       </c>
       <c r="F749" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22931,12 +22931,12 @@
       </c>
       <c r="B750" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C750" s="2" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="D750" s="2" t="inlineStr">
@@ -22945,7 +22945,7 @@
         </is>
       </c>
       <c r="E750" s="3" t="n">
-        <v>75.81</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F750" s="2" t="inlineStr">
         <is>
@@ -22961,12 +22961,12 @@
       </c>
       <c r="B751" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C751" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="D751" s="2" t="inlineStr">
@@ -22975,11 +22975,11 @@
         </is>
       </c>
       <c r="E751" s="3" t="n">
-        <v>75.76000000000001</v>
+        <v>81.73</v>
       </c>
       <c r="F751" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22991,12 +22991,12 @@
       </c>
       <c r="B752" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C752" s="2" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="D752" s="2" t="inlineStr">
@@ -23005,11 +23005,11 @@
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>75.75</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23021,12 +23021,12 @@
       </c>
       <c r="B753" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C753" s="2" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="D753" s="2" t="inlineStr">
@@ -23035,7 +23035,7 @@
         </is>
       </c>
       <c r="E753" s="3" t="n">
-        <v>74.76000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="F753" s="2" t="inlineStr">
         <is>
@@ -23051,25 +23051,25 @@
       </c>
       <c r="B754" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C754" s="2" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="D754" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E754" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>79.14</v>
       </c>
       <c r="F754" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23095,11 +23095,11 @@
         </is>
       </c>
       <c r="E755" s="3" t="n">
-        <v>74.17</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="F755" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23111,12 +23111,12 @@
       </c>
       <c r="B756" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C756" s="2" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="D756" s="2" t="inlineStr">
@@ -23125,7 +23125,7 @@
         </is>
       </c>
       <c r="E756" s="3" t="n">
-        <v>71.38</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
@@ -23141,25 +23141,25 @@
       </c>
       <c r="B757" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C757" s="2" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="D757" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E757" s="3" t="n">
-        <v>69.83</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F757" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23171,12 +23171,12 @@
       </c>
       <c r="B758" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="C758" s="2" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="D758" s="2" t="inlineStr">
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>67.39</v>
+        <v>72.83</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23215,11 +23215,11 @@
         </is>
       </c>
       <c r="E759" s="3" t="n">
-        <v>65.89</v>
+        <v>71.66</v>
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23231,12 +23231,12 @@
       </c>
       <c r="B760" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C760" s="2" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="D760" s="2" t="inlineStr">
@@ -23245,11 +23245,11 @@
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>65.09</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23261,12 +23261,12 @@
       </c>
       <c r="B761" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C761" s="2" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="D761" s="2" t="inlineStr">
@@ -23275,7 +23275,7 @@
         </is>
       </c>
       <c r="E761" s="3" t="n">
-        <v>64.33</v>
+        <v>71.38</v>
       </c>
       <c r="F761" s="2" t="inlineStr">
         <is>
@@ -23291,12 +23291,12 @@
       </c>
       <c r="B762" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C762" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="D762" s="2" t="inlineStr">
@@ -23305,11 +23305,11 @@
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>63.6</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23321,12 +23321,12 @@
       </c>
       <c r="B763" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C763" s="2" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="D763" s="2" t="inlineStr">
@@ -23335,11 +23335,11 @@
         </is>
       </c>
       <c r="E763" s="3" t="n">
-        <v>62.58</v>
+        <v>68.3</v>
       </c>
       <c r="F763" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23351,12 +23351,12 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="D764" s="2" t="inlineStr">
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>62.22</v>
+        <v>64.87</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23381,12 +23381,12 @@
       </c>
       <c r="B765" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C765" s="2" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="D765" s="2" t="inlineStr">
@@ -23395,11 +23395,11 @@
         </is>
       </c>
       <c r="E765" s="3" t="n">
-        <v>61.79</v>
+        <v>63.84</v>
       </c>
       <c r="F765" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>60.87</v>
+        <v>63.63</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23441,12 +23441,12 @@
       </c>
       <c r="B767" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C767" s="2" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="D767" s="2" t="inlineStr">
@@ -23455,11 +23455,11 @@
         </is>
       </c>
       <c r="E767" s="3" t="n">
-        <v>60.68</v>
+        <v>63.6</v>
       </c>
       <c r="F767" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23471,12 +23471,12 @@
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="D768" s="2" t="inlineStr">
@@ -23485,11 +23485,11 @@
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>60.31</v>
+        <v>63.28</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23515,11 +23515,11 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>60.3</v>
+        <v>62.66</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23531,12 +23531,12 @@
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
@@ -23545,11 +23545,11 @@
         </is>
       </c>
       <c r="E770" s="3" t="n">
-        <v>59.75</v>
+        <v>62.58</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23561,12 +23561,12 @@
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
@@ -23575,11 +23575,11 @@
         </is>
       </c>
       <c r="E771" s="3" t="n">
-        <v>58.93</v>
+        <v>61.83</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23591,12 +23591,12 @@
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -23605,11 +23605,11 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>58.85</v>
+        <v>60.88</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23621,12 +23621,12 @@
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D773" s="2" t="inlineStr">
@@ -23635,11 +23635,11 @@
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>58.47</v>
+        <v>60.74</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23651,21 +23651,21 @@
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E774" s="3" t="n">
-        <v>57.22</v>
+        <v>60.31</v>
       </c>
       <c r="F774" s="2" t="inlineStr">
         <is>
@@ -23695,11 +23695,11 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>56.83</v>
+        <v>58.89</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23711,12 +23711,12 @@
       </c>
       <c r="B776" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C776" s="2" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="D776" s="2" t="inlineStr">
@@ -23725,11 +23725,11 @@
         </is>
       </c>
       <c r="E776" s="3" t="n">
-        <v>56.5</v>
+        <v>57.86</v>
       </c>
       <c r="F776" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23741,12 +23741,12 @@
       </c>
       <c r="B777" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C777" s="2" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="D777" s="2" t="inlineStr">
@@ -23755,11 +23755,11 @@
         </is>
       </c>
       <c r="E777" s="3" t="n">
-        <v>56.35</v>
+        <v>57.79</v>
       </c>
       <c r="F777" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23771,12 +23771,12 @@
       </c>
       <c r="B778" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C778" s="2" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D778" s="2" t="inlineStr">
@@ -23785,11 +23785,11 @@
         </is>
       </c>
       <c r="E778" s="3" t="n">
-        <v>55.05</v>
+        <v>57.61</v>
       </c>
       <c r="F778" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23801,12 +23801,12 @@
       </c>
       <c r="B779" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C779" s="2" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="D779" s="2" t="inlineStr">
@@ -23815,11 +23815,11 @@
         </is>
       </c>
       <c r="E779" s="3" t="n">
-        <v>53.95</v>
+        <v>57.53</v>
       </c>
       <c r="F779" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23831,25 +23831,25 @@
       </c>
       <c r="B780" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C780" s="2" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="D780" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E780" s="3" t="n">
-        <v>53.65</v>
+        <v>57.22</v>
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23861,12 +23861,12 @@
       </c>
       <c r="B781" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C781" s="2" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="D781" s="2" t="inlineStr">
@@ -23875,11 +23875,11 @@
         </is>
       </c>
       <c r="E781" s="3" t="n">
-        <v>53.24</v>
+        <v>57.18</v>
       </c>
       <c r="F781" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23891,12 +23891,12 @@
       </c>
       <c r="B782" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C782" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="D782" s="2" t="inlineStr">
@@ -23905,11 +23905,11 @@
         </is>
       </c>
       <c r="E782" s="3" t="n">
-        <v>53.15</v>
+        <v>56.85</v>
       </c>
       <c r="F782" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23921,12 +23921,12 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="D783" s="2" t="inlineStr">
@@ -23935,11 +23935,11 @@
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>52.93</v>
+        <v>56.5</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23951,12 +23951,12 @@
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
@@ -23965,11 +23965,11 @@
         </is>
       </c>
       <c r="E784" s="3" t="n">
-        <v>52.76</v>
+        <v>56.5</v>
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23981,12 +23981,12 @@
       </c>
       <c r="B785" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C785" s="2" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="D785" s="2" t="inlineStr">
@@ -23995,7 +23995,7 @@
         </is>
       </c>
       <c r="E785" s="3" t="n">
-        <v>52.57</v>
+        <v>55.05</v>
       </c>
       <c r="F785" s="2" t="inlineStr">
         <is>
@@ -24011,12 +24011,12 @@
       </c>
       <c r="B786" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C786" s="2" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="D786" s="2" t="inlineStr">
@@ -24025,7 +24025,7 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>52.12</v>
+        <v>53.95</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
@@ -24041,12 +24041,12 @@
       </c>
       <c r="B787" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C787" s="2" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="D787" s="2" t="inlineStr">
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>51.71</v>
+        <v>53.88</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24071,12 +24071,12 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="D788" s="2" t="inlineStr">
@@ -24085,7 +24085,7 @@
         </is>
       </c>
       <c r="E788" s="3" t="n">
-        <v>51.5</v>
+        <v>53.24</v>
       </c>
       <c r="F788" s="2" t="inlineStr">
         <is>
@@ -24101,12 +24101,12 @@
       </c>
       <c r="B789" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C789" s="2" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D789" s="2" t="inlineStr">
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>49.22</v>
+        <v>53</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24131,12 +24131,12 @@
       </c>
       <c r="B790" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C790" s="2" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="D790" s="2" t="inlineStr">
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="E790" s="3" t="n">
-        <v>48.04</v>
+        <v>52.57</v>
       </c>
       <c r="F790" s="2" t="inlineStr">
         <is>
@@ -24161,12 +24161,12 @@
       </c>
       <c r="B791" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C791" s="2" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="D791" s="2" t="inlineStr">
@@ -24175,11 +24175,11 @@
         </is>
       </c>
       <c r="E791" s="3" t="n">
-        <v>47.99</v>
+        <v>52.13</v>
       </c>
       <c r="F791" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24191,12 +24191,12 @@
       </c>
       <c r="B792" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C792" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="D792" s="2" t="inlineStr">
@@ -24205,11 +24205,11 @@
         </is>
       </c>
       <c r="E792" s="3" t="n">
-        <v>47.84</v>
+        <v>51.59</v>
       </c>
       <c r="F792" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24221,12 +24221,12 @@
       </c>
       <c r="B793" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C793" s="2" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="D793" s="2" t="inlineStr">
@@ -24235,11 +24235,11 @@
         </is>
       </c>
       <c r="E793" s="3" t="n">
-        <v>47.32</v>
+        <v>50.49</v>
       </c>
       <c r="F793" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24251,12 +24251,12 @@
       </c>
       <c r="B794" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C794" s="2" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="D794" s="2" t="inlineStr">
@@ -24265,11 +24265,11 @@
         </is>
       </c>
       <c r="E794" s="3" t="n">
-        <v>47.23</v>
+        <v>50.13</v>
       </c>
       <c r="F794" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24281,12 +24281,12 @@
       </c>
       <c r="B795" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C795" s="2" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D795" s="2" t="inlineStr">
@@ -24295,11 +24295,11 @@
         </is>
       </c>
       <c r="E795" s="3" t="n">
-        <v>46.1</v>
+        <v>48.09</v>
       </c>
       <c r="F795" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24311,12 +24311,12 @@
       </c>
       <c r="B796" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C796" s="2" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="D796" s="2" t="inlineStr">
@@ -24325,7 +24325,7 @@
         </is>
       </c>
       <c r="E796" s="3" t="n">
-        <v>45.68</v>
+        <v>48.04</v>
       </c>
       <c r="F796" s="2" t="inlineStr">
         <is>
@@ -24341,12 +24341,12 @@
       </c>
       <c r="B797" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C797" s="2" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="D797" s="2" t="inlineStr">
@@ -24355,11 +24355,11 @@
         </is>
       </c>
       <c r="E797" s="3" t="n">
-        <v>45.53</v>
+        <v>47.99</v>
       </c>
       <c r="F797" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24371,12 +24371,12 @@
       </c>
       <c r="B798" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C798" s="2" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="D798" s="2" t="inlineStr">
@@ -24385,11 +24385,11 @@
         </is>
       </c>
       <c r="E798" s="3" t="n">
-        <v>44.68</v>
+        <v>47.23</v>
       </c>
       <c r="F798" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="B799" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C799" s="2" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="D799" s="2" t="inlineStr">
@@ -24415,11 +24415,11 @@
         </is>
       </c>
       <c r="E799" s="3" t="n">
-        <v>44.19</v>
+        <v>46.65</v>
       </c>
       <c r="F799" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24431,12 +24431,12 @@
       </c>
       <c r="B800" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C800" s="2" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="D800" s="2" t="inlineStr">
@@ -24445,11 +24445,11 @@
         </is>
       </c>
       <c r="E800" s="3" t="n">
-        <v>41.34</v>
+        <v>46.1</v>
       </c>
       <c r="F800" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24461,12 +24461,12 @@
       </c>
       <c r="B801" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C801" s="2" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D801" s="2" t="inlineStr">
@@ -24475,11 +24475,11 @@
         </is>
       </c>
       <c r="E801" s="3" t="n">
-        <v>40.43</v>
+        <v>46</v>
       </c>
       <c r="F801" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24491,12 +24491,12 @@
       </c>
       <c r="B802" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C802" s="2" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="D802" s="2" t="inlineStr">
@@ -24505,11 +24505,11 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>39.51</v>
+        <v>45.85</v>
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24521,12 +24521,12 @@
       </c>
       <c r="B803" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C803" s="2" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="D803" s="2" t="inlineStr">
@@ -24535,11 +24535,11 @@
         </is>
       </c>
       <c r="E803" s="3" t="n">
-        <v>39.41</v>
+        <v>44.93</v>
       </c>
       <c r="F803" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24551,12 +24551,12 @@
       </c>
       <c r="B804" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C804" s="2" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="D804" s="2" t="inlineStr">
@@ -24565,11 +24565,11 @@
         </is>
       </c>
       <c r="E804" s="3" t="n">
-        <v>38.97</v>
+        <v>44.93</v>
       </c>
       <c r="F804" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24581,12 +24581,12 @@
       </c>
       <c r="B805" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C805" s="2" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="D805" s="2" t="inlineStr">
@@ -24595,11 +24595,11 @@
         </is>
       </c>
       <c r="E805" s="3" t="n">
-        <v>38.88</v>
+        <v>44.67</v>
       </c>
       <c r="F805" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24611,12 +24611,12 @@
       </c>
       <c r="B806" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C806" s="2" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="D806" s="2" t="inlineStr">
@@ -24625,7 +24625,7 @@
         </is>
       </c>
       <c r="E806" s="3" t="n">
-        <v>37.65</v>
+        <v>44.19</v>
       </c>
       <c r="F806" s="2" t="inlineStr">
         <is>
@@ -24641,12 +24641,12 @@
       </c>
       <c r="B807" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="C807" s="2" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="D807" s="2" t="inlineStr">
@@ -24655,11 +24655,11 @@
         </is>
       </c>
       <c r="E807" s="3" t="n">
-        <v>36.59</v>
+        <v>40.51</v>
       </c>
       <c r="F807" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24671,12 +24671,12 @@
       </c>
       <c r="B808" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C808" s="2" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="D808" s="2" t="inlineStr">
@@ -24685,11 +24685,11 @@
         </is>
       </c>
       <c r="E808" s="3" t="n">
-        <v>36.5</v>
+        <v>39.2</v>
       </c>
       <c r="F808" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24701,12 +24701,12 @@
       </c>
       <c r="B809" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C809" s="2" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="D809" s="2" t="inlineStr">
@@ -24715,7 +24715,7 @@
         </is>
       </c>
       <c r="E809" s="3" t="n">
-        <v>36.48</v>
+        <v>38.88</v>
       </c>
       <c r="F809" s="2" t="inlineStr">
         <is>
@@ -24731,12 +24731,12 @@
       </c>
       <c r="B810" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C810" s="2" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="D810" s="2" t="inlineStr">
@@ -24745,7 +24745,7 @@
         </is>
       </c>
       <c r="E810" s="3" t="n">
-        <v>36.31</v>
+        <v>37.65</v>
       </c>
       <c r="F810" s="2" t="inlineStr">
         <is>
@@ -24761,12 +24761,12 @@
       </c>
       <c r="B811" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C811" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="D811" s="2" t="inlineStr">
@@ -24775,11 +24775,11 @@
         </is>
       </c>
       <c r="E811" s="3" t="n">
-        <v>36.05</v>
+        <v>37.45</v>
       </c>
       <c r="F811" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24791,12 +24791,12 @@
       </c>
       <c r="B812" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C812" s="2" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="D812" s="2" t="inlineStr">
@@ -24805,11 +24805,11 @@
         </is>
       </c>
       <c r="E812" s="3" t="n">
-        <v>34.1</v>
+        <v>36.75</v>
       </c>
       <c r="F812" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24821,12 +24821,12 @@
       </c>
       <c r="B813" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C813" s="2" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="D813" s="2" t="inlineStr">
@@ -24835,11 +24835,11 @@
         </is>
       </c>
       <c r="E813" s="3" t="n">
-        <v>34.05</v>
+        <v>36.59</v>
       </c>
       <c r="F813" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24851,12 +24851,12 @@
       </c>
       <c r="B814" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C814" s="2" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="D814" s="2" t="inlineStr">
@@ -24865,11 +24865,11 @@
         </is>
       </c>
       <c r="E814" s="3" t="n">
-        <v>31.32</v>
+        <v>36.31</v>
       </c>
       <c r="F814" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24881,12 +24881,12 @@
       </c>
       <c r="B815" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C815" s="2" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="D815" s="2" t="inlineStr">
@@ -24895,11 +24895,11 @@
         </is>
       </c>
       <c r="E815" s="3" t="n">
-        <v>31.26</v>
+        <v>35.89</v>
       </c>
       <c r="F815" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24911,12 +24911,12 @@
       </c>
       <c r="B816" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C816" s="2" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="D816" s="2" t="inlineStr">
@@ -24925,11 +24925,11 @@
         </is>
       </c>
       <c r="E816" s="3" t="n">
-        <v>31.24</v>
+        <v>34.13</v>
       </c>
       <c r="F816" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24941,12 +24941,12 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="D817" s="2" t="inlineStr">
@@ -24955,11 +24955,11 @@
         </is>
       </c>
       <c r="E817" s="3" t="n">
-        <v>30.47</v>
+        <v>34.1</v>
       </c>
       <c r="F817" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24971,12 +24971,12 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="D818" s="2" t="inlineStr">
@@ -24985,11 +24985,11 @@
         </is>
       </c>
       <c r="E818" s="3" t="n">
-        <v>30.11</v>
+        <v>34.05</v>
       </c>
       <c r="F818" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25001,12 +25001,12 @@
       </c>
       <c r="B819" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C819" s="2" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="D819" s="2" t="inlineStr">
@@ -25015,11 +25015,11 @@
         </is>
       </c>
       <c r="E819" s="3" t="n">
-        <v>29.27</v>
+        <v>32.8</v>
       </c>
       <c r="F819" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25031,12 +25031,12 @@
       </c>
       <c r="B820" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="C820" s="2" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="D820" s="2" t="inlineStr">
@@ -25045,11 +25045,11 @@
         </is>
       </c>
       <c r="E820" s="3" t="n">
-        <v>29.1</v>
+        <v>31.24</v>
       </c>
       <c r="F820" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25061,12 +25061,12 @@
       </c>
       <c r="B821" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C821" s="2" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="D821" s="2" t="inlineStr">
@@ -25075,11 +25075,11 @@
         </is>
       </c>
       <c r="E821" s="3" t="n">
-        <v>28.85</v>
+        <v>30.66</v>
       </c>
       <c r="F821" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25091,12 +25091,12 @@
       </c>
       <c r="B822" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C822" s="2" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="D822" s="2" t="inlineStr">
@@ -25105,11 +25105,11 @@
         </is>
       </c>
       <c r="E822" s="3" t="n">
-        <v>28.46</v>
+        <v>29.4</v>
       </c>
       <c r="F822" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25121,12 +25121,12 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="D823" s="2" t="inlineStr">
@@ -25135,11 +25135,11 @@
         </is>
       </c>
       <c r="E823" s="3" t="n">
-        <v>27.03</v>
+        <v>29.27</v>
       </c>
       <c r="F823" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25151,12 +25151,12 @@
       </c>
       <c r="B824" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C824" s="2" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="D824" s="2" t="inlineStr">
@@ -25165,11 +25165,11 @@
         </is>
       </c>
       <c r="E824" s="3" t="n">
-        <v>26.3</v>
+        <v>28.85</v>
       </c>
       <c r="F824" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25181,25 +25181,25 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="D825" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E825" s="3" t="n">
-        <v>26.15</v>
+        <v>27.22</v>
       </c>
       <c r="F825" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25225,11 +25225,11 @@
         </is>
       </c>
       <c r="E826" s="3" t="n">
-        <v>26.14</v>
+        <v>26.67</v>
       </c>
       <c r="F826" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25241,21 +25241,21 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="D827" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E827" s="3" t="n">
-        <v>25.79</v>
+        <v>26.15</v>
       </c>
       <c r="F827" s="2" t="inlineStr">
         <is>
@@ -25285,11 +25285,11 @@
         </is>
       </c>
       <c r="E828" s="3" t="n">
-        <v>24.1</v>
+        <v>24.7</v>
       </c>
       <c r="F828" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25301,12 +25301,12 @@
       </c>
       <c r="B829" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C829" s="2" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D829" s="2" t="inlineStr">
@@ -25315,11 +25315,11 @@
         </is>
       </c>
       <c r="E829" s="3" t="n">
-        <v>23.74</v>
+        <v>23.99</v>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25331,12 +25331,12 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="D830" s="2" t="inlineStr">
@@ -25345,7 +25345,7 @@
         </is>
       </c>
       <c r="E830" s="3" t="n">
-        <v>22.39</v>
+        <v>23.74</v>
       </c>
       <c r="F830" s="2" t="inlineStr">
         <is>
@@ -25361,12 +25361,12 @@
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C831" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="D831" s="2" t="inlineStr">
@@ -25375,7 +25375,7 @@
         </is>
       </c>
       <c r="E831" s="3" t="n">
-        <v>22.3</v>
+        <v>22.39</v>
       </c>
       <c r="F831" s="2" t="inlineStr">
         <is>
@@ -25405,11 +25405,11 @@
         </is>
       </c>
       <c r="E832" s="3" t="n">
-        <v>21.69</v>
+        <v>21.7</v>
       </c>
       <c r="F832" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25421,12 +25421,12 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="D833" s="2" t="inlineStr">
@@ -25435,11 +25435,11 @@
         </is>
       </c>
       <c r="E833" s="3" t="n">
-        <v>21.21</v>
+        <v>21.54</v>
       </c>
       <c r="F833" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25451,25 +25451,25 @@
       </c>
       <c r="B834" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C834" s="2" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="D834" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E834" s="3" t="n">
-        <v>21.17</v>
+        <v>21.26</v>
       </c>
       <c r="F834" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25481,12 +25481,12 @@
       </c>
       <c r="B835" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C835" s="2" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="D835" s="2" t="inlineStr">
@@ -25495,7 +25495,7 @@
         </is>
       </c>
       <c r="E835" s="3" t="n">
-        <v>20.98</v>
+        <v>21.21</v>
       </c>
       <c r="F835" s="2" t="inlineStr">
         <is>
@@ -25511,12 +25511,12 @@
       </c>
       <c r="B836" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C836" s="2" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="D836" s="2" t="inlineStr">
@@ -25525,7 +25525,7 @@
         </is>
       </c>
       <c r="E836" s="3" t="n">
-        <v>20.61</v>
+        <v>21.17</v>
       </c>
       <c r="F836" s="2" t="inlineStr">
         <is>
@@ -25541,12 +25541,12 @@
       </c>
       <c r="B837" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C837" s="2" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="D837" s="2" t="inlineStr">
@@ -25555,7 +25555,7 @@
         </is>
       </c>
       <c r="E837" s="3" t="n">
-        <v>20.12</v>
+        <v>20.98</v>
       </c>
       <c r="F837" s="2" t="inlineStr">
         <is>
@@ -25571,12 +25571,12 @@
       </c>
       <c r="B838" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C838" s="2" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="D838" s="2" t="inlineStr">
@@ -25585,7 +25585,7 @@
         </is>
       </c>
       <c r="E838" s="3" t="n">
-        <v>19.65</v>
+        <v>20.61</v>
       </c>
       <c r="F838" s="2" t="inlineStr">
         <is>
@@ -25601,12 +25601,12 @@
       </c>
       <c r="B839" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C839" s="2" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="D839" s="2" t="inlineStr">
@@ -25615,11 +25615,11 @@
         </is>
       </c>
       <c r="E839" s="3" t="n">
-        <v>19.52</v>
+        <v>20.26</v>
       </c>
       <c r="F839" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25631,12 +25631,12 @@
       </c>
       <c r="B840" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C840" s="2" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="D840" s="2" t="inlineStr">
@@ -25645,11 +25645,11 @@
         </is>
       </c>
       <c r="E840" s="3" t="n">
-        <v>17.81</v>
+        <v>20.12</v>
       </c>
       <c r="F840" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25661,12 +25661,12 @@
       </c>
       <c r="B841" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C841" s="2" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="D841" s="2" t="inlineStr">
@@ -25675,7 +25675,7 @@
         </is>
       </c>
       <c r="E841" s="3" t="n">
-        <v>17.57</v>
+        <v>19.65</v>
       </c>
       <c r="F841" s="2" t="inlineStr">
         <is>
@@ -25691,12 +25691,12 @@
       </c>
       <c r="B842" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C842" s="2" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="D842" s="2" t="inlineStr">
@@ -25705,11 +25705,11 @@
         </is>
       </c>
       <c r="E842" s="3" t="n">
-        <v>17.49</v>
+        <v>19.52</v>
       </c>
       <c r="F842" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -25721,12 +25721,12 @@
       </c>
       <c r="B843" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C843" s="2" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="D843" s="2" t="inlineStr">
@@ -25735,11 +25735,11 @@
         </is>
       </c>
       <c r="E843" s="3" t="n">
-        <v>17.45</v>
+        <v>17.76</v>
       </c>
       <c r="F843" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25751,25 +25751,25 @@
       </c>
       <c r="B844" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C844" s="2" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="D844" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E844" s="3" t="n">
-        <v>16.14</v>
+        <v>17.57</v>
       </c>
       <c r="F844" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25781,12 +25781,12 @@
       </c>
       <c r="B845" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C845" s="2" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="D845" s="2" t="inlineStr">
@@ -25795,7 +25795,7 @@
         </is>
       </c>
       <c r="E845" s="3" t="n">
-        <v>15.77</v>
+        <v>17.49</v>
       </c>
       <c r="F845" s="2" t="inlineStr">
         <is>
@@ -25811,12 +25811,12 @@
       </c>
       <c r="B846" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C846" s="2" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="D846" s="2" t="inlineStr">
@@ -25825,7 +25825,7 @@
         </is>
       </c>
       <c r="E846" s="3" t="n">
-        <v>15.35</v>
+        <v>17.45</v>
       </c>
       <c r="F846" s="2" t="inlineStr">
         <is>
@@ -25841,12 +25841,12 @@
       </c>
       <c r="B847" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C847" s="2" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D847" s="2" t="inlineStr">
@@ -25855,11 +25855,11 @@
         </is>
       </c>
       <c r="E847" s="3" t="n">
-        <v>13.98</v>
+        <v>17.23</v>
       </c>
       <c r="F847" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25871,12 +25871,12 @@
       </c>
       <c r="B848" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C848" s="2" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="D848" s="2" t="inlineStr">
@@ -25885,7 +25885,7 @@
         </is>
       </c>
       <c r="E848" s="3" t="n">
-        <v>12.48</v>
+        <v>15.77</v>
       </c>
       <c r="F848" s="2" t="inlineStr">
         <is>
@@ -25915,11 +25915,11 @@
         </is>
       </c>
       <c r="E849" s="3" t="n">
-        <v>12.21</v>
+        <v>15.44</v>
       </c>
       <c r="F849" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25931,12 +25931,12 @@
       </c>
       <c r="B850" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C850" s="2" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="D850" s="2" t="inlineStr">
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="E850" s="3" t="n">
-        <v>12.19</v>
+        <v>15.35</v>
       </c>
       <c r="F850" s="2" t="inlineStr">
         <is>
@@ -25961,12 +25961,12 @@
       </c>
       <c r="B851" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C851" s="2" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="D851" s="2" t="inlineStr">
@@ -25975,11 +25975,11 @@
         </is>
       </c>
       <c r="E851" s="3" t="n">
-        <v>11.86</v>
+        <v>12.48</v>
       </c>
       <c r="F851" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25991,12 +25991,12 @@
       </c>
       <c r="B852" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C852" s="2" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="D852" s="2" t="inlineStr">
@@ -26005,7 +26005,7 @@
         </is>
       </c>
       <c r="E852" s="3" t="n">
-        <v>10.75</v>
+        <v>12.19</v>
       </c>
       <c r="F852" s="2" t="inlineStr">
         <is>
@@ -26035,11 +26035,11 @@
         </is>
       </c>
       <c r="E853" s="3" t="n">
-        <v>10.72</v>
+        <v>11.47</v>
       </c>
       <c r="F853" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -26051,12 +26051,12 @@
       </c>
       <c r="B854" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C854" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="D854" s="2" t="inlineStr">
@@ -26065,11 +26065,11 @@
         </is>
       </c>
       <c r="E854" s="3" t="n">
-        <v>10.7</v>
+        <v>10.75</v>
       </c>
       <c r="F854" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26081,12 +26081,12 @@
       </c>
       <c r="B855" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C855" s="2" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="D855" s="2" t="inlineStr">
@@ -26095,11 +26095,11 @@
         </is>
       </c>
       <c r="E855" s="3" t="n">
-        <v>10.07</v>
+        <v>10.18</v>
       </c>
       <c r="F855" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -26111,12 +26111,12 @@
       </c>
       <c r="B856" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C856" s="2" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="D856" s="2" t="inlineStr">
@@ -26125,7 +26125,7 @@
         </is>
       </c>
       <c r="E856" s="3" t="n">
-        <v>9.27</v>
+        <v>10.07</v>
       </c>
       <c r="F856" s="2" t="inlineStr">
         <is>
@@ -26141,12 +26141,12 @@
       </c>
       <c r="B857" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C857" s="2" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="D857" s="2" t="inlineStr">
@@ -26155,7 +26155,7 @@
         </is>
       </c>
       <c r="E857" s="3" t="n">
-        <v>8.529999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="F857" s="2" t="inlineStr">
         <is>
@@ -26171,12 +26171,12 @@
       </c>
       <c r="B858" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413773R6G</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C858" s="2" t="inlineStr">
         <is>
-          <t>812807</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="D858" s="2" t="inlineStr">
@@ -26185,7 +26185,7 @@
         </is>
       </c>
       <c r="E858" s="3" t="n">
-        <v>7.91</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="F858" s="2" t="inlineStr">
         <is>
@@ -26201,12 +26201,12 @@
       </c>
       <c r="B859" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0541381584X</t>
+          <t>KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="C859" s="2" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>812807</t>
         </is>
       </c>
       <c r="D859" s="2" t="inlineStr">
@@ -26215,7 +26215,7 @@
         </is>
       </c>
       <c r="E859" s="3" t="n">
-        <v>7.74</v>
+        <v>7.91</v>
       </c>
       <c r="F859" s="2" t="inlineStr">
         <is>
@@ -26231,12 +26231,12 @@
       </c>
       <c r="B860" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M0541381584X</t>
         </is>
       </c>
       <c r="C860" s="2" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>812810</t>
         </is>
       </c>
       <c r="D860" s="2" t="inlineStr">
@@ -26245,7 +26245,7 @@
         </is>
       </c>
       <c r="E860" s="3" t="n">
-        <v>7.52</v>
+        <v>7.74</v>
       </c>
       <c r="F860" s="2" t="inlineStr">
         <is>
@@ -26261,12 +26261,12 @@
       </c>
       <c r="B861" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C861" s="2" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="D861" s="2" t="inlineStr">
@@ -26275,7 +26275,7 @@
         </is>
       </c>
       <c r="E861" s="3" t="n">
-        <v>5.53</v>
+        <v>7.52</v>
       </c>
       <c r="F861" s="2" t="inlineStr">
         <is>
@@ -26291,12 +26291,12 @@
       </c>
       <c r="B862" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413775N9M</t>
+          <t>KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="C862" s="2" t="inlineStr">
         <is>
-          <t>812818</t>
+          <t>816274</t>
         </is>
       </c>
       <c r="D862" s="2" t="inlineStr">
@@ -26305,11 +26305,11 @@
         </is>
       </c>
       <c r="E862" s="3" t="n">
-        <v>4.49</v>
+        <v>6.2</v>
       </c>
       <c r="F862" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -26321,12 +26321,12 @@
       </c>
       <c r="B863" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604747TPT</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C863" s="2" t="inlineStr">
         <is>
-          <t>809873</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="D863" s="2" t="inlineStr">
@@ -26335,7 +26335,7 @@
         </is>
       </c>
       <c r="E863" s="3" t="n">
-        <v>2.93</v>
+        <v>5.53</v>
       </c>
       <c r="F863" s="2" t="inlineStr">
         <is>
@@ -26351,12 +26351,12 @@
       </c>
       <c r="B864" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138292ZP</t>
+          <t>KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="C864" s="2" t="inlineStr">
         <is>
-          <t>812784</t>
+          <t>812818</t>
         </is>
       </c>
       <c r="D864" s="2" t="inlineStr">
@@ -26365,7 +26365,7 @@
         </is>
       </c>
       <c r="E864" s="3" t="n">
-        <v>2.8</v>
+        <v>4.49</v>
       </c>
       <c r="F864" s="2" t="inlineStr">
         <is>
@@ -26381,12 +26381,12 @@
       </c>
       <c r="B865" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872588W8G</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C865" s="2" t="inlineStr">
         <is>
-          <t>816100</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="D865" s="2" t="inlineStr">
@@ -26395,11 +26395,11 @@
         </is>
       </c>
       <c r="E865" s="3" t="n">
-        <v>2.64</v>
+        <v>3.66</v>
       </c>
       <c r="F865" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -26411,12 +26411,12 @@
       </c>
       <c r="B866" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="C866" s="2" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>809873</t>
         </is>
       </c>
       <c r="D866" s="2" t="inlineStr">
@@ -26425,11 +26425,11 @@
         </is>
       </c>
       <c r="E866" s="3" t="n">
-        <v>2.55</v>
+        <v>2.93</v>
       </c>
       <c r="F866" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26441,12 +26441,12 @@
       </c>
       <c r="B867" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413772977</t>
+          <t>KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="C867" s="2" t="inlineStr">
         <is>
-          <t>812841</t>
+          <t>812784</t>
         </is>
       </c>
       <c r="D867" s="2" t="inlineStr">
@@ -26455,7 +26455,7 @@
         </is>
       </c>
       <c r="E867" s="3" t="n">
-        <v>1.76</v>
+        <v>2.8</v>
       </c>
       <c r="F867" s="2" t="inlineStr">
         <is>
@@ -26471,12 +26471,12 @@
       </c>
       <c r="B868" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413780XFH</t>
+          <t>KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="C868" s="2" t="inlineStr">
         <is>
-          <t>812833</t>
+          <t>816100</t>
         </is>
       </c>
       <c r="D868" s="2" t="inlineStr">
@@ -26485,11 +26485,11 @@
         </is>
       </c>
       <c r="E868" s="3" t="n">
-        <v>1.57</v>
+        <v>2.64</v>
       </c>
       <c r="F868" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26501,25 +26501,25 @@
       </c>
       <c r="B869" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000832637V6</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C869" s="2" t="inlineStr">
         <is>
-          <t>816334</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="D869" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E869" s="3" t="n">
-        <v>0.39</v>
+        <v>2.18</v>
       </c>
       <c r="F869" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -26531,12 +26531,12 @@
       </c>
       <c r="B870" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563503XXP</t>
+          <t>KIT4M05413772977</t>
         </is>
       </c>
       <c r="C870" s="2" t="inlineStr">
         <is>
-          <t>814430</t>
+          <t>812841</t>
         </is>
       </c>
       <c r="D870" s="2" t="inlineStr">
@@ -26545,7 +26545,7 @@
         </is>
       </c>
       <c r="E870" s="3" t="n">
-        <v>0.36</v>
+        <v>1.76</v>
       </c>
       <c r="F870" s="2" t="inlineStr">
         <is>
@@ -26561,25 +26561,25 @@
       </c>
       <c r="B871" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000655962DJ</t>
+          <t>KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="C871" s="2" t="inlineStr">
         <is>
-          <t>809604</t>
+          <t>812833</t>
         </is>
       </c>
       <c r="D871" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E871" s="3" t="n">
-        <v>0.26</v>
+        <v>1.6</v>
       </c>
       <c r="F871" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -26591,21 +26591,21 @@
       </c>
       <c r="B872" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413830JN7</t>
+          <t>KIT4P000832637V6</t>
         </is>
       </c>
       <c r="C872" s="2" t="inlineStr">
         <is>
-          <t>810105</t>
+          <t>816334</t>
         </is>
       </c>
       <c r="D872" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E872" s="3" t="n">
-        <v>0.12</v>
+        <v>0.39</v>
       </c>
       <c r="F872" s="2" t="inlineStr">
         <is>
@@ -26621,21 +26621,21 @@
       </c>
       <c r="B873" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065640BFW</t>
+          <t>KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="C873" s="2" t="inlineStr">
         <is>
-          <t>812929</t>
+          <t>814430</t>
         </is>
       </c>
       <c r="D873" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E873" s="3" t="n">
-        <v>0.06</v>
+        <v>0.36</v>
       </c>
       <c r="F873" s="2" t="inlineStr">
         <is>
@@ -26651,21 +26651,21 @@
       </c>
       <c r="B874" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4P000655962DJ</t>
         </is>
       </c>
       <c r="C874" s="2" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>809604</t>
         </is>
       </c>
       <c r="D874" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E874" s="3" t="n">
-        <v>0.04</v>
+        <v>0.26</v>
       </c>
       <c r="F874" s="2" t="inlineStr">
         <is>
@@ -26681,12 +26681,12 @@
       </c>
       <c r="B875" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413813HSJ</t>
+          <t>KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="C875" s="2" t="inlineStr">
         <is>
-          <t>812797</t>
+          <t>810105</t>
         </is>
       </c>
       <c r="D875" s="2" t="inlineStr">
@@ -26695,7 +26695,7 @@
         </is>
       </c>
       <c r="E875" s="3" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F875" s="2" t="inlineStr">
         <is>
@@ -26711,12 +26711,12 @@
       </c>
       <c r="B876" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563610HM2</t>
+          <t>KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="C876" s="2" t="inlineStr">
         <is>
-          <t>814486</t>
+          <t>809607</t>
         </is>
       </c>
       <c r="D876" s="2" t="inlineStr">
@@ -26725,11 +26725,11 @@
         </is>
       </c>
       <c r="E876" s="3" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="F876" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -26741,21 +26741,21 @@
       </c>
       <c r="B877" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563549RSR</t>
+          <t>KIT4P00065640BFW</t>
         </is>
       </c>
       <c r="C877" s="2" t="inlineStr">
         <is>
-          <t>814483</t>
+          <t>812929</t>
         </is>
       </c>
       <c r="D877" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E877" s="3" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="F877" s="2" t="inlineStr">
         <is>
@@ -26771,12 +26771,12 @@
       </c>
       <c r="B878" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C878" s="2" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="D878" s="2" t="inlineStr">
@@ -26785,7 +26785,7 @@
         </is>
       </c>
       <c r="E878" s="3" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F878" s="2" t="inlineStr">
         <is>
@@ -26801,12 +26801,12 @@
       </c>
       <c r="B879" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872513F7N</t>
+          <t>KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="C879" s="2" t="inlineStr">
         <is>
-          <t>816161</t>
+          <t>812797</t>
         </is>
       </c>
       <c r="D879" s="2" t="inlineStr">
@@ -26815,7 +26815,7 @@
         </is>
       </c>
       <c r="E879" s="3" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F879" s="2" t="inlineStr">
         <is>
@@ -26831,21 +26831,21 @@
       </c>
       <c r="B880" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083890S2G</t>
+          <t>KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="C880" s="2" t="inlineStr">
         <is>
-          <t>816226</t>
+          <t>814486</t>
         </is>
       </c>
       <c r="D880" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E880" s="3" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F880" s="2" t="inlineStr">
         <is>
@@ -26861,12 +26861,12 @@
       </c>
       <c r="B881" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866627GHD</t>
+          <t>KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="C881" s="2" t="inlineStr">
         <is>
-          <t>809619</t>
+          <t>814483</t>
         </is>
       </c>
       <c r="D881" s="2" t="inlineStr">
@@ -26875,7 +26875,7 @@
         </is>
       </c>
       <c r="E881" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F881" s="2" t="inlineStr">
         <is>
@@ -26891,12 +26891,12 @@
       </c>
       <c r="B882" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041546939GJ</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C882" s="2" t="inlineStr">
         <is>
-          <t>809607</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="D882" s="2" t="inlineStr">
@@ -26905,7 +26905,7 @@
         </is>
       </c>
       <c r="E882" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F882" s="2" t="inlineStr">
         <is>
@@ -26921,12 +26921,12 @@
       </c>
       <c r="B883" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04350554X4Z</t>
+          <t>KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="C883" s="2" t="inlineStr">
         <is>
-          <t>809866</t>
+          <t>816161</t>
         </is>
       </c>
       <c r="D883" s="2" t="inlineStr">
@@ -26935,7 +26935,7 @@
         </is>
       </c>
       <c r="E883" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F883" s="2" t="inlineStr">
         <is>
@@ -26951,21 +26951,21 @@
       </c>
       <c r="B884" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604734ZZX</t>
+          <t>KIT4P00083890S2G</t>
         </is>
       </c>
       <c r="C884" s="2" t="inlineStr">
         <is>
-          <t>809876</t>
+          <t>816226</t>
         </is>
       </c>
       <c r="D884" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E884" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F884" s="2" t="inlineStr">
         <is>
@@ -26981,12 +26981,12 @@
       </c>
       <c r="B885" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="C885" s="2" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>809619</t>
         </is>
       </c>
       <c r="D885" s="2" t="inlineStr">
@@ -27011,12 +27011,12 @@
       </c>
       <c r="B886" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368340DMZ</t>
+          <t>KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="C886" s="2" t="inlineStr">
         <is>
-          <t>810649</t>
+          <t>809866</t>
         </is>
       </c>
       <c r="D886" s="2" t="inlineStr">
@@ -27041,12 +27041,12 @@
       </c>
       <c r="B887" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413774JZX</t>
+          <t>KIT4M04604734ZZX</t>
         </is>
       </c>
       <c r="C887" s="2" t="inlineStr">
         <is>
-          <t>812836</t>
+          <t>809876</t>
         </is>
       </c>
       <c r="D887" s="2" t="inlineStr">
@@ -27071,12 +27071,12 @@
       </c>
       <c r="B888" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413778RBR</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C888" s="2" t="inlineStr">
         <is>
-          <t>812843</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="D888" s="2" t="inlineStr">
@@ -27101,12 +27101,12 @@
       </c>
       <c r="B889" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413790XCD</t>
+          <t>KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="C889" s="2" t="inlineStr">
         <is>
-          <t>812822</t>
+          <t>810649</t>
         </is>
       </c>
       <c r="D889" s="2" t="inlineStr">
@@ -27131,12 +27131,12 @@
       </c>
       <c r="B890" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413791FK5</t>
+          <t>KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="C890" s="2" t="inlineStr">
         <is>
-          <t>812842</t>
+          <t>812836</t>
         </is>
       </c>
       <c r="D890" s="2" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="B891" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137938P7</t>
+          <t>KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="C891" s="2" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>812843</t>
         </is>
       </c>
       <c r="D891" s="2" t="inlineStr">
@@ -27191,12 +27191,12 @@
       </c>
       <c r="B892" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="C892" s="2" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="D892" s="2" t="inlineStr">
@@ -27221,12 +27221,12 @@
       </c>
       <c r="B893" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M05413791FK5</t>
         </is>
       </c>
       <c r="C893" s="2" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>812842</t>
         </is>
       </c>
       <c r="D893" s="2" t="inlineStr">
@@ -27251,12 +27251,12 @@
       </c>
       <c r="B894" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4M054137938P7</t>
         </is>
       </c>
       <c r="C894" s="2" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>812848</t>
         </is>
       </c>
       <c r="D894" s="2" t="inlineStr">
@@ -27281,12 +27281,12 @@
       </c>
       <c r="B895" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413809J58</t>
+          <t>KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C895" s="2" t="inlineStr">
         <is>
-          <t>812805</t>
+          <t>812813</t>
         </is>
       </c>
       <c r="D895" s="2" t="inlineStr">
@@ -27311,12 +27311,12 @@
       </c>
       <c r="B896" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413821GGW</t>
+          <t>KIT4M05413809J58</t>
         </is>
       </c>
       <c r="C896" s="2" t="inlineStr">
         <is>
-          <t>812830</t>
+          <t>812805</t>
         </is>
       </c>
       <c r="D896" s="2" t="inlineStr">
@@ -27341,12 +27341,12 @@
       </c>
       <c r="B897" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563505WPS</t>
+          <t>KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="C897" s="2" t="inlineStr">
         <is>
-          <t>814448</t>
+          <t>812830</t>
         </is>
       </c>
       <c r="D897" s="2" t="inlineStr">
@@ -27371,12 +27371,12 @@
       </c>
       <c r="B898" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563517BVR</t>
+          <t>KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="C898" s="2" t="inlineStr">
         <is>
-          <t>814438</t>
+          <t>814448</t>
         </is>
       </c>
       <c r="D898" s="2" t="inlineStr">
@@ -27401,12 +27401,12 @@
       </c>
       <c r="B899" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563536BPJ</t>
+          <t>KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="C899" s="2" t="inlineStr">
         <is>
-          <t>814466</t>
+          <t>814438</t>
         </is>
       </c>
       <c r="D899" s="2" t="inlineStr">
@@ -27431,12 +27431,12 @@
       </c>
       <c r="B900" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563554WCW</t>
+          <t>KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="C900" s="2" t="inlineStr">
         <is>
-          <t>814444</t>
+          <t>814466</t>
         </is>
       </c>
       <c r="D900" s="2" t="inlineStr">
@@ -27461,12 +27461,12 @@
       </c>
       <c r="B901" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556355588P</t>
+          <t>KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="C901" s="2" t="inlineStr">
         <is>
-          <t>814455</t>
+          <t>814444</t>
         </is>
       </c>
       <c r="D901" s="2" t="inlineStr">
@@ -27491,12 +27491,12 @@
       </c>
       <c r="B902" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996395ZF</t>
+          <t>KIT4M0556355588P</t>
         </is>
       </c>
       <c r="C902" s="2" t="inlineStr">
         <is>
-          <t>816268</t>
+          <t>814455</t>
         </is>
       </c>
       <c r="D902" s="2" t="inlineStr">
@@ -27521,12 +27521,12 @@
       </c>
       <c r="B903" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799709G5Q</t>
+          <t>KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="C903" s="2" t="inlineStr">
         <is>
-          <t>816274</t>
+          <t>816268</t>
         </is>
       </c>
       <c r="D903" s="2" t="inlineStr">

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2245.64</v>
+        <v>2269.29</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -19795,11 +19795,11 @@
         </is>
       </c>
       <c r="E645" s="3" t="n">
-        <v>1784.76</v>
+        <v>1821.96</v>
       </c>
       <c r="F645" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -19885,11 +19885,11 @@
         </is>
       </c>
       <c r="E648" s="3" t="n">
-        <v>992.95</v>
+        <v>1003.52</v>
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>960.47</v>
+        <v>984.46</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20005,11 +20005,11 @@
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>682.47</v>
+        <v>703.4</v>
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20035,11 +20035,11 @@
         </is>
       </c>
       <c r="E653" s="3" t="n">
-        <v>669.9400000000001</v>
+        <v>688.98</v>
       </c>
       <c r="F653" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20095,11 +20095,11 @@
         </is>
       </c>
       <c r="E655" s="3" t="n">
-        <v>604.02</v>
+        <v>605.52</v>
       </c>
       <c r="F655" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20111,25 +20111,25 @@
       </c>
       <c r="B656" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739124KF</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C656" s="2" t="inlineStr">
         <is>
-          <t>814640</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="D656" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E656" s="3" t="n">
-        <v>592.92</v>
+        <v>593.35</v>
       </c>
       <c r="F656" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20141,21 +20141,21 @@
       </c>
       <c r="B657" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4P000739124KF</t>
         </is>
       </c>
       <c r="C657" s="2" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>814640</t>
         </is>
       </c>
       <c r="D657" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>591.8099999999999</v>
+        <v>592.92</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
@@ -20185,11 +20185,11 @@
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>582.08</v>
+        <v>585.6900000000001</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20215,11 +20215,11 @@
         </is>
       </c>
       <c r="E659" s="3" t="n">
-        <v>550.36</v>
+        <v>556.21</v>
       </c>
       <c r="F659" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20245,11 +20245,11 @@
         </is>
       </c>
       <c r="E660" s="3" t="n">
-        <v>542.9</v>
+        <v>548.27</v>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20261,12 +20261,12 @@
       </c>
       <c r="B661" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C661" s="2" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="D661" s="2" t="inlineStr">
@@ -20275,11 +20275,11 @@
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>513.88</v>
+        <v>524.21</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20291,12 +20291,12 @@
       </c>
       <c r="B662" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C662" s="2" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="D662" s="2" t="inlineStr">
@@ -20305,11 +20305,11 @@
         </is>
       </c>
       <c r="E662" s="3" t="n">
-        <v>512.99</v>
+        <v>513.88</v>
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20365,11 +20365,11 @@
         </is>
       </c>
       <c r="E664" s="3" t="n">
-        <v>482.48</v>
+        <v>485.2</v>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20425,11 +20425,11 @@
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>472.04</v>
+        <v>473.39</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20441,25 +20441,25 @@
       </c>
       <c r="B667" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C667" s="2" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="D667" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E667" s="3" t="n">
-        <v>466.53</v>
+        <v>470.76</v>
       </c>
       <c r="F667" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20471,25 +20471,25 @@
       </c>
       <c r="B668" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C668" s="2" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="D668" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E668" s="3" t="n">
-        <v>460.8</v>
+        <v>466.53</v>
       </c>
       <c r="F668" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20515,11 +20515,11 @@
         </is>
       </c>
       <c r="E669" s="3" t="n">
-        <v>446.17</v>
+        <v>449.91</v>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20561,25 +20561,25 @@
       </c>
       <c r="B671" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084601T5F</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C671" s="2" t="inlineStr">
         <is>
-          <t>816335</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="D671" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E671" s="3" t="n">
-        <v>401.51</v>
+        <v>403.12</v>
       </c>
       <c r="F671" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20591,25 +20591,25 @@
       </c>
       <c r="B672" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="C672" s="2" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>816335</t>
         </is>
       </c>
       <c r="D672" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E672" s="3" t="n">
-        <v>394.8</v>
+        <v>401.51</v>
       </c>
       <c r="F672" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20621,12 +20621,12 @@
       </c>
       <c r="B673" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C673" s="2" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="D673" s="2" t="inlineStr">
@@ -20635,11 +20635,11 @@
         </is>
       </c>
       <c r="E673" s="3" t="n">
-        <v>372</v>
+        <v>378.91</v>
       </c>
       <c r="F673" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20651,25 +20651,25 @@
       </c>
       <c r="B674" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C674" s="2" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="D674" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E674" s="3" t="n">
-        <v>366.52</v>
+        <v>374.64</v>
       </c>
       <c r="F674" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20681,25 +20681,25 @@
       </c>
       <c r="B675" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C675" s="2" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="D675" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>365</v>
+        <v>366.97</v>
       </c>
       <c r="F675" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20725,11 +20725,11 @@
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>326.28</v>
+        <v>328.16</v>
       </c>
       <c r="F676" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20815,11 +20815,11 @@
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>297.42</v>
+        <v>305.69</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>278.51</v>
+        <v>287.3</v>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20875,11 +20875,11 @@
         </is>
       </c>
       <c r="E681" s="3" t="n">
-        <v>275.32</v>
+        <v>275.64</v>
       </c>
       <c r="F681" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -20995,11 +20995,11 @@
         </is>
       </c>
       <c r="E685" s="3" t="n">
-        <v>242.62</v>
+        <v>242.65</v>
       </c>
       <c r="F685" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21025,11 +21025,11 @@
         </is>
       </c>
       <c r="E686" s="3" t="n">
-        <v>237.92</v>
+        <v>239.25</v>
       </c>
       <c r="F686" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21085,11 +21085,11 @@
         </is>
       </c>
       <c r="E688" s="3" t="n">
-        <v>222.04</v>
+        <v>223.24</v>
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21101,25 +21101,25 @@
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="D689" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>210.22</v>
+        <v>214.68</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21131,12 +21131,12 @@
       </c>
       <c r="B690" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C690" s="2" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="D690" s="2" t="inlineStr">
@@ -21145,11 +21145,11 @@
         </is>
       </c>
       <c r="E690" s="3" t="n">
-        <v>208.78</v>
+        <v>210.52</v>
       </c>
       <c r="F690" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21161,25 +21161,25 @@
       </c>
       <c r="B691" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C691" s="2" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="D691" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E691" s="3" t="n">
-        <v>206.24</v>
+        <v>208.79</v>
       </c>
       <c r="F691" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21205,11 +21205,11 @@
         </is>
       </c>
       <c r="E692" s="3" t="n">
-        <v>204.31</v>
+        <v>204.43</v>
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21235,11 +21235,11 @@
         </is>
       </c>
       <c r="E693" s="3" t="n">
-        <v>193.94</v>
+        <v>197.22</v>
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21265,11 +21265,11 @@
         </is>
       </c>
       <c r="E694" s="3" t="n">
-        <v>193.42</v>
+        <v>194.42</v>
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>192.37</v>
+        <v>193</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>173.09</v>
+        <v>176.16</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="E698" s="3" t="n">
-        <v>170.77</v>
+        <v>170.8</v>
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>168.2</v>
+        <v>168.72</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21431,12 +21431,12 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="D700" s="2" t="inlineStr">
@@ -21445,11 +21445,11 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>158.82</v>
+        <v>160.14</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21461,12 +21461,12 @@
       </c>
       <c r="B701" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C701" s="2" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="D701" s="2" t="inlineStr">
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>158.38</v>
+        <v>158.82</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21505,11 +21505,11 @@
         </is>
       </c>
       <c r="E702" s="3" t="n">
-        <v>154.17</v>
+        <v>154.57</v>
       </c>
       <c r="F702" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21565,11 +21565,11 @@
         </is>
       </c>
       <c r="E704" s="3" t="n">
-        <v>147.36</v>
+        <v>147.37</v>
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>146.72</v>
+        <v>147.2</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21625,11 +21625,11 @@
         </is>
       </c>
       <c r="E706" s="3" t="n">
-        <v>140.59</v>
+        <v>143.19</v>
       </c>
       <c r="F706" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21685,11 +21685,11 @@
         </is>
       </c>
       <c r="E708" s="3" t="n">
-        <v>134.03</v>
+        <v>134.18</v>
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21701,12 +21701,12 @@
       </c>
       <c r="B709" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C709" s="2" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="D709" s="2" t="inlineStr">
@@ -21715,11 +21715,11 @@
         </is>
       </c>
       <c r="E709" s="3" t="n">
-        <v>132.39</v>
+        <v>132.43</v>
       </c>
       <c r="F709" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21731,12 +21731,12 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="D710" s="2" t="inlineStr">
@@ -21745,11 +21745,11 @@
         </is>
       </c>
       <c r="E710" s="3" t="n">
-        <v>131.75</v>
+        <v>132.39</v>
       </c>
       <c r="F710" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21761,12 +21761,12 @@
       </c>
       <c r="B711" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C711" s="2" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="D711" s="2" t="inlineStr">
@@ -21775,11 +21775,11 @@
         </is>
       </c>
       <c r="E711" s="3" t="n">
-        <v>131.31</v>
+        <v>131.75</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -21791,12 +21791,12 @@
       </c>
       <c r="B712" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C712" s="2" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="D712" s="2" t="inlineStr">
@@ -21805,11 +21805,11 @@
         </is>
       </c>
       <c r="E712" s="3" t="n">
-        <v>131.27</v>
+        <v>131.31</v>
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21865,11 +21865,11 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>127.39</v>
+        <v>128.42</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>123.44</v>
+        <v>123.45</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>121.08</v>
+        <v>122.51</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22015,11 +22015,11 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>120.6</v>
+        <v>120.85</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22075,11 +22075,11 @@
         </is>
       </c>
       <c r="E721" s="3" t="n">
-        <v>116.72</v>
+        <v>117.79</v>
       </c>
       <c r="F721" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22165,11 +22165,11 @@
         </is>
       </c>
       <c r="E724" s="3" t="n">
-        <v>111.11</v>
+        <v>111.17</v>
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22195,11 +22195,11 @@
         </is>
       </c>
       <c r="E725" s="3" t="n">
-        <v>110.55</v>
+        <v>110.73</v>
       </c>
       <c r="F725" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22225,11 +22225,11 @@
         </is>
       </c>
       <c r="E726" s="3" t="n">
-        <v>108.09</v>
+        <v>108.56</v>
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22255,11 +22255,11 @@
         </is>
       </c>
       <c r="E727" s="3" t="n">
-        <v>107.86</v>
+        <v>107.87</v>
       </c>
       <c r="F727" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22361,12 +22361,12 @@
       </c>
       <c r="B731" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="D731" s="2" t="inlineStr">
@@ -22375,11 +22375,11 @@
         </is>
       </c>
       <c r="E731" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>100.47</v>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22391,12 +22391,12 @@
       </c>
       <c r="B732" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="D732" s="2" t="inlineStr">
@@ -22405,11 +22405,11 @@
         </is>
       </c>
       <c r="E732" s="3" t="n">
-        <v>98.84999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22465,11 +22465,11 @@
         </is>
       </c>
       <c r="E734" s="3" t="n">
-        <v>96.97</v>
+        <v>97.04000000000001</v>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22481,12 +22481,12 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
@@ -22495,11 +22495,11 @@
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>95.31999999999999</v>
+        <v>95.53</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22511,12 +22511,12 @@
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
@@ -22525,11 +22525,11 @@
         </is>
       </c>
       <c r="E736" s="3" t="n">
-        <v>93.83</v>
+        <v>95.36</v>
       </c>
       <c r="F736" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22541,12 +22541,12 @@
       </c>
       <c r="B737" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D737" s="2" t="inlineStr">
@@ -22555,11 +22555,11 @@
         </is>
       </c>
       <c r="E737" s="3" t="n">
-        <v>93.78</v>
+        <v>93.83</v>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22571,12 +22571,12 @@
       </c>
       <c r="B738" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="D738" s="2" t="inlineStr">
@@ -22585,11 +22585,11 @@
         </is>
       </c>
       <c r="E738" s="3" t="n">
-        <v>91.25</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22601,12 +22601,12 @@
       </c>
       <c r="B739" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C739" s="2" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D739" s="2" t="inlineStr">
@@ -22615,11 +22615,11 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>89.79000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22631,21 +22631,21 @@
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E740" s="3" t="n">
-        <v>89.48999999999999</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
@@ -22661,25 +22661,25 @@
       </c>
       <c r="B741" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="D741" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E741" s="3" t="n">
-        <v>88.95</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F741" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>88.5</v>
+        <v>88.86</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22751,12 +22751,12 @@
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="D744" s="2" t="inlineStr">
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>87.69</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22781,12 +22781,12 @@
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr">
@@ -22795,11 +22795,11 @@
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>84.86</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22811,12 +22811,12 @@
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
@@ -22825,11 +22825,11 @@
         </is>
       </c>
       <c r="E746" s="3" t="n">
-        <v>84.23999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22841,12 +22841,12 @@
       </c>
       <c r="B747" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C747" s="2" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="D747" s="2" t="inlineStr">
@@ -22855,11 +22855,11 @@
         </is>
       </c>
       <c r="E747" s="3" t="n">
-        <v>84.08</v>
+        <v>85.22</v>
       </c>
       <c r="F747" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22871,12 +22871,12 @@
       </c>
       <c r="B748" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C748" s="2" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="D748" s="2" t="inlineStr">
@@ -22885,7 +22885,7 @@
         </is>
       </c>
       <c r="E748" s="3" t="n">
-        <v>83.34999999999999</v>
+        <v>84.86</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
@@ -22901,12 +22901,12 @@
       </c>
       <c r="B749" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C749" s="2" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="D749" s="2" t="inlineStr">
@@ -22915,11 +22915,11 @@
         </is>
       </c>
       <c r="E749" s="3" t="n">
-        <v>82.73</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F749" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23005,11 +23005,11 @@
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>80.84999999999999</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23065,11 +23065,11 @@
         </is>
       </c>
       <c r="E754" s="3" t="n">
-        <v>79.14</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="F754" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23171,12 +23171,12 @@
       </c>
       <c r="B758" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C758" s="2" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="D758" s="2" t="inlineStr">
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>72.83</v>
+        <v>72.97</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23201,12 +23201,12 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="D759" s="2" t="inlineStr">
@@ -23215,7 +23215,7 @@
         </is>
       </c>
       <c r="E759" s="3" t="n">
-        <v>71.66</v>
+        <v>72.83</v>
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
@@ -23245,11 +23245,11 @@
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>71.51000000000001</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23305,11 +23305,11 @@
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>69.45999999999999</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23335,11 +23335,11 @@
         </is>
       </c>
       <c r="E763" s="3" t="n">
-        <v>68.3</v>
+        <v>68.5</v>
       </c>
       <c r="F763" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>64.87</v>
+        <v>64.88</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23395,11 +23395,11 @@
         </is>
       </c>
       <c r="E765" s="3" t="n">
-        <v>63.84</v>
+        <v>64.45</v>
       </c>
       <c r="F765" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>63.63</v>
+        <v>63.66</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23485,11 +23485,11 @@
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>63.28</v>
+        <v>63.45</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23515,11 +23515,11 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>62.66</v>
+        <v>62.83</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23591,12 +23591,12 @@
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -23605,11 +23605,11 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>60.88</v>
+        <v>61.83</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23621,12 +23621,12 @@
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D773" s="2" t="inlineStr">
@@ -23635,7 +23635,7 @@
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>60.74</v>
+        <v>60.88</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
@@ -23651,12 +23651,12 @@
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr">
@@ -23665,11 +23665,11 @@
         </is>
       </c>
       <c r="E774" s="3" t="n">
-        <v>60.31</v>
+        <v>60.74</v>
       </c>
       <c r="F774" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -23681,12 +23681,12 @@
       </c>
       <c r="B775" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C775" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D775" s="2" t="inlineStr">
@@ -23695,11 +23695,11 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>58.89</v>
+        <v>60.46</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23711,12 +23711,12 @@
       </c>
       <c r="B776" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C776" s="2" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="D776" s="2" t="inlineStr">
@@ -23725,11 +23725,11 @@
         </is>
       </c>
       <c r="E776" s="3" t="n">
-        <v>57.86</v>
+        <v>58.9</v>
       </c>
       <c r="F776" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23755,11 +23755,11 @@
         </is>
       </c>
       <c r="E777" s="3" t="n">
-        <v>57.79</v>
+        <v>58.76</v>
       </c>
       <c r="F777" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23771,12 +23771,12 @@
       </c>
       <c r="B778" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C778" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="D778" s="2" t="inlineStr">
@@ -23785,7 +23785,7 @@
         </is>
       </c>
       <c r="E778" s="3" t="n">
-        <v>57.61</v>
+        <v>57.86</v>
       </c>
       <c r="F778" s="2" t="inlineStr">
         <is>
@@ -23831,17 +23831,17 @@
       </c>
       <c r="B780" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C780" s="2" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="D780" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E780" s="3" t="n">
@@ -23849,7 +23849,7 @@
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23861,25 +23861,25 @@
       </c>
       <c r="B781" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C781" s="2" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="D781" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E781" s="3" t="n">
-        <v>57.18</v>
+        <v>57.22</v>
       </c>
       <c r="F781" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23921,12 +23921,12 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D783" s="2" t="inlineStr">
@@ -23935,11 +23935,11 @@
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>56.5</v>
+        <v>56.53</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23951,12 +23951,12 @@
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
@@ -23969,7 +23969,7 @@
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24011,12 +24011,12 @@
       </c>
       <c r="B786" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C786" s="2" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="D786" s="2" t="inlineStr">
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>53.95</v>
+        <v>54.59</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -24041,12 +24041,12 @@
       </c>
       <c r="B787" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C787" s="2" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="D787" s="2" t="inlineStr">
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>53.88</v>
+        <v>53.95</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24071,12 +24071,12 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="D788" s="2" t="inlineStr">
@@ -24085,11 +24085,11 @@
         </is>
       </c>
       <c r="E788" s="3" t="n">
-        <v>53.24</v>
+        <v>53.91</v>
       </c>
       <c r="F788" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>53</v>
+        <v>53.53</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -24131,12 +24131,12 @@
       </c>
       <c r="B790" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C790" s="2" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="D790" s="2" t="inlineStr">
@@ -24145,11 +24145,11 @@
         </is>
       </c>
       <c r="E790" s="3" t="n">
-        <v>52.57</v>
+        <v>53.24</v>
       </c>
       <c r="F790" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -24161,12 +24161,12 @@
       </c>
       <c r="B791" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C791" s="2" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="D791" s="2" t="inlineStr">
@@ -24175,11 +24175,11 @@
         </is>
       </c>
       <c r="E791" s="3" t="n">
-        <v>52.13</v>
+        <v>52.57</v>
       </c>
       <c r="F791" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24191,12 +24191,12 @@
       </c>
       <c r="B792" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C792" s="2" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="D792" s="2" t="inlineStr">
@@ -24205,11 +24205,11 @@
         </is>
       </c>
       <c r="E792" s="3" t="n">
-        <v>51.59</v>
+        <v>52.42</v>
       </c>
       <c r="F792" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -24235,11 +24235,11 @@
         </is>
       </c>
       <c r="E793" s="3" t="n">
-        <v>50.49</v>
+        <v>50.51</v>
       </c>
       <c r="F793" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -24295,11 +24295,11 @@
         </is>
       </c>
       <c r="E795" s="3" t="n">
-        <v>48.09</v>
+        <v>48.74</v>
       </c>
       <c r="F795" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -24431,12 +24431,12 @@
       </c>
       <c r="B800" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C800" s="2" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D800" s="2" t="inlineStr">
@@ -24445,11 +24445,11 @@
         </is>
       </c>
       <c r="E800" s="3" t="n">
-        <v>46.1</v>
+        <v>46.46</v>
       </c>
       <c r="F800" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -24461,12 +24461,12 @@
       </c>
       <c r="B801" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C801" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="D801" s="2" t="inlineStr">
@@ -24475,11 +24475,11 @@
         </is>
       </c>
       <c r="E801" s="3" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="F801" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24505,11 +24505,11 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>45.85</v>
+        <v>45.88</v>
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -24535,11 +24535,11 @@
         </is>
       </c>
       <c r="E803" s="3" t="n">
-        <v>44.93</v>
+        <v>44.94</v>
       </c>
       <c r="F803" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -24595,11 +24595,11 @@
         </is>
       </c>
       <c r="E805" s="3" t="n">
-        <v>44.67</v>
+        <v>44.71</v>
       </c>
       <c r="F805" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -24731,12 +24731,12 @@
       </c>
       <c r="B810" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C810" s="2" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="D810" s="2" t="inlineStr">
@@ -24745,11 +24745,11 @@
         </is>
       </c>
       <c r="E810" s="3" t="n">
-        <v>37.65</v>
+        <v>37.86</v>
       </c>
       <c r="F810" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -24761,12 +24761,12 @@
       </c>
       <c r="B811" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C811" s="2" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="D811" s="2" t="inlineStr">
@@ -24775,11 +24775,11 @@
         </is>
       </c>
       <c r="E811" s="3" t="n">
-        <v>37.45</v>
+        <v>37.65</v>
       </c>
       <c r="F811" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24851,12 +24851,12 @@
       </c>
       <c r="B814" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C814" s="2" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="D814" s="2" t="inlineStr">
@@ -24865,11 +24865,11 @@
         </is>
       </c>
       <c r="E814" s="3" t="n">
-        <v>36.31</v>
+        <v>36.37</v>
       </c>
       <c r="F814" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -24881,12 +24881,12 @@
       </c>
       <c r="B815" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C815" s="2" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="D815" s="2" t="inlineStr">
@@ -24895,11 +24895,11 @@
         </is>
       </c>
       <c r="E815" s="3" t="n">
-        <v>35.89</v>
+        <v>36.31</v>
       </c>
       <c r="F815" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25015,11 +25015,11 @@
         </is>
       </c>
       <c r="E819" s="3" t="n">
-        <v>32.8</v>
+        <v>33.09</v>
       </c>
       <c r="F819" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -25105,11 +25105,11 @@
         </is>
       </c>
       <c r="E822" s="3" t="n">
-        <v>29.4</v>
+        <v>29.63</v>
       </c>
       <c r="F822" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -25151,12 +25151,12 @@
       </c>
       <c r="B824" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C824" s="2" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D824" s="2" t="inlineStr">
@@ -25165,11 +25165,11 @@
         </is>
       </c>
       <c r="E824" s="3" t="n">
-        <v>28.85</v>
+        <v>28.88</v>
       </c>
       <c r="F824" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -25181,12 +25181,12 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="D825" s="2" t="inlineStr">
@@ -25195,11 +25195,11 @@
         </is>
       </c>
       <c r="E825" s="3" t="n">
-        <v>27.22</v>
+        <v>28.85</v>
       </c>
       <c r="F825" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25211,12 +25211,12 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="D826" s="2" t="inlineStr">
@@ -25225,7 +25225,7 @@
         </is>
       </c>
       <c r="E826" s="3" t="n">
-        <v>26.67</v>
+        <v>27.22</v>
       </c>
       <c r="F826" s="2" t="inlineStr">
         <is>
@@ -25241,25 +25241,25 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="D827" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E827" s="3" t="n">
-        <v>26.15</v>
+        <v>26.7</v>
       </c>
       <c r="F827" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -25271,25 +25271,25 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="D828" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E828" s="3" t="n">
-        <v>24.7</v>
+        <v>26.15</v>
       </c>
       <c r="F828" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25301,12 +25301,12 @@
       </c>
       <c r="B829" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C829" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="D829" s="2" t="inlineStr">
@@ -25315,11 +25315,11 @@
         </is>
       </c>
       <c r="E829" s="3" t="n">
-        <v>23.99</v>
+        <v>24.71</v>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -25391,12 +25391,12 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="D832" s="2" t="inlineStr">
@@ -25405,11 +25405,11 @@
         </is>
       </c>
       <c r="E832" s="3" t="n">
-        <v>21.7</v>
+        <v>21.89</v>
       </c>
       <c r="F832" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -25421,12 +25421,12 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="D833" s="2" t="inlineStr">
@@ -25435,7 +25435,7 @@
         </is>
       </c>
       <c r="E833" s="3" t="n">
-        <v>21.54</v>
+        <v>21.7</v>
       </c>
       <c r="F833" s="2" t="inlineStr">
         <is>
@@ -25465,11 +25465,11 @@
         </is>
       </c>
       <c r="E834" s="3" t="n">
-        <v>21.26</v>
+        <v>21.35</v>
       </c>
       <c r="F834" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -25615,11 +25615,11 @@
         </is>
       </c>
       <c r="E839" s="3" t="n">
-        <v>20.26</v>
+        <v>20.36</v>
       </c>
       <c r="F839" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -25751,12 +25751,12 @@
       </c>
       <c r="B844" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C844" s="2" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="D844" s="2" t="inlineStr">
@@ -25765,11 +25765,11 @@
         </is>
       </c>
       <c r="E844" s="3" t="n">
-        <v>17.57</v>
+        <v>17.63</v>
       </c>
       <c r="F844" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -25781,12 +25781,12 @@
       </c>
       <c r="B845" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C845" s="2" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="D845" s="2" t="inlineStr">
@@ -25795,7 +25795,7 @@
         </is>
       </c>
       <c r="E845" s="3" t="n">
-        <v>17.49</v>
+        <v>17.57</v>
       </c>
       <c r="F845" s="2" t="inlineStr">
         <is>
@@ -25811,12 +25811,12 @@
       </c>
       <c r="B846" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C846" s="2" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="D846" s="2" t="inlineStr">
@@ -25825,7 +25825,7 @@
         </is>
       </c>
       <c r="E846" s="3" t="n">
-        <v>17.45</v>
+        <v>17.49</v>
       </c>
       <c r="F846" s="2" t="inlineStr">
         <is>
@@ -25841,12 +25841,12 @@
       </c>
       <c r="B847" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C847" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="D847" s="2" t="inlineStr">
@@ -25855,11 +25855,11 @@
         </is>
       </c>
       <c r="E847" s="3" t="n">
-        <v>17.23</v>
+        <v>17.45</v>
       </c>
       <c r="F847" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25871,12 +25871,12 @@
       </c>
       <c r="B848" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C848" s="2" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D848" s="2" t="inlineStr">
@@ -25885,11 +25885,11 @@
         </is>
       </c>
       <c r="E848" s="3" t="n">
-        <v>15.77</v>
+        <v>17.4</v>
       </c>
       <c r="F848" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -25901,12 +25901,12 @@
       </c>
       <c r="B849" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C849" s="2" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="D849" s="2" t="inlineStr">
@@ -25915,11 +25915,11 @@
         </is>
       </c>
       <c r="E849" s="3" t="n">
-        <v>15.44</v>
+        <v>15.77</v>
       </c>
       <c r="F849" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26305,11 +26305,11 @@
         </is>
       </c>
       <c r="E862" s="3" t="n">
-        <v>6.2</v>
+        <v>6.21</v>
       </c>
       <c r="F862" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -26381,12 +26381,12 @@
       </c>
       <c r="B865" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C865" s="2" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="D865" s="2" t="inlineStr">
@@ -26395,11 +26395,11 @@
         </is>
       </c>
       <c r="E865" s="3" t="n">
-        <v>3.66</v>
+        <v>4.15</v>
       </c>
       <c r="F865" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -26411,12 +26411,12 @@
       </c>
       <c r="B866" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604747TPT</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C866" s="2" t="inlineStr">
         <is>
-          <t>809873</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="D866" s="2" t="inlineStr">
@@ -26425,11 +26425,11 @@
         </is>
       </c>
       <c r="E866" s="3" t="n">
-        <v>2.93</v>
+        <v>3.66</v>
       </c>
       <c r="F866" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -26441,12 +26441,12 @@
       </c>
       <c r="B867" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138292ZP</t>
+          <t>KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="C867" s="2" t="inlineStr">
         <is>
-          <t>812784</t>
+          <t>809873</t>
         </is>
       </c>
       <c r="D867" s="2" t="inlineStr">
@@ -26455,7 +26455,7 @@
         </is>
       </c>
       <c r="E867" s="3" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="F867" s="2" t="inlineStr">
         <is>
@@ -26471,12 +26471,12 @@
       </c>
       <c r="B868" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872588W8G</t>
+          <t>KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="C868" s="2" t="inlineStr">
         <is>
-          <t>816100</t>
+          <t>812784</t>
         </is>
       </c>
       <c r="D868" s="2" t="inlineStr">
@@ -26485,7 +26485,7 @@
         </is>
       </c>
       <c r="E868" s="3" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="F868" s="2" t="inlineStr">
         <is>
@@ -26501,12 +26501,12 @@
       </c>
       <c r="B869" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="C869" s="2" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>816100</t>
         </is>
       </c>
       <c r="D869" s="2" t="inlineStr">
@@ -26515,11 +26515,11 @@
         </is>
       </c>
       <c r="E869" s="3" t="n">
-        <v>2.18</v>
+        <v>2.64</v>
       </c>
       <c r="F869" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2269.29</v>
+        <v>2286.25</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -19795,11 +19795,11 @@
         </is>
       </c>
       <c r="E645" s="3" t="n">
-        <v>1821.96</v>
+        <v>1869.69</v>
       </c>
       <c r="F645" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -19885,11 +19885,11 @@
         </is>
       </c>
       <c r="E648" s="3" t="n">
-        <v>1003.52</v>
+        <v>1013.81</v>
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>984.46</v>
+        <v>1000.21</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -19991,25 +19991,25 @@
       </c>
       <c r="B652" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413776H84</t>
+          <t>KIT4P000739257CR</t>
         </is>
       </c>
       <c r="C652" s="2" t="inlineStr">
         <is>
-          <t>810101</t>
+          <t>814609</t>
         </is>
       </c>
       <c r="D652" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>703.4</v>
+        <v>719.61</v>
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20021,25 +20021,25 @@
       </c>
       <c r="B653" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739257CR</t>
+          <t>KIT4M05413776H84</t>
         </is>
       </c>
       <c r="C653" s="2" t="inlineStr">
         <is>
-          <t>814609</t>
+          <t>810101</t>
         </is>
       </c>
       <c r="D653" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E653" s="3" t="n">
-        <v>688.98</v>
+        <v>707.25</v>
       </c>
       <c r="F653" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20095,11 +20095,11 @@
         </is>
       </c>
       <c r="E655" s="3" t="n">
-        <v>605.52</v>
+        <v>606.37</v>
       </c>
       <c r="F655" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20111,25 +20111,25 @@
       </c>
       <c r="B656" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4P000739124KF</t>
         </is>
       </c>
       <c r="C656" s="2" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>814640</t>
         </is>
       </c>
       <c r="D656" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E656" s="3" t="n">
-        <v>593.35</v>
+        <v>598.02</v>
       </c>
       <c r="F656" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20141,25 +20141,25 @@
       </c>
       <c r="B657" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739124KF</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C657" s="2" t="inlineStr">
         <is>
-          <t>814640</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="D657" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>592.92</v>
+        <v>596.73</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20185,11 +20185,11 @@
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>585.6900000000001</v>
+        <v>596.3200000000001</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20215,11 +20215,11 @@
         </is>
       </c>
       <c r="E659" s="3" t="n">
-        <v>556.21</v>
+        <v>557.42</v>
       </c>
       <c r="F659" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20245,11 +20245,11 @@
         </is>
       </c>
       <c r="E660" s="3" t="n">
-        <v>548.27</v>
+        <v>549.29</v>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20275,11 +20275,11 @@
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>524.21</v>
+        <v>525.55</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20365,11 +20365,11 @@
         </is>
       </c>
       <c r="E664" s="3" t="n">
-        <v>485.2</v>
+        <v>488.57</v>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20425,11 +20425,11 @@
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>473.39</v>
+        <v>478.46</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20455,11 +20455,11 @@
         </is>
       </c>
       <c r="E667" s="3" t="n">
-        <v>470.76</v>
+        <v>474.04</v>
       </c>
       <c r="F667" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20515,11 +20515,11 @@
         </is>
       </c>
       <c r="E669" s="3" t="n">
-        <v>449.91</v>
+        <v>451.12</v>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20575,11 +20575,11 @@
         </is>
       </c>
       <c r="E671" s="3" t="n">
-        <v>403.12</v>
+        <v>409.33</v>
       </c>
       <c r="F671" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20621,12 +20621,12 @@
       </c>
       <c r="B673" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C673" s="2" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="D673" s="2" t="inlineStr">
@@ -20635,11 +20635,11 @@
         </is>
       </c>
       <c r="E673" s="3" t="n">
-        <v>378.91</v>
+        <v>381.85</v>
       </c>
       <c r="F673" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20651,12 +20651,12 @@
       </c>
       <c r="B674" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C674" s="2" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="D674" s="2" t="inlineStr">
@@ -20665,11 +20665,11 @@
         </is>
       </c>
       <c r="E674" s="3" t="n">
-        <v>374.64</v>
+        <v>381.7</v>
       </c>
       <c r="F674" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20695,11 +20695,11 @@
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>366.97</v>
+        <v>370.6</v>
       </c>
       <c r="F675" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20725,11 +20725,11 @@
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>328.16</v>
+        <v>330.54</v>
       </c>
       <c r="F676" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20771,12 +20771,12 @@
       </c>
       <c r="B678" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C678" s="2" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="D678" s="2" t="inlineStr">
@@ -20785,11 +20785,11 @@
         </is>
       </c>
       <c r="E678" s="3" t="n">
-        <v>309.36</v>
+        <v>314.54</v>
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20801,12 +20801,12 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="D679" s="2" t="inlineStr">
@@ -20815,11 +20815,11 @@
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>305.69</v>
+        <v>309.36</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>287.3</v>
+        <v>295.94</v>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20875,11 +20875,11 @@
         </is>
       </c>
       <c r="E681" s="3" t="n">
-        <v>275.64</v>
+        <v>276.08</v>
       </c>
       <c r="F681" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -20995,11 +20995,11 @@
         </is>
       </c>
       <c r="E685" s="3" t="n">
-        <v>242.65</v>
+        <v>243.08</v>
       </c>
       <c r="F685" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21025,11 +21025,11 @@
         </is>
       </c>
       <c r="E686" s="3" t="n">
-        <v>239.25</v>
+        <v>241.09</v>
       </c>
       <c r="F686" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21071,25 +21071,25 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="D688" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E688" s="3" t="n">
-        <v>223.24</v>
+        <v>227.81</v>
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21101,25 +21101,25 @@
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="D689" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>214.68</v>
+        <v>223.91</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21145,11 +21145,11 @@
         </is>
       </c>
       <c r="E690" s="3" t="n">
-        <v>210.52</v>
+        <v>211.47</v>
       </c>
       <c r="F690" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21175,11 +21175,11 @@
         </is>
       </c>
       <c r="E691" s="3" t="n">
-        <v>208.79</v>
+        <v>209.62</v>
       </c>
       <c r="F691" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21205,11 +21205,11 @@
         </is>
       </c>
       <c r="E692" s="3" t="n">
-        <v>204.43</v>
+        <v>207.01</v>
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21235,11 +21235,11 @@
         </is>
       </c>
       <c r="E693" s="3" t="n">
-        <v>197.22</v>
+        <v>201.27</v>
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21265,11 +21265,11 @@
         </is>
       </c>
       <c r="E694" s="3" t="n">
-        <v>194.42</v>
+        <v>196.99</v>
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>193</v>
+        <v>193.05</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>176.16</v>
+        <v>176.55</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21371,12 +21371,12 @@
       </c>
       <c r="B698" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C698" s="2" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="D698" s="2" t="inlineStr">
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="E698" s="3" t="n">
-        <v>170.8</v>
+        <v>172.83</v>
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21401,12 +21401,12 @@
       </c>
       <c r="B699" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C699" s="2" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="D699" s="2" t="inlineStr">
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>168.72</v>
+        <v>171.82</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21445,11 +21445,11 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>160.14</v>
+        <v>162.2</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21505,11 +21505,11 @@
         </is>
       </c>
       <c r="E702" s="3" t="n">
-        <v>154.57</v>
+        <v>156.84</v>
       </c>
       <c r="F702" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>149.78</v>
+        <v>150</v>
       </c>
       <c r="F703" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21551,12 +21551,12 @@
       </c>
       <c r="B704" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C704" s="2" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="D704" s="2" t="inlineStr">
@@ -21565,11 +21565,11 @@
         </is>
       </c>
       <c r="E704" s="3" t="n">
-        <v>147.37</v>
+        <v>149.69</v>
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21581,12 +21581,12 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="D705" s="2" t="inlineStr">
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>147.2</v>
+        <v>148</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21625,11 +21625,11 @@
         </is>
       </c>
       <c r="E706" s="3" t="n">
-        <v>143.19</v>
+        <v>145.06</v>
       </c>
       <c r="F706" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21685,11 +21685,11 @@
         </is>
       </c>
       <c r="E708" s="3" t="n">
-        <v>134.18</v>
+        <v>134.79</v>
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21715,11 +21715,11 @@
         </is>
       </c>
       <c r="E709" s="3" t="n">
-        <v>132.43</v>
+        <v>133.24</v>
       </c>
       <c r="F709" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21775,11 +21775,11 @@
         </is>
       </c>
       <c r="E711" s="3" t="n">
-        <v>131.75</v>
+        <v>132.07</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21865,11 +21865,11 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>128.42</v>
+        <v>128.76</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>123.45</v>
+        <v>123.59</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>122.51</v>
+        <v>123.28</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22015,11 +22015,11 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>120.85</v>
+        <v>120.96</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22075,11 +22075,11 @@
         </is>
       </c>
       <c r="E721" s="3" t="n">
-        <v>117.79</v>
+        <v>117.93</v>
       </c>
       <c r="F721" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22165,11 +22165,11 @@
         </is>
       </c>
       <c r="E724" s="3" t="n">
-        <v>111.17</v>
+        <v>111.34</v>
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22225,11 +22225,11 @@
         </is>
       </c>
       <c r="E726" s="3" t="n">
-        <v>108.56</v>
+        <v>110.37</v>
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22255,11 +22255,11 @@
         </is>
       </c>
       <c r="E727" s="3" t="n">
-        <v>107.87</v>
+        <v>108.13</v>
       </c>
       <c r="F727" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22285,11 +22285,11 @@
         </is>
       </c>
       <c r="E728" s="3" t="n">
-        <v>106.76</v>
+        <v>107.14</v>
       </c>
       <c r="F728" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22331,12 +22331,12 @@
       </c>
       <c r="B730" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C730" s="2" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="D730" s="2" t="inlineStr">
@@ -22345,11 +22345,11 @@
         </is>
       </c>
       <c r="E730" s="3" t="n">
-        <v>100.93</v>
+        <v>101.58</v>
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22361,12 +22361,12 @@
       </c>
       <c r="B731" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="D731" s="2" t="inlineStr">
@@ -22375,11 +22375,11 @@
         </is>
       </c>
       <c r="E731" s="3" t="n">
-        <v>100.47</v>
+        <v>100.93</v>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22391,12 +22391,12 @@
       </c>
       <c r="B732" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D732" s="2" t="inlineStr">
@@ -22405,11 +22405,11 @@
         </is>
       </c>
       <c r="E732" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>99.92</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22421,12 +22421,12 @@
       </c>
       <c r="B733" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="D733" s="2" t="inlineStr">
@@ -22435,7 +22435,7 @@
         </is>
       </c>
       <c r="E733" s="3" t="n">
-        <v>97.44</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
@@ -22451,12 +22451,12 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
@@ -22465,11 +22465,11 @@
         </is>
       </c>
       <c r="E734" s="3" t="n">
-        <v>97.04000000000001</v>
+        <v>98.37</v>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22481,12 +22481,12 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
@@ -22495,11 +22495,11 @@
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>95.53</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22511,12 +22511,12 @@
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
@@ -22525,11 +22525,11 @@
         </is>
       </c>
       <c r="E736" s="3" t="n">
-        <v>95.36</v>
+        <v>97.44</v>
       </c>
       <c r="F736" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22541,12 +22541,12 @@
       </c>
       <c r="B737" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D737" s="2" t="inlineStr">
@@ -22555,11 +22555,11 @@
         </is>
       </c>
       <c r="E737" s="3" t="n">
-        <v>93.83</v>
+        <v>94.34</v>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22585,11 +22585,11 @@
         </is>
       </c>
       <c r="E738" s="3" t="n">
-        <v>93.79000000000001</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22601,12 +22601,12 @@
       </c>
       <c r="B739" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C739" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D739" s="2" t="inlineStr">
@@ -22615,11 +22615,11 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>92.7</v>
+        <v>93.83</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22631,12 +22631,12 @@
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
@@ -22645,11 +22645,11 @@
         </is>
       </c>
       <c r="E740" s="3" t="n">
-        <v>89.79000000000001</v>
+        <v>92.88</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22661,21 +22661,21 @@
       </c>
       <c r="B741" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="D741" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E741" s="3" t="n">
-        <v>89.48999999999999</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F741" s="2" t="inlineStr">
         <is>
@@ -22691,25 +22691,25 @@
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>88.86</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22721,12 +22721,12 @@
       </c>
       <c r="B743" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C743" s="2" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="D743" s="2" t="inlineStr">
@@ -22735,11 +22735,11 @@
         </is>
       </c>
       <c r="E743" s="3" t="n">
-        <v>87.73</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>87.69</v>
+        <v>87.98</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22781,12 +22781,12 @@
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr">
@@ -22795,7 +22795,7 @@
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>87.73</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
@@ -22811,12 +22811,12 @@
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
@@ -22825,11 +22825,11 @@
         </is>
       </c>
       <c r="E746" s="3" t="n">
-        <v>85.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22841,12 +22841,12 @@
       </c>
       <c r="B747" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C747" s="2" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="D747" s="2" t="inlineStr">
@@ -22855,11 +22855,11 @@
         </is>
       </c>
       <c r="E747" s="3" t="n">
-        <v>85.22</v>
+        <v>86.2</v>
       </c>
       <c r="F747" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22885,11 +22885,11 @@
         </is>
       </c>
       <c r="E748" s="3" t="n">
-        <v>84.86</v>
+        <v>85.77</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22915,11 +22915,11 @@
         </is>
       </c>
       <c r="E749" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="F749" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23005,11 +23005,11 @@
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>81.31999999999999</v>
+        <v>81.33</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23021,12 +23021,12 @@
       </c>
       <c r="B753" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C753" s="2" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="D753" s="2" t="inlineStr">
@@ -23035,11 +23035,11 @@
         </is>
       </c>
       <c r="E753" s="3" t="n">
-        <v>79.44</v>
+        <v>80.5</v>
       </c>
       <c r="F753" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23051,12 +23051,12 @@
       </c>
       <c r="B754" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C754" s="2" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="D754" s="2" t="inlineStr">
@@ -23065,11 +23065,11 @@
         </is>
       </c>
       <c r="E754" s="3" t="n">
-        <v>79.23999999999999</v>
+        <v>79.44</v>
       </c>
       <c r="F754" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>72.97</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23215,11 +23215,11 @@
         </is>
       </c>
       <c r="E759" s="3" t="n">
-        <v>72.83</v>
+        <v>72.88</v>
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23245,11 +23245,11 @@
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>71.54000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23305,11 +23305,11 @@
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>69.48999999999999</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>64.88</v>
+        <v>65.55</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23395,11 +23395,11 @@
         </is>
       </c>
       <c r="E765" s="3" t="n">
-        <v>64.45</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="F765" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23411,12 +23411,12 @@
       </c>
       <c r="B766" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C766" s="2" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="D766" s="2" t="inlineStr">
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>63.66</v>
+        <v>63.96</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23441,12 +23441,12 @@
       </c>
       <c r="B767" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C767" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="D767" s="2" t="inlineStr">
@@ -23455,11 +23455,11 @@
         </is>
       </c>
       <c r="E767" s="3" t="n">
-        <v>63.6</v>
+        <v>63.8</v>
       </c>
       <c r="F767" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23485,11 +23485,11 @@
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>63.45</v>
+        <v>63.69</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23501,12 @@
       </c>
       <c r="B769" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C769" s="2" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="D769" s="2" t="inlineStr">
@@ -23515,11 +23515,11 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>62.83</v>
+        <v>63.6</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23561,12 +23561,12 @@
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
@@ -23575,11 +23575,11 @@
         </is>
       </c>
       <c r="E771" s="3" t="n">
-        <v>61.83</v>
+        <v>62.5</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23591,12 +23591,12 @@
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -23605,11 +23605,11 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>61.83</v>
+        <v>62.28</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23621,12 +23621,12 @@
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="D773" s="2" t="inlineStr">
@@ -23635,11 +23635,11 @@
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>60.88</v>
+        <v>61.86</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23651,12 +23651,12 @@
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr">
@@ -23665,11 +23665,11 @@
         </is>
       </c>
       <c r="E774" s="3" t="n">
-        <v>60.74</v>
+        <v>61.83</v>
       </c>
       <c r="F774" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23681,12 +23681,12 @@
       </c>
       <c r="B775" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C775" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D775" s="2" t="inlineStr">
@@ -23695,11 +23695,11 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>60.46</v>
+        <v>60.9</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23711,12 +23711,12 @@
       </c>
       <c r="B776" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C776" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="D776" s="2" t="inlineStr">
@@ -23725,11 +23725,11 @@
         </is>
       </c>
       <c r="E776" s="3" t="n">
-        <v>58.9</v>
+        <v>59.99</v>
       </c>
       <c r="F776" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23741,12 +23741,12 @@
       </c>
       <c r="B777" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C777" s="2" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="D777" s="2" t="inlineStr">
@@ -23755,11 +23755,11 @@
         </is>
       </c>
       <c r="E777" s="3" t="n">
-        <v>58.76</v>
+        <v>59.02</v>
       </c>
       <c r="F777" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23771,12 +23771,12 @@
       </c>
       <c r="B778" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C778" s="2" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D778" s="2" t="inlineStr">
@@ -23785,11 +23785,11 @@
         </is>
       </c>
       <c r="E778" s="3" t="n">
-        <v>57.86</v>
+        <v>58.66</v>
       </c>
       <c r="F778" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23801,12 +23801,12 @@
       </c>
       <c r="B779" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C779" s="2" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="D779" s="2" t="inlineStr">
@@ -23815,7 +23815,7 @@
         </is>
       </c>
       <c r="E779" s="3" t="n">
-        <v>57.53</v>
+        <v>57.86</v>
       </c>
       <c r="F779" s="2" t="inlineStr">
         <is>
@@ -23831,12 +23831,12 @@
       </c>
       <c r="B780" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C780" s="2" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="D780" s="2" t="inlineStr">
@@ -23845,11 +23845,11 @@
         </is>
       </c>
       <c r="E780" s="3" t="n">
-        <v>57.22</v>
+        <v>57.57</v>
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23861,25 +23861,25 @@
       </c>
       <c r="B781" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C781" s="2" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="D781" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E781" s="3" t="n">
-        <v>57.22</v>
+        <v>57.54</v>
       </c>
       <c r="F781" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23891,12 +23891,12 @@
       </c>
       <c r="B782" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C782" s="2" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="D782" s="2" t="inlineStr">
@@ -23905,11 +23905,11 @@
         </is>
       </c>
       <c r="E782" s="3" t="n">
-        <v>56.85</v>
+        <v>57.39</v>
       </c>
       <c r="F782" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -23921,25 +23921,25 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="D783" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>56.53</v>
+        <v>57.22</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>54.59</v>
+        <v>54.68</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24041,12 +24041,12 @@
       </c>
       <c r="B787" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C787" s="2" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="D787" s="2" t="inlineStr">
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>53.95</v>
+        <v>54.43</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24071,12 +24071,12 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D788" s="2" t="inlineStr">
@@ -24085,11 +24085,11 @@
         </is>
       </c>
       <c r="E788" s="3" t="n">
-        <v>53.91</v>
+        <v>54.03</v>
       </c>
       <c r="F788" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24101,12 +24101,12 @@
       </c>
       <c r="B789" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C789" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="D789" s="2" t="inlineStr">
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>53.53</v>
+        <v>53.95</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24145,11 +24145,11 @@
         </is>
       </c>
       <c r="E790" s="3" t="n">
-        <v>53.24</v>
+        <v>53.25</v>
       </c>
       <c r="F790" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24221,12 +24221,12 @@
       </c>
       <c r="B793" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C793" s="2" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D793" s="2" t="inlineStr">
@@ -24235,11 +24235,11 @@
         </is>
       </c>
       <c r="E793" s="3" t="n">
-        <v>50.51</v>
+        <v>51.82</v>
       </c>
       <c r="F793" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24251,12 +24251,12 @@
       </c>
       <c r="B794" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C794" s="2" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="D794" s="2" t="inlineStr">
@@ -24265,11 +24265,11 @@
         </is>
       </c>
       <c r="E794" s="3" t="n">
-        <v>50.13</v>
+        <v>50.96</v>
       </c>
       <c r="F794" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24281,12 +24281,12 @@
       </c>
       <c r="B795" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C795" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="D795" s="2" t="inlineStr">
@@ -24295,11 +24295,11 @@
         </is>
       </c>
       <c r="E795" s="3" t="n">
-        <v>48.74</v>
+        <v>50.13</v>
       </c>
       <c r="F795" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24311,12 +24311,12 @@
       </c>
       <c r="B796" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C796" s="2" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D796" s="2" t="inlineStr">
@@ -24325,11 +24325,11 @@
         </is>
       </c>
       <c r="E796" s="3" t="n">
-        <v>48.04</v>
+        <v>49.88</v>
       </c>
       <c r="F796" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24341,12 +24341,12 @@
       </c>
       <c r="B797" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C797" s="2" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="D797" s="2" t="inlineStr">
@@ -24355,11 +24355,11 @@
         </is>
       </c>
       <c r="E797" s="3" t="n">
-        <v>47.99</v>
+        <v>48.04</v>
       </c>
       <c r="F797" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24371,12 +24371,12 @@
       </c>
       <c r="B798" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C798" s="2" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="D798" s="2" t="inlineStr">
@@ -24385,11 +24385,11 @@
         </is>
       </c>
       <c r="E798" s="3" t="n">
-        <v>47.23</v>
+        <v>47.99</v>
       </c>
       <c r="F798" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="B799" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C799" s="2" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="D799" s="2" t="inlineStr">
@@ -24415,11 +24415,11 @@
         </is>
       </c>
       <c r="E799" s="3" t="n">
-        <v>46.65</v>
+        <v>47.23</v>
       </c>
       <c r="F799" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24431,12 +24431,12 @@
       </c>
       <c r="B800" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C800" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="D800" s="2" t="inlineStr">
@@ -24445,11 +24445,11 @@
         </is>
       </c>
       <c r="E800" s="3" t="n">
-        <v>46.46</v>
+        <v>46.67</v>
       </c>
       <c r="F800" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24461,12 +24461,12 @@
       </c>
       <c r="B801" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C801" s="2" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="D801" s="2" t="inlineStr">
@@ -24475,11 +24475,11 @@
         </is>
       </c>
       <c r="E801" s="3" t="n">
-        <v>46.1</v>
+        <v>46.17</v>
       </c>
       <c r="F801" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24491,12 +24491,12 @@
       </c>
       <c r="B802" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C802" s="2" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="D802" s="2" t="inlineStr">
@@ -24505,11 +24505,11 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>45.88</v>
+        <v>46.1</v>
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24535,11 +24535,11 @@
         </is>
       </c>
       <c r="E803" s="3" t="n">
-        <v>44.94</v>
+        <v>45.43</v>
       </c>
       <c r="F803" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24595,11 +24595,11 @@
         </is>
       </c>
       <c r="E805" s="3" t="n">
-        <v>44.71</v>
+        <v>44.8</v>
       </c>
       <c r="F805" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24655,11 +24655,11 @@
         </is>
       </c>
       <c r="E807" s="3" t="n">
-        <v>40.51</v>
+        <v>40.98</v>
       </c>
       <c r="F807" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24671,12 +24671,12 @@
       </c>
       <c r="B808" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C808" s="2" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="D808" s="2" t="inlineStr">
@@ -24685,11 +24685,11 @@
         </is>
       </c>
       <c r="E808" s="3" t="n">
-        <v>39.2</v>
+        <v>40.09</v>
       </c>
       <c r="F808" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24701,12 +24701,12 @@
       </c>
       <c r="B809" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C809" s="2" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="D809" s="2" t="inlineStr">
@@ -24715,11 +24715,11 @@
         </is>
       </c>
       <c r="E809" s="3" t="n">
-        <v>38.88</v>
+        <v>39.2</v>
       </c>
       <c r="F809" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24865,11 +24865,11 @@
         </is>
       </c>
       <c r="E814" s="3" t="n">
-        <v>36.37</v>
+        <v>36.39</v>
       </c>
       <c r="F814" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24925,11 +24925,11 @@
         </is>
       </c>
       <c r="E816" s="3" t="n">
-        <v>34.13</v>
+        <v>35.72</v>
       </c>
       <c r="F816" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -25015,11 +25015,11 @@
         </is>
       </c>
       <c r="E819" s="3" t="n">
-        <v>33.09</v>
+        <v>33.35</v>
       </c>
       <c r="F819" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -25031,12 +25031,12 @@
       </c>
       <c r="B820" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C820" s="2" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D820" s="2" t="inlineStr">
@@ -25045,11 +25045,11 @@
         </is>
       </c>
       <c r="E820" s="3" t="n">
-        <v>31.24</v>
+        <v>31.53</v>
       </c>
       <c r="F820" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -25061,12 +25061,12 @@
       </c>
       <c r="B821" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="C821" s="2" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="D821" s="2" t="inlineStr">
@@ -25075,11 +25075,11 @@
         </is>
       </c>
       <c r="E821" s="3" t="n">
-        <v>30.66</v>
+        <v>31.24</v>
       </c>
       <c r="F821" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25091,12 +25091,12 @@
       </c>
       <c r="B822" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C822" s="2" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="D822" s="2" t="inlineStr">
@@ -25105,11 +25105,11 @@
         </is>
       </c>
       <c r="E822" s="3" t="n">
-        <v>29.63</v>
+        <v>30.72</v>
       </c>
       <c r="F822" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -25121,12 +25121,12 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="D823" s="2" t="inlineStr">
@@ -25135,11 +25135,11 @@
         </is>
       </c>
       <c r="E823" s="3" t="n">
-        <v>29.27</v>
+        <v>29.67</v>
       </c>
       <c r="F823" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -25151,12 +25151,12 @@
       </c>
       <c r="B824" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C824" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="D824" s="2" t="inlineStr">
@@ -25165,11 +25165,11 @@
         </is>
       </c>
       <c r="E824" s="3" t="n">
-        <v>28.88</v>
+        <v>29.27</v>
       </c>
       <c r="F824" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25225,11 +25225,11 @@
         </is>
       </c>
       <c r="E826" s="3" t="n">
-        <v>27.22</v>
+        <v>27.26</v>
       </c>
       <c r="F826" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -25255,11 +25255,11 @@
         </is>
       </c>
       <c r="E827" s="3" t="n">
-        <v>26.7</v>
+        <v>26.77</v>
       </c>
       <c r="F827" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -25361,25 +25361,25 @@
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C831" s="2" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="D831" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E831" s="3" t="n">
-        <v>22.39</v>
+        <v>22.83</v>
       </c>
       <c r="F831" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -25391,12 +25391,12 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="D832" s="2" t="inlineStr">
@@ -25405,11 +25405,11 @@
         </is>
       </c>
       <c r="E832" s="3" t="n">
-        <v>21.89</v>
+        <v>22.39</v>
       </c>
       <c r="F832" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25421,12 +25421,12 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="D833" s="2" t="inlineStr">
@@ -25435,11 +25435,11 @@
         </is>
       </c>
       <c r="E833" s="3" t="n">
-        <v>21.7</v>
+        <v>22.35</v>
       </c>
       <c r="F833" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -25451,25 +25451,25 @@
       </c>
       <c r="B834" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C834" s="2" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="D834" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E834" s="3" t="n">
-        <v>21.35</v>
+        <v>21.7</v>
       </c>
       <c r="F834" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25511,12 +25511,12 @@
       </c>
       <c r="B836" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C836" s="2" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="D836" s="2" t="inlineStr">
@@ -25525,11 +25525,11 @@
         </is>
       </c>
       <c r="E836" s="3" t="n">
-        <v>21.17</v>
+        <v>21.2</v>
       </c>
       <c r="F836" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -25541,12 +25541,12 @@
       </c>
       <c r="B837" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C837" s="2" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="D837" s="2" t="inlineStr">
@@ -25555,7 +25555,7 @@
         </is>
       </c>
       <c r="E837" s="3" t="n">
-        <v>20.98</v>
+        <v>21.17</v>
       </c>
       <c r="F837" s="2" t="inlineStr">
         <is>
@@ -25571,12 +25571,12 @@
       </c>
       <c r="B838" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C838" s="2" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="D838" s="2" t="inlineStr">
@@ -25585,7 +25585,7 @@
         </is>
       </c>
       <c r="E838" s="3" t="n">
-        <v>20.61</v>
+        <v>20.98</v>
       </c>
       <c r="F838" s="2" t="inlineStr">
         <is>
@@ -25601,12 +25601,12 @@
       </c>
       <c r="B839" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C839" s="2" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="D839" s="2" t="inlineStr">
@@ -25615,11 +25615,11 @@
         </is>
       </c>
       <c r="E839" s="3" t="n">
-        <v>20.36</v>
+        <v>20.61</v>
       </c>
       <c r="F839" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25721,12 +25721,12 @@
       </c>
       <c r="B843" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C843" s="2" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="D843" s="2" t="inlineStr">
@@ -25735,11 +25735,11 @@
         </is>
       </c>
       <c r="E843" s="3" t="n">
-        <v>17.76</v>
+        <v>18.81</v>
       </c>
       <c r="F843" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -25751,12 +25751,12 @@
       </c>
       <c r="B844" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C844" s="2" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="D844" s="2" t="inlineStr">
@@ -25765,11 +25765,11 @@
         </is>
       </c>
       <c r="E844" s="3" t="n">
-        <v>17.63</v>
+        <v>17.76</v>
       </c>
       <c r="F844" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25781,12 +25781,12 @@
       </c>
       <c r="B845" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C845" s="2" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D845" s="2" t="inlineStr">
@@ -25795,11 +25795,11 @@
         </is>
       </c>
       <c r="E845" s="3" t="n">
-        <v>17.57</v>
+        <v>17.68</v>
       </c>
       <c r="F845" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -25811,12 +25811,12 @@
       </c>
       <c r="B846" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C846" s="2" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="D846" s="2" t="inlineStr">
@@ -25825,7 +25825,7 @@
         </is>
       </c>
       <c r="E846" s="3" t="n">
-        <v>17.49</v>
+        <v>17.57</v>
       </c>
       <c r="F846" s="2" t="inlineStr">
         <is>
@@ -25841,12 +25841,12 @@
       </c>
       <c r="B847" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C847" s="2" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="D847" s="2" t="inlineStr">
@@ -25855,7 +25855,7 @@
         </is>
       </c>
       <c r="E847" s="3" t="n">
-        <v>17.45</v>
+        <v>17.49</v>
       </c>
       <c r="F847" s="2" t="inlineStr">
         <is>
@@ -25871,12 +25871,12 @@
       </c>
       <c r="B848" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C848" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="D848" s="2" t="inlineStr">
@@ -25885,11 +25885,11 @@
         </is>
       </c>
       <c r="E848" s="3" t="n">
-        <v>17.4</v>
+        <v>17.45</v>
       </c>
       <c r="F848" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26305,11 +26305,11 @@
         </is>
       </c>
       <c r="E862" s="3" t="n">
-        <v>6.21</v>
+        <v>6.32</v>
       </c>
       <c r="F862" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -26395,11 +26395,11 @@
         </is>
       </c>
       <c r="E865" s="3" t="n">
-        <v>4.15</v>
+        <v>4.48</v>
       </c>
       <c r="F865" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2286.25</v>
+        <v>2302.06</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -19795,11 +19795,11 @@
         </is>
       </c>
       <c r="E645" s="3" t="n">
-        <v>1869.69</v>
+        <v>1927.82</v>
       </c>
       <c r="F645" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -19885,11 +19885,11 @@
         </is>
       </c>
       <c r="E648" s="3" t="n">
-        <v>1013.81</v>
+        <v>1033.73</v>
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>1000.21</v>
+        <v>1030.84</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -19961,12 +19961,12 @@
       </c>
       <c r="B651" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084602TKW</t>
+          <t>KIT4P000739257CR</t>
         </is>
       </c>
       <c r="C651" s="2" t="inlineStr">
         <is>
-          <t>816225</t>
+          <t>814609</t>
         </is>
       </c>
       <c r="D651" s="2" t="inlineStr">
@@ -19975,11 +19975,11 @@
         </is>
       </c>
       <c r="E651" s="3" t="n">
-        <v>771.66</v>
+        <v>771.6900000000001</v>
       </c>
       <c r="F651" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -19991,12 +19991,12 @@
       </c>
       <c r="B652" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739257CR</t>
+          <t>KIT4P00084602TKW</t>
         </is>
       </c>
       <c r="C652" s="2" t="inlineStr">
         <is>
-          <t>814609</t>
+          <t>816225</t>
         </is>
       </c>
       <c r="D652" s="2" t="inlineStr">
@@ -20005,11 +20005,11 @@
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>719.61</v>
+        <v>771.66</v>
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20035,11 +20035,11 @@
         </is>
       </c>
       <c r="E653" s="3" t="n">
-        <v>707.25</v>
+        <v>713.34</v>
       </c>
       <c r="F653" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20081,25 +20081,25 @@
       </c>
       <c r="B655" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4P000739124KF</t>
         </is>
       </c>
       <c r="C655" s="2" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>814640</t>
         </is>
       </c>
       <c r="D655" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E655" s="3" t="n">
-        <v>606.37</v>
+        <v>611.98</v>
       </c>
       <c r="F655" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20111,25 +20111,25 @@
       </c>
       <c r="B656" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739124KF</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C656" s="2" t="inlineStr">
         <is>
-          <t>814640</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="D656" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E656" s="3" t="n">
-        <v>598.02</v>
+        <v>610.63</v>
       </c>
       <c r="F656" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20141,25 +20141,25 @@
       </c>
       <c r="B657" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C657" s="2" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="D657" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>596.73</v>
+        <v>608.17</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20171,25 +20171,25 @@
       </c>
       <c r="B658" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C658" s="2" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="D658" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>596.3200000000001</v>
+        <v>598.3099999999999</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20215,11 +20215,11 @@
         </is>
       </c>
       <c r="E659" s="3" t="n">
-        <v>557.42</v>
+        <v>569.0700000000001</v>
       </c>
       <c r="F659" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20245,11 +20245,11 @@
         </is>
       </c>
       <c r="E660" s="3" t="n">
-        <v>549.29</v>
+        <v>556.66</v>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20275,11 +20275,11 @@
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>525.55</v>
+        <v>529.1900000000001</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20365,11 +20365,11 @@
         </is>
       </c>
       <c r="E664" s="3" t="n">
-        <v>488.57</v>
+        <v>495.62</v>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20381,12 +20381,12 @@
       </c>
       <c r="B665" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
@@ -20395,11 +20395,11 @@
         </is>
       </c>
       <c r="E665" s="3" t="n">
-        <v>480.85</v>
+        <v>481.34</v>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20411,12 +20411,12 @@
       </c>
       <c r="B666" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
@@ -20425,11 +20425,11 @@
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>478.46</v>
+        <v>480.85</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20455,11 +20455,11 @@
         </is>
       </c>
       <c r="E667" s="3" t="n">
-        <v>474.04</v>
+        <v>475.95</v>
       </c>
       <c r="F667" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20515,11 +20515,11 @@
         </is>
       </c>
       <c r="E669" s="3" t="n">
-        <v>451.12</v>
+        <v>453.41</v>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20531,12 +20531,12 @@
       </c>
       <c r="B670" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065631CPZ</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C670" s="2" t="inlineStr">
         <is>
-          <t>812930</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="D670" s="2" t="inlineStr">
@@ -20545,11 +20545,11 @@
         </is>
       </c>
       <c r="E670" s="3" t="n">
-        <v>415.73</v>
+        <v>422.94</v>
       </c>
       <c r="F670" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20561,25 +20561,25 @@
       </c>
       <c r="B671" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="C671" s="2" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>812930</t>
         </is>
       </c>
       <c r="D671" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E671" s="3" t="n">
-        <v>409.33</v>
+        <v>415.73</v>
       </c>
       <c r="F671" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20591,25 +20591,25 @@
       </c>
       <c r="B672" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084601T5F</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C672" s="2" t="inlineStr">
         <is>
-          <t>816335</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="D672" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E672" s="3" t="n">
-        <v>401.51</v>
+        <v>410.16</v>
       </c>
       <c r="F672" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20621,12 +20621,12 @@
       </c>
       <c r="B673" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="C673" s="2" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>816335</t>
         </is>
       </c>
       <c r="D673" s="2" t="inlineStr">
@@ -20635,11 +20635,11 @@
         </is>
       </c>
       <c r="E673" s="3" t="n">
-        <v>381.85</v>
+        <v>401.51</v>
       </c>
       <c r="F673" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20651,12 +20651,12 @@
       </c>
       <c r="B674" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C674" s="2" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="D674" s="2" t="inlineStr">
@@ -20665,11 +20665,11 @@
         </is>
       </c>
       <c r="E674" s="3" t="n">
-        <v>381.7</v>
+        <v>391.32</v>
       </c>
       <c r="F674" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20695,11 +20695,11 @@
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>370.6</v>
+        <v>374.6</v>
       </c>
       <c r="F675" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20741,12 +20741,12 @@
       </c>
       <c r="B677" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C677" s="2" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="D677" s="2" t="inlineStr">
@@ -20755,11 +20755,11 @@
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>318.87</v>
+        <v>323.63</v>
       </c>
       <c r="F677" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20771,12 +20771,12 @@
       </c>
       <c r="B678" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C678" s="2" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="D678" s="2" t="inlineStr">
@@ -20785,11 +20785,11 @@
         </is>
       </c>
       <c r="E678" s="3" t="n">
-        <v>314.54</v>
+        <v>318.87</v>
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20801,12 +20801,12 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="D679" s="2" t="inlineStr">
@@ -20815,11 +20815,11 @@
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>309.36</v>
+        <v>317.28</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>295.94</v>
+        <v>308.25</v>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20875,11 +20875,11 @@
         </is>
       </c>
       <c r="E681" s="3" t="n">
-        <v>276.08</v>
+        <v>276.09</v>
       </c>
       <c r="F681" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20935,11 +20935,11 @@
         </is>
       </c>
       <c r="E683" s="3" t="n">
-        <v>264</v>
+        <v>265.66</v>
       </c>
       <c r="F683" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20951,12 +20951,12 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="D684" s="2" t="inlineStr">
@@ -20965,11 +20965,11 @@
         </is>
       </c>
       <c r="E684" s="3" t="n">
-        <v>246.96</v>
+        <v>255.03</v>
       </c>
       <c r="F684" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20981,12 +20981,12 @@
       </c>
       <c r="B685" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C685" s="2" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="D685" s="2" t="inlineStr">
@@ -20995,11 +20995,11 @@
         </is>
       </c>
       <c r="E685" s="3" t="n">
-        <v>243.08</v>
+        <v>246.96</v>
       </c>
       <c r="F685" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21011,25 +21011,25 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="D686" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E686" s="3" t="n">
-        <v>241.09</v>
+        <v>244.01</v>
       </c>
       <c r="F686" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21041,12 +21041,12 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="D687" s="2" t="inlineStr">
@@ -21055,11 +21055,11 @@
         </is>
       </c>
       <c r="E687" s="3" t="n">
-        <v>237.44</v>
+        <v>243.37</v>
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21071,25 +21071,25 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="D688" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E688" s="3" t="n">
-        <v>227.81</v>
+        <v>237.44</v>
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21115,11 +21115,11 @@
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>223.91</v>
+        <v>226.35</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21131,12 +21131,12 @@
       </c>
       <c r="B690" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="C690" s="2" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="D690" s="2" t="inlineStr">
@@ -21145,11 +21145,11 @@
         </is>
       </c>
       <c r="E690" s="3" t="n">
-        <v>211.47</v>
+        <v>214.79</v>
       </c>
       <c r="F690" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21161,12 +21161,12 @@
       </c>
       <c r="B691" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C691" s="2" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="D691" s="2" t="inlineStr">
@@ -21175,11 +21175,11 @@
         </is>
       </c>
       <c r="E691" s="3" t="n">
-        <v>209.62</v>
+        <v>214.33</v>
       </c>
       <c r="F691" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21191,12 +21191,12 @@
       </c>
       <c r="B692" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C692" s="2" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="D692" s="2" t="inlineStr">
@@ -21205,11 +21205,11 @@
         </is>
       </c>
       <c r="E692" s="3" t="n">
-        <v>207.01</v>
+        <v>210.07</v>
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21235,11 +21235,11 @@
         </is>
       </c>
       <c r="E693" s="3" t="n">
-        <v>201.27</v>
+        <v>203.78</v>
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21265,11 +21265,11 @@
         </is>
       </c>
       <c r="E694" s="3" t="n">
-        <v>196.99</v>
+        <v>201.27</v>
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>193.05</v>
+        <v>193.81</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21311,12 +21311,12 @@
       </c>
       <c r="B696" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C696" s="2" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="D696" s="2" t="inlineStr">
@@ -21325,11 +21325,11 @@
         </is>
       </c>
       <c r="E696" s="3" t="n">
-        <v>180.28</v>
+        <v>189.49</v>
       </c>
       <c r="F696" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21341,12 +21341,12 @@
       </c>
       <c r="B697" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C697" s="2" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="D697" s="2" t="inlineStr">
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>176.55</v>
+        <v>180.59</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21371,12 +21371,12 @@
       </c>
       <c r="B698" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C698" s="2" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="D698" s="2" t="inlineStr">
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="E698" s="3" t="n">
-        <v>172.83</v>
+        <v>177.81</v>
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>171.82</v>
+        <v>175.92</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21445,11 +21445,11 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>162.2</v>
+        <v>166.02</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21461,12 +21461,12 @@
       </c>
       <c r="B701" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C701" s="2" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="D701" s="2" t="inlineStr">
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>158.82</v>
+        <v>159.16</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21491,12 +21491,12 @@
       </c>
       <c r="B702" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C702" s="2" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="D702" s="2" t="inlineStr">
@@ -21505,11 +21505,11 @@
         </is>
       </c>
       <c r="E702" s="3" t="n">
-        <v>156.84</v>
+        <v>158.82</v>
       </c>
       <c r="F702" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21521,12 +21521,12 @@
       </c>
       <c r="B703" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C703" s="2" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="D703" s="2" t="inlineStr">
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>150</v>
+        <v>154.5</v>
       </c>
       <c r="F703" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21551,12 +21551,12 @@
       </c>
       <c r="B704" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C704" s="2" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="D704" s="2" t="inlineStr">
@@ -21565,11 +21565,11 @@
         </is>
       </c>
       <c r="E704" s="3" t="n">
-        <v>149.69</v>
+        <v>154.15</v>
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21581,12 +21581,12 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="D705" s="2" t="inlineStr">
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>148</v>
+        <v>150.01</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21625,11 +21625,11 @@
         </is>
       </c>
       <c r="E706" s="3" t="n">
-        <v>145.06</v>
+        <v>147.64</v>
       </c>
       <c r="F706" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21655,11 +21655,11 @@
         </is>
       </c>
       <c r="E707" s="3" t="n">
-        <v>138.36</v>
+        <v>143.24</v>
       </c>
       <c r="F707" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21685,11 +21685,11 @@
         </is>
       </c>
       <c r="E708" s="3" t="n">
-        <v>134.79</v>
+        <v>137.79</v>
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21715,11 +21715,11 @@
         </is>
       </c>
       <c r="E709" s="3" t="n">
-        <v>133.24</v>
+        <v>134.39</v>
       </c>
       <c r="F709" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21731,12 +21731,12 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="D710" s="2" t="inlineStr">
@@ -21745,11 +21745,11 @@
         </is>
       </c>
       <c r="E710" s="3" t="n">
-        <v>132.39</v>
+        <v>133.73</v>
       </c>
       <c r="F710" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21761,12 +21761,12 @@
       </c>
       <c r="B711" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C711" s="2" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="D711" s="2" t="inlineStr">
@@ -21775,11 +21775,11 @@
         </is>
       </c>
       <c r="E711" s="3" t="n">
-        <v>132.07</v>
+        <v>132.39</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21851,12 +21851,12 @@
       </c>
       <c r="B714" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C714" s="2" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="D714" s="2" t="inlineStr">
@@ -21865,11 +21865,11 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>128.76</v>
+        <v>130.85</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21881,12 +21881,12 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="D715" s="2" t="inlineStr">
@@ -21895,11 +21895,11 @@
         </is>
       </c>
       <c r="E715" s="3" t="n">
-        <v>126.03</v>
+        <v>129.39</v>
       </c>
       <c r="F715" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21911,12 +21911,12 @@
       </c>
       <c r="B716" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C716" s="2" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="D716" s="2" t="inlineStr">
@@ -21925,11 +21925,11 @@
         </is>
       </c>
       <c r="E716" s="3" t="n">
-        <v>125.25</v>
+        <v>126.21</v>
       </c>
       <c r="F716" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B717" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C717" s="2" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="D717" s="2" t="inlineStr">
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>123.59</v>
+        <v>126.03</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21971,12 +21971,12 @@
       </c>
       <c r="B718" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr">
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>123.28</v>
+        <v>125.51</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22015,11 +22015,11 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>120.96</v>
+        <v>124.47</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22091,12 +22091,12 @@
       </c>
       <c r="B722" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C722" s="2" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="D722" s="2" t="inlineStr">
@@ -22105,11 +22105,11 @@
         </is>
       </c>
       <c r="E722" s="3" t="n">
-        <v>114.07</v>
+        <v>116.01</v>
       </c>
       <c r="F722" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22121,12 +22121,12 @@
       </c>
       <c r="B723" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C723" s="2" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="D723" s="2" t="inlineStr">
@@ -22135,11 +22135,11 @@
         </is>
       </c>
       <c r="E723" s="3" t="n">
-        <v>113.25</v>
+        <v>114.07</v>
       </c>
       <c r="F723" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22165,11 +22165,11 @@
         </is>
       </c>
       <c r="E724" s="3" t="n">
-        <v>111.34</v>
+        <v>113.82</v>
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22181,12 +22181,12 @@
       </c>
       <c r="B725" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C725" s="2" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="D725" s="2" t="inlineStr">
@@ -22195,11 +22195,11 @@
         </is>
       </c>
       <c r="E725" s="3" t="n">
-        <v>110.73</v>
+        <v>113.25</v>
       </c>
       <c r="F725" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22211,12 +22211,12 @@
       </c>
       <c r="B726" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C726" s="2" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="D726" s="2" t="inlineStr">
@@ -22225,11 +22225,11 @@
         </is>
       </c>
       <c r="E726" s="3" t="n">
-        <v>110.37</v>
+        <v>110.73</v>
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22255,11 +22255,11 @@
         </is>
       </c>
       <c r="E727" s="3" t="n">
-        <v>108.13</v>
+        <v>108.51</v>
       </c>
       <c r="F727" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22285,11 +22285,11 @@
         </is>
       </c>
       <c r="E728" s="3" t="n">
-        <v>107.14</v>
+        <v>108.21</v>
       </c>
       <c r="F728" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22345,11 +22345,11 @@
         </is>
       </c>
       <c r="E730" s="3" t="n">
-        <v>101.58</v>
+        <v>103.28</v>
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22361,12 +22361,12 @@
       </c>
       <c r="B731" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D731" s="2" t="inlineStr">
@@ -22375,11 +22375,11 @@
         </is>
       </c>
       <c r="E731" s="3" t="n">
-        <v>100.93</v>
+        <v>103.07</v>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22391,12 +22391,12 @@
       </c>
       <c r="B732" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D732" s="2" t="inlineStr">
@@ -22405,11 +22405,11 @@
         </is>
       </c>
       <c r="E732" s="3" t="n">
-        <v>99.92</v>
+        <v>101.51</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22421,12 +22421,12 @@
       </c>
       <c r="B733" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="D733" s="2" t="inlineStr">
@@ -22435,7 +22435,7 @@
         </is>
       </c>
       <c r="E733" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>100.93</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
@@ -22451,12 +22451,12 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
@@ -22465,11 +22465,11 @@
         </is>
       </c>
       <c r="E734" s="3" t="n">
-        <v>98.37</v>
+        <v>100.53</v>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22481,12 +22481,12 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
@@ -22495,11 +22495,11 @@
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22511,12 +22511,12 @@
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
@@ -22525,11 +22525,11 @@
         </is>
       </c>
       <c r="E736" s="3" t="n">
-        <v>97.44</v>
+        <v>98.64</v>
       </c>
       <c r="F736" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22555,11 +22555,11 @@
         </is>
       </c>
       <c r="E737" s="3" t="n">
-        <v>94.34</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22571,12 +22571,12 @@
       </c>
       <c r="B738" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="D738" s="2" t="inlineStr">
@@ -22585,11 +22585,11 @@
         </is>
       </c>
       <c r="E738" s="3" t="n">
-        <v>94.06999999999999</v>
+        <v>97.44</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22601,12 +22601,12 @@
       </c>
       <c r="B739" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C739" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="D739" s="2" t="inlineStr">
@@ -22615,11 +22615,11 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>93.83</v>
+        <v>95.89</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22631,12 +22631,12 @@
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
@@ -22645,11 +22645,11 @@
         </is>
       </c>
       <c r="E740" s="3" t="n">
-        <v>92.88</v>
+        <v>95.06</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22661,12 +22661,12 @@
       </c>
       <c r="B741" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D741" s="2" t="inlineStr">
@@ -22675,11 +22675,11 @@
         </is>
       </c>
       <c r="E741" s="3" t="n">
-        <v>89.79000000000001</v>
+        <v>93.83</v>
       </c>
       <c r="F741" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22691,25 +22691,25 @@
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>89.48999999999999</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22721,12 +22721,12 @@
       </c>
       <c r="B743" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C743" s="2" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="D743" s="2" t="inlineStr">
@@ -22735,11 +22735,11 @@
         </is>
       </c>
       <c r="E743" s="3" t="n">
-        <v>87.98999999999999</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22751,12 +22751,12 @@
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="D744" s="2" t="inlineStr">
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>87.98</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22781,21 +22781,21 @@
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>87.73</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
@@ -22811,12 +22811,12 @@
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
@@ -22825,11 +22825,11 @@
         </is>
       </c>
       <c r="E746" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22841,12 +22841,12 @@
       </c>
       <c r="B747" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C747" s="2" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="D747" s="2" t="inlineStr">
@@ -22855,11 +22855,11 @@
         </is>
       </c>
       <c r="E747" s="3" t="n">
-        <v>86.2</v>
+        <v>87.73</v>
       </c>
       <c r="F747" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22885,11 +22885,11 @@
         </is>
       </c>
       <c r="E748" s="3" t="n">
-        <v>85.77</v>
+        <v>87.69</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22901,12 +22901,12 @@
       </c>
       <c r="B749" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C749" s="2" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="D749" s="2" t="inlineStr">
@@ -22915,11 +22915,11 @@
         </is>
       </c>
       <c r="E749" s="3" t="n">
-        <v>85.34999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F749" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22931,12 +22931,12 @@
       </c>
       <c r="B750" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C750" s="2" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="D750" s="2" t="inlineStr">
@@ -22945,11 +22945,11 @@
         </is>
       </c>
       <c r="E750" s="3" t="n">
-        <v>82.18000000000001</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="F750" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22961,12 +22961,12 @@
       </c>
       <c r="B751" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C751" s="2" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="D751" s="2" t="inlineStr">
@@ -22975,11 +22975,11 @@
         </is>
       </c>
       <c r="E751" s="3" t="n">
-        <v>81.73</v>
+        <v>82.36</v>
       </c>
       <c r="F751" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22991,12 +22991,12 @@
       </c>
       <c r="B752" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C752" s="2" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="D752" s="2" t="inlineStr">
@@ -23005,11 +23005,11 @@
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>81.33</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23021,12 +23021,12 @@
       </c>
       <c r="B753" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C753" s="2" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="D753" s="2" t="inlineStr">
@@ -23035,11 +23035,11 @@
         </is>
       </c>
       <c r="E753" s="3" t="n">
-        <v>80.5</v>
+        <v>81.73</v>
       </c>
       <c r="F753" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23051,12 +23051,12 @@
       </c>
       <c r="B754" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C754" s="2" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="D754" s="2" t="inlineStr">
@@ -23065,11 +23065,11 @@
         </is>
       </c>
       <c r="E754" s="3" t="n">
-        <v>79.44</v>
+        <v>81.61</v>
       </c>
       <c r="F754" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23081,12 +23081,12 @@
       </c>
       <c r="B755" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C755" s="2" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="D755" s="2" t="inlineStr">
@@ -23095,11 +23095,11 @@
         </is>
       </c>
       <c r="E755" s="3" t="n">
-        <v>76.93000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="F755" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23111,12 +23111,12 @@
       </c>
       <c r="B756" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C756" s="2" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="D756" s="2" t="inlineStr">
@@ -23125,11 +23125,11 @@
         </is>
       </c>
       <c r="E756" s="3" t="n">
-        <v>74.76000000000001</v>
+        <v>77.37</v>
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23141,25 +23141,25 @@
       </c>
       <c r="B757" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="C757" s="2" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="D757" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E757" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="F757" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23171,12 +23171,12 @@
       </c>
       <c r="B758" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C758" s="2" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="D758" s="2" t="inlineStr">
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>74.01000000000001</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23201,25 +23201,25 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="D759" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E759" s="3" t="n">
-        <v>72.88</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23245,11 +23245,11 @@
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23305,11 +23305,11 @@
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>70.01000000000001</v>
+        <v>70.48</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23351,12 +23351,12 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="D764" s="2" t="inlineStr">
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>65.55</v>
+        <v>67.63</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23381,12 +23381,12 @@
       </c>
       <c r="B765" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C765" s="2" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="D765" s="2" t="inlineStr">
@@ -23395,11 +23395,11 @@
         </is>
       </c>
       <c r="E765" s="3" t="n">
-        <v>64.70999999999999</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="F765" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23411,12 +23411,12 @@
       </c>
       <c r="B766" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C766" s="2" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="D766" s="2" t="inlineStr">
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>63.96</v>
+        <v>66.38</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23441,12 +23441,12 @@
       </c>
       <c r="B767" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C767" s="2" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D767" s="2" t="inlineStr">
@@ -23455,11 +23455,11 @@
         </is>
       </c>
       <c r="E767" s="3" t="n">
-        <v>63.8</v>
+        <v>66.2</v>
       </c>
       <c r="F767" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23471,12 +23471,12 @@
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="D768" s="2" t="inlineStr">
@@ -23485,11 +23485,11 @@
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>63.69</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23501,12 @@
       </c>
       <c r="B769" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C769" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="D769" s="2" t="inlineStr">
@@ -23515,11 +23515,11 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>63.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23531,12 +23531,12 @@
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
@@ -23545,11 +23545,11 @@
         </is>
       </c>
       <c r="E770" s="3" t="n">
-        <v>62.58</v>
+        <v>64.95</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23561,12 +23561,12 @@
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
@@ -23575,11 +23575,11 @@
         </is>
       </c>
       <c r="E771" s="3" t="n">
-        <v>62.5</v>
+        <v>64.47</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23591,12 +23591,12 @@
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -23605,11 +23605,11 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>62.28</v>
+        <v>63.6</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23635,11 +23635,11 @@
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>61.86</v>
+        <v>63.33</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23651,12 +23651,12 @@
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr">
@@ -23665,11 +23665,11 @@
         </is>
       </c>
       <c r="E774" s="3" t="n">
-        <v>61.83</v>
+        <v>63.03</v>
       </c>
       <c r="F774" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23681,12 +23681,12 @@
       </c>
       <c r="B775" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C775" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D775" s="2" t="inlineStr">
@@ -23695,11 +23695,11 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>60.9</v>
+        <v>62.84</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23711,12 +23711,12 @@
       </c>
       <c r="B776" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C776" s="2" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="D776" s="2" t="inlineStr">
@@ -23725,11 +23725,11 @@
         </is>
       </c>
       <c r="E776" s="3" t="n">
-        <v>59.99</v>
+        <v>61.85</v>
       </c>
       <c r="F776" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23741,12 +23741,12 @@
       </c>
       <c r="B777" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C777" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D777" s="2" t="inlineStr">
@@ -23755,11 +23755,11 @@
         </is>
       </c>
       <c r="E777" s="3" t="n">
-        <v>59.02</v>
+        <v>61.83</v>
       </c>
       <c r="F777" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23771,12 +23771,12 @@
       </c>
       <c r="B778" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C778" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D778" s="2" t="inlineStr">
@@ -23785,11 +23785,11 @@
         </is>
       </c>
       <c r="E778" s="3" t="n">
-        <v>58.66</v>
+        <v>61.5</v>
       </c>
       <c r="F778" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23801,12 +23801,12 @@
       </c>
       <c r="B779" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C779" s="2" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D779" s="2" t="inlineStr">
@@ -23815,11 +23815,11 @@
         </is>
       </c>
       <c r="E779" s="3" t="n">
-        <v>57.86</v>
+        <v>61.47</v>
       </c>
       <c r="F779" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23831,12 +23831,12 @@
       </c>
       <c r="B780" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C780" s="2" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="D780" s="2" t="inlineStr">
@@ -23845,11 +23845,11 @@
         </is>
       </c>
       <c r="E780" s="3" t="n">
-        <v>57.57</v>
+        <v>60.59</v>
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23861,12 +23861,12 @@
       </c>
       <c r="B781" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C781" s="2" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="D781" s="2" t="inlineStr">
@@ -23875,11 +23875,11 @@
         </is>
       </c>
       <c r="E781" s="3" t="n">
-        <v>57.54</v>
+        <v>60.28</v>
       </c>
       <c r="F781" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23891,12 +23891,12 @@
       </c>
       <c r="B782" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C782" s="2" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="D782" s="2" t="inlineStr">
@@ -23905,11 +23905,11 @@
         </is>
       </c>
       <c r="E782" s="3" t="n">
-        <v>57.39</v>
+        <v>58.3</v>
       </c>
       <c r="F782" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23921,25 +23921,25 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="D783" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>57.22</v>
+        <v>58.09</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23951,21 +23951,21 @@
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E784" s="3" t="n">
-        <v>56.5</v>
+        <v>57.22</v>
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
@@ -23981,12 +23981,12 @@
       </c>
       <c r="B785" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C785" s="2" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="D785" s="2" t="inlineStr">
@@ -23995,7 +23995,7 @@
         </is>
       </c>
       <c r="E785" s="3" t="n">
-        <v>55.05</v>
+        <v>56.5</v>
       </c>
       <c r="F785" s="2" t="inlineStr">
         <is>
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>54.68</v>
+        <v>56.21</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24041,12 +24041,12 @@
       </c>
       <c r="B787" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C787" s="2" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D787" s="2" t="inlineStr">
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>54.43</v>
+        <v>55.66</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24071,12 +24071,12 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="D788" s="2" t="inlineStr">
@@ -24085,11 +24085,11 @@
         </is>
       </c>
       <c r="E788" s="3" t="n">
-        <v>54.03</v>
+        <v>55.05</v>
       </c>
       <c r="F788" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24101,12 +24101,12 @@
       </c>
       <c r="B789" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C789" s="2" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="D789" s="2" t="inlineStr">
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>53.95</v>
+        <v>54.44</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24131,12 +24131,12 @@
       </c>
       <c r="B790" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C790" s="2" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="D790" s="2" t="inlineStr">
@@ -24145,11 +24145,11 @@
         </is>
       </c>
       <c r="E790" s="3" t="n">
-        <v>53.25</v>
+        <v>53.95</v>
       </c>
       <c r="F790" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24161,12 +24161,12 @@
       </c>
       <c r="B791" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C791" s="2" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="D791" s="2" t="inlineStr">
@@ -24175,11 +24175,11 @@
         </is>
       </c>
       <c r="E791" s="3" t="n">
-        <v>52.57</v>
+        <v>53.25</v>
       </c>
       <c r="F791" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24191,12 +24191,12 @@
       </c>
       <c r="B792" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C792" s="2" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="D792" s="2" t="inlineStr">
@@ -24205,11 +24205,11 @@
         </is>
       </c>
       <c r="E792" s="3" t="n">
-        <v>52.42</v>
+        <v>52.64</v>
       </c>
       <c r="F792" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24221,12 +24221,12 @@
       </c>
       <c r="B793" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C793" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D793" s="2" t="inlineStr">
@@ -24235,11 +24235,11 @@
         </is>
       </c>
       <c r="E793" s="3" t="n">
-        <v>51.82</v>
+        <v>52.63</v>
       </c>
       <c r="F793" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24251,12 +24251,12 @@
       </c>
       <c r="B794" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C794" s="2" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="D794" s="2" t="inlineStr">
@@ -24265,11 +24265,11 @@
         </is>
       </c>
       <c r="E794" s="3" t="n">
-        <v>50.96</v>
+        <v>52.57</v>
       </c>
       <c r="F794" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24281,12 +24281,12 @@
       </c>
       <c r="B795" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C795" s="2" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="D795" s="2" t="inlineStr">
@@ -24295,11 +24295,11 @@
         </is>
       </c>
       <c r="E795" s="3" t="n">
-        <v>50.13</v>
+        <v>52.42</v>
       </c>
       <c r="F795" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -24311,12 +24311,12 @@
       </c>
       <c r="B796" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C796" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="D796" s="2" t="inlineStr">
@@ -24325,11 +24325,11 @@
         </is>
       </c>
       <c r="E796" s="3" t="n">
-        <v>49.88</v>
+        <v>50.13</v>
       </c>
       <c r="F796" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24341,12 +24341,12 @@
       </c>
       <c r="B797" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C797" s="2" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="D797" s="2" t="inlineStr">
@@ -24355,11 +24355,11 @@
         </is>
       </c>
       <c r="E797" s="3" t="n">
-        <v>48.04</v>
+        <v>49.95</v>
       </c>
       <c r="F797" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24371,12 +24371,12 @@
       </c>
       <c r="B798" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C798" s="2" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="D798" s="2" t="inlineStr">
@@ -24385,11 +24385,11 @@
         </is>
       </c>
       <c r="E798" s="3" t="n">
-        <v>47.99</v>
+        <v>48.04</v>
       </c>
       <c r="F798" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="B799" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C799" s="2" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="D799" s="2" t="inlineStr">
@@ -24415,11 +24415,11 @@
         </is>
       </c>
       <c r="E799" s="3" t="n">
-        <v>47.23</v>
+        <v>47.99</v>
       </c>
       <c r="F799" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24431,12 +24431,12 @@
       </c>
       <c r="B800" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C800" s="2" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="D800" s="2" t="inlineStr">
@@ -24445,11 +24445,11 @@
         </is>
       </c>
       <c r="E800" s="3" t="n">
-        <v>46.67</v>
+        <v>47.23</v>
       </c>
       <c r="F800" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24475,11 +24475,11 @@
         </is>
       </c>
       <c r="E801" s="3" t="n">
-        <v>46.17</v>
+        <v>46.92</v>
       </c>
       <c r="F801" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24491,12 +24491,12 @@
       </c>
       <c r="B802" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C802" s="2" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="D802" s="2" t="inlineStr">
@@ -24505,11 +24505,11 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>46.1</v>
+        <v>46.8</v>
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24521,12 +24521,12 @@
       </c>
       <c r="B803" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C803" s="2" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="D803" s="2" t="inlineStr">
@@ -24535,11 +24535,11 @@
         </is>
       </c>
       <c r="E803" s="3" t="n">
-        <v>45.43</v>
+        <v>46.4</v>
       </c>
       <c r="F803" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24551,12 +24551,12 @@
       </c>
       <c r="B804" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C804" s="2" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="D804" s="2" t="inlineStr">
@@ -24565,11 +24565,11 @@
         </is>
       </c>
       <c r="E804" s="3" t="n">
-        <v>44.93</v>
+        <v>45.71</v>
       </c>
       <c r="F804" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24581,12 +24581,12 @@
       </c>
       <c r="B805" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C805" s="2" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="D805" s="2" t="inlineStr">
@@ -24595,11 +24595,11 @@
         </is>
       </c>
       <c r="E805" s="3" t="n">
-        <v>44.8</v>
+        <v>45.23</v>
       </c>
       <c r="F805" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24611,12 +24611,12 @@
       </c>
       <c r="B806" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C806" s="2" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="D806" s="2" t="inlineStr">
@@ -24625,11 +24625,11 @@
         </is>
       </c>
       <c r="E806" s="3" t="n">
-        <v>44.19</v>
+        <v>44.8</v>
       </c>
       <c r="F806" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24641,12 +24641,12 @@
       </c>
       <c r="B807" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C807" s="2" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="D807" s="2" t="inlineStr">
@@ -24655,11 +24655,11 @@
         </is>
       </c>
       <c r="E807" s="3" t="n">
-        <v>40.98</v>
+        <v>44.19</v>
       </c>
       <c r="F807" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24671,12 +24671,12 @@
       </c>
       <c r="B808" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="C808" s="2" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="D808" s="2" t="inlineStr">
@@ -24685,11 +24685,11 @@
         </is>
       </c>
       <c r="E808" s="3" t="n">
-        <v>40.09</v>
+        <v>43.24</v>
       </c>
       <c r="F808" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24701,12 +24701,12 @@
       </c>
       <c r="B809" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C809" s="2" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D809" s="2" t="inlineStr">
@@ -24715,11 +24715,11 @@
         </is>
       </c>
       <c r="E809" s="3" t="n">
-        <v>39.2</v>
+        <v>39.77</v>
       </c>
       <c r="F809" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24731,12 +24731,12 @@
       </c>
       <c r="B810" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C810" s="2" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="D810" s="2" t="inlineStr">
@@ -24745,11 +24745,11 @@
         </is>
       </c>
       <c r="E810" s="3" t="n">
-        <v>37.86</v>
+        <v>39.35</v>
       </c>
       <c r="F810" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24761,12 +24761,12 @@
       </c>
       <c r="B811" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C811" s="2" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="D811" s="2" t="inlineStr">
@@ -24775,11 +24775,11 @@
         </is>
       </c>
       <c r="E811" s="3" t="n">
-        <v>37.65</v>
+        <v>39.2</v>
       </c>
       <c r="F811" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24791,12 +24791,12 @@
       </c>
       <c r="B812" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C812" s="2" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="D812" s="2" t="inlineStr">
@@ -24805,11 +24805,11 @@
         </is>
       </c>
       <c r="E812" s="3" t="n">
-        <v>36.75</v>
+        <v>38.54</v>
       </c>
       <c r="F812" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24821,12 +24821,12 @@
       </c>
       <c r="B813" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C813" s="2" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="D813" s="2" t="inlineStr">
@@ -24835,11 +24835,11 @@
         </is>
       </c>
       <c r="E813" s="3" t="n">
-        <v>36.59</v>
+        <v>37.83</v>
       </c>
       <c r="F813" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24851,12 +24851,12 @@
       </c>
       <c r="B814" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C814" s="2" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="D814" s="2" t="inlineStr">
@@ -24865,11 +24865,11 @@
         </is>
       </c>
       <c r="E814" s="3" t="n">
-        <v>36.39</v>
+        <v>37.65</v>
       </c>
       <c r="F814" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24881,12 +24881,12 @@
       </c>
       <c r="B815" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C815" s="2" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="D815" s="2" t="inlineStr">
@@ -24895,11 +24895,11 @@
         </is>
       </c>
       <c r="E815" s="3" t="n">
-        <v>36.31</v>
+        <v>36.75</v>
       </c>
       <c r="F815" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24911,12 +24911,12 @@
       </c>
       <c r="B816" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C816" s="2" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="D816" s="2" t="inlineStr">
@@ -24925,11 +24925,11 @@
         </is>
       </c>
       <c r="E816" s="3" t="n">
-        <v>35.72</v>
+        <v>36.59</v>
       </c>
       <c r="F816" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24941,12 +24941,12 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="D817" s="2" t="inlineStr">
@@ -24955,7 +24955,7 @@
         </is>
       </c>
       <c r="E817" s="3" t="n">
-        <v>34.1</v>
+        <v>36.31</v>
       </c>
       <c r="F817" s="2" t="inlineStr">
         <is>
@@ -24971,12 +24971,12 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="D818" s="2" t="inlineStr">
@@ -24985,11 +24985,11 @@
         </is>
       </c>
       <c r="E818" s="3" t="n">
-        <v>34.05</v>
+        <v>36.16</v>
       </c>
       <c r="F818" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -25001,12 +25001,12 @@
       </c>
       <c r="B819" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C819" s="2" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="D819" s="2" t="inlineStr">
@@ -25015,11 +25015,11 @@
         </is>
       </c>
       <c r="E819" s="3" t="n">
-        <v>33.35</v>
+        <v>34.1</v>
       </c>
       <c r="F819" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25031,12 +25031,12 @@
       </c>
       <c r="B820" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="C820" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="D820" s="2" t="inlineStr">
@@ -25045,11 +25045,11 @@
         </is>
       </c>
       <c r="E820" s="3" t="n">
-        <v>31.53</v>
+        <v>34.05</v>
       </c>
       <c r="F820" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25105,11 +25105,11 @@
         </is>
       </c>
       <c r="E822" s="3" t="n">
-        <v>30.72</v>
+        <v>31.03</v>
       </c>
       <c r="F822" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -25225,11 +25225,11 @@
         </is>
       </c>
       <c r="E826" s="3" t="n">
-        <v>27.26</v>
+        <v>27.39</v>
       </c>
       <c r="F826" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -25255,11 +25255,11 @@
         </is>
       </c>
       <c r="E827" s="3" t="n">
-        <v>26.77</v>
+        <v>26.86</v>
       </c>
       <c r="F827" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -25315,11 +25315,11 @@
         </is>
       </c>
       <c r="E829" s="3" t="n">
-        <v>24.71</v>
+        <v>25.28</v>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -25361,25 +25361,25 @@
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C831" s="2" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="D831" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E831" s="3" t="n">
-        <v>22.83</v>
+        <v>23.41</v>
       </c>
       <c r="F831" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -25391,25 +25391,25 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="D832" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E832" s="3" t="n">
-        <v>22.39</v>
+        <v>23.16</v>
       </c>
       <c r="F832" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -25421,12 +25421,12 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="D833" s="2" t="inlineStr">
@@ -25435,11 +25435,11 @@
         </is>
       </c>
       <c r="E833" s="3" t="n">
-        <v>22.35</v>
+        <v>22.88</v>
       </c>
       <c r="F833" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -25451,12 +25451,12 @@
       </c>
       <c r="B834" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C834" s="2" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="D834" s="2" t="inlineStr">
@@ -25465,11 +25465,11 @@
         </is>
       </c>
       <c r="E834" s="3" t="n">
-        <v>21.7</v>
+        <v>22.39</v>
       </c>
       <c r="F834" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25481,12 +25481,12 @@
       </c>
       <c r="B835" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C835" s="2" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="D835" s="2" t="inlineStr">
@@ -25495,11 +25495,11 @@
         </is>
       </c>
       <c r="E835" s="3" t="n">
-        <v>21.21</v>
+        <v>21.81</v>
       </c>
       <c r="F835" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -25511,12 +25511,12 @@
       </c>
       <c r="B836" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C836" s="2" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="D836" s="2" t="inlineStr">
@@ -25525,11 +25525,11 @@
         </is>
       </c>
       <c r="E836" s="3" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="F836" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25541,12 +25541,12 @@
       </c>
       <c r="B837" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C837" s="2" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="D837" s="2" t="inlineStr">
@@ -25555,7 +25555,7 @@
         </is>
       </c>
       <c r="E837" s="3" t="n">
-        <v>21.17</v>
+        <v>21.21</v>
       </c>
       <c r="F837" s="2" t="inlineStr">
         <is>
@@ -25571,12 +25571,12 @@
       </c>
       <c r="B838" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C838" s="2" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="D838" s="2" t="inlineStr">
@@ -25585,7 +25585,7 @@
         </is>
       </c>
       <c r="E838" s="3" t="n">
-        <v>20.98</v>
+        <v>21.17</v>
       </c>
       <c r="F838" s="2" t="inlineStr">
         <is>
@@ -25601,12 +25601,12 @@
       </c>
       <c r="B839" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C839" s="2" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="D839" s="2" t="inlineStr">
@@ -25615,7 +25615,7 @@
         </is>
       </c>
       <c r="E839" s="3" t="n">
-        <v>20.61</v>
+        <v>20.98</v>
       </c>
       <c r="F839" s="2" t="inlineStr">
         <is>
@@ -25631,12 +25631,12 @@
       </c>
       <c r="B840" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C840" s="2" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="D840" s="2" t="inlineStr">
@@ -25645,7 +25645,7 @@
         </is>
       </c>
       <c r="E840" s="3" t="n">
-        <v>20.12</v>
+        <v>20.61</v>
       </c>
       <c r="F840" s="2" t="inlineStr">
         <is>
@@ -25661,12 +25661,12 @@
       </c>
       <c r="B841" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C841" s="2" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="D841" s="2" t="inlineStr">
@@ -25675,7 +25675,7 @@
         </is>
       </c>
       <c r="E841" s="3" t="n">
-        <v>19.65</v>
+        <v>20.12</v>
       </c>
       <c r="F841" s="2" t="inlineStr">
         <is>
@@ -25691,12 +25691,12 @@
       </c>
       <c r="B842" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C842" s="2" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="D842" s="2" t="inlineStr">
@@ -25705,11 +25705,11 @@
         </is>
       </c>
       <c r="E842" s="3" t="n">
-        <v>19.52</v>
+        <v>19.65</v>
       </c>
       <c r="F842" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25721,12 +25721,12 @@
       </c>
       <c r="B843" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C843" s="2" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="D843" s="2" t="inlineStr">
@@ -25735,11 +25735,11 @@
         </is>
       </c>
       <c r="E843" s="3" t="n">
-        <v>18.81</v>
+        <v>19.52</v>
       </c>
       <c r="F843" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -25751,12 +25751,12 @@
       </c>
       <c r="B844" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C844" s="2" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D844" s="2" t="inlineStr">
@@ -25765,11 +25765,11 @@
         </is>
       </c>
       <c r="E844" s="3" t="n">
-        <v>17.76</v>
+        <v>19.19</v>
       </c>
       <c r="F844" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -25781,12 +25781,12 @@
       </c>
       <c r="B845" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C845" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="D845" s="2" t="inlineStr">
@@ -25795,11 +25795,11 @@
         </is>
       </c>
       <c r="E845" s="3" t="n">
-        <v>17.68</v>
+        <v>17.76</v>
       </c>
       <c r="F845" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25931,12 +25931,12 @@
       </c>
       <c r="B850" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C850" s="2" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="D850" s="2" t="inlineStr">
@@ -25945,11 +25945,11 @@
         </is>
       </c>
       <c r="E850" s="3" t="n">
-        <v>15.35</v>
+        <v>15.51</v>
       </c>
       <c r="F850" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -25961,12 +25961,12 @@
       </c>
       <c r="B851" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C851" s="2" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="D851" s="2" t="inlineStr">
@@ -25975,7 +25975,7 @@
         </is>
       </c>
       <c r="E851" s="3" t="n">
-        <v>12.48</v>
+        <v>15.35</v>
       </c>
       <c r="F851" s="2" t="inlineStr">
         <is>
@@ -25991,12 +25991,12 @@
       </c>
       <c r="B852" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C852" s="2" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="D852" s="2" t="inlineStr">
@@ -26005,7 +26005,7 @@
         </is>
       </c>
       <c r="E852" s="3" t="n">
-        <v>12.19</v>
+        <v>12.48</v>
       </c>
       <c r="F852" s="2" t="inlineStr">
         <is>
@@ -26021,12 +26021,12 @@
       </c>
       <c r="B853" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413801QJB</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C853" s="2" t="inlineStr">
         <is>
-          <t>812824</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="D853" s="2" t="inlineStr">
@@ -26035,11 +26035,11 @@
         </is>
       </c>
       <c r="E853" s="3" t="n">
-        <v>11.47</v>
+        <v>12.19</v>
       </c>
       <c r="F853" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26051,12 +26051,12 @@
       </c>
       <c r="B854" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="C854" s="2" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>812824</t>
         </is>
       </c>
       <c r="D854" s="2" t="inlineStr">
@@ -26065,11 +26065,11 @@
         </is>
       </c>
       <c r="E854" s="3" t="n">
-        <v>10.75</v>
+        <v>11.47</v>
       </c>
       <c r="F854" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -26081,12 +26081,12 @@
       </c>
       <c r="B855" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C855" s="2" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="D855" s="2" t="inlineStr">
@@ -26095,11 +26095,11 @@
         </is>
       </c>
       <c r="E855" s="3" t="n">
-        <v>10.18</v>
+        <v>10.75</v>
       </c>
       <c r="F855" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26111,12 +26111,12 @@
       </c>
       <c r="B856" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="C856" s="2" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>816274</t>
         </is>
       </c>
       <c r="D856" s="2" t="inlineStr">
@@ -26125,11 +26125,11 @@
         </is>
       </c>
       <c r="E856" s="3" t="n">
-        <v>10.07</v>
+        <v>10.3</v>
       </c>
       <c r="F856" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -26141,12 +26141,12 @@
       </c>
       <c r="B857" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C857" s="2" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="D857" s="2" t="inlineStr">
@@ -26155,7 +26155,7 @@
         </is>
       </c>
       <c r="E857" s="3" t="n">
-        <v>9.27</v>
+        <v>10.07</v>
       </c>
       <c r="F857" s="2" t="inlineStr">
         <is>
@@ -26171,12 +26171,12 @@
       </c>
       <c r="B858" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C858" s="2" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="D858" s="2" t="inlineStr">
@@ -26185,7 +26185,7 @@
         </is>
       </c>
       <c r="E858" s="3" t="n">
-        <v>8.529999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="F858" s="2" t="inlineStr">
         <is>
@@ -26201,12 +26201,12 @@
       </c>
       <c r="B859" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413773R6G</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C859" s="2" t="inlineStr">
         <is>
-          <t>812807</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="D859" s="2" t="inlineStr">
@@ -26215,7 +26215,7 @@
         </is>
       </c>
       <c r="E859" s="3" t="n">
-        <v>7.91</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="F859" s="2" t="inlineStr">
         <is>
@@ -26231,12 +26231,12 @@
       </c>
       <c r="B860" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0541381584X</t>
+          <t>KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="C860" s="2" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>812807</t>
         </is>
       </c>
       <c r="D860" s="2" t="inlineStr">
@@ -26245,7 +26245,7 @@
         </is>
       </c>
       <c r="E860" s="3" t="n">
-        <v>7.74</v>
+        <v>7.91</v>
       </c>
       <c r="F860" s="2" t="inlineStr">
         <is>
@@ -26261,12 +26261,12 @@
       </c>
       <c r="B861" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M0541381584X</t>
         </is>
       </c>
       <c r="C861" s="2" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>812810</t>
         </is>
       </c>
       <c r="D861" s="2" t="inlineStr">
@@ -26275,7 +26275,7 @@
         </is>
       </c>
       <c r="E861" s="3" t="n">
-        <v>7.52</v>
+        <v>7.74</v>
       </c>
       <c r="F861" s="2" t="inlineStr">
         <is>
@@ -26291,12 +26291,12 @@
       </c>
       <c r="B862" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799709G5Q</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C862" s="2" t="inlineStr">
         <is>
-          <t>816274</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="D862" s="2" t="inlineStr">
@@ -26305,11 +26305,11 @@
         </is>
       </c>
       <c r="E862" s="3" t="n">
-        <v>6.32</v>
+        <v>7.52</v>
       </c>
       <c r="F862" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26351,12 +26351,12 @@
       </c>
       <c r="B864" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413775N9M</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C864" s="2" t="inlineStr">
         <is>
-          <t>812818</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="D864" s="2" t="inlineStr">
@@ -26365,11 +26365,11 @@
         </is>
       </c>
       <c r="E864" s="3" t="n">
-        <v>4.49</v>
+        <v>5.19</v>
       </c>
       <c r="F864" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -26381,12 +26381,12 @@
       </c>
       <c r="B865" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="C865" s="2" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>812818</t>
         </is>
       </c>
       <c r="D865" s="2" t="inlineStr">
@@ -26395,11 +26395,11 @@
         </is>
       </c>
       <c r="E865" s="3" t="n">
-        <v>4.48</v>
+        <v>4.49</v>
       </c>
       <c r="F865" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26425,11 +26425,11 @@
         </is>
       </c>
       <c r="E866" s="3" t="n">
-        <v>3.66</v>
+        <v>4.26</v>
       </c>
       <c r="F866" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2302.06</v>
+        <v>2324.48</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -19795,11 +19795,11 @@
         </is>
       </c>
       <c r="E645" s="3" t="n">
-        <v>1927.82</v>
+        <v>1964.07</v>
       </c>
       <c r="F645" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -19885,11 +19885,11 @@
         </is>
       </c>
       <c r="E648" s="3" t="n">
-        <v>1033.73</v>
+        <v>1055.27</v>
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>1030.84</v>
+        <v>1050.69</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -19975,11 +19975,11 @@
         </is>
       </c>
       <c r="E651" s="3" t="n">
-        <v>771.6900000000001</v>
+        <v>798.91</v>
       </c>
       <c r="F651" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20035,11 +20035,11 @@
         </is>
       </c>
       <c r="E653" s="3" t="n">
-        <v>713.34</v>
+        <v>735.71</v>
       </c>
       <c r="F653" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20081,12 +20081,12 @@
       </c>
       <c r="B655" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739124KF</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C655" s="2" t="inlineStr">
         <is>
-          <t>814640</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="D655" s="2" t="inlineStr">
@@ -20095,11 +20095,11 @@
         </is>
       </c>
       <c r="E655" s="3" t="n">
-        <v>611.98</v>
+        <v>617.02</v>
       </c>
       <c r="F655" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20125,11 +20125,11 @@
         </is>
       </c>
       <c r="E656" s="3" t="n">
-        <v>610.63</v>
+        <v>613.48</v>
       </c>
       <c r="F656" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20141,12 +20141,12 @@
       </c>
       <c r="B657" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4P000739124KF</t>
         </is>
       </c>
       <c r="C657" s="2" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>814640</t>
         </is>
       </c>
       <c r="D657" s="2" t="inlineStr">
@@ -20155,11 +20155,11 @@
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>608.17</v>
+        <v>612.21</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20185,11 +20185,11 @@
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>598.3099999999999</v>
+        <v>599.25</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20215,11 +20215,11 @@
         </is>
       </c>
       <c r="E659" s="3" t="n">
-        <v>569.0700000000001</v>
+        <v>570.26</v>
       </c>
       <c r="F659" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20245,11 +20245,11 @@
         </is>
       </c>
       <c r="E660" s="3" t="n">
-        <v>556.66</v>
+        <v>557.17</v>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20275,11 +20275,11 @@
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>529.1900000000001</v>
+        <v>538.58</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20365,11 +20365,11 @@
         </is>
       </c>
       <c r="E664" s="3" t="n">
-        <v>495.62</v>
+        <v>500.18</v>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20381,25 +20381,25 @@
       </c>
       <c r="B665" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E665" s="3" t="n">
-        <v>481.34</v>
+        <v>490.06</v>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20411,12 +20411,12 @@
       </c>
       <c r="B666" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
@@ -20425,11 +20425,11 @@
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>480.85</v>
+        <v>485.08</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20441,25 +20441,25 @@
       </c>
       <c r="B667" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C667" s="2" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="D667" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E667" s="3" t="n">
-        <v>475.95</v>
+        <v>480.85</v>
       </c>
       <c r="F667" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20515,11 +20515,11 @@
         </is>
       </c>
       <c r="E669" s="3" t="n">
-        <v>453.41</v>
+        <v>458.15</v>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20545,11 +20545,11 @@
         </is>
       </c>
       <c r="E670" s="3" t="n">
-        <v>422.94</v>
+        <v>428.3</v>
       </c>
       <c r="F670" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20561,25 +20561,25 @@
       </c>
       <c r="B671" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065631CPZ</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C671" s="2" t="inlineStr">
         <is>
-          <t>812930</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="D671" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E671" s="3" t="n">
-        <v>415.73</v>
+        <v>421.94</v>
       </c>
       <c r="F671" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20591,25 +20591,25 @@
       </c>
       <c r="B672" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="C672" s="2" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>812930</t>
         </is>
       </c>
       <c r="D672" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E672" s="3" t="n">
-        <v>410.16</v>
+        <v>415.73</v>
       </c>
       <c r="F672" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20665,11 +20665,11 @@
         </is>
       </c>
       <c r="E674" s="3" t="n">
-        <v>391.32</v>
+        <v>397.95</v>
       </c>
       <c r="F674" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20695,11 +20695,11 @@
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>374.6</v>
+        <v>375.85</v>
       </c>
       <c r="F675" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20725,11 +20725,11 @@
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>330.54</v>
+        <v>331.37</v>
       </c>
       <c r="F676" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20755,11 +20755,11 @@
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>323.63</v>
+        <v>324.42</v>
       </c>
       <c r="F677" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20771,12 +20771,12 @@
       </c>
       <c r="B678" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C678" s="2" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="D678" s="2" t="inlineStr">
@@ -20785,11 +20785,11 @@
         </is>
       </c>
       <c r="E678" s="3" t="n">
-        <v>318.87</v>
+        <v>322.77</v>
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20801,12 +20801,12 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="D679" s="2" t="inlineStr">
@@ -20815,11 +20815,11 @@
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>317.28</v>
+        <v>318.87</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>308.25</v>
+        <v>314.95</v>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20935,11 +20935,11 @@
         </is>
       </c>
       <c r="E683" s="3" t="n">
-        <v>265.66</v>
+        <v>266.36</v>
       </c>
       <c r="F683" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20965,11 +20965,11 @@
         </is>
       </c>
       <c r="E684" s="3" t="n">
-        <v>255.03</v>
+        <v>257.45</v>
       </c>
       <c r="F684" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -20981,25 +20981,25 @@
       </c>
       <c r="B685" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C685" s="2" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="D685" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E685" s="3" t="n">
-        <v>246.96</v>
+        <v>253.99</v>
       </c>
       <c r="F685" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21011,25 +21011,25 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="D686" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E686" s="3" t="n">
-        <v>244.01</v>
+        <v>246.96</v>
       </c>
       <c r="F686" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21055,11 +21055,11 @@
         </is>
       </c>
       <c r="E687" s="3" t="n">
-        <v>243.37</v>
+        <v>243.79</v>
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21115,11 +21115,11 @@
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>226.35</v>
+        <v>228.86</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21145,11 +21145,11 @@
         </is>
       </c>
       <c r="E690" s="3" t="n">
-        <v>214.79</v>
+        <v>215.89</v>
       </c>
       <c r="F690" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21175,11 +21175,11 @@
         </is>
       </c>
       <c r="E691" s="3" t="n">
-        <v>214.33</v>
+        <v>214.73</v>
       </c>
       <c r="F691" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21205,11 +21205,11 @@
         </is>
       </c>
       <c r="E692" s="3" t="n">
-        <v>210.07</v>
+        <v>210.11</v>
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21235,11 +21235,11 @@
         </is>
       </c>
       <c r="E693" s="3" t="n">
-        <v>203.78</v>
+        <v>209.97</v>
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21265,11 +21265,11 @@
         </is>
       </c>
       <c r="E694" s="3" t="n">
-        <v>201.27</v>
+        <v>202.21</v>
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>193.81</v>
+        <v>194.62</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21325,11 +21325,11 @@
         </is>
       </c>
       <c r="E696" s="3" t="n">
-        <v>189.49</v>
+        <v>191.02</v>
       </c>
       <c r="F696" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>180.59</v>
+        <v>180.6</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="E698" s="3" t="n">
-        <v>177.81</v>
+        <v>180.46</v>
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>175.92</v>
+        <v>177.05</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21445,11 +21445,11 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>166.02</v>
+        <v>169.84</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>159.16</v>
+        <v>161.48</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>154.5</v>
+        <v>157.25</v>
       </c>
       <c r="F703" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21565,11 +21565,11 @@
         </is>
       </c>
       <c r="E704" s="3" t="n">
-        <v>154.15</v>
+        <v>157.01</v>
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21581,12 +21581,12 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="D705" s="2" t="inlineStr">
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>150.01</v>
+        <v>151.89</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21611,12 +21611,12 @@
       </c>
       <c r="B706" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C706" s="2" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="D706" s="2" t="inlineStr">
@@ -21625,11 +21625,11 @@
         </is>
       </c>
       <c r="E706" s="3" t="n">
-        <v>147.64</v>
+        <v>150.25</v>
       </c>
       <c r="F706" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21655,11 +21655,11 @@
         </is>
       </c>
       <c r="E707" s="3" t="n">
-        <v>143.24</v>
+        <v>145.07</v>
       </c>
       <c r="F707" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21685,11 +21685,11 @@
         </is>
       </c>
       <c r="E708" s="3" t="n">
-        <v>137.79</v>
+        <v>139.81</v>
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21715,11 +21715,11 @@
         </is>
       </c>
       <c r="E709" s="3" t="n">
-        <v>134.39</v>
+        <v>134.82</v>
       </c>
       <c r="F709" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21745,11 +21745,11 @@
         </is>
       </c>
       <c r="E710" s="3" t="n">
-        <v>133.73</v>
+        <v>133.81</v>
       </c>
       <c r="F710" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21865,11 +21865,11 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>130.85</v>
+        <v>130.95</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21895,11 +21895,11 @@
         </is>
       </c>
       <c r="E715" s="3" t="n">
-        <v>129.39</v>
+        <v>129.75</v>
       </c>
       <c r="F715" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21925,11 +21925,11 @@
         </is>
       </c>
       <c r="E716" s="3" t="n">
-        <v>126.21</v>
+        <v>127.08</v>
       </c>
       <c r="F716" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B717" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C717" s="2" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="D717" s="2" t="inlineStr">
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>126.03</v>
+        <v>126.04</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21971,12 +21971,12 @@
       </c>
       <c r="B718" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr">
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>125.51</v>
+        <v>126.03</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22015,11 +22015,11 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>124.47</v>
+        <v>124.72</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -22061,12 +22061,12 @@
       </c>
       <c r="B721" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C721" s="2" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="D721" s="2" t="inlineStr">
@@ -22075,11 +22075,11 @@
         </is>
       </c>
       <c r="E721" s="3" t="n">
-        <v>117.93</v>
+        <v>119.22</v>
       </c>
       <c r="F721" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -22091,12 +22091,12 @@
       </c>
       <c r="B722" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C722" s="2" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="D722" s="2" t="inlineStr">
@@ -22105,11 +22105,11 @@
         </is>
       </c>
       <c r="E722" s="3" t="n">
-        <v>116.01</v>
+        <v>117.93</v>
       </c>
       <c r="F722" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22121,12 +22121,12 @@
       </c>
       <c r="B723" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C723" s="2" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="D723" s="2" t="inlineStr">
@@ -22135,11 +22135,11 @@
         </is>
       </c>
       <c r="E723" s="3" t="n">
-        <v>114.07</v>
+        <v>116.59</v>
       </c>
       <c r="F723" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -22151,12 +22151,12 @@
       </c>
       <c r="B724" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C724" s="2" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="D724" s="2" t="inlineStr">
@@ -22165,11 +22165,11 @@
         </is>
       </c>
       <c r="E724" s="3" t="n">
-        <v>113.82</v>
+        <v>114.07</v>
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22255,11 +22255,11 @@
         </is>
       </c>
       <c r="E727" s="3" t="n">
-        <v>108.51</v>
+        <v>108.57</v>
       </c>
       <c r="F727" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -22285,11 +22285,11 @@
         </is>
       </c>
       <c r="E728" s="3" t="n">
-        <v>108.21</v>
+        <v>108.23</v>
       </c>
       <c r="F728" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -22301,12 +22301,12 @@
       </c>
       <c r="B729" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C729" s="2" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="D729" s="2" t="inlineStr">
@@ -22315,11 +22315,11 @@
         </is>
       </c>
       <c r="E729" s="3" t="n">
-        <v>103.72</v>
+        <v>104.72</v>
       </c>
       <c r="F729" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -22331,12 +22331,12 @@
       </c>
       <c r="B730" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C730" s="2" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D730" s="2" t="inlineStr">
@@ -22345,11 +22345,11 @@
         </is>
       </c>
       <c r="E730" s="3" t="n">
-        <v>103.28</v>
+        <v>104.18</v>
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -22361,12 +22361,12 @@
       </c>
       <c r="B731" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D731" s="2" t="inlineStr">
@@ -22375,11 +22375,11 @@
         </is>
       </c>
       <c r="E731" s="3" t="n">
-        <v>103.07</v>
+        <v>104.17</v>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -22391,12 +22391,12 @@
       </c>
       <c r="B732" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="D732" s="2" t="inlineStr">
@@ -22405,11 +22405,11 @@
         </is>
       </c>
       <c r="E732" s="3" t="n">
-        <v>101.51</v>
+        <v>103.72</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22421,12 +22421,12 @@
       </c>
       <c r="B733" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="D733" s="2" t="inlineStr">
@@ -22435,11 +22435,11 @@
         </is>
       </c>
       <c r="E733" s="3" t="n">
-        <v>100.93</v>
+        <v>101.35</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -22451,12 +22451,12 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
@@ -22465,11 +22465,11 @@
         </is>
       </c>
       <c r="E734" s="3" t="n">
-        <v>100.53</v>
+        <v>100.93</v>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22511,12 +22511,12 @@
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
@@ -22525,11 +22525,11 @@
         </is>
       </c>
       <c r="E736" s="3" t="n">
-        <v>98.64</v>
+        <v>99.78</v>
       </c>
       <c r="F736" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -22541,12 +22541,12 @@
       </c>
       <c r="B737" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="D737" s="2" t="inlineStr">
@@ -22555,11 +22555,11 @@
         </is>
       </c>
       <c r="E737" s="3" t="n">
-        <v>97.56999999999999</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -22571,12 +22571,12 @@
       </c>
       <c r="B738" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="D738" s="2" t="inlineStr">
@@ -22585,11 +22585,11 @@
         </is>
       </c>
       <c r="E738" s="3" t="n">
-        <v>97.44</v>
+        <v>98.47</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -22601,12 +22601,12 @@
       </c>
       <c r="B739" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C739" s="2" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="D739" s="2" t="inlineStr">
@@ -22615,11 +22615,11 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>95.89</v>
+        <v>97.44</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22645,11 +22645,11 @@
         </is>
       </c>
       <c r="E740" s="3" t="n">
-        <v>95.06</v>
+        <v>95.12</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>91.04000000000001</v>
+        <v>92.22</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -22735,11 +22735,11 @@
         </is>
       </c>
       <c r="E743" s="3" t="n">
-        <v>90.48999999999999</v>
+        <v>91.16</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -22751,12 +22751,12 @@
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="D744" s="2" t="inlineStr">
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>89.79000000000001</v>
+        <v>90.86</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -22781,21 +22781,21 @@
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>89.48999999999999</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
@@ -22811,25 +22811,25 @@
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E746" s="3" t="n">
-        <v>88.2</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22841,12 +22841,12 @@
       </c>
       <c r="B747" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C747" s="2" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="D747" s="2" t="inlineStr">
@@ -22855,11 +22855,11 @@
         </is>
       </c>
       <c r="E747" s="3" t="n">
-        <v>87.73</v>
+        <v>88.27</v>
       </c>
       <c r="F747" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -22871,12 +22871,12 @@
       </c>
       <c r="B748" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C748" s="2" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="D748" s="2" t="inlineStr">
@@ -22885,11 +22885,11 @@
         </is>
       </c>
       <c r="E748" s="3" t="n">
-        <v>87.69</v>
+        <v>87.73</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22975,11 +22975,11 @@
         </is>
       </c>
       <c r="E751" s="3" t="n">
-        <v>82.36</v>
+        <v>82.69</v>
       </c>
       <c r="F751" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23065,11 +23065,11 @@
         </is>
       </c>
       <c r="E754" s="3" t="n">
-        <v>81.61</v>
+        <v>81.63</v>
       </c>
       <c r="F754" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23125,11 +23125,11 @@
         </is>
       </c>
       <c r="E756" s="3" t="n">
-        <v>77.37</v>
+        <v>78.22</v>
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23245,11 +23245,11 @@
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>73</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23321,12 +23321,12 @@
       </c>
       <c r="B763" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C763" s="2" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D763" s="2" t="inlineStr">
@@ -23335,11 +23335,11 @@
         </is>
       </c>
       <c r="E763" s="3" t="n">
-        <v>68.5</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="F763" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>67.63</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23381,12 +23381,12 @@
       </c>
       <c r="B765" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C765" s="2" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="D765" s="2" t="inlineStr">
@@ -23395,11 +23395,11 @@
         </is>
       </c>
       <c r="E765" s="3" t="n">
-        <v>66.70999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="F765" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23411,12 +23411,12 @@
       </c>
       <c r="B766" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C766" s="2" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D766" s="2" t="inlineStr">
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>66.38</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23441,12 +23441,12 @@
       </c>
       <c r="B767" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C767" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="D767" s="2" t="inlineStr">
@@ -23455,11 +23455,11 @@
         </is>
       </c>
       <c r="E767" s="3" t="n">
-        <v>66.2</v>
+        <v>66.78</v>
       </c>
       <c r="F767" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23471,12 +23471,12 @@
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="D768" s="2" t="inlineStr">
@@ -23485,11 +23485,11 @@
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>66.62</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23501,12 @@
       </c>
       <c r="B769" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C769" s="2" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="D769" s="2" t="inlineStr">
@@ -23515,7 +23515,7 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>66.38</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
@@ -23531,12 +23531,12 @@
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
@@ -23545,11 +23545,11 @@
         </is>
       </c>
       <c r="E770" s="3" t="n">
-        <v>64.95</v>
+        <v>66.12</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23561,12 +23561,12 @@
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
@@ -23575,11 +23575,11 @@
         </is>
       </c>
       <c r="E771" s="3" t="n">
-        <v>64.47</v>
+        <v>65.75</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23591,12 +23591,12 @@
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -23605,11 +23605,11 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>63.6</v>
+        <v>64.95</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23621,12 +23621,12 @@
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="D773" s="2" t="inlineStr">
@@ -23635,11 +23635,11 @@
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>63.33</v>
+        <v>63.6</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23651,12 +23651,12 @@
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr">
@@ -23665,11 +23665,11 @@
         </is>
       </c>
       <c r="E774" s="3" t="n">
-        <v>63.03</v>
+        <v>63.45</v>
       </c>
       <c r="F774" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23681,12 +23681,12 @@
       </c>
       <c r="B775" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C775" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D775" s="2" t="inlineStr">
@@ -23695,11 +23695,11 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>62.84</v>
+        <v>63.05</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23725,11 +23725,11 @@
         </is>
       </c>
       <c r="E776" s="3" t="n">
-        <v>61.85</v>
+        <v>62.12</v>
       </c>
       <c r="F776" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23741,12 +23741,12 @@
       </c>
       <c r="B777" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C777" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D777" s="2" t="inlineStr">
@@ -23755,11 +23755,11 @@
         </is>
       </c>
       <c r="E777" s="3" t="n">
-        <v>61.83</v>
+        <v>62.12</v>
       </c>
       <c r="F777" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23771,12 +23771,12 @@
       </c>
       <c r="B778" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C778" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D778" s="2" t="inlineStr">
@@ -23785,11 +23785,11 @@
         </is>
       </c>
       <c r="E778" s="3" t="n">
-        <v>61.5</v>
+        <v>61.83</v>
       </c>
       <c r="F778" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23801,12 +23801,12 @@
       </c>
       <c r="B779" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C779" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D779" s="2" t="inlineStr">
@@ -23815,11 +23815,11 @@
         </is>
       </c>
       <c r="E779" s="3" t="n">
-        <v>61.47</v>
+        <v>61.6</v>
       </c>
       <c r="F779" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23845,11 +23845,11 @@
         </is>
       </c>
       <c r="E780" s="3" t="n">
-        <v>60.59</v>
+        <v>60.82</v>
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23875,11 +23875,11 @@
         </is>
       </c>
       <c r="E781" s="3" t="n">
-        <v>60.28</v>
+        <v>60.36</v>
       </c>
       <c r="F781" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23891,12 +23891,12 @@
       </c>
       <c r="B782" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C782" s="2" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="D782" s="2" t="inlineStr">
@@ -23905,11 +23905,11 @@
         </is>
       </c>
       <c r="E782" s="3" t="n">
-        <v>58.3</v>
+        <v>59.16</v>
       </c>
       <c r="F782" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23935,11 +23935,11 @@
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>58.09</v>
+        <v>58.53</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23951,25 +23951,25 @@
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E784" s="3" t="n">
-        <v>57.22</v>
+        <v>58.34</v>
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23981,21 +23981,21 @@
       </c>
       <c r="B785" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C785" s="2" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="D785" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E785" s="3" t="n">
-        <v>56.5</v>
+        <v>57.22</v>
       </c>
       <c r="F785" s="2" t="inlineStr">
         <is>
@@ -24011,12 +24011,12 @@
       </c>
       <c r="B786" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C786" s="2" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="D786" s="2" t="inlineStr">
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>56.21</v>
+        <v>56.5</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>55.66</v>
+        <v>55.92</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>54.44</v>
+        <v>54.72</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24131,12 +24131,12 @@
       </c>
       <c r="B790" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C790" s="2" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D790" s="2" t="inlineStr">
@@ -24145,11 +24145,11 @@
         </is>
       </c>
       <c r="E790" s="3" t="n">
-        <v>53.95</v>
+        <v>54.13</v>
       </c>
       <c r="F790" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24161,12 +24161,12 @@
       </c>
       <c r="B791" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C791" s="2" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="D791" s="2" t="inlineStr">
@@ -24175,11 +24175,11 @@
         </is>
       </c>
       <c r="E791" s="3" t="n">
-        <v>53.25</v>
+        <v>53.95</v>
       </c>
       <c r="F791" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24191,12 +24191,12 @@
       </c>
       <c r="B792" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C792" s="2" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="D792" s="2" t="inlineStr">
@@ -24205,11 +24205,11 @@
         </is>
       </c>
       <c r="E792" s="3" t="n">
-        <v>52.64</v>
+        <v>53.26</v>
       </c>
       <c r="F792" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24221,12 +24221,12 @@
       </c>
       <c r="B793" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C793" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="D793" s="2" t="inlineStr">
@@ -24235,11 +24235,11 @@
         </is>
       </c>
       <c r="E793" s="3" t="n">
-        <v>52.63</v>
+        <v>52.65</v>
       </c>
       <c r="F793" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24371,12 +24371,12 @@
       </c>
       <c r="B798" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C798" s="2" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D798" s="2" t="inlineStr">
@@ -24385,11 +24385,11 @@
         </is>
       </c>
       <c r="E798" s="3" t="n">
-        <v>48.04</v>
+        <v>48.9</v>
       </c>
       <c r="F798" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="B799" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C799" s="2" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="D799" s="2" t="inlineStr">
@@ -24415,11 +24415,11 @@
         </is>
       </c>
       <c r="E799" s="3" t="n">
-        <v>47.99</v>
+        <v>48.04</v>
       </c>
       <c r="F799" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24431,12 +24431,12 @@
       </c>
       <c r="B800" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C800" s="2" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="D800" s="2" t="inlineStr">
@@ -24445,11 +24445,11 @@
         </is>
       </c>
       <c r="E800" s="3" t="n">
-        <v>47.23</v>
+        <v>47.99</v>
       </c>
       <c r="F800" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24461,12 +24461,12 @@
       </c>
       <c r="B801" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C801" s="2" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="D801" s="2" t="inlineStr">
@@ -24475,11 +24475,11 @@
         </is>
       </c>
       <c r="E801" s="3" t="n">
-        <v>46.92</v>
+        <v>47.23</v>
       </c>
       <c r="F801" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24491,12 +24491,12 @@
       </c>
       <c r="B802" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C802" s="2" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="D802" s="2" t="inlineStr">
@@ -24505,11 +24505,11 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>46.8</v>
+        <v>46.95</v>
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24521,12 +24521,12 @@
       </c>
       <c r="B803" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C803" s="2" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="D803" s="2" t="inlineStr">
@@ -24535,11 +24535,11 @@
         </is>
       </c>
       <c r="E803" s="3" t="n">
-        <v>46.4</v>
+        <v>46.86</v>
       </c>
       <c r="F803" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24551,12 +24551,12 @@
       </c>
       <c r="B804" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C804" s="2" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="D804" s="2" t="inlineStr">
@@ -24565,7 +24565,7 @@
         </is>
       </c>
       <c r="E804" s="3" t="n">
-        <v>45.71</v>
+        <v>46.4</v>
       </c>
       <c r="F804" s="2" t="inlineStr">
         <is>
@@ -24581,12 +24581,12 @@
       </c>
       <c r="B805" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C805" s="2" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="D805" s="2" t="inlineStr">
@@ -24595,11 +24595,11 @@
         </is>
       </c>
       <c r="E805" s="3" t="n">
-        <v>45.23</v>
+        <v>45.78</v>
       </c>
       <c r="F805" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24611,12 +24611,12 @@
       </c>
       <c r="B806" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C806" s="2" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="D806" s="2" t="inlineStr">
@@ -24625,11 +24625,11 @@
         </is>
       </c>
       <c r="E806" s="3" t="n">
-        <v>44.8</v>
+        <v>45.23</v>
       </c>
       <c r="F806" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24641,12 +24641,12 @@
       </c>
       <c r="B807" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C807" s="2" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="D807" s="2" t="inlineStr">
@@ -24655,11 +24655,11 @@
         </is>
       </c>
       <c r="E807" s="3" t="n">
-        <v>44.19</v>
+        <v>44.8</v>
       </c>
       <c r="F807" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24685,11 +24685,11 @@
         </is>
       </c>
       <c r="E808" s="3" t="n">
-        <v>43.24</v>
+        <v>44.77</v>
       </c>
       <c r="F808" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24701,12 +24701,12 @@
       </c>
       <c r="B809" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C809" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="D809" s="2" t="inlineStr">
@@ -24715,11 +24715,11 @@
         </is>
       </c>
       <c r="E809" s="3" t="n">
-        <v>39.77</v>
+        <v>44.19</v>
       </c>
       <c r="F809" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24745,11 +24745,11 @@
         </is>
       </c>
       <c r="E810" s="3" t="n">
-        <v>39.35</v>
+        <v>39.39</v>
       </c>
       <c r="F810" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24761,12 +24761,12 @@
       </c>
       <c r="B811" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C811" s="2" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="D811" s="2" t="inlineStr">
@@ -24775,11 +24775,11 @@
         </is>
       </c>
       <c r="E811" s="3" t="n">
-        <v>39.2</v>
+        <v>39.38</v>
       </c>
       <c r="F811" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24791,12 +24791,12 @@
       </c>
       <c r="B812" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C812" s="2" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="D812" s="2" t="inlineStr">
@@ -24805,11 +24805,11 @@
         </is>
       </c>
       <c r="E812" s="3" t="n">
-        <v>38.54</v>
+        <v>39.2</v>
       </c>
       <c r="F812" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24835,11 +24835,11 @@
         </is>
       </c>
       <c r="E813" s="3" t="n">
-        <v>37.83</v>
+        <v>37.94</v>
       </c>
       <c r="F813" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24941,12 +24941,12 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="D817" s="2" t="inlineStr">
@@ -24955,11 +24955,11 @@
         </is>
       </c>
       <c r="E817" s="3" t="n">
-        <v>36.31</v>
+        <v>36.32</v>
       </c>
       <c r="F817" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24971,12 +24971,12 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="D818" s="2" t="inlineStr">
@@ -24985,11 +24985,11 @@
         </is>
       </c>
       <c r="E818" s="3" t="n">
-        <v>36.16</v>
+        <v>36.31</v>
       </c>
       <c r="F818" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25255,11 +25255,11 @@
         </is>
       </c>
       <c r="E827" s="3" t="n">
-        <v>26.86</v>
+        <v>26.89</v>
       </c>
       <c r="F827" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -25271,25 +25271,25 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="D828" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E828" s="3" t="n">
-        <v>26.15</v>
+        <v>26.48</v>
       </c>
       <c r="F828" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -25301,25 +25301,25 @@
       </c>
       <c r="B829" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C829" s="2" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="D829" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E829" s="3" t="n">
-        <v>25.28</v>
+        <v>26.15</v>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25331,12 +25331,12 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="D830" s="2" t="inlineStr">
@@ -25345,11 +25345,11 @@
         </is>
       </c>
       <c r="E830" s="3" t="n">
-        <v>23.74</v>
+        <v>25.28</v>
       </c>
       <c r="F830" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -25361,12 +25361,12 @@
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C831" s="2" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="D831" s="2" t="inlineStr">
@@ -25375,11 +25375,11 @@
         </is>
       </c>
       <c r="E831" s="3" t="n">
-        <v>23.41</v>
+        <v>23.74</v>
       </c>
       <c r="F831" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25391,25 +25391,25 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="D832" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E832" s="3" t="n">
-        <v>23.16</v>
+        <v>23.19</v>
       </c>
       <c r="F832" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -25421,25 +25421,25 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="D833" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E833" s="3" t="n">
-        <v>22.88</v>
+        <v>23.17</v>
       </c>
       <c r="F833" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -25721,12 +25721,12 @@
       </c>
       <c r="B843" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C843" s="2" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D843" s="2" t="inlineStr">
@@ -25735,11 +25735,11 @@
         </is>
       </c>
       <c r="E843" s="3" t="n">
-        <v>19.52</v>
+        <v>19.53</v>
       </c>
       <c r="F843" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -25751,12 +25751,12 @@
       </c>
       <c r="B844" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C844" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="D844" s="2" t="inlineStr">
@@ -25765,11 +25765,11 @@
         </is>
       </c>
       <c r="E844" s="3" t="n">
-        <v>19.19</v>
+        <v>19.52</v>
       </c>
       <c r="F844" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -26125,11 +26125,11 @@
         </is>
       </c>
       <c r="E856" s="3" t="n">
-        <v>10.3</v>
+        <v>10.53</v>
       </c>
       <c r="F856" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -26171,12 +26171,12 @@
       </c>
       <c r="B858" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C858" s="2" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="D858" s="2" t="inlineStr">
@@ -26185,11 +26185,11 @@
         </is>
       </c>
       <c r="E858" s="3" t="n">
-        <v>9.27</v>
+        <v>9.48</v>
       </c>
       <c r="F858" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -26201,12 +26201,12 @@
       </c>
       <c r="B859" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C859" s="2" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="D859" s="2" t="inlineStr">
@@ -26215,7 +26215,7 @@
         </is>
       </c>
       <c r="E859" s="3" t="n">
-        <v>8.529999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="F859" s="2" t="inlineStr">
         <is>
@@ -26231,12 +26231,12 @@
       </c>
       <c r="B860" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413773R6G</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C860" s="2" t="inlineStr">
         <is>
-          <t>812807</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="D860" s="2" t="inlineStr">
@@ -26245,7 +26245,7 @@
         </is>
       </c>
       <c r="E860" s="3" t="n">
-        <v>7.91</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="F860" s="2" t="inlineStr">
         <is>
@@ -26261,12 +26261,12 @@
       </c>
       <c r="B861" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0541381584X</t>
+          <t>KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="C861" s="2" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>812807</t>
         </is>
       </c>
       <c r="D861" s="2" t="inlineStr">
@@ -26275,7 +26275,7 @@
         </is>
       </c>
       <c r="E861" s="3" t="n">
-        <v>7.74</v>
+        <v>7.91</v>
       </c>
       <c r="F861" s="2" t="inlineStr">
         <is>
@@ -26291,12 +26291,12 @@
       </c>
       <c r="B862" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M0541381584X</t>
         </is>
       </c>
       <c r="C862" s="2" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>812810</t>
         </is>
       </c>
       <c r="D862" s="2" t="inlineStr">
@@ -26305,7 +26305,7 @@
         </is>
       </c>
       <c r="E862" s="3" t="n">
-        <v>7.52</v>
+        <v>7.74</v>
       </c>
       <c r="F862" s="2" t="inlineStr">
         <is>
@@ -26321,12 +26321,12 @@
       </c>
       <c r="B863" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C863" s="2" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="D863" s="2" t="inlineStr">
@@ -26335,7 +26335,7 @@
         </is>
       </c>
       <c r="E863" s="3" t="n">
-        <v>5.53</v>
+        <v>7.52</v>
       </c>
       <c r="F863" s="2" t="inlineStr">
         <is>
@@ -26351,12 +26351,12 @@
       </c>
       <c r="B864" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C864" s="2" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="D864" s="2" t="inlineStr">
@@ -26365,11 +26365,11 @@
         </is>
       </c>
       <c r="E864" s="3" t="n">
-        <v>5.19</v>
+        <v>5.53</v>
       </c>
       <c r="F864" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26425,11 +26425,11 @@
         </is>
       </c>
       <c r="E866" s="3" t="n">
-        <v>4.26</v>
+        <v>4.33</v>
       </c>
       <c r="F866" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2324.48</v>
+        <v>2346.85</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -19795,11 +19795,11 @@
         </is>
       </c>
       <c r="E645" s="3" t="n">
-        <v>1964.07</v>
+        <v>2061.92</v>
       </c>
       <c r="F645" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -19885,11 +19885,11 @@
         </is>
       </c>
       <c r="E648" s="3" t="n">
-        <v>1055.27</v>
+        <v>1093.78</v>
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>1050.69</v>
+        <v>1093.04</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -19975,11 +19975,11 @@
         </is>
       </c>
       <c r="E651" s="3" t="n">
-        <v>798.91</v>
+        <v>861.49</v>
       </c>
       <c r="F651" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20035,11 +20035,11 @@
         </is>
       </c>
       <c r="E653" s="3" t="n">
-        <v>735.71</v>
+        <v>749.48</v>
       </c>
       <c r="F653" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20051,12 +20051,12 @@
       </c>
       <c r="B654" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00072391SZM</t>
+          <t>KIT4P000739124KF</t>
         </is>
       </c>
       <c r="C654" s="2" t="inlineStr">
         <is>
-          <t>814493</t>
+          <t>814640</t>
         </is>
       </c>
       <c r="D654" s="2" t="inlineStr">
@@ -20065,11 +20065,11 @@
         </is>
       </c>
       <c r="E654" s="3" t="n">
-        <v>638.87</v>
+        <v>709.16</v>
       </c>
       <c r="F654" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20095,11 +20095,11 @@
         </is>
       </c>
       <c r="E655" s="3" t="n">
-        <v>617.02</v>
+        <v>641.0700000000001</v>
       </c>
       <c r="F655" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20111,25 +20111,25 @@
       </c>
       <c r="B656" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="C656" s="2" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>814493</t>
         </is>
       </c>
       <c r="D656" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E656" s="3" t="n">
-        <v>613.48</v>
+        <v>638.87</v>
       </c>
       <c r="F656" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20141,25 +20141,25 @@
       </c>
       <c r="B657" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739124KF</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C657" s="2" t="inlineStr">
         <is>
-          <t>814640</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="D657" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>612.21</v>
+        <v>619.13</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20185,11 +20185,11 @@
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>599.25</v>
+        <v>603.91</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20215,11 +20215,11 @@
         </is>
       </c>
       <c r="E659" s="3" t="n">
-        <v>570.26</v>
+        <v>585.71</v>
       </c>
       <c r="F659" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20245,11 +20245,11 @@
         </is>
       </c>
       <c r="E660" s="3" t="n">
-        <v>557.17</v>
+        <v>557.1900000000001</v>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20275,11 +20275,11 @@
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>538.58</v>
+        <v>550.5</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20291,25 +20291,25 @@
       </c>
       <c r="B662" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C662" s="2" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="D662" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E662" s="3" t="n">
-        <v>513.88</v>
+        <v>519.36</v>
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20321,25 +20321,25 @@
       </c>
       <c r="B663" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066901JZZ</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C663" s="2" t="inlineStr">
         <is>
-          <t>812926</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="D663" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E663" s="3" t="n">
-        <v>500.46</v>
+        <v>513.88</v>
       </c>
       <c r="F663" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20351,25 +20351,25 @@
       </c>
       <c r="B664" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E664" s="3" t="n">
-        <v>500.18</v>
+        <v>503.81</v>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20381,25 +20381,25 @@
       </c>
       <c r="B665" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>812926</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E665" s="3" t="n">
-        <v>490.06</v>
+        <v>500.46</v>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20425,11 +20425,11 @@
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>485.08</v>
+        <v>497.8</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20471,12 +20471,12 @@
       </c>
       <c r="B668" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C668" s="2" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="D668" s="2" t="inlineStr">
@@ -20485,11 +20485,11 @@
         </is>
       </c>
       <c r="E668" s="3" t="n">
-        <v>466.53</v>
+        <v>468.68</v>
       </c>
       <c r="F668" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20501,25 +20501,25 @@
       </c>
       <c r="B669" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C669" s="2" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="D669" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E669" s="3" t="n">
-        <v>458.15</v>
+        <v>466.53</v>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20531,25 +20531,25 @@
       </c>
       <c r="B670" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C670" s="2" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="D670" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E670" s="3" t="n">
-        <v>428.3</v>
+        <v>464.89</v>
       </c>
       <c r="F670" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20575,11 +20575,11 @@
         </is>
       </c>
       <c r="E671" s="3" t="n">
-        <v>421.94</v>
+        <v>432.84</v>
       </c>
       <c r="F671" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20591,12 +20591,12 @@
       </c>
       <c r="B672" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065631CPZ</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C672" s="2" t="inlineStr">
         <is>
-          <t>812930</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="D672" s="2" t="inlineStr">
@@ -20605,11 +20605,11 @@
         </is>
       </c>
       <c r="E672" s="3" t="n">
-        <v>415.73</v>
+        <v>421.84</v>
       </c>
       <c r="F672" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20621,12 +20621,12 @@
       </c>
       <c r="B673" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084601T5F</t>
+          <t>KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="C673" s="2" t="inlineStr">
         <is>
-          <t>816335</t>
+          <t>812930</t>
         </is>
       </c>
       <c r="D673" s="2" t="inlineStr">
@@ -20635,7 +20635,7 @@
         </is>
       </c>
       <c r="E673" s="3" t="n">
-        <v>401.51</v>
+        <v>415.73</v>
       </c>
       <c r="F673" s="2" t="inlineStr">
         <is>
@@ -20651,12 +20651,12 @@
       </c>
       <c r="B674" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="C674" s="2" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>816335</t>
         </is>
       </c>
       <c r="D674" s="2" t="inlineStr">
@@ -20665,11 +20665,11 @@
         </is>
       </c>
       <c r="E674" s="3" t="n">
-        <v>397.95</v>
+        <v>401.51</v>
       </c>
       <c r="F674" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20695,11 +20695,11 @@
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>375.85</v>
+        <v>384.68</v>
       </c>
       <c r="F675" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20725,11 +20725,11 @@
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>331.37</v>
+        <v>333.44</v>
       </c>
       <c r="F676" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20741,25 +20741,25 @@
       </c>
       <c r="B677" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4P000668852J9</t>
         </is>
       </c>
       <c r="C677" s="2" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>812925</t>
         </is>
       </c>
       <c r="D677" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>324.42</v>
+        <v>326.98</v>
       </c>
       <c r="F677" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20785,11 +20785,11 @@
         </is>
       </c>
       <c r="E678" s="3" t="n">
-        <v>322.77</v>
+        <v>325.67</v>
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20801,12 +20801,12 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="D679" s="2" t="inlineStr">
@@ -20815,11 +20815,11 @@
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>318.87</v>
+        <v>325.06</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20831,25 +20831,25 @@
       </c>
       <c r="B680" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000668852J9</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C680" s="2" t="inlineStr">
         <is>
-          <t>812925</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="D680" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>314.95</v>
+        <v>318.87</v>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20861,25 +20861,25 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="D681" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E681" s="3" t="n">
-        <v>276.09</v>
+        <v>278.83</v>
       </c>
       <c r="F681" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20891,12 +20891,12 @@
       </c>
       <c r="B682" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563510TWC</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C682" s="2" t="inlineStr">
         <is>
-          <t>814433</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="D682" s="2" t="inlineStr">
@@ -20905,11 +20905,11 @@
         </is>
       </c>
       <c r="E682" s="3" t="n">
-        <v>267.37</v>
+        <v>276.09</v>
       </c>
       <c r="F682" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -20921,12 +20921,12 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="D683" s="2" t="inlineStr">
@@ -20935,11 +20935,11 @@
         </is>
       </c>
       <c r="E683" s="3" t="n">
-        <v>266.36</v>
+        <v>267.37</v>
       </c>
       <c r="F683" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20951,12 +20951,12 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="D684" s="2" t="inlineStr">
@@ -20965,11 +20965,11 @@
         </is>
       </c>
       <c r="E684" s="3" t="n">
-        <v>257.45</v>
+        <v>267.28</v>
       </c>
       <c r="F684" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20981,25 +20981,25 @@
       </c>
       <c r="B685" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C685" s="2" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="D685" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E685" s="3" t="n">
-        <v>253.99</v>
+        <v>258.3</v>
       </c>
       <c r="F685" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21055,11 +21055,11 @@
         </is>
       </c>
       <c r="E687" s="3" t="n">
-        <v>243.79</v>
+        <v>245.96</v>
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21115,11 +21115,11 @@
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>228.86</v>
+        <v>232.07</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21145,11 +21145,11 @@
         </is>
       </c>
       <c r="E690" s="3" t="n">
-        <v>215.89</v>
+        <v>226.02</v>
       </c>
       <c r="F690" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21175,11 +21175,11 @@
         </is>
       </c>
       <c r="E691" s="3" t="n">
-        <v>214.73</v>
+        <v>218.69</v>
       </c>
       <c r="F691" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21191,25 +21191,25 @@
       </c>
       <c r="B692" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C692" s="2" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="D692" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E692" s="3" t="n">
-        <v>210.11</v>
+        <v>216.72</v>
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21221,25 +21221,25 @@
       </c>
       <c r="B693" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C693" s="2" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="D693" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E693" s="3" t="n">
-        <v>209.97</v>
+        <v>213.58</v>
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21265,11 +21265,11 @@
         </is>
       </c>
       <c r="E694" s="3" t="n">
-        <v>202.21</v>
+        <v>205.1</v>
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>194.62</v>
+        <v>203.19</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21325,11 +21325,11 @@
         </is>
       </c>
       <c r="E696" s="3" t="n">
-        <v>191.02</v>
+        <v>192.33</v>
       </c>
       <c r="F696" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21341,12 +21341,12 @@
       </c>
       <c r="B697" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C697" s="2" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="D697" s="2" t="inlineStr">
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>180.6</v>
+        <v>188.25</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21371,12 +21371,12 @@
       </c>
       <c r="B698" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C698" s="2" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="D698" s="2" t="inlineStr">
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="E698" s="3" t="n">
-        <v>180.46</v>
+        <v>184.91</v>
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21401,12 +21401,12 @@
       </c>
       <c r="B699" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C699" s="2" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="D699" s="2" t="inlineStr">
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>177.05</v>
+        <v>183.84</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21445,11 +21445,11 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>169.84</v>
+        <v>177.74</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21461,12 +21461,12 @@
       </c>
       <c r="B701" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C701" s="2" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="D701" s="2" t="inlineStr">
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>161.48</v>
+        <v>169.8</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21491,12 +21491,12 @@
       </c>
       <c r="B702" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C702" s="2" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="D702" s="2" t="inlineStr">
@@ -21505,11 +21505,11 @@
         </is>
       </c>
       <c r="E702" s="3" t="n">
-        <v>158.82</v>
+        <v>167.07</v>
       </c>
       <c r="F702" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21521,12 +21521,12 @@
       </c>
       <c r="B703" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C703" s="2" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="D703" s="2" t="inlineStr">
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>157.25</v>
+        <v>159.34</v>
       </c>
       <c r="F703" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21551,12 +21551,12 @@
       </c>
       <c r="B704" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C704" s="2" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="D704" s="2" t="inlineStr">
@@ -21565,11 +21565,11 @@
         </is>
       </c>
       <c r="E704" s="3" t="n">
-        <v>157.01</v>
+        <v>158.82</v>
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21581,12 +21581,12 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="D705" s="2" t="inlineStr">
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>151.89</v>
+        <v>158.47</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21655,11 +21655,11 @@
         </is>
       </c>
       <c r="E707" s="3" t="n">
-        <v>145.07</v>
+        <v>146.93</v>
       </c>
       <c r="F707" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21685,11 +21685,11 @@
         </is>
       </c>
       <c r="E708" s="3" t="n">
-        <v>139.81</v>
+        <v>145.98</v>
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21701,12 +21701,12 @@
       </c>
       <c r="B709" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C709" s="2" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="D709" s="2" t="inlineStr">
@@ -21715,11 +21715,11 @@
         </is>
       </c>
       <c r="E709" s="3" t="n">
-        <v>134.82</v>
+        <v>138.7</v>
       </c>
       <c r="F709" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21731,12 +21731,12 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="D710" s="2" t="inlineStr">
@@ -21745,11 +21745,11 @@
         </is>
       </c>
       <c r="E710" s="3" t="n">
-        <v>133.81</v>
+        <v>135.14</v>
       </c>
       <c r="F710" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21761,12 +21761,12 @@
       </c>
       <c r="B711" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C711" s="2" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="D711" s="2" t="inlineStr">
@@ -21775,11 +21775,11 @@
         </is>
       </c>
       <c r="E711" s="3" t="n">
-        <v>132.39</v>
+        <v>133.81</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21791,12 +21791,12 @@
       </c>
       <c r="B712" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C712" s="2" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="D712" s="2" t="inlineStr">
@@ -21805,7 +21805,7 @@
         </is>
       </c>
       <c r="E712" s="3" t="n">
-        <v>131.31</v>
+        <v>132.39</v>
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
@@ -21821,12 +21821,12 @@
       </c>
       <c r="B713" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C713" s="2" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="D713" s="2" t="inlineStr">
@@ -21835,7 +21835,7 @@
         </is>
       </c>
       <c r="E713" s="3" t="n">
-        <v>131.04</v>
+        <v>131.31</v>
       </c>
       <c r="F713" s="2" t="inlineStr">
         <is>
@@ -21851,12 +21851,12 @@
       </c>
       <c r="B714" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C714" s="2" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="D714" s="2" t="inlineStr">
@@ -21865,11 +21865,11 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>130.95</v>
+        <v>131.04</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21895,11 +21895,11 @@
         </is>
       </c>
       <c r="E715" s="3" t="n">
-        <v>129.75</v>
+        <v>130.43</v>
       </c>
       <c r="F715" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21911,12 +21911,12 @@
       </c>
       <c r="B716" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C716" s="2" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="D716" s="2" t="inlineStr">
@@ -21925,11 +21925,11 @@
         </is>
       </c>
       <c r="E716" s="3" t="n">
-        <v>127.08</v>
+        <v>128.45</v>
       </c>
       <c r="F716" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B717" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C717" s="2" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="D717" s="2" t="inlineStr">
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>126.04</v>
+        <v>127.92</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -21971,12 +21971,12 @@
       </c>
       <c r="B718" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr">
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>126.03</v>
+        <v>127.04</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22001,12 +22001,12 @@
       </c>
       <c r="B719" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C719" s="2" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="D719" s="2" t="inlineStr">
@@ -22015,11 +22015,11 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>124.72</v>
+        <v>126.03</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22031,12 +22031,12 @@
       </c>
       <c r="B720" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C720" s="2" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="D720" s="2" t="inlineStr">
@@ -22045,11 +22045,11 @@
         </is>
       </c>
       <c r="E720" s="3" t="n">
-        <v>119.92</v>
+        <v>122.95</v>
       </c>
       <c r="F720" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22061,12 +22061,12 @@
       </c>
       <c r="B721" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C721" s="2" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="D721" s="2" t="inlineStr">
@@ -22075,11 +22075,11 @@
         </is>
       </c>
       <c r="E721" s="3" t="n">
-        <v>119.22</v>
+        <v>119.92</v>
       </c>
       <c r="F721" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22135,11 +22135,11 @@
         </is>
       </c>
       <c r="E723" s="3" t="n">
-        <v>116.59</v>
+        <v>117.36</v>
       </c>
       <c r="F723" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22151,12 +22151,12 @@
       </c>
       <c r="B724" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C724" s="2" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D724" s="2" t="inlineStr">
@@ -22165,11 +22165,11 @@
         </is>
       </c>
       <c r="E724" s="3" t="n">
-        <v>114.07</v>
+        <v>115.96</v>
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22181,12 +22181,12 @@
       </c>
       <c r="B725" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C725" s="2" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="D725" s="2" t="inlineStr">
@@ -22195,11 +22195,11 @@
         </is>
       </c>
       <c r="E725" s="3" t="n">
-        <v>113.25</v>
+        <v>114.07</v>
       </c>
       <c r="F725" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22211,12 +22211,12 @@
       </c>
       <c r="B726" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C726" s="2" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="D726" s="2" t="inlineStr">
@@ -22225,11 +22225,11 @@
         </is>
       </c>
       <c r="E726" s="3" t="n">
-        <v>110.73</v>
+        <v>113.25</v>
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22241,12 +22241,12 @@
       </c>
       <c r="B727" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C727" s="2" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="D727" s="2" t="inlineStr">
@@ -22255,11 +22255,11 @@
         </is>
       </c>
       <c r="E727" s="3" t="n">
-        <v>108.57</v>
+        <v>110.73</v>
       </c>
       <c r="F727" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22271,12 +22271,12 @@
       </c>
       <c r="B728" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C728" s="2" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D728" s="2" t="inlineStr">
@@ -22285,11 +22285,11 @@
         </is>
       </c>
       <c r="E728" s="3" t="n">
-        <v>108.23</v>
+        <v>110.11</v>
       </c>
       <c r="F728" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22301,12 +22301,12 @@
       </c>
       <c r="B729" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C729" s="2" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="D729" s="2" t="inlineStr">
@@ -22315,11 +22315,11 @@
         </is>
       </c>
       <c r="E729" s="3" t="n">
-        <v>104.72</v>
+        <v>109.95</v>
       </c>
       <c r="F729" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22331,12 +22331,12 @@
       </c>
       <c r="B730" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C730" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="D730" s="2" t="inlineStr">
@@ -22345,11 +22345,11 @@
         </is>
       </c>
       <c r="E730" s="3" t="n">
-        <v>104.18</v>
+        <v>109.58</v>
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22361,12 +22361,12 @@
       </c>
       <c r="B731" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="D731" s="2" t="inlineStr">
@@ -22375,11 +22375,11 @@
         </is>
       </c>
       <c r="E731" s="3" t="n">
-        <v>104.17</v>
+        <v>109.05</v>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22391,12 +22391,12 @@
       </c>
       <c r="B732" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="D732" s="2" t="inlineStr">
@@ -22405,11 +22405,11 @@
         </is>
       </c>
       <c r="E732" s="3" t="n">
-        <v>103.72</v>
+        <v>108.48</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22421,12 +22421,12 @@
       </c>
       <c r="B733" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D733" s="2" t="inlineStr">
@@ -22435,11 +22435,11 @@
         </is>
       </c>
       <c r="E733" s="3" t="n">
-        <v>101.35</v>
+        <v>107.44</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22451,12 +22451,12 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
@@ -22465,11 +22465,11 @@
         </is>
       </c>
       <c r="E734" s="3" t="n">
-        <v>100.93</v>
+        <v>105.73</v>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22481,12 +22481,12 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
@@ -22495,11 +22495,11 @@
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>104.76</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22511,12 +22511,12 @@
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
@@ -22525,11 +22525,11 @@
         </is>
       </c>
       <c r="E736" s="3" t="n">
-        <v>99.78</v>
+        <v>103.72</v>
       </c>
       <c r="F736" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22541,12 +22541,12 @@
       </c>
       <c r="B737" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="D737" s="2" t="inlineStr">
@@ -22555,11 +22555,11 @@
         </is>
       </c>
       <c r="E737" s="3" t="n">
-        <v>99.70999999999999</v>
+        <v>101.69</v>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22571,12 +22571,12 @@
       </c>
       <c r="B738" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="D738" s="2" t="inlineStr">
@@ -22585,11 +22585,11 @@
         </is>
       </c>
       <c r="E738" s="3" t="n">
-        <v>98.47</v>
+        <v>100.93</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22601,12 +22601,12 @@
       </c>
       <c r="B739" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C739" s="2" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="D739" s="2" t="inlineStr">
@@ -22615,7 +22615,7 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>97.44</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
@@ -22631,12 +22631,12 @@
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
@@ -22645,11 +22645,11 @@
         </is>
       </c>
       <c r="E740" s="3" t="n">
-        <v>95.12</v>
+        <v>97.44</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22661,12 +22661,12 @@
       </c>
       <c r="B741" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="D741" s="2" t="inlineStr">
@@ -22675,11 +22675,11 @@
         </is>
       </c>
       <c r="E741" s="3" t="n">
-        <v>93.83</v>
+        <v>95.92</v>
       </c>
       <c r="F741" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22691,12 +22691,12 @@
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>92.22</v>
+        <v>93.83</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22721,12 +22721,12 @@
       </c>
       <c r="B743" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C743" s="2" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="D743" s="2" t="inlineStr">
@@ -22735,11 +22735,11 @@
         </is>
       </c>
       <c r="E743" s="3" t="n">
-        <v>91.16</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>90.86</v>
+        <v>92.03</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22781,12 +22781,12 @@
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr">
@@ -22795,11 +22795,11 @@
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>89.79000000000001</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22811,21 +22811,21 @@
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E746" s="3" t="n">
-        <v>89.48999999999999</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
@@ -22841,25 +22841,25 @@
       </c>
       <c r="B747" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C747" s="2" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="D747" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E747" s="3" t="n">
-        <v>88.27</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F747" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22871,12 +22871,12 @@
       </c>
       <c r="B748" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C748" s="2" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="D748" s="2" t="inlineStr">
@@ -22885,11 +22885,11 @@
         </is>
       </c>
       <c r="E748" s="3" t="n">
-        <v>87.73</v>
+        <v>88.55</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22901,12 +22901,12 @@
       </c>
       <c r="B749" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C749" s="2" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="D749" s="2" t="inlineStr">
@@ -22915,7 +22915,7 @@
         </is>
       </c>
       <c r="E749" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>87.73</v>
       </c>
       <c r="F749" s="2" t="inlineStr">
         <is>
@@ -22931,12 +22931,12 @@
       </c>
       <c r="B750" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C750" s="2" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="D750" s="2" t="inlineStr">
@@ -22945,11 +22945,11 @@
         </is>
       </c>
       <c r="E750" s="3" t="n">
-        <v>85.54000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F750" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22961,12 +22961,12 @@
       </c>
       <c r="B751" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C751" s="2" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="D751" s="2" t="inlineStr">
@@ -22975,11 +22975,11 @@
         </is>
       </c>
       <c r="E751" s="3" t="n">
-        <v>82.69</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="F751" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -22991,12 +22991,12 @@
       </c>
       <c r="B752" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C752" s="2" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D752" s="2" t="inlineStr">
@@ -23005,11 +23005,11 @@
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>82.18000000000001</v>
+        <v>84.67</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23021,12 +23021,12 @@
       </c>
       <c r="B753" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C753" s="2" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="D753" s="2" t="inlineStr">
@@ -23035,11 +23035,11 @@
         </is>
       </c>
       <c r="E753" s="3" t="n">
-        <v>81.73</v>
+        <v>84.61</v>
       </c>
       <c r="F753" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23051,12 +23051,12 @@
       </c>
       <c r="B754" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C754" s="2" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="D754" s="2" t="inlineStr">
@@ -23065,11 +23065,11 @@
         </is>
       </c>
       <c r="E754" s="3" t="n">
-        <v>81.63</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F754" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23081,12 +23081,12 @@
       </c>
       <c r="B755" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C755" s="2" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="D755" s="2" t="inlineStr">
@@ -23095,11 +23095,11 @@
         </is>
       </c>
       <c r="E755" s="3" t="n">
-        <v>79.44</v>
+        <v>81.73</v>
       </c>
       <c r="F755" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23125,11 +23125,11 @@
         </is>
       </c>
       <c r="E756" s="3" t="n">
-        <v>78.22</v>
+        <v>80.38</v>
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23141,12 +23141,12 @@
       </c>
       <c r="B757" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C757" s="2" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="D757" s="2" t="inlineStr">
@@ -23155,11 +23155,11 @@
         </is>
       </c>
       <c r="E757" s="3" t="n">
-        <v>75.65000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="F757" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23171,12 +23171,12 @@
       </c>
       <c r="B758" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="C758" s="2" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="D758" s="2" t="inlineStr">
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>74.76000000000001</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23201,21 +23201,21 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="D759" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E759" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
@@ -23231,25 +23231,25 @@
       </c>
       <c r="B760" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C760" s="2" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="D760" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>73.48999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23261,12 +23261,12 @@
       </c>
       <c r="B761" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C761" s="2" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="D761" s="2" t="inlineStr">
@@ -23275,11 +23275,11 @@
         </is>
       </c>
       <c r="E761" s="3" t="n">
-        <v>71.38</v>
+        <v>73.52</v>
       </c>
       <c r="F761" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23291,12 +23291,12 @@
       </c>
       <c r="B762" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C762" s="2" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D762" s="2" t="inlineStr">
@@ -23305,11 +23305,11 @@
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>70.48</v>
+        <v>72.11</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23321,12 +23321,12 @@
       </c>
       <c r="B763" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C763" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="D763" s="2" t="inlineStr">
@@ -23335,11 +23335,11 @@
         </is>
       </c>
       <c r="E763" s="3" t="n">
-        <v>69.70999999999999</v>
+        <v>71.38</v>
       </c>
       <c r="F763" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>69.43000000000001</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23381,12 +23381,12 @@
       </c>
       <c r="B765" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C765" s="2" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="D765" s="2" t="inlineStr">
@@ -23395,11 +23395,11 @@
         </is>
       </c>
       <c r="E765" s="3" t="n">
-        <v>68.5</v>
+        <v>70.58</v>
       </c>
       <c r="F765" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23411,12 +23411,12 @@
       </c>
       <c r="B766" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C766" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="D766" s="2" t="inlineStr">
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>67.76000000000001</v>
+        <v>70.48</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23441,12 +23441,12 @@
       </c>
       <c r="B767" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C767" s="2" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="D767" s="2" t="inlineStr">
@@ -23455,11 +23455,11 @@
         </is>
       </c>
       <c r="E767" s="3" t="n">
-        <v>66.78</v>
+        <v>69.73</v>
       </c>
       <c r="F767" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23471,12 +23471,12 @@
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="D768" s="2" t="inlineStr">
@@ -23485,11 +23485,11 @@
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>66.62</v>
+        <v>68.98</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23501,12 @@
       </c>
       <c r="B769" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C769" s="2" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="D769" s="2" t="inlineStr">
@@ -23515,11 +23515,11 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>66.38</v>
+        <v>68.5</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23531,12 +23531,12 @@
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
@@ -23545,11 +23545,11 @@
         </is>
       </c>
       <c r="E770" s="3" t="n">
-        <v>66.12</v>
+        <v>68.19</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23561,12 +23561,12 @@
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
@@ -23575,11 +23575,11 @@
         </is>
       </c>
       <c r="E771" s="3" t="n">
-        <v>65.75</v>
+        <v>67.14</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23591,12 +23591,12 @@
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -23605,11 +23605,11 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>64.95</v>
+        <v>66.62</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23621,12 +23621,12 @@
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D773" s="2" t="inlineStr">
@@ -23635,11 +23635,11 @@
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>63.6</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23651,12 +23651,12 @@
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr">
@@ -23665,11 +23665,11 @@
         </is>
       </c>
       <c r="E774" s="3" t="n">
-        <v>63.45</v>
+        <v>65.72</v>
       </c>
       <c r="F774" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23681,12 +23681,12 @@
       </c>
       <c r="B775" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C775" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D775" s="2" t="inlineStr">
@@ -23695,11 +23695,11 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>63.05</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23711,12 +23711,12 @@
       </c>
       <c r="B776" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C776" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="D776" s="2" t="inlineStr">
@@ -23725,11 +23725,11 @@
         </is>
       </c>
       <c r="E776" s="3" t="n">
-        <v>62.12</v>
+        <v>64.52</v>
       </c>
       <c r="F776" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23741,12 +23741,12 @@
       </c>
       <c r="B777" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C777" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="D777" s="2" t="inlineStr">
@@ -23755,11 +23755,11 @@
         </is>
       </c>
       <c r="E777" s="3" t="n">
-        <v>62.12</v>
+        <v>63.83</v>
       </c>
       <c r="F777" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23771,12 +23771,12 @@
       </c>
       <c r="B778" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C778" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="D778" s="2" t="inlineStr">
@@ -23785,11 +23785,11 @@
         </is>
       </c>
       <c r="E778" s="3" t="n">
-        <v>61.83</v>
+        <v>63.6</v>
       </c>
       <c r="F778" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23801,12 +23801,12 @@
       </c>
       <c r="B779" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C779" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="D779" s="2" t="inlineStr">
@@ -23815,11 +23815,11 @@
         </is>
       </c>
       <c r="E779" s="3" t="n">
-        <v>61.6</v>
+        <v>63.5</v>
       </c>
       <c r="F779" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23831,12 +23831,12 @@
       </c>
       <c r="B780" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C780" s="2" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D780" s="2" t="inlineStr">
@@ -23845,11 +23845,11 @@
         </is>
       </c>
       <c r="E780" s="3" t="n">
-        <v>60.82</v>
+        <v>63.31</v>
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23861,12 +23861,12 @@
       </c>
       <c r="B781" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C781" s="2" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="D781" s="2" t="inlineStr">
@@ -23875,11 +23875,11 @@
         </is>
       </c>
       <c r="E781" s="3" t="n">
-        <v>60.36</v>
+        <v>62.6</v>
       </c>
       <c r="F781" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23891,12 +23891,12 @@
       </c>
       <c r="B782" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C782" s="2" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="D782" s="2" t="inlineStr">
@@ -23905,11 +23905,11 @@
         </is>
       </c>
       <c r="E782" s="3" t="n">
-        <v>59.16</v>
+        <v>62.39</v>
       </c>
       <c r="F782" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23921,12 +23921,12 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D783" s="2" t="inlineStr">
@@ -23935,11 +23935,11 @@
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>58.53</v>
+        <v>61.96</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23951,12 +23951,12 @@
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
@@ -23965,11 +23965,11 @@
         </is>
       </c>
       <c r="E784" s="3" t="n">
-        <v>58.34</v>
+        <v>60.23</v>
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -23981,25 +23981,25 @@
       </c>
       <c r="B785" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C785" s="2" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="D785" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E785" s="3" t="n">
-        <v>57.22</v>
+        <v>59.98</v>
       </c>
       <c r="F785" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24011,12 +24011,12 @@
       </c>
       <c r="B786" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C786" s="2" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="D786" s="2" t="inlineStr">
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>56.5</v>
+        <v>59.72</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24041,12 +24041,12 @@
       </c>
       <c r="B787" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C787" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="D787" s="2" t="inlineStr">
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>55.92</v>
+        <v>59.61</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24071,12 +24071,12 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D788" s="2" t="inlineStr">
@@ -24085,11 +24085,11 @@
         </is>
       </c>
       <c r="E788" s="3" t="n">
-        <v>55.05</v>
+        <v>58.12</v>
       </c>
       <c r="F788" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24101,12 +24101,12 @@
       </c>
       <c r="B789" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C789" s="2" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="D789" s="2" t="inlineStr">
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>54.72</v>
+        <v>57.55</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24131,25 +24131,25 @@
       </c>
       <c r="B790" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C790" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="D790" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E790" s="3" t="n">
-        <v>54.13</v>
+        <v>57.22</v>
       </c>
       <c r="F790" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24161,12 +24161,12 @@
       </c>
       <c r="B791" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C791" s="2" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="D791" s="2" t="inlineStr">
@@ -24175,11 +24175,11 @@
         </is>
       </c>
       <c r="E791" s="3" t="n">
-        <v>53.95</v>
+        <v>56.56</v>
       </c>
       <c r="F791" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24191,12 +24191,12 @@
       </c>
       <c r="B792" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C792" s="2" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="D792" s="2" t="inlineStr">
@@ -24205,11 +24205,11 @@
         </is>
       </c>
       <c r="E792" s="3" t="n">
-        <v>53.26</v>
+        <v>56.5</v>
       </c>
       <c r="F792" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24221,12 +24221,12 @@
       </c>
       <c r="B793" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C793" s="2" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="D793" s="2" t="inlineStr">
@@ -24235,7 +24235,7 @@
         </is>
       </c>
       <c r="E793" s="3" t="n">
-        <v>52.65</v>
+        <v>54.72</v>
       </c>
       <c r="F793" s="2" t="inlineStr">
         <is>
@@ -24251,12 +24251,12 @@
       </c>
       <c r="B794" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C794" s="2" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="D794" s="2" t="inlineStr">
@@ -24265,7 +24265,7 @@
         </is>
       </c>
       <c r="E794" s="3" t="n">
-        <v>52.57</v>
+        <v>53.95</v>
       </c>
       <c r="F794" s="2" t="inlineStr">
         <is>
@@ -24281,12 +24281,12 @@
       </c>
       <c r="B795" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C795" s="2" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="D795" s="2" t="inlineStr">
@@ -24295,11 +24295,11 @@
         </is>
       </c>
       <c r="E795" s="3" t="n">
-        <v>52.42</v>
+        <v>53.85</v>
       </c>
       <c r="F795" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24311,12 +24311,12 @@
       </c>
       <c r="B796" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C796" s="2" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="D796" s="2" t="inlineStr">
@@ -24325,11 +24325,11 @@
         </is>
       </c>
       <c r="E796" s="3" t="n">
-        <v>50.13</v>
+        <v>52.57</v>
       </c>
       <c r="F796" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24355,11 +24355,11 @@
         </is>
       </c>
       <c r="E797" s="3" t="n">
-        <v>49.95</v>
+        <v>52.55</v>
       </c>
       <c r="F797" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24371,12 +24371,12 @@
       </c>
       <c r="B798" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C798" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="D798" s="2" t="inlineStr">
@@ -24385,11 +24385,11 @@
         </is>
       </c>
       <c r="E798" s="3" t="n">
-        <v>48.9</v>
+        <v>52.42</v>
       </c>
       <c r="F798" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="B799" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C799" s="2" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="D799" s="2" t="inlineStr">
@@ -24415,11 +24415,11 @@
         </is>
       </c>
       <c r="E799" s="3" t="n">
-        <v>48.04</v>
+        <v>50.13</v>
       </c>
       <c r="F799" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24431,12 +24431,12 @@
       </c>
       <c r="B800" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C800" s="2" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="D800" s="2" t="inlineStr">
@@ -24445,11 +24445,11 @@
         </is>
       </c>
       <c r="E800" s="3" t="n">
-        <v>47.99</v>
+        <v>49.54</v>
       </c>
       <c r="F800" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24461,12 +24461,12 @@
       </c>
       <c r="B801" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C801" s="2" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="D801" s="2" t="inlineStr">
@@ -24475,11 +24475,11 @@
         </is>
       </c>
       <c r="E801" s="3" t="n">
-        <v>47.23</v>
+        <v>48.43</v>
       </c>
       <c r="F801" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24491,12 +24491,12 @@
       </c>
       <c r="B802" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C802" s="2" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="D802" s="2" t="inlineStr">
@@ -24505,11 +24505,11 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>46.95</v>
+        <v>48.04</v>
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24521,12 +24521,12 @@
       </c>
       <c r="B803" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C803" s="2" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="D803" s="2" t="inlineStr">
@@ -24535,11 +24535,11 @@
         </is>
       </c>
       <c r="E803" s="3" t="n">
-        <v>46.86</v>
+        <v>47.99</v>
       </c>
       <c r="F803" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24551,12 +24551,12 @@
       </c>
       <c r="B804" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C804" s="2" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="D804" s="2" t="inlineStr">
@@ -24565,11 +24565,11 @@
         </is>
       </c>
       <c r="E804" s="3" t="n">
-        <v>46.4</v>
+        <v>47.23</v>
       </c>
       <c r="F804" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24595,11 +24595,11 @@
         </is>
       </c>
       <c r="E805" s="3" t="n">
-        <v>45.78</v>
+        <v>47.03</v>
       </c>
       <c r="F805" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24611,12 +24611,12 @@
       </c>
       <c r="B806" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="C806" s="2" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="D806" s="2" t="inlineStr">
@@ -24625,11 +24625,11 @@
         </is>
       </c>
       <c r="E806" s="3" t="n">
-        <v>45.23</v>
+        <v>46.93</v>
       </c>
       <c r="F806" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24641,12 +24641,12 @@
       </c>
       <c r="B807" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C807" s="2" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="D807" s="2" t="inlineStr">
@@ -24655,11 +24655,11 @@
         </is>
       </c>
       <c r="E807" s="3" t="n">
-        <v>44.8</v>
+        <v>46.43</v>
       </c>
       <c r="F807" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24671,12 +24671,12 @@
       </c>
       <c r="B808" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C808" s="2" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="D808" s="2" t="inlineStr">
@@ -24685,11 +24685,11 @@
         </is>
       </c>
       <c r="E808" s="3" t="n">
-        <v>44.77</v>
+        <v>46.4</v>
       </c>
       <c r="F808" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24701,12 +24701,12 @@
       </c>
       <c r="B809" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C809" s="2" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="D809" s="2" t="inlineStr">
@@ -24715,11 +24715,11 @@
         </is>
       </c>
       <c r="E809" s="3" t="n">
-        <v>44.19</v>
+        <v>44.8</v>
       </c>
       <c r="F809" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24731,12 +24731,12 @@
       </c>
       <c r="B810" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C810" s="2" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="D810" s="2" t="inlineStr">
@@ -24745,11 +24745,11 @@
         </is>
       </c>
       <c r="E810" s="3" t="n">
-        <v>39.39</v>
+        <v>44.19</v>
       </c>
       <c r="F810" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24761,12 +24761,12 @@
       </c>
       <c r="B811" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C811" s="2" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="D811" s="2" t="inlineStr">
@@ -24775,7 +24775,7 @@
         </is>
       </c>
       <c r="E811" s="3" t="n">
-        <v>39.38</v>
+        <v>39.39</v>
       </c>
       <c r="F811" s="2" t="inlineStr">
         <is>
@@ -24791,12 +24791,12 @@
       </c>
       <c r="B812" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C812" s="2" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="D812" s="2" t="inlineStr">
@@ -24805,11 +24805,11 @@
         </is>
       </c>
       <c r="E812" s="3" t="n">
-        <v>39.2</v>
+        <v>39.38</v>
       </c>
       <c r="F812" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24821,12 +24821,12 @@
       </c>
       <c r="B813" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C813" s="2" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="D813" s="2" t="inlineStr">
@@ -24835,11 +24835,11 @@
         </is>
       </c>
       <c r="E813" s="3" t="n">
-        <v>37.94</v>
+        <v>39.2</v>
       </c>
       <c r="F813" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24851,12 +24851,12 @@
       </c>
       <c r="B814" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C814" s="2" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="D814" s="2" t="inlineStr">
@@ -24865,11 +24865,11 @@
         </is>
       </c>
       <c r="E814" s="3" t="n">
-        <v>37.65</v>
+        <v>39</v>
       </c>
       <c r="F814" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24881,12 +24881,12 @@
       </c>
       <c r="B815" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C815" s="2" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="D815" s="2" t="inlineStr">
@@ -24895,11 +24895,11 @@
         </is>
       </c>
       <c r="E815" s="3" t="n">
-        <v>36.75</v>
+        <v>38.79</v>
       </c>
       <c r="F815" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24911,12 +24911,12 @@
       </c>
       <c r="B816" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C816" s="2" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="D816" s="2" t="inlineStr">
@@ -24925,11 +24925,11 @@
         </is>
       </c>
       <c r="E816" s="3" t="n">
-        <v>36.59</v>
+        <v>37.65</v>
       </c>
       <c r="F816" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24941,12 +24941,12 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="D817" s="2" t="inlineStr">
@@ -24955,11 +24955,11 @@
         </is>
       </c>
       <c r="E817" s="3" t="n">
-        <v>36.32</v>
+        <v>36.75</v>
       </c>
       <c r="F817" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24971,12 +24971,12 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="D818" s="2" t="inlineStr">
@@ -24985,11 +24985,11 @@
         </is>
       </c>
       <c r="E818" s="3" t="n">
-        <v>36.31</v>
+        <v>36.59</v>
       </c>
       <c r="F818" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -25001,12 +25001,12 @@
       </c>
       <c r="B819" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C819" s="2" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="D819" s="2" t="inlineStr">
@@ -25015,7 +25015,7 @@
         </is>
       </c>
       <c r="E819" s="3" t="n">
-        <v>34.1</v>
+        <v>36.31</v>
       </c>
       <c r="F819" s="2" t="inlineStr">
         <is>
@@ -25061,12 +25061,12 @@
       </c>
       <c r="B821" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C821" s="2" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="D821" s="2" t="inlineStr">
@@ -25075,11 +25075,11 @@
         </is>
       </c>
       <c r="E821" s="3" t="n">
-        <v>31.24</v>
+        <v>31.25</v>
       </c>
       <c r="F821" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -25091,12 +25091,12 @@
       </c>
       <c r="B822" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="C822" s="2" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="D822" s="2" t="inlineStr">
@@ -25105,11 +25105,11 @@
         </is>
       </c>
       <c r="E822" s="3" t="n">
-        <v>31.03</v>
+        <v>31.24</v>
       </c>
       <c r="F822" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25121,12 +25121,12 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="D823" s="2" t="inlineStr">
@@ -25135,11 +25135,11 @@
         </is>
       </c>
       <c r="E823" s="3" t="n">
-        <v>29.67</v>
+        <v>31.18</v>
       </c>
       <c r="F823" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -25151,12 +25151,12 @@
       </c>
       <c r="B824" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C824" s="2" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="D824" s="2" t="inlineStr">
@@ -25165,11 +25165,11 @@
         </is>
       </c>
       <c r="E824" s="3" t="n">
-        <v>29.27</v>
+        <v>29.67</v>
       </c>
       <c r="F824" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -25181,12 +25181,12 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="D825" s="2" t="inlineStr">
@@ -25195,7 +25195,7 @@
         </is>
       </c>
       <c r="E825" s="3" t="n">
-        <v>28.85</v>
+        <v>29.27</v>
       </c>
       <c r="F825" s="2" t="inlineStr">
         <is>
@@ -25211,12 +25211,12 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="D826" s="2" t="inlineStr">
@@ -25225,11 +25225,11 @@
         </is>
       </c>
       <c r="E826" s="3" t="n">
-        <v>27.39</v>
+        <v>28.98</v>
       </c>
       <c r="F826" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -25241,12 +25241,12 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="D827" s="2" t="inlineStr">
@@ -25255,11 +25255,11 @@
         </is>
       </c>
       <c r="E827" s="3" t="n">
-        <v>26.89</v>
+        <v>28.85</v>
       </c>
       <c r="F827" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25271,12 +25271,12 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="D828" s="2" t="inlineStr">
@@ -25285,11 +25285,11 @@
         </is>
       </c>
       <c r="E828" s="3" t="n">
-        <v>26.48</v>
+        <v>27.39</v>
       </c>
       <c r="F828" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -25301,25 +25301,25 @@
       </c>
       <c r="B829" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C829" s="2" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="D829" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E829" s="3" t="n">
-        <v>26.15</v>
+        <v>27.29</v>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -25331,25 +25331,25 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="D830" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E830" s="3" t="n">
-        <v>25.28</v>
+        <v>26.15</v>
       </c>
       <c r="F830" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25361,12 +25361,12 @@
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C831" s="2" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="D831" s="2" t="inlineStr">
@@ -25375,11 +25375,11 @@
         </is>
       </c>
       <c r="E831" s="3" t="n">
-        <v>23.74</v>
+        <v>25.84</v>
       </c>
       <c r="F831" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -25391,25 +25391,25 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="D832" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E832" s="3" t="n">
-        <v>23.19</v>
+        <v>24.66</v>
       </c>
       <c r="F832" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -25421,25 +25421,25 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="D833" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E833" s="3" t="n">
-        <v>23.17</v>
+        <v>24.1</v>
       </c>
       <c r="F833" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -25451,12 +25451,12 @@
       </c>
       <c r="B834" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C834" s="2" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="D834" s="2" t="inlineStr">
@@ -25465,7 +25465,7 @@
         </is>
       </c>
       <c r="E834" s="3" t="n">
-        <v>22.39</v>
+        <v>23.74</v>
       </c>
       <c r="F834" s="2" t="inlineStr">
         <is>
@@ -25481,12 +25481,12 @@
       </c>
       <c r="B835" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C835" s="2" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D835" s="2" t="inlineStr">
@@ -25495,11 +25495,11 @@
         </is>
       </c>
       <c r="E835" s="3" t="n">
-        <v>21.81</v>
+        <v>23.18</v>
       </c>
       <c r="F835" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -25511,12 +25511,12 @@
       </c>
       <c r="B836" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C836" s="2" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="D836" s="2" t="inlineStr">
@@ -25525,11 +25525,11 @@
         </is>
       </c>
       <c r="E836" s="3" t="n">
-        <v>21.7</v>
+        <v>22.72</v>
       </c>
       <c r="F836" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -25541,12 +25541,12 @@
       </c>
       <c r="B837" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C837" s="2" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="D837" s="2" t="inlineStr">
@@ -25555,7 +25555,7 @@
         </is>
       </c>
       <c r="E837" s="3" t="n">
-        <v>21.21</v>
+        <v>22.39</v>
       </c>
       <c r="F837" s="2" t="inlineStr">
         <is>
@@ -25571,12 +25571,12 @@
       </c>
       <c r="B838" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C838" s="2" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="D838" s="2" t="inlineStr">
@@ -25585,11 +25585,11 @@
         </is>
       </c>
       <c r="E838" s="3" t="n">
-        <v>21.17</v>
+        <v>21.7</v>
       </c>
       <c r="F838" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25601,12 +25601,12 @@
       </c>
       <c r="B839" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C839" s="2" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="D839" s="2" t="inlineStr">
@@ -25615,7 +25615,7 @@
         </is>
       </c>
       <c r="E839" s="3" t="n">
-        <v>20.98</v>
+        <v>21.21</v>
       </c>
       <c r="F839" s="2" t="inlineStr">
         <is>
@@ -25631,12 +25631,12 @@
       </c>
       <c r="B840" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C840" s="2" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="D840" s="2" t="inlineStr">
@@ -25645,7 +25645,7 @@
         </is>
       </c>
       <c r="E840" s="3" t="n">
-        <v>20.61</v>
+        <v>21.17</v>
       </c>
       <c r="F840" s="2" t="inlineStr">
         <is>
@@ -25661,12 +25661,12 @@
       </c>
       <c r="B841" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C841" s="2" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="D841" s="2" t="inlineStr">
@@ -25675,7 +25675,7 @@
         </is>
       </c>
       <c r="E841" s="3" t="n">
-        <v>20.12</v>
+        <v>20.98</v>
       </c>
       <c r="F841" s="2" t="inlineStr">
         <is>
@@ -25691,12 +25691,12 @@
       </c>
       <c r="B842" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C842" s="2" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="D842" s="2" t="inlineStr">
@@ -25705,11 +25705,11 @@
         </is>
       </c>
       <c r="E842" s="3" t="n">
-        <v>19.65</v>
+        <v>20.78</v>
       </c>
       <c r="F842" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -25721,12 +25721,12 @@
       </c>
       <c r="B843" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C843" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="D843" s="2" t="inlineStr">
@@ -25735,11 +25735,11 @@
         </is>
       </c>
       <c r="E843" s="3" t="n">
-        <v>19.53</v>
+        <v>20.61</v>
       </c>
       <c r="F843" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25751,12 +25751,12 @@
       </c>
       <c r="B844" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C844" s="2" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="D844" s="2" t="inlineStr">
@@ -25765,11 +25765,11 @@
         </is>
       </c>
       <c r="E844" s="3" t="n">
-        <v>19.52</v>
+        <v>20.12</v>
       </c>
       <c r="F844" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25781,12 +25781,12 @@
       </c>
       <c r="B845" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C845" s="2" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="D845" s="2" t="inlineStr">
@@ -25795,11 +25795,11 @@
         </is>
       </c>
       <c r="E845" s="3" t="n">
-        <v>17.76</v>
+        <v>19.65</v>
       </c>
       <c r="F845" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25811,12 +25811,12 @@
       </c>
       <c r="B846" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C846" s="2" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="D846" s="2" t="inlineStr">
@@ -25825,11 +25825,11 @@
         </is>
       </c>
       <c r="E846" s="3" t="n">
-        <v>17.57</v>
+        <v>17.76</v>
       </c>
       <c r="F846" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25841,12 +25841,12 @@
       </c>
       <c r="B847" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C847" s="2" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="D847" s="2" t="inlineStr">
@@ -25855,7 +25855,7 @@
         </is>
       </c>
       <c r="E847" s="3" t="n">
-        <v>17.49</v>
+        <v>17.57</v>
       </c>
       <c r="F847" s="2" t="inlineStr">
         <is>
@@ -25871,12 +25871,12 @@
       </c>
       <c r="B848" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C848" s="2" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="D848" s="2" t="inlineStr">
@@ -25885,7 +25885,7 @@
         </is>
       </c>
       <c r="E848" s="3" t="n">
-        <v>17.45</v>
+        <v>17.49</v>
       </c>
       <c r="F848" s="2" t="inlineStr">
         <is>
@@ -25901,12 +25901,12 @@
       </c>
       <c r="B849" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C849" s="2" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="D849" s="2" t="inlineStr">
@@ -25915,7 +25915,7 @@
         </is>
       </c>
       <c r="E849" s="3" t="n">
-        <v>15.77</v>
+        <v>17.45</v>
       </c>
       <c r="F849" s="2" t="inlineStr">
         <is>
@@ -25931,12 +25931,12 @@
       </c>
       <c r="B850" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C850" s="2" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="D850" s="2" t="inlineStr">
@@ -25945,11 +25945,11 @@
         </is>
       </c>
       <c r="E850" s="3" t="n">
-        <v>15.51</v>
+        <v>15.77</v>
       </c>
       <c r="F850" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25991,12 +25991,12 @@
       </c>
       <c r="B852" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="C852" s="2" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>816274</t>
         </is>
       </c>
       <c r="D852" s="2" t="inlineStr">
@@ -26005,11 +26005,11 @@
         </is>
       </c>
       <c r="E852" s="3" t="n">
-        <v>12.48</v>
+        <v>14.48</v>
       </c>
       <c r="F852" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -26021,12 +26021,12 @@
       </c>
       <c r="B853" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C853" s="2" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="D853" s="2" t="inlineStr">
@@ -26035,7 +26035,7 @@
         </is>
       </c>
       <c r="E853" s="3" t="n">
-        <v>12.19</v>
+        <v>12.48</v>
       </c>
       <c r="F853" s="2" t="inlineStr">
         <is>
@@ -26051,12 +26051,12 @@
       </c>
       <c r="B854" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413801QJB</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C854" s="2" t="inlineStr">
         <is>
-          <t>812824</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="D854" s="2" t="inlineStr">
@@ -26065,11 +26065,11 @@
         </is>
       </c>
       <c r="E854" s="3" t="n">
-        <v>11.47</v>
+        <v>12.19</v>
       </c>
       <c r="F854" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26081,12 +26081,12 @@
       </c>
       <c r="B855" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C855" s="2" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="D855" s="2" t="inlineStr">
@@ -26095,11 +26095,11 @@
         </is>
       </c>
       <c r="E855" s="3" t="n">
-        <v>10.75</v>
+        <v>12.09</v>
       </c>
       <c r="F855" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -26111,12 +26111,12 @@
       </c>
       <c r="B856" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799709G5Q</t>
+          <t>KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="C856" s="2" t="inlineStr">
         <is>
-          <t>816274</t>
+          <t>812824</t>
         </is>
       </c>
       <c r="D856" s="2" t="inlineStr">
@@ -26125,11 +26125,11 @@
         </is>
       </c>
       <c r="E856" s="3" t="n">
-        <v>10.53</v>
+        <v>11.47</v>
       </c>
       <c r="F856" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -26141,12 +26141,12 @@
       </c>
       <c r="B857" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C857" s="2" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="D857" s="2" t="inlineStr">
@@ -26155,7 +26155,7 @@
         </is>
       </c>
       <c r="E857" s="3" t="n">
-        <v>10.07</v>
+        <v>10.75</v>
       </c>
       <c r="F857" s="2" t="inlineStr">
         <is>
@@ -26171,12 +26171,12 @@
       </c>
       <c r="B858" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C858" s="2" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="D858" s="2" t="inlineStr">
@@ -26185,11 +26185,11 @@
         </is>
       </c>
       <c r="E858" s="3" t="n">
-        <v>9.48</v>
+        <v>10.07</v>
       </c>
       <c r="F858" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26275,11 +26275,11 @@
         </is>
       </c>
       <c r="E861" s="3" t="n">
-        <v>7.91</v>
+        <v>7.92</v>
       </c>
       <c r="F861" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -26351,12 +26351,12 @@
       </c>
       <c r="B864" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C864" s="2" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="D864" s="2" t="inlineStr">
@@ -26365,11 +26365,11 @@
         </is>
       </c>
       <c r="E864" s="3" t="n">
-        <v>5.53</v>
+        <v>6.01</v>
       </c>
       <c r="F864" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -26381,12 +26381,12 @@
       </c>
       <c r="B865" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413775N9M</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C865" s="2" t="inlineStr">
         <is>
-          <t>812818</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="D865" s="2" t="inlineStr">
@@ -26395,7 +26395,7 @@
         </is>
       </c>
       <c r="E865" s="3" t="n">
-        <v>4.49</v>
+        <v>5.53</v>
       </c>
       <c r="F865" s="2" t="inlineStr">
         <is>
@@ -26411,12 +26411,12 @@
       </c>
       <c r="B866" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="C866" s="2" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>812818</t>
         </is>
       </c>
       <c r="D866" s="2" t="inlineStr">
@@ -26425,11 +26425,11 @@
         </is>
       </c>
       <c r="E866" s="3" t="n">
-        <v>4.33</v>
+        <v>4.49</v>
       </c>
       <c r="F866" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2346.85</v>
+        <v>2375.61</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -19795,11 +19795,11 @@
         </is>
       </c>
       <c r="E645" s="3" t="n">
-        <v>2061.92</v>
+        <v>2112.23</v>
       </c>
       <c r="F645" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -19885,11 +19885,11 @@
         </is>
       </c>
       <c r="E648" s="3" t="n">
-        <v>1093.78</v>
+        <v>1115.52</v>
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>1093.04</v>
+        <v>1113.29</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -19975,11 +19975,11 @@
         </is>
       </c>
       <c r="E651" s="3" t="n">
-        <v>861.49</v>
+        <v>865.47</v>
       </c>
       <c r="F651" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20035,11 +20035,11 @@
         </is>
       </c>
       <c r="E653" s="3" t="n">
-        <v>749.48</v>
+        <v>771.34</v>
       </c>
       <c r="F653" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20065,11 +20065,11 @@
         </is>
       </c>
       <c r="E654" s="3" t="n">
-        <v>709.16</v>
+        <v>709.34</v>
       </c>
       <c r="F654" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20095,11 +20095,11 @@
         </is>
       </c>
       <c r="E655" s="3" t="n">
-        <v>641.0700000000001</v>
+        <v>643.21</v>
       </c>
       <c r="F655" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20155,11 +20155,11 @@
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>619.13</v>
+        <v>622.4299999999999</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20185,11 +20185,11 @@
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>603.91</v>
+        <v>605.09</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20215,11 +20215,11 @@
         </is>
       </c>
       <c r="E659" s="3" t="n">
-        <v>585.71</v>
+        <v>590.46</v>
       </c>
       <c r="F659" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20275,11 +20275,11 @@
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>550.5</v>
+        <v>554.42</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20305,11 +20305,11 @@
         </is>
       </c>
       <c r="E662" s="3" t="n">
-        <v>519.36</v>
+        <v>524.87</v>
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20321,12 +20321,12 @@
       </c>
       <c r="B663" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C663" s="2" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="D663" s="2" t="inlineStr">
@@ -20335,11 +20335,11 @@
         </is>
       </c>
       <c r="E663" s="3" t="n">
-        <v>513.88</v>
+        <v>520.25</v>
       </c>
       <c r="F663" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20351,12 +20351,12 @@
       </c>
       <c r="B664" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
@@ -20365,11 +20365,11 @@
         </is>
       </c>
       <c r="E664" s="3" t="n">
-        <v>503.81</v>
+        <v>513.88</v>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20381,12 +20381,12 @@
       </c>
       <c r="B665" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066901JZZ</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>812926</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
@@ -20395,11 +20395,11 @@
         </is>
       </c>
       <c r="E665" s="3" t="n">
-        <v>500.46</v>
+        <v>501.03</v>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20411,12 +20411,12 @@
       </c>
       <c r="B666" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>812926</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
@@ -20425,11 +20425,11 @@
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>497.8</v>
+        <v>500.46</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20441,12 +20441,12 @@
       </c>
       <c r="B667" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C667" s="2" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="D667" s="2" t="inlineStr">
@@ -20455,11 +20455,11 @@
         </is>
       </c>
       <c r="E667" s="3" t="n">
-        <v>480.85</v>
+        <v>498.41</v>
       </c>
       <c r="F667" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20471,12 +20471,12 @@
       </c>
       <c r="B668" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C668" s="2" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="D668" s="2" t="inlineStr">
@@ -20485,11 +20485,11 @@
         </is>
       </c>
       <c r="E668" s="3" t="n">
-        <v>468.68</v>
+        <v>480.85</v>
       </c>
       <c r="F668" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20501,25 +20501,25 @@
       </c>
       <c r="B669" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C669" s="2" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="D669" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E669" s="3" t="n">
-        <v>466.53</v>
+        <v>467.98</v>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20531,25 +20531,25 @@
       </c>
       <c r="B670" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C670" s="2" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="D670" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E670" s="3" t="n">
-        <v>464.89</v>
+        <v>466.53</v>
       </c>
       <c r="F670" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20575,11 +20575,11 @@
         </is>
       </c>
       <c r="E671" s="3" t="n">
-        <v>432.84</v>
+        <v>442.74</v>
       </c>
       <c r="F671" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20605,11 +20605,11 @@
         </is>
       </c>
       <c r="E672" s="3" t="n">
-        <v>421.84</v>
+        <v>430.79</v>
       </c>
       <c r="F672" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20711,25 +20711,25 @@
       </c>
       <c r="B676" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4P000668852J9</t>
         </is>
       </c>
       <c r="C676" s="2" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>812925</t>
         </is>
       </c>
       <c r="D676" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>333.44</v>
+        <v>333.65</v>
       </c>
       <c r="F676" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20741,21 +20741,21 @@
       </c>
       <c r="B677" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000668852J9</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C677" s="2" t="inlineStr">
         <is>
-          <t>812925</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="D677" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>326.98</v>
+        <v>333.44</v>
       </c>
       <c r="F677" s="2" t="inlineStr">
         <is>
@@ -20785,11 +20785,11 @@
         </is>
       </c>
       <c r="E678" s="3" t="n">
-        <v>325.67</v>
+        <v>333.25</v>
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20815,11 +20815,11 @@
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>325.06</v>
+        <v>325.08</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20875,11 +20875,11 @@
         </is>
       </c>
       <c r="E681" s="3" t="n">
-        <v>278.83</v>
+        <v>286.92</v>
       </c>
       <c r="F681" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -20995,11 +20995,11 @@
         </is>
       </c>
       <c r="E685" s="3" t="n">
-        <v>258.3</v>
+        <v>260.22</v>
       </c>
       <c r="F685" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -21071,25 +21071,25 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="D688" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E688" s="3" t="n">
-        <v>237.44</v>
+        <v>242.8</v>
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -21115,11 +21115,11 @@
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>232.07</v>
+        <v>237.76</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -21131,12 +21131,12 @@
       </c>
       <c r="B690" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C690" s="2" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="D690" s="2" t="inlineStr">
@@ -21145,11 +21145,11 @@
         </is>
       </c>
       <c r="E690" s="3" t="n">
-        <v>226.02</v>
+        <v>237.44</v>
       </c>
       <c r="F690" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21161,12 +21161,12 @@
       </c>
       <c r="B691" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="C691" s="2" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="D691" s="2" t="inlineStr">
@@ -21175,11 +21175,11 @@
         </is>
       </c>
       <c r="E691" s="3" t="n">
-        <v>218.69</v>
+        <v>227.36</v>
       </c>
       <c r="F691" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -21191,25 +21191,25 @@
       </c>
       <c r="B692" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C692" s="2" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="D692" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E692" s="3" t="n">
-        <v>216.72</v>
+        <v>218.75</v>
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -21235,11 +21235,11 @@
         </is>
       </c>
       <c r="E693" s="3" t="n">
-        <v>213.58</v>
+        <v>213.61</v>
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>203.19</v>
+        <v>204.84</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -21311,12 +21311,12 @@
       </c>
       <c r="B696" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C696" s="2" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="D696" s="2" t="inlineStr">
@@ -21325,11 +21325,11 @@
         </is>
       </c>
       <c r="E696" s="3" t="n">
-        <v>192.33</v>
+        <v>195.81</v>
       </c>
       <c r="F696" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -21341,12 +21341,12 @@
       </c>
       <c r="B697" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C697" s="2" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="D697" s="2" t="inlineStr">
@@ -21355,7 +21355,7 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>188.25</v>
+        <v>192.33</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
@@ -21445,11 +21445,11 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>177.74</v>
+        <v>181.16</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>169.8</v>
+        <v>170.8</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -21505,11 +21505,11 @@
         </is>
       </c>
       <c r="E702" s="3" t="n">
-        <v>167.07</v>
+        <v>167.53</v>
       </c>
       <c r="F702" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>159.34</v>
+        <v>165.04</v>
       </c>
       <c r="F703" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -21655,11 +21655,11 @@
         </is>
       </c>
       <c r="E707" s="3" t="n">
-        <v>146.93</v>
+        <v>149.11</v>
       </c>
       <c r="F707" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -21685,11 +21685,11 @@
         </is>
       </c>
       <c r="E708" s="3" t="n">
-        <v>145.98</v>
+        <v>146.69</v>
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -21715,11 +21715,11 @@
         </is>
       </c>
       <c r="E709" s="3" t="n">
-        <v>138.7</v>
+        <v>139.11</v>
       </c>
       <c r="F709" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -21775,11 +21775,11 @@
         </is>
       </c>
       <c r="E711" s="3" t="n">
-        <v>133.81</v>
+        <v>134.04</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -21821,12 +21821,12 @@
       </c>
       <c r="B713" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C713" s="2" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="D713" s="2" t="inlineStr">
@@ -21835,11 +21835,11 @@
         </is>
       </c>
       <c r="E713" s="3" t="n">
-        <v>131.31</v>
+        <v>132.37</v>
       </c>
       <c r="F713" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -21851,12 +21851,12 @@
       </c>
       <c r="B714" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C714" s="2" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="D714" s="2" t="inlineStr">
@@ -21865,7 +21865,7 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>131.04</v>
+        <v>131.31</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
@@ -21881,12 +21881,12 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="D715" s="2" t="inlineStr">
@@ -21895,11 +21895,11 @@
         </is>
       </c>
       <c r="E715" s="3" t="n">
-        <v>130.43</v>
+        <v>131.04</v>
       </c>
       <c r="F715" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21925,11 +21925,11 @@
         </is>
       </c>
       <c r="E716" s="3" t="n">
-        <v>128.45</v>
+        <v>129.78</v>
       </c>
       <c r="F716" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -22045,11 +22045,11 @@
         </is>
       </c>
       <c r="E720" s="3" t="n">
-        <v>122.95</v>
+        <v>123.17</v>
       </c>
       <c r="F720" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -22061,12 +22061,12 @@
       </c>
       <c r="B721" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C721" s="2" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D721" s="2" t="inlineStr">
@@ -22075,11 +22075,11 @@
         </is>
       </c>
       <c r="E721" s="3" t="n">
-        <v>119.92</v>
+        <v>121.6</v>
       </c>
       <c r="F721" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -22091,12 +22091,12 @@
       </c>
       <c r="B722" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C722" s="2" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="D722" s="2" t="inlineStr">
@@ -22105,11 +22105,11 @@
         </is>
       </c>
       <c r="E722" s="3" t="n">
-        <v>117.93</v>
+        <v>119.92</v>
       </c>
       <c r="F722" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22121,12 +22121,12 @@
       </c>
       <c r="B723" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C723" s="2" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="D723" s="2" t="inlineStr">
@@ -22135,11 +22135,11 @@
         </is>
       </c>
       <c r="E723" s="3" t="n">
-        <v>117.36</v>
+        <v>117.93</v>
       </c>
       <c r="F723" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22151,12 +22151,12 @@
       </c>
       <c r="B724" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C724" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="D724" s="2" t="inlineStr">
@@ -22165,11 +22165,11 @@
         </is>
       </c>
       <c r="E724" s="3" t="n">
-        <v>115.96</v>
+        <v>117.78</v>
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -22241,12 +22241,12 @@
       </c>
       <c r="B727" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C727" s="2" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D727" s="2" t="inlineStr">
@@ -22255,11 +22255,11 @@
         </is>
       </c>
       <c r="E727" s="3" t="n">
-        <v>110.73</v>
+        <v>111.18</v>
       </c>
       <c r="F727" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -22271,12 +22271,12 @@
       </c>
       <c r="B728" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C728" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="D728" s="2" t="inlineStr">
@@ -22285,11 +22285,11 @@
         </is>
       </c>
       <c r="E728" s="3" t="n">
-        <v>110.11</v>
+        <v>110.73</v>
       </c>
       <c r="F728" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22315,11 +22315,11 @@
         </is>
       </c>
       <c r="E729" s="3" t="n">
-        <v>109.95</v>
+        <v>109.97</v>
       </c>
       <c r="F729" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -22345,11 +22345,11 @@
         </is>
       </c>
       <c r="E730" s="3" t="n">
-        <v>109.58</v>
+        <v>109.92</v>
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -22435,11 +22435,11 @@
         </is>
       </c>
       <c r="E733" s="3" t="n">
-        <v>107.44</v>
+        <v>107.65</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -22495,11 +22495,11 @@
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>104.76</v>
+        <v>105.2</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -22691,12 +22691,12 @@
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>93.83</v>
+        <v>94.69</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -22721,12 +22721,12 @@
       </c>
       <c r="B743" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C743" s="2" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="D743" s="2" t="inlineStr">
@@ -22735,11 +22735,11 @@
         </is>
       </c>
       <c r="E743" s="3" t="n">
-        <v>93.81999999999999</v>
+        <v>93.95</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -22751,12 +22751,12 @@
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D744" s="2" t="inlineStr">
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>92.03</v>
+        <v>93.83</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22795,11 +22795,11 @@
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>91.31999999999999</v>
+        <v>92.67</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -22961,12 +22961,12 @@
       </c>
       <c r="B751" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C751" s="2" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D751" s="2" t="inlineStr">
@@ -22975,11 +22975,11 @@
         </is>
       </c>
       <c r="E751" s="3" t="n">
-        <v>85.54000000000001</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="F751" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -22991,12 +22991,12 @@
       </c>
       <c r="B752" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C752" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="D752" s="2" t="inlineStr">
@@ -23005,11 +23005,11 @@
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>84.67</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23035,11 +23035,11 @@
         </is>
       </c>
       <c r="E753" s="3" t="n">
-        <v>84.61</v>
+        <v>85.12</v>
       </c>
       <c r="F753" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -23125,11 +23125,11 @@
         </is>
       </c>
       <c r="E756" s="3" t="n">
-        <v>80.38</v>
+        <v>80.75</v>
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -23261,12 +23261,12 @@
       </c>
       <c r="B761" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C761" s="2" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D761" s="2" t="inlineStr">
@@ -23275,11 +23275,11 @@
         </is>
       </c>
       <c r="E761" s="3" t="n">
-        <v>73.52</v>
+        <v>73.56</v>
       </c>
       <c r="F761" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -23291,12 +23291,12 @@
       </c>
       <c r="B762" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C762" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="D762" s="2" t="inlineStr">
@@ -23305,7 +23305,7 @@
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>72.11</v>
+        <v>73.52</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
@@ -23485,11 +23485,11 @@
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>68.98</v>
+        <v>69.3</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23501,12 @@
       </c>
       <c r="B769" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C769" s="2" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D769" s="2" t="inlineStr">
@@ -23515,11 +23515,11 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>68.5</v>
+        <v>68.53</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -23531,12 +23531,12 @@
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
@@ -23545,11 +23545,11 @@
         </is>
       </c>
       <c r="E770" s="3" t="n">
-        <v>68.19</v>
+        <v>68.5</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23561,12 +23561,12 @@
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
@@ -23575,7 +23575,7 @@
         </is>
       </c>
       <c r="E771" s="3" t="n">
-        <v>67.14</v>
+        <v>68.19</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
@@ -23591,12 +23591,12 @@
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -23605,11 +23605,11 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>66.62</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -23621,12 +23621,12 @@
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="D773" s="2" t="inlineStr">
@@ -23635,11 +23635,11 @@
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>66.15000000000001</v>
+        <v>67.27</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -23651,12 +23651,12 @@
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr">
@@ -23665,11 +23665,11 @@
         </is>
       </c>
       <c r="E774" s="3" t="n">
-        <v>65.72</v>
+        <v>66.62</v>
       </c>
       <c r="F774" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -23681,12 +23681,12 @@
       </c>
       <c r="B775" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C775" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D775" s="2" t="inlineStr">
@@ -23695,11 +23695,11 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>65.70999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -23711,12 +23711,12 @@
       </c>
       <c r="B776" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C776" s="2" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D776" s="2" t="inlineStr">
@@ -23725,11 +23725,11 @@
         </is>
       </c>
       <c r="E776" s="3" t="n">
-        <v>64.52</v>
+        <v>66.17</v>
       </c>
       <c r="F776" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -23741,12 +23741,12 @@
       </c>
       <c r="B777" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C777" s="2" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D777" s="2" t="inlineStr">
@@ -23755,11 +23755,11 @@
         </is>
       </c>
       <c r="E777" s="3" t="n">
-        <v>63.83</v>
+        <v>65.92</v>
       </c>
       <c r="F777" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -23771,12 +23771,12 @@
       </c>
       <c r="B778" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C778" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="D778" s="2" t="inlineStr">
@@ -23785,11 +23785,11 @@
         </is>
       </c>
       <c r="E778" s="3" t="n">
-        <v>63.6</v>
+        <v>63.99</v>
       </c>
       <c r="F778" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -23801,12 +23801,12 @@
       </c>
       <c r="B779" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C779" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="D779" s="2" t="inlineStr">
@@ -23815,11 +23815,11 @@
         </is>
       </c>
       <c r="E779" s="3" t="n">
-        <v>63.5</v>
+        <v>63.85</v>
       </c>
       <c r="F779" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -23831,12 +23831,12 @@
       </c>
       <c r="B780" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C780" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="D780" s="2" t="inlineStr">
@@ -23845,11 +23845,11 @@
         </is>
       </c>
       <c r="E780" s="3" t="n">
-        <v>63.31</v>
+        <v>63.6</v>
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23861,12 +23861,12 @@
       </c>
       <c r="B781" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C781" s="2" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D781" s="2" t="inlineStr">
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="E781" s="3" t="n">
-        <v>62.6</v>
+        <v>63.31</v>
       </c>
       <c r="F781" s="2" t="inlineStr">
         <is>
@@ -23891,12 +23891,12 @@
       </c>
       <c r="B782" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C782" s="2" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="D782" s="2" t="inlineStr">
@@ -23905,11 +23905,11 @@
         </is>
       </c>
       <c r="E782" s="3" t="n">
-        <v>62.39</v>
+        <v>63.15</v>
       </c>
       <c r="F782" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -23921,12 +23921,12 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="D783" s="2" t="inlineStr">
@@ -23935,7 +23935,7 @@
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>61.96</v>
+        <v>62.6</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
@@ -23951,12 +23951,12 @@
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
@@ -23965,11 +23965,11 @@
         </is>
       </c>
       <c r="E784" s="3" t="n">
-        <v>60.23</v>
+        <v>62.41</v>
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -23981,12 +23981,12 @@
       </c>
       <c r="B785" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C785" s="2" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D785" s="2" t="inlineStr">
@@ -23995,7 +23995,7 @@
         </is>
       </c>
       <c r="E785" s="3" t="n">
-        <v>59.98</v>
+        <v>61.96</v>
       </c>
       <c r="F785" s="2" t="inlineStr">
         <is>
@@ -24011,12 +24011,12 @@
       </c>
       <c r="B786" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C786" s="2" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="D786" s="2" t="inlineStr">
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>59.72</v>
+        <v>59.82</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -24041,12 +24041,12 @@
       </c>
       <c r="B787" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C787" s="2" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="D787" s="2" t="inlineStr">
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>59.61</v>
+        <v>59.73</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -24071,12 +24071,12 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="D788" s="2" t="inlineStr">
@@ -24085,11 +24085,11 @@
         </is>
       </c>
       <c r="E788" s="3" t="n">
-        <v>58.12</v>
+        <v>59.58</v>
       </c>
       <c r="F788" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -24101,12 +24101,12 @@
       </c>
       <c r="B789" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C789" s="2" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D789" s="2" t="inlineStr">
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>57.55</v>
+        <v>58.13</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -24295,11 +24295,11 @@
         </is>
       </c>
       <c r="E795" s="3" t="n">
-        <v>53.85</v>
+        <v>53.86</v>
       </c>
       <c r="F795" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -24445,11 +24445,11 @@
         </is>
       </c>
       <c r="E800" s="3" t="n">
-        <v>49.54</v>
+        <v>49.61</v>
       </c>
       <c r="F800" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -24491,12 +24491,12 @@
       </c>
       <c r="B802" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C802" s="2" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="D802" s="2" t="inlineStr">
@@ -24505,11 +24505,11 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>48.04</v>
+        <v>48.15</v>
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -24521,12 +24521,12 @@
       </c>
       <c r="B803" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C803" s="2" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="D803" s="2" t="inlineStr">
@@ -24535,11 +24535,11 @@
         </is>
       </c>
       <c r="E803" s="3" t="n">
-        <v>47.99</v>
+        <v>48.04</v>
       </c>
       <c r="F803" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24551,12 +24551,12 @@
       </c>
       <c r="B804" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C804" s="2" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="D804" s="2" t="inlineStr">
@@ -24565,11 +24565,11 @@
         </is>
       </c>
       <c r="E804" s="3" t="n">
-        <v>47.23</v>
+        <v>47.99</v>
       </c>
       <c r="F804" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24581,12 +24581,12 @@
       </c>
       <c r="B805" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C805" s="2" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="D805" s="2" t="inlineStr">
@@ -24595,11 +24595,11 @@
         </is>
       </c>
       <c r="E805" s="3" t="n">
-        <v>47.03</v>
+        <v>47.23</v>
       </c>
       <c r="F805" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24611,12 +24611,12 @@
       </c>
       <c r="B806" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C806" s="2" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="D806" s="2" t="inlineStr">
@@ -24625,11 +24625,11 @@
         </is>
       </c>
       <c r="E806" s="3" t="n">
-        <v>46.93</v>
+        <v>47.07</v>
       </c>
       <c r="F806" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -24641,12 +24641,12 @@
       </c>
       <c r="B807" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="C807" s="2" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="D807" s="2" t="inlineStr">
@@ -24655,7 +24655,7 @@
         </is>
       </c>
       <c r="E807" s="3" t="n">
-        <v>46.43</v>
+        <v>46.93</v>
       </c>
       <c r="F807" s="2" t="inlineStr">
         <is>
@@ -24761,12 +24761,12 @@
       </c>
       <c r="B811" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C811" s="2" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="D811" s="2" t="inlineStr">
@@ -24775,11 +24775,11 @@
         </is>
       </c>
       <c r="E811" s="3" t="n">
-        <v>39.39</v>
+        <v>40.45</v>
       </c>
       <c r="F811" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -24791,12 +24791,12 @@
       </c>
       <c r="B812" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C812" s="2" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="D812" s="2" t="inlineStr">
@@ -24805,11 +24805,11 @@
         </is>
       </c>
       <c r="E812" s="3" t="n">
-        <v>39.38</v>
+        <v>40.15</v>
       </c>
       <c r="F812" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -24821,12 +24821,12 @@
       </c>
       <c r="B813" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C813" s="2" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="D813" s="2" t="inlineStr">
@@ -24835,11 +24835,11 @@
         </is>
       </c>
       <c r="E813" s="3" t="n">
-        <v>39.2</v>
+        <v>39.39</v>
       </c>
       <c r="F813" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24851,12 +24851,12 @@
       </c>
       <c r="B814" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C814" s="2" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="D814" s="2" t="inlineStr">
@@ -24865,11 +24865,11 @@
         </is>
       </c>
       <c r="E814" s="3" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="F814" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25075,11 +25075,11 @@
         </is>
       </c>
       <c r="E821" s="3" t="n">
-        <v>31.25</v>
+        <v>31.68</v>
       </c>
       <c r="F821" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -25225,11 +25225,11 @@
         </is>
       </c>
       <c r="E826" s="3" t="n">
-        <v>28.98</v>
+        <v>29.11</v>
       </c>
       <c r="F826" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -25271,12 +25271,12 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="D828" s="2" t="inlineStr">
@@ -25285,11 +25285,11 @@
         </is>
       </c>
       <c r="E828" s="3" t="n">
-        <v>27.39</v>
+        <v>28.04</v>
       </c>
       <c r="F828" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -25301,12 +25301,12 @@
       </c>
       <c r="B829" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C829" s="2" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="D829" s="2" t="inlineStr">
@@ -25315,11 +25315,11 @@
         </is>
       </c>
       <c r="E829" s="3" t="n">
-        <v>27.29</v>
+        <v>27.65</v>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -25331,25 +25331,25 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="D830" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E830" s="3" t="n">
-        <v>26.15</v>
+        <v>27.39</v>
       </c>
       <c r="F830" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -25375,11 +25375,11 @@
         </is>
       </c>
       <c r="E831" s="3" t="n">
-        <v>25.84</v>
+        <v>26.76</v>
       </c>
       <c r="F831" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -25391,12 +25391,12 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="D832" s="2" t="inlineStr">
@@ -25405,11 +25405,11 @@
         </is>
       </c>
       <c r="E832" s="3" t="n">
-        <v>24.66</v>
+        <v>26.15</v>
       </c>
       <c r="F832" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25421,12 +25421,12 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="D833" s="2" t="inlineStr">
@@ -25435,11 +25435,11 @@
         </is>
       </c>
       <c r="E833" s="3" t="n">
-        <v>24.1</v>
+        <v>25.52</v>
       </c>
       <c r="F833" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -25451,25 +25451,25 @@
       </c>
       <c r="B834" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C834" s="2" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="D834" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E834" s="3" t="n">
-        <v>23.74</v>
+        <v>24.95</v>
       </c>
       <c r="F834" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -25481,12 +25481,12 @@
       </c>
       <c r="B835" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C835" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="D835" s="2" t="inlineStr">
@@ -25495,11 +25495,11 @@
         </is>
       </c>
       <c r="E835" s="3" t="n">
-        <v>23.18</v>
+        <v>24.11</v>
       </c>
       <c r="F835" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -25511,12 +25511,12 @@
       </c>
       <c r="B836" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C836" s="2" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="D836" s="2" t="inlineStr">
@@ -25525,11 +25525,11 @@
         </is>
       </c>
       <c r="E836" s="3" t="n">
-        <v>22.72</v>
+        <v>23.74</v>
       </c>
       <c r="F836" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25541,12 +25541,12 @@
       </c>
       <c r="B837" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C837" s="2" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D837" s="2" t="inlineStr">
@@ -25555,11 +25555,11 @@
         </is>
       </c>
       <c r="E837" s="3" t="n">
-        <v>22.39</v>
+        <v>23.18</v>
       </c>
       <c r="F837" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -25571,12 +25571,12 @@
       </c>
       <c r="B838" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C838" s="2" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="D838" s="2" t="inlineStr">
@@ -25585,11 +25585,11 @@
         </is>
       </c>
       <c r="E838" s="3" t="n">
-        <v>21.7</v>
+        <v>22.39</v>
       </c>
       <c r="F838" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25601,12 +25601,12 @@
       </c>
       <c r="B839" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C839" s="2" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="D839" s="2" t="inlineStr">
@@ -25615,11 +25615,11 @@
         </is>
       </c>
       <c r="E839" s="3" t="n">
-        <v>21.21</v>
+        <v>21.7</v>
       </c>
       <c r="F839" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25631,12 +25631,12 @@
       </c>
       <c r="B840" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C840" s="2" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="D840" s="2" t="inlineStr">
@@ -25645,7 +25645,7 @@
         </is>
       </c>
       <c r="E840" s="3" t="n">
-        <v>21.17</v>
+        <v>21.21</v>
       </c>
       <c r="F840" s="2" t="inlineStr">
         <is>
@@ -25661,12 +25661,12 @@
       </c>
       <c r="B841" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C841" s="2" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="D841" s="2" t="inlineStr">
@@ -25675,7 +25675,7 @@
         </is>
       </c>
       <c r="E841" s="3" t="n">
-        <v>20.98</v>
+        <v>21.17</v>
       </c>
       <c r="F841" s="2" t="inlineStr">
         <is>
@@ -25691,12 +25691,12 @@
       </c>
       <c r="B842" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C842" s="2" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="D842" s="2" t="inlineStr">
@@ -25705,11 +25705,11 @@
         </is>
       </c>
       <c r="E842" s="3" t="n">
-        <v>20.78</v>
+        <v>20.98</v>
       </c>
       <c r="F842" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26005,11 +26005,11 @@
         </is>
       </c>
       <c r="E852" s="3" t="n">
-        <v>14.48</v>
+        <v>14.51</v>
       </c>
       <c r="F852" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -26021,12 +26021,12 @@
       </c>
       <c r="B853" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C853" s="2" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="D853" s="2" t="inlineStr">
@@ -26035,11 +26035,11 @@
         </is>
       </c>
       <c r="E853" s="3" t="n">
-        <v>12.48</v>
+        <v>13.55</v>
       </c>
       <c r="F853" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 09:49</t>
         </is>
       </c>
     </row>
@@ -26051,12 +26051,12 @@
       </c>
       <c r="B854" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C854" s="2" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="D854" s="2" t="inlineStr">
@@ -26065,7 +26065,7 @@
         </is>
       </c>
       <c r="E854" s="3" t="n">
-        <v>12.19</v>
+        <v>12.48</v>
       </c>
       <c r="F854" s="2" t="inlineStr">
         <is>
@@ -26081,12 +26081,12 @@
       </c>
       <c r="B855" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C855" s="2" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="D855" s="2" t="inlineStr">
@@ -26095,11 +26095,11 @@
         </is>
       </c>
       <c r="E855" s="3" t="n">
-        <v>12.09</v>
+        <v>12.19</v>
       </c>
       <c r="F855" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2375.61</v>
+        <v>2396.9</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -19795,11 +19795,11 @@
         </is>
       </c>
       <c r="E645" s="3" t="n">
-        <v>2112.23</v>
+        <v>2164.01</v>
       </c>
       <c r="F645" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -19885,11 +19885,11 @@
         </is>
       </c>
       <c r="E648" s="3" t="n">
-        <v>1115.52</v>
+        <v>1136</v>
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>1113.29</v>
+        <v>1133.17</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -19975,11 +19975,11 @@
         </is>
       </c>
       <c r="E651" s="3" t="n">
-        <v>865.47</v>
+        <v>893.13</v>
       </c>
       <c r="F651" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -19991,25 +19991,25 @@
       </c>
       <c r="B652" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084602TKW</t>
+          <t>KIT4M05413776H84</t>
         </is>
       </c>
       <c r="C652" s="2" t="inlineStr">
         <is>
-          <t>816225</t>
+          <t>810101</t>
         </is>
       </c>
       <c r="D652" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>771.66</v>
+        <v>778.3</v>
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20021,25 +20021,25 @@
       </c>
       <c r="B653" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413776H84</t>
+          <t>KIT4P00084602TKW</t>
         </is>
       </c>
       <c r="C653" s="2" t="inlineStr">
         <is>
-          <t>810101</t>
+          <t>816225</t>
         </is>
       </c>
       <c r="D653" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E653" s="3" t="n">
-        <v>771.34</v>
+        <v>771.66</v>
       </c>
       <c r="F653" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20065,11 +20065,11 @@
         </is>
       </c>
       <c r="E654" s="3" t="n">
-        <v>709.34</v>
+        <v>720.62</v>
       </c>
       <c r="F654" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20095,11 +20095,11 @@
         </is>
       </c>
       <c r="E655" s="3" t="n">
-        <v>643.21</v>
+        <v>653.72</v>
       </c>
       <c r="F655" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20155,11 +20155,11 @@
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>622.4299999999999</v>
+        <v>623.87</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20185,11 +20185,11 @@
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>605.09</v>
+        <v>606.34</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20215,11 +20215,11 @@
         </is>
       </c>
       <c r="E659" s="3" t="n">
-        <v>590.46</v>
+        <v>601.52</v>
       </c>
       <c r="F659" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20275,11 +20275,11 @@
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>554.42</v>
+        <v>556.35</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20305,11 +20305,11 @@
         </is>
       </c>
       <c r="E662" s="3" t="n">
-        <v>524.87</v>
+        <v>536.52</v>
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         </is>
       </c>
       <c r="E663" s="3" t="n">
-        <v>520.25</v>
+        <v>529.75</v>
       </c>
       <c r="F663" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20381,12 +20381,12 @@
       </c>
       <c r="B665" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
@@ -20395,11 +20395,11 @@
         </is>
       </c>
       <c r="E665" s="3" t="n">
-        <v>501.03</v>
+        <v>504.92</v>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20411,12 +20411,12 @@
       </c>
       <c r="B666" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066901JZZ</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>812926</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
@@ -20425,11 +20425,11 @@
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>500.46</v>
+        <v>504.42</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20441,12 +20441,12 @@
       </c>
       <c r="B667" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="C667" s="2" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>812926</t>
         </is>
       </c>
       <c r="D667" s="2" t="inlineStr">
@@ -20455,11 +20455,11 @@
         </is>
       </c>
       <c r="E667" s="3" t="n">
-        <v>498.41</v>
+        <v>500.46</v>
       </c>
       <c r="F667" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20515,11 +20515,11 @@
         </is>
       </c>
       <c r="E669" s="3" t="n">
-        <v>467.98</v>
+        <v>478.68</v>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20545,11 +20545,11 @@
         </is>
       </c>
       <c r="E670" s="3" t="n">
-        <v>466.53</v>
+        <v>470.18</v>
       </c>
       <c r="F670" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20561,25 +20561,25 @@
       </c>
       <c r="B671" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C671" s="2" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="D671" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E671" s="3" t="n">
-        <v>442.74</v>
+        <v>454.44</v>
       </c>
       <c r="F671" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20591,25 +20591,25 @@
       </c>
       <c r="B672" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C672" s="2" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="D672" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E672" s="3" t="n">
-        <v>430.79</v>
+        <v>444.95</v>
       </c>
       <c r="F672" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20695,11 +20695,11 @@
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>384.68</v>
+        <v>389.13</v>
       </c>
       <c r="F675" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20725,11 +20725,11 @@
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>333.65</v>
+        <v>338.74</v>
       </c>
       <c r="F676" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20755,11 +20755,11 @@
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>333.44</v>
+        <v>334</v>
       </c>
       <c r="F677" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20785,11 +20785,11 @@
         </is>
       </c>
       <c r="E678" s="3" t="n">
-        <v>333.25</v>
+        <v>333.84</v>
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20815,11 +20815,11 @@
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>325.08</v>
+        <v>326.29</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20875,11 +20875,11 @@
         </is>
       </c>
       <c r="E681" s="3" t="n">
-        <v>286.92</v>
+        <v>316.79</v>
       </c>
       <c r="F681" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20905,11 +20905,11 @@
         </is>
       </c>
       <c r="E682" s="3" t="n">
-        <v>276.09</v>
+        <v>276.4</v>
       </c>
       <c r="F682" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20921,12 +20921,12 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563510TWC</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
         <is>
-          <t>814433</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="D683" s="2" t="inlineStr">
@@ -20935,11 +20935,11 @@
         </is>
       </c>
       <c r="E683" s="3" t="n">
-        <v>267.37</v>
+        <v>269.58</v>
       </c>
       <c r="F683" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20965,11 +20965,11 @@
         </is>
       </c>
       <c r="E684" s="3" t="n">
-        <v>267.28</v>
+        <v>268.07</v>
       </c>
       <c r="F684" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -20981,12 +20981,12 @@
       </c>
       <c r="B685" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="C685" s="2" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="D685" s="2" t="inlineStr">
@@ -20995,11 +20995,11 @@
         </is>
       </c>
       <c r="E685" s="3" t="n">
-        <v>260.22</v>
+        <v>267.37</v>
       </c>
       <c r="F685" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21011,25 +21011,25 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="D686" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E686" s="3" t="n">
-        <v>246.96</v>
+        <v>254.42</v>
       </c>
       <c r="F686" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21041,12 +21041,12 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="D687" s="2" t="inlineStr">
@@ -21055,11 +21055,11 @@
         </is>
       </c>
       <c r="E687" s="3" t="n">
-        <v>245.96</v>
+        <v>246.96</v>
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21071,25 +21071,25 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="D688" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E688" s="3" t="n">
-        <v>242.8</v>
+        <v>246.73</v>
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21115,11 +21115,11 @@
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>237.76</v>
+        <v>239.89</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21175,11 +21175,11 @@
         </is>
       </c>
       <c r="E691" s="3" t="n">
-        <v>227.36</v>
+        <v>231.75</v>
       </c>
       <c r="F691" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21205,11 +21205,11 @@
         </is>
       </c>
       <c r="E692" s="3" t="n">
-        <v>218.75</v>
+        <v>219.46</v>
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21235,11 +21235,11 @@
         </is>
       </c>
       <c r="E693" s="3" t="n">
-        <v>213.61</v>
+        <v>215.14</v>
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21265,11 +21265,11 @@
         </is>
       </c>
       <c r="E694" s="3" t="n">
-        <v>205.1</v>
+        <v>207.69</v>
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>204.84</v>
+        <v>205.38</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21311,12 +21311,12 @@
       </c>
       <c r="B696" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C696" s="2" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="D696" s="2" t="inlineStr">
@@ -21325,11 +21325,11 @@
         </is>
       </c>
       <c r="E696" s="3" t="n">
-        <v>195.81</v>
+        <v>199.59</v>
       </c>
       <c r="F696" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21341,12 +21341,12 @@
       </c>
       <c r="B697" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C697" s="2" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="D697" s="2" t="inlineStr">
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>192.33</v>
+        <v>198.27</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="E698" s="3" t="n">
-        <v>184.91</v>
+        <v>187.5</v>
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21401,12 +21401,12 @@
       </c>
       <c r="B699" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C699" s="2" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="D699" s="2" t="inlineStr">
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>183.84</v>
+        <v>184.89</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21431,12 +21431,12 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="D700" s="2" t="inlineStr">
@@ -21445,11 +21445,11 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>181.16</v>
+        <v>184.14</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>170.8</v>
+        <v>177.59</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21505,11 +21505,11 @@
         </is>
       </c>
       <c r="E702" s="3" t="n">
-        <v>167.53</v>
+        <v>169.22</v>
       </c>
       <c r="F702" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>165.04</v>
+        <v>167.02</v>
       </c>
       <c r="F703" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21551,12 +21551,12 @@
       </c>
       <c r="B704" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C704" s="2" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="D704" s="2" t="inlineStr">
@@ -21565,11 +21565,11 @@
         </is>
       </c>
       <c r="E704" s="3" t="n">
-        <v>158.82</v>
+        <v>162.32</v>
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21581,12 +21581,12 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="D705" s="2" t="inlineStr">
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>158.47</v>
+        <v>158.82</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21655,11 +21655,11 @@
         </is>
       </c>
       <c r="E707" s="3" t="n">
-        <v>149.11</v>
+        <v>149.75</v>
       </c>
       <c r="F707" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21685,11 +21685,11 @@
         </is>
       </c>
       <c r="E708" s="3" t="n">
-        <v>146.69</v>
+        <v>148.01</v>
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21715,11 +21715,11 @@
         </is>
       </c>
       <c r="E709" s="3" t="n">
-        <v>139.11</v>
+        <v>145.54</v>
       </c>
       <c r="F709" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21745,11 +21745,11 @@
         </is>
       </c>
       <c r="E710" s="3" t="n">
-        <v>135.14</v>
+        <v>135.47</v>
       </c>
       <c r="F710" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21775,11 +21775,11 @@
         </is>
       </c>
       <c r="E711" s="3" t="n">
-        <v>134.04</v>
+        <v>134.44</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21791,12 +21791,12 @@
       </c>
       <c r="B712" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C712" s="2" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="D712" s="2" t="inlineStr">
@@ -21805,11 +21805,11 @@
         </is>
       </c>
       <c r="E712" s="3" t="n">
-        <v>132.39</v>
+        <v>132.93</v>
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21821,12 +21821,12 @@
       </c>
       <c r="B713" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C713" s="2" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="D713" s="2" t="inlineStr">
@@ -21835,11 +21835,11 @@
         </is>
       </c>
       <c r="E713" s="3" t="n">
-        <v>132.37</v>
+        <v>132.39</v>
       </c>
       <c r="F713" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21925,11 +21925,11 @@
         </is>
       </c>
       <c r="E716" s="3" t="n">
-        <v>129.78</v>
+        <v>130.45</v>
       </c>
       <c r="F716" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B717" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C717" s="2" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D717" s="2" t="inlineStr">
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>127.92</v>
+        <v>127.94</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -21971,12 +21971,12 @@
       </c>
       <c r="B718" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr">
@@ -21985,7 +21985,7 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>127.04</v>
+        <v>127.92</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
@@ -22001,12 +22001,12 @@
       </c>
       <c r="B719" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C719" s="2" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="D719" s="2" t="inlineStr">
@@ -22015,11 +22015,11 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>126.03</v>
+        <v>127.04</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22031,12 +22031,12 @@
       </c>
       <c r="B720" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C720" s="2" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="D720" s="2" t="inlineStr">
@@ -22045,11 +22045,11 @@
         </is>
       </c>
       <c r="E720" s="3" t="n">
-        <v>123.17</v>
+        <v>126.03</v>
       </c>
       <c r="F720" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22061,12 +22061,12 @@
       </c>
       <c r="B721" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C721" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="D721" s="2" t="inlineStr">
@@ -22075,11 +22075,11 @@
         </is>
       </c>
       <c r="E721" s="3" t="n">
-        <v>121.6</v>
+        <v>125.48</v>
       </c>
       <c r="F721" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -22121,12 +22121,12 @@
       </c>
       <c r="B723" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C723" s="2" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="D723" s="2" t="inlineStr">
@@ -22135,11 +22135,11 @@
         </is>
       </c>
       <c r="E723" s="3" t="n">
-        <v>117.93</v>
+        <v>118.4</v>
       </c>
       <c r="F723" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -22151,12 +22151,12 @@
       </c>
       <c r="B724" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C724" s="2" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="D724" s="2" t="inlineStr">
@@ -22165,11 +22165,11 @@
         </is>
       </c>
       <c r="E724" s="3" t="n">
-        <v>117.78</v>
+        <v>117.93</v>
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -22181,12 +22181,12 @@
       </c>
       <c r="B725" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C725" s="2" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D725" s="2" t="inlineStr">
@@ -22195,11 +22195,11 @@
         </is>
       </c>
       <c r="E725" s="3" t="n">
-        <v>114.07</v>
+        <v>115.53</v>
       </c>
       <c r="F725" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -22211,12 +22211,12 @@
       </c>
       <c r="B726" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C726" s="2" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="D726" s="2" t="inlineStr">
@@ -22225,11 +22225,11 @@
         </is>
       </c>
       <c r="E726" s="3" t="n">
-        <v>113.25</v>
+        <v>115.23</v>
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -22255,11 +22255,11 @@
         </is>
       </c>
       <c r="E727" s="3" t="n">
-        <v>111.18</v>
+        <v>114.73</v>
       </c>
       <c r="F727" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -22271,12 +22271,12 @@
       </c>
       <c r="B728" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C728" s="2" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="D728" s="2" t="inlineStr">
@@ -22285,11 +22285,11 @@
         </is>
       </c>
       <c r="E728" s="3" t="n">
-        <v>110.73</v>
+        <v>114.07</v>
       </c>
       <c r="F728" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22301,12 +22301,12 @@
       </c>
       <c r="B729" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C729" s="2" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="D729" s="2" t="inlineStr">
@@ -22315,11 +22315,11 @@
         </is>
       </c>
       <c r="E729" s="3" t="n">
-        <v>109.97</v>
+        <v>113.71</v>
       </c>
       <c r="F729" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -22331,12 +22331,12 @@
       </c>
       <c r="B730" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C730" s="2" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="D730" s="2" t="inlineStr">
@@ -22345,11 +22345,11 @@
         </is>
       </c>
       <c r="E730" s="3" t="n">
-        <v>109.92</v>
+        <v>113.25</v>
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22361,12 +22361,12 @@
       </c>
       <c r="B731" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="D731" s="2" t="inlineStr">
@@ -22375,11 +22375,11 @@
         </is>
       </c>
       <c r="E731" s="3" t="n">
-        <v>109.05</v>
+        <v>110.98</v>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -22391,12 +22391,12 @@
       </c>
       <c r="B732" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="D732" s="2" t="inlineStr">
@@ -22405,11 +22405,11 @@
         </is>
       </c>
       <c r="E732" s="3" t="n">
-        <v>108.48</v>
+        <v>110.73</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -22421,12 +22421,12 @@
       </c>
       <c r="B733" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="D733" s="2" t="inlineStr">
@@ -22435,11 +22435,11 @@
         </is>
       </c>
       <c r="E733" s="3" t="n">
-        <v>107.65</v>
+        <v>110.39</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -22451,12 +22451,12 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
@@ -22465,11 +22465,11 @@
         </is>
       </c>
       <c r="E734" s="3" t="n">
-        <v>105.73</v>
+        <v>109.33</v>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -22481,12 +22481,12 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
@@ -22495,11 +22495,11 @@
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>105.2</v>
+        <v>107.67</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -22631,12 +22631,12 @@
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
@@ -22645,11 +22645,11 @@
         </is>
       </c>
       <c r="E740" s="3" t="n">
-        <v>97.44</v>
+        <v>99.44</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -22661,12 +22661,12 @@
       </c>
       <c r="B741" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D741" s="2" t="inlineStr">
@@ -22675,11 +22675,11 @@
         </is>
       </c>
       <c r="E741" s="3" t="n">
-        <v>95.92</v>
+        <v>99.01000000000001</v>
       </c>
       <c r="F741" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -22691,12 +22691,12 @@
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>94.69</v>
+        <v>97.44</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22721,12 +22721,12 @@
       </c>
       <c r="B743" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C743" s="2" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="D743" s="2" t="inlineStr">
@@ -22735,11 +22735,11 @@
         </is>
       </c>
       <c r="E743" s="3" t="n">
-        <v>93.95</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -22751,12 +22751,12 @@
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="D744" s="2" t="inlineStr">
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>93.83</v>
+        <v>95.59</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -22781,12 +22781,12 @@
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr">
@@ -22795,11 +22795,11 @@
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>92.67</v>
+        <v>93.83</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22811,12 +22811,12 @@
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
@@ -22825,11 +22825,11 @@
         </is>
       </c>
       <c r="E746" s="3" t="n">
-        <v>89.79000000000001</v>
+        <v>93.52</v>
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -22841,25 +22841,25 @@
       </c>
       <c r="B747" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C747" s="2" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="D747" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E747" s="3" t="n">
-        <v>89.48999999999999</v>
+        <v>90.73</v>
       </c>
       <c r="F747" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -22871,12 +22871,12 @@
       </c>
       <c r="B748" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C748" s="2" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="D748" s="2" t="inlineStr">
@@ -22885,11 +22885,11 @@
         </is>
       </c>
       <c r="E748" s="3" t="n">
-        <v>88.55</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22901,21 +22901,21 @@
       </c>
       <c r="B749" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C749" s="2" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="D749" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E749" s="3" t="n">
-        <v>87.73</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F749" s="2" t="inlineStr">
         <is>
@@ -22931,12 +22931,12 @@
       </c>
       <c r="B750" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C750" s="2" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="D750" s="2" t="inlineStr">
@@ -22945,11 +22945,11 @@
         </is>
       </c>
       <c r="E750" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="F750" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -22961,12 +22961,12 @@
       </c>
       <c r="B751" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C751" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="D751" s="2" t="inlineStr">
@@ -22975,11 +22975,11 @@
         </is>
       </c>
       <c r="E751" s="3" t="n">
-        <v>86.01000000000001</v>
+        <v>87.73</v>
       </c>
       <c r="F751" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22991,12 +22991,12 @@
       </c>
       <c r="B752" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C752" s="2" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="D752" s="2" t="inlineStr">
@@ -23005,11 +23005,11 @@
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>85.54000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23021,12 +23021,12 @@
       </c>
       <c r="B753" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C753" s="2" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="D753" s="2" t="inlineStr">
@@ -23035,11 +23035,11 @@
         </is>
       </c>
       <c r="E753" s="3" t="n">
-        <v>85.12</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="F753" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23051,12 +23051,12 @@
       </c>
       <c r="B754" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C754" s="2" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="D754" s="2" t="inlineStr">
@@ -23065,11 +23065,11 @@
         </is>
       </c>
       <c r="E754" s="3" t="n">
-        <v>82.18000000000001</v>
+        <v>83.59</v>
       </c>
       <c r="F754" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23081,12 +23081,12 @@
       </c>
       <c r="B755" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C755" s="2" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="D755" s="2" t="inlineStr">
@@ -23095,11 +23095,11 @@
         </is>
       </c>
       <c r="E755" s="3" t="n">
-        <v>81.73</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F755" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23111,12 +23111,12 @@
       </c>
       <c r="B756" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C756" s="2" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="D756" s="2" t="inlineStr">
@@ -23125,11 +23125,11 @@
         </is>
       </c>
       <c r="E756" s="3" t="n">
-        <v>80.75</v>
+        <v>81.73</v>
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>77.20999999999999</v>
+        <v>79</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23201,12 +23201,12 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D759" s="2" t="inlineStr">
@@ -23215,11 +23215,11 @@
         </is>
       </c>
       <c r="E759" s="3" t="n">
-        <v>74.76000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23231,25 +23231,25 @@
       </c>
       <c r="B760" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C760" s="2" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D760" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>74.95</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23261,12 +23261,12 @@
       </c>
       <c r="B761" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C761" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="D761" s="2" t="inlineStr">
@@ -23275,11 +23275,11 @@
         </is>
       </c>
       <c r="E761" s="3" t="n">
-        <v>73.56</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="F761" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23291,25 +23291,25 @@
       </c>
       <c r="B762" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C762" s="2" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="D762" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>73.52</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23321,12 +23321,12 @@
       </c>
       <c r="B763" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C763" s="2" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="D763" s="2" t="inlineStr">
@@ -23335,11 +23335,11 @@
         </is>
       </c>
       <c r="E763" s="3" t="n">
-        <v>71.38</v>
+        <v>74.56</v>
       </c>
       <c r="F763" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23351,12 +23351,12 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="D764" s="2" t="inlineStr">
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>71.34999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23381,12 +23381,12 @@
       </c>
       <c r="B765" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C765" s="2" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D765" s="2" t="inlineStr">
@@ -23395,11 +23395,11 @@
         </is>
       </c>
       <c r="E765" s="3" t="n">
-        <v>70.58</v>
+        <v>72.89</v>
       </c>
       <c r="F765" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23411,12 +23411,12 @@
       </c>
       <c r="B766" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C766" s="2" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="D766" s="2" t="inlineStr">
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>70.48</v>
+        <v>71.5</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23441,12 +23441,12 @@
       </c>
       <c r="B767" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C767" s="2" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="D767" s="2" t="inlineStr">
@@ -23455,11 +23455,11 @@
         </is>
       </c>
       <c r="E767" s="3" t="n">
-        <v>69.73</v>
+        <v>71.38</v>
       </c>
       <c r="F767" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23471,12 +23471,12 @@
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="D768" s="2" t="inlineStr">
@@ -23485,11 +23485,11 @@
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>69.3</v>
+        <v>71.38</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23501,12 @@
       </c>
       <c r="B769" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C769" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="D769" s="2" t="inlineStr">
@@ -23515,11 +23515,11 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>68.53</v>
+        <v>70.48</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23531,12 +23531,12 @@
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
@@ -23545,11 +23545,11 @@
         </is>
       </c>
       <c r="E770" s="3" t="n">
-        <v>68.5</v>
+        <v>70.16</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23561,12 +23561,12 @@
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
@@ -23575,11 +23575,11 @@
         </is>
       </c>
       <c r="E771" s="3" t="n">
-        <v>68.19</v>
+        <v>68.5</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23591,12 +23591,12 @@
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -23605,11 +23605,11 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>68.48</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23621,12 +23621,12 @@
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="D773" s="2" t="inlineStr">
@@ -23635,11 +23635,11 @@
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>67.27</v>
+        <v>68.44</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23651,12 +23651,12 @@
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr">
@@ -23665,11 +23665,11 @@
         </is>
       </c>
       <c r="E774" s="3" t="n">
-        <v>66.62</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F774" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23681,12 +23681,12 @@
       </c>
       <c r="B775" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C775" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D775" s="2" t="inlineStr">
@@ -23695,11 +23695,11 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>66.56</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23711,12 +23711,12 @@
       </c>
       <c r="B776" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C776" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="D776" s="2" t="inlineStr">
@@ -23725,11 +23725,11 @@
         </is>
       </c>
       <c r="E776" s="3" t="n">
-        <v>66.17</v>
+        <v>68.12</v>
       </c>
       <c r="F776" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23741,12 +23741,12 @@
       </c>
       <c r="B777" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C777" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D777" s="2" t="inlineStr">
@@ -23755,11 +23755,11 @@
         </is>
       </c>
       <c r="E777" s="3" t="n">
-        <v>65.92</v>
+        <v>67.14</v>
       </c>
       <c r="F777" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23771,12 +23771,12 @@
       </c>
       <c r="B778" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C778" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="D778" s="2" t="inlineStr">
@@ -23785,11 +23785,11 @@
         </is>
       </c>
       <c r="E778" s="3" t="n">
-        <v>63.99</v>
+        <v>65.61</v>
       </c>
       <c r="F778" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23815,11 +23815,11 @@
         </is>
       </c>
       <c r="E779" s="3" t="n">
-        <v>63.85</v>
+        <v>64.59</v>
       </c>
       <c r="F779" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23831,12 +23831,12 @@
       </c>
       <c r="B780" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C780" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="D780" s="2" t="inlineStr">
@@ -23845,11 +23845,11 @@
         </is>
       </c>
       <c r="E780" s="3" t="n">
-        <v>63.6</v>
+        <v>64.59</v>
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23861,12 +23861,12 @@
       </c>
       <c r="B781" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C781" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="D781" s="2" t="inlineStr">
@@ -23875,11 +23875,11 @@
         </is>
       </c>
       <c r="E781" s="3" t="n">
-        <v>63.31</v>
+        <v>63.69</v>
       </c>
       <c r="F781" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23891,12 +23891,12 @@
       </c>
       <c r="B782" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C782" s="2" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="D782" s="2" t="inlineStr">
@@ -23905,11 +23905,11 @@
         </is>
       </c>
       <c r="E782" s="3" t="n">
-        <v>63.15</v>
+        <v>63.6</v>
       </c>
       <c r="F782" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -23921,12 +23921,12 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D783" s="2" t="inlineStr">
@@ -23935,11 +23935,11 @@
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>62.6</v>
+        <v>63.48</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23951,12 +23951,12 @@
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
@@ -23965,11 +23965,11 @@
         </is>
       </c>
       <c r="E784" s="3" t="n">
-        <v>62.41</v>
+        <v>63.3</v>
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -23981,12 +23981,12 @@
       </c>
       <c r="B785" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C785" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="D785" s="2" t="inlineStr">
@@ -23995,11 +23995,11 @@
         </is>
       </c>
       <c r="E785" s="3" t="n">
-        <v>61.96</v>
+        <v>62.79</v>
       </c>
       <c r="F785" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -24011,12 +24011,12 @@
       </c>
       <c r="B786" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C786" s="2" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D786" s="2" t="inlineStr">
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>59.82</v>
+        <v>61.96</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24041,12 +24041,12 @@
       </c>
       <c r="B787" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C787" s="2" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="D787" s="2" t="inlineStr">
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>59.73</v>
+        <v>61.93</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -24071,12 +24071,12 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D788" s="2" t="inlineStr">
@@ -24085,11 +24085,11 @@
         </is>
       </c>
       <c r="E788" s="3" t="n">
-        <v>59.58</v>
+        <v>60.41</v>
       </c>
       <c r="F788" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -24101,12 +24101,12 @@
       </c>
       <c r="B789" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C789" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="D789" s="2" t="inlineStr">
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>58.13</v>
+        <v>59.98</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -24131,25 +24131,25 @@
       </c>
       <c r="B790" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C790" s="2" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="D790" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E790" s="3" t="n">
-        <v>57.22</v>
+        <v>59.78</v>
       </c>
       <c r="F790" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -24161,25 +24161,25 @@
       </c>
       <c r="B791" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C791" s="2" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="D791" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E791" s="3" t="n">
-        <v>56.56</v>
+        <v>57.22</v>
       </c>
       <c r="F791" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24311,12 +24311,12 @@
       </c>
       <c r="B796" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C796" s="2" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="D796" s="2" t="inlineStr">
@@ -24325,11 +24325,11 @@
         </is>
       </c>
       <c r="E796" s="3" t="n">
-        <v>52.57</v>
+        <v>53.52</v>
       </c>
       <c r="F796" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -24341,12 +24341,12 @@
       </c>
       <c r="B797" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C797" s="2" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="D797" s="2" t="inlineStr">
@@ -24355,11 +24355,11 @@
         </is>
       </c>
       <c r="E797" s="3" t="n">
-        <v>52.55</v>
+        <v>52.57</v>
       </c>
       <c r="F797" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="B799" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C799" s="2" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="D799" s="2" t="inlineStr">
@@ -24415,11 +24415,11 @@
         </is>
       </c>
       <c r="E799" s="3" t="n">
-        <v>50.13</v>
+        <v>51.94</v>
       </c>
       <c r="F799" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -24431,12 +24431,12 @@
       </c>
       <c r="B800" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C800" s="2" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="D800" s="2" t="inlineStr">
@@ -24445,11 +24445,11 @@
         </is>
       </c>
       <c r="E800" s="3" t="n">
-        <v>49.61</v>
+        <v>50.13</v>
       </c>
       <c r="F800" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24461,12 +24461,12 @@
       </c>
       <c r="B801" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C801" s="2" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="D801" s="2" t="inlineStr">
@@ -24475,11 +24475,11 @@
         </is>
       </c>
       <c r="E801" s="3" t="n">
-        <v>48.43</v>
+        <v>49.68</v>
       </c>
       <c r="F801" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -24505,11 +24505,11 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>48.15</v>
+        <v>49.67</v>
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -24521,12 +24521,12 @@
       </c>
       <c r="B803" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C803" s="2" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="D803" s="2" t="inlineStr">
@@ -24535,11 +24535,11 @@
         </is>
       </c>
       <c r="E803" s="3" t="n">
-        <v>48.04</v>
+        <v>48.75</v>
       </c>
       <c r="F803" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -24551,12 +24551,12 @@
       </c>
       <c r="B804" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="C804" s="2" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="D804" s="2" t="inlineStr">
@@ -24565,11 +24565,11 @@
         </is>
       </c>
       <c r="E804" s="3" t="n">
-        <v>47.99</v>
+        <v>48.18</v>
       </c>
       <c r="F804" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -24581,12 +24581,12 @@
       </c>
       <c r="B805" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C805" s="2" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="D805" s="2" t="inlineStr">
@@ -24595,7 +24595,7 @@
         </is>
       </c>
       <c r="E805" s="3" t="n">
-        <v>47.23</v>
+        <v>48.04</v>
       </c>
       <c r="F805" s="2" t="inlineStr">
         <is>
@@ -24611,12 +24611,12 @@
       </c>
       <c r="B806" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C806" s="2" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="D806" s="2" t="inlineStr">
@@ -24625,11 +24625,11 @@
         </is>
       </c>
       <c r="E806" s="3" t="n">
-        <v>47.07</v>
+        <v>47.99</v>
       </c>
       <c r="F806" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24641,12 +24641,12 @@
       </c>
       <c r="B807" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C807" s="2" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="D807" s="2" t="inlineStr">
@@ -24655,11 +24655,11 @@
         </is>
       </c>
       <c r="E807" s="3" t="n">
-        <v>46.93</v>
+        <v>47.23</v>
       </c>
       <c r="F807" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24775,11 +24775,11 @@
         </is>
       </c>
       <c r="E811" s="3" t="n">
-        <v>40.45</v>
+        <v>42.65</v>
       </c>
       <c r="F811" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -24805,11 +24805,11 @@
         </is>
       </c>
       <c r="E812" s="3" t="n">
-        <v>40.15</v>
+        <v>41.39</v>
       </c>
       <c r="F812" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -24821,12 +24821,12 @@
       </c>
       <c r="B813" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C813" s="2" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="D813" s="2" t="inlineStr">
@@ -24835,11 +24835,11 @@
         </is>
       </c>
       <c r="E813" s="3" t="n">
-        <v>39.39</v>
+        <v>39.58</v>
       </c>
       <c r="F813" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -24851,12 +24851,12 @@
       </c>
       <c r="B814" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C814" s="2" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="D814" s="2" t="inlineStr">
@@ -24865,11 +24865,11 @@
         </is>
       </c>
       <c r="E814" s="3" t="n">
-        <v>39.2</v>
+        <v>39.39</v>
       </c>
       <c r="F814" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24881,12 +24881,12 @@
       </c>
       <c r="B815" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C815" s="2" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="D815" s="2" t="inlineStr">
@@ -24895,11 +24895,11 @@
         </is>
       </c>
       <c r="E815" s="3" t="n">
-        <v>38.79</v>
+        <v>39.2</v>
       </c>
       <c r="F815" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25075,11 +25075,11 @@
         </is>
       </c>
       <c r="E821" s="3" t="n">
-        <v>31.68</v>
+        <v>31.86</v>
       </c>
       <c r="F821" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -25091,12 +25091,12 @@
       </c>
       <c r="B822" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C822" s="2" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="D822" s="2" t="inlineStr">
@@ -25105,11 +25105,11 @@
         </is>
       </c>
       <c r="E822" s="3" t="n">
-        <v>31.24</v>
+        <v>31.36</v>
       </c>
       <c r="F822" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -25121,12 +25121,12 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="D823" s="2" t="inlineStr">
@@ -25135,11 +25135,11 @@
         </is>
       </c>
       <c r="E823" s="3" t="n">
-        <v>31.18</v>
+        <v>31.24</v>
       </c>
       <c r="F823" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25225,11 +25225,11 @@
         </is>
       </c>
       <c r="E826" s="3" t="n">
-        <v>29.11</v>
+        <v>29.23</v>
       </c>
       <c r="F826" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -25241,12 +25241,12 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="D827" s="2" t="inlineStr">
@@ -25255,11 +25255,11 @@
         </is>
       </c>
       <c r="E827" s="3" t="n">
-        <v>28.85</v>
+        <v>29.1</v>
       </c>
       <c r="F827" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -25271,12 +25271,12 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="D828" s="2" t="inlineStr">
@@ -25285,11 +25285,11 @@
         </is>
       </c>
       <c r="E828" s="3" t="n">
-        <v>28.04</v>
+        <v>29.06</v>
       </c>
       <c r="F828" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -25301,12 +25301,12 @@
       </c>
       <c r="B829" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C829" s="2" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="D829" s="2" t="inlineStr">
@@ -25315,11 +25315,11 @@
         </is>
       </c>
       <c r="E829" s="3" t="n">
-        <v>27.65</v>
+        <v>28.85</v>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25331,12 +25331,12 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="D830" s="2" t="inlineStr">
@@ -25345,11 +25345,11 @@
         </is>
       </c>
       <c r="E830" s="3" t="n">
-        <v>27.39</v>
+        <v>28.82</v>
       </c>
       <c r="F830" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -25375,11 +25375,11 @@
         </is>
       </c>
       <c r="E831" s="3" t="n">
-        <v>26.76</v>
+        <v>28</v>
       </c>
       <c r="F831" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -25391,25 +25391,25 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="D832" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E832" s="3" t="n">
-        <v>26.15</v>
+        <v>27.8</v>
       </c>
       <c r="F832" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -25435,11 +25435,11 @@
         </is>
       </c>
       <c r="E833" s="3" t="n">
-        <v>25.52</v>
+        <v>26.64</v>
       </c>
       <c r="F833" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -25451,12 +25451,12 @@
       </c>
       <c r="B834" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C834" s="2" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="D834" s="2" t="inlineStr">
@@ -25465,11 +25465,11 @@
         </is>
       </c>
       <c r="E834" s="3" t="n">
-        <v>24.95</v>
+        <v>26.15</v>
       </c>
       <c r="F834" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25481,25 +25481,25 @@
       </c>
       <c r="B835" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C835" s="2" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="D835" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E835" s="3" t="n">
-        <v>24.11</v>
+        <v>25.24</v>
       </c>
       <c r="F835" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -25511,12 +25511,12 @@
       </c>
       <c r="B836" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C836" s="2" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D836" s="2" t="inlineStr">
@@ -25525,11 +25525,11 @@
         </is>
       </c>
       <c r="E836" s="3" t="n">
-        <v>23.74</v>
+        <v>24.52</v>
       </c>
       <c r="F836" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -25541,12 +25541,12 @@
       </c>
       <c r="B837" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C837" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="D837" s="2" t="inlineStr">
@@ -25555,11 +25555,11 @@
         </is>
       </c>
       <c r="E837" s="3" t="n">
-        <v>23.18</v>
+        <v>23.74</v>
       </c>
       <c r="F837" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25825,11 +25825,11 @@
         </is>
       </c>
       <c r="E846" s="3" t="n">
-        <v>17.76</v>
+        <v>17.84</v>
       </c>
       <c r="F846" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -25991,12 +25991,12 @@
       </c>
       <c r="B852" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799709G5Q</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C852" s="2" t="inlineStr">
         <is>
-          <t>816274</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="D852" s="2" t="inlineStr">
@@ -26005,11 +26005,11 @@
         </is>
       </c>
       <c r="E852" s="3" t="n">
-        <v>14.51</v>
+        <v>15.16</v>
       </c>
       <c r="F852" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -26021,12 +26021,12 @@
       </c>
       <c r="B853" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="C853" s="2" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>816274</t>
         </is>
       </c>
       <c r="D853" s="2" t="inlineStr">
@@ -26035,11 +26035,11 @@
         </is>
       </c>
       <c r="E853" s="3" t="n">
-        <v>13.55</v>
+        <v>14.58</v>
       </c>
       <c r="F853" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>
@@ -26365,11 +26365,11 @@
         </is>
       </c>
       <c r="E864" s="3" t="n">
-        <v>6.01</v>
+        <v>6.18</v>
       </c>
       <c r="F864" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-26 17:54</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2396.9</v>
+        <v>2400.99</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -19795,11 +19795,11 @@
         </is>
       </c>
       <c r="E645" s="3" t="n">
-        <v>2164.01</v>
+        <v>2304.08</v>
       </c>
       <c r="F645" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -19871,12 +19871,12 @@
       </c>
       <c r="B648" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065641GDF</t>
+          <t>KIT4P0008460369B</t>
         </is>
       </c>
       <c r="C648" s="2" t="inlineStr">
         <is>
-          <t>812924</t>
+          <t>816224</t>
         </is>
       </c>
       <c r="D648" s="2" t="inlineStr">
@@ -19885,11 +19885,11 @@
         </is>
       </c>
       <c r="E648" s="3" t="n">
-        <v>1136</v>
+        <v>1187.69</v>
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -19901,12 +19901,12 @@
       </c>
       <c r="B649" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008460369B</t>
+          <t>KIT4P00065641GDF</t>
         </is>
       </c>
       <c r="C649" s="2" t="inlineStr">
         <is>
-          <t>816224</t>
+          <t>812924</t>
         </is>
       </c>
       <c r="D649" s="2" t="inlineStr">
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>1133.17</v>
+        <v>1178.79</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -19931,12 +19931,12 @@
       </c>
       <c r="B650" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00083897XCW</t>
+          <t>KIT4P000739257CR</t>
         </is>
       </c>
       <c r="C650" s="2" t="inlineStr">
         <is>
-          <t>816223</t>
+          <t>814609</t>
         </is>
       </c>
       <c r="D650" s="2" t="inlineStr">
@@ -19945,11 +19945,11 @@
         </is>
       </c>
       <c r="E650" s="3" t="n">
-        <v>938.21</v>
+        <v>938.39</v>
       </c>
       <c r="F650" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -19961,12 +19961,12 @@
       </c>
       <c r="B651" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739257CR</t>
+          <t>KIT4P00083897XCW</t>
         </is>
       </c>
       <c r="C651" s="2" t="inlineStr">
         <is>
-          <t>814609</t>
+          <t>816223</t>
         </is>
       </c>
       <c r="D651" s="2" t="inlineStr">
@@ -19975,11 +19975,11 @@
         </is>
       </c>
       <c r="E651" s="3" t="n">
-        <v>893.13</v>
+        <v>938.21</v>
       </c>
       <c r="F651" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20005,11 +20005,11 @@
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>778.3</v>
+        <v>804</v>
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20065,11 +20065,11 @@
         </is>
       </c>
       <c r="E654" s="3" t="n">
-        <v>720.62</v>
+        <v>733.67</v>
       </c>
       <c r="F654" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20095,11 +20095,11 @@
         </is>
       </c>
       <c r="E655" s="3" t="n">
-        <v>653.72</v>
+        <v>692.98</v>
       </c>
       <c r="F655" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20155,11 +20155,11 @@
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>623.87</v>
+        <v>631.59</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20171,12 +20171,12 @@
       </c>
       <c r="B658" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C658" s="2" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="D658" s="2" t="inlineStr">
@@ -20185,11 +20185,11 @@
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>606.34</v>
+        <v>622.96</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20201,12 +20201,12 @@
       </c>
       <c r="B659" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C659" s="2" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="D659" s="2" t="inlineStr">
@@ -20215,11 +20215,11 @@
         </is>
       </c>
       <c r="E659" s="3" t="n">
-        <v>601.52</v>
+        <v>606.9400000000001</v>
       </c>
       <c r="F659" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20231,12 +20231,12 @@
       </c>
       <c r="B660" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C660" s="2" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="D660" s="2" t="inlineStr">
@@ -20245,11 +20245,11 @@
         </is>
       </c>
       <c r="E660" s="3" t="n">
-        <v>557.1900000000001</v>
+        <v>572.29</v>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20261,12 +20261,12 @@
       </c>
       <c r="B661" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C661" s="2" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="D661" s="2" t="inlineStr">
@@ -20275,11 +20275,11 @@
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>556.35</v>
+        <v>557.1900000000001</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20305,11 +20305,11 @@
         </is>
       </c>
       <c r="E662" s="3" t="n">
-        <v>536.52</v>
+        <v>550.58</v>
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         </is>
       </c>
       <c r="E663" s="3" t="n">
-        <v>529.75</v>
+        <v>534.96</v>
       </c>
       <c r="F663" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20351,25 +20351,25 @@
       </c>
       <c r="B664" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E664" s="3" t="n">
-        <v>513.88</v>
+        <v>531.08</v>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20381,12 +20381,12 @@
       </c>
       <c r="B665" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
@@ -20395,11 +20395,11 @@
         </is>
       </c>
       <c r="E665" s="3" t="n">
-        <v>504.92</v>
+        <v>529.0599999999999</v>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20425,11 +20425,11 @@
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>504.42</v>
+        <v>528.42</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20441,25 +20441,25 @@
       </c>
       <c r="B667" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066901JZZ</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C667" s="2" t="inlineStr">
         <is>
-          <t>812926</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="D667" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E667" s="3" t="n">
-        <v>500.46</v>
+        <v>513.88</v>
       </c>
       <c r="F667" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20471,12 +20471,12 @@
       </c>
       <c r="B668" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="C668" s="2" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>812926</t>
         </is>
       </c>
       <c r="D668" s="2" t="inlineStr">
@@ -20485,11 +20485,11 @@
         </is>
       </c>
       <c r="E668" s="3" t="n">
-        <v>480.85</v>
+        <v>500.46</v>
       </c>
       <c r="F668" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20501,25 +20501,25 @@
       </c>
       <c r="B669" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C669" s="2" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="D669" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E669" s="3" t="n">
-        <v>478.68</v>
+        <v>490.29</v>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20531,25 +20531,25 @@
       </c>
       <c r="B670" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C670" s="2" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="D670" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E670" s="3" t="n">
-        <v>470.18</v>
+        <v>484.64</v>
       </c>
       <c r="F670" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20561,12 +20561,12 @@
       </c>
       <c r="B671" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C671" s="2" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="D671" s="2" t="inlineStr">
@@ -20575,11 +20575,11 @@
         </is>
       </c>
       <c r="E671" s="3" t="n">
-        <v>454.44</v>
+        <v>480.85</v>
       </c>
       <c r="F671" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20605,11 +20605,11 @@
         </is>
       </c>
       <c r="E672" s="3" t="n">
-        <v>444.95</v>
+        <v>458.37</v>
       </c>
       <c r="F672" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20695,11 +20695,11 @@
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>389.13</v>
+        <v>395.6</v>
       </c>
       <c r="F675" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20711,12 +20711,12 @@
       </c>
       <c r="B676" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000668852J9</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C676" s="2" t="inlineStr">
         <is>
-          <t>812925</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="D676" s="2" t="inlineStr">
@@ -20725,11 +20725,11 @@
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>338.74</v>
+        <v>371.5</v>
       </c>
       <c r="F676" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20741,25 +20741,25 @@
       </c>
       <c r="B677" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4P000668852J9</t>
         </is>
       </c>
       <c r="C677" s="2" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>812925</t>
         </is>
       </c>
       <c r="D677" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>334</v>
+        <v>359.74</v>
       </c>
       <c r="F677" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20771,12 +20771,12 @@
       </c>
       <c r="B678" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C678" s="2" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="D678" s="2" t="inlineStr">
@@ -20785,11 +20785,11 @@
         </is>
       </c>
       <c r="E678" s="3" t="n">
-        <v>333.84</v>
+        <v>338.03</v>
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20801,12 +20801,12 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="D679" s="2" t="inlineStr">
@@ -20815,11 +20815,11 @@
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>326.29</v>
+        <v>337.65</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20831,12 +20831,12 @@
       </c>
       <c r="B680" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C680" s="2" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="D680" s="2" t="inlineStr">
@@ -20845,11 +20845,11 @@
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>318.87</v>
+        <v>327.65</v>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20861,25 +20861,25 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="D681" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E681" s="3" t="n">
-        <v>316.79</v>
+        <v>318.87</v>
       </c>
       <c r="F681" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20891,12 +20891,12 @@
       </c>
       <c r="B682" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C682" s="2" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="D682" s="2" t="inlineStr">
@@ -20905,11 +20905,11 @@
         </is>
       </c>
       <c r="E682" s="3" t="n">
-        <v>276.4</v>
+        <v>281.73</v>
       </c>
       <c r="F682" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20921,12 +20921,12 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="D683" s="2" t="inlineStr">
@@ -20935,11 +20935,11 @@
         </is>
       </c>
       <c r="E683" s="3" t="n">
-        <v>269.58</v>
+        <v>279.54</v>
       </c>
       <c r="F683" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -20965,11 +20965,11 @@
         </is>
       </c>
       <c r="E684" s="3" t="n">
-        <v>268.07</v>
+        <v>272.49</v>
       </c>
       <c r="F684" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21025,11 +21025,11 @@
         </is>
       </c>
       <c r="E686" s="3" t="n">
-        <v>254.42</v>
+        <v>261.99</v>
       </c>
       <c r="F686" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21041,12 +21041,12 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="D687" s="2" t="inlineStr">
@@ -21055,11 +21055,11 @@
         </is>
       </c>
       <c r="E687" s="3" t="n">
-        <v>246.96</v>
+        <v>253.27</v>
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21071,12 +21071,12 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="D688" s="2" t="inlineStr">
@@ -21085,11 +21085,11 @@
         </is>
       </c>
       <c r="E688" s="3" t="n">
-        <v>246.73</v>
+        <v>246.96</v>
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21115,11 +21115,11 @@
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>239.89</v>
+        <v>246.44</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21131,12 +21131,12 @@
       </c>
       <c r="B690" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="C690" s="2" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="D690" s="2" t="inlineStr">
@@ -21145,11 +21145,11 @@
         </is>
       </c>
       <c r="E690" s="3" t="n">
-        <v>237.44</v>
+        <v>244.18</v>
       </c>
       <c r="F690" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21161,12 +21161,12 @@
       </c>
       <c r="B691" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C691" s="2" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="D691" s="2" t="inlineStr">
@@ -21175,11 +21175,11 @@
         </is>
       </c>
       <c r="E691" s="3" t="n">
-        <v>231.75</v>
+        <v>237.44</v>
       </c>
       <c r="F691" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21191,12 +21191,12 @@
       </c>
       <c r="B692" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C692" s="2" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="D692" s="2" t="inlineStr">
@@ -21205,11 +21205,11 @@
         </is>
       </c>
       <c r="E692" s="3" t="n">
-        <v>219.46</v>
+        <v>225.47</v>
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21221,12 +21221,12 @@
       </c>
       <c r="B693" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C693" s="2" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="D693" s="2" t="inlineStr">
@@ -21235,11 +21235,11 @@
         </is>
       </c>
       <c r="E693" s="3" t="n">
-        <v>215.14</v>
+        <v>220.53</v>
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="B694" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872531DSZ</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C694" s="2" t="inlineStr">
         <is>
-          <t>816171</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="D694" s="2" t="inlineStr">
@@ -21265,11 +21265,11 @@
         </is>
       </c>
       <c r="E694" s="3" t="n">
-        <v>207.69</v>
+        <v>217.41</v>
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21281,12 +21281,12 @@
       </c>
       <c r="B695" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C695" s="2" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="D695" s="2" t="inlineStr">
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>205.38</v>
+        <v>215.03</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21311,12 +21311,12 @@
       </c>
       <c r="B696" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="C696" s="2" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>816171</t>
         </is>
       </c>
       <c r="D696" s="2" t="inlineStr">
@@ -21325,11 +21325,11 @@
         </is>
       </c>
       <c r="E696" s="3" t="n">
-        <v>199.59</v>
+        <v>213.49</v>
       </c>
       <c r="F696" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>198.27</v>
+        <v>208.57</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21371,12 +21371,12 @@
       </c>
       <c r="B698" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C698" s="2" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="D698" s="2" t="inlineStr">
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="E698" s="3" t="n">
-        <v>187.5</v>
+        <v>208.06</v>
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>184.89</v>
+        <v>196.63</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21431,12 +21431,12 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="D700" s="2" t="inlineStr">
@@ -21445,11 +21445,11 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>184.14</v>
+        <v>189.37</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21461,12 +21461,12 @@
       </c>
       <c r="B701" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C701" s="2" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="D701" s="2" t="inlineStr">
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>177.59</v>
+        <v>185.94</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21491,12 +21491,12 @@
       </c>
       <c r="B702" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C702" s="2" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="D702" s="2" t="inlineStr">
@@ -21505,11 +21505,11 @@
         </is>
       </c>
       <c r="E702" s="3" t="n">
-        <v>169.22</v>
+        <v>179.07</v>
       </c>
       <c r="F702" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21521,12 +21521,12 @@
       </c>
       <c r="B703" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C703" s="2" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="D703" s="2" t="inlineStr">
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>167.02</v>
+        <v>172.08</v>
       </c>
       <c r="F703" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21551,12 +21551,12 @@
       </c>
       <c r="B704" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C704" s="2" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="D704" s="2" t="inlineStr">
@@ -21565,11 +21565,11 @@
         </is>
       </c>
       <c r="E704" s="3" t="n">
-        <v>162.32</v>
+        <v>171.18</v>
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21581,12 +21581,12 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="D705" s="2" t="inlineStr">
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>158.82</v>
+        <v>160.49</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21611,12 +21611,12 @@
       </c>
       <c r="B706" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C706" s="2" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="D706" s="2" t="inlineStr">
@@ -21625,11 +21625,11 @@
         </is>
       </c>
       <c r="E706" s="3" t="n">
-        <v>150.25</v>
+        <v>158.82</v>
       </c>
       <c r="F706" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21655,11 +21655,11 @@
         </is>
       </c>
       <c r="E707" s="3" t="n">
-        <v>149.75</v>
+        <v>157.87</v>
       </c>
       <c r="F707" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21685,11 +21685,11 @@
         </is>
       </c>
       <c r="E708" s="3" t="n">
-        <v>148.01</v>
+        <v>151.74</v>
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21701,12 +21701,12 @@
       </c>
       <c r="B709" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C709" s="2" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="D709" s="2" t="inlineStr">
@@ -21715,11 +21715,11 @@
         </is>
       </c>
       <c r="E709" s="3" t="n">
-        <v>145.54</v>
+        <v>150.25</v>
       </c>
       <c r="F709" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21745,11 +21745,11 @@
         </is>
       </c>
       <c r="E710" s="3" t="n">
-        <v>135.47</v>
+        <v>136.89</v>
       </c>
       <c r="F710" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21761,12 +21761,12 @@
       </c>
       <c r="B711" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C711" s="2" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="D711" s="2" t="inlineStr">
@@ -21775,11 +21775,11 @@
         </is>
       </c>
       <c r="E711" s="3" t="n">
-        <v>134.44</v>
+        <v>136.06</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21791,12 +21791,12 @@
       </c>
       <c r="B712" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C712" s="2" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="D712" s="2" t="inlineStr">
@@ -21805,11 +21805,11 @@
         </is>
       </c>
       <c r="E712" s="3" t="n">
-        <v>132.93</v>
+        <v>134.54</v>
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21821,12 +21821,12 @@
       </c>
       <c r="B713" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C713" s="2" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="D713" s="2" t="inlineStr">
@@ -21835,11 +21835,11 @@
         </is>
       </c>
       <c r="E713" s="3" t="n">
-        <v>132.39</v>
+        <v>133.91</v>
       </c>
       <c r="F713" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21851,12 +21851,12 @@
       </c>
       <c r="B714" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C714" s="2" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="D714" s="2" t="inlineStr">
@@ -21865,7 +21865,7 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>131.31</v>
+        <v>132.39</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
@@ -21881,12 +21881,12 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="D715" s="2" t="inlineStr">
@@ -21895,11 +21895,11 @@
         </is>
       </c>
       <c r="E715" s="3" t="n">
-        <v>131.04</v>
+        <v>131.83</v>
       </c>
       <c r="F715" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -21911,12 +21911,12 @@
       </c>
       <c r="B716" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C716" s="2" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="D716" s="2" t="inlineStr">
@@ -21925,11 +21925,11 @@
         </is>
       </c>
       <c r="E716" s="3" t="n">
-        <v>130.45</v>
+        <v>131.31</v>
       </c>
       <c r="F716" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B717" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C717" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="D717" s="2" t="inlineStr">
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>127.94</v>
+        <v>131.04</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21971,12 +21971,12 @@
       </c>
       <c r="B718" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr">
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>127.92</v>
+        <v>128.6</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22001,12 +22001,12 @@
       </c>
       <c r="B719" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C719" s="2" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="D719" s="2" t="inlineStr">
@@ -22015,7 +22015,7 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>127.04</v>
+        <v>127.92</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
@@ -22031,12 +22031,12 @@
       </c>
       <c r="B720" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C720" s="2" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="D720" s="2" t="inlineStr">
@@ -22045,11 +22045,11 @@
         </is>
       </c>
       <c r="E720" s="3" t="n">
-        <v>126.03</v>
+        <v>127.83</v>
       </c>
       <c r="F720" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22061,12 +22061,12 @@
       </c>
       <c r="B721" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C721" s="2" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="D721" s="2" t="inlineStr">
@@ -22075,11 +22075,11 @@
         </is>
       </c>
       <c r="E721" s="3" t="n">
-        <v>125.48</v>
+        <v>127.72</v>
       </c>
       <c r="F721" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22091,12 +22091,12 @@
       </c>
       <c r="B722" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C722" s="2" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="D722" s="2" t="inlineStr">
@@ -22105,11 +22105,11 @@
         </is>
       </c>
       <c r="E722" s="3" t="n">
-        <v>119.92</v>
+        <v>126.48</v>
       </c>
       <c r="F722" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22121,12 +22121,12 @@
       </c>
       <c r="B723" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C723" s="2" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="D723" s="2" t="inlineStr">
@@ -22135,11 +22135,11 @@
         </is>
       </c>
       <c r="E723" s="3" t="n">
-        <v>118.4</v>
+        <v>126.03</v>
       </c>
       <c r="F723" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22165,11 +22165,11 @@
         </is>
       </c>
       <c r="E724" s="3" t="n">
-        <v>117.93</v>
+        <v>124.25</v>
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22181,12 +22181,12 @@
       </c>
       <c r="B725" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C725" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D725" s="2" t="inlineStr">
@@ -22195,11 +22195,11 @@
         </is>
       </c>
       <c r="E725" s="3" t="n">
-        <v>115.53</v>
+        <v>122.61</v>
       </c>
       <c r="F725" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22211,12 +22211,12 @@
       </c>
       <c r="B726" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C726" s="2" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D726" s="2" t="inlineStr">
@@ -22225,11 +22225,11 @@
         </is>
       </c>
       <c r="E726" s="3" t="n">
-        <v>115.23</v>
+        <v>120.97</v>
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22241,12 +22241,12 @@
       </c>
       <c r="B727" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C727" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D727" s="2" t="inlineStr">
@@ -22255,11 +22255,11 @@
         </is>
       </c>
       <c r="E727" s="3" t="n">
-        <v>114.73</v>
+        <v>120.79</v>
       </c>
       <c r="F727" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22271,12 +22271,12 @@
       </c>
       <c r="B728" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C728" s="2" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="D728" s="2" t="inlineStr">
@@ -22285,11 +22285,11 @@
         </is>
       </c>
       <c r="E728" s="3" t="n">
-        <v>114.07</v>
+        <v>120.53</v>
       </c>
       <c r="F728" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22301,12 +22301,12 @@
       </c>
       <c r="B729" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C729" s="2" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="D729" s="2" t="inlineStr">
@@ -22315,11 +22315,11 @@
         </is>
       </c>
       <c r="E729" s="3" t="n">
-        <v>113.71</v>
+        <v>120.05</v>
       </c>
       <c r="F729" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22331,12 +22331,12 @@
       </c>
       <c r="B730" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C730" s="2" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="D730" s="2" t="inlineStr">
@@ -22345,7 +22345,7 @@
         </is>
       </c>
       <c r="E730" s="3" t="n">
-        <v>113.25</v>
+        <v>119.92</v>
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
@@ -22361,12 +22361,12 @@
       </c>
       <c r="B731" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="D731" s="2" t="inlineStr">
@@ -22375,11 +22375,11 @@
         </is>
       </c>
       <c r="E731" s="3" t="n">
-        <v>110.98</v>
+        <v>114.07</v>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22391,12 +22391,12 @@
       </c>
       <c r="B732" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="D732" s="2" t="inlineStr">
@@ -22405,11 +22405,11 @@
         </is>
       </c>
       <c r="E732" s="3" t="n">
-        <v>110.73</v>
+        <v>113.25</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22435,11 +22435,11 @@
         </is>
       </c>
       <c r="E733" s="3" t="n">
-        <v>110.39</v>
+        <v>112.53</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22451,12 +22451,12 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
@@ -22465,11 +22465,11 @@
         </is>
       </c>
       <c r="E734" s="3" t="n">
-        <v>109.33</v>
+        <v>112.05</v>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22481,12 +22481,12 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
@@ -22495,11 +22495,11 @@
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>107.67</v>
+        <v>109.72</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22511,12 +22511,12 @@
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
@@ -22525,11 +22525,11 @@
         </is>
       </c>
       <c r="E736" s="3" t="n">
-        <v>103.72</v>
+        <v>109.33</v>
       </c>
       <c r="F736" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22541,12 +22541,12 @@
       </c>
       <c r="B737" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="D737" s="2" t="inlineStr">
@@ -22555,11 +22555,11 @@
         </is>
       </c>
       <c r="E737" s="3" t="n">
-        <v>101.69</v>
+        <v>103.72</v>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22571,12 +22571,12 @@
       </c>
       <c r="B738" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D738" s="2" t="inlineStr">
@@ -22585,11 +22585,11 @@
         </is>
       </c>
       <c r="E738" s="3" t="n">
-        <v>100.93</v>
+        <v>103.15</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22601,12 +22601,12 @@
       </c>
       <c r="B739" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C739" s="2" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="D739" s="2" t="inlineStr">
@@ -22615,11 +22615,11 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>101.69</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22631,12 +22631,12 @@
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
@@ -22645,11 +22645,11 @@
         </is>
       </c>
       <c r="E740" s="3" t="n">
-        <v>99.44</v>
+        <v>100.93</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22661,12 +22661,12 @@
       </c>
       <c r="B741" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="D741" s="2" t="inlineStr">
@@ -22675,11 +22675,11 @@
         </is>
       </c>
       <c r="E741" s="3" t="n">
-        <v>99.01000000000001</v>
+        <v>100.73</v>
       </c>
       <c r="F741" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22691,12 +22691,12 @@
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>97.44</v>
+        <v>99.98</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22721,12 +22721,12 @@
       </c>
       <c r="B743" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C743" s="2" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="D743" s="2" t="inlineStr">
@@ -22735,11 +22735,11 @@
         </is>
       </c>
       <c r="E743" s="3" t="n">
-        <v>96.34999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22751,12 +22751,12 @@
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="D744" s="2" t="inlineStr">
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>95.59</v>
+        <v>97.55</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22781,12 +22781,12 @@
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr">
@@ -22795,11 +22795,11 @@
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>93.83</v>
+        <v>97.44</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22811,12 +22811,12 @@
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
@@ -22825,11 +22825,11 @@
         </is>
       </c>
       <c r="E746" s="3" t="n">
-        <v>93.52</v>
+        <v>96.78</v>
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22841,12 +22841,12 @@
       </c>
       <c r="B747" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C747" s="2" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="D747" s="2" t="inlineStr">
@@ -22855,11 +22855,11 @@
         </is>
       </c>
       <c r="E747" s="3" t="n">
-        <v>90.73</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="F747" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22871,12 +22871,12 @@
       </c>
       <c r="B748" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C748" s="2" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="D748" s="2" t="inlineStr">
@@ -22885,11 +22885,11 @@
         </is>
       </c>
       <c r="E748" s="3" t="n">
-        <v>89.79000000000001</v>
+        <v>91.63</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22901,25 +22901,25 @@
       </c>
       <c r="B749" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C749" s="2" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D749" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E749" s="3" t="n">
-        <v>89.48999999999999</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="F749" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22931,12 +22931,12 @@
       </c>
       <c r="B750" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C750" s="2" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="D750" s="2" t="inlineStr">
@@ -22945,11 +22945,11 @@
         </is>
       </c>
       <c r="E750" s="3" t="n">
-        <v>89.2</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F750" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22961,12 +22961,12 @@
       </c>
       <c r="B751" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C751" s="2" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D751" s="2" t="inlineStr">
@@ -22975,11 +22975,11 @@
         </is>
       </c>
       <c r="E751" s="3" t="n">
-        <v>87.73</v>
+        <v>89.52</v>
       </c>
       <c r="F751" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22991,21 +22991,21 @@
       </c>
       <c r="B752" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C752" s="2" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="D752" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
@@ -23021,12 +23021,12 @@
       </c>
       <c r="B753" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C753" s="2" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="D753" s="2" t="inlineStr">
@@ -23035,11 +23035,11 @@
         </is>
       </c>
       <c r="E753" s="3" t="n">
-        <v>85.54000000000001</v>
+        <v>88.59</v>
       </c>
       <c r="F753" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23051,12 +23051,12 @@
       </c>
       <c r="B754" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C754" s="2" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="D754" s="2" t="inlineStr">
@@ -23065,11 +23065,11 @@
         </is>
       </c>
       <c r="E754" s="3" t="n">
-        <v>83.59</v>
+        <v>87.73</v>
       </c>
       <c r="F754" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23081,12 +23081,12 @@
       </c>
       <c r="B755" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C755" s="2" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="D755" s="2" t="inlineStr">
@@ -23095,7 +23095,7 @@
         </is>
       </c>
       <c r="E755" s="3" t="n">
-        <v>82.18000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F755" s="2" t="inlineStr">
         <is>
@@ -23111,12 +23111,12 @@
       </c>
       <c r="B756" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C756" s="2" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="D756" s="2" t="inlineStr">
@@ -23125,11 +23125,11 @@
         </is>
       </c>
       <c r="E756" s="3" t="n">
-        <v>81.73</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23141,12 +23141,12 @@
       </c>
       <c r="B757" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C757" s="2" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="D757" s="2" t="inlineStr">
@@ -23155,7 +23155,7 @@
         </is>
       </c>
       <c r="E757" s="3" t="n">
-        <v>79.44</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F757" s="2" t="inlineStr">
         <is>
@@ -23171,12 +23171,12 @@
       </c>
       <c r="B758" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C758" s="2" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="D758" s="2" t="inlineStr">
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>79</v>
+        <v>81.73</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23201,12 +23201,12 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="D759" s="2" t="inlineStr">
@@ -23215,11 +23215,11 @@
         </is>
       </c>
       <c r="E759" s="3" t="n">
-        <v>75.19</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23231,12 +23231,12 @@
       </c>
       <c r="B760" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="C760" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="D760" s="2" t="inlineStr">
@@ -23245,11 +23245,11 @@
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>74.95</v>
+        <v>80.23</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23261,12 +23261,12 @@
       </c>
       <c r="B761" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C761" s="2" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="D761" s="2" t="inlineStr">
@@ -23275,11 +23275,11 @@
         </is>
       </c>
       <c r="E761" s="3" t="n">
-        <v>74.76000000000001</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="F761" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23291,25 +23291,25 @@
       </c>
       <c r="B762" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C762" s="2" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D762" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>79.52</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23321,12 +23321,12 @@
       </c>
       <c r="B763" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C763" s="2" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="D763" s="2" t="inlineStr">
@@ -23335,11 +23335,11 @@
         </is>
       </c>
       <c r="E763" s="3" t="n">
-        <v>74.56</v>
+        <v>79.44</v>
       </c>
       <c r="F763" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23351,12 +23351,12 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="D764" s="2" t="inlineStr">
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>73.44</v>
+        <v>77.33</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23381,12 +23381,12 @@
       </c>
       <c r="B765" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C765" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="D765" s="2" t="inlineStr">
@@ -23395,11 +23395,11 @@
         </is>
       </c>
       <c r="E765" s="3" t="n">
-        <v>72.89</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="F765" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23411,12 +23411,12 @@
       </c>
       <c r="B766" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C766" s="2" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="D766" s="2" t="inlineStr">
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>71.5</v>
+        <v>74.98</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23441,12 +23441,12 @@
       </c>
       <c r="B767" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C767" s="2" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="D767" s="2" t="inlineStr">
@@ -23455,7 +23455,7 @@
         </is>
       </c>
       <c r="E767" s="3" t="n">
-        <v>71.38</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="F767" s="2" t="inlineStr">
         <is>
@@ -23471,25 +23471,25 @@
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="D768" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>71.38</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23501,12 @@
       </c>
       <c r="B769" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C769" s="2" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="D769" s="2" t="inlineStr">
@@ -23515,11 +23515,11 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>70.48</v>
+        <v>74.48</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23531,12 +23531,12 @@
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
@@ -23545,11 +23545,11 @@
         </is>
       </c>
       <c r="E770" s="3" t="n">
-        <v>70.16</v>
+        <v>73.53</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23561,12 +23561,12 @@
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
@@ -23575,11 +23575,11 @@
         </is>
       </c>
       <c r="E771" s="3" t="n">
-        <v>68.5</v>
+        <v>71.89</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23591,12 +23591,12 @@
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -23605,11 +23605,11 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>68.48</v>
+        <v>71.72</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23621,12 +23621,12 @@
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="D773" s="2" t="inlineStr">
@@ -23635,11 +23635,11 @@
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>68.44</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23651,12 +23651,12 @@
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr">
@@ -23665,11 +23665,11 @@
         </is>
       </c>
       <c r="E774" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>71.38</v>
       </c>
       <c r="F774" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23681,12 +23681,12 @@
       </c>
       <c r="B775" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C775" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="D775" s="2" t="inlineStr">
@@ -23695,11 +23695,11 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>68.20999999999999</v>
+        <v>70.48</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23711,12 +23711,12 @@
       </c>
       <c r="B776" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C776" s="2" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="D776" s="2" t="inlineStr">
@@ -23725,11 +23725,11 @@
         </is>
       </c>
       <c r="E776" s="3" t="n">
-        <v>68.12</v>
+        <v>70.12</v>
       </c>
       <c r="F776" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23741,12 +23741,12 @@
       </c>
       <c r="B777" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C777" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D777" s="2" t="inlineStr">
@@ -23755,11 +23755,11 @@
         </is>
       </c>
       <c r="E777" s="3" t="n">
-        <v>67.14</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="F777" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23785,11 +23785,11 @@
         </is>
       </c>
       <c r="E778" s="3" t="n">
-        <v>65.61</v>
+        <v>69.73</v>
       </c>
       <c r="F778" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23801,12 +23801,12 @@
       </c>
       <c r="B779" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C779" s="2" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="D779" s="2" t="inlineStr">
@@ -23815,11 +23815,11 @@
         </is>
       </c>
       <c r="E779" s="3" t="n">
-        <v>64.59</v>
+        <v>68.88</v>
       </c>
       <c r="F779" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23831,12 +23831,12 @@
       </c>
       <c r="B780" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C780" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="D780" s="2" t="inlineStr">
@@ -23845,11 +23845,11 @@
         </is>
       </c>
       <c r="E780" s="3" t="n">
-        <v>64.59</v>
+        <v>68.86</v>
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23861,12 +23861,12 @@
       </c>
       <c r="B781" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C781" s="2" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="D781" s="2" t="inlineStr">
@@ -23875,11 +23875,11 @@
         </is>
       </c>
       <c r="E781" s="3" t="n">
-        <v>63.69</v>
+        <v>68.5</v>
       </c>
       <c r="F781" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23891,12 +23891,12 @@
       </c>
       <c r="B782" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C782" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="D782" s="2" t="inlineStr">
@@ -23905,11 +23905,11 @@
         </is>
       </c>
       <c r="E782" s="3" t="n">
-        <v>63.6</v>
+        <v>65.95</v>
       </c>
       <c r="F782" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23921,12 +23921,12 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="D783" s="2" t="inlineStr">
@@ -23935,11 +23935,11 @@
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>63.48</v>
+        <v>65.84</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23951,12 +23951,12 @@
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
@@ -23965,11 +23965,11 @@
         </is>
       </c>
       <c r="E784" s="3" t="n">
-        <v>63.3</v>
+        <v>65.67</v>
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23981,12 +23981,12 @@
       </c>
       <c r="B785" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C785" s="2" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="D785" s="2" t="inlineStr">
@@ -23995,11 +23995,11 @@
         </is>
       </c>
       <c r="E785" s="3" t="n">
-        <v>62.79</v>
+        <v>65.48</v>
       </c>
       <c r="F785" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24011,12 +24011,12 @@
       </c>
       <c r="B786" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C786" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D786" s="2" t="inlineStr">
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>61.96</v>
+        <v>64.22</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24041,12 +24041,12 @@
       </c>
       <c r="B787" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C787" s="2" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="D787" s="2" t="inlineStr">
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>61.93</v>
+        <v>63.6</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24071,12 +24071,12 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D788" s="2" t="inlineStr">
@@ -24085,11 +24085,11 @@
         </is>
       </c>
       <c r="E788" s="3" t="n">
-        <v>60.41</v>
+        <v>61.96</v>
       </c>
       <c r="F788" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>59.98</v>
+        <v>61</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24145,11 +24145,11 @@
         </is>
       </c>
       <c r="E790" s="3" t="n">
-        <v>59.78</v>
+        <v>60.09</v>
       </c>
       <c r="F790" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24161,25 +24161,25 @@
       </c>
       <c r="B791" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C791" s="2" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="D791" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E791" s="3" t="n">
-        <v>57.22</v>
+        <v>57.63</v>
       </c>
       <c r="F791" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24191,21 +24191,21 @@
       </c>
       <c r="B792" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C792" s="2" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="D792" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E792" s="3" t="n">
-        <v>56.5</v>
+        <v>57.22</v>
       </c>
       <c r="F792" s="2" t="inlineStr">
         <is>
@@ -24221,12 +24221,12 @@
       </c>
       <c r="B793" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C793" s="2" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="D793" s="2" t="inlineStr">
@@ -24235,11 +24235,11 @@
         </is>
       </c>
       <c r="E793" s="3" t="n">
-        <v>54.72</v>
+        <v>56.5</v>
       </c>
       <c r="F793" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24251,12 +24251,12 @@
       </c>
       <c r="B794" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C794" s="2" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="D794" s="2" t="inlineStr">
@@ -24265,11 +24265,11 @@
         </is>
       </c>
       <c r="E794" s="3" t="n">
-        <v>53.95</v>
+        <v>55.7</v>
       </c>
       <c r="F794" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24281,12 +24281,12 @@
       </c>
       <c r="B795" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C795" s="2" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="D795" s="2" t="inlineStr">
@@ -24295,11 +24295,11 @@
         </is>
       </c>
       <c r="E795" s="3" t="n">
-        <v>53.86</v>
+        <v>55.14</v>
       </c>
       <c r="F795" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 09:49</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24311,12 +24311,12 @@
       </c>
       <c r="B796" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C796" s="2" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="D796" s="2" t="inlineStr">
@@ -24325,11 +24325,11 @@
         </is>
       </c>
       <c r="E796" s="3" t="n">
-        <v>53.52</v>
+        <v>54.45</v>
       </c>
       <c r="F796" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24341,12 +24341,12 @@
       </c>
       <c r="B797" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C797" s="2" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="D797" s="2" t="inlineStr">
@@ -24355,7 +24355,7 @@
         </is>
       </c>
       <c r="E797" s="3" t="n">
-        <v>52.57</v>
+        <v>53.95</v>
       </c>
       <c r="F797" s="2" t="inlineStr">
         <is>
@@ -24371,12 +24371,12 @@
       </c>
       <c r="B798" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C798" s="2" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="D798" s="2" t="inlineStr">
@@ -24385,11 +24385,11 @@
         </is>
       </c>
       <c r="E798" s="3" t="n">
-        <v>52.42</v>
+        <v>53.51</v>
       </c>
       <c r="F798" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="B799" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C799" s="2" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="D799" s="2" t="inlineStr">
@@ -24415,11 +24415,11 @@
         </is>
       </c>
       <c r="E799" s="3" t="n">
-        <v>51.94</v>
+        <v>52.57</v>
       </c>
       <c r="F799" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24431,12 +24431,12 @@
       </c>
       <c r="B800" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C800" s="2" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="D800" s="2" t="inlineStr">
@@ -24445,11 +24445,11 @@
         </is>
       </c>
       <c r="E800" s="3" t="n">
-        <v>50.13</v>
+        <v>52.42</v>
       </c>
       <c r="F800" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -24475,11 +24475,11 @@
         </is>
       </c>
       <c r="E801" s="3" t="n">
-        <v>49.68</v>
+        <v>50.68</v>
       </c>
       <c r="F801" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24491,12 +24491,12 @@
       </c>
       <c r="B802" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="C802" s="2" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="D802" s="2" t="inlineStr">
@@ -24505,11 +24505,11 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>49.67</v>
+        <v>50.23</v>
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24521,12 +24521,12 @@
       </c>
       <c r="B803" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C803" s="2" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="D803" s="2" t="inlineStr">
@@ -24535,11 +24535,11 @@
         </is>
       </c>
       <c r="E803" s="3" t="n">
-        <v>48.75</v>
+        <v>50.13</v>
       </c>
       <c r="F803" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24551,12 +24551,12 @@
       </c>
       <c r="B804" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C804" s="2" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="D804" s="2" t="inlineStr">
@@ -24565,11 +24565,11 @@
         </is>
       </c>
       <c r="E804" s="3" t="n">
-        <v>48.18</v>
+        <v>49.31</v>
       </c>
       <c r="F804" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24581,12 +24581,12 @@
       </c>
       <c r="B805" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C805" s="2" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="D805" s="2" t="inlineStr">
@@ -24595,11 +24595,11 @@
         </is>
       </c>
       <c r="E805" s="3" t="n">
-        <v>48.04</v>
+        <v>49.25</v>
       </c>
       <c r="F805" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24611,12 +24611,12 @@
       </c>
       <c r="B806" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C806" s="2" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="D806" s="2" t="inlineStr">
@@ -24625,11 +24625,11 @@
         </is>
       </c>
       <c r="E806" s="3" t="n">
-        <v>47.99</v>
+        <v>48.04</v>
       </c>
       <c r="F806" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24641,12 +24641,12 @@
       </c>
       <c r="B807" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C807" s="2" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="D807" s="2" t="inlineStr">
@@ -24655,11 +24655,11 @@
         </is>
       </c>
       <c r="E807" s="3" t="n">
-        <v>47.23</v>
+        <v>47.99</v>
       </c>
       <c r="F807" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24671,12 +24671,12 @@
       </c>
       <c r="B808" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C808" s="2" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="D808" s="2" t="inlineStr">
@@ -24685,11 +24685,11 @@
         </is>
       </c>
       <c r="E808" s="3" t="n">
-        <v>46.4</v>
+        <v>47.23</v>
       </c>
       <c r="F808" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24701,12 +24701,12 @@
       </c>
       <c r="B809" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C809" s="2" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="D809" s="2" t="inlineStr">
@@ -24715,11 +24715,11 @@
         </is>
       </c>
       <c r="E809" s="3" t="n">
-        <v>44.8</v>
+        <v>46.4</v>
       </c>
       <c r="F809" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24731,12 +24731,12 @@
       </c>
       <c r="B810" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C810" s="2" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="D810" s="2" t="inlineStr">
@@ -24745,11 +24745,11 @@
         </is>
       </c>
       <c r="E810" s="3" t="n">
-        <v>44.19</v>
+        <v>44.8</v>
       </c>
       <c r="F810" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24775,11 +24775,11 @@
         </is>
       </c>
       <c r="E811" s="3" t="n">
-        <v>42.65</v>
+        <v>44.5</v>
       </c>
       <c r="F811" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24791,12 +24791,12 @@
       </c>
       <c r="B812" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C812" s="2" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="D812" s="2" t="inlineStr">
@@ -24805,11 +24805,11 @@
         </is>
       </c>
       <c r="E812" s="3" t="n">
-        <v>41.39</v>
+        <v>44.19</v>
       </c>
       <c r="F812" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24821,12 +24821,12 @@
       </c>
       <c r="B813" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C813" s="2" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="D813" s="2" t="inlineStr">
@@ -24835,11 +24835,11 @@
         </is>
       </c>
       <c r="E813" s="3" t="n">
-        <v>39.58</v>
+        <v>42.84</v>
       </c>
       <c r="F813" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24851,12 +24851,12 @@
       </c>
       <c r="B814" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C814" s="2" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="D814" s="2" t="inlineStr">
@@ -24865,11 +24865,11 @@
         </is>
       </c>
       <c r="E814" s="3" t="n">
-        <v>39.39</v>
+        <v>40.54</v>
       </c>
       <c r="F814" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24881,12 +24881,12 @@
       </c>
       <c r="B815" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C815" s="2" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="D815" s="2" t="inlineStr">
@@ -24895,11 +24895,11 @@
         </is>
       </c>
       <c r="E815" s="3" t="n">
-        <v>39.2</v>
+        <v>39.39</v>
       </c>
       <c r="F815" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24911,12 +24911,12 @@
       </c>
       <c r="B816" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C816" s="2" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="D816" s="2" t="inlineStr">
@@ -24925,11 +24925,11 @@
         </is>
       </c>
       <c r="E816" s="3" t="n">
-        <v>37.65</v>
+        <v>39.2</v>
       </c>
       <c r="F816" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24941,12 +24941,12 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="D817" s="2" t="inlineStr">
@@ -24955,11 +24955,11 @@
         </is>
       </c>
       <c r="E817" s="3" t="n">
-        <v>36.75</v>
+        <v>37.65</v>
       </c>
       <c r="F817" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24971,12 +24971,12 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="D818" s="2" t="inlineStr">
@@ -24985,11 +24985,11 @@
         </is>
       </c>
       <c r="E818" s="3" t="n">
-        <v>36.59</v>
+        <v>37.48</v>
       </c>
       <c r="F818" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25001,12 +25001,12 @@
       </c>
       <c r="B819" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C819" s="2" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="D819" s="2" t="inlineStr">
@@ -25015,11 +25015,11 @@
         </is>
       </c>
       <c r="E819" s="3" t="n">
-        <v>36.31</v>
+        <v>36.75</v>
       </c>
       <c r="F819" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25031,12 +25031,12 @@
       </c>
       <c r="B820" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C820" s="2" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="D820" s="2" t="inlineStr">
@@ -25045,11 +25045,11 @@
         </is>
       </c>
       <c r="E820" s="3" t="n">
-        <v>34.05</v>
+        <v>36.59</v>
       </c>
       <c r="F820" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -25061,12 +25061,12 @@
       </c>
       <c r="B821" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C821" s="2" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="D821" s="2" t="inlineStr">
@@ -25075,11 +25075,11 @@
         </is>
       </c>
       <c r="E821" s="3" t="n">
-        <v>31.86</v>
+        <v>36.31</v>
       </c>
       <c r="F821" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25091,12 +25091,12 @@
       </c>
       <c r="B822" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C822" s="2" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="D822" s="2" t="inlineStr">
@@ -25105,11 +25105,11 @@
         </is>
       </c>
       <c r="E822" s="3" t="n">
-        <v>31.36</v>
+        <v>34.64</v>
       </c>
       <c r="F822" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25121,12 +25121,12 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="D823" s="2" t="inlineStr">
@@ -25135,7 +25135,7 @@
         </is>
       </c>
       <c r="E823" s="3" t="n">
-        <v>31.24</v>
+        <v>34.05</v>
       </c>
       <c r="F823" s="2" t="inlineStr">
         <is>
@@ -25151,12 +25151,12 @@
       </c>
       <c r="B824" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C824" s="2" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="D824" s="2" t="inlineStr">
@@ -25165,11 +25165,11 @@
         </is>
       </c>
       <c r="E824" s="3" t="n">
-        <v>29.67</v>
+        <v>31.83</v>
       </c>
       <c r="F824" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25181,12 +25181,12 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="D825" s="2" t="inlineStr">
@@ -25195,7 +25195,7 @@
         </is>
       </c>
       <c r="E825" s="3" t="n">
-        <v>29.27</v>
+        <v>31.24</v>
       </c>
       <c r="F825" s="2" t="inlineStr">
         <is>
@@ -25211,12 +25211,12 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="D826" s="2" t="inlineStr">
@@ -25225,11 +25225,11 @@
         </is>
       </c>
       <c r="E826" s="3" t="n">
-        <v>29.23</v>
+        <v>31.1</v>
       </c>
       <c r="F826" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25241,12 +25241,12 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="D827" s="2" t="inlineStr">
@@ -25255,11 +25255,11 @@
         </is>
       </c>
       <c r="E827" s="3" t="n">
-        <v>29.1</v>
+        <v>30.62</v>
       </c>
       <c r="F827" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25271,12 +25271,12 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="D828" s="2" t="inlineStr">
@@ -25285,11 +25285,11 @@
         </is>
       </c>
       <c r="E828" s="3" t="n">
-        <v>29.06</v>
+        <v>30.33</v>
       </c>
       <c r="F828" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25301,12 +25301,12 @@
       </c>
       <c r="B829" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C829" s="2" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="D829" s="2" t="inlineStr">
@@ -25315,11 +25315,11 @@
         </is>
       </c>
       <c r="E829" s="3" t="n">
-        <v>28.85</v>
+        <v>30.32</v>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25331,12 +25331,12 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="D830" s="2" t="inlineStr">
@@ -25345,11 +25345,11 @@
         </is>
       </c>
       <c r="E830" s="3" t="n">
-        <v>28.82</v>
+        <v>29.67</v>
       </c>
       <c r="F830" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -25361,12 +25361,12 @@
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C831" s="2" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="D831" s="2" t="inlineStr">
@@ -25375,11 +25375,11 @@
         </is>
       </c>
       <c r="E831" s="3" t="n">
-        <v>28</v>
+        <v>29.27</v>
       </c>
       <c r="F831" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25391,12 +25391,12 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="D832" s="2" t="inlineStr">
@@ -25405,11 +25405,11 @@
         </is>
       </c>
       <c r="E832" s="3" t="n">
-        <v>27.8</v>
+        <v>28.85</v>
       </c>
       <c r="F832" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25421,12 +25421,12 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="D833" s="2" t="inlineStr">
@@ -25435,11 +25435,11 @@
         </is>
       </c>
       <c r="E833" s="3" t="n">
-        <v>26.64</v>
+        <v>28.31</v>
       </c>
       <c r="F833" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25451,25 +25451,25 @@
       </c>
       <c r="B834" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C834" s="2" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D834" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E834" s="3" t="n">
-        <v>26.15</v>
+        <v>26.8</v>
       </c>
       <c r="F834" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25481,12 +25481,12 @@
       </c>
       <c r="B835" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C835" s="2" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="D835" s="2" t="inlineStr">
@@ -25495,11 +25495,11 @@
         </is>
       </c>
       <c r="E835" s="3" t="n">
-        <v>25.24</v>
+        <v>26.15</v>
       </c>
       <c r="F835" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25511,25 +25511,25 @@
       </c>
       <c r="B836" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C836" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="D836" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E836" s="3" t="n">
-        <v>24.52</v>
+        <v>25.32</v>
       </c>
       <c r="F836" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25825,11 +25825,11 @@
         </is>
       </c>
       <c r="E846" s="3" t="n">
-        <v>17.84</v>
+        <v>18.25</v>
       </c>
       <c r="F846" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25931,12 +25931,12 @@
       </c>
       <c r="B850" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C850" s="2" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="D850" s="2" t="inlineStr">
@@ -25945,11 +25945,11 @@
         </is>
       </c>
       <c r="E850" s="3" t="n">
-        <v>15.77</v>
+        <v>17.2</v>
       </c>
       <c r="F850" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25961,12 +25961,12 @@
       </c>
       <c r="B851" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C851" s="2" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="D851" s="2" t="inlineStr">
@@ -25975,7 +25975,7 @@
         </is>
       </c>
       <c r="E851" s="3" t="n">
-        <v>15.35</v>
+        <v>15.77</v>
       </c>
       <c r="F851" s="2" t="inlineStr">
         <is>
@@ -25991,12 +25991,12 @@
       </c>
       <c r="B852" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C852" s="2" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="D852" s="2" t="inlineStr">
@@ -26005,11 +26005,11 @@
         </is>
       </c>
       <c r="E852" s="3" t="n">
-        <v>15.16</v>
+        <v>15.35</v>
       </c>
       <c r="F852" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26365,11 +26365,11 @@
         </is>
       </c>
       <c r="E864" s="3" t="n">
-        <v>6.18</v>
+        <v>6.53</v>
       </c>
       <c r="F864" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26 17:54</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2400.99</v>
+        <v>2401.61</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -19795,11 +19795,11 @@
         </is>
       </c>
       <c r="E645" s="3" t="n">
-        <v>2304.08</v>
+        <v>2357.71</v>
       </c>
       <c r="F645" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -19885,11 +19885,11 @@
         </is>
       </c>
       <c r="E648" s="3" t="n">
-        <v>1187.69</v>
+        <v>1211.26</v>
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>1178.79</v>
+        <v>1193.55</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -19945,11 +19945,11 @@
         </is>
       </c>
       <c r="E650" s="3" t="n">
-        <v>938.39</v>
+        <v>984.12</v>
       </c>
       <c r="F650" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20005,11 +20005,11 @@
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>804</v>
+        <v>805.87</v>
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20065,11 +20065,11 @@
         </is>
       </c>
       <c r="E654" s="3" t="n">
-        <v>733.67</v>
+        <v>737.59</v>
       </c>
       <c r="F654" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20095,11 +20095,11 @@
         </is>
       </c>
       <c r="E655" s="3" t="n">
-        <v>692.98</v>
+        <v>709.95</v>
       </c>
       <c r="F655" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20155,11 +20155,11 @@
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>631.59</v>
+        <v>634.41</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20185,11 +20185,11 @@
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>622.96</v>
+        <v>631.08</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20245,11 +20245,11 @@
         </is>
       </c>
       <c r="E660" s="3" t="n">
-        <v>572.29</v>
+        <v>575.9299999999999</v>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20261,25 +20261,25 @@
       </c>
       <c r="B661" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C661" s="2" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="D661" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>557.1900000000001</v>
+        <v>558.51</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20291,25 +20291,25 @@
       </c>
       <c r="B662" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C662" s="2" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="D662" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E662" s="3" t="n">
-        <v>550.58</v>
+        <v>557.1900000000001</v>
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20321,25 +20321,25 @@
       </c>
       <c r="B663" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C663" s="2" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="D663" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E663" s="3" t="n">
-        <v>534.96</v>
+        <v>540.91</v>
       </c>
       <c r="F663" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20351,12 +20351,12 @@
       </c>
       <c r="B664" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
@@ -20365,11 +20365,11 @@
         </is>
       </c>
       <c r="E664" s="3" t="n">
-        <v>531.08</v>
+        <v>539.74</v>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20381,25 +20381,25 @@
       </c>
       <c r="B665" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E665" s="3" t="n">
-        <v>529.0599999999999</v>
+        <v>536.3</v>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20425,11 +20425,11 @@
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>528.42</v>
+        <v>533.87</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20471,12 +20471,12 @@
       </c>
       <c r="B668" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066901JZZ</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C668" s="2" t="inlineStr">
         <is>
-          <t>812926</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="D668" s="2" t="inlineStr">
@@ -20485,11 +20485,11 @@
         </is>
       </c>
       <c r="E668" s="3" t="n">
-        <v>500.46</v>
+        <v>505.38</v>
       </c>
       <c r="F668" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20501,12 +20501,12 @@
       </c>
       <c r="B669" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="C669" s="2" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>812926</t>
         </is>
       </c>
       <c r="D669" s="2" t="inlineStr">
@@ -20515,11 +20515,11 @@
         </is>
       </c>
       <c r="E669" s="3" t="n">
-        <v>490.29</v>
+        <v>500.46</v>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20545,11 +20545,11 @@
         </is>
       </c>
       <c r="E670" s="3" t="n">
-        <v>484.64</v>
+        <v>489.79</v>
       </c>
       <c r="F670" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20605,11 +20605,11 @@
         </is>
       </c>
       <c r="E672" s="3" t="n">
-        <v>458.37</v>
+        <v>463.77</v>
       </c>
       <c r="F672" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20695,11 +20695,11 @@
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>395.6</v>
+        <v>396.94</v>
       </c>
       <c r="F675" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20725,11 +20725,11 @@
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>371.5</v>
+        <v>382.08</v>
       </c>
       <c r="F676" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20755,11 +20755,11 @@
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>359.74</v>
+        <v>367.13</v>
       </c>
       <c r="F677" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20771,12 +20771,12 @@
       </c>
       <c r="B678" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C678" s="2" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="D678" s="2" t="inlineStr">
@@ -20785,11 +20785,11 @@
         </is>
       </c>
       <c r="E678" s="3" t="n">
-        <v>338.03</v>
+        <v>339.55</v>
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20801,12 +20801,12 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="D679" s="2" t="inlineStr">
@@ -20815,7 +20815,7 @@
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>337.65</v>
+        <v>338.03</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
@@ -20845,11 +20845,11 @@
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>327.65</v>
+        <v>327.78</v>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20905,11 +20905,11 @@
         </is>
       </c>
       <c r="E682" s="3" t="n">
-        <v>281.73</v>
+        <v>287.5</v>
       </c>
       <c r="F682" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20935,11 +20935,11 @@
         </is>
       </c>
       <c r="E683" s="3" t="n">
-        <v>279.54</v>
+        <v>280.86</v>
       </c>
       <c r="F683" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20965,11 +20965,11 @@
         </is>
       </c>
       <c r="E684" s="3" t="n">
-        <v>272.49</v>
+        <v>275.84</v>
       </c>
       <c r="F684" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20981,25 +20981,25 @@
       </c>
       <c r="B685" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563510TWC</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C685" s="2" t="inlineStr">
         <is>
-          <t>814433</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="D685" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E685" s="3" t="n">
-        <v>267.37</v>
+        <v>274.35</v>
       </c>
       <c r="F685" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21011,25 +21011,25 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="D686" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E686" s="3" t="n">
-        <v>261.99</v>
+        <v>267.37</v>
       </c>
       <c r="F686" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21041,12 +21041,12 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="D687" s="2" t="inlineStr">
@@ -21055,11 +21055,11 @@
         </is>
       </c>
       <c r="E687" s="3" t="n">
-        <v>253.27</v>
+        <v>256.62</v>
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21071,12 +21071,12 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="D688" s="2" t="inlineStr">
@@ -21085,11 +21085,11 @@
         </is>
       </c>
       <c r="E688" s="3" t="n">
-        <v>246.96</v>
+        <v>255.93</v>
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21115,11 +21115,11 @@
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>246.44</v>
+        <v>249.89</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21131,12 +21131,12 @@
       </c>
       <c r="B690" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C690" s="2" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="D690" s="2" t="inlineStr">
@@ -21145,11 +21145,11 @@
         </is>
       </c>
       <c r="E690" s="3" t="n">
-        <v>244.18</v>
+        <v>246.96</v>
       </c>
       <c r="F690" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21205,11 +21205,11 @@
         </is>
       </c>
       <c r="E692" s="3" t="n">
-        <v>225.47</v>
+        <v>228.99</v>
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21221,12 +21221,12 @@
       </c>
       <c r="B693" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C693" s="2" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="D693" s="2" t="inlineStr">
@@ -21235,11 +21235,11 @@
         </is>
       </c>
       <c r="E693" s="3" t="n">
-        <v>220.53</v>
+        <v>224.49</v>
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="B694" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C694" s="2" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="D694" s="2" t="inlineStr">
@@ -21265,11 +21265,11 @@
         </is>
       </c>
       <c r="E694" s="3" t="n">
-        <v>217.41</v>
+        <v>221.61</v>
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21281,12 +21281,12 @@
       </c>
       <c r="B695" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C695" s="2" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="D695" s="2" t="inlineStr">
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>215.03</v>
+        <v>218.03</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21325,11 +21325,11 @@
         </is>
       </c>
       <c r="E696" s="3" t="n">
-        <v>213.49</v>
+        <v>217.83</v>
       </c>
       <c r="F696" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>208.57</v>
+        <v>210.96</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="E698" s="3" t="n">
-        <v>208.06</v>
+        <v>210.41</v>
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>196.63</v>
+        <v>201.14</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21445,11 +21445,11 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>189.37</v>
+        <v>193.19</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>185.94</v>
+        <v>187.32</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>172.08</v>
+        <v>174.51</v>
       </c>
       <c r="F703" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21565,11 +21565,11 @@
         </is>
       </c>
       <c r="E704" s="3" t="n">
-        <v>171.18</v>
+        <v>172.45</v>
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>160.49</v>
+        <v>169.19</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21611,12 +21611,12 @@
       </c>
       <c r="B706" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C706" s="2" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="D706" s="2" t="inlineStr">
@@ -21625,11 +21625,11 @@
         </is>
       </c>
       <c r="E706" s="3" t="n">
-        <v>158.82</v>
+        <v>159.91</v>
       </c>
       <c r="F706" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21641,12 +21641,12 @@
       </c>
       <c r="B707" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C707" s="2" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="D707" s="2" t="inlineStr">
@@ -21655,11 +21655,11 @@
         </is>
       </c>
       <c r="E707" s="3" t="n">
-        <v>157.87</v>
+        <v>158.82</v>
       </c>
       <c r="F707" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21685,11 +21685,11 @@
         </is>
       </c>
       <c r="E708" s="3" t="n">
-        <v>151.74</v>
+        <v>152.28</v>
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21731,12 +21731,12 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="D710" s="2" t="inlineStr">
@@ -21745,11 +21745,11 @@
         </is>
       </c>
       <c r="E710" s="3" t="n">
-        <v>136.89</v>
+        <v>143.71</v>
       </c>
       <c r="F710" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21775,11 +21775,11 @@
         </is>
       </c>
       <c r="E711" s="3" t="n">
-        <v>136.06</v>
+        <v>138.98</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21791,12 +21791,12 @@
       </c>
       <c r="B712" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C712" s="2" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D712" s="2" t="inlineStr">
@@ -21805,11 +21805,11 @@
         </is>
       </c>
       <c r="E712" s="3" t="n">
-        <v>134.54</v>
+        <v>137.22</v>
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21821,12 +21821,12 @@
       </c>
       <c r="B713" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C713" s="2" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="D713" s="2" t="inlineStr">
@@ -21835,11 +21835,11 @@
         </is>
       </c>
       <c r="E713" s="3" t="n">
-        <v>133.91</v>
+        <v>137.03</v>
       </c>
       <c r="F713" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21851,12 +21851,12 @@
       </c>
       <c r="B714" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C714" s="2" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="D714" s="2" t="inlineStr">
@@ -21865,11 +21865,11 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>132.39</v>
+        <v>135.54</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21881,12 +21881,12 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="D715" s="2" t="inlineStr">
@@ -21895,11 +21895,11 @@
         </is>
       </c>
       <c r="E715" s="3" t="n">
-        <v>131.83</v>
+        <v>134.03</v>
       </c>
       <c r="F715" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21911,12 +21911,12 @@
       </c>
       <c r="B716" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C716" s="2" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="D716" s="2" t="inlineStr">
@@ -21925,7 +21925,7 @@
         </is>
       </c>
       <c r="E716" s="3" t="n">
-        <v>131.31</v>
+        <v>132.39</v>
       </c>
       <c r="F716" s="2" t="inlineStr">
         <is>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B717" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C717" s="2" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="D717" s="2" t="inlineStr">
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>131.04</v>
+        <v>132.12</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -21971,12 +21971,12 @@
       </c>
       <c r="B718" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr">
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>128.6</v>
+        <v>131.31</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22001,12 +22001,12 @@
       </c>
       <c r="B719" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C719" s="2" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="D719" s="2" t="inlineStr">
@@ -22015,11 +22015,11 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>127.92</v>
+        <v>131.19</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22031,12 +22031,12 @@
       </c>
       <c r="B720" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C720" s="2" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="D720" s="2" t="inlineStr">
@@ -22045,11 +22045,11 @@
         </is>
       </c>
       <c r="E720" s="3" t="n">
-        <v>127.83</v>
+        <v>131.04</v>
       </c>
       <c r="F720" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22061,12 +22061,12 @@
       </c>
       <c r="B721" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C721" s="2" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="D721" s="2" t="inlineStr">
@@ -22075,11 +22075,11 @@
         </is>
       </c>
       <c r="E721" s="3" t="n">
-        <v>127.72</v>
+        <v>130.22</v>
       </c>
       <c r="F721" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22091,12 +22091,12 @@
       </c>
       <c r="B722" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C722" s="2" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="D722" s="2" t="inlineStr">
@@ -22105,11 +22105,11 @@
         </is>
       </c>
       <c r="E722" s="3" t="n">
-        <v>126.48</v>
+        <v>129.31</v>
       </c>
       <c r="F722" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22121,12 +22121,12 @@
       </c>
       <c r="B723" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C723" s="2" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D723" s="2" t="inlineStr">
@@ -22135,11 +22135,11 @@
         </is>
       </c>
       <c r="E723" s="3" t="n">
-        <v>126.03</v>
+        <v>128.61</v>
       </c>
       <c r="F723" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22151,12 +22151,12 @@
       </c>
       <c r="B724" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C724" s="2" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="D724" s="2" t="inlineStr">
@@ -22165,11 +22165,11 @@
         </is>
       </c>
       <c r="E724" s="3" t="n">
-        <v>124.25</v>
+        <v>127.92</v>
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22181,12 +22181,12 @@
       </c>
       <c r="B725" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C725" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D725" s="2" t="inlineStr">
@@ -22195,11 +22195,11 @@
         </is>
       </c>
       <c r="E725" s="3" t="n">
-        <v>122.61</v>
+        <v>127.31</v>
       </c>
       <c r="F725" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22211,12 +22211,12 @@
       </c>
       <c r="B726" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C726" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="D726" s="2" t="inlineStr">
@@ -22225,11 +22225,11 @@
         </is>
       </c>
       <c r="E726" s="3" t="n">
-        <v>120.97</v>
+        <v>126.03</v>
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22241,12 +22241,12 @@
       </c>
       <c r="B727" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C727" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D727" s="2" t="inlineStr">
@@ -22255,11 +22255,11 @@
         </is>
       </c>
       <c r="E727" s="3" t="n">
-        <v>120.79</v>
+        <v>125.87</v>
       </c>
       <c r="F727" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22271,12 +22271,12 @@
       </c>
       <c r="B728" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C728" s="2" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="D728" s="2" t="inlineStr">
@@ -22285,11 +22285,11 @@
         </is>
       </c>
       <c r="E728" s="3" t="n">
-        <v>120.53</v>
+        <v>124.15</v>
       </c>
       <c r="F728" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22301,12 +22301,12 @@
       </c>
       <c r="B729" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C729" s="2" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="D729" s="2" t="inlineStr">
@@ -22315,11 +22315,11 @@
         </is>
       </c>
       <c r="E729" s="3" t="n">
-        <v>120.05</v>
+        <v>120.87</v>
       </c>
       <c r="F729" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22361,12 +22361,12 @@
       </c>
       <c r="B731" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="D731" s="2" t="inlineStr">
@@ -22375,11 +22375,11 @@
         </is>
       </c>
       <c r="E731" s="3" t="n">
-        <v>114.07</v>
+        <v>114.11</v>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22391,12 +22391,12 @@
       </c>
       <c r="B732" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="D732" s="2" t="inlineStr">
@@ -22405,11 +22405,11 @@
         </is>
       </c>
       <c r="E732" s="3" t="n">
-        <v>113.25</v>
+        <v>114.07</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22421,12 +22421,12 @@
       </c>
       <c r="B733" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="D733" s="2" t="inlineStr">
@@ -22435,11 +22435,11 @@
         </is>
       </c>
       <c r="E733" s="3" t="n">
-        <v>112.53</v>
+        <v>113.3</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22451,12 +22451,12 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
@@ -22465,11 +22465,11 @@
         </is>
       </c>
       <c r="E734" s="3" t="n">
-        <v>112.05</v>
+        <v>113.25</v>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22495,11 +22495,11 @@
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>109.72</v>
+        <v>110.18</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22541,12 +22541,12 @@
       </c>
       <c r="B737" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="D737" s="2" t="inlineStr">
@@ -22555,11 +22555,11 @@
         </is>
       </c>
       <c r="E737" s="3" t="n">
-        <v>103.72</v>
+        <v>108.26</v>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22571,12 +22571,12 @@
       </c>
       <c r="B738" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="D738" s="2" t="inlineStr">
@@ -22585,11 +22585,11 @@
         </is>
       </c>
       <c r="E738" s="3" t="n">
-        <v>103.15</v>
+        <v>107.56</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22601,12 +22601,12 @@
       </c>
       <c r="B739" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C739" s="2" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="D739" s="2" t="inlineStr">
@@ -22615,11 +22615,11 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>101.69</v>
+        <v>103.72</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22631,12 +22631,12 @@
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
@@ -22645,11 +22645,11 @@
         </is>
       </c>
       <c r="E740" s="3" t="n">
-        <v>100.93</v>
+        <v>103.16</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22661,12 +22661,12 @@
       </c>
       <c r="B741" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D741" s="2" t="inlineStr">
@@ -22675,7 +22675,7 @@
         </is>
       </c>
       <c r="E741" s="3" t="n">
-        <v>100.73</v>
+        <v>103.15</v>
       </c>
       <c r="F741" s="2" t="inlineStr">
         <is>
@@ -22691,12 +22691,12 @@
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>99.98</v>
+        <v>102.99</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22721,12 +22721,12 @@
       </c>
       <c r="B743" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C743" s="2" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="D743" s="2" t="inlineStr">
@@ -22735,7 +22735,7 @@
         </is>
       </c>
       <c r="E743" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>100.93</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
@@ -22751,12 +22751,12 @@
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="D744" s="2" t="inlineStr">
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>97.55</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22781,12 +22781,12 @@
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr">
@@ -22795,11 +22795,11 @@
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>97.44</v>
+        <v>98.78</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22811,12 +22811,12 @@
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
@@ -22825,11 +22825,11 @@
         </is>
       </c>
       <c r="E746" s="3" t="n">
-        <v>96.78</v>
+        <v>97.44</v>
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22841,12 +22841,12 @@
       </c>
       <c r="B747" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C747" s="2" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D747" s="2" t="inlineStr">
@@ -22855,11 +22855,11 @@
         </is>
       </c>
       <c r="E747" s="3" t="n">
-        <v>93.95999999999999</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="F747" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22871,12 +22871,12 @@
       </c>
       <c r="B748" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C748" s="2" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="D748" s="2" t="inlineStr">
@@ -22885,11 +22885,11 @@
         </is>
       </c>
       <c r="E748" s="3" t="n">
-        <v>91.63</v>
+        <v>97.06</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22901,12 +22901,12 @@
       </c>
       <c r="B749" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C749" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D749" s="2" t="inlineStr">
@@ -22915,11 +22915,11 @@
         </is>
       </c>
       <c r="E749" s="3" t="n">
-        <v>90.73999999999999</v>
+        <v>95.22</v>
       </c>
       <c r="F749" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22931,12 +22931,12 @@
       </c>
       <c r="B750" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C750" s="2" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="D750" s="2" t="inlineStr">
@@ -22945,11 +22945,11 @@
         </is>
       </c>
       <c r="E750" s="3" t="n">
-        <v>89.79000000000001</v>
+        <v>94.75</v>
       </c>
       <c r="F750" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22961,12 +22961,12 @@
       </c>
       <c r="B751" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C751" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="D751" s="2" t="inlineStr">
@@ -22975,7 +22975,7 @@
         </is>
       </c>
       <c r="E751" s="3" t="n">
-        <v>89.52</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="F751" s="2" t="inlineStr">
         <is>
@@ -22991,25 +22991,25 @@
       </c>
       <c r="B752" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C752" s="2" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="D752" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>89.48999999999999</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23021,12 +23021,12 @@
       </c>
       <c r="B753" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C753" s="2" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="D753" s="2" t="inlineStr">
@@ -23035,11 +23035,11 @@
         </is>
       </c>
       <c r="E753" s="3" t="n">
-        <v>88.59</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F753" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23051,21 +23051,21 @@
       </c>
       <c r="B754" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C754" s="2" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="D754" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E754" s="3" t="n">
-        <v>87.73</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F754" s="2" t="inlineStr">
         <is>
@@ -23081,12 +23081,12 @@
       </c>
       <c r="B755" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C755" s="2" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="D755" s="2" t="inlineStr">
@@ -23095,7 +23095,7 @@
         </is>
       </c>
       <c r="E755" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>87.73</v>
       </c>
       <c r="F755" s="2" t="inlineStr">
         <is>
@@ -23111,12 +23111,12 @@
       </c>
       <c r="B756" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C756" s="2" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="D756" s="2" t="inlineStr">
@@ -23125,11 +23125,11 @@
         </is>
       </c>
       <c r="E756" s="3" t="n">
-        <v>85.54000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23141,12 +23141,12 @@
       </c>
       <c r="B757" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C757" s="2" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="D757" s="2" t="inlineStr">
@@ -23155,11 +23155,11 @@
         </is>
       </c>
       <c r="E757" s="3" t="n">
-        <v>82.18000000000001</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="F757" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23171,12 +23171,12 @@
       </c>
       <c r="B758" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C758" s="2" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="D758" s="2" t="inlineStr">
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>81.73</v>
+        <v>84.34</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23201,12 +23201,12 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="D759" s="2" t="inlineStr">
@@ -23215,11 +23215,11 @@
         </is>
       </c>
       <c r="E759" s="3" t="n">
-        <v>80.31999999999999</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23231,12 +23231,12 @@
       </c>
       <c r="B760" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C760" s="2" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="D760" s="2" t="inlineStr">
@@ -23245,11 +23245,11 @@
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>80.23</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23261,12 +23261,12 @@
       </c>
       <c r="B761" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C761" s="2" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="D761" s="2" t="inlineStr">
@@ -23275,11 +23275,11 @@
         </is>
       </c>
       <c r="E761" s="3" t="n">
-        <v>80.20999999999999</v>
+        <v>81.73</v>
       </c>
       <c r="F761" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23291,12 +23291,12 @@
       </c>
       <c r="B762" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C762" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D762" s="2" t="inlineStr">
@@ -23305,11 +23305,11 @@
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>79.52</v>
+        <v>81.03</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23321,12 +23321,12 @@
       </c>
       <c r="B763" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C763" s="2" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D763" s="2" t="inlineStr">
@@ -23335,11 +23335,11 @@
         </is>
       </c>
       <c r="E763" s="3" t="n">
-        <v>79.44</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="F763" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23351,12 +23351,12 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="D764" s="2" t="inlineStr">
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>77.33</v>
+        <v>80.55</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23381,12 +23381,12 @@
       </c>
       <c r="B765" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C765" s="2" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="D765" s="2" t="inlineStr">
@@ -23395,11 +23395,11 @@
         </is>
       </c>
       <c r="E765" s="3" t="n">
-        <v>74.98999999999999</v>
+        <v>79.44</v>
       </c>
       <c r="F765" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23411,12 +23411,12 @@
       </c>
       <c r="B766" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C766" s="2" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="D766" s="2" t="inlineStr">
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>74.98</v>
+        <v>77.39</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23441,12 +23441,12 @@
       </c>
       <c r="B767" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C767" s="2" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="D767" s="2" t="inlineStr">
@@ -23455,11 +23455,11 @@
         </is>
       </c>
       <c r="E767" s="3" t="n">
-        <v>74.76000000000001</v>
+        <v>77.06</v>
       </c>
       <c r="F767" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23471,25 +23471,25 @@
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="D768" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23515,11 +23515,11 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>74.48</v>
+        <v>76.22</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23531,12 +23531,12 @@
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
@@ -23545,11 +23545,11 @@
         </is>
       </c>
       <c r="E770" s="3" t="n">
-        <v>73.53</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23561,25 +23561,25 @@
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E771" s="3" t="n">
-        <v>71.89</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23591,12 +23591,12 @@
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -23605,11 +23605,11 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>71.72</v>
+        <v>74.5</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23621,12 +23621,12 @@
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D773" s="2" t="inlineStr">
@@ -23635,11 +23635,11 @@
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23651,12 +23651,12 @@
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr">
@@ -23665,11 +23665,11 @@
         </is>
       </c>
       <c r="E774" s="3" t="n">
-        <v>71.38</v>
+        <v>73.17</v>
       </c>
       <c r="F774" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23681,12 +23681,12 @@
       </c>
       <c r="B775" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C775" s="2" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="D775" s="2" t="inlineStr">
@@ -23695,11 +23695,11 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>70.48</v>
+        <v>72.19</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23711,12 +23711,12 @@
       </c>
       <c r="B776" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C776" s="2" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D776" s="2" t="inlineStr">
@@ -23725,11 +23725,11 @@
         </is>
       </c>
       <c r="E776" s="3" t="n">
-        <v>70.12</v>
+        <v>72.02</v>
       </c>
       <c r="F776" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23741,12 +23741,12 @@
       </c>
       <c r="B777" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C777" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="D777" s="2" t="inlineStr">
@@ -23755,11 +23755,11 @@
         </is>
       </c>
       <c r="E777" s="3" t="n">
-        <v>70.04000000000001</v>
+        <v>71.38</v>
       </c>
       <c r="F777" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23771,12 +23771,12 @@
       </c>
       <c r="B778" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C778" s="2" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="D778" s="2" t="inlineStr">
@@ -23785,11 +23785,11 @@
         </is>
       </c>
       <c r="E778" s="3" t="n">
-        <v>69.73</v>
+        <v>70.5</v>
       </c>
       <c r="F778" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23801,12 +23801,12 @@
       </c>
       <c r="B779" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C779" s="2" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="D779" s="2" t="inlineStr">
@@ -23815,11 +23815,11 @@
         </is>
       </c>
       <c r="E779" s="3" t="n">
-        <v>68.88</v>
+        <v>70.48</v>
       </c>
       <c r="F779" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23831,12 +23831,12 @@
       </c>
       <c r="B780" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C780" s="2" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="D780" s="2" t="inlineStr">
@@ -23845,11 +23845,11 @@
         </is>
       </c>
       <c r="E780" s="3" t="n">
-        <v>68.86</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23861,12 +23861,12 @@
       </c>
       <c r="B781" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C781" s="2" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="D781" s="2" t="inlineStr">
@@ -23875,11 +23875,11 @@
         </is>
       </c>
       <c r="E781" s="3" t="n">
-        <v>68.5</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="F781" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23891,12 +23891,12 @@
       </c>
       <c r="B782" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C782" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="D782" s="2" t="inlineStr">
@@ -23905,11 +23905,11 @@
         </is>
       </c>
       <c r="E782" s="3" t="n">
-        <v>65.95</v>
+        <v>68.5</v>
       </c>
       <c r="F782" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -23935,11 +23935,11 @@
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>65.84</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23951,12 +23951,12 @@
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
@@ -23965,11 +23965,11 @@
         </is>
       </c>
       <c r="E784" s="3" t="n">
-        <v>65.67</v>
+        <v>66.45</v>
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23981,12 +23981,12 @@
       </c>
       <c r="B785" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C785" s="2" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="D785" s="2" t="inlineStr">
@@ -23995,11 +23995,11 @@
         </is>
       </c>
       <c r="E785" s="3" t="n">
-        <v>65.48</v>
+        <v>66.39</v>
       </c>
       <c r="F785" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -24011,12 +24011,12 @@
       </c>
       <c r="B786" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C786" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="D786" s="2" t="inlineStr">
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>64.22</v>
+        <v>66.34</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -24041,12 +24041,12 @@
       </c>
       <c r="B787" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C787" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="D787" s="2" t="inlineStr">
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>63.6</v>
+        <v>65.78</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -24071,12 +24071,12 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="D788" s="2" t="inlineStr">
@@ -24085,11 +24085,11 @@
         </is>
       </c>
       <c r="E788" s="3" t="n">
-        <v>61.96</v>
+        <v>63.6</v>
       </c>
       <c r="F788" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24101,12 +24101,12 @@
       </c>
       <c r="B789" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C789" s="2" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D789" s="2" t="inlineStr">
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>61</v>
+        <v>61.96</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24131,12 +24131,12 @@
       </c>
       <c r="B790" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C790" s="2" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="D790" s="2" t="inlineStr">
@@ -24145,11 +24145,11 @@
         </is>
       </c>
       <c r="E790" s="3" t="n">
-        <v>60.09</v>
+        <v>61.35</v>
       </c>
       <c r="F790" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -24175,11 +24175,11 @@
         </is>
       </c>
       <c r="E791" s="3" t="n">
-        <v>57.63</v>
+        <v>60.93</v>
       </c>
       <c r="F791" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -24191,25 +24191,25 @@
       </c>
       <c r="B792" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C792" s="2" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="D792" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E792" s="3" t="n">
-        <v>57.22</v>
+        <v>60.1</v>
       </c>
       <c r="F792" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -24221,12 +24221,12 @@
       </c>
       <c r="B793" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C793" s="2" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="D793" s="2" t="inlineStr">
@@ -24235,11 +24235,11 @@
         </is>
       </c>
       <c r="E793" s="3" t="n">
-        <v>56.5</v>
+        <v>57.89</v>
       </c>
       <c r="F793" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -24251,25 +24251,25 @@
       </c>
       <c r="B794" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C794" s="2" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="D794" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E794" s="3" t="n">
-        <v>55.7</v>
+        <v>57.22</v>
       </c>
       <c r="F794" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24281,12 +24281,12 @@
       </c>
       <c r="B795" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C795" s="2" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="D795" s="2" t="inlineStr">
@@ -24295,11 +24295,11 @@
         </is>
       </c>
       <c r="E795" s="3" t="n">
-        <v>55.14</v>
+        <v>56.5</v>
       </c>
       <c r="F795" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24311,12 +24311,12 @@
       </c>
       <c r="B796" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C796" s="2" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="D796" s="2" t="inlineStr">
@@ -24325,7 +24325,7 @@
         </is>
       </c>
       <c r="E796" s="3" t="n">
-        <v>54.45</v>
+        <v>55.14</v>
       </c>
       <c r="F796" s="2" t="inlineStr">
         <is>
@@ -24341,12 +24341,12 @@
       </c>
       <c r="B797" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C797" s="2" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="D797" s="2" t="inlineStr">
@@ -24355,11 +24355,11 @@
         </is>
       </c>
       <c r="E797" s="3" t="n">
-        <v>53.95</v>
+        <v>54.45</v>
       </c>
       <c r="F797" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24371,12 +24371,12 @@
       </c>
       <c r="B798" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C798" s="2" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="D798" s="2" t="inlineStr">
@@ -24385,11 +24385,11 @@
         </is>
       </c>
       <c r="E798" s="3" t="n">
-        <v>53.51</v>
+        <v>53.95</v>
       </c>
       <c r="F798" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="B799" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C799" s="2" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="D799" s="2" t="inlineStr">
@@ -24415,11 +24415,11 @@
         </is>
       </c>
       <c r="E799" s="3" t="n">
-        <v>52.57</v>
+        <v>53.86</v>
       </c>
       <c r="F799" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -24431,12 +24431,12 @@
       </c>
       <c r="B800" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C800" s="2" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="D800" s="2" t="inlineStr">
@@ -24445,11 +24445,11 @@
         </is>
       </c>
       <c r="E800" s="3" t="n">
-        <v>52.42</v>
+        <v>52.57</v>
       </c>
       <c r="F800" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24461,12 +24461,12 @@
       </c>
       <c r="B801" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C801" s="2" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="D801" s="2" t="inlineStr">
@@ -24475,11 +24475,11 @@
         </is>
       </c>
       <c r="E801" s="3" t="n">
-        <v>50.68</v>
+        <v>52.53</v>
       </c>
       <c r="F801" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -24491,12 +24491,12 @@
       </c>
       <c r="B802" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C802" s="2" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="D802" s="2" t="inlineStr">
@@ -24505,11 +24505,11 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>50.23</v>
+        <v>50.74</v>
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -24521,12 +24521,12 @@
       </c>
       <c r="B803" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C803" s="2" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="D803" s="2" t="inlineStr">
@@ -24535,11 +24535,11 @@
         </is>
       </c>
       <c r="E803" s="3" t="n">
-        <v>50.13</v>
+        <v>50.34</v>
       </c>
       <c r="F803" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -24551,12 +24551,12 @@
       </c>
       <c r="B804" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="C804" s="2" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="D804" s="2" t="inlineStr">
@@ -24565,7 +24565,7 @@
         </is>
       </c>
       <c r="E804" s="3" t="n">
-        <v>49.31</v>
+        <v>50.23</v>
       </c>
       <c r="F804" s="2" t="inlineStr">
         <is>
@@ -24581,12 +24581,12 @@
       </c>
       <c r="B805" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C805" s="2" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="D805" s="2" t="inlineStr">
@@ -24595,11 +24595,11 @@
         </is>
       </c>
       <c r="E805" s="3" t="n">
-        <v>49.25</v>
+        <v>50.13</v>
       </c>
       <c r="F805" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24731,12 +24731,12 @@
       </c>
       <c r="B810" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C810" s="2" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="D810" s="2" t="inlineStr">
@@ -24745,11 +24745,11 @@
         </is>
       </c>
       <c r="E810" s="3" t="n">
-        <v>44.8</v>
+        <v>44.98</v>
       </c>
       <c r="F810" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -24761,12 +24761,12 @@
       </c>
       <c r="B811" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C811" s="2" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="D811" s="2" t="inlineStr">
@@ -24775,11 +24775,11 @@
         </is>
       </c>
       <c r="E811" s="3" t="n">
-        <v>44.5</v>
+        <v>44.8</v>
       </c>
       <c r="F811" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24821,12 +24821,12 @@
       </c>
       <c r="B813" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C813" s="2" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="D813" s="2" t="inlineStr">
@@ -24835,11 +24835,11 @@
         </is>
       </c>
       <c r="E813" s="3" t="n">
-        <v>42.84</v>
+        <v>42.9</v>
       </c>
       <c r="F813" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -24851,12 +24851,12 @@
       </c>
       <c r="B814" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C814" s="2" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="D814" s="2" t="inlineStr">
@@ -24865,7 +24865,7 @@
         </is>
       </c>
       <c r="E814" s="3" t="n">
-        <v>40.54</v>
+        <v>42.84</v>
       </c>
       <c r="F814" s="2" t="inlineStr">
         <is>
@@ -24881,12 +24881,12 @@
       </c>
       <c r="B815" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C815" s="2" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="D815" s="2" t="inlineStr">
@@ -24895,11 +24895,11 @@
         </is>
       </c>
       <c r="E815" s="3" t="n">
-        <v>39.39</v>
+        <v>41.12</v>
       </c>
       <c r="F815" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -24911,12 +24911,12 @@
       </c>
       <c r="B816" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C816" s="2" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="D816" s="2" t="inlineStr">
@@ -24925,11 +24925,11 @@
         </is>
       </c>
       <c r="E816" s="3" t="n">
-        <v>39.2</v>
+        <v>39.39</v>
       </c>
       <c r="F816" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -24941,12 +24941,12 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="D817" s="2" t="inlineStr">
@@ -24955,11 +24955,11 @@
         </is>
       </c>
       <c r="E817" s="3" t="n">
-        <v>37.65</v>
+        <v>39.2</v>
       </c>
       <c r="F817" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -24971,12 +24971,12 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="D818" s="2" t="inlineStr">
@@ -24985,11 +24985,11 @@
         </is>
       </c>
       <c r="E818" s="3" t="n">
-        <v>37.48</v>
+        <v>37.65</v>
       </c>
       <c r="F818" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25121,12 +25121,12 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="D823" s="2" t="inlineStr">
@@ -25135,11 +25135,11 @@
         </is>
       </c>
       <c r="E823" s="3" t="n">
-        <v>34.05</v>
+        <v>34.15</v>
       </c>
       <c r="F823" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -25151,12 +25151,12 @@
       </c>
       <c r="B824" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="C824" s="2" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="D824" s="2" t="inlineStr">
@@ -25165,11 +25165,11 @@
         </is>
       </c>
       <c r="E824" s="3" t="n">
-        <v>31.83</v>
+        <v>34.05</v>
       </c>
       <c r="F824" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25181,12 +25181,12 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="D825" s="2" t="inlineStr">
@@ -25195,11 +25195,11 @@
         </is>
       </c>
       <c r="E825" s="3" t="n">
-        <v>31.24</v>
+        <v>31.83</v>
       </c>
       <c r="F825" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25225,11 +25225,11 @@
         </is>
       </c>
       <c r="E826" s="3" t="n">
-        <v>31.1</v>
+        <v>31.69</v>
       </c>
       <c r="F826" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -25241,12 +25241,12 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="D827" s="2" t="inlineStr">
@@ -25255,11 +25255,11 @@
         </is>
       </c>
       <c r="E827" s="3" t="n">
-        <v>30.62</v>
+        <v>31.24</v>
       </c>
       <c r="F827" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25285,11 +25285,11 @@
         </is>
       </c>
       <c r="E828" s="3" t="n">
-        <v>30.33</v>
+        <v>30.54</v>
       </c>
       <c r="F828" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -25315,11 +25315,11 @@
         </is>
       </c>
       <c r="E829" s="3" t="n">
-        <v>30.32</v>
+        <v>30.38</v>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -25331,12 +25331,12 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D830" s="2" t="inlineStr">
@@ -25345,11 +25345,11 @@
         </is>
       </c>
       <c r="E830" s="3" t="n">
-        <v>29.67</v>
+        <v>29.81</v>
       </c>
       <c r="F830" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -25361,12 +25361,12 @@
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C831" s="2" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="D831" s="2" t="inlineStr">
@@ -25375,11 +25375,11 @@
         </is>
       </c>
       <c r="E831" s="3" t="n">
-        <v>29.27</v>
+        <v>29.67</v>
       </c>
       <c r="F831" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -25391,12 +25391,12 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="D832" s="2" t="inlineStr">
@@ -25405,7 +25405,7 @@
         </is>
       </c>
       <c r="E832" s="3" t="n">
-        <v>28.85</v>
+        <v>29.27</v>
       </c>
       <c r="F832" s="2" t="inlineStr">
         <is>
@@ -25435,11 +25435,11 @@
         </is>
       </c>
       <c r="E833" s="3" t="n">
-        <v>28.31</v>
+        <v>28.89</v>
       </c>
       <c r="F833" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -25451,12 +25451,12 @@
       </c>
       <c r="B834" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C834" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="D834" s="2" t="inlineStr">
@@ -25465,11 +25465,11 @@
         </is>
       </c>
       <c r="E834" s="3" t="n">
-        <v>26.8</v>
+        <v>28.85</v>
       </c>
       <c r="F834" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25481,25 +25481,25 @@
       </c>
       <c r="B835" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C835" s="2" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="D835" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E835" s="3" t="n">
-        <v>26.15</v>
+        <v>28.56</v>
       </c>
       <c r="F835" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -25511,12 +25511,12 @@
       </c>
       <c r="B836" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C836" s="2" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="D836" s="2" t="inlineStr">
@@ -25525,11 +25525,11 @@
         </is>
       </c>
       <c r="E836" s="3" t="n">
-        <v>25.32</v>
+        <v>26.15</v>
       </c>
       <c r="F836" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25541,25 +25541,25 @@
       </c>
       <c r="B837" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C837" s="2" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="D837" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E837" s="3" t="n">
-        <v>23.74</v>
+        <v>25.34</v>
       </c>
       <c r="F837" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -25571,12 +25571,12 @@
       </c>
       <c r="B838" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C838" s="2" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="D838" s="2" t="inlineStr">
@@ -25585,7 +25585,7 @@
         </is>
       </c>
       <c r="E838" s="3" t="n">
-        <v>22.39</v>
+        <v>23.74</v>
       </c>
       <c r="F838" s="2" t="inlineStr">
         <is>
@@ -25601,12 +25601,12 @@
       </c>
       <c r="B839" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C839" s="2" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="D839" s="2" t="inlineStr">
@@ -25615,11 +25615,11 @@
         </is>
       </c>
       <c r="E839" s="3" t="n">
-        <v>21.7</v>
+        <v>22.39</v>
       </c>
       <c r="F839" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25631,12 +25631,12 @@
       </c>
       <c r="B840" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C840" s="2" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="D840" s="2" t="inlineStr">
@@ -25645,11 +25645,11 @@
         </is>
       </c>
       <c r="E840" s="3" t="n">
-        <v>21.21</v>
+        <v>21.7</v>
       </c>
       <c r="F840" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25661,12 +25661,12 @@
       </c>
       <c r="B841" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C841" s="2" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="D841" s="2" t="inlineStr">
@@ -25675,7 +25675,7 @@
         </is>
       </c>
       <c r="E841" s="3" t="n">
-        <v>21.17</v>
+        <v>21.21</v>
       </c>
       <c r="F841" s="2" t="inlineStr">
         <is>
@@ -25691,12 +25691,12 @@
       </c>
       <c r="B842" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C842" s="2" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="D842" s="2" t="inlineStr">
@@ -25705,7 +25705,7 @@
         </is>
       </c>
       <c r="E842" s="3" t="n">
-        <v>20.98</v>
+        <v>21.17</v>
       </c>
       <c r="F842" s="2" t="inlineStr">
         <is>
@@ -25721,12 +25721,12 @@
       </c>
       <c r="B843" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C843" s="2" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="D843" s="2" t="inlineStr">
@@ -25735,7 +25735,7 @@
         </is>
       </c>
       <c r="E843" s="3" t="n">
-        <v>20.61</v>
+        <v>20.98</v>
       </c>
       <c r="F843" s="2" t="inlineStr">
         <is>
@@ -25751,12 +25751,12 @@
       </c>
       <c r="B844" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C844" s="2" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="D844" s="2" t="inlineStr">
@@ -25765,7 +25765,7 @@
         </is>
       </c>
       <c r="E844" s="3" t="n">
-        <v>20.12</v>
+        <v>20.61</v>
       </c>
       <c r="F844" s="2" t="inlineStr">
         <is>
@@ -25781,12 +25781,12 @@
       </c>
       <c r="B845" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C845" s="2" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="D845" s="2" t="inlineStr">
@@ -25795,7 +25795,7 @@
         </is>
       </c>
       <c r="E845" s="3" t="n">
-        <v>19.65</v>
+        <v>20.12</v>
       </c>
       <c r="F845" s="2" t="inlineStr">
         <is>
@@ -25811,12 +25811,12 @@
       </c>
       <c r="B846" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C846" s="2" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="D846" s="2" t="inlineStr">
@@ -25825,11 +25825,11 @@
         </is>
       </c>
       <c r="E846" s="3" t="n">
-        <v>18.25</v>
+        <v>19.65</v>
       </c>
       <c r="F846" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25841,12 +25841,12 @@
       </c>
       <c r="B847" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C847" s="2" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="D847" s="2" t="inlineStr">
@@ -25855,11 +25855,11 @@
         </is>
       </c>
       <c r="E847" s="3" t="n">
-        <v>17.57</v>
+        <v>18.25</v>
       </c>
       <c r="F847" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25871,12 +25871,12 @@
       </c>
       <c r="B848" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C848" s="2" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="D848" s="2" t="inlineStr">
@@ -25885,7 +25885,7 @@
         </is>
       </c>
       <c r="E848" s="3" t="n">
-        <v>17.49</v>
+        <v>17.57</v>
       </c>
       <c r="F848" s="2" t="inlineStr">
         <is>
@@ -25901,12 +25901,12 @@
       </c>
       <c r="B849" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C849" s="2" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="D849" s="2" t="inlineStr">
@@ -25915,7 +25915,7 @@
         </is>
       </c>
       <c r="E849" s="3" t="n">
-        <v>17.45</v>
+        <v>17.49</v>
       </c>
       <c r="F849" s="2" t="inlineStr">
         <is>
@@ -25931,12 +25931,12 @@
       </c>
       <c r="B850" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C850" s="2" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="D850" s="2" t="inlineStr">
@@ -25945,11 +25945,11 @@
         </is>
       </c>
       <c r="E850" s="3" t="n">
-        <v>17.2</v>
+        <v>17.45</v>
       </c>
       <c r="F850" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26365,11 +26365,11 @@
         </is>
       </c>
       <c r="E864" s="3" t="n">
-        <v>6.53</v>
+        <v>7.1</v>
       </c>
       <c r="F864" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2401.61</v>
+        <v>2405.6</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -19795,11 +19795,11 @@
         </is>
       </c>
       <c r="E645" s="3" t="n">
-        <v>2357.71</v>
+        <v>2400.95</v>
       </c>
       <c r="F645" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -19885,11 +19885,11 @@
         </is>
       </c>
       <c r="E648" s="3" t="n">
-        <v>1211.26</v>
+        <v>1228.53</v>
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>1193.55</v>
+        <v>1205.47</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -19945,11 +19945,11 @@
         </is>
       </c>
       <c r="E650" s="3" t="n">
-        <v>984.12</v>
+        <v>992.48</v>
       </c>
       <c r="F650" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20005,11 +20005,11 @@
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>805.87</v>
+        <v>820.3200000000001</v>
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20095,11 +20095,11 @@
         </is>
       </c>
       <c r="E655" s="3" t="n">
-        <v>709.95</v>
+        <v>719.2</v>
       </c>
       <c r="F655" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20155,11 +20155,11 @@
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>634.41</v>
+        <v>638.49</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20185,11 +20185,11 @@
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>631.08</v>
+        <v>633.29</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20245,11 +20245,11 @@
         </is>
       </c>
       <c r="E660" s="3" t="n">
-        <v>575.9299999999999</v>
+        <v>581.85</v>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20275,11 +20275,11 @@
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>558.51</v>
+        <v>562.9299999999999</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20321,12 +20321,12 @@
       </c>
       <c r="B663" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C663" s="2" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="D663" s="2" t="inlineStr">
@@ -20335,11 +20335,11 @@
         </is>
       </c>
       <c r="E663" s="3" t="n">
-        <v>540.91</v>
+        <v>555.3</v>
       </c>
       <c r="F663" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20351,12 +20351,12 @@
       </c>
       <c r="B664" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
@@ -20365,11 +20365,11 @@
         </is>
       </c>
       <c r="E664" s="3" t="n">
-        <v>539.74</v>
+        <v>546.52</v>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20381,25 +20381,25 @@
       </c>
       <c r="B665" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E665" s="3" t="n">
-        <v>536.3</v>
+        <v>536.48</v>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20411,25 +20411,25 @@
       </c>
       <c r="B666" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>533.87</v>
+        <v>536.3099999999999</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20485,11 +20485,11 @@
         </is>
       </c>
       <c r="E668" s="3" t="n">
-        <v>505.38</v>
+        <v>512</v>
       </c>
       <c r="F668" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20545,11 +20545,11 @@
         </is>
       </c>
       <c r="E670" s="3" t="n">
-        <v>489.79</v>
+        <v>494.11</v>
       </c>
       <c r="F670" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20605,11 +20605,11 @@
         </is>
       </c>
       <c r="E672" s="3" t="n">
-        <v>463.77</v>
+        <v>473.36</v>
       </c>
       <c r="F672" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20681,25 +20681,25 @@
       </c>
       <c r="B675" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C675" s="2" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="D675" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>396.94</v>
+        <v>399.55</v>
       </c>
       <c r="F675" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20711,25 +20711,25 @@
       </c>
       <c r="B676" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C676" s="2" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="D676" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>382.08</v>
+        <v>397.34</v>
       </c>
       <c r="F676" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20755,11 +20755,11 @@
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>367.13</v>
+        <v>380.93</v>
       </c>
       <c r="F677" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20815,11 +20815,11 @@
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>338.03</v>
+        <v>338.25</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>327.78</v>
+        <v>328.52</v>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20905,11 +20905,11 @@
         </is>
       </c>
       <c r="E682" s="3" t="n">
-        <v>287.5</v>
+        <v>288.81</v>
       </c>
       <c r="F682" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20921,25 +20921,25 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="D683" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E683" s="3" t="n">
-        <v>280.86</v>
+        <v>281.02</v>
       </c>
       <c r="F683" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20951,12 +20951,12 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="D684" s="2" t="inlineStr">
@@ -20965,11 +20965,11 @@
         </is>
       </c>
       <c r="E684" s="3" t="n">
-        <v>275.84</v>
+        <v>280.91</v>
       </c>
       <c r="F684" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -20981,21 +20981,21 @@
       </c>
       <c r="B685" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C685" s="2" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="D685" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E685" s="3" t="n">
-        <v>274.35</v>
+        <v>275.84</v>
       </c>
       <c r="F685" s="2" t="inlineStr">
         <is>
@@ -21055,11 +21055,11 @@
         </is>
       </c>
       <c r="E687" s="3" t="n">
-        <v>256.62</v>
+        <v>261.94</v>
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21085,11 +21085,11 @@
         </is>
       </c>
       <c r="E688" s="3" t="n">
-        <v>255.93</v>
+        <v>256.01</v>
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21115,11 +21115,11 @@
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>249.89</v>
+        <v>251.37</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21205,11 +21205,11 @@
         </is>
       </c>
       <c r="E692" s="3" t="n">
-        <v>228.99</v>
+        <v>229.2</v>
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21235,11 +21235,11 @@
         </is>
       </c>
       <c r="E693" s="3" t="n">
-        <v>224.49</v>
+        <v>225.79</v>
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21265,11 +21265,11 @@
         </is>
       </c>
       <c r="E694" s="3" t="n">
-        <v>221.61</v>
+        <v>221.68</v>
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21281,12 +21281,12 @@
       </c>
       <c r="B695" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="C695" s="2" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>816171</t>
         </is>
       </c>
       <c r="D695" s="2" t="inlineStr">
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>218.03</v>
+        <v>219.26</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21311,12 +21311,12 @@
       </c>
       <c r="B696" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872531DSZ</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C696" s="2" t="inlineStr">
         <is>
-          <t>816171</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="D696" s="2" t="inlineStr">
@@ -21325,7 +21325,7 @@
         </is>
       </c>
       <c r="E696" s="3" t="n">
-        <v>217.83</v>
+        <v>218.03</v>
       </c>
       <c r="F696" s="2" t="inlineStr">
         <is>
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>210.96</v>
+        <v>211.61</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="E698" s="3" t="n">
-        <v>210.41</v>
+        <v>210.62</v>
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>201.14</v>
+        <v>201.96</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>187.32</v>
+        <v>188.64</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>174.51</v>
+        <v>174.82</v>
       </c>
       <c r="F703" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21565,11 +21565,11 @@
         </is>
       </c>
       <c r="E704" s="3" t="n">
-        <v>172.45</v>
+        <v>172.72</v>
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>169.19</v>
+        <v>169.21</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21625,11 +21625,11 @@
         </is>
       </c>
       <c r="E706" s="3" t="n">
-        <v>159.91</v>
+        <v>165.64</v>
       </c>
       <c r="F706" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21685,11 +21685,11 @@
         </is>
       </c>
       <c r="E708" s="3" t="n">
-        <v>152.28</v>
+        <v>152.35</v>
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21745,11 +21745,11 @@
         </is>
       </c>
       <c r="E710" s="3" t="n">
-        <v>143.71</v>
+        <v>145.28</v>
       </c>
       <c r="F710" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21761,12 +21761,12 @@
       </c>
       <c r="B711" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C711" s="2" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D711" s="2" t="inlineStr">
@@ -21775,11 +21775,11 @@
         </is>
       </c>
       <c r="E711" s="3" t="n">
-        <v>138.98</v>
+        <v>141.68</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21791,12 +21791,12 @@
       </c>
       <c r="B712" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C712" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="D712" s="2" t="inlineStr">
@@ -21805,11 +21805,11 @@
         </is>
       </c>
       <c r="E712" s="3" t="n">
-        <v>137.22</v>
+        <v>139.35</v>
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21835,11 +21835,11 @@
         </is>
       </c>
       <c r="E713" s="3" t="n">
-        <v>137.03</v>
+        <v>138.13</v>
       </c>
       <c r="F713" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21851,12 +21851,12 @@
       </c>
       <c r="B714" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C714" s="2" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="D714" s="2" t="inlineStr">
@@ -21865,11 +21865,11 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>135.54</v>
+        <v>135.96</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21881,12 +21881,12 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="D715" s="2" t="inlineStr">
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="E715" s="3" t="n">
-        <v>134.03</v>
+        <v>135.54</v>
       </c>
       <c r="F715" s="2" t="inlineStr">
         <is>
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>132.12</v>
+        <v>132.38</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -21971,12 +21971,12 @@
       </c>
       <c r="B718" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr">
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>131.31</v>
+        <v>131.59</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -22001,12 +22001,12 @@
       </c>
       <c r="B719" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C719" s="2" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D719" s="2" t="inlineStr">
@@ -22015,11 +22015,11 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>131.19</v>
+        <v>131.41</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -22031,12 +22031,12 @@
       </c>
       <c r="B720" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C720" s="2" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="D720" s="2" t="inlineStr">
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="E720" s="3" t="n">
-        <v>131.04</v>
+        <v>131.31</v>
       </c>
       <c r="F720" s="2" t="inlineStr">
         <is>
@@ -22061,12 +22061,12 @@
       </c>
       <c r="B721" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C721" s="2" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="D721" s="2" t="inlineStr">
@@ -22075,11 +22075,11 @@
         </is>
       </c>
       <c r="E721" s="3" t="n">
-        <v>130.22</v>
+        <v>131.04</v>
       </c>
       <c r="F721" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22091,12 +22091,12 @@
       </c>
       <c r="B722" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C722" s="2" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="D722" s="2" t="inlineStr">
@@ -22105,7 +22105,7 @@
         </is>
       </c>
       <c r="E722" s="3" t="n">
-        <v>129.31</v>
+        <v>130.22</v>
       </c>
       <c r="F722" s="2" t="inlineStr">
         <is>
@@ -22121,12 +22121,12 @@
       </c>
       <c r="B723" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C723" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="D723" s="2" t="inlineStr">
@@ -22135,7 +22135,7 @@
         </is>
       </c>
       <c r="E723" s="3" t="n">
-        <v>128.61</v>
+        <v>129.31</v>
       </c>
       <c r="F723" s="2" t="inlineStr">
         <is>
@@ -22151,12 +22151,12 @@
       </c>
       <c r="B724" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C724" s="2" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D724" s="2" t="inlineStr">
@@ -22165,11 +22165,11 @@
         </is>
       </c>
       <c r="E724" s="3" t="n">
-        <v>127.92</v>
+        <v>128.61</v>
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22181,12 +22181,12 @@
       </c>
       <c r="B725" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C725" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="D725" s="2" t="inlineStr">
@@ -22195,11 +22195,11 @@
         </is>
       </c>
       <c r="E725" s="3" t="n">
-        <v>127.31</v>
+        <v>127.92</v>
       </c>
       <c r="F725" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22211,12 +22211,12 @@
       </c>
       <c r="B726" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C726" s="2" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D726" s="2" t="inlineStr">
@@ -22225,11 +22225,11 @@
         </is>
       </c>
       <c r="E726" s="3" t="n">
-        <v>126.03</v>
+        <v>127.01</v>
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -22241,12 +22241,12 @@
       </c>
       <c r="B727" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C727" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="D727" s="2" t="inlineStr">
@@ -22255,11 +22255,11 @@
         </is>
       </c>
       <c r="E727" s="3" t="n">
-        <v>125.87</v>
+        <v>126.03</v>
       </c>
       <c r="F727" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22285,11 +22285,11 @@
         </is>
       </c>
       <c r="E728" s="3" t="n">
-        <v>124.15</v>
+        <v>124.29</v>
       </c>
       <c r="F728" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -22375,11 +22375,11 @@
         </is>
       </c>
       <c r="E731" s="3" t="n">
-        <v>114.11</v>
+        <v>114.67</v>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -22481,12 +22481,12 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
@@ -22495,11 +22495,11 @@
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>110.18</v>
+        <v>110.34</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -22511,12 +22511,12 @@
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
@@ -22525,11 +22525,11 @@
         </is>
       </c>
       <c r="E736" s="3" t="n">
-        <v>109.33</v>
+        <v>110.23</v>
       </c>
       <c r="F736" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -22541,12 +22541,12 @@
       </c>
       <c r="B737" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="D737" s="2" t="inlineStr">
@@ -22555,11 +22555,11 @@
         </is>
       </c>
       <c r="E737" s="3" t="n">
-        <v>108.26</v>
+        <v>109.33</v>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22585,11 +22585,11 @@
         </is>
       </c>
       <c r="E738" s="3" t="n">
-        <v>107.56</v>
+        <v>107.57</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -22601,12 +22601,12 @@
       </c>
       <c r="B739" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C739" s="2" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D739" s="2" t="inlineStr">
@@ -22615,11 +22615,11 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>103.72</v>
+        <v>105.26</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -22645,11 +22645,11 @@
         </is>
       </c>
       <c r="E740" s="3" t="n">
-        <v>103.16</v>
+        <v>103.83</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -22661,12 +22661,12 @@
       </c>
       <c r="B741" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="D741" s="2" t="inlineStr">
@@ -22675,11 +22675,11 @@
         </is>
       </c>
       <c r="E741" s="3" t="n">
-        <v>103.15</v>
+        <v>103.72</v>
       </c>
       <c r="F741" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>102.99</v>
+        <v>103.13</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -22751,12 +22751,12 @@
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D744" s="2" t="inlineStr">
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>100.73</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -22781,12 +22781,12 @@
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr">
@@ -22795,11 +22795,11 @@
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>98.78</v>
+        <v>100.43</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -22811,12 +22811,12 @@
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
@@ -22825,7 +22825,7 @@
         </is>
       </c>
       <c r="E746" s="3" t="n">
-        <v>97.44</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
@@ -22841,12 +22841,12 @@
       </c>
       <c r="B747" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C747" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="D747" s="2" t="inlineStr">
@@ -22855,7 +22855,7 @@
         </is>
       </c>
       <c r="E747" s="3" t="n">
-        <v>97.23999999999999</v>
+        <v>98.78</v>
       </c>
       <c r="F747" s="2" t="inlineStr">
         <is>
@@ -22871,12 +22871,12 @@
       </c>
       <c r="B748" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C748" s="2" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="D748" s="2" t="inlineStr">
@@ -22885,11 +22885,11 @@
         </is>
       </c>
       <c r="E748" s="3" t="n">
-        <v>97.06</v>
+        <v>97.44</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22901,12 +22901,12 @@
       </c>
       <c r="B749" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C749" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="D749" s="2" t="inlineStr">
@@ -22915,11 +22915,11 @@
         </is>
       </c>
       <c r="E749" s="3" t="n">
-        <v>95.22</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="F749" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -22945,11 +22945,11 @@
         </is>
       </c>
       <c r="E750" s="3" t="n">
-        <v>94.75</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="F750" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -23005,11 +23005,11 @@
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>90.95999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -23095,11 +23095,11 @@
         </is>
       </c>
       <c r="E755" s="3" t="n">
-        <v>87.73</v>
+        <v>87.88</v>
       </c>
       <c r="F755" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -23111,12 +23111,12 @@
       </c>
       <c r="B756" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C756" s="2" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="D756" s="2" t="inlineStr">
@@ -23125,11 +23125,11 @@
         </is>
       </c>
       <c r="E756" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -23141,12 +23141,12 @@
       </c>
       <c r="B757" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C757" s="2" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="D757" s="2" t="inlineStr">
@@ -23155,11 +23155,11 @@
         </is>
       </c>
       <c r="E757" s="3" t="n">
-        <v>85.54000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F757" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23171,12 +23171,12 @@
       </c>
       <c r="B758" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C758" s="2" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D758" s="2" t="inlineStr">
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>84.34</v>
+        <v>85.84</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -23201,12 +23201,12 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="D759" s="2" t="inlineStr">
@@ -23215,11 +23215,11 @@
         </is>
       </c>
       <c r="E759" s="3" t="n">
-        <v>82.48999999999999</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23231,12 +23231,12 @@
       </c>
       <c r="B760" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C760" s="2" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="D760" s="2" t="inlineStr">
@@ -23245,11 +23245,11 @@
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>82.18000000000001</v>
+        <v>85.45</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -23261,12 +23261,12 @@
       </c>
       <c r="B761" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C761" s="2" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="D761" s="2" t="inlineStr">
@@ -23275,11 +23275,11 @@
         </is>
       </c>
       <c r="E761" s="3" t="n">
-        <v>81.73</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F761" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23291,12 +23291,12 @@
       </c>
       <c r="B762" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C762" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="D762" s="2" t="inlineStr">
@@ -23305,11 +23305,11 @@
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>81.03</v>
+        <v>81.73</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23321,12 +23321,12 @@
       </c>
       <c r="B763" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C763" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D763" s="2" t="inlineStr">
@@ -23335,11 +23335,11 @@
         </is>
       </c>
       <c r="E763" s="3" t="n">
-        <v>80.84999999999999</v>
+        <v>81.05</v>
       </c>
       <c r="F763" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>80.55</v>
+        <v>80.59</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -23411,12 +23411,12 @@
       </c>
       <c r="B766" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C766" s="2" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="D766" s="2" t="inlineStr">
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>77.39</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -23441,12 +23441,12 @@
       </c>
       <c r="B767" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C767" s="2" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="D767" s="2" t="inlineStr">
@@ -23455,7 +23455,7 @@
         </is>
       </c>
       <c r="E767" s="3" t="n">
-        <v>77.06</v>
+        <v>77.39</v>
       </c>
       <c r="F767" s="2" t="inlineStr">
         <is>
@@ -23471,12 +23471,12 @@
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="D768" s="2" t="inlineStr">
@@ -23485,11 +23485,11 @@
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>77.28</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -23515,11 +23515,11 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>76.22</v>
+        <v>76.25</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -23531,12 +23531,12 @@
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
@@ -23545,11 +23545,11 @@
         </is>
       </c>
       <c r="E770" s="3" t="n">
-        <v>74.76000000000001</v>
+        <v>74.94</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -23561,25 +23561,25 @@
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E771" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>74.88</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -23591,12 +23591,12 @@
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -23605,11 +23605,11 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>74.5</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23621,25 +23621,25 @@
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="D773" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23651,12 +23651,12 @@
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr">
@@ -23665,7 +23665,7 @@
         </is>
       </c>
       <c r="E774" s="3" t="n">
-        <v>73.17</v>
+        <v>74.5</v>
       </c>
       <c r="F774" s="2" t="inlineStr">
         <is>
@@ -23681,12 +23681,12 @@
       </c>
       <c r="B775" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C775" s="2" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="D775" s="2" t="inlineStr">
@@ -23695,11 +23695,11 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>72.19</v>
+        <v>73.25</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -23711,12 +23711,12 @@
       </c>
       <c r="B776" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C776" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="D776" s="2" t="inlineStr">
@@ -23725,7 +23725,7 @@
         </is>
       </c>
       <c r="E776" s="3" t="n">
-        <v>72.02</v>
+        <v>72.19</v>
       </c>
       <c r="F776" s="2" t="inlineStr">
         <is>
@@ -23845,11 +23845,11 @@
         </is>
       </c>
       <c r="E780" s="3" t="n">
-        <v>69.81999999999999</v>
+        <v>70.22</v>
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -23921,12 +23921,12 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="D783" s="2" t="inlineStr">
@@ -23935,11 +23935,11 @@
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>66.45999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -23951,12 +23951,12 @@
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
@@ -23965,11 +23965,11 @@
         </is>
       </c>
       <c r="E784" s="3" t="n">
-        <v>66.45</v>
+        <v>66.63</v>
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -23981,12 +23981,12 @@
       </c>
       <c r="B785" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C785" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D785" s="2" t="inlineStr">
@@ -23995,11 +23995,11 @@
         </is>
       </c>
       <c r="E785" s="3" t="n">
-        <v>66.39</v>
+        <v>66.63</v>
       </c>
       <c r="F785" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -24011,12 +24011,12 @@
       </c>
       <c r="B786" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C786" s="2" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="D786" s="2" t="inlineStr">
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>66.34</v>
+        <v>66.47</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -24041,12 +24041,12 @@
       </c>
       <c r="B787" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C787" s="2" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="D787" s="2" t="inlineStr">
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>65.78</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -24071,12 +24071,12 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="D788" s="2" t="inlineStr">
@@ -24085,11 +24085,11 @@
         </is>
       </c>
       <c r="E788" s="3" t="n">
-        <v>63.6</v>
+        <v>65.66</v>
       </c>
       <c r="F788" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -24101,12 +24101,12 @@
       </c>
       <c r="B789" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C789" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="D789" s="2" t="inlineStr">
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>61.96</v>
+        <v>63.6</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24131,12 +24131,12 @@
       </c>
       <c r="B790" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C790" s="2" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D790" s="2" t="inlineStr">
@@ -24145,11 +24145,11 @@
         </is>
       </c>
       <c r="E790" s="3" t="n">
-        <v>61.35</v>
+        <v>61.96</v>
       </c>
       <c r="F790" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24161,12 +24161,12 @@
       </c>
       <c r="B791" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C791" s="2" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="D791" s="2" t="inlineStr">
@@ -24175,11 +24175,11 @@
         </is>
       </c>
       <c r="E791" s="3" t="n">
-        <v>60.93</v>
+        <v>61.58</v>
       </c>
       <c r="F791" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -24205,11 +24205,11 @@
         </is>
       </c>
       <c r="E792" s="3" t="n">
-        <v>60.1</v>
+        <v>60.11</v>
       </c>
       <c r="F792" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -24235,11 +24235,11 @@
         </is>
       </c>
       <c r="E793" s="3" t="n">
-        <v>57.89</v>
+        <v>57.93</v>
       </c>
       <c r="F793" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -24355,11 +24355,11 @@
         </is>
       </c>
       <c r="E797" s="3" t="n">
-        <v>54.45</v>
+        <v>54.84</v>
       </c>
       <c r="F797" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -24371,12 +24371,12 @@
       </c>
       <c r="B798" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C798" s="2" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="D798" s="2" t="inlineStr">
@@ -24385,11 +24385,11 @@
         </is>
       </c>
       <c r="E798" s="3" t="n">
-        <v>53.95</v>
+        <v>54.09</v>
       </c>
       <c r="F798" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="B799" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C799" s="2" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="D799" s="2" t="inlineStr">
@@ -24415,11 +24415,11 @@
         </is>
       </c>
       <c r="E799" s="3" t="n">
-        <v>53.86</v>
+        <v>53.95</v>
       </c>
       <c r="F799" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24505,11 +24505,11 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>50.74</v>
+        <v>50.83</v>
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -24535,11 +24535,11 @@
         </is>
       </c>
       <c r="E803" s="3" t="n">
-        <v>50.34</v>
+        <v>50.45</v>
       </c>
       <c r="F803" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -24745,11 +24745,11 @@
         </is>
       </c>
       <c r="E810" s="3" t="n">
-        <v>44.98</v>
+        <v>45</v>
       </c>
       <c r="F810" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -24835,11 +24835,11 @@
         </is>
       </c>
       <c r="E813" s="3" t="n">
-        <v>42.9</v>
+        <v>42.92</v>
       </c>
       <c r="F813" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -24911,12 +24911,12 @@
       </c>
       <c r="B816" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C816" s="2" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="D816" s="2" t="inlineStr">
@@ -24925,11 +24925,11 @@
         </is>
       </c>
       <c r="E816" s="3" t="n">
-        <v>39.39</v>
+        <v>39.43</v>
       </c>
       <c r="F816" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -24941,12 +24941,12 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="D817" s="2" t="inlineStr">
@@ -24955,11 +24955,11 @@
         </is>
       </c>
       <c r="E817" s="3" t="n">
-        <v>39.2</v>
+        <v>39.39</v>
       </c>
       <c r="F817" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -25135,11 +25135,11 @@
         </is>
       </c>
       <c r="E823" s="3" t="n">
-        <v>34.15</v>
+        <v>34.4</v>
       </c>
       <c r="F823" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -25181,12 +25181,12 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="D825" s="2" t="inlineStr">
@@ -25195,11 +25195,11 @@
         </is>
       </c>
       <c r="E825" s="3" t="n">
-        <v>31.83</v>
+        <v>32.73</v>
       </c>
       <c r="F825" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -25225,11 +25225,11 @@
         </is>
       </c>
       <c r="E826" s="3" t="n">
-        <v>31.69</v>
+        <v>32.4</v>
       </c>
       <c r="F826" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -25241,12 +25241,12 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="D827" s="2" t="inlineStr">
@@ -25255,11 +25255,11 @@
         </is>
       </c>
       <c r="E827" s="3" t="n">
-        <v>31.24</v>
+        <v>31.83</v>
       </c>
       <c r="F827" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25271,12 +25271,12 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="D828" s="2" t="inlineStr">
@@ -25285,11 +25285,11 @@
         </is>
       </c>
       <c r="E828" s="3" t="n">
-        <v>30.54</v>
+        <v>31.24</v>
       </c>
       <c r="F828" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25301,12 +25301,12 @@
       </c>
       <c r="B829" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C829" s="2" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="D829" s="2" t="inlineStr">
@@ -25315,11 +25315,11 @@
         </is>
       </c>
       <c r="E829" s="3" t="n">
-        <v>30.38</v>
+        <v>30.74</v>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -25331,12 +25331,12 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="D830" s="2" t="inlineStr">
@@ -25345,11 +25345,11 @@
         </is>
       </c>
       <c r="E830" s="3" t="n">
-        <v>29.81</v>
+        <v>30.39</v>
       </c>
       <c r="F830" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -25361,12 +25361,12 @@
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C831" s="2" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D831" s="2" t="inlineStr">
@@ -25375,11 +25375,11 @@
         </is>
       </c>
       <c r="E831" s="3" t="n">
-        <v>29.67</v>
+        <v>29.81</v>
       </c>
       <c r="F831" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -25391,12 +25391,12 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="D832" s="2" t="inlineStr">
@@ -25405,11 +25405,11 @@
         </is>
       </c>
       <c r="E832" s="3" t="n">
-        <v>29.27</v>
+        <v>29.67</v>
       </c>
       <c r="F832" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -25421,12 +25421,12 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="D833" s="2" t="inlineStr">
@@ -25435,11 +25435,11 @@
         </is>
       </c>
       <c r="E833" s="3" t="n">
-        <v>28.89</v>
+        <v>29.27</v>
       </c>
       <c r="F833" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25451,12 +25451,12 @@
       </c>
       <c r="B834" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C834" s="2" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="D834" s="2" t="inlineStr">
@@ -25465,11 +25465,11 @@
         </is>
       </c>
       <c r="E834" s="3" t="n">
-        <v>28.85</v>
+        <v>28.94</v>
       </c>
       <c r="F834" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -25481,12 +25481,12 @@
       </c>
       <c r="B835" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C835" s="2" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="D835" s="2" t="inlineStr">
@@ -25495,11 +25495,11 @@
         </is>
       </c>
       <c r="E835" s="3" t="n">
-        <v>28.56</v>
+        <v>28.85</v>
       </c>
       <c r="F835" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26365,11 +26365,11 @@
         </is>
       </c>
       <c r="E864" s="3" t="n">
-        <v>7.1</v>
+        <v>7.11</v>
       </c>
       <c r="F864" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19751,12 +19751,12 @@
       </c>
       <c r="B644" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066915CBF</t>
+          <t>KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="C644" s="2" t="inlineStr">
         <is>
-          <t>812921</t>
+          <t>816227</t>
         </is>
       </c>
       <c r="D644" s="2" t="inlineStr">
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2405.6</v>
+        <v>2427.48</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -19781,12 +19781,12 @@
       </c>
       <c r="B645" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084593R9F</t>
+          <t>KIT4P00066915CBF</t>
         </is>
       </c>
       <c r="C645" s="2" t="inlineStr">
         <is>
-          <t>816227</t>
+          <t>812921</t>
         </is>
       </c>
       <c r="D645" s="2" t="inlineStr">
@@ -19795,11 +19795,11 @@
         </is>
       </c>
       <c r="E645" s="3" t="n">
-        <v>2400.95</v>
+        <v>2406.78</v>
       </c>
       <c r="F645" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -19885,11 +19885,11 @@
         </is>
       </c>
       <c r="E648" s="3" t="n">
-        <v>1228.53</v>
+        <v>1237.42</v>
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>1205.47</v>
+        <v>1211.83</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -19945,11 +19945,11 @@
         </is>
       </c>
       <c r="E650" s="3" t="n">
-        <v>992.48</v>
+        <v>995.95</v>
       </c>
       <c r="F650" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20005,11 +20005,11 @@
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>820.3200000000001</v>
+        <v>827.22</v>
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20095,11 +20095,11 @@
         </is>
       </c>
       <c r="E655" s="3" t="n">
-        <v>719.2</v>
+        <v>721.1799999999999</v>
       </c>
       <c r="F655" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20111,25 +20111,25 @@
       </c>
       <c r="B656" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00072391SZM</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C656" s="2" t="inlineStr">
         <is>
-          <t>814493</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="D656" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E656" s="3" t="n">
-        <v>638.87</v>
+        <v>639.04</v>
       </c>
       <c r="F656" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20141,25 +20141,25 @@
       </c>
       <c r="B657" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="C657" s="2" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>814493</t>
         </is>
       </c>
       <c r="D657" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>638.49</v>
+        <v>638.87</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20185,11 +20185,11 @@
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>633.29</v>
+        <v>634.4400000000001</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20245,11 +20245,11 @@
         </is>
       </c>
       <c r="E660" s="3" t="n">
-        <v>581.85</v>
+        <v>582.37</v>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20275,11 +20275,11 @@
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>562.9299999999999</v>
+        <v>569.4</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20291,25 +20291,25 @@
       </c>
       <c r="B662" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C662" s="2" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="D662" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E662" s="3" t="n">
-        <v>557.1900000000001</v>
+        <v>561.7</v>
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20321,25 +20321,25 @@
       </c>
       <c r="B663" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C663" s="2" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="D663" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E663" s="3" t="n">
-        <v>555.3</v>
+        <v>557.1900000000001</v>
       </c>
       <c r="F663" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -20365,11 +20365,11 @@
         </is>
       </c>
       <c r="E664" s="3" t="n">
-        <v>546.52</v>
+        <v>549.22</v>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20395,11 +20395,11 @@
         </is>
       </c>
       <c r="E665" s="3" t="n">
-        <v>536.48</v>
+        <v>537.16</v>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20425,11 +20425,11 @@
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>536.3099999999999</v>
+        <v>536.86</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20441,25 +20441,25 @@
       </c>
       <c r="B667" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C667" s="2" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="D667" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E667" s="3" t="n">
-        <v>513.88</v>
+        <v>518.26</v>
       </c>
       <c r="F667" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20471,25 +20471,25 @@
       </c>
       <c r="B668" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C668" s="2" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="D668" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E668" s="3" t="n">
-        <v>512</v>
+        <v>513.88</v>
       </c>
       <c r="F668" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20545,11 +20545,11 @@
         </is>
       </c>
       <c r="E670" s="3" t="n">
-        <v>494.11</v>
+        <v>497.62</v>
       </c>
       <c r="F670" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20605,11 +20605,11 @@
         </is>
       </c>
       <c r="E672" s="3" t="n">
-        <v>473.36</v>
+        <v>476.01</v>
       </c>
       <c r="F672" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20651,12 +20651,12 @@
       </c>
       <c r="B674" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084601T5F</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C674" s="2" t="inlineStr">
         <is>
-          <t>816335</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="D674" s="2" t="inlineStr">
@@ -20665,11 +20665,11 @@
         </is>
       </c>
       <c r="E674" s="3" t="n">
-        <v>401.51</v>
+        <v>404.31</v>
       </c>
       <c r="F674" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20681,12 +20681,12 @@
       </c>
       <c r="B675" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="C675" s="2" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>816335</t>
         </is>
       </c>
       <c r="D675" s="2" t="inlineStr">
@@ -20695,11 +20695,11 @@
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>399.55</v>
+        <v>401.51</v>
       </c>
       <c r="F675" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20725,11 +20725,11 @@
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>397.34</v>
+        <v>397.41</v>
       </c>
       <c r="F676" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20755,11 +20755,11 @@
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>380.93</v>
+        <v>382.29</v>
       </c>
       <c r="F677" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20771,12 +20771,12 @@
       </c>
       <c r="B678" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C678" s="2" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="D678" s="2" t="inlineStr">
@@ -20785,11 +20785,11 @@
         </is>
       </c>
       <c r="E678" s="3" t="n">
-        <v>339.55</v>
+        <v>341.46</v>
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20801,12 +20801,12 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="D679" s="2" t="inlineStr">
@@ -20815,11 +20815,11 @@
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>338.25</v>
+        <v>340.27</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>328.52</v>
+        <v>330.88</v>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20905,11 +20905,11 @@
         </is>
       </c>
       <c r="E682" s="3" t="n">
-        <v>288.81</v>
+        <v>289.09</v>
       </c>
       <c r="F682" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20935,11 +20935,11 @@
         </is>
       </c>
       <c r="E683" s="3" t="n">
-        <v>281.02</v>
+        <v>282.87</v>
       </c>
       <c r="F683" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -20965,11 +20965,11 @@
         </is>
       </c>
       <c r="E684" s="3" t="n">
-        <v>280.91</v>
+        <v>281.35</v>
       </c>
       <c r="F684" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21055,11 +21055,11 @@
         </is>
       </c>
       <c r="E687" s="3" t="n">
-        <v>261.94</v>
+        <v>262.9</v>
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21085,11 +21085,11 @@
         </is>
       </c>
       <c r="E688" s="3" t="n">
-        <v>256.01</v>
+        <v>256.33</v>
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21115,11 +21115,11 @@
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>251.37</v>
+        <v>251.66</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21235,11 +21235,11 @@
         </is>
       </c>
       <c r="E693" s="3" t="n">
-        <v>225.79</v>
+        <v>226.5</v>
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21265,11 +21265,11 @@
         </is>
       </c>
       <c r="E694" s="3" t="n">
-        <v>221.68</v>
+        <v>222.3</v>
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>219.26</v>
+        <v>220.74</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>211.61</v>
+        <v>212.78</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>201.96</v>
+        <v>204.09</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21445,11 +21445,11 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>193.19</v>
+        <v>193.26</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>188.64</v>
+        <v>188.73</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21581,12 +21581,12 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="D705" s="2" t="inlineStr">
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>169.21</v>
+        <v>170.56</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21611,12 +21611,12 @@
       </c>
       <c r="B706" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C706" s="2" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="D706" s="2" t="inlineStr">
@@ -21625,7 +21625,7 @@
         </is>
       </c>
       <c r="E706" s="3" t="n">
-        <v>165.64</v>
+        <v>169.21</v>
       </c>
       <c r="F706" s="2" t="inlineStr">
         <is>
@@ -21685,11 +21685,11 @@
         </is>
       </c>
       <c r="E708" s="3" t="n">
-        <v>152.35</v>
+        <v>152.67</v>
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21775,11 +21775,11 @@
         </is>
       </c>
       <c r="E711" s="3" t="n">
-        <v>141.68</v>
+        <v>143</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21805,11 +21805,11 @@
         </is>
       </c>
       <c r="E712" s="3" t="n">
-        <v>139.35</v>
+        <v>140</v>
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21835,11 +21835,11 @@
         </is>
       </c>
       <c r="E713" s="3" t="n">
-        <v>138.13</v>
+        <v>138.2</v>
       </c>
       <c r="F713" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21865,11 +21865,11 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>135.96</v>
+        <v>136.04</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21911,12 +21911,12 @@
       </c>
       <c r="B716" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C716" s="2" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="D716" s="2" t="inlineStr">
@@ -21925,11 +21925,11 @@
         </is>
       </c>
       <c r="E716" s="3" t="n">
-        <v>132.39</v>
+        <v>132.89</v>
       </c>
       <c r="F716" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B717" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C717" s="2" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="D717" s="2" t="inlineStr">
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>132.38</v>
+        <v>132.39</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21971,12 +21971,12 @@
       </c>
       <c r="B718" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr">
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>131.59</v>
+        <v>132.32</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -22001,12 +22001,12 @@
       </c>
       <c r="B719" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C719" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="D719" s="2" t="inlineStr">
@@ -22015,11 +22015,11 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>131.41</v>
+        <v>131.97</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -22121,12 +22121,12 @@
       </c>
       <c r="B723" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C723" s="2" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D723" s="2" t="inlineStr">
@@ -22135,11 +22135,11 @@
         </is>
       </c>
       <c r="E723" s="3" t="n">
-        <v>129.31</v>
+        <v>129.78</v>
       </c>
       <c r="F723" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -22151,12 +22151,12 @@
       </c>
       <c r="B724" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C724" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="D724" s="2" t="inlineStr">
@@ -22165,7 +22165,7 @@
         </is>
       </c>
       <c r="E724" s="3" t="n">
-        <v>128.61</v>
+        <v>129.31</v>
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
@@ -22181,12 +22181,12 @@
       </c>
       <c r="B725" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C725" s="2" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D725" s="2" t="inlineStr">
@@ -22195,11 +22195,11 @@
         </is>
       </c>
       <c r="E725" s="3" t="n">
-        <v>127.92</v>
+        <v>128.05</v>
       </c>
       <c r="F725" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -22211,12 +22211,12 @@
       </c>
       <c r="B726" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C726" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="D726" s="2" t="inlineStr">
@@ -22225,11 +22225,11 @@
         </is>
       </c>
       <c r="E726" s="3" t="n">
-        <v>127.01</v>
+        <v>127.92</v>
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22315,11 +22315,11 @@
         </is>
       </c>
       <c r="E729" s="3" t="n">
-        <v>120.87</v>
+        <v>121.09</v>
       </c>
       <c r="F729" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -22375,11 +22375,11 @@
         </is>
       </c>
       <c r="E731" s="3" t="n">
-        <v>114.67</v>
+        <v>115.05</v>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -22495,11 +22495,11 @@
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>110.34</v>
+        <v>110.43</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -22585,11 +22585,11 @@
         </is>
       </c>
       <c r="E738" s="3" t="n">
-        <v>107.57</v>
+        <v>107.81</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -22615,11 +22615,11 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>105.26</v>
+        <v>106.59</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -22645,11 +22645,11 @@
         </is>
       </c>
       <c r="E740" s="3" t="n">
-        <v>103.83</v>
+        <v>103.92</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -22691,12 +22691,12 @@
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>103.13</v>
+        <v>103.32</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -22721,12 +22721,12 @@
       </c>
       <c r="B743" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C743" s="2" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="D743" s="2" t="inlineStr">
@@ -22735,11 +22735,11 @@
         </is>
       </c>
       <c r="E743" s="3" t="n">
-        <v>100.93</v>
+        <v>103.16</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -22751,12 +22751,12 @@
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D744" s="2" t="inlineStr">
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>100.73</v>
+        <v>101.09</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -22781,12 +22781,12 @@
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr">
@@ -22795,11 +22795,11 @@
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>100.43</v>
+        <v>100.93</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22945,11 +22945,11 @@
         </is>
       </c>
       <c r="E750" s="3" t="n">
-        <v>94.79000000000001</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="F750" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -22961,12 +22961,12 @@
       </c>
       <c r="B751" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C751" s="2" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="D751" s="2" t="inlineStr">
@@ -22975,11 +22975,11 @@
         </is>
       </c>
       <c r="E751" s="3" t="n">
-        <v>93.95999999999999</v>
+        <v>94.31</v>
       </c>
       <c r="F751" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -22991,12 +22991,12 @@
       </c>
       <c r="B752" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C752" s="2" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="D752" s="2" t="inlineStr">
@@ -23005,11 +23005,11 @@
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>92.3</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23095,11 +23095,11 @@
         </is>
       </c>
       <c r="E755" s="3" t="n">
-        <v>87.88</v>
+        <v>87.95</v>
       </c>
       <c r="F755" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -23125,11 +23125,11 @@
         </is>
       </c>
       <c r="E756" s="3" t="n">
-        <v>87.18000000000001</v>
+        <v>87.23</v>
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>85.84</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -23201,12 +23201,12 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="D759" s="2" t="inlineStr">
@@ -23215,11 +23215,11 @@
         </is>
       </c>
       <c r="E759" s="3" t="n">
-        <v>85.54000000000001</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -23231,12 +23231,12 @@
       </c>
       <c r="B760" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C760" s="2" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="D760" s="2" t="inlineStr">
@@ -23245,11 +23245,11 @@
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>85.45</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>80.59</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>77.70999999999999</v>
+        <v>78.17</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -23441,12 +23441,12 @@
       </c>
       <c r="B767" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C767" s="2" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="D767" s="2" t="inlineStr">
@@ -23455,11 +23455,11 @@
         </is>
       </c>
       <c r="E767" s="3" t="n">
-        <v>77.39</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F767" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -23471,12 +23471,12 @@
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="D768" s="2" t="inlineStr">
@@ -23485,11 +23485,11 @@
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>77.28</v>
+        <v>77.39</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23515,11 +23515,11 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>76.25</v>
+        <v>76.33</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -23531,12 +23531,12 @@
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
@@ -23545,11 +23545,11 @@
         </is>
       </c>
       <c r="E770" s="3" t="n">
-        <v>74.94</v>
+        <v>75.63</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -23561,12 +23561,12 @@
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
@@ -23575,11 +23575,11 @@
         </is>
       </c>
       <c r="E771" s="3" t="n">
-        <v>74.88</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -23695,11 +23695,11 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>73.25</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -23921,12 +23921,12 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="D783" s="2" t="inlineStr">
@@ -23935,11 +23935,11 @@
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>66.67</v>
+        <v>66.88</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -23951,12 +23951,12 @@
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
@@ -23965,11 +23965,11 @@
         </is>
       </c>
       <c r="E784" s="3" t="n">
-        <v>66.63</v>
+        <v>66.78</v>
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -23981,12 +23981,12 @@
       </c>
       <c r="B785" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C785" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="D785" s="2" t="inlineStr">
@@ -23995,11 +23995,11 @@
         </is>
       </c>
       <c r="E785" s="3" t="n">
-        <v>66.63</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="F785" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -24011,12 +24011,12 @@
       </c>
       <c r="B786" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C786" s="2" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D786" s="2" t="inlineStr">
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>66.47</v>
+        <v>66.66</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -24041,12 +24041,12 @@
       </c>
       <c r="B787" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C787" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="D787" s="2" t="inlineStr">
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>66.53</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -24071,12 +24071,12 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="D788" s="2" t="inlineStr">
@@ -24085,11 +24085,11 @@
         </is>
       </c>
       <c r="E788" s="3" t="n">
-        <v>65.66</v>
+        <v>66.5</v>
       </c>
       <c r="F788" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -24175,11 +24175,11 @@
         </is>
       </c>
       <c r="E791" s="3" t="n">
-        <v>61.58</v>
+        <v>61.69</v>
       </c>
       <c r="F791" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -24205,11 +24205,11 @@
         </is>
       </c>
       <c r="E792" s="3" t="n">
-        <v>60.11</v>
+        <v>60.12</v>
       </c>
       <c r="F792" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -24505,11 +24505,11 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>50.83</v>
+        <v>50.84</v>
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -24535,11 +24535,11 @@
         </is>
       </c>
       <c r="E803" s="3" t="n">
-        <v>50.45</v>
+        <v>50.52</v>
       </c>
       <c r="F803" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -24821,12 +24821,12 @@
       </c>
       <c r="B813" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C813" s="2" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="D813" s="2" t="inlineStr">
@@ -24835,11 +24835,11 @@
         </is>
       </c>
       <c r="E813" s="3" t="n">
-        <v>42.92</v>
+        <v>43.09</v>
       </c>
       <c r="F813" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -24851,12 +24851,12 @@
       </c>
       <c r="B814" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C814" s="2" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="D814" s="2" t="inlineStr">
@@ -24865,11 +24865,11 @@
         </is>
       </c>
       <c r="E814" s="3" t="n">
-        <v>42.84</v>
+        <v>42.92</v>
       </c>
       <c r="F814" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -25135,11 +25135,11 @@
         </is>
       </c>
       <c r="E823" s="3" t="n">
-        <v>34.4</v>
+        <v>34.59</v>
       </c>
       <c r="F823" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -25195,11 +25195,11 @@
         </is>
       </c>
       <c r="E825" s="3" t="n">
-        <v>32.73</v>
+        <v>33.29</v>
       </c>
       <c r="F825" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -25225,11 +25225,11 @@
         </is>
       </c>
       <c r="E826" s="3" t="n">
-        <v>32.4</v>
+        <v>32.41</v>
       </c>
       <c r="F826" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -25315,11 +25315,11 @@
         </is>
       </c>
       <c r="E829" s="3" t="n">
-        <v>30.74</v>
+        <v>30.77</v>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -25345,11 +25345,11 @@
         </is>
       </c>
       <c r="E830" s="3" t="n">
-        <v>30.39</v>
+        <v>30.4</v>
       </c>
       <c r="F830" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -25375,11 +25375,11 @@
         </is>
       </c>
       <c r="E831" s="3" t="n">
-        <v>29.81</v>
+        <v>29.9</v>
       </c>
       <c r="F831" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -25465,11 +25465,11 @@
         </is>
       </c>
       <c r="E834" s="3" t="n">
-        <v>28.94</v>
+        <v>29.06</v>
       </c>
       <c r="F834" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>
@@ -25555,11 +25555,11 @@
         </is>
       </c>
       <c r="E837" s="3" t="n">
-        <v>25.34</v>
+        <v>25.69</v>
       </c>
       <c r="F837" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-28 16:36</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2427.48</v>
+        <v>2560.37</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -19795,11 +19795,11 @@
         </is>
       </c>
       <c r="E645" s="3" t="n">
-        <v>2406.78</v>
+        <v>2413.34</v>
       </c>
       <c r="F645" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -19885,11 +19885,11 @@
         </is>
       </c>
       <c r="E648" s="3" t="n">
-        <v>1237.42</v>
+        <v>1291.4</v>
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>1211.83</v>
+        <v>1253.05</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -19945,11 +19945,11 @@
         </is>
       </c>
       <c r="E650" s="3" t="n">
-        <v>995.95</v>
+        <v>1059.53</v>
       </c>
       <c r="F650" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20005,11 +20005,11 @@
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>827.22</v>
+        <v>860.34</v>
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20051,12 +20051,12 @@
       </c>
       <c r="B654" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000739124KF</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C654" s="2" t="inlineStr">
         <is>
-          <t>814640</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="D654" s="2" t="inlineStr">
@@ -20065,11 +20065,11 @@
         </is>
       </c>
       <c r="E654" s="3" t="n">
-        <v>737.59</v>
+        <v>738.9400000000001</v>
       </c>
       <c r="F654" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20081,12 +20081,12 @@
       </c>
       <c r="B655" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4P000739124KF</t>
         </is>
       </c>
       <c r="C655" s="2" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>814640</t>
         </is>
       </c>
       <c r="D655" s="2" t="inlineStr">
@@ -20095,11 +20095,11 @@
         </is>
       </c>
       <c r="E655" s="3" t="n">
-        <v>721.1799999999999</v>
+        <v>737.59</v>
       </c>
       <c r="F655" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -20111,12 +20111,12 @@
       </c>
       <c r="B656" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C656" s="2" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="D656" s="2" t="inlineStr">
@@ -20125,11 +20125,11 @@
         </is>
       </c>
       <c r="E656" s="3" t="n">
-        <v>639.04</v>
+        <v>661.89</v>
       </c>
       <c r="F656" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20141,25 +20141,25 @@
       </c>
       <c r="B657" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00072391SZM</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C657" s="2" t="inlineStr">
         <is>
-          <t>814493</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="D657" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>638.87</v>
+        <v>651.3</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20171,25 +20171,25 @@
       </c>
       <c r="B658" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="C658" s="2" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>814493</t>
         </is>
       </c>
       <c r="D658" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>634.4400000000001</v>
+        <v>638.87</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20231,25 +20231,25 @@
       </c>
       <c r="B660" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C660" s="2" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="D660" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E660" s="3" t="n">
-        <v>582.37</v>
+        <v>597.91</v>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20261,12 +20261,12 @@
       </c>
       <c r="B661" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C661" s="2" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="D661" s="2" t="inlineStr">
@@ -20275,11 +20275,11 @@
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>569.4</v>
+        <v>596.58</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20291,25 +20291,25 @@
       </c>
       <c r="B662" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C662" s="2" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="D662" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E662" s="3" t="n">
-        <v>561.7</v>
+        <v>589.23</v>
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20321,25 +20321,25 @@
       </c>
       <c r="B663" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C663" s="2" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="D663" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E663" s="3" t="n">
-        <v>557.1900000000001</v>
+        <v>569.0599999999999</v>
       </c>
       <c r="F663" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20351,25 +20351,25 @@
       </c>
       <c r="B664" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E664" s="3" t="n">
-        <v>549.22</v>
+        <v>566.61</v>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20381,12 +20381,12 @@
       </c>
       <c r="B665" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
@@ -20395,11 +20395,11 @@
         </is>
       </c>
       <c r="E665" s="3" t="n">
-        <v>537.16</v>
+        <v>554.79</v>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20411,25 +20411,25 @@
       </c>
       <c r="B666" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>536.86</v>
+        <v>554.5</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20441,25 +20441,25 @@
       </c>
       <c r="B667" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C667" s="2" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="D667" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E667" s="3" t="n">
-        <v>518.26</v>
+        <v>539.09</v>
       </c>
       <c r="F667" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20501,25 +20501,25 @@
       </c>
       <c r="B669" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066901JZZ</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C669" s="2" t="inlineStr">
         <is>
-          <t>812926</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="D669" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E669" s="3" t="n">
-        <v>500.46</v>
+        <v>501.38</v>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20531,25 +20531,25 @@
       </c>
       <c r="B670" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="C670" s="2" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>812926</t>
         </is>
       </c>
       <c r="D670" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E670" s="3" t="n">
-        <v>497.62</v>
+        <v>500.46</v>
       </c>
       <c r="F670" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20561,25 +20561,25 @@
       </c>
       <c r="B671" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073152MPN</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C671" s="2" t="inlineStr">
         <is>
-          <t>814494</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="D671" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E671" s="3" t="n">
-        <v>480.85</v>
+        <v>486.23</v>
       </c>
       <c r="F671" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20591,25 +20591,25 @@
       </c>
       <c r="B672" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4P00073152MPN</t>
         </is>
       </c>
       <c r="C672" s="2" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>814494</t>
         </is>
       </c>
       <c r="D672" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E672" s="3" t="n">
-        <v>476.01</v>
+        <v>480.85</v>
       </c>
       <c r="F672" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20621,12 +20621,12 @@
       </c>
       <c r="B673" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065631CPZ</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C673" s="2" t="inlineStr">
         <is>
-          <t>812930</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="D673" s="2" t="inlineStr">
@@ -20635,11 +20635,11 @@
         </is>
       </c>
       <c r="E673" s="3" t="n">
-        <v>415.73</v>
+        <v>439.1</v>
       </c>
       <c r="F673" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20651,12 +20651,12 @@
       </c>
       <c r="B674" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="C674" s="2" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>812930</t>
         </is>
       </c>
       <c r="D674" s="2" t="inlineStr">
@@ -20665,11 +20665,11 @@
         </is>
       </c>
       <c r="E674" s="3" t="n">
-        <v>404.31</v>
+        <v>415.73</v>
       </c>
       <c r="F674" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20681,25 +20681,25 @@
       </c>
       <c r="B675" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084601T5F</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C675" s="2" t="inlineStr">
         <is>
-          <t>816335</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="D675" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>401.51</v>
+        <v>408.74</v>
       </c>
       <c r="F675" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20711,25 +20711,25 @@
       </c>
       <c r="B676" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="C676" s="2" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>816335</t>
         </is>
       </c>
       <c r="D676" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>397.41</v>
+        <v>401.51</v>
       </c>
       <c r="F676" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20755,11 +20755,11 @@
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>382.29</v>
+        <v>388.82</v>
       </c>
       <c r="F677" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20771,12 +20771,12 @@
       </c>
       <c r="B678" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C678" s="2" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="D678" s="2" t="inlineStr">
@@ -20785,11 +20785,11 @@
         </is>
       </c>
       <c r="E678" s="3" t="n">
-        <v>341.46</v>
+        <v>343.4</v>
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20801,12 +20801,12 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="D679" s="2" t="inlineStr">
@@ -20815,11 +20815,11 @@
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>340.27</v>
+        <v>342.21</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>330.88</v>
+        <v>335.49</v>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20905,11 +20905,11 @@
         </is>
       </c>
       <c r="E682" s="3" t="n">
-        <v>289.09</v>
+        <v>289.78</v>
       </c>
       <c r="F682" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20921,25 +20921,25 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="D683" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E683" s="3" t="n">
-        <v>282.87</v>
+        <v>287.18</v>
       </c>
       <c r="F683" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20951,25 +20951,25 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="D684" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E684" s="3" t="n">
-        <v>281.35</v>
+        <v>285.68</v>
       </c>
       <c r="F684" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20995,11 +20995,11 @@
         </is>
       </c>
       <c r="E685" s="3" t="n">
-        <v>275.84</v>
+        <v>278.34</v>
       </c>
       <c r="F685" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21011,12 +21011,12 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563510TWC</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
         <is>
-          <t>814433</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="D686" s="2" t="inlineStr">
@@ -21025,11 +21025,11 @@
         </is>
       </c>
       <c r="E686" s="3" t="n">
-        <v>267.37</v>
+        <v>274.84</v>
       </c>
       <c r="F686" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21041,12 +21041,12 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="D687" s="2" t="inlineStr">
@@ -21055,11 +21055,11 @@
         </is>
       </c>
       <c r="E687" s="3" t="n">
-        <v>262.9</v>
+        <v>267.37</v>
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21085,11 +21085,11 @@
         </is>
       </c>
       <c r="E688" s="3" t="n">
-        <v>256.33</v>
+        <v>260.02</v>
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21115,11 +21115,11 @@
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>251.66</v>
+        <v>256.29</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21161,12 +21161,12 @@
       </c>
       <c r="B691" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C691" s="2" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="D691" s="2" t="inlineStr">
@@ -21175,11 +21175,11 @@
         </is>
       </c>
       <c r="E691" s="3" t="n">
-        <v>237.44</v>
+        <v>242.35</v>
       </c>
       <c r="F691" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21205,11 +21205,11 @@
         </is>
       </c>
       <c r="E692" s="3" t="n">
-        <v>229.2</v>
+        <v>239.2</v>
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21221,12 +21221,12 @@
       </c>
       <c r="B693" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C693" s="2" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="D693" s="2" t="inlineStr">
@@ -21235,11 +21235,11 @@
         </is>
       </c>
       <c r="E693" s="3" t="n">
-        <v>226.5</v>
+        <v>237.44</v>
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="B694" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="C694" s="2" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>816171</t>
         </is>
       </c>
       <c r="D694" s="2" t="inlineStr">
@@ -21265,11 +21265,11 @@
         </is>
       </c>
       <c r="E694" s="3" t="n">
-        <v>222.3</v>
+        <v>224.12</v>
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21281,12 +21281,12 @@
       </c>
       <c r="B695" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872531DSZ</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C695" s="2" t="inlineStr">
         <is>
-          <t>816171</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="D695" s="2" t="inlineStr">
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>220.74</v>
+        <v>223.55</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21325,11 +21325,11 @@
         </is>
       </c>
       <c r="E696" s="3" t="n">
-        <v>218.03</v>
+        <v>219.71</v>
       </c>
       <c r="F696" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>212.78</v>
+        <v>215.97</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="E698" s="3" t="n">
-        <v>210.62</v>
+        <v>215.35</v>
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>204.09</v>
+        <v>213.41</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21445,11 +21445,11 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>193.26</v>
+        <v>199.21</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>188.73</v>
+        <v>189.94</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21491,12 +21491,12 @@
       </c>
       <c r="B702" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C702" s="2" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="D702" s="2" t="inlineStr">
@@ -21505,11 +21505,11 @@
         </is>
       </c>
       <c r="E702" s="3" t="n">
-        <v>179.07</v>
+        <v>185.84</v>
       </c>
       <c r="F702" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21521,12 +21521,12 @@
       </c>
       <c r="B703" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C703" s="2" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="D703" s="2" t="inlineStr">
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>174.82</v>
+        <v>183.34</v>
       </c>
       <c r="F703" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21551,12 +21551,12 @@
       </c>
       <c r="B704" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C704" s="2" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="D704" s="2" t="inlineStr">
@@ -21565,11 +21565,11 @@
         </is>
       </c>
       <c r="E704" s="3" t="n">
-        <v>172.72</v>
+        <v>179.96</v>
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21581,12 +21581,12 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="D705" s="2" t="inlineStr">
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>170.56</v>
+        <v>173.39</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21611,12 +21611,12 @@
       </c>
       <c r="B706" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C706" s="2" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="D706" s="2" t="inlineStr">
@@ -21625,7 +21625,7 @@
         </is>
       </c>
       <c r="E706" s="3" t="n">
-        <v>169.21</v>
+        <v>172.72</v>
       </c>
       <c r="F706" s="2" t="inlineStr">
         <is>
@@ -21641,12 +21641,12 @@
       </c>
       <c r="B707" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C707" s="2" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D707" s="2" t="inlineStr">
@@ -21655,11 +21655,11 @@
         </is>
       </c>
       <c r="E707" s="3" t="n">
-        <v>158.82</v>
+        <v>171.02</v>
       </c>
       <c r="F707" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21671,12 +21671,12 @@
       </c>
       <c r="B708" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C708" s="2" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="D708" s="2" t="inlineStr">
@@ -21685,11 +21685,11 @@
         </is>
       </c>
       <c r="E708" s="3" t="n">
-        <v>152.67</v>
+        <v>158.82</v>
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21701,12 +21701,12 @@
       </c>
       <c r="B709" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C709" s="2" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="D709" s="2" t="inlineStr">
@@ -21715,11 +21715,11 @@
         </is>
       </c>
       <c r="E709" s="3" t="n">
-        <v>150.25</v>
+        <v>155.92</v>
       </c>
       <c r="F709" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21731,12 +21731,12 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="D710" s="2" t="inlineStr">
@@ -21745,11 +21745,11 @@
         </is>
       </c>
       <c r="E710" s="3" t="n">
-        <v>145.28</v>
+        <v>150.25</v>
       </c>
       <c r="F710" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21761,12 +21761,12 @@
       </c>
       <c r="B711" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C711" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="D711" s="2" t="inlineStr">
@@ -21775,11 +21775,11 @@
         </is>
       </c>
       <c r="E711" s="3" t="n">
-        <v>143</v>
+        <v>147.39</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21791,12 +21791,12 @@
       </c>
       <c r="B712" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C712" s="2" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="D712" s="2" t="inlineStr">
@@ -21805,11 +21805,11 @@
         </is>
       </c>
       <c r="E712" s="3" t="n">
-        <v>140</v>
+        <v>145.66</v>
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21821,12 +21821,12 @@
       </c>
       <c r="B713" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C713" s="2" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D713" s="2" t="inlineStr">
@@ -21835,11 +21835,11 @@
         </is>
       </c>
       <c r="E713" s="3" t="n">
-        <v>138.2</v>
+        <v>143.26</v>
       </c>
       <c r="F713" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21851,12 +21851,12 @@
       </c>
       <c r="B714" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C714" s="2" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D714" s="2" t="inlineStr">
@@ -21865,11 +21865,11 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>136.04</v>
+        <v>142.2</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21881,12 +21881,12 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="D715" s="2" t="inlineStr">
@@ -21895,11 +21895,11 @@
         </is>
       </c>
       <c r="E715" s="3" t="n">
-        <v>135.54</v>
+        <v>141.56</v>
       </c>
       <c r="F715" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21911,12 +21911,12 @@
       </c>
       <c r="B716" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C716" s="2" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="D716" s="2" t="inlineStr">
@@ -21925,11 +21925,11 @@
         </is>
       </c>
       <c r="E716" s="3" t="n">
-        <v>132.89</v>
+        <v>140.44</v>
       </c>
       <c r="F716" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B717" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C717" s="2" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="D717" s="2" t="inlineStr">
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>132.39</v>
+        <v>139.42</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21971,12 +21971,12 @@
       </c>
       <c r="B718" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr">
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>132.32</v>
+        <v>135.76</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22001,12 +22001,12 @@
       </c>
       <c r="B719" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C719" s="2" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="D719" s="2" t="inlineStr">
@@ -22015,11 +22015,11 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>131.97</v>
+        <v>135.54</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22031,12 +22031,12 @@
       </c>
       <c r="B720" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C720" s="2" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D720" s="2" t="inlineStr">
@@ -22045,11 +22045,11 @@
         </is>
       </c>
       <c r="E720" s="3" t="n">
-        <v>131.31</v>
+        <v>134.56</v>
       </c>
       <c r="F720" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22061,12 +22061,12 @@
       </c>
       <c r="B721" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C721" s="2" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="D721" s="2" t="inlineStr">
@@ -22075,11 +22075,11 @@
         </is>
       </c>
       <c r="E721" s="3" t="n">
-        <v>131.04</v>
+        <v>133.02</v>
       </c>
       <c r="F721" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22091,12 +22091,12 @@
       </c>
       <c r="B722" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C722" s="2" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="D722" s="2" t="inlineStr">
@@ -22105,11 +22105,11 @@
         </is>
       </c>
       <c r="E722" s="3" t="n">
-        <v>130.22</v>
+        <v>132.39</v>
       </c>
       <c r="F722" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22121,12 +22121,12 @@
       </c>
       <c r="B723" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C723" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="D723" s="2" t="inlineStr">
@@ -22135,11 +22135,11 @@
         </is>
       </c>
       <c r="E723" s="3" t="n">
-        <v>129.78</v>
+        <v>131.31</v>
       </c>
       <c r="F723" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22151,12 +22151,12 @@
       </c>
       <c r="B724" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C724" s="2" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="D724" s="2" t="inlineStr">
@@ -22165,11 +22165,11 @@
         </is>
       </c>
       <c r="E724" s="3" t="n">
-        <v>129.31</v>
+        <v>131.16</v>
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22181,12 +22181,12 @@
       </c>
       <c r="B725" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C725" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="D725" s="2" t="inlineStr">
@@ -22195,11 +22195,11 @@
         </is>
       </c>
       <c r="E725" s="3" t="n">
-        <v>128.05</v>
+        <v>131.04</v>
       </c>
       <c r="F725" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22211,12 +22211,12 @@
       </c>
       <c r="B726" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C726" s="2" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="D726" s="2" t="inlineStr">
@@ -22225,11 +22225,11 @@
         </is>
       </c>
       <c r="E726" s="3" t="n">
-        <v>127.92</v>
+        <v>129.31</v>
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22241,12 +22241,12 @@
       </c>
       <c r="B727" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C727" s="2" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="D727" s="2" t="inlineStr">
@@ -22255,11 +22255,11 @@
         </is>
       </c>
       <c r="E727" s="3" t="n">
-        <v>126.03</v>
+        <v>127.92</v>
       </c>
       <c r="F727" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -22271,12 +22271,12 @@
       </c>
       <c r="B728" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C728" s="2" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="D728" s="2" t="inlineStr">
@@ -22285,11 +22285,11 @@
         </is>
       </c>
       <c r="E728" s="3" t="n">
-        <v>124.29</v>
+        <v>126.03</v>
       </c>
       <c r="F728" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22301,12 +22301,12 @@
       </c>
       <c r="B729" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C729" s="2" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="D729" s="2" t="inlineStr">
@@ -22315,11 +22315,11 @@
         </is>
       </c>
       <c r="E729" s="3" t="n">
-        <v>121.09</v>
+        <v>124.29</v>
       </c>
       <c r="F729" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-28 08:10</t>
         </is>
       </c>
     </row>
@@ -22331,12 +22331,12 @@
       </c>
       <c r="B730" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C730" s="2" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="D730" s="2" t="inlineStr">
@@ -22345,11 +22345,11 @@
         </is>
       </c>
       <c r="E730" s="3" t="n">
-        <v>119.92</v>
+        <v>121.22</v>
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22361,12 +22361,12 @@
       </c>
       <c r="B731" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="D731" s="2" t="inlineStr">
@@ -22375,11 +22375,11 @@
         </is>
       </c>
       <c r="E731" s="3" t="n">
-        <v>115.05</v>
+        <v>119.92</v>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22391,12 +22391,12 @@
       </c>
       <c r="B732" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="D732" s="2" t="inlineStr">
@@ -22405,11 +22405,11 @@
         </is>
       </c>
       <c r="E732" s="3" t="n">
-        <v>114.07</v>
+        <v>116.34</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22435,11 +22435,11 @@
         </is>
       </c>
       <c r="E733" s="3" t="n">
-        <v>113.3</v>
+        <v>115.83</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22451,12 +22451,12 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
@@ -22465,11 +22465,11 @@
         </is>
       </c>
       <c r="E734" s="3" t="n">
-        <v>113.25</v>
+        <v>114.07</v>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22481,12 +22481,12 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
@@ -22495,11 +22495,11 @@
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>110.43</v>
+        <v>113.25</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22525,11 +22525,11 @@
         </is>
       </c>
       <c r="E736" s="3" t="n">
-        <v>110.23</v>
+        <v>112.53</v>
       </c>
       <c r="F736" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22541,12 +22541,12 @@
       </c>
       <c r="B737" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="D737" s="2" t="inlineStr">
@@ -22555,11 +22555,11 @@
         </is>
       </c>
       <c r="E737" s="3" t="n">
-        <v>109.33</v>
+        <v>112.19</v>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22585,11 +22585,11 @@
         </is>
       </c>
       <c r="E738" s="3" t="n">
-        <v>107.81</v>
+        <v>111.95</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22615,11 +22615,11 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>106.59</v>
+        <v>109.64</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22631,12 +22631,12 @@
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
@@ -22645,11 +22645,11 @@
         </is>
       </c>
       <c r="E740" s="3" t="n">
-        <v>103.92</v>
+        <v>109.33</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22661,12 +22661,12 @@
       </c>
       <c r="B741" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D741" s="2" t="inlineStr">
@@ -22675,11 +22675,11 @@
         </is>
       </c>
       <c r="E741" s="3" t="n">
-        <v>103.72</v>
+        <v>108</v>
       </c>
       <c r="F741" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22691,12 +22691,12 @@
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>103.32</v>
+        <v>106.94</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22735,11 +22735,11 @@
         </is>
       </c>
       <c r="E743" s="3" t="n">
-        <v>103.16</v>
+        <v>106.11</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22751,12 +22751,12 @@
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="D744" s="2" t="inlineStr">
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>101.09</v>
+        <v>103.72</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -22811,12 +22811,12 @@
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
@@ -22825,11 +22825,11 @@
         </is>
       </c>
       <c r="E746" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>100.06</v>
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22841,12 +22841,12 @@
       </c>
       <c r="B747" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C747" s="2" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="D747" s="2" t="inlineStr">
@@ -22855,11 +22855,11 @@
         </is>
       </c>
       <c r="E747" s="3" t="n">
-        <v>98.78</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F747" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22871,12 +22871,12 @@
       </c>
       <c r="B748" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C748" s="2" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="D748" s="2" t="inlineStr">
@@ -22885,11 +22885,11 @@
         </is>
       </c>
       <c r="E748" s="3" t="n">
-        <v>97.44</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22901,12 +22901,12 @@
       </c>
       <c r="B749" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C749" s="2" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="D749" s="2" t="inlineStr">
@@ -22915,11 +22915,11 @@
         </is>
       </c>
       <c r="E749" s="3" t="n">
-        <v>97.15000000000001</v>
+        <v>98.78</v>
       </c>
       <c r="F749" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22931,12 +22931,12 @@
       </c>
       <c r="B750" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C750" s="2" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="D750" s="2" t="inlineStr">
@@ -22945,11 +22945,11 @@
         </is>
       </c>
       <c r="E750" s="3" t="n">
-        <v>94.81999999999999</v>
+        <v>97.81</v>
       </c>
       <c r="F750" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22961,12 +22961,12 @@
       </c>
       <c r="B751" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C751" s="2" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="D751" s="2" t="inlineStr">
@@ -22975,11 +22975,11 @@
         </is>
       </c>
       <c r="E751" s="3" t="n">
-        <v>94.31</v>
+        <v>97.44</v>
       </c>
       <c r="F751" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22991,12 +22991,12 @@
       </c>
       <c r="B752" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C752" s="2" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="D752" s="2" t="inlineStr">
@@ -23005,11 +23005,11 @@
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>93.95999999999999</v>
+        <v>95.47</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23021,12 +23021,12 @@
       </c>
       <c r="B753" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C753" s="2" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="D753" s="2" t="inlineStr">
@@ -23035,11 +23035,11 @@
         </is>
       </c>
       <c r="E753" s="3" t="n">
-        <v>89.79000000000001</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="F753" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23051,25 +23051,25 @@
       </c>
       <c r="B754" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C754" s="2" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="D754" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E754" s="3" t="n">
-        <v>89.48999999999999</v>
+        <v>90.83</v>
       </c>
       <c r="F754" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23081,12 +23081,12 @@
       </c>
       <c r="B755" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C755" s="2" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="D755" s="2" t="inlineStr">
@@ -23095,11 +23095,11 @@
         </is>
       </c>
       <c r="E755" s="3" t="n">
-        <v>87.95</v>
+        <v>89.89</v>
       </c>
       <c r="F755" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23111,12 +23111,12 @@
       </c>
       <c r="B756" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C756" s="2" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="D756" s="2" t="inlineStr">
@@ -23125,11 +23125,11 @@
         </is>
       </c>
       <c r="E756" s="3" t="n">
-        <v>87.23</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23141,21 +23141,21 @@
       </c>
       <c r="B757" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C757" s="2" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="D757" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E757" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F757" s="2" t="inlineStr">
         <is>
@@ -23171,12 +23171,12 @@
       </c>
       <c r="B758" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C758" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="D758" s="2" t="inlineStr">
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>86.73999999999999</v>
+        <v>88.73</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23201,12 +23201,12 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="D759" s="2" t="inlineStr">
@@ -23215,11 +23215,11 @@
         </is>
       </c>
       <c r="E759" s="3" t="n">
-        <v>85.93000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23231,12 +23231,12 @@
       </c>
       <c r="B760" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C760" s="2" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D760" s="2" t="inlineStr">
@@ -23245,11 +23245,11 @@
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>85.54000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23261,12 +23261,12 @@
       </c>
       <c r="B761" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C761" s="2" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="D761" s="2" t="inlineStr">
@@ -23275,11 +23275,11 @@
         </is>
       </c>
       <c r="E761" s="3" t="n">
-        <v>82.18000000000001</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="F761" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23291,12 +23291,12 @@
       </c>
       <c r="B762" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C762" s="2" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="D762" s="2" t="inlineStr">
@@ -23305,11 +23305,11 @@
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>81.73</v>
+        <v>84.41</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23321,12 +23321,12 @@
       </c>
       <c r="B763" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C763" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="D763" s="2" t="inlineStr">
@@ -23335,11 +23335,11 @@
         </is>
       </c>
       <c r="E763" s="3" t="n">
-        <v>81.05</v>
+        <v>82.37</v>
       </c>
       <c r="F763" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23351,12 +23351,12 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="D764" s="2" t="inlineStr">
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>80.65000000000001</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23381,12 +23381,12 @@
       </c>
       <c r="B765" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C765" s="2" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="D765" s="2" t="inlineStr">
@@ -23395,11 +23395,11 @@
         </is>
       </c>
       <c r="E765" s="3" t="n">
-        <v>79.44</v>
+        <v>81.73</v>
       </c>
       <c r="F765" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23411,12 +23411,12 @@
       </c>
       <c r="B766" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C766" s="2" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="D766" s="2" t="inlineStr">
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>78.17</v>
+        <v>81.45</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23441,12 +23441,12 @@
       </c>
       <c r="B767" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="C767" s="2" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="D767" s="2" t="inlineStr">
@@ -23455,11 +23455,11 @@
         </is>
       </c>
       <c r="E767" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>80.98</v>
       </c>
       <c r="F767" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23471,12 +23471,12 @@
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D768" s="2" t="inlineStr">
@@ -23485,11 +23485,11 @@
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>77.39</v>
+        <v>80.17</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23501,12 @@
       </c>
       <c r="B769" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C769" s="2" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="D769" s="2" t="inlineStr">
@@ -23515,11 +23515,11 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>76.33</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23531,12 +23531,12 @@
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
@@ -23545,11 +23545,11 @@
         </is>
       </c>
       <c r="E770" s="3" t="n">
-        <v>75.63</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23561,12 +23561,12 @@
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
@@ -23575,11 +23575,11 @@
         </is>
       </c>
       <c r="E771" s="3" t="n">
-        <v>75.45999999999999</v>
+        <v>79.12</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23591,12 +23591,12 @@
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -23605,11 +23605,11 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>74.76000000000001</v>
+        <v>78.34</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23621,25 +23621,25 @@
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="D773" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>77.39</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23651,12 +23651,12 @@
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr">
@@ -23665,11 +23665,11 @@
         </is>
       </c>
       <c r="E774" s="3" t="n">
-        <v>74.5</v>
+        <v>77.28</v>
       </c>
       <c r="F774" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23681,12 +23681,12 @@
       </c>
       <c r="B775" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C775" s="2" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="D775" s="2" t="inlineStr">
@@ -23695,11 +23695,11 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>73.84999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23711,12 +23711,12 @@
       </c>
       <c r="B776" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C776" s="2" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="D776" s="2" t="inlineStr">
@@ -23725,11 +23725,11 @@
         </is>
       </c>
       <c r="E776" s="3" t="n">
-        <v>72.19</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="F776" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23741,21 +23741,21 @@
       </c>
       <c r="B777" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C777" s="2" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="D777" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E777" s="3" t="n">
-        <v>71.38</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F777" s="2" t="inlineStr">
         <is>
@@ -23771,12 +23771,12 @@
       </c>
       <c r="B778" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C778" s="2" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="D778" s="2" t="inlineStr">
@@ -23785,11 +23785,11 @@
         </is>
       </c>
       <c r="E778" s="3" t="n">
-        <v>70.5</v>
+        <v>73.55</v>
       </c>
       <c r="F778" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23801,12 +23801,12 @@
       </c>
       <c r="B779" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C779" s="2" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="D779" s="2" t="inlineStr">
@@ -23815,11 +23815,11 @@
         </is>
       </c>
       <c r="E779" s="3" t="n">
-        <v>70.48</v>
+        <v>73.08</v>
       </c>
       <c r="F779" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23831,12 +23831,12 @@
       </c>
       <c r="B780" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C780" s="2" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="D780" s="2" t="inlineStr">
@@ -23845,11 +23845,11 @@
         </is>
       </c>
       <c r="E780" s="3" t="n">
-        <v>70.22</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23861,12 +23861,12 @@
       </c>
       <c r="B781" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C781" s="2" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="D781" s="2" t="inlineStr">
@@ -23875,11 +23875,11 @@
         </is>
       </c>
       <c r="E781" s="3" t="n">
-        <v>69.56999999999999</v>
+        <v>71.38</v>
       </c>
       <c r="F781" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23891,12 +23891,12 @@
       </c>
       <c r="B782" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C782" s="2" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="D782" s="2" t="inlineStr">
@@ -23905,11 +23905,11 @@
         </is>
       </c>
       <c r="E782" s="3" t="n">
-        <v>68.5</v>
+        <v>70.98</v>
       </c>
       <c r="F782" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23921,12 +23921,12 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="D783" s="2" t="inlineStr">
@@ -23935,11 +23935,11 @@
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>66.88</v>
+        <v>70.63</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23951,12 +23951,12 @@
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
@@ -23965,11 +23965,11 @@
         </is>
       </c>
       <c r="E784" s="3" t="n">
-        <v>66.78</v>
+        <v>70.48</v>
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23981,12 +23981,12 @@
       </c>
       <c r="B785" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C785" s="2" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D785" s="2" t="inlineStr">
@@ -23995,11 +23995,11 @@
         </is>
       </c>
       <c r="E785" s="3" t="n">
-        <v>66.68000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F785" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -24011,12 +24011,12 @@
       </c>
       <c r="B786" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C786" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="D786" s="2" t="inlineStr">
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>66.66</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -24041,12 +24041,12 @@
       </c>
       <c r="B787" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C787" s="2" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="D787" s="2" t="inlineStr">
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>66.53</v>
+        <v>68.5</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -24071,12 +24071,12 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="D788" s="2" t="inlineStr">
@@ -24085,11 +24085,11 @@
         </is>
       </c>
       <c r="E788" s="3" t="n">
-        <v>66.5</v>
+        <v>66.77</v>
       </c>
       <c r="F788" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -24101,12 +24101,12 @@
       </c>
       <c r="B789" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C789" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="D789" s="2" t="inlineStr">
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>63.6</v>
+        <v>65.84</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -24131,12 +24131,12 @@
       </c>
       <c r="B790" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C790" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="D790" s="2" t="inlineStr">
@@ -24145,11 +24145,11 @@
         </is>
       </c>
       <c r="E790" s="3" t="n">
-        <v>61.96</v>
+        <v>64.13</v>
       </c>
       <c r="F790" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -24161,12 +24161,12 @@
       </c>
       <c r="B791" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C791" s="2" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="D791" s="2" t="inlineStr">
@@ -24175,11 +24175,11 @@
         </is>
       </c>
       <c r="E791" s="3" t="n">
-        <v>61.69</v>
+        <v>63.6</v>
       </c>
       <c r="F791" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24191,12 +24191,12 @@
       </c>
       <c r="B792" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C792" s="2" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D792" s="2" t="inlineStr">
@@ -24205,11 +24205,11 @@
         </is>
       </c>
       <c r="E792" s="3" t="n">
-        <v>60.12</v>
+        <v>61.96</v>
       </c>
       <c r="F792" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -24221,12 +24221,12 @@
       </c>
       <c r="B793" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C793" s="2" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="D793" s="2" t="inlineStr">
@@ -24235,11 +24235,11 @@
         </is>
       </c>
       <c r="E793" s="3" t="n">
-        <v>57.93</v>
+        <v>61.07</v>
       </c>
       <c r="F793" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -24251,25 +24251,25 @@
       </c>
       <c r="B794" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C794" s="2" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="D794" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E794" s="3" t="n">
-        <v>57.22</v>
+        <v>60.67</v>
       </c>
       <c r="F794" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -24281,21 +24281,21 @@
       </c>
       <c r="B795" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C795" s="2" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="D795" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E795" s="3" t="n">
-        <v>56.5</v>
+        <v>57.22</v>
       </c>
       <c r="F795" s="2" t="inlineStr">
         <is>
@@ -24311,12 +24311,12 @@
       </c>
       <c r="B796" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C796" s="2" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="D796" s="2" t="inlineStr">
@@ -24325,11 +24325,11 @@
         </is>
       </c>
       <c r="E796" s="3" t="n">
-        <v>55.14</v>
+        <v>56.2</v>
       </c>
       <c r="F796" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -24341,12 +24341,12 @@
       </c>
       <c r="B797" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C797" s="2" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="D797" s="2" t="inlineStr">
@@ -24355,11 +24355,11 @@
         </is>
       </c>
       <c r="E797" s="3" t="n">
-        <v>54.84</v>
+        <v>55.14</v>
       </c>
       <c r="F797" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24371,12 +24371,12 @@
       </c>
       <c r="B798" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C798" s="2" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="D798" s="2" t="inlineStr">
@@ -24385,11 +24385,11 @@
         </is>
       </c>
       <c r="E798" s="3" t="n">
-        <v>54.09</v>
+        <v>55</v>
       </c>
       <c r="F798" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -24431,12 +24431,12 @@
       </c>
       <c r="B800" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C800" s="2" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="D800" s="2" t="inlineStr">
@@ -24445,11 +24445,11 @@
         </is>
       </c>
       <c r="E800" s="3" t="n">
-        <v>52.57</v>
+        <v>53.17</v>
       </c>
       <c r="F800" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -24461,12 +24461,12 @@
       </c>
       <c r="B801" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C801" s="2" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="D801" s="2" t="inlineStr">
@@ -24475,11 +24475,11 @@
         </is>
       </c>
       <c r="E801" s="3" t="n">
-        <v>52.53</v>
+        <v>52.57</v>
       </c>
       <c r="F801" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24491,12 +24491,12 @@
       </c>
       <c r="B802" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C802" s="2" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="D802" s="2" t="inlineStr">
@@ -24505,11 +24505,11 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>50.84</v>
+        <v>52.53</v>
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -24535,11 +24535,11 @@
         </is>
       </c>
       <c r="E803" s="3" t="n">
-        <v>50.52</v>
+        <v>51.44</v>
       </c>
       <c r="F803" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -24701,12 +24701,12 @@
       </c>
       <c r="B809" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C809" s="2" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="D809" s="2" t="inlineStr">
@@ -24715,11 +24715,11 @@
         </is>
       </c>
       <c r="E809" s="3" t="n">
-        <v>46.4</v>
+        <v>46.96</v>
       </c>
       <c r="F809" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -24745,11 +24745,11 @@
         </is>
       </c>
       <c r="E810" s="3" t="n">
-        <v>45</v>
+        <v>46.81</v>
       </c>
       <c r="F810" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -24761,12 +24761,12 @@
       </c>
       <c r="B811" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C811" s="2" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="D811" s="2" t="inlineStr">
@@ -24775,11 +24775,11 @@
         </is>
       </c>
       <c r="E811" s="3" t="n">
-        <v>44.8</v>
+        <v>46.4</v>
       </c>
       <c r="F811" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24791,12 +24791,12 @@
       </c>
       <c r="B812" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C812" s="2" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="D812" s="2" t="inlineStr">
@@ -24805,11 +24805,11 @@
         </is>
       </c>
       <c r="E812" s="3" t="n">
-        <v>44.19</v>
+        <v>44.95</v>
       </c>
       <c r="F812" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -24821,12 +24821,12 @@
       </c>
       <c r="B813" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C813" s="2" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="D813" s="2" t="inlineStr">
@@ -24835,11 +24835,11 @@
         </is>
       </c>
       <c r="E813" s="3" t="n">
-        <v>43.09</v>
+        <v>44.8</v>
       </c>
       <c r="F813" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24865,11 +24865,11 @@
         </is>
       </c>
       <c r="E814" s="3" t="n">
-        <v>42.92</v>
+        <v>44.45</v>
       </c>
       <c r="F814" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -24881,12 +24881,12 @@
       </c>
       <c r="B815" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C815" s="2" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="D815" s="2" t="inlineStr">
@@ -24895,11 +24895,11 @@
         </is>
       </c>
       <c r="E815" s="3" t="n">
-        <v>41.12</v>
+        <v>44.19</v>
       </c>
       <c r="F815" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24925,11 +24925,11 @@
         </is>
       </c>
       <c r="E816" s="3" t="n">
-        <v>39.43</v>
+        <v>41.14</v>
       </c>
       <c r="F816" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -24941,12 +24941,12 @@
       </c>
       <c r="B817" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C817" s="2" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="D817" s="2" t="inlineStr">
@@ -24955,11 +24955,11 @@
         </is>
       </c>
       <c r="E817" s="3" t="n">
-        <v>39.39</v>
+        <v>39.85</v>
       </c>
       <c r="F817" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -24971,12 +24971,12 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="D818" s="2" t="inlineStr">
@@ -24985,11 +24985,11 @@
         </is>
       </c>
       <c r="E818" s="3" t="n">
-        <v>37.65</v>
+        <v>39.39</v>
       </c>
       <c r="F818" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -25001,12 +25001,12 @@
       </c>
       <c r="B819" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C819" s="2" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="D819" s="2" t="inlineStr">
@@ -25015,11 +25015,11 @@
         </is>
       </c>
       <c r="E819" s="3" t="n">
-        <v>36.75</v>
+        <v>37.65</v>
       </c>
       <c r="F819" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25031,12 +25031,12 @@
       </c>
       <c r="B820" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C820" s="2" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D820" s="2" t="inlineStr">
@@ -25045,11 +25045,11 @@
         </is>
       </c>
       <c r="E820" s="3" t="n">
-        <v>36.59</v>
+        <v>37.42</v>
       </c>
       <c r="F820" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -25061,12 +25061,12 @@
       </c>
       <c r="B821" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C821" s="2" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="D821" s="2" t="inlineStr">
@@ -25075,11 +25075,11 @@
         </is>
       </c>
       <c r="E821" s="3" t="n">
-        <v>36.31</v>
+        <v>36.75</v>
       </c>
       <c r="F821" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25091,12 +25091,12 @@
       </c>
       <c r="B822" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C822" s="2" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="D822" s="2" t="inlineStr">
@@ -25105,11 +25105,11 @@
         </is>
       </c>
       <c r="E822" s="3" t="n">
-        <v>34.64</v>
+        <v>36.59</v>
       </c>
       <c r="F822" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -25121,12 +25121,12 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="D823" s="2" t="inlineStr">
@@ -25135,11 +25135,11 @@
         </is>
       </c>
       <c r="E823" s="3" t="n">
-        <v>34.59</v>
+        <v>36.31</v>
       </c>
       <c r="F823" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25151,12 +25151,12 @@
       </c>
       <c r="B824" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C824" s="2" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="D824" s="2" t="inlineStr">
@@ -25165,11 +25165,11 @@
         </is>
       </c>
       <c r="E824" s="3" t="n">
-        <v>34.05</v>
+        <v>36.05</v>
       </c>
       <c r="F824" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -25181,12 +25181,12 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="D825" s="2" t="inlineStr">
@@ -25195,11 +25195,11 @@
         </is>
       </c>
       <c r="E825" s="3" t="n">
-        <v>33.29</v>
+        <v>34.92</v>
       </c>
       <c r="F825" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -25211,12 +25211,12 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="D826" s="2" t="inlineStr">
@@ -25225,11 +25225,11 @@
         </is>
       </c>
       <c r="E826" s="3" t="n">
-        <v>32.41</v>
+        <v>34.64</v>
       </c>
       <c r="F826" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25241,12 +25241,12 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="D827" s="2" t="inlineStr">
@@ -25255,11 +25255,11 @@
         </is>
       </c>
       <c r="E827" s="3" t="n">
-        <v>31.83</v>
+        <v>34.05</v>
       </c>
       <c r="F827" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25271,12 +25271,12 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="D828" s="2" t="inlineStr">
@@ -25285,11 +25285,11 @@
         </is>
       </c>
       <c r="E828" s="3" t="n">
-        <v>31.24</v>
+        <v>32.52</v>
       </c>
       <c r="F828" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -25315,11 +25315,11 @@
         </is>
       </c>
       <c r="E829" s="3" t="n">
-        <v>30.77</v>
+        <v>31.45</v>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -25331,12 +25331,12 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="D830" s="2" t="inlineStr">
@@ -25345,11 +25345,11 @@
         </is>
       </c>
       <c r="E830" s="3" t="n">
-        <v>30.4</v>
+        <v>31.24</v>
       </c>
       <c r="F830" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25361,12 +25361,12 @@
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C831" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="D831" s="2" t="inlineStr">
@@ -25375,11 +25375,11 @@
         </is>
       </c>
       <c r="E831" s="3" t="n">
-        <v>29.9</v>
+        <v>30.89</v>
       </c>
       <c r="F831" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -25421,12 +25421,12 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="D833" s="2" t="inlineStr">
@@ -25435,11 +25435,11 @@
         </is>
       </c>
       <c r="E833" s="3" t="n">
-        <v>29.27</v>
+        <v>29.65</v>
       </c>
       <c r="F833" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -25451,12 +25451,12 @@
       </c>
       <c r="B834" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C834" s="2" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="D834" s="2" t="inlineStr">
@@ -25465,11 +25465,11 @@
         </is>
       </c>
       <c r="E834" s="3" t="n">
-        <v>29.06</v>
+        <v>29.27</v>
       </c>
       <c r="F834" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25511,12 +25511,12 @@
       </c>
       <c r="B836" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C836" s="2" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="D836" s="2" t="inlineStr">
@@ -25525,11 +25525,11 @@
         </is>
       </c>
       <c r="E836" s="3" t="n">
-        <v>26.15</v>
+        <v>26.29</v>
       </c>
       <c r="F836" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -25541,12 +25541,12 @@
       </c>
       <c r="B837" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C837" s="2" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="D837" s="2" t="inlineStr">
@@ -25555,11 +25555,11 @@
         </is>
       </c>
       <c r="E837" s="3" t="n">
-        <v>25.69</v>
+        <v>26.15</v>
       </c>
       <c r="F837" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:36</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -26261,12 +26261,12 @@
       </c>
       <c r="B861" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413773R6G</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C861" s="2" t="inlineStr">
         <is>
-          <t>812807</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="D861" s="2" t="inlineStr">
@@ -26275,11 +26275,11 @@
         </is>
       </c>
       <c r="E861" s="3" t="n">
-        <v>7.92</v>
+        <v>8.32</v>
       </c>
       <c r="F861" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -26291,12 +26291,12 @@
       </c>
       <c r="B862" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0541381584X</t>
+          <t>KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="C862" s="2" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>812807</t>
         </is>
       </c>
       <c r="D862" s="2" t="inlineStr">
@@ -26305,11 +26305,11 @@
         </is>
       </c>
       <c r="E862" s="3" t="n">
-        <v>7.74</v>
+        <v>7.92</v>
       </c>
       <c r="F862" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-25 21:10</t>
         </is>
       </c>
     </row>
@@ -26321,12 +26321,12 @@
       </c>
       <c r="B863" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M0541381584X</t>
         </is>
       </c>
       <c r="C863" s="2" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>812810</t>
         </is>
       </c>
       <c r="D863" s="2" t="inlineStr">
@@ -26335,7 +26335,7 @@
         </is>
       </c>
       <c r="E863" s="3" t="n">
-        <v>7.52</v>
+        <v>7.74</v>
       </c>
       <c r="F863" s="2" t="inlineStr">
         <is>
@@ -26351,12 +26351,12 @@
       </c>
       <c r="B864" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C864" s="2" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="D864" s="2" t="inlineStr">
@@ -26365,11 +26365,11 @@
         </is>
       </c>
       <c r="E864" s="3" t="n">
-        <v>7.11</v>
+        <v>7.52</v>
       </c>
       <c r="F864" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2560.37</v>
+        <v>2608.53</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -19795,11 +19795,11 @@
         </is>
       </c>
       <c r="E645" s="3" t="n">
-        <v>2413.34</v>
+        <v>2414.8</v>
       </c>
       <c r="F645" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -19885,11 +19885,11 @@
         </is>
       </c>
       <c r="E648" s="3" t="n">
-        <v>1291.4</v>
+        <v>1301.63</v>
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>1253.05</v>
+        <v>1262.1</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -19945,11 +19945,11 @@
         </is>
       </c>
       <c r="E650" s="3" t="n">
-        <v>1059.53</v>
+        <v>1067.18</v>
       </c>
       <c r="F650" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20005,11 +20005,11 @@
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>860.34</v>
+        <v>866.55</v>
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20065,11 +20065,11 @@
         </is>
       </c>
       <c r="E654" s="3" t="n">
-        <v>738.9400000000001</v>
+        <v>743.6900000000001</v>
       </c>
       <c r="F654" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20125,11 +20125,11 @@
         </is>
       </c>
       <c r="E656" s="3" t="n">
-        <v>661.89</v>
+        <v>662.9299999999999</v>
       </c>
       <c r="F656" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20155,11 +20155,11 @@
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>651.3</v>
+        <v>652.3099999999999</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20231,12 +20231,12 @@
       </c>
       <c r="B660" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C660" s="2" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="D660" s="2" t="inlineStr">
@@ -20245,11 +20245,11 @@
         </is>
       </c>
       <c r="E660" s="3" t="n">
-        <v>597.91</v>
+        <v>603.14</v>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20261,12 +20261,12 @@
       </c>
       <c r="B661" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C661" s="2" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="D661" s="2" t="inlineStr">
@@ -20275,11 +20275,11 @@
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>596.58</v>
+        <v>603.0599999999999</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20305,11 +20305,11 @@
         </is>
       </c>
       <c r="E662" s="3" t="n">
-        <v>589.23</v>
+        <v>590.4</v>
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         </is>
       </c>
       <c r="E663" s="3" t="n">
-        <v>569.0599999999999</v>
+        <v>574.0599999999999</v>
       </c>
       <c r="F663" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20351,25 +20351,25 @@
       </c>
       <c r="B664" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E664" s="3" t="n">
-        <v>566.61</v>
+        <v>571.48</v>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20381,25 +20381,25 @@
       </c>
       <c r="B665" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E665" s="3" t="n">
-        <v>554.79</v>
+        <v>566.73</v>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20425,11 +20425,11 @@
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>554.5</v>
+        <v>556.37</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20455,11 +20455,11 @@
         </is>
       </c>
       <c r="E667" s="3" t="n">
-        <v>539.09</v>
+        <v>540.12</v>
       </c>
       <c r="F667" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20575,11 +20575,11 @@
         </is>
       </c>
       <c r="E671" s="3" t="n">
-        <v>486.23</v>
+        <v>492.99</v>
       </c>
       <c r="F671" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20635,11 +20635,11 @@
         </is>
       </c>
       <c r="E673" s="3" t="n">
-        <v>439.1</v>
+        <v>442.76</v>
       </c>
       <c r="F673" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20695,11 +20695,11 @@
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>408.74</v>
+        <v>409.4</v>
       </c>
       <c r="F675" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20755,11 +20755,11 @@
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>388.82</v>
+        <v>390.29</v>
       </c>
       <c r="F677" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20785,11 +20785,11 @@
         </is>
       </c>
       <c r="E678" s="3" t="n">
-        <v>343.4</v>
+        <v>344.6</v>
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20815,11 +20815,11 @@
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>342.21</v>
+        <v>344.57</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>335.49</v>
+        <v>335.69</v>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20905,11 +20905,11 @@
         </is>
       </c>
       <c r="E682" s="3" t="n">
-        <v>289.78</v>
+        <v>295.99</v>
       </c>
       <c r="F682" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -20935,11 +20935,11 @@
         </is>
       </c>
       <c r="E683" s="3" t="n">
-        <v>287.18</v>
+        <v>287.66</v>
       </c>
       <c r="F683" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21025,11 +21025,11 @@
         </is>
       </c>
       <c r="E686" s="3" t="n">
-        <v>274.84</v>
+        <v>276.3</v>
       </c>
       <c r="F686" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21085,11 +21085,11 @@
         </is>
       </c>
       <c r="E688" s="3" t="n">
-        <v>260.02</v>
+        <v>260.79</v>
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21115,11 +21115,11 @@
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>256.29</v>
+        <v>257.71</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21175,11 +21175,11 @@
         </is>
       </c>
       <c r="E691" s="3" t="n">
-        <v>242.35</v>
+        <v>242.99</v>
       </c>
       <c r="F691" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21205,11 +21205,11 @@
         </is>
       </c>
       <c r="E692" s="3" t="n">
-        <v>239.2</v>
+        <v>239.6</v>
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>223.55</v>
+        <v>223.61</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21325,11 +21325,11 @@
         </is>
       </c>
       <c r="E696" s="3" t="n">
-        <v>219.71</v>
+        <v>219.91</v>
       </c>
       <c r="F696" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>215.97</v>
+        <v>218.19</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21371,12 +21371,12 @@
       </c>
       <c r="B698" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C698" s="2" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="D698" s="2" t="inlineStr">
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="E698" s="3" t="n">
-        <v>215.35</v>
+        <v>216.52</v>
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21401,12 +21401,12 @@
       </c>
       <c r="B699" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C699" s="2" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="D699" s="2" t="inlineStr">
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>213.41</v>
+        <v>215.36</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21445,11 +21445,11 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>199.21</v>
+        <v>199.37</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>189.94</v>
+        <v>190.35</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21521,12 +21521,12 @@
       </c>
       <c r="B703" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C703" s="2" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="D703" s="2" t="inlineStr">
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>183.34</v>
+        <v>183.76</v>
       </c>
       <c r="F703" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21551,12 +21551,12 @@
       </c>
       <c r="B704" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C704" s="2" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="D704" s="2" t="inlineStr">
@@ -21565,11 +21565,11 @@
         </is>
       </c>
       <c r="E704" s="3" t="n">
-        <v>179.96</v>
+        <v>183.69</v>
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>173.39</v>
+        <v>173.65</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21715,11 +21715,11 @@
         </is>
       </c>
       <c r="E709" s="3" t="n">
-        <v>155.92</v>
+        <v>156.6</v>
       </c>
       <c r="F709" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21775,11 +21775,11 @@
         </is>
       </c>
       <c r="E711" s="3" t="n">
-        <v>147.39</v>
+        <v>148.38</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21805,11 +21805,11 @@
         </is>
       </c>
       <c r="E712" s="3" t="n">
-        <v>145.66</v>
+        <v>145.68</v>
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21835,11 +21835,11 @@
         </is>
       </c>
       <c r="E713" s="3" t="n">
-        <v>143.26</v>
+        <v>143.67</v>
       </c>
       <c r="F713" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21851,12 +21851,12 @@
       </c>
       <c r="B714" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C714" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="D714" s="2" t="inlineStr">
@@ -21865,11 +21865,11 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>142.2</v>
+        <v>142.81</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21881,12 +21881,12 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D715" s="2" t="inlineStr">
@@ -21895,11 +21895,11 @@
         </is>
       </c>
       <c r="E715" s="3" t="n">
-        <v>141.56</v>
+        <v>142.8</v>
       </c>
       <c r="F715" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21911,12 +21911,12 @@
       </c>
       <c r="B716" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C716" s="2" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="D716" s="2" t="inlineStr">
@@ -21925,7 +21925,7 @@
         </is>
       </c>
       <c r="E716" s="3" t="n">
-        <v>140.44</v>
+        <v>141.56</v>
       </c>
       <c r="F716" s="2" t="inlineStr">
         <is>
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>139.42</v>
+        <v>139.64</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21971,12 +21971,12 @@
       </c>
       <c r="B718" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr">
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>135.76</v>
+        <v>136.12</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -22001,12 +22001,12 @@
       </c>
       <c r="B719" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C719" s="2" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D719" s="2" t="inlineStr">
@@ -22015,11 +22015,11 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>135.54</v>
+        <v>135.77</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -22031,12 +22031,12 @@
       </c>
       <c r="B720" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C720" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="D720" s="2" t="inlineStr">
@@ -22045,11 +22045,11 @@
         </is>
       </c>
       <c r="E720" s="3" t="n">
-        <v>134.56</v>
+        <v>135.55</v>
       </c>
       <c r="F720" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -22345,11 +22345,11 @@
         </is>
       </c>
       <c r="E730" s="3" t="n">
-        <v>121.22</v>
+        <v>122.06</v>
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -22405,11 +22405,11 @@
         </is>
       </c>
       <c r="E732" s="3" t="n">
-        <v>116.34</v>
+        <v>117.34</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -22481,12 +22481,12 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
@@ -22495,11 +22495,11 @@
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>113.25</v>
+        <v>113.28</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -22511,12 +22511,12 @@
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
@@ -22525,11 +22525,11 @@
         </is>
       </c>
       <c r="E736" s="3" t="n">
-        <v>112.53</v>
+        <v>113.25</v>
       </c>
       <c r="F736" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22541,12 +22541,12 @@
       </c>
       <c r="B737" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D737" s="2" t="inlineStr">
@@ -22555,11 +22555,11 @@
         </is>
       </c>
       <c r="E737" s="3" t="n">
-        <v>112.19</v>
+        <v>112.74</v>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -22571,12 +22571,12 @@
       </c>
       <c r="B738" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="D738" s="2" t="inlineStr">
@@ -22585,7 +22585,7 @@
         </is>
       </c>
       <c r="E738" s="3" t="n">
-        <v>111.95</v>
+        <v>112.53</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
@@ -22601,12 +22601,12 @@
       </c>
       <c r="B739" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C739" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="D739" s="2" t="inlineStr">
@@ -22615,11 +22615,11 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>109.64</v>
+        <v>112.27</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -22631,12 +22631,12 @@
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
@@ -22645,11 +22645,11 @@
         </is>
       </c>
       <c r="E740" s="3" t="n">
-        <v>109.33</v>
+        <v>109.36</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -22661,12 +22661,12 @@
       </c>
       <c r="B741" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="D741" s="2" t="inlineStr">
@@ -22675,11 +22675,11 @@
         </is>
       </c>
       <c r="E741" s="3" t="n">
-        <v>108</v>
+        <v>109.33</v>
       </c>
       <c r="F741" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>106.94</v>
+        <v>108.12</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -22735,11 +22735,11 @@
         </is>
       </c>
       <c r="E743" s="3" t="n">
-        <v>106.11</v>
+        <v>106.63</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>103.72</v>
+        <v>103.89</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -22781,12 +22781,12 @@
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr">
@@ -22795,11 +22795,11 @@
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>100.93</v>
+        <v>101.94</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -22811,12 +22811,12 @@
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
@@ -22825,11 +22825,11 @@
         </is>
       </c>
       <c r="E746" s="3" t="n">
-        <v>100.06</v>
+        <v>100.93</v>
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22885,11 +22885,11 @@
         </is>
       </c>
       <c r="E748" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>99.77</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -23005,11 +23005,11 @@
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>95.47</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -23021,12 +23021,12 @@
       </c>
       <c r="B753" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C753" s="2" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="D753" s="2" t="inlineStr">
@@ -23035,11 +23035,11 @@
         </is>
       </c>
       <c r="E753" s="3" t="n">
-        <v>93.95999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F753" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -23051,12 +23051,12 @@
       </c>
       <c r="B754" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C754" s="2" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="D754" s="2" t="inlineStr">
@@ -23065,11 +23065,11 @@
         </is>
       </c>
       <c r="E754" s="3" t="n">
-        <v>90.83</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="F754" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23095,11 +23095,11 @@
         </is>
       </c>
       <c r="E755" s="3" t="n">
-        <v>89.89</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="F755" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>88.73</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -23245,11 +23245,11 @@
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>86.3</v>
+        <v>86.38</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -23305,11 +23305,11 @@
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>84.41</v>
+        <v>84.73</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -23335,11 +23335,11 @@
         </is>
       </c>
       <c r="E763" s="3" t="n">
-        <v>82.37</v>
+        <v>82.7</v>
       </c>
       <c r="F763" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -23351,12 +23351,12 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="D764" s="2" t="inlineStr">
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>82.18000000000001</v>
+        <v>82.19</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -23381,12 +23381,12 @@
       </c>
       <c r="B765" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C765" s="2" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="D765" s="2" t="inlineStr">
@@ -23395,11 +23395,11 @@
         </is>
       </c>
       <c r="E765" s="3" t="n">
-        <v>81.73</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F765" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23411,12 +23411,12 @@
       </c>
       <c r="B766" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C766" s="2" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="D766" s="2" t="inlineStr">
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>81.45</v>
+        <v>81.73</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23471,12 +23471,12 @@
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="D768" s="2" t="inlineStr">
@@ -23485,11 +23485,11 @@
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>80.17</v>
+        <v>80.22</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23501,12 @@
       </c>
       <c r="B769" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C769" s="2" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D769" s="2" t="inlineStr">
@@ -23515,7 +23515,7 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>79.79000000000001</v>
+        <v>80.17</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
@@ -23531,12 +23531,12 @@
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
@@ -23545,11 +23545,11 @@
         </is>
       </c>
       <c r="E770" s="3" t="n">
-        <v>79.79000000000001</v>
+        <v>79.86</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -23561,12 +23561,12 @@
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
@@ -23575,11 +23575,11 @@
         </is>
       </c>
       <c r="E771" s="3" t="n">
-        <v>79.12</v>
+        <v>79.47</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -23591,12 +23591,12 @@
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -23605,7 +23605,7 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>78.34</v>
+        <v>79.12</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
@@ -23621,12 +23621,12 @@
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="D773" s="2" t="inlineStr">
@@ -23635,11 +23635,11 @@
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>77.39</v>
+        <v>77.7</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -23651,12 +23651,12 @@
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr">
@@ -23665,11 +23665,11 @@
         </is>
       </c>
       <c r="E774" s="3" t="n">
-        <v>77.28</v>
+        <v>77.39</v>
       </c>
       <c r="F774" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -23815,11 +23815,11 @@
         </is>
       </c>
       <c r="E779" s="3" t="n">
-        <v>73.08</v>
+        <v>73.39</v>
       </c>
       <c r="F779" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         </is>
       </c>
       <c r="E782" s="3" t="n">
-        <v>70.98</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="F782" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -23935,11 +23935,11 @@
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>70.63</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -23995,11 +23995,11 @@
         </is>
       </c>
       <c r="E785" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>69.56</v>
       </c>
       <c r="F785" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>68.51000000000001</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -24085,11 +24085,11 @@
         </is>
       </c>
       <c r="E788" s="3" t="n">
-        <v>66.77</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F788" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>65.84</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -24145,11 +24145,11 @@
         </is>
       </c>
       <c r="E790" s="3" t="n">
-        <v>64.13</v>
+        <v>64.28</v>
       </c>
       <c r="F790" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -24235,11 +24235,11 @@
         </is>
       </c>
       <c r="E793" s="3" t="n">
-        <v>61.07</v>
+        <v>61.08</v>
       </c>
       <c r="F793" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -24265,11 +24265,11 @@
         </is>
       </c>
       <c r="E794" s="3" t="n">
-        <v>60.67</v>
+        <v>60.68</v>
       </c>
       <c r="F794" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -24325,11 +24325,11 @@
         </is>
       </c>
       <c r="E796" s="3" t="n">
-        <v>56.2</v>
+        <v>56.26</v>
       </c>
       <c r="F796" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -24385,11 +24385,11 @@
         </is>
       </c>
       <c r="E798" s="3" t="n">
-        <v>55</v>
+        <v>55.07</v>
       </c>
       <c r="F798" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -24671,12 +24671,12 @@
       </c>
       <c r="B808" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C808" s="2" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="D808" s="2" t="inlineStr">
@@ -24685,11 +24685,11 @@
         </is>
       </c>
       <c r="E808" s="3" t="n">
-        <v>47.23</v>
+        <v>47.83</v>
       </c>
       <c r="F808" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -24701,12 +24701,12 @@
       </c>
       <c r="B809" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C809" s="2" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="D809" s="2" t="inlineStr">
@@ -24715,11 +24715,11 @@
         </is>
       </c>
       <c r="E809" s="3" t="n">
-        <v>46.96</v>
+        <v>47.33</v>
       </c>
       <c r="F809" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -24731,12 +24731,12 @@
       </c>
       <c r="B810" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C810" s="2" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="D810" s="2" t="inlineStr">
@@ -24745,11 +24745,11 @@
         </is>
       </c>
       <c r="E810" s="3" t="n">
-        <v>46.81</v>
+        <v>47.23</v>
       </c>
       <c r="F810" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24955,11 +24955,11 @@
         </is>
       </c>
       <c r="E817" s="3" t="n">
-        <v>39.85</v>
+        <v>40.11</v>
       </c>
       <c r="F817" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -25061,12 +25061,12 @@
       </c>
       <c r="B821" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C821" s="2" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="D821" s="2" t="inlineStr">
@@ -25075,11 +25075,11 @@
         </is>
       </c>
       <c r="E821" s="3" t="n">
-        <v>36.75</v>
+        <v>36.93</v>
       </c>
       <c r="F821" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -25091,12 +25091,12 @@
       </c>
       <c r="B822" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C822" s="2" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="D822" s="2" t="inlineStr">
@@ -25105,11 +25105,11 @@
         </is>
       </c>
       <c r="E822" s="3" t="n">
-        <v>36.59</v>
+        <v>36.75</v>
       </c>
       <c r="F822" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25121,12 +25121,12 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="D823" s="2" t="inlineStr">
@@ -25135,11 +25135,11 @@
         </is>
       </c>
       <c r="E823" s="3" t="n">
-        <v>36.31</v>
+        <v>36.59</v>
       </c>
       <c r="F823" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -25151,12 +25151,12 @@
       </c>
       <c r="B824" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C824" s="2" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="D824" s="2" t="inlineStr">
@@ -25165,11 +25165,11 @@
         </is>
       </c>
       <c r="E824" s="3" t="n">
-        <v>36.05</v>
+        <v>36.31</v>
       </c>
       <c r="F824" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25181,12 +25181,12 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="D825" s="2" t="inlineStr">
@@ -25195,11 +25195,11 @@
         </is>
       </c>
       <c r="E825" s="3" t="n">
-        <v>34.92</v>
+        <v>36.06</v>
       </c>
       <c r="F825" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -25285,11 +25285,11 @@
         </is>
       </c>
       <c r="E828" s="3" t="n">
-        <v>32.52</v>
+        <v>32.76</v>
       </c>
       <c r="F828" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -25315,11 +25315,11 @@
         </is>
       </c>
       <c r="E829" s="3" t="n">
-        <v>31.45</v>
+        <v>32.27</v>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -25375,11 +25375,11 @@
         </is>
       </c>
       <c r="E831" s="3" t="n">
-        <v>30.89</v>
+        <v>30.9</v>
       </c>
       <c r="F831" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -25391,12 +25391,12 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="D832" s="2" t="inlineStr">
@@ -25405,11 +25405,11 @@
         </is>
       </c>
       <c r="E832" s="3" t="n">
-        <v>29.67</v>
+        <v>30.33</v>
       </c>
       <c r="F832" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -25421,12 +25421,12 @@
       </c>
       <c r="B833" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C833" s="2" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="D833" s="2" t="inlineStr">
@@ -25435,11 +25435,11 @@
         </is>
       </c>
       <c r="E833" s="3" t="n">
-        <v>29.65</v>
+        <v>29.67</v>
       </c>
       <c r="F833" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -25525,11 +25525,11 @@
         </is>
       </c>
       <c r="E836" s="3" t="n">
-        <v>26.29</v>
+        <v>27.21</v>
       </c>
       <c r="F836" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -26275,11 +26275,11 @@
         </is>
       </c>
       <c r="E861" s="3" t="n">
-        <v>8.32</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F861" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2608.53</v>
+        <v>2714.93</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -19795,11 +19795,11 @@
         </is>
       </c>
       <c r="E645" s="3" t="n">
-        <v>2414.8</v>
+        <v>2430.24</v>
       </c>
       <c r="F645" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -19885,11 +19885,11 @@
         </is>
       </c>
       <c r="E648" s="3" t="n">
-        <v>1301.63</v>
+        <v>1337.01</v>
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>1262.1</v>
+        <v>1320.54</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -19945,11 +19945,11 @@
         </is>
       </c>
       <c r="E650" s="3" t="n">
-        <v>1067.18</v>
+        <v>1124.79</v>
       </c>
       <c r="F650" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20005,11 +20005,11 @@
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>866.55</v>
+        <v>887.75</v>
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20065,11 +20065,11 @@
         </is>
       </c>
       <c r="E654" s="3" t="n">
-        <v>743.6900000000001</v>
+        <v>753.77</v>
       </c>
       <c r="F654" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20125,11 +20125,11 @@
         </is>
       </c>
       <c r="E656" s="3" t="n">
-        <v>662.9299999999999</v>
+        <v>678.1</v>
       </c>
       <c r="F656" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20155,11 +20155,11 @@
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>652.3099999999999</v>
+        <v>663.76</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20171,12 +20171,12 @@
       </c>
       <c r="B658" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00072391SZM</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C658" s="2" t="inlineStr">
         <is>
-          <t>814493</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="D658" s="2" t="inlineStr">
@@ -20185,11 +20185,11 @@
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>638.87</v>
+        <v>644.98</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20201,25 +20201,25 @@
       </c>
       <c r="B659" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="C659" s="2" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>814493</t>
         </is>
       </c>
       <c r="D659" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E659" s="3" t="n">
-        <v>606.9400000000001</v>
+        <v>638.87</v>
       </c>
       <c r="F659" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20231,12 +20231,12 @@
       </c>
       <c r="B660" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C660" s="2" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="D660" s="2" t="inlineStr">
@@ -20245,11 +20245,11 @@
         </is>
       </c>
       <c r="E660" s="3" t="n">
-        <v>603.14</v>
+        <v>626.0700000000001</v>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20261,12 +20261,12 @@
       </c>
       <c r="B661" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C661" s="2" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="D661" s="2" t="inlineStr">
@@ -20275,11 +20275,11 @@
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>603.0599999999999</v>
+        <v>622.35</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20305,11 +20305,11 @@
         </is>
       </c>
       <c r="E662" s="3" t="n">
-        <v>590.4</v>
+        <v>608.42</v>
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20321,25 +20321,25 @@
       </c>
       <c r="B663" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C663" s="2" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="D663" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E663" s="3" t="n">
-        <v>574.0599999999999</v>
+        <v>607.89</v>
       </c>
       <c r="F663" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20351,12 +20351,12 @@
       </c>
       <c r="B664" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
@@ -20365,11 +20365,11 @@
         </is>
       </c>
       <c r="E664" s="3" t="n">
-        <v>571.48</v>
+        <v>593.67</v>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20395,11 +20395,11 @@
         </is>
       </c>
       <c r="E665" s="3" t="n">
-        <v>566.73</v>
+        <v>569.52</v>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20425,11 +20425,11 @@
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>556.37</v>
+        <v>568.09</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20455,11 +20455,11 @@
         </is>
       </c>
       <c r="E667" s="3" t="n">
-        <v>540.12</v>
+        <v>541.41</v>
       </c>
       <c r="F667" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20501,12 +20501,12 @@
       </c>
       <c r="B669" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C669" s="2" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="D669" s="2" t="inlineStr">
@@ -20515,11 +20515,11 @@
         </is>
       </c>
       <c r="E669" s="3" t="n">
-        <v>501.38</v>
+        <v>505.05</v>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20531,25 +20531,25 @@
       </c>
       <c r="B670" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066901JZZ</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C670" s="2" t="inlineStr">
         <is>
-          <t>812926</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="D670" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E670" s="3" t="n">
-        <v>500.46</v>
+        <v>501.38</v>
       </c>
       <c r="F670" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -20561,25 +20561,25 @@
       </c>
       <c r="B671" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4P00066901JZZ</t>
         </is>
       </c>
       <c r="C671" s="2" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>812926</t>
         </is>
       </c>
       <c r="D671" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E671" s="3" t="n">
-        <v>492.99</v>
+        <v>500.46</v>
       </c>
       <c r="F671" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -20635,11 +20635,11 @@
         </is>
       </c>
       <c r="E673" s="3" t="n">
-        <v>442.76</v>
+        <v>464.92</v>
       </c>
       <c r="F673" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20651,25 +20651,25 @@
       </c>
       <c r="B674" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065631CPZ</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C674" s="2" t="inlineStr">
         <is>
-          <t>812930</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="D674" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E674" s="3" t="n">
-        <v>415.73</v>
+        <v>416.92</v>
       </c>
       <c r="F674" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20681,25 +20681,25 @@
       </c>
       <c r="B675" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="C675" s="2" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>812930</t>
         </is>
       </c>
       <c r="D675" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>409.4</v>
+        <v>415.73</v>
       </c>
       <c r="F675" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20755,11 +20755,11 @@
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>390.29</v>
+        <v>395.85</v>
       </c>
       <c r="F677" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20771,12 +20771,12 @@
       </c>
       <c r="B678" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C678" s="2" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="D678" s="2" t="inlineStr">
@@ -20785,11 +20785,11 @@
         </is>
       </c>
       <c r="E678" s="3" t="n">
-        <v>344.6</v>
+        <v>345.73</v>
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20801,12 +20801,12 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="D679" s="2" t="inlineStr">
@@ -20815,7 +20815,7 @@
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>344.57</v>
+        <v>344.6</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
@@ -20845,11 +20845,11 @@
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>335.69</v>
+        <v>339.22</v>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20905,11 +20905,11 @@
         </is>
       </c>
       <c r="E682" s="3" t="n">
-        <v>295.99</v>
+        <v>302.54</v>
       </c>
       <c r="F682" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20921,12 +20921,12 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="D683" s="2" t="inlineStr">
@@ -20935,11 +20935,11 @@
         </is>
       </c>
       <c r="E683" s="3" t="n">
-        <v>287.66</v>
+        <v>301.83</v>
       </c>
       <c r="F683" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20951,25 +20951,25 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="D684" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E684" s="3" t="n">
-        <v>285.68</v>
+        <v>290.93</v>
       </c>
       <c r="F684" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -20981,21 +20981,21 @@
       </c>
       <c r="B685" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C685" s="2" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="D685" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E685" s="3" t="n">
-        <v>278.34</v>
+        <v>285.68</v>
       </c>
       <c r="F685" s="2" t="inlineStr">
         <is>
@@ -21011,12 +21011,12 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="D686" s="2" t="inlineStr">
@@ -21025,11 +21025,11 @@
         </is>
       </c>
       <c r="E686" s="3" t="n">
-        <v>276.3</v>
+        <v>281.29</v>
       </c>
       <c r="F686" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21041,12 +21041,12 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563510TWC</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
         <is>
-          <t>814433</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="D687" s="2" t="inlineStr">
@@ -21055,11 +21055,11 @@
         </is>
       </c>
       <c r="E687" s="3" t="n">
-        <v>267.37</v>
+        <v>269.66</v>
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21071,12 +21071,12 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="D688" s="2" t="inlineStr">
@@ -21085,11 +21085,11 @@
         </is>
       </c>
       <c r="E688" s="3" t="n">
-        <v>260.79</v>
+        <v>267.37</v>
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21101,12 +21101,12 @@
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="D689" s="2" t="inlineStr">
@@ -21115,11 +21115,11 @@
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>257.71</v>
+        <v>262.67</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21131,12 +21131,12 @@
       </c>
       <c r="B690" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C690" s="2" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="D690" s="2" t="inlineStr">
@@ -21145,11 +21145,11 @@
         </is>
       </c>
       <c r="E690" s="3" t="n">
-        <v>246.96</v>
+        <v>257.71</v>
       </c>
       <c r="F690" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 16:45</t>
         </is>
       </c>
     </row>
@@ -21161,12 +21161,12 @@
       </c>
       <c r="B691" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C691" s="2" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="D691" s="2" t="inlineStr">
@@ -21175,11 +21175,11 @@
         </is>
       </c>
       <c r="E691" s="3" t="n">
-        <v>242.99</v>
+        <v>246.96</v>
       </c>
       <c r="F691" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21205,11 +21205,11 @@
         </is>
       </c>
       <c r="E692" s="3" t="n">
-        <v>239.6</v>
+        <v>243.69</v>
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="B694" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872531DSZ</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C694" s="2" t="inlineStr">
         <is>
-          <t>816171</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="D694" s="2" t="inlineStr">
@@ -21265,11 +21265,11 @@
         </is>
       </c>
       <c r="E694" s="3" t="n">
-        <v>224.12</v>
+        <v>226.61</v>
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21281,12 +21281,12 @@
       </c>
       <c r="B695" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C695" s="2" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="D695" s="2" t="inlineStr">
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>223.61</v>
+        <v>225.72</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21311,12 +21311,12 @@
       </c>
       <c r="B696" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="C696" s="2" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>816171</t>
         </is>
       </c>
       <c r="D696" s="2" t="inlineStr">
@@ -21325,11 +21325,11 @@
         </is>
       </c>
       <c r="E696" s="3" t="n">
-        <v>219.91</v>
+        <v>224.12</v>
       </c>
       <c r="F696" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21341,12 +21341,12 @@
       </c>
       <c r="B697" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C697" s="2" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="D697" s="2" t="inlineStr">
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>218.19</v>
+        <v>221.13</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21371,12 +21371,12 @@
       </c>
       <c r="B698" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C698" s="2" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="D698" s="2" t="inlineStr">
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="E698" s="3" t="n">
-        <v>216.52</v>
+        <v>220.89</v>
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21401,12 +21401,12 @@
       </c>
       <c r="B699" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C699" s="2" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="D699" s="2" t="inlineStr">
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>215.36</v>
+        <v>220.63</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21445,11 +21445,11 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>199.37</v>
+        <v>204.48</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21461,12 +21461,12 @@
       </c>
       <c r="B701" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C701" s="2" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D701" s="2" t="inlineStr">
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>190.35</v>
+        <v>193.3</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21491,12 +21491,12 @@
       </c>
       <c r="B702" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C702" s="2" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="D702" s="2" t="inlineStr">
@@ -21505,11 +21505,11 @@
         </is>
       </c>
       <c r="E702" s="3" t="n">
-        <v>185.84</v>
+        <v>193</v>
       </c>
       <c r="F702" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21521,12 +21521,12 @@
       </c>
       <c r="B703" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C703" s="2" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="D703" s="2" t="inlineStr">
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>183.76</v>
+        <v>192.5</v>
       </c>
       <c r="F703" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21565,11 +21565,11 @@
         </is>
       </c>
       <c r="E704" s="3" t="n">
-        <v>183.69</v>
+        <v>190.67</v>
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21581,12 +21581,12 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="D705" s="2" t="inlineStr">
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>173.65</v>
+        <v>187.91</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21611,12 +21611,12 @@
       </c>
       <c r="B706" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C706" s="2" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="D706" s="2" t="inlineStr">
@@ -21625,11 +21625,11 @@
         </is>
       </c>
       <c r="E706" s="3" t="n">
-        <v>172.72</v>
+        <v>175.23</v>
       </c>
       <c r="F706" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:10</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21641,12 +21641,12 @@
       </c>
       <c r="B707" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C707" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="D707" s="2" t="inlineStr">
@@ -21655,11 +21655,11 @@
         </is>
       </c>
       <c r="E707" s="3" t="n">
-        <v>171.02</v>
+        <v>173.11</v>
       </c>
       <c r="F707" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21671,12 +21671,12 @@
       </c>
       <c r="B708" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C708" s="2" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="D708" s="2" t="inlineStr">
@@ -21685,11 +21685,11 @@
         </is>
       </c>
       <c r="E708" s="3" t="n">
-        <v>158.82</v>
+        <v>160.18</v>
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21701,12 +21701,12 @@
       </c>
       <c r="B709" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C709" s="2" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="D709" s="2" t="inlineStr">
@@ -21715,11 +21715,11 @@
         </is>
       </c>
       <c r="E709" s="3" t="n">
-        <v>156.6</v>
+        <v>158.82</v>
       </c>
       <c r="F709" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21731,12 +21731,12 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="D710" s="2" t="inlineStr">
@@ -21745,11 +21745,11 @@
         </is>
       </c>
       <c r="E710" s="3" t="n">
-        <v>150.25</v>
+        <v>158.06</v>
       </c>
       <c r="F710" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21761,12 +21761,12 @@
       </c>
       <c r="B711" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C711" s="2" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="D711" s="2" t="inlineStr">
@@ -21775,11 +21775,11 @@
         </is>
       </c>
       <c r="E711" s="3" t="n">
-        <v>148.38</v>
+        <v>150.25</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21805,11 +21805,11 @@
         </is>
       </c>
       <c r="E712" s="3" t="n">
-        <v>145.68</v>
+        <v>148.69</v>
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21835,11 +21835,11 @@
         </is>
       </c>
       <c r="E713" s="3" t="n">
-        <v>143.67</v>
+        <v>148.3</v>
       </c>
       <c r="F713" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21865,11 +21865,11 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>142.81</v>
+        <v>145.69</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21895,11 +21895,11 @@
         </is>
       </c>
       <c r="E715" s="3" t="n">
-        <v>142.8</v>
+        <v>143.46</v>
       </c>
       <c r="F715" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>139.64</v>
+        <v>140.95</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>136.12</v>
+        <v>140.28</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22015,11 +22015,11 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>135.77</v>
+        <v>138.54</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22045,11 +22045,11 @@
         </is>
       </c>
       <c r="E720" s="3" t="n">
-        <v>135.55</v>
+        <v>136.86</v>
       </c>
       <c r="F720" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22075,11 +22075,11 @@
         </is>
       </c>
       <c r="E721" s="3" t="n">
-        <v>133.02</v>
+        <v>134.96</v>
       </c>
       <c r="F721" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22121,12 +22121,12 @@
       </c>
       <c r="B723" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C723" s="2" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="D723" s="2" t="inlineStr">
@@ -22135,11 +22135,11 @@
         </is>
       </c>
       <c r="E723" s="3" t="n">
-        <v>131.31</v>
+        <v>131.74</v>
       </c>
       <c r="F723" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22151,12 +22151,12 @@
       </c>
       <c r="B724" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C724" s="2" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="D724" s="2" t="inlineStr">
@@ -22165,11 +22165,11 @@
         </is>
       </c>
       <c r="E724" s="3" t="n">
-        <v>131.16</v>
+        <v>131.31</v>
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22345,11 +22345,11 @@
         </is>
       </c>
       <c r="E730" s="3" t="n">
-        <v>122.06</v>
+        <v>122.37</v>
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22405,11 +22405,11 @@
         </is>
       </c>
       <c r="E732" s="3" t="n">
-        <v>117.34</v>
+        <v>118.31</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22421,12 +22421,12 @@
       </c>
       <c r="B733" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="D733" s="2" t="inlineStr">
@@ -22435,11 +22435,11 @@
         </is>
       </c>
       <c r="E733" s="3" t="n">
-        <v>115.83</v>
+        <v>118.01</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22451,12 +22451,12 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
@@ -22465,11 +22465,11 @@
         </is>
       </c>
       <c r="E734" s="3" t="n">
-        <v>114.07</v>
+        <v>117.64</v>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22481,12 +22481,12 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
@@ -22495,11 +22495,11 @@
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>113.28</v>
+        <v>117.18</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22511,12 +22511,12 @@
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
@@ -22525,11 +22525,11 @@
         </is>
       </c>
       <c r="E736" s="3" t="n">
-        <v>113.25</v>
+        <v>115.64</v>
       </c>
       <c r="F736" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22541,12 +22541,12 @@
       </c>
       <c r="B737" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="D737" s="2" t="inlineStr">
@@ -22555,11 +22555,11 @@
         </is>
       </c>
       <c r="E737" s="3" t="n">
-        <v>112.74</v>
+        <v>114.7</v>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22571,12 +22571,12 @@
       </c>
       <c r="B738" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="D738" s="2" t="inlineStr">
@@ -22585,11 +22585,11 @@
         </is>
       </c>
       <c r="E738" s="3" t="n">
-        <v>112.53</v>
+        <v>114.07</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22601,12 +22601,12 @@
       </c>
       <c r="B739" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C739" s="2" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="D739" s="2" t="inlineStr">
@@ -22615,11 +22615,11 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>112.27</v>
+        <v>113.77</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22631,12 +22631,12 @@
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
@@ -22645,11 +22645,11 @@
         </is>
       </c>
       <c r="E740" s="3" t="n">
-        <v>109.36</v>
+        <v>113.25</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22661,12 +22661,12 @@
       </c>
       <c r="B741" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="D741" s="2" t="inlineStr">
@@ -22675,11 +22675,11 @@
         </is>
       </c>
       <c r="E741" s="3" t="n">
-        <v>109.33</v>
+        <v>112.82</v>
       </c>
       <c r="F741" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22691,12 +22691,12 @@
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>108.12</v>
+        <v>111.24</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22721,12 +22721,12 @@
       </c>
       <c r="B743" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C743" s="2" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="D743" s="2" t="inlineStr">
@@ -22735,11 +22735,11 @@
         </is>
       </c>
       <c r="E743" s="3" t="n">
-        <v>106.63</v>
+        <v>109.33</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>103.89</v>
+        <v>106.32</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22781,12 +22781,12 @@
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr">
@@ -22795,11 +22795,11 @@
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>101.94</v>
+        <v>104.07</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22811,12 +22811,12 @@
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
@@ -22825,11 +22825,11 @@
         </is>
       </c>
       <c r="E746" s="3" t="n">
-        <v>100.93</v>
+        <v>103.2</v>
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22841,12 +22841,12 @@
       </c>
       <c r="B747" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C747" s="2" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="D747" s="2" t="inlineStr">
@@ -22855,7 +22855,7 @@
         </is>
       </c>
       <c r="E747" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>100.93</v>
       </c>
       <c r="F747" s="2" t="inlineStr">
         <is>
@@ -22871,12 +22871,12 @@
       </c>
       <c r="B748" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C748" s="2" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="D748" s="2" t="inlineStr">
@@ -22885,11 +22885,11 @@
         </is>
       </c>
       <c r="E748" s="3" t="n">
-        <v>99.77</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22915,11 +22915,11 @@
         </is>
       </c>
       <c r="E749" s="3" t="n">
-        <v>98.78</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="F749" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -22991,12 +22991,12 @@
       </c>
       <c r="B752" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C752" s="2" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="D752" s="2" t="inlineStr">
@@ -23005,11 +23005,11 @@
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>95.48999999999999</v>
+        <v>96.69</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23021,12 +23021,12 @@
       </c>
       <c r="B753" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C753" s="2" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="D753" s="2" t="inlineStr">
@@ -23035,11 +23035,11 @@
         </is>
       </c>
       <c r="E753" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>96.22</v>
       </c>
       <c r="F753" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23081,12 +23081,12 @@
       </c>
       <c r="B755" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C755" s="2" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="D755" s="2" t="inlineStr">
@@ -23095,11 +23095,11 @@
         </is>
       </c>
       <c r="E755" s="3" t="n">
-        <v>90.45999999999999</v>
+        <v>92.44</v>
       </c>
       <c r="F755" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23111,12 +23111,12 @@
       </c>
       <c r="B756" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C756" s="2" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="D756" s="2" t="inlineStr">
@@ -23125,11 +23125,11 @@
         </is>
       </c>
       <c r="E756" s="3" t="n">
-        <v>89.79000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23141,25 +23141,25 @@
       </c>
       <c r="B757" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C757" s="2" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D757" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E757" s="3" t="n">
-        <v>89.48999999999999</v>
+        <v>91</v>
       </c>
       <c r="F757" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>89.18000000000001</v>
+        <v>90.37</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23201,12 +23201,12 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="D759" s="2" t="inlineStr">
@@ -23215,7 +23215,7 @@
         </is>
       </c>
       <c r="E759" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
@@ -23231,25 +23231,25 @@
       </c>
       <c r="B760" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C760" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="D760" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>86.38</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23261,12 +23261,12 @@
       </c>
       <c r="B761" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C761" s="2" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="D761" s="2" t="inlineStr">
@@ -23275,11 +23275,11 @@
         </is>
       </c>
       <c r="E761" s="3" t="n">
-        <v>85.54000000000001</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="F761" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23305,11 +23305,11 @@
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>84.73</v>
+        <v>87.75</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23321,12 +23321,12 @@
       </c>
       <c r="B763" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C763" s="2" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="D763" s="2" t="inlineStr">
@@ -23335,11 +23335,11 @@
         </is>
       </c>
       <c r="E763" s="3" t="n">
-        <v>82.7</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F763" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>82.19</v>
+        <v>86.19</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23381,12 +23381,12 @@
       </c>
       <c r="B765" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C765" s="2" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="D765" s="2" t="inlineStr">
@@ -23395,11 +23395,11 @@
         </is>
       </c>
       <c r="E765" s="3" t="n">
-        <v>82.18000000000001</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="F765" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23411,12 +23411,12 @@
       </c>
       <c r="B766" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C766" s="2" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="D766" s="2" t="inlineStr">
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>81.73</v>
+        <v>85.13</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23441,12 +23441,12 @@
       </c>
       <c r="B767" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C767" s="2" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="D767" s="2" t="inlineStr">
@@ -23455,11 +23455,11 @@
         </is>
       </c>
       <c r="E767" s="3" t="n">
-        <v>80.98</v>
+        <v>83.86</v>
       </c>
       <c r="F767" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23485,11 +23485,11 @@
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>80.22</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23501,12 @@
       </c>
       <c r="B769" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C769" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D769" s="2" t="inlineStr">
@@ -23515,11 +23515,11 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>80.17</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23531,12 +23531,12 @@
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
@@ -23545,11 +23545,11 @@
         </is>
       </c>
       <c r="E770" s="3" t="n">
-        <v>79.86</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23561,12 +23561,12 @@
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
@@ -23575,11 +23575,11 @@
         </is>
       </c>
       <c r="E771" s="3" t="n">
-        <v>79.47</v>
+        <v>81.73</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23591,12 +23591,12 @@
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="D772" s="2" t="inlineStr">
@@ -23605,11 +23605,11 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>79.12</v>
+        <v>81.59</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23635,11 +23635,11 @@
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>77.7</v>
+        <v>80.28</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23651,12 +23651,12 @@
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr">
@@ -23665,11 +23665,11 @@
         </is>
       </c>
       <c r="E774" s="3" t="n">
-        <v>77.39</v>
+        <v>80.17</v>
       </c>
       <c r="F774" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23681,12 +23681,12 @@
       </c>
       <c r="B775" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C775" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="D775" s="2" t="inlineStr">
@@ -23695,11 +23695,11 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23711,12 +23711,12 @@
       </c>
       <c r="B776" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C776" s="2" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="D776" s="2" t="inlineStr">
@@ -23725,11 +23725,11 @@
         </is>
       </c>
       <c r="E776" s="3" t="n">
-        <v>74.76000000000001</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="F776" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23741,25 +23741,25 @@
       </c>
       <c r="B777" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C777" s="2" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="D777" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E777" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F777" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23771,12 +23771,12 @@
       </c>
       <c r="B778" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C778" s="2" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="D778" s="2" t="inlineStr">
@@ -23785,11 +23785,11 @@
         </is>
       </c>
       <c r="E778" s="3" t="n">
-        <v>73.55</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="F778" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23801,25 +23801,25 @@
       </c>
       <c r="B779" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C779" s="2" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="D779" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E779" s="3" t="n">
-        <v>73.39</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F779" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23831,12 +23831,12 @@
       </c>
       <c r="B780" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C780" s="2" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="D780" s="2" t="inlineStr">
@@ -23845,11 +23845,11 @@
         </is>
       </c>
       <c r="E780" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23861,12 +23861,12 @@
       </c>
       <c r="B781" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C781" s="2" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="D781" s="2" t="inlineStr">
@@ -23875,11 +23875,11 @@
         </is>
       </c>
       <c r="E781" s="3" t="n">
-        <v>71.38</v>
+        <v>73.55</v>
       </c>
       <c r="F781" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23905,11 +23905,11 @@
         </is>
       </c>
       <c r="E782" s="3" t="n">
-        <v>70.98999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="F782" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23921,12 +23921,12 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D783" s="2" t="inlineStr">
@@ -23935,11 +23935,11 @@
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>70.95999999999999</v>
+        <v>71.53</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -23951,12 +23951,12 @@
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
@@ -23965,11 +23965,11 @@
         </is>
       </c>
       <c r="E784" s="3" t="n">
-        <v>70.48</v>
+        <v>71.38</v>
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23981,12 +23981,12 @@
       </c>
       <c r="B785" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C785" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="D785" s="2" t="inlineStr">
@@ -23995,11 +23995,11 @@
         </is>
       </c>
       <c r="E785" s="3" t="n">
-        <v>69.56</v>
+        <v>70.48</v>
       </c>
       <c r="F785" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24011,12 +24011,12 @@
       </c>
       <c r="B786" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C786" s="2" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="D786" s="2" t="inlineStr">
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>68.68000000000001</v>
+        <v>69.42</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -24041,12 +24041,12 @@
       </c>
       <c r="B787" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C787" s="2" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="D787" s="2" t="inlineStr">
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>68.5</v>
+        <v>69.17</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:36</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -24071,12 +24071,12 @@
       </c>
       <c r="B788" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C788" s="2" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="D788" s="2" t="inlineStr">
@@ -24085,11 +24085,11 @@
         </is>
       </c>
       <c r="E788" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="F788" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-24 07:36</t>
         </is>
       </c>
     </row>
@@ -24101,12 +24101,12 @@
       </c>
       <c r="B789" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C789" s="2" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="D789" s="2" t="inlineStr">
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>65.95999999999999</v>
+        <v>67.98</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -24131,12 +24131,12 @@
       </c>
       <c r="B790" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C790" s="2" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="D790" s="2" t="inlineStr">
@@ -24145,11 +24145,11 @@
         </is>
       </c>
       <c r="E790" s="3" t="n">
-        <v>64.28</v>
+        <v>67.67</v>
       </c>
       <c r="F790" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -24161,12 +24161,12 @@
       </c>
       <c r="B791" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C791" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="D791" s="2" t="inlineStr">
@@ -24175,11 +24175,11 @@
         </is>
       </c>
       <c r="E791" s="3" t="n">
-        <v>63.6</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="F791" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -24191,12 +24191,12 @@
       </c>
       <c r="B792" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C792" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="D792" s="2" t="inlineStr">
@@ -24205,11 +24205,11 @@
         </is>
       </c>
       <c r="E792" s="3" t="n">
-        <v>61.96</v>
+        <v>63.6</v>
       </c>
       <c r="F792" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24221,12 +24221,12 @@
       </c>
       <c r="B793" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C793" s="2" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D793" s="2" t="inlineStr">
@@ -24235,11 +24235,11 @@
         </is>
       </c>
       <c r="E793" s="3" t="n">
-        <v>61.08</v>
+        <v>62.34</v>
       </c>
       <c r="F793" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -24265,11 +24265,11 @@
         </is>
       </c>
       <c r="E794" s="3" t="n">
-        <v>60.68</v>
+        <v>61.42</v>
       </c>
       <c r="F794" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -24281,25 +24281,25 @@
       </c>
       <c r="B795" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C795" s="2" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="D795" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E795" s="3" t="n">
-        <v>57.22</v>
+        <v>59.77</v>
       </c>
       <c r="F795" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -24311,25 +24311,25 @@
       </c>
       <c r="B796" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C796" s="2" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="D796" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E796" s="3" t="n">
-        <v>56.26</v>
+        <v>57.22</v>
       </c>
       <c r="F796" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24341,12 +24341,12 @@
       </c>
       <c r="B797" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C797" s="2" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="D797" s="2" t="inlineStr">
@@ -24355,11 +24355,11 @@
         </is>
       </c>
       <c r="E797" s="3" t="n">
-        <v>55.14</v>
+        <v>55.31</v>
       </c>
       <c r="F797" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -24371,12 +24371,12 @@
       </c>
       <c r="B798" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C798" s="2" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="D798" s="2" t="inlineStr">
@@ -24385,11 +24385,11 @@
         </is>
       </c>
       <c r="E798" s="3" t="n">
-        <v>55.07</v>
+        <v>55.14</v>
       </c>
       <c r="F798" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24461,12 +24461,12 @@
       </c>
       <c r="B801" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C801" s="2" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="D801" s="2" t="inlineStr">
@@ -24475,11 +24475,11 @@
         </is>
       </c>
       <c r="E801" s="3" t="n">
-        <v>52.57</v>
+        <v>52.9</v>
       </c>
       <c r="F801" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -24491,12 +24491,12 @@
       </c>
       <c r="B802" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C802" s="2" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="D802" s="2" t="inlineStr">
@@ -24505,11 +24505,11 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>52.53</v>
+        <v>52.57</v>
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24551,12 +24551,12 @@
       </c>
       <c r="B804" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C804" s="2" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="D804" s="2" t="inlineStr">
@@ -24565,11 +24565,11 @@
         </is>
       </c>
       <c r="E804" s="3" t="n">
-        <v>50.23</v>
+        <v>50.99</v>
       </c>
       <c r="F804" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -24595,11 +24595,11 @@
         </is>
       </c>
       <c r="E805" s="3" t="n">
-        <v>50.13</v>
+        <v>50.79</v>
       </c>
       <c r="F805" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -24611,12 +24611,12 @@
       </c>
       <c r="B806" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="C806" s="2" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="D806" s="2" t="inlineStr">
@@ -24625,11 +24625,11 @@
         </is>
       </c>
       <c r="E806" s="3" t="n">
-        <v>48.04</v>
+        <v>50.23</v>
       </c>
       <c r="F806" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -24641,12 +24641,12 @@
       </c>
       <c r="B807" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C807" s="2" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="D807" s="2" t="inlineStr">
@@ -24655,11 +24655,11 @@
         </is>
       </c>
       <c r="E807" s="3" t="n">
-        <v>47.99</v>
+        <v>48.04</v>
       </c>
       <c r="F807" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24671,12 +24671,12 @@
       </c>
       <c r="B808" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C808" s="2" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="D808" s="2" t="inlineStr">
@@ -24685,11 +24685,11 @@
         </is>
       </c>
       <c r="E808" s="3" t="n">
-        <v>47.83</v>
+        <v>47.99</v>
       </c>
       <c r="F808" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -24715,11 +24715,11 @@
         </is>
       </c>
       <c r="E809" s="3" t="n">
-        <v>47.33</v>
+        <v>47.7</v>
       </c>
       <c r="F809" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -24761,12 +24761,12 @@
       </c>
       <c r="B811" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C811" s="2" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="D811" s="2" t="inlineStr">
@@ -24775,11 +24775,11 @@
         </is>
       </c>
       <c r="E811" s="3" t="n">
-        <v>46.4</v>
+        <v>46.77</v>
       </c>
       <c r="F811" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -24791,12 +24791,12 @@
       </c>
       <c r="B812" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C812" s="2" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="D812" s="2" t="inlineStr">
@@ -24805,11 +24805,11 @@
         </is>
       </c>
       <c r="E812" s="3" t="n">
-        <v>44.95</v>
+        <v>46.4</v>
       </c>
       <c r="F812" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24821,12 +24821,12 @@
       </c>
       <c r="B813" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C813" s="2" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="D813" s="2" t="inlineStr">
@@ -24835,11 +24835,11 @@
         </is>
       </c>
       <c r="E813" s="3" t="n">
-        <v>44.8</v>
+        <v>45.69</v>
       </c>
       <c r="F813" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -24851,12 +24851,12 @@
       </c>
       <c r="B814" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C814" s="2" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="D814" s="2" t="inlineStr">
@@ -24865,11 +24865,11 @@
         </is>
       </c>
       <c r="E814" s="3" t="n">
-        <v>44.45</v>
+        <v>44.8</v>
       </c>
       <c r="F814" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-24 16:21</t>
         </is>
       </c>
     </row>
@@ -24925,11 +24925,11 @@
         </is>
       </c>
       <c r="E816" s="3" t="n">
-        <v>41.14</v>
+        <v>44.06</v>
       </c>
       <c r="F816" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -25001,12 +25001,12 @@
       </c>
       <c r="B819" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C819" s="2" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="D819" s="2" t="inlineStr">
@@ -25015,11 +25015,11 @@
         </is>
       </c>
       <c r="E819" s="3" t="n">
-        <v>37.65</v>
+        <v>38.92</v>
       </c>
       <c r="F819" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -25031,12 +25031,12 @@
       </c>
       <c r="B820" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C820" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="D820" s="2" t="inlineStr">
@@ -25045,11 +25045,11 @@
         </is>
       </c>
       <c r="E820" s="3" t="n">
-        <v>37.42</v>
+        <v>38.61</v>
       </c>
       <c r="F820" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -25061,12 +25061,12 @@
       </c>
       <c r="B821" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C821" s="2" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="D821" s="2" t="inlineStr">
@@ -25075,11 +25075,11 @@
         </is>
       </c>
       <c r="E821" s="3" t="n">
-        <v>36.93</v>
+        <v>37.96</v>
       </c>
       <c r="F821" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -25091,12 +25091,12 @@
       </c>
       <c r="B822" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C822" s="2" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D822" s="2" t="inlineStr">
@@ -25105,11 +25105,11 @@
         </is>
       </c>
       <c r="E822" s="3" t="n">
-        <v>36.75</v>
+        <v>37.42</v>
       </c>
       <c r="F822" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -25121,12 +25121,12 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="D823" s="2" t="inlineStr">
@@ -25135,11 +25135,11 @@
         </is>
       </c>
       <c r="E823" s="3" t="n">
-        <v>36.59</v>
+        <v>37</v>
       </c>
       <c r="F823" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:39</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -25151,12 +25151,12 @@
       </c>
       <c r="B824" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C824" s="2" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="D824" s="2" t="inlineStr">
@@ -25165,11 +25165,11 @@
         </is>
       </c>
       <c r="E824" s="3" t="n">
-        <v>36.31</v>
+        <v>36.75</v>
       </c>
       <c r="F824" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-23 22:37</t>
         </is>
       </c>
     </row>
@@ -25181,12 +25181,12 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="D825" s="2" t="inlineStr">
@@ -25195,11 +25195,11 @@
         </is>
       </c>
       <c r="E825" s="3" t="n">
-        <v>36.06</v>
+        <v>36.59</v>
       </c>
       <c r="F825" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-21 21:39</t>
         </is>
       </c>
     </row>
@@ -25211,12 +25211,12 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="D826" s="2" t="inlineStr">
@@ -25225,11 +25225,11 @@
         </is>
       </c>
       <c r="E826" s="3" t="n">
-        <v>34.64</v>
+        <v>36.31</v>
       </c>
       <c r="F826" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25241,12 +25241,12 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="D827" s="2" t="inlineStr">
@@ -25255,11 +25255,11 @@
         </is>
       </c>
       <c r="E827" s="3" t="n">
-        <v>34.05</v>
+        <v>34.64</v>
       </c>
       <c r="F827" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25271,12 +25271,12 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="D828" s="2" t="inlineStr">
@@ -25285,11 +25285,11 @@
         </is>
       </c>
       <c r="E828" s="3" t="n">
-        <v>32.76</v>
+        <v>34.05</v>
       </c>
       <c r="F828" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25315,11 +25315,11 @@
         </is>
       </c>
       <c r="E829" s="3" t="n">
-        <v>32.27</v>
+        <v>33.61</v>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -25331,12 +25331,12 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="D830" s="2" t="inlineStr">
@@ -25345,11 +25345,11 @@
         </is>
       </c>
       <c r="E830" s="3" t="n">
-        <v>31.24</v>
+        <v>33.55</v>
       </c>
       <c r="F830" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -25375,11 +25375,11 @@
         </is>
       </c>
       <c r="E831" s="3" t="n">
-        <v>30.9</v>
+        <v>32.6</v>
       </c>
       <c r="F831" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -25391,12 +25391,12 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="D832" s="2" t="inlineStr">
@@ -25405,11 +25405,11 @@
         </is>
       </c>
       <c r="E832" s="3" t="n">
-        <v>30.33</v>
+        <v>31.24</v>
       </c>
       <c r="F832" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25435,11 +25435,11 @@
         </is>
       </c>
       <c r="E833" s="3" t="n">
-        <v>29.67</v>
+        <v>29.69</v>
       </c>
       <c r="F833" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:21</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -25525,11 +25525,11 @@
         </is>
       </c>
       <c r="E836" s="3" t="n">
-        <v>27.21</v>
+        <v>28.09</v>
       </c>
       <c r="F836" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -26201,12 +26201,12 @@
       </c>
       <c r="B859" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C859" s="2" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="D859" s="2" t="inlineStr">
@@ -26215,11 +26215,11 @@
         </is>
       </c>
       <c r="E859" s="3" t="n">
-        <v>9.27</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="F859" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 07:40</t>
         </is>
       </c>
     </row>
@@ -26231,12 +26231,12 @@
       </c>
       <c r="B860" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C860" s="2" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="D860" s="2" t="inlineStr">
@@ -26245,7 +26245,7 @@
         </is>
       </c>
       <c r="E860" s="3" t="n">
-        <v>8.529999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="F860" s="2" t="inlineStr">
         <is>
@@ -26261,12 +26261,12 @@
       </c>
       <c r="B861" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C861" s="2" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="D861" s="2" t="inlineStr">
@@ -26275,11 +26275,11 @@
         </is>
       </c>
       <c r="E861" s="3" t="n">
-        <v>8.380000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="F861" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2714.93</v>
+        <v>2715.75</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -19795,11 +19795,11 @@
         </is>
       </c>
       <c r="E645" s="3" t="n">
-        <v>2430.24</v>
+        <v>2430.31</v>
       </c>
       <c r="F645" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -19885,11 +19885,11 @@
         </is>
       </c>
       <c r="E648" s="3" t="n">
-        <v>1337.01</v>
+        <v>1337.14</v>
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>1320.54</v>
+        <v>1320.86</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -19945,11 +19945,11 @@
         </is>
       </c>
       <c r="E650" s="3" t="n">
-        <v>1124.79</v>
+        <v>1125.61</v>
       </c>
       <c r="F650" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -20005,11 +20005,11 @@
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>887.75</v>
+        <v>888.5599999999999</v>
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -20065,11 +20065,11 @@
         </is>
       </c>
       <c r="E654" s="3" t="n">
-        <v>753.77</v>
+        <v>754</v>
       </c>
       <c r="F654" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -20155,11 +20155,11 @@
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>663.76</v>
+        <v>663.85</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -20185,11 +20185,11 @@
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>644.98</v>
+        <v>645.39</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -20245,11 +20245,11 @@
         </is>
       </c>
       <c r="E660" s="3" t="n">
-        <v>626.0700000000001</v>
+        <v>627.04</v>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -20275,11 +20275,11 @@
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>622.35</v>
+        <v>622.5700000000001</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -20305,11 +20305,11 @@
         </is>
       </c>
       <c r="E662" s="3" t="n">
-        <v>608.42</v>
+        <v>608.46</v>
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -20365,11 +20365,11 @@
         </is>
       </c>
       <c r="E664" s="3" t="n">
-        <v>593.67</v>
+        <v>593.77</v>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -20425,11 +20425,11 @@
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>568.09</v>
+        <v>568.66</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -20515,11 +20515,11 @@
         </is>
       </c>
       <c r="E669" s="3" t="n">
-        <v>505.05</v>
+        <v>508.22</v>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -20635,11 +20635,11 @@
         </is>
       </c>
       <c r="E673" s="3" t="n">
-        <v>464.92</v>
+        <v>465</v>
       </c>
       <c r="F673" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -20785,11 +20785,11 @@
         </is>
       </c>
       <c r="E678" s="3" t="n">
-        <v>345.73</v>
+        <v>347.33</v>
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>225.72</v>
+        <v>225.99</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -21461,12 +21461,12 @@
       </c>
       <c r="B701" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C701" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="D701" s="2" t="inlineStr">
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>193.3</v>
+        <v>196.05</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -21491,12 +21491,12 @@
       </c>
       <c r="B702" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C702" s="2" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D702" s="2" t="inlineStr">
@@ -21505,7 +21505,7 @@
         </is>
       </c>
       <c r="E702" s="3" t="n">
-        <v>193</v>
+        <v>193.3</v>
       </c>
       <c r="F702" s="2" t="inlineStr">
         <is>
@@ -21791,12 +21791,12 @@
       </c>
       <c r="B712" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C712" s="2" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D712" s="2" t="inlineStr">
@@ -21805,11 +21805,11 @@
         </is>
       </c>
       <c r="E712" s="3" t="n">
-        <v>148.69</v>
+        <v>148.96</v>
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -21821,12 +21821,12 @@
       </c>
       <c r="B713" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C713" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="D713" s="2" t="inlineStr">
@@ -21835,7 +21835,7 @@
         </is>
       </c>
       <c r="E713" s="3" t="n">
-        <v>148.3</v>
+        <v>148.69</v>
       </c>
       <c r="F713" s="2" t="inlineStr">
         <is>
@@ -21865,11 +21865,11 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>145.69</v>
+        <v>145.71</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>140.28</v>
+        <v>140.57</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -22421,12 +22421,12 @@
       </c>
       <c r="B733" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D733" s="2" t="inlineStr">
@@ -22435,11 +22435,11 @@
         </is>
       </c>
       <c r="E733" s="3" t="n">
-        <v>118.01</v>
+        <v>118.08</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -22451,12 +22451,12 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
@@ -22465,7 +22465,7 @@
         </is>
       </c>
       <c r="E734" s="3" t="n">
-        <v>117.64</v>
+        <v>118.01</v>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
@@ -23005,11 +23005,11 @@
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>96.69</v>
+        <v>96.7</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>90.37</v>
+        <v>90.75</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -23305,11 +23305,11 @@
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>87.75</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>86.19</v>
+        <v>86.44</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -23695,11 +23695,11 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>67.98</v>
+        <v>68</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -25015,11 +25015,11 @@
         </is>
       </c>
       <c r="E819" s="3" t="n">
-        <v>38.92</v>
+        <v>38.93</v>
       </c>
       <c r="F819" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -25135,11 +25135,11 @@
         </is>
       </c>
       <c r="E823" s="3" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="F823" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>
@@ -25315,11 +25315,11 @@
         </is>
       </c>
       <c r="E829" s="3" t="n">
-        <v>33.61</v>
+        <v>33.62</v>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -19765,11 +19765,11 @@
         </is>
       </c>
       <c r="E644" s="3" t="n">
-        <v>2715.75</v>
+        <v>2788.71</v>
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -19795,11 +19795,11 @@
         </is>
       </c>
       <c r="E645" s="3" t="n">
-        <v>2430.31</v>
+        <v>2433.92</v>
       </c>
       <c r="F645" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -19885,11 +19885,11 @@
         </is>
       </c>
       <c r="E648" s="3" t="n">
-        <v>1337.14</v>
+        <v>1357.49</v>
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19915,11 @@
         </is>
       </c>
       <c r="E649" s="3" t="n">
-        <v>1320.86</v>
+        <v>1337.8</v>
       </c>
       <c r="F649" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -19945,11 +19945,11 @@
         </is>
       </c>
       <c r="E650" s="3" t="n">
-        <v>1125.61</v>
+        <v>1148.83</v>
       </c>
       <c r="F650" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20005,11 +20005,11 @@
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>888.5599999999999</v>
+        <v>897.8</v>
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20065,11 +20065,11 @@
         </is>
       </c>
       <c r="E654" s="3" t="n">
-        <v>754</v>
+        <v>757.9299999999999</v>
       </c>
       <c r="F654" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20125,11 +20125,11 @@
         </is>
       </c>
       <c r="E656" s="3" t="n">
-        <v>678.1</v>
+        <v>680.29</v>
       </c>
       <c r="F656" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20155,11 +20155,11 @@
         </is>
       </c>
       <c r="E657" s="3" t="n">
-        <v>663.85</v>
+        <v>666.64</v>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20185,11 +20185,11 @@
         </is>
       </c>
       <c r="E658" s="3" t="n">
-        <v>645.39</v>
+        <v>660.0700000000001</v>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20201,12 +20201,12 @@
       </c>
       <c r="B659" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00072391SZM</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C659" s="2" t="inlineStr">
         <is>
-          <t>814493</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="D659" s="2" t="inlineStr">
@@ -20215,11 +20215,11 @@
         </is>
       </c>
       <c r="E659" s="3" t="n">
-        <v>638.87</v>
+        <v>649.02</v>
       </c>
       <c r="F659" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20231,12 +20231,12 @@
       </c>
       <c r="B660" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4P00072391SZM</t>
         </is>
       </c>
       <c r="C660" s="2" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>814493</t>
         </is>
       </c>
       <c r="D660" s="2" t="inlineStr">
@@ -20245,11 +20245,11 @@
         </is>
       </c>
       <c r="E660" s="3" t="n">
-        <v>627.04</v>
+        <v>638.87</v>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20261,12 +20261,12 @@
       </c>
       <c r="B661" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C661" s="2" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="D661" s="2" t="inlineStr">
@@ -20275,11 +20275,11 @@
         </is>
       </c>
       <c r="E661" s="3" t="n">
-        <v>622.5700000000001</v>
+        <v>631.41</v>
       </c>
       <c r="F661" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20305,11 +20305,11 @@
         </is>
       </c>
       <c r="E662" s="3" t="n">
-        <v>608.46</v>
+        <v>609.64</v>
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20335,11 +20335,11 @@
         </is>
       </c>
       <c r="E663" s="3" t="n">
-        <v>607.89</v>
+        <v>608.24</v>
       </c>
       <c r="F663" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20365,11 +20365,11 @@
         </is>
       </c>
       <c r="E664" s="3" t="n">
-        <v>593.77</v>
+        <v>599.99</v>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20381,25 +20381,25 @@
       </c>
       <c r="B665" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E665" s="3" t="n">
-        <v>569.52</v>
+        <v>577.53</v>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20411,25 +20411,25 @@
       </c>
       <c r="B666" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E666" s="3" t="n">
-        <v>568.66</v>
+        <v>569.6799999999999</v>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20455,11 +20455,11 @@
         </is>
       </c>
       <c r="E667" s="3" t="n">
-        <v>541.41</v>
+        <v>541.51</v>
       </c>
       <c r="F667" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20515,11 +20515,11 @@
         </is>
       </c>
       <c r="E669" s="3" t="n">
-        <v>508.22</v>
+        <v>510.51</v>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20635,11 +20635,11 @@
         </is>
       </c>
       <c r="E673" s="3" t="n">
-        <v>465</v>
+        <v>476.68</v>
       </c>
       <c r="F673" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20711,12 +20711,12 @@
       </c>
       <c r="B676" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084601T5F</t>
+          <t>KIT4P000668852J9</t>
         </is>
       </c>
       <c r="C676" s="2" t="inlineStr">
         <is>
-          <t>816335</t>
+          <t>812925</t>
         </is>
       </c>
       <c r="D676" s="2" t="inlineStr">
@@ -20725,11 +20725,11 @@
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>401.51</v>
+        <v>403.71</v>
       </c>
       <c r="F676" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20741,12 +20741,12 @@
       </c>
       <c r="B677" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000668852J9</t>
+          <t>KIT4P00084601T5F</t>
         </is>
       </c>
       <c r="C677" s="2" t="inlineStr">
         <is>
-          <t>812925</t>
+          <t>816335</t>
         </is>
       </c>
       <c r="D677" s="2" t="inlineStr">
@@ -20755,11 +20755,11 @@
         </is>
       </c>
       <c r="E677" s="3" t="n">
-        <v>395.85</v>
+        <v>401.51</v>
       </c>
       <c r="F677" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -20785,11 +20785,11 @@
         </is>
       </c>
       <c r="E678" s="3" t="n">
-        <v>347.33</v>
+        <v>348.8</v>
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20815,11 +20815,11 @@
         </is>
       </c>
       <c r="E679" s="3" t="n">
-        <v>344.6</v>
+        <v>348.75</v>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20845,11 +20845,11 @@
         </is>
       </c>
       <c r="E680" s="3" t="n">
-        <v>339.22</v>
+        <v>341.19</v>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20875,11 +20875,11 @@
         </is>
       </c>
       <c r="E681" s="3" t="n">
-        <v>318.87</v>
+        <v>329.3</v>
       </c>
       <c r="F681" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:37</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20905,11 +20905,11 @@
         </is>
       </c>
       <c r="E682" s="3" t="n">
-        <v>302.54</v>
+        <v>307.05</v>
       </c>
       <c r="F682" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20935,11 +20935,11 @@
         </is>
       </c>
       <c r="E683" s="3" t="n">
-        <v>301.83</v>
+        <v>302.69</v>
       </c>
       <c r="F683" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -20965,11 +20965,11 @@
         </is>
       </c>
       <c r="E684" s="3" t="n">
-        <v>290.93</v>
+        <v>292.16</v>
       </c>
       <c r="F684" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21055,11 +21055,11 @@
         </is>
       </c>
       <c r="E687" s="3" t="n">
-        <v>269.66</v>
+        <v>275.18</v>
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21115,11 +21115,11 @@
         </is>
       </c>
       <c r="E689" s="3" t="n">
-        <v>262.67</v>
+        <v>264.65</v>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21205,11 +21205,11 @@
         </is>
       </c>
       <c r="E692" s="3" t="n">
-        <v>243.69</v>
+        <v>244.64</v>
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="B694" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C694" s="2" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="D694" s="2" t="inlineStr">
@@ -21265,11 +21265,11 @@
         </is>
       </c>
       <c r="E694" s="3" t="n">
-        <v>226.61</v>
+        <v>227.66</v>
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21281,12 +21281,12 @@
       </c>
       <c r="B695" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C695" s="2" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="D695" s="2" t="inlineStr">
@@ -21295,11 +21295,11 @@
         </is>
       </c>
       <c r="E695" s="3" t="n">
-        <v>225.99</v>
+        <v>227.33</v>
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21311,12 +21311,12 @@
       </c>
       <c r="B696" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872531DSZ</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C696" s="2" t="inlineStr">
         <is>
-          <t>816171</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="D696" s="2" t="inlineStr">
@@ -21325,11 +21325,11 @@
         </is>
       </c>
       <c r="E696" s="3" t="n">
-        <v>224.12</v>
+        <v>225.9</v>
       </c>
       <c r="F696" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21341,12 +21341,12 @@
       </c>
       <c r="B697" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="C697" s="2" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>816171</t>
         </is>
       </c>
       <c r="D697" s="2" t="inlineStr">
@@ -21355,11 +21355,11 @@
         </is>
       </c>
       <c r="E697" s="3" t="n">
-        <v>221.13</v>
+        <v>224.12</v>
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -21371,12 +21371,12 @@
       </c>
       <c r="B698" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C698" s="2" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="D698" s="2" t="inlineStr">
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="E698" s="3" t="n">
-        <v>220.89</v>
+        <v>222.31</v>
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21401,12 +21401,12 @@
       </c>
       <c r="B699" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C699" s="2" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="D699" s="2" t="inlineStr">
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="E699" s="3" t="n">
-        <v>220.63</v>
+        <v>221.26</v>
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21445,11 +21445,11 @@
         </is>
       </c>
       <c r="E700" s="3" t="n">
-        <v>204.48</v>
+        <v>205.35</v>
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21461,12 +21461,12 @@
       </c>
       <c r="B701" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C701" s="2" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D701" s="2" t="inlineStr">
@@ -21475,11 +21475,11 @@
         </is>
       </c>
       <c r="E701" s="3" t="n">
-        <v>196.05</v>
+        <v>201.99</v>
       </c>
       <c r="F701" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21491,12 +21491,12 @@
       </c>
       <c r="B702" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C702" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="D702" s="2" t="inlineStr">
@@ -21505,11 +21505,11 @@
         </is>
       </c>
       <c r="E702" s="3" t="n">
-        <v>193.3</v>
+        <v>198.21</v>
       </c>
       <c r="F702" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21521,12 +21521,12 @@
       </c>
       <c r="B703" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C703" s="2" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="D703" s="2" t="inlineStr">
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="E703" s="3" t="n">
-        <v>192.5</v>
+        <v>194.04</v>
       </c>
       <c r="F703" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21551,12 +21551,12 @@
       </c>
       <c r="B704" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C704" s="2" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="D704" s="2" t="inlineStr">
@@ -21565,11 +21565,11 @@
         </is>
       </c>
       <c r="E704" s="3" t="n">
-        <v>190.67</v>
+        <v>193.26</v>
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21595,11 +21595,11 @@
         </is>
       </c>
       <c r="E705" s="3" t="n">
-        <v>187.91</v>
+        <v>188.62</v>
       </c>
       <c r="F705" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21625,11 +21625,11 @@
         </is>
       </c>
       <c r="E706" s="3" t="n">
-        <v>175.23</v>
+        <v>180.41</v>
       </c>
       <c r="F706" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21655,11 +21655,11 @@
         </is>
       </c>
       <c r="E707" s="3" t="n">
-        <v>173.11</v>
+        <v>174.9</v>
       </c>
       <c r="F707" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21685,11 +21685,11 @@
         </is>
       </c>
       <c r="E708" s="3" t="n">
-        <v>160.18</v>
+        <v>165.02</v>
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21701,12 +21701,12 @@
       </c>
       <c r="B709" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C709" s="2" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="D709" s="2" t="inlineStr">
@@ -21715,11 +21715,11 @@
         </is>
       </c>
       <c r="E709" s="3" t="n">
-        <v>158.82</v>
+        <v>160.34</v>
       </c>
       <c r="F709" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21731,12 +21731,12 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="D710" s="2" t="inlineStr">
@@ -21745,11 +21745,11 @@
         </is>
       </c>
       <c r="E710" s="3" t="n">
-        <v>158.06</v>
+        <v>158.82</v>
       </c>
       <c r="F710" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -21761,12 +21761,12 @@
       </c>
       <c r="B711" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C711" s="2" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D711" s="2" t="inlineStr">
@@ -21775,11 +21775,11 @@
         </is>
       </c>
       <c r="E711" s="3" t="n">
-        <v>150.25</v>
+        <v>151.56</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21791,12 +21791,12 @@
       </c>
       <c r="B712" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C712" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="D712" s="2" t="inlineStr">
@@ -21805,11 +21805,11 @@
         </is>
       </c>
       <c r="E712" s="3" t="n">
-        <v>148.96</v>
+        <v>150.25</v>
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -21835,11 +21835,11 @@
         </is>
       </c>
       <c r="E713" s="3" t="n">
-        <v>148.69</v>
+        <v>149.92</v>
       </c>
       <c r="F713" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21865,11 +21865,11 @@
         </is>
       </c>
       <c r="E714" s="3" t="n">
-        <v>145.71</v>
+        <v>146.4</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21911,12 +21911,12 @@
       </c>
       <c r="B716" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C716" s="2" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D716" s="2" t="inlineStr">
@@ -21925,11 +21925,11 @@
         </is>
       </c>
       <c r="E716" s="3" t="n">
-        <v>141.56</v>
+        <v>141.85</v>
       </c>
       <c r="F716" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21955,11 +21955,11 @@
         </is>
       </c>
       <c r="E717" s="3" t="n">
-        <v>140.95</v>
+        <v>141.62</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -21971,12 +21971,12 @@
       </c>
       <c r="B718" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr">
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="E718" s="3" t="n">
-        <v>140.57</v>
+        <v>141.56</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22015,11 +22015,11 @@
         </is>
       </c>
       <c r="E719" s="3" t="n">
-        <v>138.54</v>
+        <v>141.53</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22045,11 +22045,11 @@
         </is>
       </c>
       <c r="E720" s="3" t="n">
-        <v>136.86</v>
+        <v>137.1</v>
       </c>
       <c r="F720" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22135,11 +22135,11 @@
         </is>
       </c>
       <c r="E723" s="3" t="n">
-        <v>131.74</v>
+        <v>132.19</v>
       </c>
       <c r="F723" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22211,12 +22211,12 @@
       </c>
       <c r="B726" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C726" s="2" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="D726" s="2" t="inlineStr">
@@ -22225,11 +22225,11 @@
         </is>
       </c>
       <c r="E726" s="3" t="n">
-        <v>129.31</v>
+        <v>130.54</v>
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:53</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22241,12 +22241,12 @@
       </c>
       <c r="B727" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C727" s="2" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="D727" s="2" t="inlineStr">
@@ -22255,11 +22255,11 @@
         </is>
       </c>
       <c r="E727" s="3" t="n">
-        <v>127.92</v>
+        <v>129.31</v>
       </c>
       <c r="F727" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:10</t>
+          <t>2026-09-27 22:53</t>
         </is>
       </c>
     </row>
@@ -22345,11 +22345,11 @@
         </is>
       </c>
       <c r="E730" s="3" t="n">
-        <v>122.37</v>
+        <v>123.73</v>
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22361,12 +22361,12 @@
       </c>
       <c r="B731" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D731" s="2" t="inlineStr">
@@ -22375,11 +22375,11 @@
         </is>
       </c>
       <c r="E731" s="3" t="n">
-        <v>119.92</v>
+        <v>120.07</v>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22391,12 +22391,12 @@
       </c>
       <c r="B732" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="D732" s="2" t="inlineStr">
@@ -22405,11 +22405,11 @@
         </is>
       </c>
       <c r="E732" s="3" t="n">
-        <v>118.31</v>
+        <v>119.92</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22421,12 +22421,12 @@
       </c>
       <c r="B733" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="D733" s="2" t="inlineStr">
@@ -22435,11 +22435,11 @@
         </is>
       </c>
       <c r="E733" s="3" t="n">
-        <v>118.08</v>
+        <v>119.78</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22451,12 +22451,12 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
@@ -22465,11 +22465,11 @@
         </is>
       </c>
       <c r="E734" s="3" t="n">
-        <v>118.01</v>
+        <v>119.23</v>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22481,12 +22481,12 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
@@ -22495,11 +22495,11 @@
         </is>
       </c>
       <c r="E735" s="3" t="n">
-        <v>117.18</v>
+        <v>118.7</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22511,12 +22511,12 @@
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
@@ -22525,11 +22525,11 @@
         </is>
       </c>
       <c r="E736" s="3" t="n">
-        <v>115.64</v>
+        <v>117.83</v>
       </c>
       <c r="F736" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22571,12 +22571,12 @@
       </c>
       <c r="B738" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="D738" s="2" t="inlineStr">
@@ -22585,11 +22585,11 @@
         </is>
       </c>
       <c r="E738" s="3" t="n">
-        <v>114.07</v>
+        <v>114.57</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22601,12 +22601,12 @@
       </c>
       <c r="B739" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C739" s="2" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="D739" s="2" t="inlineStr">
@@ -22615,11 +22615,11 @@
         </is>
       </c>
       <c r="E739" s="3" t="n">
-        <v>113.77</v>
+        <v>114.07</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -22631,12 +22631,12 @@
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
@@ -22645,11 +22645,11 @@
         </is>
       </c>
       <c r="E740" s="3" t="n">
-        <v>113.25</v>
+        <v>113.73</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22661,12 +22661,12 @@
       </c>
       <c r="B741" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="D741" s="2" t="inlineStr">
@@ -22675,11 +22675,11 @@
         </is>
       </c>
       <c r="E741" s="3" t="n">
-        <v>112.82</v>
+        <v>113.64</v>
       </c>
       <c r="F741" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22691,12 +22691,12 @@
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="E742" s="3" t="n">
-        <v>111.24</v>
+        <v>113.25</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22735,11 +22735,11 @@
         </is>
       </c>
       <c r="E743" s="3" t="n">
-        <v>109.33</v>
+        <v>109.71</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22765,11 +22765,11 @@
         </is>
       </c>
       <c r="E744" s="3" t="n">
-        <v>106.32</v>
+        <v>107.1</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22795,11 +22795,11 @@
         </is>
       </c>
       <c r="E745" s="3" t="n">
-        <v>104.07</v>
+        <v>105.19</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22871,12 +22871,12 @@
       </c>
       <c r="B748" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C748" s="2" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="D748" s="2" t="inlineStr">
@@ -22885,11 +22885,11 @@
         </is>
       </c>
       <c r="E748" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>100.72</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22901,12 +22901,12 @@
       </c>
       <c r="B749" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C749" s="2" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="D749" s="2" t="inlineStr">
@@ -22915,11 +22915,11 @@
         </is>
       </c>
       <c r="E749" s="3" t="n">
-        <v>99.20999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F749" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -22931,12 +22931,12 @@
       </c>
       <c r="B750" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C750" s="2" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="D750" s="2" t="inlineStr">
@@ -22945,11 +22945,11 @@
         </is>
       </c>
       <c r="E750" s="3" t="n">
-        <v>97.81</v>
+        <v>98.45</v>
       </c>
       <c r="F750" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -22961,12 +22961,12 @@
       </c>
       <c r="B751" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C751" s="2" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="D751" s="2" t="inlineStr">
@@ -22975,11 +22975,11 @@
         </is>
       </c>
       <c r="E751" s="3" t="n">
-        <v>97.44</v>
+        <v>97.81</v>
       </c>
       <c r="F751" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -22991,12 +22991,12 @@
       </c>
       <c r="B752" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C752" s="2" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="D752" s="2" t="inlineStr">
@@ -23005,11 +23005,11 @@
         </is>
       </c>
       <c r="E752" s="3" t="n">
-        <v>96.7</v>
+        <v>97.44</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23021,12 +23021,12 @@
       </c>
       <c r="B753" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C753" s="2" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="D753" s="2" t="inlineStr">
@@ -23035,11 +23035,11 @@
         </is>
       </c>
       <c r="E753" s="3" t="n">
-        <v>96.22</v>
+        <v>97.41</v>
       </c>
       <c r="F753" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23051,12 +23051,12 @@
       </c>
       <c r="B754" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C754" s="2" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="D754" s="2" t="inlineStr">
@@ -23069,7 +23069,7 @@
       </c>
       <c r="F754" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23081,12 +23081,12 @@
       </c>
       <c r="B755" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C755" s="2" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="D755" s="2" t="inlineStr">
@@ -23095,11 +23095,11 @@
         </is>
       </c>
       <c r="E755" s="3" t="n">
-        <v>92.44</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="F755" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -23111,12 +23111,12 @@
       </c>
       <c r="B756" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C756" s="2" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D756" s="2" t="inlineStr">
@@ -23125,11 +23125,11 @@
         </is>
       </c>
       <c r="E756" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23141,12 +23141,12 @@
       </c>
       <c r="B757" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C757" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="D757" s="2" t="inlineStr">
@@ -23155,7 +23155,7 @@
         </is>
       </c>
       <c r="E757" s="3" t="n">
-        <v>91</v>
+        <v>92.44</v>
       </c>
       <c r="F757" s="2" t="inlineStr">
         <is>
@@ -23185,11 +23185,11 @@
         </is>
       </c>
       <c r="E758" s="3" t="n">
-        <v>90.75</v>
+        <v>91.13</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23201,12 +23201,12 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="D759" s="2" t="inlineStr">
@@ -23215,11 +23215,11 @@
         </is>
       </c>
       <c r="E759" s="3" t="n">
-        <v>89.79000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23231,21 +23231,21 @@
       </c>
       <c r="B760" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073957GV5</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C760" s="2" t="inlineStr">
         <is>
-          <t>814642</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="D760" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E760" s="3" t="n">
-        <v>89.48999999999999</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
@@ -23261,25 +23261,25 @@
       </c>
       <c r="B761" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4P00073957GV5</t>
         </is>
       </c>
       <c r="C761" s="2" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>814642</t>
         </is>
       </c>
       <c r="D761" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E761" s="3" t="n">
-        <v>87.98999999999999</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F761" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23305,11 +23305,11 @@
         </is>
       </c>
       <c r="E762" s="3" t="n">
-        <v>87.76000000000001</v>
+        <v>88.53</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23321,12 +23321,12 @@
       </c>
       <c r="B763" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C763" s="2" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="D763" s="2" t="inlineStr">
@@ -23335,11 +23335,11 @@
         </is>
       </c>
       <c r="E763" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>87.62</v>
       </c>
       <c r="F763" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23365,11 +23365,11 @@
         </is>
       </c>
       <c r="E764" s="3" t="n">
-        <v>86.44</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23381,12 +23381,12 @@
       </c>
       <c r="B765" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C765" s="2" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="D765" s="2" t="inlineStr">
@@ -23395,11 +23395,11 @@
         </is>
       </c>
       <c r="E765" s="3" t="n">
-        <v>85.54000000000001</v>
+        <v>87.33</v>
       </c>
       <c r="F765" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23411,12 +23411,12 @@
       </c>
       <c r="B766" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C766" s="2" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="D766" s="2" t="inlineStr">
@@ -23425,11 +23425,11 @@
         </is>
       </c>
       <c r="E766" s="3" t="n">
-        <v>85.13</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23455,11 +23455,11 @@
         </is>
       </c>
       <c r="E767" s="3" t="n">
-        <v>83.86</v>
+        <v>85.92</v>
       </c>
       <c r="F767" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23471,12 +23471,12 @@
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="D768" s="2" t="inlineStr">
@@ -23485,11 +23485,11 @@
         </is>
       </c>
       <c r="E768" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -23501,12 +23501,12 @@
       </c>
       <c r="B769" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C769" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="D769" s="2" t="inlineStr">
@@ -23515,11 +23515,11 @@
         </is>
       </c>
       <c r="E769" s="3" t="n">
-        <v>82.73999999999999</v>
+        <v>84.01000000000001</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23531,12 +23531,12 @@
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D770" s="2" t="inlineStr">
@@ -23545,11 +23545,11 @@
         </is>
       </c>
       <c r="E770" s="3" t="n">
-        <v>82.18000000000001</v>
+        <v>83.67</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23561,12 +23561,12 @@
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="D771" s="2" t="inlineStr">
@@ -23575,11 +23575,11 @@
         </is>
       </c>
       <c r="E771" s="3" t="n">
-        <v>81.73</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:24</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23605,11 +23605,11 @@
         </is>
       </c>
       <c r="E772" s="3" t="n">
-        <v>81.59</v>
+        <v>82.06</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23621,12 +23621,12 @@
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="D773" s="2" t="inlineStr">
@@ -23635,11 +23635,11 @@
         </is>
       </c>
       <c r="E773" s="3" t="n">
-        <v>80.28</v>
+        <v>81.73</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-22 08:24</t>
         </is>
       </c>
     </row>
@@ -23695,11 +23695,11 @@
         </is>
       </c>
       <c r="E775" s="3" t="n">
-        <v>78.48999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F775" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23725,11 +23725,11 @@
         </is>
       </c>
       <c r="E776" s="3" t="n">
-        <v>75.51000000000001</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="F776" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23741,12 +23741,12 @@
       </c>
       <c r="B777" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C777" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="D777" s="2" t="inlineStr">
@@ -23755,11 +23755,11 @@
         </is>
       </c>
       <c r="E777" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="F777" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23771,12 +23771,12 @@
       </c>
       <c r="B778" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C778" s="2" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="D778" s="2" t="inlineStr">
@@ -23785,11 +23785,11 @@
         </is>
       </c>
       <c r="E778" s="3" t="n">
-        <v>74.76000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F778" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23801,21 +23801,21 @@
       </c>
       <c r="B779" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073954DZ8</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C779" s="2" t="inlineStr">
         <is>
-          <t>814644</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="D779" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E779" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="F779" s="2" t="inlineStr">
         <is>
@@ -23831,25 +23831,25 @@
       </c>
       <c r="B780" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4P00073954DZ8</t>
         </is>
       </c>
       <c r="C780" s="2" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>814644</t>
         </is>
       </c>
       <c r="D780" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E780" s="3" t="n">
-        <v>74.06999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -23861,12 +23861,12 @@
       </c>
       <c r="B781" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C781" s="2" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D781" s="2" t="inlineStr">
@@ -23875,11 +23875,11 @@
         </is>
       </c>
       <c r="E781" s="3" t="n">
-        <v>73.55</v>
+        <v>73.64</v>
       </c>
       <c r="F781" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23891,12 +23891,12 @@
       </c>
       <c r="B782" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C782" s="2" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="D782" s="2" t="inlineStr">
@@ -23905,11 +23905,11 @@
         </is>
       </c>
       <c r="E782" s="3" t="n">
-        <v>72.23</v>
+        <v>73.55</v>
       </c>
       <c r="F782" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-29 08:30</t>
         </is>
       </c>
     </row>
@@ -23921,12 +23921,12 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="D783" s="2" t="inlineStr">
@@ -23935,11 +23935,11 @@
         </is>
       </c>
       <c r="E783" s="3" t="n">
-        <v>71.53</v>
+        <v>73.11</v>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23951,12 +23951,12 @@
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
@@ -23965,11 +23965,11 @@
         </is>
       </c>
       <c r="E784" s="3" t="n">
-        <v>71.38</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -23981,12 +23981,12 @@
       </c>
       <c r="B785" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C785" s="2" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="D785" s="2" t="inlineStr">
@@ -23995,11 +23995,11 @@
         </is>
       </c>
       <c r="E785" s="3" t="n">
-        <v>70.48</v>
+        <v>71.38</v>
       </c>
       <c r="F785" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 21:17</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24011,12 +24011,12 @@
       </c>
       <c r="B786" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C786" s="2" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="D786" s="2" t="inlineStr">
@@ -24025,11 +24025,11 @@
         </is>
       </c>
       <c r="E786" s="3" t="n">
-        <v>69.42</v>
+        <v>70.48</v>
       </c>
       <c r="F786" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-24 21:17</t>
         </is>
       </c>
     </row>
@@ -24055,11 +24055,11 @@
         </is>
       </c>
       <c r="E787" s="3" t="n">
-        <v>69.17</v>
+        <v>69.39</v>
       </c>
       <c r="F787" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -24115,11 +24115,11 @@
         </is>
       </c>
       <c r="E789" s="3" t="n">
-        <v>68</v>
+        <v>68.03</v>
       </c>
       <c r="F789" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -24145,11 +24145,11 @@
         </is>
       </c>
       <c r="E790" s="3" t="n">
-        <v>67.67</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F790" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -24175,11 +24175,11 @@
         </is>
       </c>
       <c r="E791" s="3" t="n">
-        <v>64.45999999999999</v>
+        <v>66.48</v>
       </c>
       <c r="F791" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -24235,11 +24235,11 @@
         </is>
       </c>
       <c r="E793" s="3" t="n">
-        <v>62.34</v>
+        <v>62.58</v>
       </c>
       <c r="F793" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -24265,11 +24265,11 @@
         </is>
       </c>
       <c r="E794" s="3" t="n">
-        <v>61.42</v>
+        <v>61.69</v>
       </c>
       <c r="F794" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -24295,11 +24295,11 @@
         </is>
       </c>
       <c r="E795" s="3" t="n">
-        <v>59.77</v>
+        <v>60.03</v>
       </c>
       <c r="F795" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -24355,11 +24355,11 @@
         </is>
       </c>
       <c r="E797" s="3" t="n">
-        <v>55.31</v>
+        <v>55.33</v>
       </c>
       <c r="F797" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -24445,11 +24445,11 @@
         </is>
       </c>
       <c r="E800" s="3" t="n">
-        <v>53.17</v>
+        <v>53.49</v>
       </c>
       <c r="F800" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -24461,12 +24461,12 @@
       </c>
       <c r="B801" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C801" s="2" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="D801" s="2" t="inlineStr">
@@ -24475,11 +24475,11 @@
         </is>
       </c>
       <c r="E801" s="3" t="n">
-        <v>52.9</v>
+        <v>53.29</v>
       </c>
       <c r="F801" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -24491,12 +24491,12 @@
       </c>
       <c r="B802" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C802" s="2" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="D802" s="2" t="inlineStr">
@@ -24505,11 +24505,11 @@
         </is>
       </c>
       <c r="E802" s="3" t="n">
-        <v>52.57</v>
+        <v>52.91</v>
       </c>
       <c r="F802" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -24521,12 +24521,12 @@
       </c>
       <c r="B803" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C803" s="2" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="D803" s="2" t="inlineStr">
@@ -24535,11 +24535,11 @@
         </is>
       </c>
       <c r="E803" s="3" t="n">
-        <v>51.44</v>
+        <v>52.57</v>
       </c>
       <c r="F803" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 08:30</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24551,12 +24551,12 @@
       </c>
       <c r="B804" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C804" s="2" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="D804" s="2" t="inlineStr">
@@ -24565,11 +24565,11 @@
         </is>
       </c>
       <c r="E804" s="3" t="n">
-        <v>50.99</v>
+        <v>51.64</v>
       </c>
       <c r="F804" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -24595,11 +24595,11 @@
         </is>
       </c>
       <c r="E805" s="3" t="n">
-        <v>50.79</v>
+        <v>50.91</v>
       </c>
       <c r="F805" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -24715,11 +24715,11 @@
         </is>
       </c>
       <c r="E809" s="3" t="n">
-        <v>47.7</v>
+        <v>47.93</v>
       </c>
       <c r="F809" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -24775,11 +24775,11 @@
         </is>
       </c>
       <c r="E811" s="3" t="n">
-        <v>46.77</v>
+        <v>46.94</v>
       </c>
       <c r="F811" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -24835,11 +24835,11 @@
         </is>
       </c>
       <c r="E813" s="3" t="n">
-        <v>45.69</v>
+        <v>45.87</v>
       </c>
       <c r="F813" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -24881,12 +24881,12 @@
       </c>
       <c r="B815" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C815" s="2" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="D815" s="2" t="inlineStr">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="F815" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -24911,12 +24911,12 @@
       </c>
       <c r="B816" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C816" s="2" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="D816" s="2" t="inlineStr">
@@ -24925,11 +24925,11 @@
         </is>
       </c>
       <c r="E816" s="3" t="n">
-        <v>44.06</v>
+        <v>44.19</v>
       </c>
       <c r="F816" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -24971,12 +24971,12 @@
       </c>
       <c r="B818" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C818" s="2" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="D818" s="2" t="inlineStr">
@@ -24985,11 +24985,11 @@
         </is>
       </c>
       <c r="E818" s="3" t="n">
-        <v>39.39</v>
+        <v>39.86</v>
       </c>
       <c r="F818" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 08:41</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -25001,12 +25001,12 @@
       </c>
       <c r="B819" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C819" s="2" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="D819" s="2" t="inlineStr">
@@ -25015,11 +25015,11 @@
         </is>
       </c>
       <c r="E819" s="3" t="n">
-        <v>38.93</v>
+        <v>39.39</v>
       </c>
       <c r="F819" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-25 08:41</t>
         </is>
       </c>
     </row>
@@ -25045,11 +25045,11 @@
         </is>
       </c>
       <c r="E820" s="3" t="n">
-        <v>38.61</v>
+        <v>38.65</v>
       </c>
       <c r="F820" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -25135,11 +25135,11 @@
         </is>
       </c>
       <c r="E823" s="3" t="n">
-        <v>37.1</v>
+        <v>37.16</v>
       </c>
       <c r="F823" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -25241,12 +25241,12 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="D827" s="2" t="inlineStr">
@@ -25255,11 +25255,11 @@
         </is>
       </c>
       <c r="E827" s="3" t="n">
-        <v>34.64</v>
+        <v>35.12</v>
       </c>
       <c r="F827" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 16:08</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -25271,12 +25271,12 @@
       </c>
       <c r="B828" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C828" s="2" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="D828" s="2" t="inlineStr">
@@ -25285,11 +25285,11 @@
         </is>
       </c>
       <c r="E828" s="3" t="n">
-        <v>34.05</v>
+        <v>34.64</v>
       </c>
       <c r="F828" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
+          <t>2026-09-27 16:08</t>
         </is>
       </c>
     </row>
@@ -25301,12 +25301,12 @@
       </c>
       <c r="B829" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C829" s="2" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="D829" s="2" t="inlineStr">
@@ -25315,11 +25315,11 @@
         </is>
       </c>
       <c r="E829" s="3" t="n">
-        <v>33.62</v>
+        <v>34.17</v>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -25331,12 +25331,12 @@
       </c>
       <c r="B830" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="C830" s="2" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="D830" s="2" t="inlineStr">
@@ -25345,11 +25345,11 @@
         </is>
       </c>
       <c r="E830" s="3" t="n">
-        <v>33.55</v>
+        <v>34.05</v>
       </c>
       <c r="F830" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-21 17:05</t>
         </is>
       </c>
     </row>
@@ -25375,11 +25375,11 @@
         </is>
       </c>
       <c r="E831" s="3" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="F831" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>
@@ -25525,11 +25525,11 @@
         </is>
       </c>
       <c r="E836" s="3" t="n">
-        <v>28.09</v>
+        <v>28.48</v>
       </c>
       <c r="F836" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 07:40</t>
+          <t>2026-09-30 17:04</t>
         </is>
       </c>
     </row>

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -30385,11 +30385,11 @@
         </is>
       </c>
       <c r="E998" s="3" t="n">
-        <v>26.18</v>
+        <v>153.65</v>
       </c>
       <c r="F998" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30401,12 +30401,12 @@
       </c>
       <c r="B999" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4P00066848VQM</t>
         </is>
       </c>
       <c r="C999" s="2" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>812923</t>
         </is>
       </c>
       <c r="D999" s="2" t="inlineStr">
@@ -30415,11 +30415,11 @@
         </is>
       </c>
       <c r="E999" s="3" t="n">
-        <v>5.8</v>
+        <v>84.2</v>
       </c>
       <c r="F999" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30431,12 +30431,12 @@
       </c>
       <c r="B1000" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066848VQM</t>
+          <t>KIT4P00065641GDF</t>
         </is>
       </c>
       <c r="C1000" s="2" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>812924</t>
         </is>
       </c>
       <c r="D1000" s="2" t="inlineStr">
@@ -30445,11 +30445,11 @@
         </is>
       </c>
       <c r="E1000" s="3" t="n">
-        <v>5.48</v>
+        <v>67.98</v>
       </c>
       <c r="F1000" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30461,12 +30461,12 @@
       </c>
       <c r="B1001" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065641GDF</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C1001" s="2" t="inlineStr">
         <is>
-          <t>812924</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="D1001" s="2" t="inlineStr">
@@ -30475,11 +30475,11 @@
         </is>
       </c>
       <c r="E1001" s="3" t="n">
-        <v>4.64</v>
+        <v>64.14</v>
       </c>
       <c r="F1001" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30491,12 +30491,12 @@
       </c>
       <c r="B1002" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008460369B</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C1002" s="2" t="inlineStr">
         <is>
-          <t>816224</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="D1002" s="2" t="inlineStr">
@@ -30505,11 +30505,11 @@
         </is>
       </c>
       <c r="E1002" s="3" t="n">
-        <v>3.65</v>
+        <v>59.68</v>
       </c>
       <c r="F1002" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30521,12 +30521,12 @@
       </c>
       <c r="B1003" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M05413776H84</t>
         </is>
       </c>
       <c r="C1003" s="2" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>810101</t>
         </is>
       </c>
       <c r="D1003" s="2" t="inlineStr">
@@ -30535,11 +30535,11 @@
         </is>
       </c>
       <c r="E1003" s="3" t="n">
-        <v>2.65</v>
+        <v>56.1</v>
       </c>
       <c r="F1003" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30551,25 +30551,25 @@
       </c>
       <c r="B1004" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4P0008460369B</t>
         </is>
       </c>
       <c r="C1004" s="2" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>816224</t>
         </is>
       </c>
       <c r="D1004" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E1004" s="3" t="n">
-        <v>2.29</v>
+        <v>54.72</v>
       </c>
       <c r="F1004" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30581,25 +30581,25 @@
       </c>
       <c r="B1005" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C1005" s="2" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D1005" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E1005" s="3" t="n">
-        <v>2.18</v>
+        <v>44.74</v>
       </c>
       <c r="F1005" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30611,12 +30611,12 @@
       </c>
       <c r="B1006" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413776H84</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C1006" s="2" t="inlineStr">
         <is>
-          <t>810101</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="D1006" s="2" t="inlineStr">
@@ -30625,11 +30625,11 @@
         </is>
       </c>
       <c r="E1006" s="3" t="n">
-        <v>2.08</v>
+        <v>43.69</v>
       </c>
       <c r="F1006" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30641,25 +30641,25 @@
       </c>
       <c r="B1007" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C1007" s="2" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="D1007" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E1007" s="3" t="n">
-        <v>1.45</v>
+        <v>39.54</v>
       </c>
       <c r="F1007" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30671,12 +30671,12 @@
       </c>
       <c r="B1008" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C1008" s="2" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D1008" s="2" t="inlineStr">
@@ -30685,11 +30685,11 @@
         </is>
       </c>
       <c r="E1008" s="3" t="n">
-        <v>1.37</v>
+        <v>38.15</v>
       </c>
       <c r="F1008" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30701,12 +30701,12 @@
       </c>
       <c r="B1009" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066915CBF</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C1009" s="2" t="inlineStr">
         <is>
-          <t>812921</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="D1009" s="2" t="inlineStr">
@@ -30715,11 +30715,11 @@
         </is>
       </c>
       <c r="E1009" s="3" t="n">
-        <v>1.21</v>
+        <v>30.7</v>
       </c>
       <c r="F1009" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30731,12 +30731,12 @@
       </c>
       <c r="B1010" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C1010" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="D1010" s="2" t="inlineStr">
@@ -30745,11 +30745,11 @@
         </is>
       </c>
       <c r="E1010" s="3" t="n">
-        <v>1.19</v>
+        <v>29.16</v>
       </c>
       <c r="F1010" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30761,25 +30761,25 @@
       </c>
       <c r="B1011" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C1011" s="2" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="D1011" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E1011" s="3" t="n">
-        <v>1.17</v>
+        <v>27.73</v>
       </c>
       <c r="F1011" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30791,25 +30791,25 @@
       </c>
       <c r="B1012" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C1012" s="2" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D1012" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E1012" s="3" t="n">
-        <v>1.16</v>
+        <v>26.9</v>
       </c>
       <c r="F1012" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30821,12 +30821,12 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="D1013" s="2" t="inlineStr">
@@ -30835,11 +30835,11 @@
         </is>
       </c>
       <c r="E1013" s="3" t="n">
-        <v>1.14</v>
+        <v>26.5</v>
       </c>
       <c r="F1013" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30851,25 +30851,25 @@
       </c>
       <c r="B1014" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C1014" s="2" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="D1014" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E1014" s="3" t="n">
-        <v>1.14</v>
+        <v>23.52</v>
       </c>
       <c r="F1014" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30881,12 +30881,12 @@
       </c>
       <c r="B1015" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C1015" s="2" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="D1015" s="2" t="inlineStr">
@@ -30895,11 +30895,11 @@
         </is>
       </c>
       <c r="E1015" s="3" t="n">
-        <v>1.09</v>
+        <v>21.29</v>
       </c>
       <c r="F1015" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30911,25 +30911,25 @@
       </c>
       <c r="B1016" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4P00066915CBF</t>
         </is>
       </c>
       <c r="C1016" s="2" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>812921</t>
         </is>
       </c>
       <c r="D1016" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E1016" s="3" t="n">
-        <v>1.06</v>
+        <v>20.54</v>
       </c>
       <c r="F1016" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30941,12 +30941,12 @@
       </c>
       <c r="B1017" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C1017" s="2" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="D1017" s="2" t="inlineStr">
@@ -30955,11 +30955,11 @@
         </is>
       </c>
       <c r="E1017" s="3" t="n">
-        <v>1.03</v>
+        <v>18.37</v>
       </c>
       <c r="F1017" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -30971,12 +30971,12 @@
       </c>
       <c r="B1018" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C1018" s="2" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="D1018" s="2" t="inlineStr">
@@ -30985,11 +30985,11 @@
         </is>
       </c>
       <c r="E1018" s="3" t="n">
-        <v>0.98</v>
+        <v>17.28</v>
       </c>
       <c r="F1018" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31001,12 +31001,12 @@
       </c>
       <c r="B1019" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C1019" s="2" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="D1019" s="2" t="inlineStr">
@@ -31015,11 +31015,11 @@
         </is>
       </c>
       <c r="E1019" s="3" t="n">
-        <v>0.93</v>
+        <v>16.39</v>
       </c>
       <c r="F1019" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31031,12 +31031,12 @@
       </c>
       <c r="B1020" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C1020" s="2" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="D1020" s="2" t="inlineStr">
@@ -31045,11 +31045,11 @@
         </is>
       </c>
       <c r="E1020" s="3" t="n">
-        <v>0.84</v>
+        <v>15.24</v>
       </c>
       <c r="F1020" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31061,12 +31061,12 @@
       </c>
       <c r="B1021" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C1021" s="2" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="D1021" s="2" t="inlineStr">
@@ -31075,11 +31075,11 @@
         </is>
       </c>
       <c r="E1021" s="3" t="n">
-        <v>0.8</v>
+        <v>14.85</v>
       </c>
       <c r="F1021" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31091,25 +31091,25 @@
       </c>
       <c r="B1022" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C1022" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="D1022" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E1022" s="3" t="n">
-        <v>0.75</v>
+        <v>14.67</v>
       </c>
       <c r="F1022" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31121,12 +31121,12 @@
       </c>
       <c r="B1023" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C1023" s="2" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="D1023" s="2" t="inlineStr">
@@ -31135,11 +31135,11 @@
         </is>
       </c>
       <c r="E1023" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>13.01</v>
       </c>
       <c r="F1023" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31151,12 +31151,12 @@
       </c>
       <c r="B1024" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C1024" s="2" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="D1024" s="2" t="inlineStr">
@@ -31165,11 +31165,11 @@
         </is>
       </c>
       <c r="E1024" s="3" t="n">
-        <v>0.67</v>
+        <v>11.32</v>
       </c>
       <c r="F1024" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31181,25 +31181,25 @@
       </c>
       <c r="B1025" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C1025" s="2" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D1025" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E1025" s="3" t="n">
-        <v>0.67</v>
+        <v>11.22</v>
       </c>
       <c r="F1025" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31211,12 +31211,12 @@
       </c>
       <c r="B1026" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C1026" s="2" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="D1026" s="2" t="inlineStr">
@@ -31225,11 +31225,11 @@
         </is>
       </c>
       <c r="E1026" s="3" t="n">
-        <v>0.62</v>
+        <v>10.92</v>
       </c>
       <c r="F1026" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31241,25 +31241,25 @@
       </c>
       <c r="B1027" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C1027" s="2" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="D1027" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E1027" s="3" t="n">
-        <v>0.62</v>
+        <v>10.59</v>
       </c>
       <c r="F1027" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31271,25 +31271,25 @@
       </c>
       <c r="B1028" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000668852J9</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C1028" s="2" t="inlineStr">
         <is>
-          <t>812925</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="D1028" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E1028" s="3" t="n">
-        <v>0.58</v>
+        <v>10.28</v>
       </c>
       <c r="F1028" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31301,12 +31301,12 @@
       </c>
       <c r="B1029" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C1029" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="D1029" s="2" t="inlineStr">
@@ -31315,11 +31315,11 @@
         </is>
       </c>
       <c r="E1029" s="3" t="n">
-        <v>0.57</v>
+        <v>10.17</v>
       </c>
       <c r="F1029" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31331,12 +31331,12 @@
       </c>
       <c r="B1030" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C1030" s="2" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="D1030" s="2" t="inlineStr">
@@ -31345,11 +31345,11 @@
         </is>
       </c>
       <c r="E1030" s="3" t="n">
-        <v>0.55</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F1030" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31361,12 +31361,12 @@
       </c>
       <c r="B1031" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="C1031" s="2" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="D1031" s="2" t="inlineStr">
@@ -31375,11 +31375,11 @@
         </is>
       </c>
       <c r="E1031" s="3" t="n">
-        <v>0.51</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F1031" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31391,12 +31391,12 @@
       </c>
       <c r="B1032" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C1032" s="2" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="D1032" s="2" t="inlineStr">
@@ -31405,11 +31405,11 @@
         </is>
       </c>
       <c r="E1032" s="3" t="n">
-        <v>0.48</v>
+        <v>8.85</v>
       </c>
       <c r="F1032" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31421,12 +31421,12 @@
       </c>
       <c r="B1033" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="C1033" s="2" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="D1033" s="2" t="inlineStr">
@@ -31435,11 +31435,11 @@
         </is>
       </c>
       <c r="E1033" s="3" t="n">
-        <v>0.47</v>
+        <v>8.66</v>
       </c>
       <c r="F1033" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31451,12 +31451,12 @@
       </c>
       <c r="B1034" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C1034" s="2" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="D1034" s="2" t="inlineStr">
@@ -31465,11 +31465,11 @@
         </is>
       </c>
       <c r="E1034" s="3" t="n">
-        <v>0.47</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="F1034" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31481,12 +31481,12 @@
       </c>
       <c r="B1035" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C1035" s="2" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="D1035" s="2" t="inlineStr">
@@ -31495,11 +31495,11 @@
         </is>
       </c>
       <c r="E1035" s="3" t="n">
-        <v>0.45</v>
+        <v>7.25</v>
       </c>
       <c r="F1035" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31511,25 +31511,25 @@
       </c>
       <c r="B1036" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4P000668852J9</t>
         </is>
       </c>
       <c r="C1036" s="2" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>812925</t>
         </is>
       </c>
       <c r="D1036" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E1036" s="3" t="n">
-        <v>0.44</v>
+        <v>7.12</v>
       </c>
       <c r="F1036" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31541,12 +31541,12 @@
       </c>
       <c r="B1037" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C1037" s="2" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="D1037" s="2" t="inlineStr">
@@ -31555,11 +31555,11 @@
         </is>
       </c>
       <c r="E1037" s="3" t="n">
-        <v>0.42</v>
+        <v>6.71</v>
       </c>
       <c r="F1037" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31571,12 +31571,12 @@
       </c>
       <c r="B1038" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C1038" s="2" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="D1038" s="2" t="inlineStr">
@@ -31585,11 +31585,11 @@
         </is>
       </c>
       <c r="E1038" s="3" t="n">
-        <v>0.42</v>
+        <v>6.4</v>
       </c>
       <c r="F1038" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31601,12 +31601,12 @@
       </c>
       <c r="B1039" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C1039" s="2" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="D1039" s="2" t="inlineStr">
@@ -31615,11 +31615,11 @@
         </is>
       </c>
       <c r="E1039" s="3" t="n">
-        <v>0.4</v>
+        <v>6.21</v>
       </c>
       <c r="F1039" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31631,12 +31631,12 @@
       </c>
       <c r="B1040" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C1040" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="D1040" s="2" t="inlineStr">
@@ -31645,11 +31645,11 @@
         </is>
       </c>
       <c r="E1040" s="3" t="n">
-        <v>0.4</v>
+        <v>6.14</v>
       </c>
       <c r="F1040" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31661,12 +31661,12 @@
       </c>
       <c r="B1041" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C1041" s="2" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="D1041" s="2" t="inlineStr">
@@ -31675,11 +31675,11 @@
         </is>
       </c>
       <c r="E1041" s="3" t="n">
-        <v>0.39</v>
+        <v>5.94</v>
       </c>
       <c r="F1041" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31691,12 +31691,12 @@
       </c>
       <c r="B1042" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C1042" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="D1042" s="2" t="inlineStr">
@@ -31705,11 +31705,11 @@
         </is>
       </c>
       <c r="E1042" s="3" t="n">
-        <v>0.39</v>
+        <v>5.91</v>
       </c>
       <c r="F1042" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31721,12 +31721,12 @@
       </c>
       <c r="B1043" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C1043" s="2" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="D1043" s="2" t="inlineStr">
@@ -31735,11 +31735,11 @@
         </is>
       </c>
       <c r="E1043" s="3" t="n">
-        <v>0.38</v>
+        <v>5.69</v>
       </c>
       <c r="F1043" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31751,12 +31751,12 @@
       </c>
       <c r="B1044" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C1044" s="2" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="D1044" s="2" t="inlineStr">
@@ -31765,11 +31765,11 @@
         </is>
       </c>
       <c r="E1044" s="3" t="n">
-        <v>0.36</v>
+        <v>5.39</v>
       </c>
       <c r="F1044" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31781,12 +31781,12 @@
       </c>
       <c r="B1045" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C1045" s="2" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="D1045" s="2" t="inlineStr">
@@ -31795,11 +31795,11 @@
         </is>
       </c>
       <c r="E1045" s="3" t="n">
-        <v>0.36</v>
+        <v>5.28</v>
       </c>
       <c r="F1045" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31811,12 +31811,12 @@
       </c>
       <c r="B1046" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C1046" s="2" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="D1046" s="2" t="inlineStr">
@@ -31825,11 +31825,11 @@
         </is>
       </c>
       <c r="E1046" s="3" t="n">
-        <v>0.34</v>
+        <v>5.18</v>
       </c>
       <c r="F1046" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31841,12 +31841,12 @@
       </c>
       <c r="B1047" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C1047" s="2" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="D1047" s="2" t="inlineStr">
@@ -31855,11 +31855,11 @@
         </is>
       </c>
       <c r="E1047" s="3" t="n">
-        <v>0.32</v>
+        <v>5.07</v>
       </c>
       <c r="F1047" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31871,12 +31871,12 @@
       </c>
       <c r="B1048" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C1048" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D1048" s="2" t="inlineStr">
@@ -31885,11 +31885,11 @@
         </is>
       </c>
       <c r="E1048" s="3" t="n">
-        <v>0.31</v>
+        <v>4.88</v>
       </c>
       <c r="F1048" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31915,11 +31915,11 @@
         </is>
       </c>
       <c r="E1049" s="3" t="n">
-        <v>0.3</v>
+        <v>4.88</v>
       </c>
       <c r="F1049" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31931,12 +31931,12 @@
       </c>
       <c r="B1050" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C1050" s="2" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="D1050" s="2" t="inlineStr">
@@ -31945,11 +31945,11 @@
         </is>
       </c>
       <c r="E1050" s="3" t="n">
-        <v>0.3</v>
+        <v>4.83</v>
       </c>
       <c r="F1050" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31961,12 +31961,12 @@
       </c>
       <c r="B1051" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C1051" s="2" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="D1051" s="2" t="inlineStr">
@@ -31975,11 +31975,11 @@
         </is>
       </c>
       <c r="E1051" s="3" t="n">
-        <v>0.28</v>
+        <v>4.69</v>
       </c>
       <c r="F1051" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -31991,12 +31991,12 @@
       </c>
       <c r="B1052" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C1052" s="2" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="D1052" s="2" t="inlineStr">
@@ -32005,11 +32005,11 @@
         </is>
       </c>
       <c r="E1052" s="3" t="n">
-        <v>0.28</v>
+        <v>4.59</v>
       </c>
       <c r="F1052" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32021,12 +32021,12 @@
       </c>
       <c r="B1053" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C1053" s="2" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="D1053" s="2" t="inlineStr">
@@ -32035,11 +32035,11 @@
         </is>
       </c>
       <c r="E1053" s="3" t="n">
-        <v>0.28</v>
+        <v>4.56</v>
       </c>
       <c r="F1053" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32051,12 +32051,12 @@
       </c>
       <c r="B1054" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C1054" s="2" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="D1054" s="2" t="inlineStr">
@@ -32065,11 +32065,11 @@
         </is>
       </c>
       <c r="E1054" s="3" t="n">
-        <v>0.27</v>
+        <v>4.53</v>
       </c>
       <c r="F1054" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32081,12 +32081,12 @@
       </c>
       <c r="B1055" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C1055" s="2" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D1055" s="2" t="inlineStr">
@@ -32095,11 +32095,11 @@
         </is>
       </c>
       <c r="E1055" s="3" t="n">
-        <v>0.27</v>
+        <v>4.39</v>
       </c>
       <c r="F1055" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32111,12 +32111,12 @@
       </c>
       <c r="B1056" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C1056" s="2" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="D1056" s="2" t="inlineStr">
@@ -32125,11 +32125,11 @@
         </is>
       </c>
       <c r="E1056" s="3" t="n">
-        <v>0.27</v>
+        <v>4.24</v>
       </c>
       <c r="F1056" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32155,11 +32155,11 @@
         </is>
       </c>
       <c r="E1057" s="3" t="n">
-        <v>0.25</v>
+        <v>4.01</v>
       </c>
       <c r="F1057" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32171,12 +32171,12 @@
       </c>
       <c r="B1058" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C1058" s="2" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="D1058" s="2" t="inlineStr">
@@ -32185,11 +32185,11 @@
         </is>
       </c>
       <c r="E1058" s="3" t="n">
-        <v>0.24</v>
+        <v>3.94</v>
       </c>
       <c r="F1058" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32201,12 +32201,12 @@
       </c>
       <c r="B1059" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C1059" s="2" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="D1059" s="2" t="inlineStr">
@@ -32215,11 +32215,11 @@
         </is>
       </c>
       <c r="E1059" s="3" t="n">
-        <v>0.23</v>
+        <v>3.71</v>
       </c>
       <c r="F1059" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32231,12 +32231,12 @@
       </c>
       <c r="B1060" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C1060" s="2" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="D1060" s="2" t="inlineStr">
@@ -32245,11 +32245,11 @@
         </is>
       </c>
       <c r="E1060" s="3" t="n">
-        <v>0.23</v>
+        <v>3.62</v>
       </c>
       <c r="F1060" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32261,12 +32261,12 @@
       </c>
       <c r="B1061" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C1061" s="2" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="D1061" s="2" t="inlineStr">
@@ -32275,11 +32275,11 @@
         </is>
       </c>
       <c r="E1061" s="3" t="n">
-        <v>0.23</v>
+        <v>3.57</v>
       </c>
       <c r="F1061" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32291,12 +32291,12 @@
       </c>
       <c r="B1062" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C1062" s="2" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="D1062" s="2" t="inlineStr">
@@ -32305,11 +32305,11 @@
         </is>
       </c>
       <c r="E1062" s="3" t="n">
-        <v>0.21</v>
+        <v>3.32</v>
       </c>
       <c r="F1062" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32321,12 +32321,12 @@
       </c>
       <c r="B1063" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C1063" s="2" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="D1063" s="2" t="inlineStr">
@@ -32335,11 +32335,11 @@
         </is>
       </c>
       <c r="E1063" s="3" t="n">
-        <v>0.2</v>
+        <v>3.29</v>
       </c>
       <c r="F1063" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32351,12 +32351,12 @@
       </c>
       <c r="B1064" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="C1064" s="2" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>812824</t>
         </is>
       </c>
       <c r="D1064" s="2" t="inlineStr">
@@ -32365,11 +32365,11 @@
         </is>
       </c>
       <c r="E1064" s="3" t="n">
-        <v>0.19</v>
+        <v>3.23</v>
       </c>
       <c r="F1064" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32381,12 +32381,12 @@
       </c>
       <c r="B1065" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C1065" s="2" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="D1065" s="2" t="inlineStr">
@@ -32395,11 +32395,11 @@
         </is>
       </c>
       <c r="E1065" s="3" t="n">
-        <v>0.18</v>
+        <v>3.03</v>
       </c>
       <c r="F1065" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32411,12 +32411,12 @@
       </c>
       <c r="B1066" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C1066" s="2" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="D1066" s="2" t="inlineStr">
@@ -32425,11 +32425,11 @@
         </is>
       </c>
       <c r="E1066" s="3" t="n">
-        <v>0.18</v>
+        <v>2.99</v>
       </c>
       <c r="F1066" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32441,12 +32441,12 @@
       </c>
       <c r="B1067" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C1067" s="2" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="D1067" s="2" t="inlineStr">
@@ -32455,11 +32455,11 @@
         </is>
       </c>
       <c r="E1067" s="3" t="n">
-        <v>0.16</v>
+        <v>2.9</v>
       </c>
       <c r="F1067" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32471,12 +32471,12 @@
       </c>
       <c r="B1068" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C1068" s="2" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="D1068" s="2" t="inlineStr">
@@ -32485,11 +32485,11 @@
         </is>
       </c>
       <c r="E1068" s="3" t="n">
-        <v>0.16</v>
+        <v>2.89</v>
       </c>
       <c r="F1068" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32501,12 +32501,12 @@
       </c>
       <c r="B1069" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C1069" s="2" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="D1069" s="2" t="inlineStr">
@@ -32515,11 +32515,11 @@
         </is>
       </c>
       <c r="E1069" s="3" t="n">
-        <v>0.16</v>
+        <v>2.87</v>
       </c>
       <c r="F1069" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32531,12 +32531,12 @@
       </c>
       <c r="B1070" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C1070" s="2" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D1070" s="2" t="inlineStr">
@@ -32545,11 +32545,11 @@
         </is>
       </c>
       <c r="E1070" s="3" t="n">
-        <v>0.16</v>
+        <v>2.84</v>
       </c>
       <c r="F1070" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32561,12 +32561,12 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D1071" s="2" t="inlineStr">
@@ -32575,11 +32575,11 @@
         </is>
       </c>
       <c r="E1071" s="3" t="n">
-        <v>0.13</v>
+        <v>2.75</v>
       </c>
       <c r="F1071" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32591,12 +32591,12 @@
       </c>
       <c r="B1072" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C1072" s="2" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="D1072" s="2" t="inlineStr">
@@ -32605,11 +32605,11 @@
         </is>
       </c>
       <c r="E1072" s="3" t="n">
-        <v>0.13</v>
+        <v>2.68</v>
       </c>
       <c r="F1072" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32621,12 +32621,12 @@
       </c>
       <c r="B1073" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C1073" s="2" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="D1073" s="2" t="inlineStr">
@@ -32635,11 +32635,11 @@
         </is>
       </c>
       <c r="E1073" s="3" t="n">
-        <v>0.12</v>
+        <v>2.65</v>
       </c>
       <c r="F1073" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32651,12 +32651,12 @@
       </c>
       <c r="B1074" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C1074" s="2" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="D1074" s="2" t="inlineStr">
@@ -32665,11 +32665,11 @@
         </is>
       </c>
       <c r="E1074" s="3" t="n">
-        <v>0.11</v>
+        <v>2.49</v>
       </c>
       <c r="F1074" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32681,12 +32681,12 @@
       </c>
       <c r="B1075" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C1075" s="2" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="D1075" s="2" t="inlineStr">
@@ -32695,11 +32695,11 @@
         </is>
       </c>
       <c r="E1075" s="3" t="n">
-        <v>0.11</v>
+        <v>2.48</v>
       </c>
       <c r="F1075" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32711,12 +32711,12 @@
       </c>
       <c r="B1076" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C1076" s="2" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="D1076" s="2" t="inlineStr">
@@ -32725,11 +32725,11 @@
         </is>
       </c>
       <c r="E1076" s="3" t="n">
-        <v>0.1</v>
+        <v>2.42</v>
       </c>
       <c r="F1076" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32741,12 +32741,12 @@
       </c>
       <c r="B1077" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C1077" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="D1077" s="2" t="inlineStr">
@@ -32755,11 +32755,11 @@
         </is>
       </c>
       <c r="E1077" s="3" t="n">
-        <v>0.1</v>
+        <v>2.39</v>
       </c>
       <c r="F1077" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32771,12 +32771,12 @@
       </c>
       <c r="B1078" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C1078" s="2" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="D1078" s="2" t="inlineStr">
@@ -32785,11 +32785,11 @@
         </is>
       </c>
       <c r="E1078" s="3" t="n">
-        <v>0.09</v>
+        <v>2.34</v>
       </c>
       <c r="F1078" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32801,12 +32801,12 @@
       </c>
       <c r="B1079" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C1079" s="2" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="D1079" s="2" t="inlineStr">
@@ -32815,11 +32815,11 @@
         </is>
       </c>
       <c r="E1079" s="3" t="n">
-        <v>0.08</v>
+        <v>2.27</v>
       </c>
       <c r="F1079" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32831,12 +32831,12 @@
       </c>
       <c r="B1080" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C1080" s="2" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="D1080" s="2" t="inlineStr">
@@ -32845,11 +32845,11 @@
         </is>
       </c>
       <c r="E1080" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.21</v>
       </c>
       <c r="F1080" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32861,12 +32861,12 @@
       </c>
       <c r="B1081" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C1081" s="2" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="D1081" s="2" t="inlineStr">
@@ -32875,11 +32875,11 @@
         </is>
       </c>
       <c r="E1081" s="3" t="n">
-        <v>0.06</v>
+        <v>2.17</v>
       </c>
       <c r="F1081" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32891,12 +32891,12 @@
       </c>
       <c r="B1082" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C1082" s="2" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="D1082" s="2" t="inlineStr">
@@ -32905,11 +32905,11 @@
         </is>
       </c>
       <c r="E1082" s="3" t="n">
-        <v>0.06</v>
+        <v>2.16</v>
       </c>
       <c r="F1082" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32921,12 +32921,12 @@
       </c>
       <c r="B1083" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C1083" s="2" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="D1083" s="2" t="inlineStr">
@@ -32935,11 +32935,11 @@
         </is>
       </c>
       <c r="E1083" s="3" t="n">
-        <v>0.05</v>
+        <v>1.87</v>
       </c>
       <c r="F1083" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32951,12 +32951,12 @@
       </c>
       <c r="B1084" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C1084" s="2" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="D1084" s="2" t="inlineStr">
@@ -32965,11 +32965,11 @@
         </is>
       </c>
       <c r="E1084" s="3" t="n">
-        <v>0.05</v>
+        <v>1.8</v>
       </c>
       <c r="F1084" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -32981,12 +32981,12 @@
       </c>
       <c r="B1085" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C1085" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="D1085" s="2" t="inlineStr">
@@ -32995,11 +32995,11 @@
         </is>
       </c>
       <c r="E1085" s="3" t="n">
-        <v>0.05</v>
+        <v>1.66</v>
       </c>
       <c r="F1085" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33011,12 +33011,12 @@
       </c>
       <c r="B1086" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C1086" s="2" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="D1086" s="2" t="inlineStr">
@@ -33025,11 +33025,11 @@
         </is>
       </c>
       <c r="E1086" s="3" t="n">
-        <v>0.05</v>
+        <v>1.62</v>
       </c>
       <c r="F1086" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33041,12 +33041,12 @@
       </c>
       <c r="B1087" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C1087" s="2" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="D1087" s="2" t="inlineStr">
@@ -33055,11 +33055,11 @@
         </is>
       </c>
       <c r="E1087" s="3" t="n">
-        <v>0.04</v>
+        <v>1.59</v>
       </c>
       <c r="F1087" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33071,12 +33071,12 @@
       </c>
       <c r="B1088" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C1088" s="2" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="D1088" s="2" t="inlineStr">
@@ -33085,11 +33085,11 @@
         </is>
       </c>
       <c r="E1088" s="3" t="n">
-        <v>0.03</v>
+        <v>1.52</v>
       </c>
       <c r="F1088" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33101,12 +33101,12 @@
       </c>
       <c r="B1089" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C1089" s="2" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="D1089" s="2" t="inlineStr">
@@ -33115,11 +33115,11 @@
         </is>
       </c>
       <c r="E1089" s="3" t="n">
-        <v>0.03</v>
+        <v>1.51</v>
       </c>
       <c r="F1089" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33131,12 +33131,12 @@
       </c>
       <c r="B1090" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C1090" s="2" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="D1090" s="2" t="inlineStr">
@@ -33145,11 +33145,11 @@
         </is>
       </c>
       <c r="E1090" s="3" t="n">
-        <v>0.02</v>
+        <v>1.5</v>
       </c>
       <c r="F1090" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33161,25 +33161,25 @@
       </c>
       <c r="B1091" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C1091" s="2" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="D1091" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E1091" s="3" t="n">
-        <v>0.02</v>
+        <v>1.31</v>
       </c>
       <c r="F1091" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33191,12 +33191,12 @@
       </c>
       <c r="B1092" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C1092" s="2" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="D1092" s="2" t="inlineStr">
@@ -33205,11 +33205,11 @@
         </is>
       </c>
       <c r="E1092" s="3" t="n">
-        <v>0.01</v>
+        <v>1.25</v>
       </c>
       <c r="F1092" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33221,12 +33221,12 @@
       </c>
       <c r="B1093" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C1093" s="2" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="D1093" s="2" t="inlineStr">
@@ -33235,11 +33235,11 @@
         </is>
       </c>
       <c r="E1093" s="3" t="n">
-        <v>0.01</v>
+        <v>1.17</v>
       </c>
       <c r="F1093" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33251,12 +33251,12 @@
       </c>
       <c r="B1094" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C1094" s="2" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="D1094" s="2" t="inlineStr">
@@ -33265,11 +33265,11 @@
         </is>
       </c>
       <c r="E1094" s="3" t="n">
-        <v>0.01</v>
+        <v>1.15</v>
       </c>
       <c r="F1094" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33281,12 +33281,12 @@
       </c>
       <c r="B1095" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C1095" s="2" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="D1095" s="2" t="inlineStr">
@@ -33295,7 +33295,7 @@
         </is>
       </c>
       <c r="E1095" s="3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="F1095" s="2" t="inlineStr">
         <is>
@@ -33311,12 +33311,12 @@
       </c>
       <c r="B1096" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C1096" s="2" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="D1096" s="2" t="inlineStr">
@@ -33325,11 +33325,11 @@
         </is>
       </c>
       <c r="E1096" s="3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="F1096" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33341,12 +33341,12 @@
       </c>
       <c r="B1097" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866627GHD</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C1097" s="2" t="inlineStr">
         <is>
-          <t>809619</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="D1097" s="2" t="inlineStr">
@@ -33355,11 +33355,11 @@
         </is>
       </c>
       <c r="E1097" s="3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="F1097" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33371,12 +33371,12 @@
       </c>
       <c r="B1098" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C1098" s="2" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="D1098" s="2" t="inlineStr">
@@ -33385,11 +33385,11 @@
         </is>
       </c>
       <c r="E1098" s="3" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="F1098" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33401,12 +33401,12 @@
       </c>
       <c r="B1099" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C1099" s="2" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="D1099" s="2" t="inlineStr">
@@ -33415,11 +33415,11 @@
         </is>
       </c>
       <c r="E1099" s="3" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="F1099" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33431,12 +33431,12 @@
       </c>
       <c r="B1100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C1100" s="2" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="D1100" s="2" t="inlineStr">
@@ -33445,11 +33445,11 @@
         </is>
       </c>
       <c r="E1100" s="3" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F1100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33461,12 +33461,12 @@
       </c>
       <c r="B1101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C1101" s="2" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="D1101" s="2" t="inlineStr">
@@ -33475,11 +33475,11 @@
         </is>
       </c>
       <c r="E1101" s="3" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="F1101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33491,12 +33491,12 @@
       </c>
       <c r="B1102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C1102" s="2" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="D1102" s="2" t="inlineStr">
@@ -33505,11 +33505,11 @@
         </is>
       </c>
       <c r="E1102" s="3" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="F1102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33521,12 +33521,12 @@
       </c>
       <c r="B1103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041546939GJ</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C1103" s="2" t="inlineStr">
         <is>
-          <t>809607</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="D1103" s="2" t="inlineStr">
@@ -33535,11 +33535,11 @@
         </is>
       </c>
       <c r="E1103" s="3" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="F1103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33551,12 +33551,12 @@
       </c>
       <c r="B1104" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C1104" s="2" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="D1104" s="2" t="inlineStr">
@@ -33565,11 +33565,11 @@
         </is>
       </c>
       <c r="E1104" s="3" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="F1104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33581,12 +33581,12 @@
       </c>
       <c r="B1105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C1105" s="2" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="D1105" s="2" t="inlineStr">
@@ -33595,11 +33595,11 @@
         </is>
       </c>
       <c r="E1105" s="3" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="F1105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33611,12 +33611,12 @@
       </c>
       <c r="B1106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04350554X4Z</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C1106" s="2" t="inlineStr">
         <is>
-          <t>809866</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="D1106" s="2" t="inlineStr">
@@ -33625,7 +33625,7 @@
         </is>
       </c>
       <c r="E1106" s="3" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="F1106" s="2" t="inlineStr">
         <is>
@@ -33641,12 +33641,12 @@
       </c>
       <c r="B1107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C1107" s="2" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="D1107" s="2" t="inlineStr">
@@ -33655,11 +33655,11 @@
         </is>
       </c>
       <c r="E1107" s="3" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="F1107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33671,12 +33671,12 @@
       </c>
       <c r="B1108" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C1108" s="2" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="D1108" s="2" t="inlineStr">
@@ -33685,11 +33685,11 @@
         </is>
       </c>
       <c r="E1108" s="3" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="F1108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33701,25 +33701,25 @@
       </c>
       <c r="B1109" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C1109" s="2" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="D1109" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E1109" s="3" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="F1109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33731,12 +33731,12 @@
       </c>
       <c r="B1110" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C1110" s="2" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="D1110" s="2" t="inlineStr">
@@ -33745,11 +33745,11 @@
         </is>
       </c>
       <c r="E1110" s="3" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="F1110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33761,12 +33761,12 @@
       </c>
       <c r="B1111" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604734ZZX</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C1111" s="2" t="inlineStr">
         <is>
-          <t>809876</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D1111" s="2" t="inlineStr">
@@ -33775,11 +33775,11 @@
         </is>
       </c>
       <c r="E1111" s="3" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="F1111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33791,12 +33791,12 @@
       </c>
       <c r="B1112" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C1112" s="2" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="D1112" s="2" t="inlineStr">
@@ -33805,11 +33805,11 @@
         </is>
       </c>
       <c r="E1112" s="3" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="F1112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33821,12 +33821,12 @@
       </c>
       <c r="B1113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="C1113" s="2" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>816274</t>
         </is>
       </c>
       <c r="D1113" s="2" t="inlineStr">
@@ -33835,11 +33835,11 @@
         </is>
       </c>
       <c r="E1113" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="F1113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33851,12 +33851,12 @@
       </c>
       <c r="B1114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C1114" s="2" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="D1114" s="2" t="inlineStr">
@@ -33865,11 +33865,11 @@
         </is>
       </c>
       <c r="E1114" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F1114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33881,12 +33881,12 @@
       </c>
       <c r="B1115" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C1115" s="2" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="D1115" s="2" t="inlineStr">
@@ -33895,11 +33895,11 @@
         </is>
       </c>
       <c r="E1115" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F1115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33911,12 +33911,12 @@
       </c>
       <c r="B1116" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C1116" s="2" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="D1116" s="2" t="inlineStr">
@@ -33925,7 +33925,7 @@
         </is>
       </c>
       <c r="E1116" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F1116" s="2" t="inlineStr">
         <is>
@@ -33941,12 +33941,12 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="D1117" s="2" t="inlineStr">
@@ -33955,11 +33955,11 @@
         </is>
       </c>
       <c r="E1117" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F1117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -33971,12 +33971,12 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="D1118" s="2" t="inlineStr">
@@ -33985,11 +33985,11 @@
         </is>
       </c>
       <c r="E1118" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F1118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -34001,25 +34001,25 @@
       </c>
       <c r="B1119" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C1119" s="2" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="D1119" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E1119" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F1119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -34031,12 +34031,12 @@
       </c>
       <c r="B1120" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604747TPT</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C1120" s="2" t="inlineStr">
         <is>
-          <t>809873</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="D1120" s="2" t="inlineStr">
@@ -34061,12 +34061,12 @@
       </c>
       <c r="B1121" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="C1121" s="2" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>809619</t>
         </is>
       </c>
       <c r="D1121" s="2" t="inlineStr">
@@ -34091,12 +34091,12 @@
       </c>
       <c r="B1122" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C1122" s="2" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="D1122" s="2" t="inlineStr">
@@ -34121,12 +34121,12 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="D1123" s="2" t="inlineStr">
@@ -34151,12 +34151,12 @@
       </c>
       <c r="B1124" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C1124" s="2" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="D1124" s="2" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="B1125" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="C1125" s="2" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>809607</t>
         </is>
       </c>
       <c r="D1125" s="2" t="inlineStr">
@@ -34211,12 +34211,12 @@
       </c>
       <c r="B1126" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C1126" s="2" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="D1126" s="2" t="inlineStr">
@@ -34241,12 +34241,12 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>809866</t>
         </is>
       </c>
       <c r="D1127" s="2" t="inlineStr">
@@ -34271,12 +34271,12 @@
       </c>
       <c r="B1128" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C1128" s="2" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="D1128" s="2" t="inlineStr">
@@ -34301,12 +34301,12 @@
       </c>
       <c r="B1129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C1129" s="2" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="D1129" s="2" t="inlineStr">
@@ -34331,12 +34331,12 @@
       </c>
       <c r="B1130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368340DMZ</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C1130" s="2" t="inlineStr">
         <is>
-          <t>810649</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="D1130" s="2" t="inlineStr">
@@ -34361,12 +34361,12 @@
       </c>
       <c r="B1131" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M04604734ZZX</t>
         </is>
       </c>
       <c r="C1131" s="2" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>809876</t>
         </is>
       </c>
       <c r="D1131" s="2" t="inlineStr">
@@ -34391,12 +34391,12 @@
       </c>
       <c r="B1132" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C1132" s="2" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="D1132" s="2" t="inlineStr">
@@ -34421,12 +34421,12 @@
       </c>
       <c r="B1133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413772977</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C1133" s="2" t="inlineStr">
         <is>
-          <t>812841</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="D1133" s="2" t="inlineStr">
@@ -34451,12 +34451,12 @@
       </c>
       <c r="B1134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413773R6G</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C1134" s="2" t="inlineStr">
         <is>
-          <t>812807</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="D1134" s="2" t="inlineStr">
@@ -34481,12 +34481,12 @@
       </c>
       <c r="B1135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413774JZX</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C1135" s="2" t="inlineStr">
         <is>
-          <t>812836</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="D1135" s="2" t="inlineStr">
@@ -34511,12 +34511,12 @@
       </c>
       <c r="B1136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413775N9M</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C1136" s="2" t="inlineStr">
         <is>
-          <t>812818</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="D1136" s="2" t="inlineStr">
@@ -34541,12 +34541,12 @@
       </c>
       <c r="B1137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C1137" s="2" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="D1137" s="2" t="inlineStr">
@@ -34571,12 +34571,12 @@
       </c>
       <c r="B1138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413778RBR</t>
+          <t>KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="C1138" s="2" t="inlineStr">
         <is>
-          <t>812843</t>
+          <t>809873</t>
         </is>
       </c>
       <c r="D1138" s="2" t="inlineStr">
@@ -34601,12 +34601,12 @@
       </c>
       <c r="B1139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413780XFH</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C1139" s="2" t="inlineStr">
         <is>
-          <t>812833</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="D1139" s="2" t="inlineStr">
@@ -34631,12 +34631,12 @@
       </c>
       <c r="B1140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C1140" s="2" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="D1140" s="2" t="inlineStr">
@@ -34661,12 +34661,12 @@
       </c>
       <c r="B1141" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C1141" s="2" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D1141" s="2" t="inlineStr">
@@ -34691,12 +34691,12 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="D1142" s="2" t="inlineStr">
@@ -34721,12 +34721,12 @@
       </c>
       <c r="B1143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C1143" s="2" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="D1143" s="2" t="inlineStr">
@@ -34751,12 +34751,12 @@
       </c>
       <c r="B1144" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C1144" s="2" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="D1144" s="2" t="inlineStr">
@@ -34781,12 +34781,12 @@
       </c>
       <c r="B1145" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413790XCD</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C1145" s="2" t="inlineStr">
         <is>
-          <t>812822</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="D1145" s="2" t="inlineStr">
@@ -34811,12 +34811,12 @@
       </c>
       <c r="B1146" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413791FK5</t>
+          <t>KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="C1146" s="2" t="inlineStr">
         <is>
-          <t>812842</t>
+          <t>810649</t>
         </is>
       </c>
       <c r="D1146" s="2" t="inlineStr">
@@ -34841,12 +34841,12 @@
       </c>
       <c r="B1147" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="C1147" s="2" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="D1147" s="2" t="inlineStr">
@@ -34871,12 +34871,12 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137938P7</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="D1148" s="2" t="inlineStr">
@@ -34901,12 +34901,12 @@
       </c>
       <c r="B1149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M05413772977</t>
         </is>
       </c>
       <c r="C1149" s="2" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>812841</t>
         </is>
       </c>
       <c r="D1149" s="2" t="inlineStr">
@@ -34931,12 +34931,12 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>812807</t>
         </is>
       </c>
       <c r="D1150" s="2" t="inlineStr">
@@ -34961,12 +34961,12 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>812836</t>
         </is>
       </c>
       <c r="D1151" s="2" t="inlineStr">
@@ -34991,12 +34991,12 @@
       </c>
       <c r="B1152" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413801QJB</t>
+          <t>KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="C1152" s="2" t="inlineStr">
         <is>
-          <t>812824</t>
+          <t>812818</t>
         </is>
       </c>
       <c r="D1152" s="2" t="inlineStr">
@@ -35021,12 +35021,12 @@
       </c>
       <c r="B1153" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C1153" s="2" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="D1153" s="2" t="inlineStr">
@@ -35051,12 +35051,12 @@
       </c>
       <c r="B1154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="C1154" s="2" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>812843</t>
         </is>
       </c>
       <c r="D1154" s="2" t="inlineStr">
@@ -35081,12 +35081,12 @@
       </c>
       <c r="B1155" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413809J58</t>
+          <t>KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="C1155" s="2" t="inlineStr">
         <is>
-          <t>812805</t>
+          <t>812833</t>
         </is>
       </c>
       <c r="D1155" s="2" t="inlineStr">
@@ -35111,12 +35111,12 @@
       </c>
       <c r="B1156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C1156" s="2" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="D1156" s="2" t="inlineStr">
@@ -35141,12 +35141,12 @@
       </c>
       <c r="B1157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413813HSJ</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C1157" s="2" t="inlineStr">
         <is>
-          <t>812797</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="D1157" s="2" t="inlineStr">
@@ -35171,12 +35171,12 @@
       </c>
       <c r="B1158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C1158" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="D1158" s="2" t="inlineStr">
@@ -35201,12 +35201,12 @@
       </c>
       <c r="B1159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0541381584X</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C1159" s="2" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="D1159" s="2" t="inlineStr">
@@ -35231,12 +35231,12 @@
       </c>
       <c r="B1160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="C1160" s="2" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="D1160" s="2" t="inlineStr">
@@ -35261,12 +35261,12 @@
       </c>
       <c r="B1161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4M05413791FK5</t>
         </is>
       </c>
       <c r="C1161" s="2" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>812842</t>
         </is>
       </c>
       <c r="D1161" s="2" t="inlineStr">
@@ -35291,12 +35291,12 @@
       </c>
       <c r="B1162" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C1162" s="2" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="D1162" s="2" t="inlineStr">
@@ -35321,12 +35321,12 @@
       </c>
       <c r="B1163" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M054137938P7</t>
         </is>
       </c>
       <c r="C1163" s="2" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>812848</t>
         </is>
       </c>
       <c r="D1163" s="2" t="inlineStr">
@@ -35351,12 +35351,12 @@
       </c>
       <c r="B1164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413821GGW</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C1164" s="2" t="inlineStr">
         <is>
-          <t>812830</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="D1164" s="2" t="inlineStr">
@@ -35381,12 +35381,12 @@
       </c>
       <c r="B1165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C1165" s="2" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="D1165" s="2" t="inlineStr">
@@ -35411,12 +35411,12 @@
       </c>
       <c r="B1166" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C1166" s="2" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="D1166" s="2" t="inlineStr">
@@ -35441,12 +35441,12 @@
       </c>
       <c r="B1167" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C1167" s="2" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>812813</t>
         </is>
       </c>
       <c r="D1167" s="2" t="inlineStr">
@@ -35471,12 +35471,12 @@
       </c>
       <c r="B1168" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C1168" s="2" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="D1168" s="2" t="inlineStr">
@@ -35501,12 +35501,12 @@
       </c>
       <c r="B1169" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M05413809J58</t>
         </is>
       </c>
       <c r="C1169" s="2" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>812805</t>
         </is>
       </c>
       <c r="D1169" s="2" t="inlineStr">
@@ -35531,12 +35531,12 @@
       </c>
       <c r="B1170" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C1170" s="2" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="D1170" s="2" t="inlineStr">
@@ -35561,12 +35561,12 @@
       </c>
       <c r="B1171" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138292ZP</t>
+          <t>KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="C1171" s="2" t="inlineStr">
         <is>
-          <t>812784</t>
+          <t>812797</t>
         </is>
       </c>
       <c r="D1171" s="2" t="inlineStr">
@@ -35591,12 +35591,12 @@
       </c>
       <c r="B1172" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413830JN7</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C1172" s="2" t="inlineStr">
         <is>
-          <t>810105</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="D1172" s="2" t="inlineStr">
@@ -35621,12 +35621,12 @@
       </c>
       <c r="B1173" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M0541381584X</t>
         </is>
       </c>
       <c r="C1173" s="2" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>812810</t>
         </is>
       </c>
       <c r="D1173" s="2" t="inlineStr">
@@ -35651,12 +35651,12 @@
       </c>
       <c r="B1174" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C1174" s="2" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="D1174" s="2" t="inlineStr">
@@ -35681,12 +35681,12 @@
       </c>
       <c r="B1175" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C1175" s="2" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="D1175" s="2" t="inlineStr">
@@ -35711,12 +35711,12 @@
       </c>
       <c r="B1176" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C1176" s="2" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="D1176" s="2" t="inlineStr">
@@ -35741,12 +35741,12 @@
       </c>
       <c r="B1177" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C1177" s="2" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="D1177" s="2" t="inlineStr">
@@ -35771,12 +35771,12 @@
       </c>
       <c r="B1178" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563503XXP</t>
+          <t>KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="C1178" s="2" t="inlineStr">
         <is>
-          <t>814430</t>
+          <t>812830</t>
         </is>
       </c>
       <c r="D1178" s="2" t="inlineStr">
@@ -35801,12 +35801,12 @@
       </c>
       <c r="B1179" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563505WPS</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C1179" s="2" t="inlineStr">
         <is>
-          <t>814448</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="D1179" s="2" t="inlineStr">
@@ -35831,12 +35831,12 @@
       </c>
       <c r="B1180" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C1180" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="D1180" s="2" t="inlineStr">
@@ -35861,12 +35861,12 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563510TWC</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
         <is>
-          <t>814433</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="D1181" s="2" t="inlineStr">
@@ -35891,12 +35891,12 @@
       </c>
       <c r="B1182" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C1182" s="2" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="D1182" s="2" t="inlineStr">
@@ -35921,12 +35921,12 @@
       </c>
       <c r="B1183" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C1183" s="2" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="D1183" s="2" t="inlineStr">
@@ -35951,12 +35951,12 @@
       </c>
       <c r="B1184" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563517BVR</t>
+          <t>KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="C1184" s="2" t="inlineStr">
         <is>
-          <t>814438</t>
+          <t>812784</t>
         </is>
       </c>
       <c r="D1184" s="2" t="inlineStr">
@@ -35981,12 +35981,12 @@
       </c>
       <c r="B1185" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="C1185" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>810105</t>
         </is>
       </c>
       <c r="D1185" s="2" t="inlineStr">
@@ -36011,12 +36011,12 @@
       </c>
       <c r="B1186" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C1186" s="2" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="D1186" s="2" t="inlineStr">
@@ -36041,12 +36041,12 @@
       </c>
       <c r="B1187" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C1187" s="2" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="D1187" s="2" t="inlineStr">
@@ -36071,12 +36071,12 @@
       </c>
       <c r="B1188" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="C1188" s="2" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="D1188" s="2" t="inlineStr">
@@ -36101,12 +36101,12 @@
       </c>
       <c r="B1189" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C1189" s="2" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="D1189" s="2" t="inlineStr">
@@ -36131,12 +36131,12 @@
       </c>
       <c r="B1190" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C1190" s="2" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="D1190" s="2" t="inlineStr">
@@ -36161,12 +36161,12 @@
       </c>
       <c r="B1191" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="C1191" s="2" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>814430</t>
         </is>
       </c>
       <c r="D1191" s="2" t="inlineStr">
@@ -36191,12 +36191,12 @@
       </c>
       <c r="B1192" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="C1192" s="2" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>814448</t>
         </is>
       </c>
       <c r="D1192" s="2" t="inlineStr">
@@ -36221,12 +36221,12 @@
       </c>
       <c r="B1193" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563536BPJ</t>
+          <t>KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="C1193" s="2" t="inlineStr">
         <is>
-          <t>814466</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="D1193" s="2" t="inlineStr">
@@ -36251,12 +36251,12 @@
       </c>
       <c r="B1194" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C1194" s="2" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="D1194" s="2" t="inlineStr">
@@ -36281,12 +36281,12 @@
       </c>
       <c r="B1195" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C1195" s="2" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="D1195" s="2" t="inlineStr">
@@ -36311,12 +36311,12 @@
       </c>
       <c r="B1196" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563549RSR</t>
+          <t>KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="C1196" s="2" t="inlineStr">
         <is>
-          <t>814483</t>
+          <t>814438</t>
         </is>
       </c>
       <c r="D1196" s="2" t="inlineStr">
@@ -36341,12 +36341,12 @@
       </c>
       <c r="B1197" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563554WCW</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C1197" s="2" t="inlineStr">
         <is>
-          <t>814444</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D1197" s="2" t="inlineStr">
@@ -36371,12 +36371,12 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556355588P</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
         <is>
-          <t>814455</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="D1198" s="2" t="inlineStr">
@@ -36401,12 +36401,12 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="D1199" s="2" t="inlineStr">
@@ -36431,12 +36431,12 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="D1200" s="2" t="inlineStr">
@@ -36461,12 +36461,12 @@
       </c>
       <c r="B1201" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C1201" s="2" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="D1201" s="2" t="inlineStr">
@@ -36491,12 +36491,12 @@
       </c>
       <c r="B1202" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="C1202" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>814466</t>
         </is>
       </c>
       <c r="D1202" s="2" t="inlineStr">
@@ -36521,12 +36521,12 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="D1203" s="2" t="inlineStr">
@@ -36551,12 +36551,12 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>814483</t>
         </is>
       </c>
       <c r="D1204" s="2" t="inlineStr">
@@ -36581,12 +36581,12 @@
       </c>
       <c r="B1205" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="C1205" s="2" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>814444</t>
         </is>
       </c>
       <c r="D1205" s="2" t="inlineStr">
@@ -36611,12 +36611,12 @@
       </c>
       <c r="B1206" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M0556355588P</t>
         </is>
       </c>
       <c r="C1206" s="2" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>814455</t>
         </is>
       </c>
       <c r="D1206" s="2" t="inlineStr">
@@ -36641,12 +36641,12 @@
       </c>
       <c r="B1207" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563610HM2</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C1207" s="2" t="inlineStr">
         <is>
-          <t>814486</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D1207" s="2" t="inlineStr">
@@ -36671,12 +36671,12 @@
       </c>
       <c r="B1208" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996395ZF</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C1208" s="2" t="inlineStr">
         <is>
-          <t>816268</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="D1208" s="2" t="inlineStr">
@@ -36701,12 +36701,12 @@
       </c>
       <c r="B1209" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C1209" s="2" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="D1209" s="2" t="inlineStr">
@@ -36731,12 +36731,12 @@
       </c>
       <c r="B1210" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C1210" s="2" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D1210" s="2" t="inlineStr">
@@ -36761,12 +36761,12 @@
       </c>
       <c r="B1211" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799709G5Q</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C1211" s="2" t="inlineStr">
         <is>
-          <t>816274</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="D1211" s="2" t="inlineStr">
@@ -36791,12 +36791,12 @@
       </c>
       <c r="B1212" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C1212" s="2" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D1212" s="2" t="inlineStr">
@@ -36821,12 +36821,12 @@
       </c>
       <c r="B1213" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C1213" s="2" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="D1213" s="2" t="inlineStr">
@@ -36851,12 +36851,12 @@
       </c>
       <c r="B1214" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="C1214" s="2" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>814486</t>
         </is>
       </c>
       <c r="D1214" s="2" t="inlineStr">
@@ -36881,12 +36881,12 @@
       </c>
       <c r="B1215" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872496MW6</t>
+          <t>KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="C1215" s="2" t="inlineStr">
         <is>
-          <t>816206</t>
+          <t>816268</t>
         </is>
       </c>
       <c r="D1215" s="2" t="inlineStr">
@@ -36911,12 +36911,12 @@
       </c>
       <c r="B1216" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C1216" s="2" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="D1216" s="2" t="inlineStr">
@@ -36941,12 +36941,12 @@
       </c>
       <c r="B1217" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872498PP4</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C1217" s="2" t="inlineStr">
         <is>
-          <t>816104</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="D1217" s="2" t="inlineStr">
@@ -36971,12 +36971,12 @@
       </c>
       <c r="B1218" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C1218" s="2" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="D1218" s="2" t="inlineStr">
@@ -37001,12 +37001,12 @@
       </c>
       <c r="B1219" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C1219" s="2" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="D1219" s="2" t="inlineStr">
@@ -37031,12 +37031,12 @@
       </c>
       <c r="B1220" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872506TTB</t>
+          <t>KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="C1220" s="2" t="inlineStr">
         <is>
-          <t>816082</t>
+          <t>816206</t>
         </is>
       </c>
       <c r="D1220" s="2" t="inlineStr">
@@ -37061,12 +37061,12 @@
       </c>
       <c r="B1221" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725108K2</t>
+          <t>KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="C1221" s="2" t="inlineStr">
         <is>
-          <t>816287</t>
+          <t>816104</t>
         </is>
       </c>
       <c r="D1221" s="2" t="inlineStr">
@@ -37091,12 +37091,12 @@
       </c>
       <c r="B1222" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="C1222" s="2" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="D1222" s="2" t="inlineStr">
@@ -37121,12 +37121,12 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872513F7N</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
         <is>
-          <t>816161</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="D1223" s="2" t="inlineStr">
@@ -37151,12 +37151,12 @@
       </c>
       <c r="B1224" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872515PJT</t>
+          <t>KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="C1224" s="2" t="inlineStr">
         <is>
-          <t>816218</t>
+          <t>816082</t>
         </is>
       </c>
       <c r="D1224" s="2" t="inlineStr">
@@ -37181,12 +37181,12 @@
       </c>
       <c r="B1225" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M058725108K2</t>
         </is>
       </c>
       <c r="C1225" s="2" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>816287</t>
         </is>
       </c>
       <c r="D1225" s="2" t="inlineStr">
@@ -37211,12 +37211,12 @@
       </c>
       <c r="B1226" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872518P78</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C1226" s="2" t="inlineStr">
         <is>
-          <t>816184</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="D1226" s="2" t="inlineStr">
@@ -37241,12 +37241,12 @@
       </c>
       <c r="B1227" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="C1227" s="2" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>816161</t>
         </is>
       </c>
       <c r="D1227" s="2" t="inlineStr">
@@ -37271,12 +37271,12 @@
       </c>
       <c r="B1228" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="C1228" s="2" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>816218</t>
         </is>
       </c>
       <c r="D1228" s="2" t="inlineStr">
@@ -37301,12 +37301,12 @@
       </c>
       <c r="B1229" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872522W7W</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C1229" s="2" t="inlineStr">
         <is>
-          <t>816217</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="D1229" s="2" t="inlineStr">
@@ -37331,12 +37331,12 @@
       </c>
       <c r="B1230" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872523VVB</t>
+          <t>KIT4M05872518P78</t>
         </is>
       </c>
       <c r="C1230" s="2" t="inlineStr">
         <is>
-          <t>816215</t>
+          <t>816184</t>
         </is>
       </c>
       <c r="D1230" s="2" t="inlineStr">
@@ -37361,12 +37361,12 @@
       </c>
       <c r="B1231" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872524CFG</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C1231" s="2" t="inlineStr">
         <is>
-          <t>816205</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="D1231" s="2" t="inlineStr">
@@ -37391,12 +37391,12 @@
       </c>
       <c r="B1232" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872525NP5</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C1232" s="2" t="inlineStr">
         <is>
-          <t>816213</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="D1232" s="2" t="inlineStr">
@@ -37421,12 +37421,12 @@
       </c>
       <c r="B1233" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872527QK6</t>
+          <t>KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="C1233" s="2" t="inlineStr">
         <is>
-          <t>816214</t>
+          <t>816217</t>
         </is>
       </c>
       <c r="D1233" s="2" t="inlineStr">
@@ -37451,12 +37451,12 @@
       </c>
       <c r="B1234" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872531DSZ</t>
+          <t>KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="C1234" s="2" t="inlineStr">
         <is>
-          <t>816171</t>
+          <t>816215</t>
         </is>
       </c>
       <c r="D1234" s="2" t="inlineStr">
@@ -37481,12 +37481,12 @@
       </c>
       <c r="B1235" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587253378R</t>
+          <t>KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="C1235" s="2" t="inlineStr">
         <is>
-          <t>816210</t>
+          <t>816205</t>
         </is>
       </c>
       <c r="D1235" s="2" t="inlineStr">
@@ -37511,12 +37511,12 @@
       </c>
       <c r="B1236" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872534RXS</t>
+          <t>KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="C1236" s="2" t="inlineStr">
         <is>
-          <t>816216</t>
+          <t>816213</t>
         </is>
       </c>
       <c r="D1236" s="2" t="inlineStr">
@@ -37541,12 +37541,12 @@
       </c>
       <c r="B1237" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M05872527QK6</t>
         </is>
       </c>
       <c r="C1237" s="2" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>816214</t>
         </is>
       </c>
       <c r="D1237" s="2" t="inlineStr">
@@ -37571,12 +37571,12 @@
       </c>
       <c r="B1238" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872539ZMR</t>
+          <t>KIT4M05872531DSZ</t>
         </is>
       </c>
       <c r="C1238" s="2" t="inlineStr">
         <is>
-          <t>816108</t>
+          <t>816171</t>
         </is>
       </c>
       <c r="D1238" s="2" t="inlineStr">
@@ -37601,12 +37601,12 @@
       </c>
       <c r="B1239" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725438WP</t>
+          <t>KIT4M0587253378R</t>
         </is>
       </c>
       <c r="C1239" s="2" t="inlineStr">
         <is>
-          <t>816115</t>
+          <t>816210</t>
         </is>
       </c>
       <c r="D1239" s="2" t="inlineStr">
@@ -37631,12 +37631,12 @@
       </c>
       <c r="B1240" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872544BXG</t>
+          <t>KIT4M05872534RXS</t>
         </is>
       </c>
       <c r="C1240" s="2" t="inlineStr">
         <is>
-          <t>816176</t>
+          <t>816216</t>
         </is>
       </c>
       <c r="D1240" s="2" t="inlineStr">
@@ -37661,12 +37661,12 @@
       </c>
       <c r="B1241" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872545Q8H</t>
+          <t>KIT4M05872539ZMR</t>
         </is>
       </c>
       <c r="C1241" s="2" t="inlineStr">
         <is>
-          <t>816112</t>
+          <t>816108</t>
         </is>
       </c>
       <c r="D1241" s="2" t="inlineStr">
@@ -37691,12 +37691,12 @@
       </c>
       <c r="B1242" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872547MK2</t>
+          <t>KIT4M058725438WP</t>
         </is>
       </c>
       <c r="C1242" s="2" t="inlineStr">
         <is>
-          <t>816209</t>
+          <t>816115</t>
         </is>
       </c>
       <c r="D1242" s="2" t="inlineStr">
@@ -37721,12 +37721,12 @@
       </c>
       <c r="B1243" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872548P2H</t>
+          <t>KIT4M05872544BXG</t>
         </is>
       </c>
       <c r="C1243" s="2" t="inlineStr">
         <is>
-          <t>816066</t>
+          <t>816176</t>
         </is>
       </c>
       <c r="D1243" s="2" t="inlineStr">
@@ -37751,12 +37751,12 @@
       </c>
       <c r="B1244" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725505J5</t>
+          <t>KIT4M05872545Q8H</t>
         </is>
       </c>
       <c r="C1244" s="2" t="inlineStr">
         <is>
-          <t>816117</t>
+          <t>816112</t>
         </is>
       </c>
       <c r="D1244" s="2" t="inlineStr">
@@ -37781,12 +37781,12 @@
       </c>
       <c r="B1245" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872551G9S</t>
+          <t>KIT4M05872547MK2</t>
         </is>
       </c>
       <c r="C1245" s="2" t="inlineStr">
         <is>
-          <t>816180</t>
+          <t>816209</t>
         </is>
       </c>
       <c r="D1245" s="2" t="inlineStr">
@@ -37811,12 +37811,12 @@
       </c>
       <c r="B1246" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872553WFR</t>
+          <t>KIT4M05872548P2H</t>
         </is>
       </c>
       <c r="C1246" s="2" t="inlineStr">
         <is>
-          <t>816116</t>
+          <t>816066</t>
         </is>
       </c>
       <c r="D1246" s="2" t="inlineStr">
@@ -37841,12 +37841,12 @@
       </c>
       <c r="B1247" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872554RHM</t>
+          <t>KIT4M058725505J5</t>
         </is>
       </c>
       <c r="C1247" s="2" t="inlineStr">
         <is>
-          <t>816071</t>
+          <t>816117</t>
         </is>
       </c>
       <c r="D1247" s="2" t="inlineStr">
@@ -37871,12 +37871,12 @@
       </c>
       <c r="B1248" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M05872551G9S</t>
         </is>
       </c>
       <c r="C1248" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>816180</t>
         </is>
       </c>
       <c r="D1248" s="2" t="inlineStr">
@@ -37901,12 +37901,12 @@
       </c>
       <c r="B1249" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872556RC9</t>
+          <t>KIT4M05872553WFR</t>
         </is>
       </c>
       <c r="C1249" s="2" t="inlineStr">
         <is>
-          <t>816118</t>
+          <t>816116</t>
         </is>
       </c>
       <c r="D1249" s="2" t="inlineStr">
@@ -37931,12 +37931,12 @@
       </c>
       <c r="B1250" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872557NFB</t>
+          <t>KIT4M05872554RHM</t>
         </is>
       </c>
       <c r="C1250" s="2" t="inlineStr">
         <is>
-          <t>816095</t>
+          <t>816071</t>
         </is>
       </c>
       <c r="D1250" s="2" t="inlineStr">
@@ -37961,12 +37961,12 @@
       </c>
       <c r="B1251" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872559VR9</t>
+          <t>KIT4M05872556RC9</t>
         </is>
       </c>
       <c r="C1251" s="2" t="inlineStr">
         <is>
-          <t>816114</t>
+          <t>816118</t>
         </is>
       </c>
       <c r="D1251" s="2" t="inlineStr">
@@ -37991,12 +37991,12 @@
       </c>
       <c r="B1252" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256196K</t>
+          <t>KIT4M05872557NFB</t>
         </is>
       </c>
       <c r="C1252" s="2" t="inlineStr">
         <is>
-          <t>816098</t>
+          <t>816095</t>
         </is>
       </c>
       <c r="D1252" s="2" t="inlineStr">
@@ -38021,12 +38021,12 @@
       </c>
       <c r="B1253" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872563FWB</t>
+          <t>KIT4M05872559VR9</t>
         </is>
       </c>
       <c r="C1253" s="2" t="inlineStr">
         <is>
-          <t>816208</t>
+          <t>816114</t>
         </is>
       </c>
       <c r="D1253" s="2" t="inlineStr">
@@ -38051,12 +38051,12 @@
       </c>
       <c r="B1254" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872564MCF</t>
+          <t>KIT4M0587256196K</t>
         </is>
       </c>
       <c r="C1254" s="2" t="inlineStr">
         <is>
-          <t>816203</t>
+          <t>816098</t>
         </is>
       </c>
       <c r="D1254" s="2" t="inlineStr">
@@ -38081,12 +38081,12 @@
       </c>
       <c r="B1255" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872565VJK</t>
+          <t>KIT4M05872563FWB</t>
         </is>
       </c>
       <c r="C1255" s="2" t="inlineStr">
         <is>
-          <t>816109</t>
+          <t>816208</t>
         </is>
       </c>
       <c r="D1255" s="2" t="inlineStr">
@@ -38111,12 +38111,12 @@
       </c>
       <c r="B1256" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587256692N</t>
+          <t>KIT4M05872564MCF</t>
         </is>
       </c>
       <c r="C1256" s="2" t="inlineStr">
         <is>
-          <t>816072</t>
+          <t>816203</t>
         </is>
       </c>
       <c r="D1256" s="2" t="inlineStr">
@@ -38141,12 +38141,12 @@
       </c>
       <c r="B1257" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872567V72</t>
+          <t>KIT4M05872565VJK</t>
         </is>
       </c>
       <c r="C1257" s="2" t="inlineStr">
         <is>
-          <t>816099</t>
+          <t>816109</t>
         </is>
       </c>
       <c r="D1257" s="2" t="inlineStr">
@@ -38171,12 +38171,12 @@
       </c>
       <c r="B1258" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872568PR6</t>
+          <t>KIT4M0587256692N</t>
         </is>
       </c>
       <c r="C1258" s="2" t="inlineStr">
         <is>
-          <t>816094</t>
+          <t>816072</t>
         </is>
       </c>
       <c r="D1258" s="2" t="inlineStr">
@@ -38201,12 +38201,12 @@
       </c>
       <c r="B1259" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725695CN</t>
+          <t>KIT4M05872567V72</t>
         </is>
       </c>
       <c r="C1259" s="2" t="inlineStr">
         <is>
-          <t>816101</t>
+          <t>816099</t>
         </is>
       </c>
       <c r="D1259" s="2" t="inlineStr">
@@ -38231,12 +38231,12 @@
       </c>
       <c r="B1260" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872570FCC</t>
+          <t>KIT4M05872568PR6</t>
         </is>
       </c>
       <c r="C1260" s="2" t="inlineStr">
         <is>
-          <t>816105</t>
+          <t>816094</t>
         </is>
       </c>
       <c r="D1260" s="2" t="inlineStr">
@@ -38261,12 +38261,12 @@
       </c>
       <c r="B1261" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872571T4K</t>
+          <t>KIT4M058725695CN</t>
         </is>
       </c>
       <c r="C1261" s="2" t="inlineStr">
         <is>
-          <t>816106</t>
+          <t>816101</t>
         </is>
       </c>
       <c r="D1261" s="2" t="inlineStr">
@@ -38291,12 +38291,12 @@
       </c>
       <c r="B1262" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587257292W</t>
+          <t>KIT4M05872570FCC</t>
         </is>
       </c>
       <c r="C1262" s="2" t="inlineStr">
         <is>
-          <t>816207</t>
+          <t>816105</t>
         </is>
       </c>
       <c r="D1262" s="2" t="inlineStr">
@@ -38321,12 +38321,12 @@
       </c>
       <c r="B1263" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872573K7P</t>
+          <t>KIT4M05872571T4K</t>
         </is>
       </c>
       <c r="C1263" s="2" t="inlineStr">
         <is>
-          <t>816067</t>
+          <t>816106</t>
         </is>
       </c>
       <c r="D1263" s="2" t="inlineStr">
@@ -38351,12 +38351,12 @@
       </c>
       <c r="B1264" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872574NKX</t>
+          <t>KIT4M0587257292W</t>
         </is>
       </c>
       <c r="C1264" s="2" t="inlineStr">
         <is>
-          <t>816113</t>
+          <t>816207</t>
         </is>
       </c>
       <c r="D1264" s="2" t="inlineStr">
@@ -38381,12 +38381,12 @@
       </c>
       <c r="B1265" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872575BC8</t>
+          <t>KIT4M05872573K7P</t>
         </is>
       </c>
       <c r="C1265" s="2" t="inlineStr">
         <is>
-          <t>816103</t>
+          <t>816067</t>
         </is>
       </c>
       <c r="D1265" s="2" t="inlineStr">
@@ -38411,12 +38411,12 @@
       </c>
       <c r="B1266" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872576R4B</t>
+          <t>KIT4M05872574NKX</t>
         </is>
       </c>
       <c r="C1266" s="2" t="inlineStr">
         <is>
-          <t>816110</t>
+          <t>816113</t>
         </is>
       </c>
       <c r="D1266" s="2" t="inlineStr">
@@ -38441,12 +38441,12 @@
       </c>
       <c r="B1267" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872577TWT</t>
+          <t>KIT4M05872575BC8</t>
         </is>
       </c>
       <c r="C1267" s="2" t="inlineStr">
         <is>
-          <t>816212</t>
+          <t>816103</t>
         </is>
       </c>
       <c r="D1267" s="2" t="inlineStr">
@@ -38471,12 +38471,12 @@
       </c>
       <c r="B1268" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872578G7Q</t>
+          <t>KIT4M05872576R4B</t>
         </is>
       </c>
       <c r="C1268" s="2" t="inlineStr">
         <is>
-          <t>816102</t>
+          <t>816110</t>
         </is>
       </c>
       <c r="D1268" s="2" t="inlineStr">
@@ -38501,12 +38501,12 @@
       </c>
       <c r="B1269" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872579JPF</t>
+          <t>KIT4M05872577TWT</t>
         </is>
       </c>
       <c r="C1269" s="2" t="inlineStr">
         <is>
-          <t>816111</t>
+          <t>816212</t>
         </is>
       </c>
       <c r="D1269" s="2" t="inlineStr">
@@ -38531,12 +38531,12 @@
       </c>
       <c r="B1270" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872580C6X</t>
+          <t>KIT4M05872578G7Q</t>
         </is>
       </c>
       <c r="C1270" s="2" t="inlineStr">
         <is>
-          <t>816097</t>
+          <t>816102</t>
         </is>
       </c>
       <c r="D1270" s="2" t="inlineStr">
@@ -38561,12 +38561,12 @@
       </c>
       <c r="B1271" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872582TC7</t>
+          <t>KIT4M05872579JPF</t>
         </is>
       </c>
       <c r="C1271" s="2" t="inlineStr">
         <is>
-          <t>816107</t>
+          <t>816111</t>
         </is>
       </c>
       <c r="D1271" s="2" t="inlineStr">
@@ -38591,12 +38591,12 @@
       </c>
       <c r="B1272" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872584M6H</t>
+          <t>KIT4M05872580C6X</t>
         </is>
       </c>
       <c r="C1272" s="2" t="inlineStr">
         <is>
-          <t>816096</t>
+          <t>816097</t>
         </is>
       </c>
       <c r="D1272" s="2" t="inlineStr">
@@ -38621,12 +38621,12 @@
       </c>
       <c r="B1273" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872585HZZ</t>
+          <t>KIT4M05872582TC7</t>
         </is>
       </c>
       <c r="C1273" s="2" t="inlineStr">
         <is>
-          <t>816211</t>
+          <t>816107</t>
         </is>
       </c>
       <c r="D1273" s="2" t="inlineStr">
@@ -38651,12 +38651,12 @@
       </c>
       <c r="B1274" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M05872584M6H</t>
         </is>
       </c>
       <c r="C1274" s="2" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>816096</t>
         </is>
       </c>
       <c r="D1274" s="2" t="inlineStr">
@@ -38681,12 +38681,12 @@
       </c>
       <c r="B1275" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872588W8G</t>
+          <t>KIT4M05872585HZZ</t>
         </is>
       </c>
       <c r="C1275" s="2" t="inlineStr">
         <is>
-          <t>816100</t>
+          <t>816211</t>
         </is>
       </c>
       <c r="D1275" s="2" t="inlineStr">
@@ -38711,12 +38711,12 @@
       </c>
       <c r="B1276" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872589TM9</t>
+          <t>KIT4M05872588W8G</t>
         </is>
       </c>
       <c r="C1276" s="2" t="inlineStr">
         <is>
-          <t>816195</t>
+          <t>816100</t>
         </is>
       </c>
       <c r="D1276" s="2" t="inlineStr">
@@ -38741,12 +38741,12 @@
       </c>
       <c r="B1277" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872590N8X</t>
+          <t>KIT4M05872589TM9</t>
         </is>
       </c>
       <c r="C1277" s="2" t="inlineStr">
         <is>
-          <t>816204</t>
+          <t>816195</t>
         </is>
       </c>
       <c r="D1277" s="2" t="inlineStr">
@@ -38771,12 +38771,12 @@
       </c>
       <c r="B1278" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490319DDN</t>
+          <t>KIT4M05872590N8X</t>
         </is>
       </c>
       <c r="C1278" s="2" t="inlineStr">
         <is>
-          <t>816220</t>
+          <t>816204</t>
         </is>
       </c>
       <c r="D1278" s="2" t="inlineStr">
@@ -38801,12 +38801,12 @@
       </c>
       <c r="B1279" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490321NJX</t>
+          <t>KIT4M06490319DDN</t>
         </is>
       </c>
       <c r="C1279" s="2" t="inlineStr">
         <is>
-          <t>816219</t>
+          <t>816220</t>
         </is>
       </c>
       <c r="D1279" s="2" t="inlineStr">
@@ -38831,12 +38831,12 @@
       </c>
       <c r="B1280" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06490327GMP</t>
+          <t>KIT4M06490321NJX</t>
         </is>
       </c>
       <c r="C1280" s="2" t="inlineStr">
         <is>
-          <t>816199</t>
+          <t>816219</t>
         </is>
       </c>
       <c r="D1280" s="2" t="inlineStr">
@@ -38861,12 +38861,12 @@
       </c>
       <c r="B1281" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491786BS9</t>
+          <t>KIT4M06490327GMP</t>
         </is>
       </c>
       <c r="C1281" s="2" t="inlineStr">
         <is>
-          <t>816396</t>
+          <t>816199</t>
         </is>
       </c>
       <c r="D1281" s="2" t="inlineStr">
@@ -38891,12 +38891,12 @@
       </c>
       <c r="B1282" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491789PJ6</t>
+          <t>KIT4M06491786BS9</t>
         </is>
       </c>
       <c r="C1282" s="2" t="inlineStr">
         <is>
-          <t>816407</t>
+          <t>816396</t>
         </is>
       </c>
       <c r="D1282" s="2" t="inlineStr">
@@ -38921,12 +38921,12 @@
       </c>
       <c r="B1283" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491790945</t>
+          <t>KIT4M06491789PJ6</t>
         </is>
       </c>
       <c r="C1283" s="2" t="inlineStr">
         <is>
-          <t>816410</t>
+          <t>816407</t>
         </is>
       </c>
       <c r="D1283" s="2" t="inlineStr">
@@ -38951,12 +38951,12 @@
       </c>
       <c r="B1284" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917914G5</t>
+          <t>KIT4M06491790945</t>
         </is>
       </c>
       <c r="C1284" s="2" t="inlineStr">
         <is>
-          <t>816392</t>
+          <t>816410</t>
         </is>
       </c>
       <c r="D1284" s="2" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="B1285" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917925MB</t>
+          <t>KIT4M064917914G5</t>
         </is>
       </c>
       <c r="C1285" s="2" t="inlineStr">
         <is>
-          <t>816381</t>
+          <t>816392</t>
         </is>
       </c>
       <c r="D1285" s="2" t="inlineStr">
@@ -39011,12 +39011,12 @@
       </c>
       <c r="B1286" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064917936NF</t>
+          <t>KIT4M064917925MB</t>
         </is>
       </c>
       <c r="C1286" s="2" t="inlineStr">
         <is>
-          <t>816404</t>
+          <t>816381</t>
         </is>
       </c>
       <c r="D1286" s="2" t="inlineStr">
@@ -39041,12 +39041,12 @@
       </c>
       <c r="B1287" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491794MTJ</t>
+          <t>KIT4M064917936NF</t>
         </is>
       </c>
       <c r="C1287" s="2" t="inlineStr">
         <is>
-          <t>816375</t>
+          <t>816404</t>
         </is>
       </c>
       <c r="D1287" s="2" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="B1288" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491795MWG</t>
+          <t>KIT4M06491794MTJ</t>
         </is>
       </c>
       <c r="C1288" s="2" t="inlineStr">
         <is>
-          <t>816383</t>
+          <t>816375</t>
         </is>
       </c>
       <c r="D1288" s="2" t="inlineStr">
@@ -39101,12 +39101,12 @@
       </c>
       <c r="B1289" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491796QQN</t>
+          <t>KIT4M06491795MWG</t>
         </is>
       </c>
       <c r="C1289" s="2" t="inlineStr">
         <is>
-          <t>816405</t>
+          <t>816383</t>
         </is>
       </c>
       <c r="D1289" s="2" t="inlineStr">
@@ -39131,12 +39131,12 @@
       </c>
       <c r="B1290" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491797NCX</t>
+          <t>KIT4M06491796QQN</t>
         </is>
       </c>
       <c r="C1290" s="2" t="inlineStr">
         <is>
-          <t>816408</t>
+          <t>816405</t>
         </is>
       </c>
       <c r="D1290" s="2" t="inlineStr">
@@ -39161,12 +39161,12 @@
       </c>
       <c r="B1291" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491798S8Q</t>
+          <t>KIT4M06491797NCX</t>
         </is>
       </c>
       <c r="C1291" s="2" t="inlineStr">
         <is>
-          <t>816395</t>
+          <t>816408</t>
         </is>
       </c>
       <c r="D1291" s="2" t="inlineStr">
@@ -39191,12 +39191,12 @@
       </c>
       <c r="B1292" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491799CRP</t>
+          <t>KIT4M06491798S8Q</t>
         </is>
       </c>
       <c r="C1292" s="2" t="inlineStr">
         <is>
-          <t>816394</t>
+          <t>816395</t>
         </is>
       </c>
       <c r="D1292" s="2" t="inlineStr">
@@ -39221,12 +39221,12 @@
       </c>
       <c r="B1293" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491800F52</t>
+          <t>KIT4M06491799CRP</t>
         </is>
       </c>
       <c r="C1293" s="2" t="inlineStr">
         <is>
-          <t>816406</t>
+          <t>816394</t>
         </is>
       </c>
       <c r="D1293" s="2" t="inlineStr">
@@ -39251,12 +39251,12 @@
       </c>
       <c r="B1294" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918015Z2</t>
+          <t>KIT4M06491800F52</t>
         </is>
       </c>
       <c r="C1294" s="2" t="inlineStr">
         <is>
-          <t>816376</t>
+          <t>816406</t>
         </is>
       </c>
       <c r="D1294" s="2" t="inlineStr">
@@ -39281,12 +39281,12 @@
       </c>
       <c r="B1295" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491802BZV</t>
+          <t>KIT4M064918015Z2</t>
         </is>
       </c>
       <c r="C1295" s="2" t="inlineStr">
         <is>
-          <t>816390</t>
+          <t>816376</t>
         </is>
       </c>
       <c r="D1295" s="2" t="inlineStr">
@@ -39311,12 +39311,12 @@
       </c>
       <c r="B1296" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491803672</t>
+          <t>KIT4M06491802BZV</t>
         </is>
       </c>
       <c r="C1296" s="2" t="inlineStr">
         <is>
-          <t>816391</t>
+          <t>816390</t>
         </is>
       </c>
       <c r="D1296" s="2" t="inlineStr">
@@ -39341,12 +39341,12 @@
       </c>
       <c r="B1297" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491804TBC</t>
+          <t>KIT4M06491803672</t>
         </is>
       </c>
       <c r="C1297" s="2" t="inlineStr">
         <is>
-          <t>816373</t>
+          <t>816391</t>
         </is>
       </c>
       <c r="D1297" s="2" t="inlineStr">
@@ -39371,12 +39371,12 @@
       </c>
       <c r="B1298" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491805F7Z</t>
+          <t>KIT4M06491804TBC</t>
         </is>
       </c>
       <c r="C1298" s="2" t="inlineStr">
         <is>
-          <t>816382</t>
+          <t>816373</t>
         </is>
       </c>
       <c r="D1298" s="2" t="inlineStr">
@@ -39401,12 +39401,12 @@
       </c>
       <c r="B1299" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918068FF</t>
+          <t>KIT4M06491805F7Z</t>
         </is>
       </c>
       <c r="C1299" s="2" t="inlineStr">
         <is>
-          <t>816400</t>
+          <t>816382</t>
         </is>
       </c>
       <c r="D1299" s="2" t="inlineStr">
@@ -39431,12 +39431,12 @@
       </c>
       <c r="B1300" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491807TRH</t>
+          <t>KIT4M064918068FF</t>
         </is>
       </c>
       <c r="C1300" s="2" t="inlineStr">
         <is>
-          <t>816386</t>
+          <t>816400</t>
         </is>
       </c>
       <c r="D1300" s="2" t="inlineStr">
@@ -39461,12 +39461,12 @@
       </c>
       <c r="B1301" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491808P4F</t>
+          <t>KIT4M06491807TRH</t>
         </is>
       </c>
       <c r="C1301" s="2" t="inlineStr">
         <is>
-          <t>816399</t>
+          <t>816386</t>
         </is>
       </c>
       <c r="D1301" s="2" t="inlineStr">
@@ -39491,12 +39491,12 @@
       </c>
       <c r="B1302" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491809ZR6</t>
+          <t>KIT4M06491808P4F</t>
         </is>
       </c>
       <c r="C1302" s="2" t="inlineStr">
         <is>
-          <t>816402</t>
+          <t>816399</t>
         </is>
       </c>
       <c r="D1302" s="2" t="inlineStr">
@@ -39521,12 +39521,12 @@
       </c>
       <c r="B1303" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649181062D</t>
+          <t>KIT4M06491809ZR6</t>
         </is>
       </c>
       <c r="C1303" s="2" t="inlineStr">
         <is>
-          <t>816388</t>
+          <t>816402</t>
         </is>
       </c>
       <c r="D1303" s="2" t="inlineStr">
@@ -39551,12 +39551,12 @@
       </c>
       <c r="B1304" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491811JB5</t>
+          <t>KIT4M0649181062D</t>
         </is>
       </c>
       <c r="C1304" s="2" t="inlineStr">
         <is>
-          <t>816411</t>
+          <t>816388</t>
         </is>
       </c>
       <c r="D1304" s="2" t="inlineStr">
@@ -39581,12 +39581,12 @@
       </c>
       <c r="B1305" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491812JDV</t>
+          <t>KIT4M06491811JB5</t>
         </is>
       </c>
       <c r="C1305" s="2" t="inlineStr">
         <is>
-          <t>816409</t>
+          <t>816411</t>
         </is>
       </c>
       <c r="D1305" s="2" t="inlineStr">
@@ -39611,12 +39611,12 @@
       </c>
       <c r="B1306" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491813KGS</t>
+          <t>KIT4M06491812JDV</t>
         </is>
       </c>
       <c r="C1306" s="2" t="inlineStr">
         <is>
-          <t>816377</t>
+          <t>816409</t>
         </is>
       </c>
       <c r="D1306" s="2" t="inlineStr">
@@ -39641,12 +39641,12 @@
       </c>
       <c r="B1307" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491814FV7</t>
+          <t>KIT4M06491813KGS</t>
         </is>
       </c>
       <c r="C1307" s="2" t="inlineStr">
         <is>
-          <t>816370</t>
+          <t>816377</t>
         </is>
       </c>
       <c r="D1307" s="2" t="inlineStr">
@@ -39671,12 +39671,12 @@
       </c>
       <c r="B1308" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918154FM</t>
+          <t>KIT4M06491814FV7</t>
         </is>
       </c>
       <c r="C1308" s="2" t="inlineStr">
         <is>
-          <t>816368</t>
+          <t>816370</t>
         </is>
       </c>
       <c r="D1308" s="2" t="inlineStr">
@@ -39701,12 +39701,12 @@
       </c>
       <c r="B1309" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918165MW</t>
+          <t>KIT4M064918154FM</t>
         </is>
       </c>
       <c r="C1309" s="2" t="inlineStr">
         <is>
-          <t>816374</t>
+          <t>816368</t>
         </is>
       </c>
       <c r="D1309" s="2" t="inlineStr">
@@ -39731,12 +39731,12 @@
       </c>
       <c r="B1310" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491817T79</t>
+          <t>KIT4M064918165MW</t>
         </is>
       </c>
       <c r="C1310" s="2" t="inlineStr">
         <is>
-          <t>816415</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="D1310" s="2" t="inlineStr">
@@ -39761,12 +39761,12 @@
       </c>
       <c r="B1311" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491818QD2</t>
+          <t>KIT4M06491817T79</t>
         </is>
       </c>
       <c r="C1311" s="2" t="inlineStr">
         <is>
-          <t>816378</t>
+          <t>816415</t>
         </is>
       </c>
       <c r="D1311" s="2" t="inlineStr">
@@ -39791,12 +39791,12 @@
       </c>
       <c r="B1312" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918197VX</t>
+          <t>KIT4M06491818QD2</t>
         </is>
       </c>
       <c r="C1312" s="2" t="inlineStr">
         <is>
-          <t>816397</t>
+          <t>816378</t>
         </is>
       </c>
       <c r="D1312" s="2" t="inlineStr">
@@ -39821,12 +39821,12 @@
       </c>
       <c r="B1313" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491820X58</t>
+          <t>KIT4M064918197VX</t>
         </is>
       </c>
       <c r="C1313" s="2" t="inlineStr">
         <is>
-          <t>816385</t>
+          <t>816397</t>
         </is>
       </c>
       <c r="D1313" s="2" t="inlineStr">
@@ -39851,12 +39851,12 @@
       </c>
       <c r="B1314" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491821G25</t>
+          <t>KIT4M06491820X58</t>
         </is>
       </c>
       <c r="C1314" s="2" t="inlineStr">
         <is>
-          <t>816379</t>
+          <t>816385</t>
         </is>
       </c>
       <c r="D1314" s="2" t="inlineStr">
@@ -39881,12 +39881,12 @@
       </c>
       <c r="B1315" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491822SF6</t>
+          <t>KIT4M06491821G25</t>
         </is>
       </c>
       <c r="C1315" s="2" t="inlineStr">
         <is>
-          <t>816412</t>
+          <t>816379</t>
         </is>
       </c>
       <c r="D1315" s="2" t="inlineStr">
@@ -39911,12 +39911,12 @@
       </c>
       <c r="B1316" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918239TM</t>
+          <t>KIT4M06491822SF6</t>
         </is>
       </c>
       <c r="C1316" s="2" t="inlineStr">
         <is>
-          <t>816398</t>
+          <t>816412</t>
         </is>
       </c>
       <c r="D1316" s="2" t="inlineStr">
@@ -39941,12 +39941,12 @@
       </c>
       <c r="B1317" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491824JCK</t>
+          <t>KIT4M064918239TM</t>
         </is>
       </c>
       <c r="C1317" s="2" t="inlineStr">
         <is>
-          <t>816413</t>
+          <t>816398</t>
         </is>
       </c>
       <c r="D1317" s="2" t="inlineStr">
@@ -39971,12 +39971,12 @@
       </c>
       <c r="B1318" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491825PF9</t>
+          <t>KIT4M06491824JCK</t>
         </is>
       </c>
       <c r="C1318" s="2" t="inlineStr">
         <is>
-          <t>816367</t>
+          <t>816413</t>
         </is>
       </c>
       <c r="D1318" s="2" t="inlineStr">
@@ -40001,12 +40001,12 @@
       </c>
       <c r="B1319" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491826SQM</t>
+          <t>KIT4M06491825PF9</t>
         </is>
       </c>
       <c r="C1319" s="2" t="inlineStr">
         <is>
-          <t>816380</t>
+          <t>816367</t>
         </is>
       </c>
       <c r="D1319" s="2" t="inlineStr">
@@ -40031,12 +40031,12 @@
       </c>
       <c r="B1320" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918277QF</t>
+          <t>KIT4M06491826SQM</t>
         </is>
       </c>
       <c r="C1320" s="2" t="inlineStr">
         <is>
-          <t>816403</t>
+          <t>816380</t>
         </is>
       </c>
       <c r="D1320" s="2" t="inlineStr">
@@ -40061,12 +40061,12 @@
       </c>
       <c r="B1321" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491828XWF</t>
+          <t>KIT4M064918277QF</t>
         </is>
       </c>
       <c r="C1321" s="2" t="inlineStr">
         <is>
-          <t>816387</t>
+          <t>816403</t>
         </is>
       </c>
       <c r="D1321" s="2" t="inlineStr">
@@ -40091,12 +40091,12 @@
       </c>
       <c r="B1322" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491829CD2</t>
+          <t>KIT4M06491828XWF</t>
         </is>
       </c>
       <c r="C1322" s="2" t="inlineStr">
         <is>
-          <t>816393</t>
+          <t>816387</t>
         </is>
       </c>
       <c r="D1322" s="2" t="inlineStr">
@@ -40121,12 +40121,12 @@
       </c>
       <c r="B1323" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491830G2J</t>
+          <t>KIT4M06491829CD2</t>
         </is>
       </c>
       <c r="C1323" s="2" t="inlineStr">
         <is>
-          <t>816372</t>
+          <t>816393</t>
         </is>
       </c>
       <c r="D1323" s="2" t="inlineStr">
@@ -40151,12 +40151,12 @@
       </c>
       <c r="B1324" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0649183125S</t>
+          <t>KIT4M06491830G2J</t>
         </is>
       </c>
       <c r="C1324" s="2" t="inlineStr">
         <is>
-          <t>816371</t>
+          <t>816372</t>
         </is>
       </c>
       <c r="D1324" s="2" t="inlineStr">
@@ -40181,12 +40181,12 @@
       </c>
       <c r="B1325" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918322GZ</t>
+          <t>KIT4M0649183125S</t>
         </is>
       </c>
       <c r="C1325" s="2" t="inlineStr">
         <is>
-          <t>816414</t>
+          <t>816371</t>
         </is>
       </c>
       <c r="D1325" s="2" t="inlineStr">
@@ -40211,12 +40211,12 @@
       </c>
       <c r="B1326" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491833JGV</t>
+          <t>KIT4M064918322GZ</t>
         </is>
       </c>
       <c r="C1326" s="2" t="inlineStr">
         <is>
-          <t>816384</t>
+          <t>816414</t>
         </is>
       </c>
       <c r="D1326" s="2" t="inlineStr">
@@ -40241,12 +40241,12 @@
       </c>
       <c r="B1327" s="2" t="inlineStr">
         <is>
-          <t>KIT4M064918346DB</t>
+          <t>KIT4M06491833JGV</t>
         </is>
       </c>
       <c r="C1327" s="2" t="inlineStr">
         <is>
-          <t>816369</t>
+          <t>816384</t>
         </is>
       </c>
       <c r="D1327" s="2" t="inlineStr">
@@ -40271,12 +40271,12 @@
       </c>
       <c r="B1328" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491835TD6</t>
+          <t>KIT4M064918346DB</t>
         </is>
       </c>
       <c r="C1328" s="2" t="inlineStr">
         <is>
-          <t>816401</t>
+          <t>816369</t>
         </is>
       </c>
       <c r="D1328" s="2" t="inlineStr">
@@ -40301,12 +40301,12 @@
       </c>
       <c r="B1329" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491836Z2D</t>
+          <t>KIT4M06491835TD6</t>
         </is>
       </c>
       <c r="C1329" s="2" t="inlineStr">
         <is>
-          <t>816366</t>
+          <t>816401</t>
         </is>
       </c>
       <c r="D1329" s="2" t="inlineStr">
@@ -40331,12 +40331,12 @@
       </c>
       <c r="B1330" s="2" t="inlineStr">
         <is>
-          <t>KIT4M06491837DPX</t>
+          <t>KIT4M06491836Z2D</t>
         </is>
       </c>
       <c r="C1330" s="2" t="inlineStr">
         <is>
-          <t>816389</t>
+          <t>816366</t>
         </is>
       </c>
       <c r="D1330" s="2" t="inlineStr">
@@ -40361,17 +40361,17 @@
       </c>
       <c r="B1331" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000655962DJ</t>
+          <t>KIT4M06491837DPX</t>
         </is>
       </c>
       <c r="C1331" s="2" t="inlineStr">
         <is>
-          <t>809604</t>
+          <t>816389</t>
         </is>
       </c>
       <c r="D1331" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E1331" s="3" t="n">
@@ -40391,12 +40391,12 @@
       </c>
       <c r="B1332" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065612DJF</t>
+          <t>KIT4P000655962DJ</t>
         </is>
       </c>
       <c r="C1332" s="2" t="inlineStr">
         <is>
-          <t>809605</t>
+          <t>809604</t>
         </is>
       </c>
       <c r="D1332" s="2" t="inlineStr">
@@ -40421,12 +40421,12 @@
       </c>
       <c r="B1333" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065631CPZ</t>
+          <t>KIT4P00065612DJF</t>
         </is>
       </c>
       <c r="C1333" s="2" t="inlineStr">
         <is>
-          <t>812930</t>
+          <t>809605</t>
         </is>
       </c>
       <c r="D1333" s="2" t="inlineStr">
@@ -40451,12 +40451,12 @@
       </c>
       <c r="B1334" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065633ZXC</t>
+          <t>KIT4P00065631CPZ</t>
         </is>
       </c>
       <c r="C1334" s="2" t="inlineStr">
         <is>
-          <t>812922</t>
+          <t>812930</t>
         </is>
       </c>
       <c r="D1334" s="2" t="inlineStr">
@@ -40481,12 +40481,12 @@
       </c>
       <c r="B1335" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4P00065633ZXC</t>
         </is>
       </c>
       <c r="C1335" s="2" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>812922</t>
         </is>
       </c>
       <c r="D1335" s="2" t="inlineStr">

--- a/Starlink_Usage_Kit_History.xlsx
+++ b/Starlink_Usage_Kit_History.xlsx
@@ -30371,12 +30371,12 @@
       </c>
       <c r="B998" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00084593R9F</t>
+          <t>KIT4P00065641GDF</t>
         </is>
       </c>
       <c r="C998" s="2" t="inlineStr">
         <is>
-          <t>816227</t>
+          <t>812924</t>
         </is>
       </c>
       <c r="D998" s="2" t="inlineStr">
@@ -30385,11 +30385,11 @@
         </is>
       </c>
       <c r="E998" s="3" t="n">
-        <v>153.65</v>
+        <v>347.26</v>
       </c>
       <c r="F998" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30415,11 +30415,11 @@
         </is>
       </c>
       <c r="E999" s="3" t="n">
-        <v>84.2</v>
+        <v>224.52</v>
       </c>
       <c r="F999" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30431,12 +30431,12 @@
       </c>
       <c r="B1000" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065641GDF</t>
+          <t>KIT4P00065644SB2</t>
         </is>
       </c>
       <c r="C1000" s="2" t="inlineStr">
         <is>
-          <t>812924</t>
+          <t>812928</t>
         </is>
       </c>
       <c r="D1000" s="2" t="inlineStr">
@@ -30445,11 +30445,11 @@
         </is>
       </c>
       <c r="E1000" s="3" t="n">
-        <v>67.98</v>
+        <v>220.38</v>
       </c>
       <c r="F1000" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30461,25 +30461,25 @@
       </c>
       <c r="B1001" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065593VWC</t>
+          <t>KIT4M05413776H84</t>
         </is>
       </c>
       <c r="C1001" s="2" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>810101</t>
         </is>
       </c>
       <c r="D1001" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E1001" s="3" t="n">
-        <v>64.14</v>
+        <v>156.28</v>
       </c>
       <c r="F1001" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30491,12 +30491,12 @@
       </c>
       <c r="B1002" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065644SB2</t>
+          <t>KIT4P00084593R9F</t>
         </is>
       </c>
       <c r="C1002" s="2" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>816227</t>
         </is>
       </c>
       <c r="D1002" s="2" t="inlineStr">
@@ -30505,11 +30505,11 @@
         </is>
       </c>
       <c r="E1002" s="3" t="n">
-        <v>59.68</v>
+        <v>153.69</v>
       </c>
       <c r="F1002" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30521,25 +30521,25 @@
       </c>
       <c r="B1003" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413776H84</t>
+          <t>KIT4P00065593VWC</t>
         </is>
       </c>
       <c r="C1003" s="2" t="inlineStr">
         <is>
-          <t>810101</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="D1003" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E1003" s="3" t="n">
-        <v>56.1</v>
+        <v>141.1</v>
       </c>
       <c r="F1003" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30551,12 +30551,12 @@
       </c>
       <c r="B1004" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008460369B</t>
+          <t>KIT4P0007258645B</t>
         </is>
       </c>
       <c r="C1004" s="2" t="inlineStr">
         <is>
-          <t>816224</t>
+          <t>814495</t>
         </is>
       </c>
       <c r="D1004" s="2" t="inlineStr">
@@ -30565,11 +30565,11 @@
         </is>
       </c>
       <c r="E1004" s="3" t="n">
-        <v>54.72</v>
+        <v>140.15</v>
       </c>
       <c r="F1004" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30581,12 +30581,12 @@
       </c>
       <c r="B1005" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635887MK</t>
+          <t>KIT4M05368194X6V</t>
         </is>
       </c>
       <c r="C1005" s="2" t="inlineStr">
         <is>
-          <t>814446</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="D1005" s="2" t="inlineStr">
@@ -30595,11 +30595,11 @@
         </is>
       </c>
       <c r="E1005" s="3" t="n">
-        <v>44.74</v>
+        <v>137.37</v>
       </c>
       <c r="F1005" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30611,12 +30611,12 @@
       </c>
       <c r="B1006" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475151HTP</t>
+          <t>KIT4M05413808FFZ</t>
         </is>
       </c>
       <c r="C1006" s="2" t="inlineStr">
         <is>
-          <t>809867</t>
+          <t>812828</t>
         </is>
       </c>
       <c r="D1006" s="2" t="inlineStr">
@@ -30625,11 +30625,11 @@
         </is>
       </c>
       <c r="E1006" s="3" t="n">
-        <v>43.69</v>
+        <v>122.99</v>
       </c>
       <c r="F1006" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30641,25 +30641,25 @@
       </c>
       <c r="B1007" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0007258645B</t>
+          <t>KIT4M055635887MK</t>
         </is>
       </c>
       <c r="C1007" s="2" t="inlineStr">
         <is>
-          <t>814495</t>
+          <t>814446</t>
         </is>
       </c>
       <c r="D1007" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E1007" s="3" t="n">
-        <v>39.54</v>
+        <v>116.4</v>
       </c>
       <c r="F1007" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30671,25 +30671,25 @@
       </c>
       <c r="B1008" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368194X6V</t>
+          <t>KIT4P0008459589D</t>
         </is>
       </c>
       <c r="C1008" s="2" t="inlineStr">
         <is>
-          <t>810644</t>
+          <t>816222</t>
         </is>
       </c>
       <c r="D1008" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E1008" s="3" t="n">
-        <v>38.15</v>
+        <v>115.7</v>
       </c>
       <c r="F1008" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30701,12 +30701,12 @@
       </c>
       <c r="B1009" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00065630DZT</t>
+          <t>KIT4P0008460369B</t>
         </is>
       </c>
       <c r="C1009" s="2" t="inlineStr">
         <is>
-          <t>807635</t>
+          <t>816224</t>
         </is>
       </c>
       <c r="D1009" s="2" t="inlineStr">
@@ -30715,11 +30715,11 @@
         </is>
       </c>
       <c r="E1009" s="3" t="n">
-        <v>30.7</v>
+        <v>101.55</v>
       </c>
       <c r="F1009" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30731,25 +30731,25 @@
       </c>
       <c r="B1010" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563504MBB</t>
+          <t>KIT4P00065630DZT</t>
         </is>
       </c>
       <c r="C1010" s="2" t="inlineStr">
         <is>
-          <t>814460</t>
+          <t>807635</t>
         </is>
       </c>
       <c r="D1010" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E1010" s="3" t="n">
-        <v>29.16</v>
+        <v>100.46</v>
       </c>
       <c r="F1010" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30761,12 +30761,12 @@
       </c>
       <c r="B1011" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475149XG5</t>
+          <t>KIT4M05799717WZV</t>
         </is>
       </c>
       <c r="C1011" s="2" t="inlineStr">
         <is>
-          <t>809657</t>
+          <t>816280</t>
         </is>
       </c>
       <c r="D1011" s="2" t="inlineStr">
@@ -30775,11 +30775,11 @@
         </is>
       </c>
       <c r="E1011" s="3" t="n">
-        <v>27.73</v>
+        <v>97.78</v>
       </c>
       <c r="F1011" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30791,12 +30791,12 @@
       </c>
       <c r="B1012" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872583P58</t>
+          <t>KIT4M046047372KJ</t>
         </is>
       </c>
       <c r="C1012" s="2" t="inlineStr">
         <is>
-          <t>816069</t>
+          <t>809658</t>
         </is>
       </c>
       <c r="D1012" s="2" t="inlineStr">
@@ -30805,11 +30805,11 @@
         </is>
       </c>
       <c r="E1012" s="3" t="n">
-        <v>26.9</v>
+        <v>89.08</v>
       </c>
       <c r="F1012" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30821,12 +30821,12 @@
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047467T4</t>
+          <t>KIT4M04475149XG5</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>809657</t>
         </is>
       </c>
       <c r="D1013" s="2" t="inlineStr">
@@ -30835,11 +30835,11 @@
         </is>
       </c>
       <c r="E1013" s="3" t="n">
-        <v>26.5</v>
+        <v>84.17</v>
       </c>
       <c r="F1013" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30851,12 +30851,12 @@
       </c>
       <c r="B1014" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563502GJS</t>
+          <t>KIT4M05563585TXM</t>
         </is>
       </c>
       <c r="C1014" s="2" t="inlineStr">
         <is>
-          <t>814470</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="D1014" s="2" t="inlineStr">
@@ -30865,11 +30865,11 @@
         </is>
       </c>
       <c r="E1014" s="3" t="n">
-        <v>23.52</v>
+        <v>75.38</v>
       </c>
       <c r="F1014" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30881,12 +30881,12 @@
       </c>
       <c r="B1015" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872536JFD</t>
+          <t>KIT4M046047467T4</t>
         </is>
       </c>
       <c r="C1015" s="2" t="inlineStr">
         <is>
-          <t>816070</t>
+          <t>809865</t>
         </is>
       </c>
       <c r="D1015" s="2" t="inlineStr">
@@ -30895,11 +30895,11 @@
         </is>
       </c>
       <c r="E1015" s="3" t="n">
-        <v>21.29</v>
+        <v>74.5</v>
       </c>
       <c r="F1015" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30911,25 +30911,25 @@
       </c>
       <c r="B1016" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066915CBF</t>
+          <t>KIT4M02578775B9Q</t>
         </is>
       </c>
       <c r="C1016" s="2" t="inlineStr">
         <is>
-          <t>812921</t>
+          <t>809611</t>
         </is>
       </c>
       <c r="D1016" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E1016" s="3" t="n">
-        <v>20.54</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="F1016" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30941,12 +30941,12 @@
       </c>
       <c r="B1017" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138064J9</t>
+          <t>KIT4M05563502GJS</t>
         </is>
       </c>
       <c r="C1017" s="2" t="inlineStr">
         <is>
-          <t>812844</t>
+          <t>814470</t>
         </is>
       </c>
       <c r="D1017" s="2" t="inlineStr">
@@ -30955,11 +30955,11 @@
         </is>
       </c>
       <c r="E1017" s="3" t="n">
-        <v>18.37</v>
+        <v>70.39</v>
       </c>
       <c r="F1017" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -30971,25 +30971,25 @@
       </c>
       <c r="B1018" s="2" t="inlineStr">
         <is>
-          <t>KIT4M02578775B9Q</t>
+          <t>KIT4P00066915CBF</t>
         </is>
       </c>
       <c r="C1018" s="2" t="inlineStr">
         <is>
-          <t>809611</t>
+          <t>812921</t>
         </is>
       </c>
       <c r="D1018" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E1018" s="3" t="n">
-        <v>17.28</v>
+        <v>69.23</v>
       </c>
       <c r="F1018" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31001,12 +31001,12 @@
       </c>
       <c r="B1019" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563585TXM</t>
+          <t>KIT4M05872583P58</t>
         </is>
       </c>
       <c r="C1019" s="2" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>816069</t>
         </is>
       </c>
       <c r="D1019" s="2" t="inlineStr">
@@ -31015,11 +31015,11 @@
         </is>
       </c>
       <c r="E1019" s="3" t="n">
-        <v>16.39</v>
+        <v>68.67</v>
       </c>
       <c r="F1019" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31031,12 +31031,12 @@
       </c>
       <c r="B1020" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413837SMB</t>
+          <t>KIT4M04475151HTP</t>
         </is>
       </c>
       <c r="C1020" s="2" t="inlineStr">
         <is>
-          <t>810100</t>
+          <t>809867</t>
         </is>
       </c>
       <c r="D1020" s="2" t="inlineStr">
@@ -31045,11 +31045,11 @@
         </is>
       </c>
       <c r="E1020" s="3" t="n">
-        <v>15.24</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F1020" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31061,12 +31061,12 @@
       </c>
       <c r="B1021" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563534GZ7</t>
+          <t>KIT4M05872536JFD</t>
         </is>
       </c>
       <c r="C1021" s="2" t="inlineStr">
         <is>
-          <t>814467</t>
+          <t>816070</t>
         </is>
       </c>
       <c r="D1021" s="2" t="inlineStr">
@@ -31075,11 +31075,11 @@
         </is>
       </c>
       <c r="E1021" s="3" t="n">
-        <v>14.85</v>
+        <v>66.86</v>
       </c>
       <c r="F1021" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31091,25 +31091,25 @@
       </c>
       <c r="B1022" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0008459589D</t>
+          <t>KIT4M054138064J9</t>
         </is>
       </c>
       <c r="C1022" s="2" t="inlineStr">
         <is>
-          <t>816222</t>
+          <t>812844</t>
         </is>
       </c>
       <c r="D1022" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E1022" s="3" t="n">
-        <v>14.67</v>
+        <v>60.07</v>
       </c>
       <c r="F1022" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31121,12 +31121,12 @@
       </c>
       <c r="B1023" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635475JB</t>
+          <t>KIT4M05563504MBB</t>
         </is>
       </c>
       <c r="C1023" s="2" t="inlineStr">
         <is>
-          <t>814465</t>
+          <t>814460</t>
         </is>
       </c>
       <c r="D1023" s="2" t="inlineStr">
@@ -31135,11 +31135,11 @@
         </is>
       </c>
       <c r="E1023" s="3" t="n">
-        <v>13.01</v>
+        <v>59.06</v>
       </c>
       <c r="F1023" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31151,12 +31151,12 @@
       </c>
       <c r="B1024" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413808FFZ</t>
+          <t>KIT4M05413837SMB</t>
         </is>
       </c>
       <c r="C1024" s="2" t="inlineStr">
         <is>
-          <t>812828</t>
+          <t>810100</t>
         </is>
       </c>
       <c r="D1024" s="2" t="inlineStr">
@@ -31165,11 +31165,11 @@
         </is>
       </c>
       <c r="E1024" s="3" t="n">
-        <v>11.32</v>
+        <v>56.41</v>
       </c>
       <c r="F1024" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31181,12 +31181,12 @@
       </c>
       <c r="B1025" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563573WKC</t>
+          <t>KIT4M055635475JB</t>
         </is>
       </c>
       <c r="C1025" s="2" t="inlineStr">
         <is>
-          <t>814488</t>
+          <t>814465</t>
         </is>
       </c>
       <c r="D1025" s="2" t="inlineStr">
@@ -31195,11 +31195,11 @@
         </is>
       </c>
       <c r="E1025" s="3" t="n">
-        <v>11.22</v>
+        <v>47.96</v>
       </c>
       <c r="F1025" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31211,25 +31211,25 @@
       </c>
       <c r="B1026" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724947VX</t>
+          <t>KIT4P00073918HBX</t>
         </is>
       </c>
       <c r="C1026" s="2" t="inlineStr">
         <is>
-          <t>816086</t>
+          <t>814645</t>
         </is>
       </c>
       <c r="D1026" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E1026" s="3" t="n">
-        <v>10.92</v>
+        <v>44.61</v>
       </c>
       <c r="F1026" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31241,12 +31241,12 @@
       </c>
       <c r="B1027" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00073918HBX</t>
+          <t>KIT4P00066070HN4</t>
         </is>
       </c>
       <c r="C1027" s="2" t="inlineStr">
         <is>
-          <t>814645</t>
+          <t>807636</t>
         </is>
       </c>
       <c r="D1027" s="2" t="inlineStr">
@@ -31255,11 +31255,11 @@
         </is>
       </c>
       <c r="E1027" s="3" t="n">
-        <v>10.59</v>
+        <v>44.34</v>
       </c>
       <c r="F1027" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31271,12 +31271,12 @@
       </c>
       <c r="B1028" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563584FVC</t>
+          <t>KIT4M05872512N5W</t>
         </is>
       </c>
       <c r="C1028" s="2" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="D1028" s="2" t="inlineStr">
@@ -31285,11 +31285,11 @@
         </is>
       </c>
       <c r="E1028" s="3" t="n">
-        <v>10.28</v>
+        <v>43.51</v>
       </c>
       <c r="F1028" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31301,12 +31301,12 @@
       </c>
       <c r="B1029" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872512N5W</t>
+          <t>KIT4M05563534GZ7</t>
         </is>
       </c>
       <c r="C1029" s="2" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>814467</t>
         </is>
       </c>
       <c r="D1029" s="2" t="inlineStr">
@@ -31315,11 +31315,11 @@
         </is>
       </c>
       <c r="E1029" s="3" t="n">
-        <v>10.17</v>
+        <v>43.36</v>
       </c>
       <c r="F1029" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31331,12 +31331,12 @@
       </c>
       <c r="B1030" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413787HHK</t>
+          <t>KIT4M05368213974</t>
         </is>
       </c>
       <c r="C1030" s="2" t="inlineStr">
         <is>
-          <t>812809</t>
+          <t>810647</t>
         </is>
       </c>
       <c r="D1030" s="2" t="inlineStr">
@@ -31345,11 +31345,11 @@
         </is>
       </c>
       <c r="E1030" s="3" t="n">
-        <v>9.960000000000001</v>
+        <v>41.58</v>
       </c>
       <c r="F1030" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31361,12 +31361,12 @@
       </c>
       <c r="B1031" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872507528</t>
+          <t>KIT4M05563584FVC</t>
         </is>
       </c>
       <c r="C1031" s="2" t="inlineStr">
         <is>
-          <t>816083</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="D1031" s="2" t="inlineStr">
@@ -31375,11 +31375,11 @@
         </is>
       </c>
       <c r="E1031" s="3" t="n">
-        <v>8.859999999999999</v>
+        <v>38.77</v>
       </c>
       <c r="F1031" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31391,12 +31391,12 @@
       </c>
       <c r="B1032" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138189C7</t>
+          <t>KIT4M05413801QJB</t>
         </is>
       </c>
       <c r="C1032" s="2" t="inlineStr">
         <is>
-          <t>812831</t>
+          <t>812824</t>
         </is>
       </c>
       <c r="D1032" s="2" t="inlineStr">
@@ -31405,11 +31405,11 @@
         </is>
       </c>
       <c r="E1032" s="3" t="n">
-        <v>8.85</v>
+        <v>35.99</v>
       </c>
       <c r="F1032" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31421,12 +31421,12 @@
       </c>
       <c r="B1033" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368213974</t>
+          <t>KIT4M058724975J4</t>
         </is>
       </c>
       <c r="C1033" s="2" t="inlineStr">
         <is>
-          <t>810647</t>
+          <t>816075</t>
         </is>
       </c>
       <c r="D1033" s="2" t="inlineStr">
@@ -31435,11 +31435,11 @@
         </is>
       </c>
       <c r="E1033" s="3" t="n">
-        <v>8.66</v>
+        <v>35.79</v>
       </c>
       <c r="F1033" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31451,12 +31451,12 @@
       </c>
       <c r="B1034" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0587258755W</t>
+          <t>KIT4M04476539RJ5</t>
         </is>
       </c>
       <c r="C1034" s="2" t="inlineStr">
         <is>
-          <t>816187</t>
+          <t>809612</t>
         </is>
       </c>
       <c r="D1034" s="2" t="inlineStr">
@@ -31465,11 +31465,11 @@
         </is>
       </c>
       <c r="E1034" s="3" t="n">
-        <v>8.529999999999999</v>
+        <v>32.14</v>
       </c>
       <c r="F1034" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31481,12 +31481,12 @@
       </c>
       <c r="B1035" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04476539RJ5</t>
+          <t>KIT4M05563560225</t>
         </is>
       </c>
       <c r="C1035" s="2" t="inlineStr">
         <is>
-          <t>809612</t>
+          <t>814454</t>
         </is>
       </c>
       <c r="D1035" s="2" t="inlineStr">
@@ -31495,11 +31495,11 @@
         </is>
       </c>
       <c r="E1035" s="3" t="n">
-        <v>7.25</v>
+        <v>29.54</v>
       </c>
       <c r="F1035" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31511,25 +31511,25 @@
       </c>
       <c r="B1036" s="2" t="inlineStr">
         <is>
-          <t>KIT4P000668852J9</t>
+          <t>KIT4M05413787HHK</t>
         </is>
       </c>
       <c r="C1036" s="2" t="inlineStr">
         <is>
-          <t>812925</t>
+          <t>812809</t>
         </is>
       </c>
       <c r="D1036" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E1036" s="3" t="n">
-        <v>7.12</v>
+        <v>29.26</v>
       </c>
       <c r="F1036" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31541,12 +31541,12 @@
       </c>
       <c r="B1037" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635158PC</t>
+          <t>KIT4M05413795QHK</t>
         </is>
       </c>
       <c r="C1037" s="2" t="inlineStr">
         <is>
-          <t>814457</t>
+          <t>812801</t>
         </is>
       </c>
       <c r="D1037" s="2" t="inlineStr">
@@ -31555,11 +31555,11 @@
         </is>
       </c>
       <c r="E1037" s="3" t="n">
-        <v>6.71</v>
+        <v>28.27</v>
       </c>
       <c r="F1037" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31571,12 +31571,12 @@
       </c>
       <c r="B1038" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635329VD</t>
+          <t>KIT4M0587258755W</t>
         </is>
       </c>
       <c r="C1038" s="2" t="inlineStr">
         <is>
-          <t>814479</t>
+          <t>816187</t>
         </is>
       </c>
       <c r="D1038" s="2" t="inlineStr">
@@ -31585,11 +31585,11 @@
         </is>
       </c>
       <c r="E1038" s="3" t="n">
-        <v>6.4</v>
+        <v>27.42</v>
       </c>
       <c r="F1038" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31601,12 +31601,12 @@
       </c>
       <c r="B1039" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413771PVH</t>
+          <t>KIT4M058725094XP</t>
         </is>
       </c>
       <c r="C1039" s="2" t="inlineStr">
         <is>
-          <t>812800</t>
+          <t>816085</t>
         </is>
       </c>
       <c r="D1039" s="2" t="inlineStr">
@@ -31615,11 +31615,11 @@
         </is>
       </c>
       <c r="E1039" s="3" t="n">
-        <v>6.21</v>
+        <v>26.59</v>
       </c>
       <c r="F1039" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31631,12 +31631,12 @@
       </c>
       <c r="B1040" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158967K28</t>
+          <t>KIT4M058724947VX</t>
         </is>
       </c>
       <c r="C1040" s="2" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>816086</t>
         </is>
       </c>
       <c r="D1040" s="2" t="inlineStr">
@@ -31645,11 +31645,11 @@
         </is>
       </c>
       <c r="E1040" s="3" t="n">
-        <v>6.14</v>
+        <v>26.26</v>
       </c>
       <c r="F1040" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31661,12 +31661,12 @@
       </c>
       <c r="B1041" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368221HQ5</t>
+          <t>KIT4M055635834N7</t>
         </is>
       </c>
       <c r="C1041" s="2" t="inlineStr">
         <is>
-          <t>810834</t>
+          <t>814462</t>
         </is>
       </c>
       <c r="D1041" s="2" t="inlineStr">
@@ -31675,11 +31675,11 @@
         </is>
       </c>
       <c r="E1041" s="3" t="n">
-        <v>5.94</v>
+        <v>25.54</v>
       </c>
       <c r="F1041" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31691,12 +31691,12 @@
       </c>
       <c r="B1042" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158973M2C</t>
+          <t>KIT4M05563573WKC</t>
         </is>
       </c>
       <c r="C1042" s="2" t="inlineStr">
         <is>
-          <t>809610</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="D1042" s="2" t="inlineStr">
@@ -31705,11 +31705,11 @@
         </is>
       </c>
       <c r="E1042" s="3" t="n">
-        <v>5.91</v>
+        <v>24.71</v>
       </c>
       <c r="F1042" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31721,12 +31721,12 @@
       </c>
       <c r="B1043" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368219KRH</t>
+          <t>KIT4M05563593DMC</t>
         </is>
       </c>
       <c r="C1043" s="2" t="inlineStr">
         <is>
-          <t>810646</t>
+          <t>814442</t>
         </is>
       </c>
       <c r="D1043" s="2" t="inlineStr">
@@ -31735,11 +31735,11 @@
         </is>
       </c>
       <c r="E1043" s="3" t="n">
-        <v>5.69</v>
+        <v>22.78</v>
       </c>
       <c r="F1043" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31751,12 +31751,12 @@
       </c>
       <c r="B1044" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563593DMC</t>
+          <t>KIT4M055635329VD</t>
         </is>
       </c>
       <c r="C1044" s="2" t="inlineStr">
         <is>
-          <t>814442</t>
+          <t>814479</t>
         </is>
       </c>
       <c r="D1044" s="2" t="inlineStr">
@@ -31765,11 +31765,11 @@
         </is>
       </c>
       <c r="E1044" s="3" t="n">
-        <v>5.39</v>
+        <v>21.96</v>
       </c>
       <c r="F1044" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31781,12 +31781,12 @@
       </c>
       <c r="B1045" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563579H9F</t>
+          <t>KIT4M05563590ZFQ</t>
         </is>
       </c>
       <c r="C1045" s="2" t="inlineStr">
         <is>
-          <t>814480</t>
+          <t>814461</t>
         </is>
       </c>
       <c r="D1045" s="2" t="inlineStr">
@@ -31795,11 +31795,11 @@
         </is>
       </c>
       <c r="E1045" s="3" t="n">
-        <v>5.28</v>
+        <v>21.21</v>
       </c>
       <c r="F1045" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31811,12 +31811,12 @@
       </c>
       <c r="B1046" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725094XP</t>
+          <t>KIT4M04158967K28</t>
         </is>
       </c>
       <c r="C1046" s="2" t="inlineStr">
         <is>
-          <t>816085</t>
+          <t>809620</t>
         </is>
       </c>
       <c r="D1046" s="2" t="inlineStr">
@@ -31825,11 +31825,11 @@
         </is>
       </c>
       <c r="E1046" s="3" t="n">
-        <v>5.18</v>
+        <v>19.83</v>
       </c>
       <c r="F1046" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31841,12 +31841,12 @@
       </c>
       <c r="B1047" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413795QHK</t>
+          <t>KIT4M05413771PVH</t>
         </is>
       </c>
       <c r="C1047" s="2" t="inlineStr">
         <is>
-          <t>812801</t>
+          <t>812800</t>
         </is>
       </c>
       <c r="D1047" s="2" t="inlineStr">
@@ -31855,11 +31855,11 @@
         </is>
       </c>
       <c r="E1047" s="3" t="n">
-        <v>5.07</v>
+        <v>19.79</v>
       </c>
       <c r="F1047" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31871,12 +31871,12 @@
       </c>
       <c r="B1048" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563509CHJ</t>
+          <t>KIT4M05563527J4C</t>
         </is>
       </c>
       <c r="C1048" s="2" t="inlineStr">
         <is>
-          <t>814431</t>
+          <t>814452</t>
         </is>
       </c>
       <c r="D1048" s="2" t="inlineStr">
@@ -31885,11 +31885,11 @@
         </is>
       </c>
       <c r="E1048" s="3" t="n">
-        <v>4.88</v>
+        <v>18.99</v>
       </c>
       <c r="F1048" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31901,25 +31901,25 @@
       </c>
       <c r="B1049" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563528MKX</t>
+          <t>KIT4P000668852J9</t>
         </is>
       </c>
       <c r="C1049" s="2" t="inlineStr">
         <is>
-          <t>814471</t>
+          <t>812925</t>
         </is>
       </c>
       <c r="D1049" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E1049" s="3" t="n">
-        <v>4.88</v>
+        <v>18.61</v>
       </c>
       <c r="F1049" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31931,12 +31931,12 @@
       </c>
       <c r="B1050" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867737P9P</t>
+          <t>KIT4M04604742S6S</t>
         </is>
       </c>
       <c r="C1050" s="2" t="inlineStr">
         <is>
-          <t>809622</t>
+          <t>809874</t>
         </is>
       </c>
       <c r="D1050" s="2" t="inlineStr">
@@ -31945,11 +31945,11 @@
         </is>
       </c>
       <c r="E1050" s="3" t="n">
-        <v>4.83</v>
+        <v>18.47</v>
       </c>
       <c r="F1050" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31961,12 +31961,12 @@
       </c>
       <c r="B1051" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413826Z6Z</t>
+          <t>KIT4M0556351956H</t>
         </is>
       </c>
       <c r="C1051" s="2" t="inlineStr">
         <is>
-          <t>812804</t>
+          <t>814477</t>
         </is>
       </c>
       <c r="D1051" s="2" t="inlineStr">
@@ -31975,11 +31975,11 @@
         </is>
       </c>
       <c r="E1051" s="3" t="n">
-        <v>4.69</v>
+        <v>18.11</v>
       </c>
       <c r="F1051" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -31991,12 +31991,12 @@
       </c>
       <c r="B1052" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563537G4G</t>
+          <t>KIT4M054138125NW</t>
         </is>
       </c>
       <c r="C1052" s="2" t="inlineStr">
         <is>
-          <t>814456</t>
+          <t>812826</t>
         </is>
       </c>
       <c r="D1052" s="2" t="inlineStr">
@@ -32005,11 +32005,11 @@
         </is>
       </c>
       <c r="E1052" s="3" t="n">
-        <v>4.59</v>
+        <v>17.22</v>
       </c>
       <c r="F1052" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32021,12 +32021,12 @@
       </c>
       <c r="B1053" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047372KJ</t>
+          <t>KIT4M05563598Z74</t>
         </is>
       </c>
       <c r="C1053" s="2" t="inlineStr">
         <is>
-          <t>809658</t>
+          <t>814474</t>
         </is>
       </c>
       <c r="D1053" s="2" t="inlineStr">
@@ -32035,11 +32035,11 @@
         </is>
       </c>
       <c r="E1053" s="3" t="n">
-        <v>4.56</v>
+        <v>16.03</v>
       </c>
       <c r="F1053" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32051,12 +32051,12 @@
       </c>
       <c r="B1054" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635238J6</t>
+          <t>KIT4M03867737P9P</t>
         </is>
       </c>
       <c r="C1054" s="2" t="inlineStr">
         <is>
-          <t>814449</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="D1054" s="2" t="inlineStr">
@@ -32065,11 +32065,11 @@
         </is>
       </c>
       <c r="E1054" s="3" t="n">
-        <v>4.53</v>
+        <v>15.72</v>
       </c>
       <c r="F1054" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32081,12 +32081,12 @@
       </c>
       <c r="B1055" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635834N7</t>
+          <t>KIT4M05413826Z6Z</t>
         </is>
       </c>
       <c r="C1055" s="2" t="inlineStr">
         <is>
-          <t>814462</t>
+          <t>812804</t>
         </is>
       </c>
       <c r="D1055" s="2" t="inlineStr">
@@ -32095,11 +32095,11 @@
         </is>
       </c>
       <c r="E1055" s="3" t="n">
-        <v>4.39</v>
+        <v>15.49</v>
       </c>
       <c r="F1055" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32111,12 +32111,12 @@
       </c>
       <c r="B1056" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872537SGZ</t>
+          <t>KIT4M03867749CW5</t>
         </is>
       </c>
       <c r="C1056" s="2" t="inlineStr">
         <is>
-          <t>816073</t>
+          <t>809877</t>
         </is>
       </c>
       <c r="D1056" s="2" t="inlineStr">
@@ -32125,11 +32125,11 @@
         </is>
       </c>
       <c r="E1056" s="3" t="n">
-        <v>4.24</v>
+        <v>15.44</v>
       </c>
       <c r="F1056" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32141,12 +32141,12 @@
       </c>
       <c r="B1057" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563514P8T</t>
+          <t>KIT4M05563551N6Q</t>
         </is>
       </c>
       <c r="C1057" s="2" t="inlineStr">
         <is>
-          <t>814436</t>
+          <t>814450</t>
         </is>
       </c>
       <c r="D1057" s="2" t="inlineStr">
@@ -32155,11 +32155,11 @@
         </is>
       </c>
       <c r="E1057" s="3" t="n">
-        <v>4.01</v>
+        <v>15.44</v>
       </c>
       <c r="F1057" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32171,12 +32171,12 @@
       </c>
       <c r="B1058" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138318Q7</t>
+          <t>KIT4M04158951RH6</t>
         </is>
       </c>
       <c r="C1058" s="2" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>809614</t>
         </is>
       </c>
       <c r="D1058" s="2" t="inlineStr">
@@ -32185,11 +32185,11 @@
         </is>
       </c>
       <c r="E1058" s="3" t="n">
-        <v>3.94</v>
+        <v>15.21</v>
       </c>
       <c r="F1058" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32201,12 +32201,12 @@
       </c>
       <c r="B1059" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604740BM6</t>
+          <t>KIT4M05563537G4G</t>
         </is>
       </c>
       <c r="C1059" s="2" t="inlineStr">
         <is>
-          <t>809872</t>
+          <t>814456</t>
         </is>
       </c>
       <c r="D1059" s="2" t="inlineStr">
@@ -32215,11 +32215,11 @@
         </is>
       </c>
       <c r="E1059" s="3" t="n">
-        <v>3.71</v>
+        <v>15.13</v>
       </c>
       <c r="F1059" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32231,12 +32231,12 @@
       </c>
       <c r="B1060" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413796V9K</t>
+          <t>KIT4M055635227ZR</t>
         </is>
       </c>
       <c r="C1060" s="2" t="inlineStr">
         <is>
-          <t>812820</t>
+          <t>814482</t>
         </is>
       </c>
       <c r="D1060" s="2" t="inlineStr">
@@ -32245,11 +32245,11 @@
         </is>
       </c>
       <c r="E1060" s="3" t="n">
-        <v>3.62</v>
+        <v>14.34</v>
       </c>
       <c r="F1060" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32261,12 +32261,12 @@
       </c>
       <c r="B1061" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413785QCG</t>
+          <t>KIT4M05413783PFQ</t>
         </is>
       </c>
       <c r="C1061" s="2" t="inlineStr">
         <is>
-          <t>812806</t>
+          <t>812845</t>
         </is>
       </c>
       <c r="D1061" s="2" t="inlineStr">
@@ -32275,11 +32275,11 @@
         </is>
       </c>
       <c r="E1061" s="3" t="n">
-        <v>3.57</v>
+        <v>13.74</v>
       </c>
       <c r="F1061" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32291,12 +32291,12 @@
       </c>
       <c r="B1062" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368206BZP</t>
+          <t>KIT4M05872528P9D</t>
         </is>
       </c>
       <c r="C1062" s="2" t="inlineStr">
         <is>
-          <t>810645</t>
+          <t>816089</t>
         </is>
       </c>
       <c r="D1062" s="2" t="inlineStr">
@@ -32305,11 +32305,11 @@
         </is>
       </c>
       <c r="E1062" s="3" t="n">
-        <v>3.32</v>
+        <v>13.65</v>
       </c>
       <c r="F1062" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32321,12 +32321,12 @@
       </c>
       <c r="B1063" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635227ZR</t>
+          <t>KIT4M05799709G5Q</t>
         </is>
       </c>
       <c r="C1063" s="2" t="inlineStr">
         <is>
-          <t>814482</t>
+          <t>816274</t>
         </is>
       </c>
       <c r="D1063" s="2" t="inlineStr">
@@ -32335,11 +32335,11 @@
         </is>
       </c>
       <c r="E1063" s="3" t="n">
-        <v>3.29</v>
+        <v>13.59</v>
       </c>
       <c r="F1063" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32351,12 +32351,12 @@
       </c>
       <c r="B1064" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413801QJB</t>
+          <t>KIT4M05563511FF4</t>
         </is>
       </c>
       <c r="C1064" s="2" t="inlineStr">
         <is>
-          <t>812824</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="D1064" s="2" t="inlineStr">
@@ -32365,11 +32365,11 @@
         </is>
       </c>
       <c r="E1064" s="3" t="n">
-        <v>3.23</v>
+        <v>13.43</v>
       </c>
       <c r="F1064" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32381,12 +32381,12 @@
       </c>
       <c r="B1065" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563603CP4</t>
+          <t>KIT4M04475159PMD</t>
         </is>
       </c>
       <c r="C1065" s="2" t="inlineStr">
         <is>
-          <t>814447</t>
+          <t>809868</t>
         </is>
       </c>
       <c r="D1065" s="2" t="inlineStr">
@@ -32395,11 +32395,11 @@
         </is>
       </c>
       <c r="E1065" s="3" t="n">
-        <v>3.03</v>
+        <v>13.11</v>
       </c>
       <c r="F1065" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32411,12 +32411,12 @@
       </c>
       <c r="B1066" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413803FDK</t>
+          <t>KIT4M05872537SGZ</t>
         </is>
       </c>
       <c r="C1066" s="2" t="inlineStr">
         <is>
-          <t>812850</t>
+          <t>816073</t>
         </is>
       </c>
       <c r="D1066" s="2" t="inlineStr">
@@ -32425,11 +32425,11 @@
         </is>
       </c>
       <c r="E1066" s="3" t="n">
-        <v>2.99</v>
+        <v>13.09</v>
       </c>
       <c r="F1066" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32441,12 +32441,12 @@
       </c>
       <c r="B1067" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413797HK5</t>
+          <t>KIT4M054138318Q7</t>
         </is>
       </c>
       <c r="C1067" s="2" t="inlineStr">
         <is>
-          <t>812808</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="D1067" s="2" t="inlineStr">
@@ -32455,11 +32455,11 @@
         </is>
       </c>
       <c r="E1067" s="3" t="n">
-        <v>2.9</v>
+        <v>13</v>
       </c>
       <c r="F1067" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32471,12 +32471,12 @@
       </c>
       <c r="B1068" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563562F45</t>
+          <t>KIT4M05413785QCG</t>
         </is>
       </c>
       <c r="C1068" s="2" t="inlineStr">
         <is>
-          <t>814443</t>
+          <t>812806</t>
         </is>
       </c>
       <c r="D1068" s="2" t="inlineStr">
@@ -32485,11 +32485,11 @@
         </is>
       </c>
       <c r="E1068" s="3" t="n">
-        <v>2.89</v>
+        <v>12.9</v>
       </c>
       <c r="F1068" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32501,12 +32501,12 @@
       </c>
       <c r="B1069" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563551N6Q</t>
+          <t>KIT4M05563528MKX</t>
         </is>
       </c>
       <c r="C1069" s="2" t="inlineStr">
         <is>
-          <t>814450</t>
+          <t>814471</t>
         </is>
       </c>
       <c r="D1069" s="2" t="inlineStr">
@@ -32515,11 +32515,11 @@
         </is>
       </c>
       <c r="E1069" s="3" t="n">
-        <v>2.87</v>
+        <v>12.18</v>
       </c>
       <c r="F1069" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32531,12 +32531,12 @@
       </c>
       <c r="B1070" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872530RPF</t>
+          <t>KIT4M055635158PC</t>
         </is>
       </c>
       <c r="C1070" s="2" t="inlineStr">
         <is>
-          <t>816079</t>
+          <t>814457</t>
         </is>
       </c>
       <c r="D1070" s="2" t="inlineStr">
@@ -32545,11 +32545,11 @@
         </is>
       </c>
       <c r="E1070" s="3" t="n">
-        <v>2.84</v>
+        <v>12.06</v>
       </c>
       <c r="F1070" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32561,12 +32561,12 @@
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563511FF4</t>
+          <t>KIT4M055635238J6</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>814449</t>
         </is>
       </c>
       <c r="D1071" s="2" t="inlineStr">
@@ -32575,11 +32575,11 @@
         </is>
       </c>
       <c r="E1071" s="3" t="n">
-        <v>2.75</v>
+        <v>11.92</v>
       </c>
       <c r="F1071" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32591,12 +32591,12 @@
       </c>
       <c r="B1072" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563531XSB</t>
+          <t>KIT4M05563606ZRC</t>
         </is>
       </c>
       <c r="C1072" s="2" t="inlineStr">
         <is>
-          <t>814469</t>
+          <t>814464</t>
         </is>
       </c>
       <c r="D1072" s="2" t="inlineStr">
@@ -32605,11 +32605,11 @@
         </is>
       </c>
       <c r="E1072" s="3" t="n">
-        <v>2.68</v>
+        <v>11.53</v>
       </c>
       <c r="F1072" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32621,12 +32621,12 @@
       </c>
       <c r="B1073" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563533M9N</t>
+          <t>KIT4M05563603CP4</t>
         </is>
       </c>
       <c r="C1073" s="2" t="inlineStr">
         <is>
-          <t>814485</t>
+          <t>814447</t>
         </is>
       </c>
       <c r="D1073" s="2" t="inlineStr">
@@ -32635,11 +32635,11 @@
         </is>
       </c>
       <c r="E1073" s="3" t="n">
-        <v>2.65</v>
+        <v>11.42</v>
       </c>
       <c r="F1073" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32651,12 +32651,12 @@
       </c>
       <c r="B1074" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413782GHW</t>
+          <t>KIT4M054138324MW</t>
         </is>
       </c>
       <c r="C1074" s="2" t="inlineStr">
         <is>
-          <t>812835</t>
+          <t>812834</t>
         </is>
       </c>
       <c r="D1074" s="2" t="inlineStr">
@@ -32665,11 +32665,11 @@
         </is>
       </c>
       <c r="E1074" s="3" t="n">
-        <v>2.49</v>
+        <v>11.25</v>
       </c>
       <c r="F1074" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32681,12 +32681,12 @@
       </c>
       <c r="B1075" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563590ZFQ</t>
+          <t>KIT4M055635305RS</t>
         </is>
       </c>
       <c r="C1075" s="2" t="inlineStr">
         <is>
-          <t>814461</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="D1075" s="2" t="inlineStr">
@@ -32695,11 +32695,11 @@
         </is>
       </c>
       <c r="E1075" s="3" t="n">
-        <v>2.48</v>
+        <v>11.25</v>
       </c>
       <c r="F1075" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32711,12 +32711,12 @@
       </c>
       <c r="B1076" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635088NK</t>
+          <t>KIT4M05413811F4Q</t>
         </is>
       </c>
       <c r="C1076" s="2" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>810104</t>
         </is>
       </c>
       <c r="D1076" s="2" t="inlineStr">
@@ -32725,11 +32725,11 @@
         </is>
       </c>
       <c r="E1076" s="3" t="n">
-        <v>2.42</v>
+        <v>11.13</v>
       </c>
       <c r="F1076" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32741,12 +32741,12 @@
       </c>
       <c r="B1077" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556351956H</t>
+          <t>KIT4M03986267RWH</t>
         </is>
       </c>
       <c r="C1077" s="2" t="inlineStr">
         <is>
-          <t>814477</t>
+          <t>809616</t>
         </is>
       </c>
       <c r="D1077" s="2" t="inlineStr">
@@ -32755,11 +32755,11 @@
         </is>
       </c>
       <c r="E1077" s="3" t="n">
-        <v>2.39</v>
+        <v>10.53</v>
       </c>
       <c r="F1077" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32771,12 +32771,12 @@
       </c>
       <c r="B1078" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04158951RH6</t>
+          <t>KIT4M05872508VTN</t>
         </is>
       </c>
       <c r="C1078" s="2" t="inlineStr">
         <is>
-          <t>809614</t>
+          <t>816076</t>
         </is>
       </c>
       <c r="D1078" s="2" t="inlineStr">
@@ -32785,11 +32785,11 @@
         </is>
       </c>
       <c r="E1078" s="3" t="n">
-        <v>2.34</v>
+        <v>10.45</v>
       </c>
       <c r="F1078" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32801,12 +32801,12 @@
       </c>
       <c r="B1079" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872528P9D</t>
+          <t>KIT4M05563579H9F</t>
         </is>
       </c>
       <c r="C1079" s="2" t="inlineStr">
         <is>
-          <t>816089</t>
+          <t>814480</t>
         </is>
       </c>
       <c r="D1079" s="2" t="inlineStr">
@@ -32815,11 +32815,11 @@
         </is>
       </c>
       <c r="E1079" s="3" t="n">
-        <v>2.27</v>
+        <v>10.2</v>
       </c>
       <c r="F1079" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32831,12 +32831,12 @@
       </c>
       <c r="B1080" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413805MKQ</t>
+          <t>KIT4M055635088NK</t>
         </is>
       </c>
       <c r="C1080" s="2" t="inlineStr">
         <is>
-          <t>812849</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="D1080" s="2" t="inlineStr">
@@ -32845,11 +32845,11 @@
         </is>
       </c>
       <c r="E1080" s="3" t="n">
-        <v>2.21</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="F1080" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32861,12 +32861,12 @@
       </c>
       <c r="B1081" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635305RS</t>
+          <t>KIT4M05368206BZP</t>
         </is>
       </c>
       <c r="C1081" s="2" t="inlineStr">
         <is>
-          <t>814440</t>
+          <t>810645</t>
         </is>
       </c>
       <c r="D1081" s="2" t="inlineStr">
@@ -32875,11 +32875,11 @@
         </is>
       </c>
       <c r="E1081" s="3" t="n">
-        <v>2.17</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="F1081" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32891,12 +32891,12 @@
       </c>
       <c r="B1082" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799663CPM</t>
+          <t>KIT4M05413836KJC</t>
         </is>
       </c>
       <c r="C1082" s="2" t="inlineStr">
         <is>
-          <t>816272</t>
+          <t>810097</t>
         </is>
       </c>
       <c r="D1082" s="2" t="inlineStr">
@@ -32905,11 +32905,11 @@
         </is>
       </c>
       <c r="E1082" s="3" t="n">
-        <v>2.16</v>
+        <v>9.57</v>
       </c>
       <c r="F1082" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32921,12 +32921,12 @@
       </c>
       <c r="B1083" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872508VTN</t>
+          <t>KIT4M05413784W4K</t>
         </is>
       </c>
       <c r="C1083" s="2" t="inlineStr">
         <is>
-          <t>816076</t>
+          <t>812821</t>
         </is>
       </c>
       <c r="D1083" s="2" t="inlineStr">
@@ -32935,11 +32935,11 @@
         </is>
       </c>
       <c r="E1083" s="3" t="n">
-        <v>1.87</v>
+        <v>9.5</v>
       </c>
       <c r="F1083" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32951,12 +32951,12 @@
       </c>
       <c r="B1084" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725299QP</t>
+          <t>KIT4M05368219KRH</t>
         </is>
       </c>
       <c r="C1084" s="2" t="inlineStr">
         <is>
-          <t>816080</t>
+          <t>810646</t>
         </is>
       </c>
       <c r="D1084" s="2" t="inlineStr">
@@ -32965,11 +32965,11 @@
         </is>
       </c>
       <c r="E1084" s="3" t="n">
-        <v>1.8</v>
+        <v>9.35</v>
       </c>
       <c r="F1084" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -32981,12 +32981,12 @@
       </c>
       <c r="B1085" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799717WZV</t>
+          <t>KIT4M05563514P8T</t>
         </is>
       </c>
       <c r="C1085" s="2" t="inlineStr">
         <is>
-          <t>816280</t>
+          <t>814436</t>
         </is>
       </c>
       <c r="D1085" s="2" t="inlineStr">
@@ -32995,11 +32995,11 @@
         </is>
       </c>
       <c r="E1085" s="3" t="n">
-        <v>1.66</v>
+        <v>9.15</v>
       </c>
       <c r="F1085" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33011,12 +33011,12 @@
       </c>
       <c r="B1086" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413779VSD</t>
+          <t>KIT4M05872507528</t>
         </is>
       </c>
       <c r="C1086" s="2" t="inlineStr">
         <is>
-          <t>810103</t>
+          <t>816083</t>
         </is>
       </c>
       <c r="D1086" s="2" t="inlineStr">
@@ -33025,11 +33025,11 @@
         </is>
       </c>
       <c r="E1086" s="3" t="n">
-        <v>1.62</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F1086" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33041,12 +33041,12 @@
       </c>
       <c r="B1087" s="2" t="inlineStr">
         <is>
-          <t>KIT4M038677586ZX</t>
+          <t>KIT4M04604740BM6</t>
         </is>
       </c>
       <c r="C1087" s="2" t="inlineStr">
         <is>
-          <t>809623</t>
+          <t>809872</t>
         </is>
       </c>
       <c r="D1087" s="2" t="inlineStr">
@@ -33055,11 +33055,11 @@
         </is>
       </c>
       <c r="E1087" s="3" t="n">
-        <v>1.59</v>
+        <v>9.09</v>
       </c>
       <c r="F1087" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33071,12 +33071,12 @@
       </c>
       <c r="B1088" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563606ZRC</t>
+          <t>KIT4M05799663CPM</t>
         </is>
       </c>
       <c r="C1088" s="2" t="inlineStr">
         <is>
-          <t>814464</t>
+          <t>816272</t>
         </is>
       </c>
       <c r="D1088" s="2" t="inlineStr">
@@ -33085,11 +33085,11 @@
         </is>
       </c>
       <c r="E1088" s="3" t="n">
-        <v>1.52</v>
+        <v>9.09</v>
       </c>
       <c r="F1088" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33101,12 +33101,12 @@
       </c>
       <c r="B1089" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563598Z74</t>
+          <t>KIT4M025787739XF</t>
         </is>
       </c>
       <c r="C1089" s="2" t="inlineStr">
         <is>
-          <t>814474</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="D1089" s="2" t="inlineStr">
@@ -33115,11 +33115,11 @@
         </is>
       </c>
       <c r="E1089" s="3" t="n">
-        <v>1.51</v>
+        <v>8.98</v>
       </c>
       <c r="F1089" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33131,12 +33131,12 @@
       </c>
       <c r="B1090" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138007JF</t>
+          <t>KIT4M05368221HQ5</t>
         </is>
       </c>
       <c r="C1090" s="2" t="inlineStr">
         <is>
-          <t>810095</t>
+          <t>810834</t>
         </is>
       </c>
       <c r="D1090" s="2" t="inlineStr">
@@ -33145,11 +33145,11 @@
         </is>
       </c>
       <c r="E1090" s="3" t="n">
-        <v>1.5</v>
+        <v>8.92</v>
       </c>
       <c r="F1090" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33161,12 +33161,12 @@
       </c>
       <c r="B1091" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867749CW5</t>
+          <t>KIT4M054138189C7</t>
         </is>
       </c>
       <c r="C1091" s="2" t="inlineStr">
         <is>
-          <t>809877</t>
+          <t>812831</t>
         </is>
       </c>
       <c r="D1091" s="2" t="inlineStr">
@@ -33175,7 +33175,7 @@
         </is>
       </c>
       <c r="E1091" s="3" t="n">
-        <v>1.31</v>
+        <v>8.85</v>
       </c>
       <c r="F1091" s="2" t="inlineStr">
         <is>
@@ -33191,12 +33191,12 @@
       </c>
       <c r="B1092" s="2" t="inlineStr">
         <is>
-          <t>KIT4M025787739XF</t>
+          <t>KIT4M058725299QP</t>
         </is>
       </c>
       <c r="C1092" s="2" t="inlineStr">
         <is>
-          <t>809864</t>
+          <t>816080</t>
         </is>
       </c>
       <c r="D1092" s="2" t="inlineStr">
@@ -33205,11 +33205,11 @@
         </is>
       </c>
       <c r="E1092" s="3" t="n">
-        <v>1.25</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F1092" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33221,12 +33221,12 @@
       </c>
       <c r="B1093" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413836KJC</t>
+          <t>KIT4M05563562F45</t>
         </is>
       </c>
       <c r="C1093" s="2" t="inlineStr">
         <is>
-          <t>810097</t>
+          <t>814443</t>
         </is>
       </c>
       <c r="D1093" s="2" t="inlineStr">
@@ -33235,11 +33235,11 @@
         </is>
       </c>
       <c r="E1093" s="3" t="n">
-        <v>1.17</v>
+        <v>7.79</v>
       </c>
       <c r="F1093" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33251,12 +33251,12 @@
       </c>
       <c r="B1094" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368201SNV</t>
+          <t>KIT4M05413779VSD</t>
         </is>
       </c>
       <c r="C1094" s="2" t="inlineStr">
         <is>
-          <t>810651</t>
+          <t>810103</t>
         </is>
       </c>
       <c r="D1094" s="2" t="inlineStr">
@@ -33265,11 +33265,11 @@
         </is>
       </c>
       <c r="E1094" s="3" t="n">
-        <v>1.15</v>
+        <v>7.69</v>
       </c>
       <c r="F1094" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33281,12 +33281,12 @@
       </c>
       <c r="B1095" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563526WNC</t>
+          <t>KIT4M054138007JF</t>
         </is>
       </c>
       <c r="C1095" s="2" t="inlineStr">
         <is>
-          <t>814463</t>
+          <t>810095</t>
         </is>
       </c>
       <c r="D1095" s="2" t="inlineStr">
@@ -33295,11 +33295,11 @@
         </is>
       </c>
       <c r="E1095" s="3" t="n">
-        <v>1.14</v>
+        <v>7.57</v>
       </c>
       <c r="F1095" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33311,12 +33311,12 @@
       </c>
       <c r="B1096" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866596RZG</t>
+          <t>KIT4M038677586ZX</t>
         </is>
       </c>
       <c r="C1096" s="2" t="inlineStr">
         <is>
-          <t>809869</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="D1096" s="2" t="inlineStr">
@@ -33325,11 +33325,11 @@
         </is>
       </c>
       <c r="E1096" s="3" t="n">
-        <v>1.05</v>
+        <v>7.37</v>
       </c>
       <c r="F1096" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33341,12 +33341,12 @@
       </c>
       <c r="B1097" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604745G8Z</t>
+          <t>KIT4M05563533M9N</t>
         </is>
       </c>
       <c r="C1097" s="2" t="inlineStr">
         <is>
-          <t>809661</t>
+          <t>814485</t>
         </is>
       </c>
       <c r="D1097" s="2" t="inlineStr">
@@ -33355,11 +33355,11 @@
         </is>
       </c>
       <c r="E1097" s="3" t="n">
-        <v>1.01</v>
+        <v>7.3</v>
       </c>
       <c r="F1097" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33371,12 +33371,12 @@
       </c>
       <c r="B1098" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058724975J4</t>
+          <t>KIT4M05563526WNC</t>
         </is>
       </c>
       <c r="C1098" s="2" t="inlineStr">
         <is>
-          <t>816075</t>
+          <t>814463</t>
         </is>
       </c>
       <c r="D1098" s="2" t="inlineStr">
@@ -33385,11 +33385,11 @@
         </is>
       </c>
       <c r="E1098" s="3" t="n">
-        <v>0.93</v>
+        <v>7.18</v>
       </c>
       <c r="F1098" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33401,12 +33401,12 @@
       </c>
       <c r="B1099" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138249M8</t>
+          <t>KIT4M05563509CHJ</t>
         </is>
       </c>
       <c r="C1099" s="2" t="inlineStr">
         <is>
-          <t>812794</t>
+          <t>814431</t>
         </is>
       </c>
       <c r="D1099" s="2" t="inlineStr">
@@ -33415,11 +33415,11 @@
         </is>
       </c>
       <c r="E1099" s="3" t="n">
-        <v>0.91</v>
+        <v>6.8</v>
       </c>
       <c r="F1099" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33431,12 +33431,12 @@
       </c>
       <c r="B1100" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413783PFQ</t>
+          <t>KIT4M05413805MKQ</t>
         </is>
       </c>
       <c r="C1100" s="2" t="inlineStr">
         <is>
-          <t>812845</t>
+          <t>812849</t>
         </is>
       </c>
       <c r="D1100" s="2" t="inlineStr">
@@ -33445,11 +33445,11 @@
         </is>
       </c>
       <c r="E1100" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>6.47</v>
       </c>
       <c r="F1100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33461,12 +33461,12 @@
       </c>
       <c r="B1101" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604742S6S</t>
+          <t>KIT4M04475128THH</t>
         </is>
       </c>
       <c r="C1101" s="2" t="inlineStr">
         <is>
-          <t>809874</t>
+          <t>809860</t>
         </is>
       </c>
       <c r="D1101" s="2" t="inlineStr">
@@ -33475,11 +33475,11 @@
         </is>
       </c>
       <c r="E1101" s="3" t="n">
-        <v>0.64</v>
+        <v>5.97</v>
       </c>
       <c r="F1101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33491,12 +33491,12 @@
       </c>
       <c r="B1102" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872586VCH</t>
+          <t>KIT4M05413782GHW</t>
         </is>
       </c>
       <c r="C1102" s="2" t="inlineStr">
         <is>
-          <t>816068</t>
+          <t>812835</t>
         </is>
       </c>
       <c r="D1102" s="2" t="inlineStr">
@@ -33505,11 +33505,11 @@
         </is>
       </c>
       <c r="E1102" s="3" t="n">
-        <v>0.64</v>
+        <v>5.96</v>
       </c>
       <c r="F1102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33521,12 +33521,12 @@
       </c>
       <c r="B1103" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986267RWH</t>
+          <t>KIT4M04158973M2C</t>
         </is>
       </c>
       <c r="C1103" s="2" t="inlineStr">
         <is>
-          <t>809616</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="D1103" s="2" t="inlineStr">
@@ -33535,7 +33535,7 @@
         </is>
       </c>
       <c r="E1103" s="3" t="n">
-        <v>0.52</v>
+        <v>5.91</v>
       </c>
       <c r="F1103" s="2" t="inlineStr">
         <is>
@@ -33551,12 +33551,12 @@
       </c>
       <c r="B1104" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475128THH</t>
+          <t>KIT4M05413803FDK</t>
         </is>
       </c>
       <c r="C1104" s="2" t="inlineStr">
         <is>
-          <t>809860</t>
+          <t>812850</t>
         </is>
       </c>
       <c r="D1104" s="2" t="inlineStr">
@@ -33565,11 +33565,11 @@
         </is>
       </c>
       <c r="E1104" s="3" t="n">
-        <v>0.51</v>
+        <v>5.27</v>
       </c>
       <c r="F1104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33581,12 +33581,12 @@
       </c>
       <c r="B1105" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872516CJM</t>
+          <t>KIT4M05563531XSB</t>
         </is>
       </c>
       <c r="C1105" s="2" t="inlineStr">
         <is>
-          <t>816087</t>
+          <t>814469</t>
         </is>
       </c>
       <c r="D1105" s="2" t="inlineStr">
@@ -33595,11 +33595,11 @@
         </is>
       </c>
       <c r="E1105" s="3" t="n">
-        <v>0.48</v>
+        <v>5.14</v>
       </c>
       <c r="F1105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33611,12 +33611,12 @@
       </c>
       <c r="B1106" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138125NW</t>
+          <t>KIT4M05413796V9K</t>
         </is>
       </c>
       <c r="C1106" s="2" t="inlineStr">
         <is>
-          <t>812826</t>
+          <t>812820</t>
         </is>
       </c>
       <c r="D1106" s="2" t="inlineStr">
@@ -33625,11 +33625,11 @@
         </is>
       </c>
       <c r="E1106" s="3" t="n">
-        <v>0.45</v>
+        <v>5.08</v>
       </c>
       <c r="F1106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33641,12 +33641,12 @@
       </c>
       <c r="B1107" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138074NS</t>
+          <t>KIT4M05872530RPF</t>
         </is>
       </c>
       <c r="C1107" s="2" t="inlineStr">
         <is>
-          <t>812816</t>
+          <t>816079</t>
         </is>
       </c>
       <c r="D1107" s="2" t="inlineStr">
@@ -33655,11 +33655,11 @@
         </is>
       </c>
       <c r="E1107" s="3" t="n">
-        <v>0.41</v>
+        <v>4.94</v>
       </c>
       <c r="F1107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33671,12 +33671,12 @@
       </c>
       <c r="B1108" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563529K2D</t>
+          <t>KIT4M05413797HK5</t>
         </is>
       </c>
       <c r="C1108" s="2" t="inlineStr">
         <is>
-          <t>814473</t>
+          <t>812808</t>
         </is>
       </c>
       <c r="D1108" s="2" t="inlineStr">
@@ -33685,11 +33685,11 @@
         </is>
       </c>
       <c r="E1108" s="3" t="n">
-        <v>0.29</v>
+        <v>4.56</v>
       </c>
       <c r="F1108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33701,25 +33701,25 @@
       </c>
       <c r="B1109" s="2" t="inlineStr">
         <is>
-          <t>KIT4P00066070HN4</t>
+          <t>KIT4M05368201SNV</t>
         </is>
       </c>
       <c r="C1109" s="2" t="inlineStr">
         <is>
-          <t>807636</t>
+          <t>810651</t>
         </is>
       </c>
       <c r="D1109" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E1109" s="3" t="n">
-        <v>0.27</v>
+        <v>4.07</v>
       </c>
       <c r="F1109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33731,12 +33731,12 @@
       </c>
       <c r="B1110" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563548P9Q</t>
+          <t>KIT4M054138249M8</t>
         </is>
       </c>
       <c r="C1110" s="2" t="inlineStr">
         <is>
-          <t>814468</t>
+          <t>812794</t>
         </is>
       </c>
       <c r="D1110" s="2" t="inlineStr">
@@ -33745,11 +33745,11 @@
         </is>
       </c>
       <c r="E1110" s="3" t="n">
-        <v>0.21</v>
+        <v>3.75</v>
       </c>
       <c r="F1110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33761,12 +33761,12 @@
       </c>
       <c r="B1111" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872555BJR</t>
+          <t>KIT4M03866596RZG</t>
         </is>
       </c>
       <c r="C1111" s="2" t="inlineStr">
         <is>
-          <t>816074</t>
+          <t>809869</t>
         </is>
       </c>
       <c r="D1111" s="2" t="inlineStr">
@@ -33775,11 +33775,11 @@
         </is>
       </c>
       <c r="E1111" s="3" t="n">
-        <v>0.21</v>
+        <v>3.17</v>
       </c>
       <c r="F1111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33791,12 +33791,12 @@
       </c>
       <c r="B1112" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413811F4Q</t>
+          <t>KIT4M05872516CJM</t>
         </is>
       </c>
       <c r="C1112" s="2" t="inlineStr">
         <is>
-          <t>810104</t>
+          <t>816087</t>
         </is>
       </c>
       <c r="D1112" s="2" t="inlineStr">
@@ -33805,11 +33805,11 @@
         </is>
       </c>
       <c r="E1112" s="3" t="n">
-        <v>0.19</v>
+        <v>3.05</v>
       </c>
       <c r="F1112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33821,12 +33821,12 @@
       </c>
       <c r="B1113" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799709G5Q</t>
+          <t>KIT4M05563529K2D</t>
         </is>
       </c>
       <c r="C1113" s="2" t="inlineStr">
         <is>
-          <t>816274</t>
+          <t>814473</t>
         </is>
       </c>
       <c r="D1113" s="2" t="inlineStr">
@@ -33835,11 +33835,11 @@
         </is>
       </c>
       <c r="E1113" s="3" t="n">
-        <v>0.15</v>
+        <v>2.86</v>
       </c>
       <c r="F1113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33851,12 +33851,12 @@
       </c>
       <c r="B1114" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563524MJ4</t>
+          <t>KIT4M054138074NS</t>
         </is>
       </c>
       <c r="C1114" s="2" t="inlineStr">
         <is>
-          <t>814472</t>
+          <t>812816</t>
         </is>
       </c>
       <c r="D1114" s="2" t="inlineStr">
@@ -33865,11 +33865,11 @@
         </is>
       </c>
       <c r="E1114" s="3" t="n">
-        <v>0.1</v>
+        <v>2.37</v>
       </c>
       <c r="F1114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33881,12 +33881,12 @@
       </c>
       <c r="B1115" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368226W57</t>
+          <t>KIT4M04604745G8Z</t>
         </is>
       </c>
       <c r="C1115" s="2" t="inlineStr">
         <is>
-          <t>810833</t>
+          <t>809661</t>
         </is>
       </c>
       <c r="D1115" s="2" t="inlineStr">
@@ -33895,11 +33895,11 @@
         </is>
       </c>
       <c r="E1115" s="3" t="n">
-        <v>0.04</v>
+        <v>1.56</v>
       </c>
       <c r="F1115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33911,12 +33911,12 @@
       </c>
       <c r="B1116" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725265DP</t>
+          <t>KIT4M03986264P49</t>
         </is>
       </c>
       <c r="C1116" s="2" t="inlineStr">
         <is>
-          <t>816192</t>
+          <t>809875</t>
         </is>
       </c>
       <c r="D1116" s="2" t="inlineStr">
@@ -33925,11 +33925,11 @@
         </is>
       </c>
       <c r="E1116" s="3" t="n">
-        <v>0.04</v>
+        <v>1.23</v>
       </c>
       <c r="F1116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33941,12 +33941,12 @@
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413784W4K</t>
+          <t>KIT4M05872586VCH</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
         <is>
-          <t>812821</t>
+          <t>816068</t>
         </is>
       </c>
       <c r="D1117" s="2" t="inlineStr">
@@ -33955,11 +33955,11 @@
         </is>
       </c>
       <c r="E1117" s="3" t="n">
-        <v>0.03</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F1117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -33971,12 +33971,12 @@
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041536494G6</t>
+          <t>KIT4M058725265DP</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
         <is>
-          <t>809617</t>
+          <t>816192</t>
         </is>
       </c>
       <c r="D1118" s="2" t="inlineStr">
@@ -33985,11 +33985,11 @@
         </is>
       </c>
       <c r="E1118" s="3" t="n">
-        <v>0.02</v>
+        <v>0.63</v>
       </c>
       <c r="F1118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -34001,25 +34001,25 @@
       </c>
       <c r="B1119" s="2" t="inlineStr">
         <is>
-          <t>KIT4P0006563862J</t>
+          <t>KIT4M05872555BJR</t>
         </is>
       </c>
       <c r="C1119" s="2" t="inlineStr">
         <is>
-          <t>812927</t>
+          <t>816074</t>
         </is>
       </c>
       <c r="D1119" s="2" t="inlineStr">
         <is>
-          <t>Gen 3</t>
+          <t>Mini</t>
         </is>
       </c>
       <c r="E1119" s="3" t="n">
-        <v>0.01</v>
+        <v>0.61</v>
       </c>
       <c r="F1119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:26</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -34031,25 +34031,25 @@
       </c>
       <c r="B1120" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03476116F45</t>
+          <t>KIT4P000739124KF</t>
         </is>
       </c>
       <c r="C1120" s="2" t="inlineStr">
         <is>
-          <t>809608</t>
+          <t>814640</t>
         </is>
       </c>
       <c r="D1120" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E1120" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F1120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -34061,12 +34061,12 @@
       </c>
       <c r="B1121" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03866627GHD</t>
+          <t>KIT4M05368226W57</t>
         </is>
       </c>
       <c r="C1121" s="2" t="inlineStr">
         <is>
-          <t>809619</t>
+          <t>810833</t>
         </is>
       </c>
       <c r="D1121" s="2" t="inlineStr">
@@ -34075,11 +34075,11 @@
         </is>
       </c>
       <c r="E1121" s="3" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="F1121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -34091,12 +34091,12 @@
       </c>
       <c r="B1122" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03867766NGK</t>
+          <t>KIT4M05563548P9Q</t>
         </is>
       </c>
       <c r="C1122" s="2" t="inlineStr">
         <is>
-          <t>809615</t>
+          <t>814468</t>
         </is>
       </c>
       <c r="D1122" s="2" t="inlineStr">
@@ -34105,11 +34105,11 @@
         </is>
       </c>
       <c r="E1122" s="3" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="F1122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -34121,12 +34121,12 @@
       </c>
       <c r="B1123" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986264P49</t>
+          <t>KIT4M055635779MM</t>
         </is>
       </c>
       <c r="C1123" s="2" t="inlineStr">
         <is>
-          <t>809875</t>
+          <t>814487</t>
         </is>
       </c>
       <c r="D1123" s="2" t="inlineStr">
@@ -34135,11 +34135,11 @@
         </is>
       </c>
       <c r="E1123" s="3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F1123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-05 11:34</t>
         </is>
       </c>
     </row>
@@ -34151,12 +34151,12 @@
       </c>
       <c r="B1124" s="2" t="inlineStr">
         <is>
-          <t>KIT4M03986275Q4M</t>
+          <t>KIT4M05563524MJ4</t>
         </is>
       </c>
       <c r="C1124" s="2" t="inlineStr">
         <is>
-          <t>809621</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="D1124" s="2" t="inlineStr">
@@ -34165,11 +34165,11 @@
         </is>
       </c>
       <c r="E1124" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F1124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="B1125" s="2" t="inlineStr">
         <is>
-          <t>KIT4M041546939GJ</t>
+          <t>KIT4M041536494G6</t>
         </is>
       </c>
       <c r="C1125" s="2" t="inlineStr">
         <is>
-          <t>809607</t>
+          <t>809617</t>
         </is>
       </c>
       <c r="D1125" s="2" t="inlineStr">
@@ -34195,11 +34195,11 @@
         </is>
       </c>
       <c r="E1125" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F1125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -34211,25 +34211,25 @@
       </c>
       <c r="B1126" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0415609166K</t>
+          <t>KIT4P0006563862J</t>
         </is>
       </c>
       <c r="C1126" s="2" t="inlineStr">
         <is>
-          <t>809609</t>
+          <t>812927</t>
         </is>
       </c>
       <c r="D1126" s="2" t="inlineStr">
         <is>
-          <t>Mini</t>
+          <t>Gen 3</t>
         </is>
       </c>
       <c r="E1126" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F1126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:42</t>
+          <t>2026-10-02 09:26</t>
         </is>
       </c>
     </row>
@@ -34241,12 +34241,12 @@
       </c>
       <c r="B1127" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04350554X4Z</t>
+          <t>KIT4M03476116F45</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
         <is>
-          <t>809866</t>
+          <t>809608</t>
         </is>
       </c>
       <c r="D1127" s="2" t="inlineStr">
@@ -34271,12 +34271,12 @@
       </c>
       <c r="B1128" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475152RGR</t>
+          <t>KIT4M03866627GHD</t>
         </is>
       </c>
       <c r="C1128" s="2" t="inlineStr">
         <is>
-          <t>809861</t>
+          <t>809619</t>
         </is>
       </c>
       <c r="D1128" s="2" t="inlineStr">
@@ -34301,12 +34301,12 @@
       </c>
       <c r="B1129" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04475159PMD</t>
+          <t>KIT4M03867766NGK</t>
         </is>
       </c>
       <c r="C1129" s="2" t="inlineStr">
         <is>
-          <t>809868</t>
+          <t>809615</t>
         </is>
       </c>
       <c r="D1129" s="2" t="inlineStr">
@@ -34331,12 +34331,12 @@
       </c>
       <c r="B1130" s="2" t="inlineStr">
         <is>
-          <t>KIT4M044751638F5</t>
+          <t>KIT4M03986275Q4M</t>
         </is>
       </c>
       <c r="C1130" s="2" t="inlineStr">
         <is>
-          <t>809618</t>
+          <t>809621</t>
         </is>
       </c>
       <c r="D1130" s="2" t="inlineStr">
@@ -34361,12 +34361,12 @@
       </c>
       <c r="B1131" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604734ZZX</t>
+          <t>KIT4M041546939GJ</t>
         </is>
       </c>
       <c r="C1131" s="2" t="inlineStr">
         <is>
-          <t>809876</t>
+          <t>809607</t>
         </is>
       </c>
       <c r="D1131" s="2" t="inlineStr">
@@ -34391,12 +34391,12 @@
       </c>
       <c r="B1132" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604736T7C</t>
+          <t>KIT4M0415609166K</t>
         </is>
       </c>
       <c r="C1132" s="2" t="inlineStr">
         <is>
-          <t>809662</t>
+          <t>809609</t>
         </is>
       </c>
       <c r="D1132" s="2" t="inlineStr">
@@ -34421,12 +34421,12 @@
       </c>
       <c r="B1133" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047384RX</t>
+          <t>KIT4M04350554X4Z</t>
         </is>
       </c>
       <c r="C1133" s="2" t="inlineStr">
         <is>
-          <t>809870</t>
+          <t>809866</t>
         </is>
       </c>
       <c r="D1133" s="2" t="inlineStr">
@@ -34451,12 +34451,12 @@
       </c>
       <c r="B1134" s="2" t="inlineStr">
         <is>
-          <t>KIT4M046047397TM</t>
+          <t>KIT4M04475152RGR</t>
         </is>
       </c>
       <c r="C1134" s="2" t="inlineStr">
         <is>
-          <t>809863</t>
+          <t>809861</t>
         </is>
       </c>
       <c r="D1134" s="2" t="inlineStr">
@@ -34481,12 +34481,12 @@
       </c>
       <c r="B1135" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604741P2X</t>
+          <t>KIT4M044751638F5</t>
         </is>
       </c>
       <c r="C1135" s="2" t="inlineStr">
         <is>
-          <t>809871</t>
+          <t>809618</t>
         </is>
       </c>
       <c r="D1135" s="2" t="inlineStr">
@@ -34511,12 +34511,12 @@
       </c>
       <c r="B1136" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604743HSS</t>
+          <t>KIT4M04604734ZZX</t>
         </is>
       </c>
       <c r="C1136" s="2" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>809876</t>
         </is>
       </c>
       <c r="D1136" s="2" t="inlineStr">
@@ -34541,12 +34541,12 @@
       </c>
       <c r="B1137" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604744V6K</t>
+          <t>KIT4M04604736T7C</t>
         </is>
       </c>
       <c r="C1137" s="2" t="inlineStr">
         <is>
-          <t>809659</t>
+          <t>809662</t>
         </is>
       </c>
       <c r="D1137" s="2" t="inlineStr">
@@ -34571,12 +34571,12 @@
       </c>
       <c r="B1138" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04604747TPT</t>
+          <t>KIT4M046047384RX</t>
         </is>
       </c>
       <c r="C1138" s="2" t="inlineStr">
         <is>
-          <t>809873</t>
+          <t>809870</t>
         </is>
       </c>
       <c r="D1138" s="2" t="inlineStr">
@@ -34601,12 +34601,12 @@
       </c>
       <c r="B1139" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0460475549Z</t>
+          <t>KIT4M046047397TM</t>
         </is>
       </c>
       <c r="C1139" s="2" t="inlineStr">
         <is>
-          <t>809859</t>
+          <t>809863</t>
         </is>
       </c>
       <c r="D1139" s="2" t="inlineStr">
@@ -34631,12 +34631,12 @@
       </c>
       <c r="B1140" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606110GTV</t>
+          <t>KIT4M04604741P2X</t>
         </is>
       </c>
       <c r="C1140" s="2" t="inlineStr">
         <is>
-          <t>809660</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="D1140" s="2" t="inlineStr">
@@ -34661,12 +34661,12 @@
       </c>
       <c r="B1141" s="2" t="inlineStr">
         <is>
-          <t>KIT4M04606113TPB</t>
+          <t>KIT4M04604743HSS</t>
         </is>
       </c>
       <c r="C1141" s="2" t="inlineStr">
         <is>
-          <t>809862</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="D1141" s="2" t="inlineStr">
@@ -34691,12 +34691,12 @@
       </c>
       <c r="B1142" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368200MVF</t>
+          <t>KIT4M04604744V6K</t>
         </is>
       </c>
       <c r="C1142" s="2" t="inlineStr">
         <is>
-          <t>810650</t>
+          <t>809659</t>
         </is>
       </c>
       <c r="D1142" s="2" t="inlineStr">
@@ -34721,12 +34721,12 @@
       </c>
       <c r="B1143" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368220FG8</t>
+          <t>KIT4M04604747TPT</t>
         </is>
       </c>
       <c r="C1143" s="2" t="inlineStr">
         <is>
-          <t>810648</t>
+          <t>809873</t>
         </is>
       </c>
       <c r="D1143" s="2" t="inlineStr">
@@ -34751,12 +34751,12 @@
       </c>
       <c r="B1144" s="2" t="inlineStr">
         <is>
-          <t>KIT4M053683324KZ</t>
+          <t>KIT4M0460475549Z</t>
         </is>
       </c>
       <c r="C1144" s="2" t="inlineStr">
         <is>
-          <t>810832</t>
+          <t>809859</t>
         </is>
       </c>
       <c r="D1144" s="2" t="inlineStr">
@@ -34781,12 +34781,12 @@
       </c>
       <c r="B1145" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368336DBC</t>
+          <t>KIT4M04606110GTV</t>
         </is>
       </c>
       <c r="C1145" s="2" t="inlineStr">
         <is>
-          <t>810831</t>
+          <t>809660</t>
         </is>
       </c>
       <c r="D1145" s="2" t="inlineStr">
@@ -34811,12 +34811,12 @@
       </c>
       <c r="B1146" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05368340DMZ</t>
+          <t>KIT4M04606113TPB</t>
         </is>
       </c>
       <c r="C1146" s="2" t="inlineStr">
         <is>
-          <t>810649</t>
+          <t>809862</t>
         </is>
       </c>
       <c r="D1146" s="2" t="inlineStr">
@@ -34841,12 +34841,12 @@
       </c>
       <c r="B1147" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413769796</t>
+          <t>KIT4M05368200MVF</t>
         </is>
       </c>
       <c r="C1147" s="2" t="inlineStr">
         <is>
-          <t>812839</t>
+          <t>810650</t>
         </is>
       </c>
       <c r="D1147" s="2" t="inlineStr">
@@ -34871,12 +34871,12 @@
       </c>
       <c r="B1148" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413770WCC</t>
+          <t>KIT4M05368220FG8</t>
         </is>
       </c>
       <c r="C1148" s="2" t="inlineStr">
         <is>
-          <t>812819</t>
+          <t>810648</t>
         </is>
       </c>
       <c r="D1148" s="2" t="inlineStr">
@@ -34901,12 +34901,12 @@
       </c>
       <c r="B1149" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413772977</t>
+          <t>KIT4M053683324KZ</t>
         </is>
       </c>
       <c r="C1149" s="2" t="inlineStr">
         <is>
-          <t>812841</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="D1149" s="2" t="inlineStr">
@@ -34931,12 +34931,12 @@
       </c>
       <c r="B1150" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413773R6G</t>
+          <t>KIT4M05368336DBC</t>
         </is>
       </c>
       <c r="C1150" s="2" t="inlineStr">
         <is>
-          <t>812807</t>
+          <t>810831</t>
         </is>
       </c>
       <c r="D1150" s="2" t="inlineStr">
@@ -34961,12 +34961,12 @@
       </c>
       <c r="B1151" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413774JZX</t>
+          <t>KIT4M05368340DMZ</t>
         </is>
       </c>
       <c r="C1151" s="2" t="inlineStr">
         <is>
-          <t>812836</t>
+          <t>810649</t>
         </is>
       </c>
       <c r="D1151" s="2" t="inlineStr">
@@ -34991,12 +34991,12 @@
       </c>
       <c r="B1152" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413775N9M</t>
+          <t>KIT4M05413769796</t>
         </is>
       </c>
       <c r="C1152" s="2" t="inlineStr">
         <is>
-          <t>812818</t>
+          <t>812839</t>
         </is>
       </c>
       <c r="D1152" s="2" t="inlineStr">
@@ -35021,12 +35021,12 @@
       </c>
       <c r="B1153" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413777DGG</t>
+          <t>KIT4M05413770WCC</t>
         </is>
       </c>
       <c r="C1153" s="2" t="inlineStr">
         <is>
-          <t>812802</t>
+          <t>812819</t>
         </is>
       </c>
       <c r="D1153" s="2" t="inlineStr">
@@ -35051,12 +35051,12 @@
       </c>
       <c r="B1154" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413778RBR</t>
+          <t>KIT4M05413772977</t>
         </is>
       </c>
       <c r="C1154" s="2" t="inlineStr">
         <is>
-          <t>812843</t>
+          <t>812841</t>
         </is>
       </c>
       <c r="D1154" s="2" t="inlineStr">
@@ -35081,12 +35081,12 @@
       </c>
       <c r="B1155" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413780XFH</t>
+          <t>KIT4M05413773R6G</t>
         </is>
       </c>
       <c r="C1155" s="2" t="inlineStr">
         <is>
-          <t>812833</t>
+          <t>812807</t>
         </is>
       </c>
       <c r="D1155" s="2" t="inlineStr">
@@ -35111,12 +35111,12 @@
       </c>
       <c r="B1156" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413781K6C</t>
+          <t>KIT4M05413774JZX</t>
         </is>
       </c>
       <c r="C1156" s="2" t="inlineStr">
         <is>
-          <t>812798</t>
+          <t>812836</t>
         </is>
       </c>
       <c r="D1156" s="2" t="inlineStr">
@@ -35141,12 +35141,12 @@
       </c>
       <c r="B1157" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413786BXC</t>
+          <t>KIT4M05413775N9M</t>
         </is>
       </c>
       <c r="C1157" s="2" t="inlineStr">
         <is>
-          <t>812838</t>
+          <t>812818</t>
         </is>
       </c>
       <c r="D1157" s="2" t="inlineStr">
@@ -35171,12 +35171,12 @@
       </c>
       <c r="B1158" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137885SM</t>
+          <t>KIT4M05413777DGG</t>
         </is>
       </c>
       <c r="C1158" s="2" t="inlineStr">
         <is>
-          <t>812846</t>
+          <t>812802</t>
         </is>
       </c>
       <c r="D1158" s="2" t="inlineStr">
@@ -35201,12 +35201,12 @@
       </c>
       <c r="B1159" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413789Z8C</t>
+          <t>KIT4M05413778RBR</t>
         </is>
       </c>
       <c r="C1159" s="2" t="inlineStr">
         <is>
-          <t>812840</t>
+          <t>812843</t>
         </is>
       </c>
       <c r="D1159" s="2" t="inlineStr">
@@ -35231,12 +35231,12 @@
       </c>
       <c r="B1160" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413790XCD</t>
+          <t>KIT4M05413780XFH</t>
         </is>
       </c>
       <c r="C1160" s="2" t="inlineStr">
         <is>
-          <t>812822</t>
+          <t>812833</t>
         </is>
       </c>
       <c r="D1160" s="2" t="inlineStr">
@@ -35261,12 +35261,12 @@
       </c>
       <c r="B1161" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413791FK5</t>
+          <t>KIT4M05413781K6C</t>
         </is>
       </c>
       <c r="C1161" s="2" t="inlineStr">
         <is>
-          <t>812842</t>
+          <t>812798</t>
         </is>
       </c>
       <c r="D1161" s="2" t="inlineStr">
@@ -35291,12 +35291,12 @@
       </c>
       <c r="B1162" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413792H8C</t>
+          <t>KIT4M05413786BXC</t>
         </is>
       </c>
       <c r="C1162" s="2" t="inlineStr">
         <is>
-          <t>812803</t>
+          <t>812838</t>
         </is>
       </c>
       <c r="D1162" s="2" t="inlineStr">
@@ -35321,12 +35321,12 @@
       </c>
       <c r="B1163" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137938P7</t>
+          <t>KIT4M054137885SM</t>
         </is>
       </c>
       <c r="C1163" s="2" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>812846</t>
         </is>
       </c>
       <c r="D1163" s="2" t="inlineStr">
@@ -35351,12 +35351,12 @@
       </c>
       <c r="B1164" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413794SSC</t>
+          <t>KIT4M05413789Z8C</t>
         </is>
       </c>
       <c r="C1164" s="2" t="inlineStr">
         <is>
-          <t>812847</t>
+          <t>812840</t>
         </is>
       </c>
       <c r="D1164" s="2" t="inlineStr">
@@ -35381,12 +35381,12 @@
       </c>
       <c r="B1165" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137987GJ</t>
+          <t>KIT4M05413790XCD</t>
         </is>
       </c>
       <c r="C1165" s="2" t="inlineStr">
         <is>
-          <t>812795</t>
+          <t>812822</t>
         </is>
       </c>
       <c r="D1165" s="2" t="inlineStr">
@@ -35411,12 +35411,12 @@
       </c>
       <c r="B1166" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054137997HR</t>
+          <t>KIT4M05413791FK5</t>
         </is>
       </c>
       <c r="C1166" s="2" t="inlineStr">
         <is>
-          <t>812825</t>
+          <t>812842</t>
         </is>
       </c>
       <c r="D1166" s="2" t="inlineStr">
@@ -35441,12 +35441,12 @@
       </c>
       <c r="B1167" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413802FVN</t>
+          <t>KIT4M05413792H8C</t>
         </is>
       </c>
       <c r="C1167" s="2" t="inlineStr">
         <is>
-          <t>812813</t>
+          <t>812803</t>
         </is>
       </c>
       <c r="D1167" s="2" t="inlineStr">
@@ -35471,12 +35471,12 @@
       </c>
       <c r="B1168" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413804SKS</t>
+          <t>KIT4M054137938P7</t>
         </is>
       </c>
       <c r="C1168" s="2" t="inlineStr">
         <is>
-          <t>810102</t>
+          <t>812848</t>
         </is>
       </c>
       <c r="D1168" s="2" t="inlineStr">
@@ -35501,12 +35501,12 @@
       </c>
       <c r="B1169" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413809J58</t>
+          <t>KIT4M05413794SSC</t>
         </is>
       </c>
       <c r="C1169" s="2" t="inlineStr">
         <is>
-          <t>812805</t>
+          <t>812847</t>
         </is>
       </c>
       <c r="D1169" s="2" t="inlineStr">
@@ -35531,12 +35531,12 @@
       </c>
       <c r="B1170" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413810Q4Z</t>
+          <t>KIT4M054137987GJ</t>
         </is>
       </c>
       <c r="C1170" s="2" t="inlineStr">
         <is>
-          <t>812815</t>
+          <t>812795</t>
         </is>
       </c>
       <c r="D1170" s="2" t="inlineStr">
@@ -35561,12 +35561,12 @@
       </c>
       <c r="B1171" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413813HSJ</t>
+          <t>KIT4M054137997HR</t>
         </is>
       </c>
       <c r="C1171" s="2" t="inlineStr">
         <is>
-          <t>812797</t>
+          <t>812825</t>
         </is>
       </c>
       <c r="D1171" s="2" t="inlineStr">
@@ -35591,12 +35591,12 @@
       </c>
       <c r="B1172" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413814GPJ</t>
+          <t>KIT4M05413802FVN</t>
         </is>
       </c>
       <c r="C1172" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>812813</t>
         </is>
       </c>
       <c r="D1172" s="2" t="inlineStr">
@@ -35621,12 +35621,12 @@
       </c>
       <c r="B1173" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0541381584X</t>
+          <t>KIT4M05413804SKS</t>
         </is>
       </c>
       <c r="C1173" s="2" t="inlineStr">
         <is>
-          <t>812810</t>
+          <t>810102</t>
         </is>
       </c>
       <c r="D1173" s="2" t="inlineStr">
@@ -35651,12 +35651,12 @@
       </c>
       <c r="B1174" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413816N8K</t>
+          <t>KIT4M05413809J58</t>
         </is>
       </c>
       <c r="C1174" s="2" t="inlineStr">
         <is>
-          <t>812832</t>
+          <t>812805</t>
         </is>
       </c>
       <c r="D1174" s="2" t="inlineStr">
@@ -35681,12 +35681,12 @@
       </c>
       <c r="B1175" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138175VJ</t>
+          <t>KIT4M05413810Q4Z</t>
         </is>
       </c>
       <c r="C1175" s="2" t="inlineStr">
         <is>
-          <t>812823</t>
+          <t>812815</t>
         </is>
       </c>
       <c r="D1175" s="2" t="inlineStr">
@@ -35711,12 +35711,12 @@
       </c>
       <c r="B1176" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413819JV5</t>
+          <t>KIT4M05413813HSJ</t>
         </is>
       </c>
       <c r="C1176" s="2" t="inlineStr">
         <is>
-          <t>812796</t>
+          <t>812797</t>
         </is>
       </c>
       <c r="D1176" s="2" t="inlineStr">
@@ -35741,12 +35741,12 @@
       </c>
       <c r="B1177" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413820QXJ</t>
+          <t>KIT4M05413814GPJ</t>
         </is>
       </c>
       <c r="C1177" s="2" t="inlineStr">
         <is>
-          <t>810098</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="D1177" s="2" t="inlineStr">
@@ -35771,12 +35771,12 @@
       </c>
       <c r="B1178" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413821GGW</t>
+          <t>KIT4M0541381584X</t>
         </is>
       </c>
       <c r="C1178" s="2" t="inlineStr">
         <is>
-          <t>812830</t>
+          <t>812810</t>
         </is>
       </c>
       <c r="D1178" s="2" t="inlineStr">
@@ -35801,12 +35801,12 @@
       </c>
       <c r="B1179" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138222CP</t>
+          <t>KIT4M05413816N8K</t>
         </is>
       </c>
       <c r="C1179" s="2" t="inlineStr">
         <is>
-          <t>812811</t>
+          <t>812832</t>
         </is>
       </c>
       <c r="D1179" s="2" t="inlineStr">
@@ -35831,12 +35831,12 @@
       </c>
       <c r="B1180" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413823B5P</t>
+          <t>KIT4M054138175VJ</t>
         </is>
       </c>
       <c r="C1180" s="2" t="inlineStr">
         <is>
-          <t>812837</t>
+          <t>812823</t>
         </is>
       </c>
       <c r="D1180" s="2" t="inlineStr">
@@ -35861,12 +35861,12 @@
       </c>
       <c r="B1181" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138257Z7</t>
+          <t>KIT4M05413819JV5</t>
         </is>
       </c>
       <c r="C1181" s="2" t="inlineStr">
         <is>
-          <t>810106</t>
+          <t>812796</t>
         </is>
       </c>
       <c r="D1181" s="2" t="inlineStr">
@@ -35891,12 +35891,12 @@
       </c>
       <c r="B1182" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413827DC4</t>
+          <t>KIT4M05413820QXJ</t>
         </is>
       </c>
       <c r="C1182" s="2" t="inlineStr">
         <is>
-          <t>812829</t>
+          <t>810098</t>
         </is>
       </c>
       <c r="D1182" s="2" t="inlineStr">
@@ -35921,12 +35921,12 @@
       </c>
       <c r="B1183" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413828PCT</t>
+          <t>KIT4M05413821GGW</t>
         </is>
       </c>
       <c r="C1183" s="2" t="inlineStr">
         <is>
-          <t>812799</t>
+          <t>812830</t>
         </is>
       </c>
       <c r="D1183" s="2" t="inlineStr">
@@ -35951,12 +35951,12 @@
       </c>
       <c r="B1184" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138292ZP</t>
+          <t>KIT4M054138222CP</t>
         </is>
       </c>
       <c r="C1184" s="2" t="inlineStr">
         <is>
-          <t>812784</t>
+          <t>812811</t>
         </is>
       </c>
       <c r="D1184" s="2" t="inlineStr">
@@ -35981,12 +35981,12 @@
       </c>
       <c r="B1185" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413830JN7</t>
+          <t>KIT4M05413823B5P</t>
         </is>
       </c>
       <c r="C1185" s="2" t="inlineStr">
         <is>
-          <t>810105</t>
+          <t>812837</t>
         </is>
       </c>
       <c r="D1185" s="2" t="inlineStr">
@@ -36011,12 +36011,12 @@
       </c>
       <c r="B1186" s="2" t="inlineStr">
         <is>
-          <t>KIT4M054138324MW</t>
+          <t>KIT4M054138257Z7</t>
         </is>
       </c>
       <c r="C1186" s="2" t="inlineStr">
         <is>
-          <t>812834</t>
+          <t>810106</t>
         </is>
       </c>
       <c r="D1186" s="2" t="inlineStr">
@@ -36041,12 +36041,12 @@
       </c>
       <c r="B1187" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413834FTH</t>
+          <t>KIT4M05413827DC4</t>
         </is>
       </c>
       <c r="C1187" s="2" t="inlineStr">
         <is>
-          <t>812817</t>
+          <t>812829</t>
         </is>
       </c>
       <c r="D1187" s="2" t="inlineStr">
@@ -36071,12 +36071,12 @@
       </c>
       <c r="B1188" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413835RPF</t>
+          <t>KIT4M05413828PCT</t>
         </is>
       </c>
       <c r="C1188" s="2" t="inlineStr">
         <is>
-          <t>812827</t>
+          <t>812799</t>
         </is>
       </c>
       <c r="D1188" s="2" t="inlineStr">
@@ -36101,12 +36101,12 @@
       </c>
       <c r="B1189" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413839D24</t>
+          <t>KIT4M054138292ZP</t>
         </is>
       </c>
       <c r="C1189" s="2" t="inlineStr">
         <is>
-          <t>810096</t>
+          <t>812784</t>
         </is>
       </c>
       <c r="D1189" s="2" t="inlineStr">
@@ -36131,12 +36131,12 @@
       </c>
       <c r="B1190" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05413840D9J</t>
+          <t>KIT4M05413830JN7</t>
         </is>
       </c>
       <c r="C1190" s="2" t="inlineStr">
         <is>
-          <t>810099</t>
+          <t>810105</t>
         </is>
       </c>
       <c r="D1190" s="2" t="inlineStr">
@@ -36161,12 +36161,12 @@
       </c>
       <c r="B1191" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563503XXP</t>
+          <t>KIT4M05413834FTH</t>
         </is>
       </c>
       <c r="C1191" s="2" t="inlineStr">
         <is>
-          <t>814430</t>
+          <t>812817</t>
         </is>
       </c>
       <c r="D1191" s="2" t="inlineStr">
@@ -36191,12 +36191,12 @@
       </c>
       <c r="B1192" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563505WPS</t>
+          <t>KIT4M05413835RPF</t>
         </is>
       </c>
       <c r="C1192" s="2" t="inlineStr">
         <is>
-          <t>814448</t>
+          <t>812827</t>
         </is>
       </c>
       <c r="D1192" s="2" t="inlineStr">
@@ -36221,12 +36221,12 @@
       </c>
       <c r="B1193" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563510TWC</t>
+          <t>KIT4M05413839D24</t>
         </is>
       </c>
       <c r="C1193" s="2" t="inlineStr">
         <is>
-          <t>814433</t>
+          <t>810096</t>
         </is>
       </c>
       <c r="D1193" s="2" t="inlineStr">
@@ -36251,12 +36251,12 @@
       </c>
       <c r="B1194" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563512GBQ</t>
+          <t>KIT4M05413840D9J</t>
         </is>
       </c>
       <c r="C1194" s="2" t="inlineStr">
         <is>
-          <t>814435</t>
+          <t>810099</t>
         </is>
       </c>
       <c r="D1194" s="2" t="inlineStr">
@@ -36281,12 +36281,12 @@
       </c>
       <c r="B1195" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563513GTF</t>
+          <t>KIT4M05563503XXP</t>
         </is>
       </c>
       <c r="C1195" s="2" t="inlineStr">
         <is>
-          <t>814432</t>
+          <t>814430</t>
         </is>
       </c>
       <c r="D1195" s="2" t="inlineStr">
@@ -36311,12 +36311,12 @@
       </c>
       <c r="B1196" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563517BVR</t>
+          <t>KIT4M05563505WPS</t>
         </is>
       </c>
       <c r="C1196" s="2" t="inlineStr">
         <is>
-          <t>814438</t>
+          <t>814448</t>
         </is>
       </c>
       <c r="D1196" s="2" t="inlineStr">
@@ -36341,12 +36341,12 @@
       </c>
       <c r="B1197" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563518ZJD</t>
+          <t>KIT4M05563510TWC</t>
         </is>
       </c>
       <c r="C1197" s="2" t="inlineStr">
         <is>
-          <t>814451</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="D1197" s="2" t="inlineStr">
@@ -36371,12 +36371,12 @@
       </c>
       <c r="B1198" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563520SH2</t>
+          <t>KIT4M05563512GBQ</t>
         </is>
       </c>
       <c r="C1198" s="2" t="inlineStr">
         <is>
-          <t>814478</t>
+          <t>814435</t>
         </is>
       </c>
       <c r="D1198" s="2" t="inlineStr">
@@ -36401,12 +36401,12 @@
       </c>
       <c r="B1199" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563521ZSX</t>
+          <t>KIT4M05563513GTF</t>
         </is>
       </c>
       <c r="C1199" s="2" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>814432</t>
         </is>
       </c>
       <c r="D1199" s="2" t="inlineStr">
@@ -36431,12 +36431,12 @@
       </c>
       <c r="B1200" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563525VC6</t>
+          <t>KIT4M05563517BVR</t>
         </is>
       </c>
       <c r="C1200" s="2" t="inlineStr">
         <is>
-          <t>814458</t>
+          <t>814438</t>
         </is>
       </c>
       <c r="D1200" s="2" t="inlineStr">
@@ -36461,12 +36461,12 @@
       </c>
       <c r="B1201" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563527J4C</t>
+          <t>KIT4M05563518ZJD</t>
         </is>
       </c>
       <c r="C1201" s="2" t="inlineStr">
         <is>
-          <t>814452</t>
+          <t>814451</t>
         </is>
       </c>
       <c r="D1201" s="2" t="inlineStr">
@@ -36491,12 +36491,12 @@
       </c>
       <c r="B1202" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563536BPJ</t>
+          <t>KIT4M05563520SH2</t>
         </is>
       </c>
       <c r="C1202" s="2" t="inlineStr">
         <is>
-          <t>814466</t>
+          <t>814478</t>
         </is>
       </c>
       <c r="D1202" s="2" t="inlineStr">
@@ -36521,12 +36521,12 @@
       </c>
       <c r="B1203" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563538RZV</t>
+          <t>KIT4M05563521ZSX</t>
         </is>
       </c>
       <c r="C1203" s="2" t="inlineStr">
         <is>
-          <t>814459</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="D1203" s="2" t="inlineStr">
@@ -36551,12 +36551,12 @@
       </c>
       <c r="B1204" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563549RSR</t>
+          <t>KIT4M05563525VC6</t>
         </is>
       </c>
       <c r="C1204" s="2" t="inlineStr">
         <is>
-          <t>814483</t>
+          <t>814458</t>
         </is>
       </c>
       <c r="D1204" s="2" t="inlineStr">
@@ -36581,12 +36581,12 @@
       </c>
       <c r="B1205" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563554WCW</t>
+          <t>KIT4M05563536BPJ</t>
         </is>
       </c>
       <c r="C1205" s="2" t="inlineStr">
         <is>
-          <t>814444</t>
+          <t>814466</t>
         </is>
       </c>
       <c r="D1205" s="2" t="inlineStr">
@@ -36611,12 +36611,12 @@
       </c>
       <c r="B1206" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556355588P</t>
+          <t>KIT4M05563538RZV</t>
         </is>
       </c>
       <c r="C1206" s="2" t="inlineStr">
         <is>
-          <t>814455</t>
+          <t>814459</t>
         </is>
       </c>
       <c r="D1206" s="2" t="inlineStr">
@@ -36641,12 +36641,12 @@
       </c>
       <c r="B1207" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563560225</t>
+          <t>KIT4M05563549RSR</t>
         </is>
       </c>
       <c r="C1207" s="2" t="inlineStr">
         <is>
-          <t>814454</t>
+          <t>814483</t>
         </is>
       </c>
       <c r="D1207" s="2" t="inlineStr">
@@ -36671,12 +36671,12 @@
       </c>
       <c r="B1208" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563571G8W</t>
+          <t>KIT4M05563554WCW</t>
         </is>
       </c>
       <c r="C1208" s="2" t="inlineStr">
         <is>
-          <t>814481</t>
+          <t>814444</t>
         </is>
       </c>
       <c r="D1208" s="2" t="inlineStr">
@@ -36701,12 +36701,12 @@
       </c>
       <c r="B1209" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563574ZBN</t>
+          <t>KIT4M0556355588P</t>
         </is>
       </c>
       <c r="C1209" s="2" t="inlineStr">
         <is>
-          <t>814453</t>
+          <t>814455</t>
         </is>
       </c>
       <c r="D1209" s="2" t="inlineStr">
@@ -36731,12 +36731,12 @@
       </c>
       <c r="B1210" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635779MM</t>
+          <t>KIT4M05563571G8W</t>
         </is>
       </c>
       <c r="C1210" s="2" t="inlineStr">
         <is>
-          <t>814487</t>
+          <t>814481</t>
         </is>
       </c>
       <c r="D1210" s="2" t="inlineStr">
@@ -36761,12 +36761,12 @@
       </c>
       <c r="B1211" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563586ZTR</t>
+          <t>KIT4M05563574ZBN</t>
         </is>
       </c>
       <c r="C1211" s="2" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>814453</t>
         </is>
       </c>
       <c r="D1211" s="2" t="inlineStr">
@@ -36791,12 +36791,12 @@
       </c>
       <c r="B1212" s="2" t="inlineStr">
         <is>
-          <t>KIT4M0556358988Z</t>
+          <t>KIT4M05563586ZTR</t>
         </is>
       </c>
       <c r="C1212" s="2" t="inlineStr">
         <is>
-          <t>814484</t>
+          <t>814445</t>
         </is>
       </c>
       <c r="D1212" s="2" t="inlineStr">
@@ -36821,12 +36821,12 @@
       </c>
       <c r="B1213" s="2" t="inlineStr">
         <is>
-          <t>KIT4M055635979XD</t>
+          <t>KIT4M0556358988Z</t>
         </is>
       </c>
       <c r="C1213" s="2" t="inlineStr">
         <is>
-          <t>814441</t>
+          <t>814484</t>
         </is>
       </c>
       <c r="D1213" s="2" t="inlineStr">
@@ -36851,12 +36851,12 @@
       </c>
       <c r="B1214" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05563610HM2</t>
+          <t>KIT4M055635979XD</t>
         </is>
       </c>
       <c r="C1214" s="2" t="inlineStr">
         <is>
-          <t>814486</t>
+          <t>814441</t>
         </is>
       </c>
       <c r="D1214" s="2" t="inlineStr">
@@ -36881,12 +36881,12 @@
       </c>
       <c r="B1215" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996395ZF</t>
+          <t>KIT4M05563610HM2</t>
         </is>
       </c>
       <c r="C1215" s="2" t="inlineStr">
         <is>
-          <t>816268</t>
+          <t>814486</t>
         </is>
       </c>
       <c r="D1215" s="2" t="inlineStr">
@@ -36911,12 +36911,12 @@
       </c>
       <c r="B1216" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799678R5P</t>
+          <t>KIT4M057996395ZF</t>
         </is>
       </c>
       <c r="C1216" s="2" t="inlineStr">
         <is>
-          <t>816281</t>
+          <t>816268</t>
         </is>
       </c>
       <c r="D1216" s="2" t="inlineStr">
@@ -36941,12 +36941,12 @@
       </c>
       <c r="B1217" s="2" t="inlineStr">
         <is>
-          <t>KIT4M057996885ZV</t>
+          <t>KIT4M05799678R5P</t>
         </is>
       </c>
       <c r="C1217" s="2" t="inlineStr">
         <is>
-          <t>816269</t>
+          <t>816281</t>
         </is>
       </c>
       <c r="D1217" s="2" t="inlineStr">
@@ -36971,12 +36971,12 @@
       </c>
       <c r="B1218" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05799733FPK</t>
+          <t>KIT4M057996885ZV</t>
         </is>
       </c>
       <c r="C1218" s="2" t="inlineStr">
         <is>
-          <t>816286</t>
+          <t>816269</t>
         </is>
       </c>
       <c r="D1218" s="2" t="inlineStr">
@@ -37001,12 +37001,12 @@
       </c>
       <c r="B1219" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872486FXZ</t>
+          <t>KIT4M05799733FPK</t>
         </is>
       </c>
       <c r="C1219" s="2" t="inlineStr">
         <is>
-          <t>816088</t>
+          <t>816286</t>
         </is>
       </c>
       <c r="D1219" s="2" t="inlineStr">
@@ -37031,12 +37031,12 @@
       </c>
       <c r="B1220" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872496MW6</t>
+          <t>KIT4M05872486FXZ</t>
         </is>
       </c>
       <c r="C1220" s="2" t="inlineStr">
         <is>
-          <t>816206</t>
+          <t>816088</t>
         </is>
       </c>
       <c r="D1220" s="2" t="inlineStr">
@@ -37061,12 +37061,12 @@
       </c>
       <c r="B1221" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872498PP4</t>
+          <t>KIT4M05872496MW6</t>
         </is>
       </c>
       <c r="C1221" s="2" t="inlineStr">
         <is>
-          <t>816104</t>
+          <t>816206</t>
         </is>
       </c>
       <c r="D1221" s="2" t="inlineStr">
@@ -37091,12 +37091,12 @@
       </c>
       <c r="B1222" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872500684</t>
+          <t>KIT4M05872498PP4</t>
         </is>
       </c>
       <c r="C1222" s="2" t="inlineStr">
         <is>
-          <t>816081</t>
+          <t>816104</t>
         </is>
       </c>
       <c r="D1222" s="2" t="inlineStr">
@@ -37121,12 +37121,12 @@
       </c>
       <c r="B1223" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725047FZ</t>
+          <t>KIT4M05872500684</t>
         </is>
       </c>
       <c r="C1223" s="2" t="inlineStr">
         <is>
-          <t>816289</t>
+          <t>816081</t>
         </is>
       </c>
       <c r="D1223" s="2" t="inlineStr">
@@ -37151,12 +37151,12 @@
       </c>
       <c r="B1224" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872506TTB</t>
+          <t>KIT4M058725047FZ</t>
         </is>
       </c>
       <c r="C1224" s="2" t="inlineStr">
         <is>
-          <t>816082</t>
+          <t>816289</t>
         </is>
       </c>
       <c r="D1224" s="2" t="inlineStr">
@@ -37181,12 +37181,12 @@
       </c>
       <c r="B1225" s="2" t="inlineStr">
         <is>
-          <t>KIT4M058725108K2</t>
+          <t>KIT4M05872506TTB</t>
         </is>
       </c>
       <c r="C1225" s="2" t="inlineStr">
         <is>
-          <t>816287</t>
+          <t>816082</t>
         </is>
       </c>
       <c r="D1225" s="2" t="inlineStr">
@@ -37211,12 +37211,12 @@
       </c>
       <c r="B1226" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872511F6P</t>
+          <t>KIT4M058725108K2</t>
         </is>
       </c>
       <c r="C1226" s="2" t="inlineStr">
         <is>
-          <t>816090</t>
+          <t>816287</t>
         </is>
       </c>
       <c r="D1226" s="2" t="inlineStr">
@@ -37241,12 +37241,12 @@
       </c>
       <c r="B1227" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872513F7N</t>
+          <t>KIT4M05872511F6P</t>
         </is>
       </c>
       <c r="C1227" s="2" t="inlineStr">
         <is>
-          <t>816161</t>
+          <t>816090</t>
         </is>
       </c>
       <c r="D1227" s="2" t="inlineStr">
@@ -37271,12 +37271,12 @@
       </c>
       <c r="B1228" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872515PJT</t>
+          <t>KIT4M05872513F7N</t>
         </is>
       </c>
       <c r="C1228" s="2" t="inlineStr">
         <is>
-          <t>816218</t>
+          <t>816161</t>
         </is>
       </c>
       <c r="D1228" s="2" t="inlineStr">
@@ -37301,12 +37301,12 @@
       </c>
       <c r="B1229" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872517VS2</t>
+          <t>KIT4M05872515PJT</t>
         </is>
       </c>
       <c r="C1229" s="2" t="inlineStr">
         <is>
-          <t>816288</t>
+          <t>816218</t>
         </is>
       </c>
       <c r="D1229" s="2" t="inlineStr">
@@ -37331,12 +37331,12 @@
       </c>
       <c r="B1230" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872518P78</t>
+          <t>KIT4M05872517VS2</t>
         </is>
       </c>
       <c r="C1230" s="2" t="inlineStr">
         <is>
-          <t>816184</t>
+          <t>816288</t>
         </is>
       </c>
       <c r="D1230" s="2" t="inlineStr">
@@ -37361,12 +37361,12 @@
       </c>
       <c r="B1231" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872519KTN</t>
+          <t>KIT4M05872518P78</t>
         </is>
       </c>
       <c r="C1231" s="2" t="inlineStr">
         <is>
-          <t>816084</t>
+          <t>816184</t>
         </is>
       </c>
       <c r="D1231" s="2" t="inlineStr">
@@ -37391,12 +37391,12 @@
       </c>
       <c r="B1232" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872520QJM</t>
+          <t>KIT4M05872519KTN</t>
         </is>
       </c>
       <c r="C1232" s="2" t="inlineStr">
         <is>
-          <t>816078</t>
+          <t>816084</t>
         </is>
       </c>
       <c r="D1232" s="2" t="inlineStr">
@@ -37421,12 +37421,12 @@
       </c>
       <c r="B1233" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872522W7W</t>
+          <t>KIT4M05872520QJM</t>
         </is>
       </c>
       <c r="C1233" s="2" t="inlineStr">
         <is>
-          <t>816217</t>
+          <t>816078</t>
         </is>
       </c>
       <c r="D1233" s="2" t="inlineStr">
@@ -37451,12 +37451,12 @@
       </c>
       <c r="B1234" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872523VVB</t>
+          <t>KIT4M05872522W7W</t>
         </is>
       </c>
       <c r="C1234" s="2" t="inlineStr">
         <is>
-          <t>816215</t>
+          <t>816217</t>
         </is>
       </c>
       <c r="D1234" s="2" t="inlineStr">
@@ -37481,12 +37481,12 @@
       </c>
       <c r="B1235" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872524CFG</t>
+          <t>KIT4M05872523VVB</t>
         </is>
       </c>
       <c r="C1235" s="2" t="inlineStr">
         <is>
-          <t>816205</t>
+          <t>816215</t>
         </is>
       </c>
       <c r="D1235" s="2" t="inlineStr">
@@ -37511,12 +37511,12 @@
       </c>
       <c r="B1236" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872525NP5</t>
+          <t>KIT4M05872524CFG</t>
         </is>
       </c>
       <c r="C1236" s="2" t="inlineStr">
         <is>
-          <t>816213</t>
+          <t>816205</t>
         </is>
       </c>
       <c r="D1236" s="2" t="inlineStr">
@@ -37541,12 +37541,12 @@
       </c>
       <c r="B1237" s="2" t="inlineStr">
         <is>
-          <t>KIT4M05872527QK6</t>
+          <t>KIT4M05872525NP5</t>
         </is>
       </c>
       <c r="C1237" s="2" t="inlineStr">
         <is>
-          <t>816214</t>
+          <t>816213</t>
         </is>
       </c>
       <c r="D1237" s="2" t="inlineStr">
@@ -